--- a/output/contacts_primary.xlsx
+++ b/output/contacts_primary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR61"/>
+  <dimension ref="A1:AV62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,19 +601,19 @@
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
+          <t>role_evidence</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
           <t>resolution_reason</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>search_fingerprint</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>role_evidence</t>
-        </is>
-      </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>verification_review_required</t>
@@ -626,25 +626,45 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>verification_schema_version</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>identity_name_verified</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>identity_specialty_verified</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>identity_evidence</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
           <t>candidate_rank</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>shared_contact</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>send_eligible</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>personalization_safe</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>outreach_scope</t>
         </is>
@@ -769,7 +789,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>1.981130226599622e+16</v>
+        <v>5.943390679798868e+16</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -790,19 +810,23 @@
         <v>0</v>
       </c>
       <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV2" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -927,7 +951,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>1.605950830338262e+16</v>
+        <v>4.817852491014786e+16</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -948,19 +972,23 @@
         <v>0</v>
       </c>
       <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV3" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -1085,7 +1113,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>1.605950830338262e+16</v>
+        <v>4.817852491014786e+16</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1106,19 +1134,23 @@
         <v>0</v>
       </c>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV4" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -1246,7 +1278,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>1.605950830338262e+16</v>
+        <v>4.817852491014786e+16</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1267,19 +1299,23 @@
         <v>0</v>
       </c>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV5" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -1405,7 +1441,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>1.605950830338262e+16</v>
+        <v>4.817852491014786e+16</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1426,19 +1462,23 @@
         <v>0</v>
       </c>
       <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV6" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -1563,7 +1603,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>1.97655486810863e+16</v>
+        <v>5.929664604325891e+16</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1584,19 +1624,23 @@
         <v>0</v>
       </c>
       <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV7" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -1721,7 +1765,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>1.97655486810863e+16</v>
+        <v>5.929664604325891e+16</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1742,19 +1786,23 @@
         <v>0</v>
       </c>
       <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV8" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -1879,7 +1927,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>1.854545308348838e+16</v>
+        <v>5.563635925046515e+16</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -1900,19 +1948,23 @@
         <v>0</v>
       </c>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV9" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -2037,7 +2089,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>1.607495011933712e+16</v>
+        <v>4.822485035801138e+16</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2058,19 +2110,23 @@
         <v>0</v>
       </c>
       <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR10" t="inlineStr">
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV10" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -2195,7 +2251,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>1.60747594983526e+16</v>
+        <v>4.822427849505779e+16</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2216,19 +2272,23 @@
         <v>0</v>
       </c>
       <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV11" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -2353,7 +2413,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>1.981808057487177e+16</v>
+        <v>5.945424172461531e+16</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2374,19 +2434,23 @@
         <v>0</v>
       </c>
       <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR12" t="inlineStr">
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV12" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -2511,7 +2575,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>1.607495011933715e+16</v>
+        <v>4.822485035801146e+16</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2532,19 +2596,23 @@
         <v>0</v>
       </c>
       <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR13" t="inlineStr">
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV13" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -2669,7 +2737,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>1.97655486810863e+16</v>
+        <v>5.929664604325891e+16</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2690,19 +2758,23 @@
         <v>0</v>
       </c>
       <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR14" t="inlineStr">
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV14" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -2827,7 +2899,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>1.605950830338262e+16</v>
+        <v>4.817852491014786e+16</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2848,19 +2920,23 @@
         <v>0</v>
       </c>
       <c r="AM15" t="inlineStr"/>
-      <c r="AN15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR15" t="inlineStr">
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV15" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -2985,7 +3061,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>1.605950830338262e+16</v>
+        <v>4.817852491014786e+16</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3006,19 +3082,23 @@
         <v>0</v>
       </c>
       <c r="AM16" t="inlineStr"/>
-      <c r="AN16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR16" t="inlineStr">
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV16" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -3143,7 +3223,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>1.605950830338262e+16</v>
+        <v>4.817852491014786e+16</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3164,19 +3244,23 @@
         <v>0</v>
       </c>
       <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="n">
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="n">
         <v>2</v>
       </c>
-      <c r="AO17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR17" t="inlineStr">
+      <c r="AS17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV17" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -3301,7 +3385,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>1.607495011933715e+16</v>
+        <v>4.822485035801146e+16</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3322,19 +3406,23 @@
         <v>0</v>
       </c>
       <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR18" t="inlineStr">
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV18" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -3459,7 +3547,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>1.60747594983526e+16</v>
+        <v>4.822427849505779e+16</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3480,19 +3568,23 @@
         <v>0</v>
       </c>
       <c r="AM19" t="inlineStr"/>
-      <c r="AN19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="inlineStr">
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -3617,7 +3709,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>1.606478265601749e+16</v>
+        <v>4.819434796805247e+16</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3638,19 +3730,23 @@
         <v>0</v>
       </c>
       <c r="AM20" t="inlineStr"/>
-      <c r="AN20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR20" t="inlineStr">
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV20" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -3775,7 +3871,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>1.605950830338262e+16</v>
+        <v>4.817852491014786e+16</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3796,19 +3892,23 @@
         <v>0</v>
       </c>
       <c r="AM21" t="inlineStr"/>
-      <c r="AN21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR21" t="inlineStr">
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV21" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -3933,7 +4033,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>1.605950830338262e+16</v>
+        <v>4.817852491014786e+16</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -3954,19 +4054,23 @@
         <v>0</v>
       </c>
       <c r="AM22" t="inlineStr"/>
-      <c r="AN22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR22" t="inlineStr">
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV22" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -4091,7 +4195,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>1.524102750666068e+16</v>
+        <v>4.572308251998205e+16</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4112,19 +4216,23 @@
         <v>0</v>
       </c>
       <c r="AM23" t="inlineStr"/>
-      <c r="AN23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR23" t="inlineStr">
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV23" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -4249,7 +4357,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>1.524102750666068e+16</v>
+        <v>4.572308251998205e+16</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4270,19 +4378,23 @@
         <v>0</v>
       </c>
       <c r="AM24" t="inlineStr"/>
-      <c r="AN24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR24" t="inlineStr">
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -4407,7 +4519,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>1.486991509572465e+16</v>
+        <v>4.460974528717395e+16</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4428,19 +4540,23 @@
         <v>0</v>
       </c>
       <c r="AM25" t="inlineStr"/>
-      <c r="AN25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR25" t="inlineStr">
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV25" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -4565,7 +4681,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>1.486991509572465e+16</v>
+        <v>4.460974528717395e+16</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4586,19 +4702,23 @@
         <v>0</v>
       </c>
       <c r="AM26" t="inlineStr"/>
-      <c r="AN26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="inlineStr">
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -4724,7 +4844,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>1.486991509572465e+16</v>
+        <v>4.460974528717395e+16</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4745,19 +4865,23 @@
         <v>0</v>
       </c>
       <c r="AM27" t="inlineStr"/>
-      <c r="AN27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="inlineStr">
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -4882,7 +5006,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>1.486991509572465e+16</v>
+        <v>4.460974528717395e+16</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4903,19 +5027,23 @@
         <v>0</v>
       </c>
       <c r="AM28" t="inlineStr"/>
-      <c r="AN28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR28" t="inlineStr">
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV28" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -5040,7 +5168,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>1.486991509572465e+16</v>
+        <v>4.460974528717395e+16</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5061,19 +5189,23 @@
         <v>0</v>
       </c>
       <c r="AM29" t="inlineStr"/>
-      <c r="AN29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR29" t="inlineStr">
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV29" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -5198,7 +5330,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>1.981130226599622e+16</v>
+        <v>5.943390679798868e+16</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5219,19 +5351,23 @@
         <v>0</v>
       </c>
       <c r="AM30" t="inlineStr"/>
-      <c r="AN30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR30" t="inlineStr">
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr"/>
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV30" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -5246,7 +5382,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>אופיר אלמסי</t>
+          <t>אוהד חורי</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5277,7 +5413,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>ofiral@bgu.ac.il</t>
+          <t>ohadho@clalit.org.il</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -5290,7 +5426,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -5300,17 +5436,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>بحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان אופיר אלמסי ד"ר אופיר אלמסי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ofiral@bgu.ac.il Cookies Settings</t>
+          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>"אופיר אלמסי"</t>
+          <t>"אוהד חורי" יילוד site:clalit.co.il</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -5327,36 +5463,36 @@
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-09-04T13:52:28.665114+00:00</t>
+          <t>2026-09-09T23:21:42.073181+00:00</t>
         </is>
       </c>
       <c r="W31" t="n">
+        <v>8</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA31" t="n">
         <v>2</v>
       </c>
-      <c r="X31" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1</v>
-      </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/ofiral/", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/almasi-o.aspx", "https://www.bgu.ac.il/ar/people/ofiral/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx", "https://www.doctorita.co.il/experts/94233", "https://www.ha-makom.co.il/author/vhdcvry/", "https://foody.co.il/author/ohad/", "https://knowmore.co.il/doctors/אוהד-חורי-2/", "https://stage.ha-makom.co.il/author/vhdcvry/", "https://www.facebook.com/YoldotBeilinson/videos/%D7%9E%D7%94-%D7%96%D7%95-%D7%9C%D7%99%D7%93%D7%AA-vbac-%D7%A9%D7%9B%D7%95%D7%9C%D7%9F-%D7%9E%D7%93%D7%91%D7%A8%D7%95%D7%AA-%D7%A2%D7%9C%D7%99%D7%94-%D7%A2%D7%95%D7%A9%D7%99%D7%9D-%D7%9C%D7%9B%D7%9F-%D7%A1%D7%93%D7%A8-%D7%91%D7%9E%D7%95%D7%A9%D7%92%D7%99%D7%9D-%D7%A2%D7%9D-%D7%93%D7%A8-%D7%90%D7%95%D7%94%D7%93-%D7%97%D7%95%D7%A8%D7%99-%D7%A9%D7%9B%D7%90%D7%9F-%D7%9B%D7%93%D7%99/1754039901764363/"]</t>
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>1.606459203503928e+16</v>
+        <v>4.81943479680715e+16</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5367,29 +5503,41 @@
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr"/>
       <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="inlineStr"/>
-      <c r="AL31" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL31" t="inlineStr"/>
       <c r="AM31" t="inlineStr"/>
       <c r="AN31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP31" t="b">
         <v>1</v>
       </c>
-      <c r="AQ31" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR31" t="inlineStr">
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
+        </is>
+      </c>
+      <c r="AR31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV31" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -5404,7 +5552,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>אורנה רייכמן</t>
+          <t>אופיר אלמסי</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5435,7 +5583,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>oreich@szmc.org.il</t>
+          <t>ofiral@bgu.ac.il</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -5448,7 +5596,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
+          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -5458,12 +5606,12 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t xml:space="preserve">אזור אישי רופאים בשערי צדק ד"ר אורנה  רייכמן מנהלת יולדות א' Dr. Orna  Reichman התמחות: גינקולוגיה ויילוד תת התמחות: מחלות שפירות של העריה והלדן הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית משרד 02-6666708 משרד: 02-6666708 oreich@szmc.org.il oreich@szmc.org.il לימודים והכשרה תואר ראשון במדעי החיים באוניברסיטה העברית בירושלים בהצטיינות - 1993 לימודי הרפואה בבית ספר לרפואה של האוניברסיטה העברית הדסה - 1999 ההתמחות במיילדות וגניקולוגיה במרכז </t>
+          <t>بحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان אופיר אלמסי ד"ר אופיר אלמסי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ofiral@bgu.ac.il Cookies Settings</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>"אורנה רייכמן"</t>
+          <t>"אופיר אלמסי"</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -5485,36 +5633,36 @@
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-09-04T13:56:16.031154+00:00</t>
+          <t>2026-09-04T13:52:28.665114+00:00</t>
         </is>
       </c>
       <c r="W32" t="n">
         <v>2</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z32" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AA32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>["https://www.infomed.co.il/experts/149541/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A8%D7%99%D7%99%D7%9B%D7%9E%D7%9F-%D7%90%D7%95%D7%A8%D7%A0%D7%94/", "https://docsrated.com/doctors/אורנה-רייכמן", "https://www.doctorita.co.il/experts/95406", "https://drtor.co.il/doctor/23937", "https://drtor.co.il/cdn-cgi/l/email-protection#8cefe3e2f8edeff8cce8fef8e3fea2efe3a2e5e0", "https://www.beok.co.il/doctors/Doctors-1340/", "https://www.szmc.org.il/doctors/reichman-orna/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://drtor.co.il/cdn-cgi/l/email-protection#3b5854554f5a584f7b5f494f5449155854155257"]</t>
+          <t>["https://www.bgu.ac.il/people/ofiral/", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/almasi-o.aspx", "https://www.bgu.ac.il/ar/people/ofiral/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>1.606459203503928e+16</v>
+        <v>4.819377610511784e+16</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5525,7 +5673,7 @@
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
+          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr"/>
@@ -5535,19 +5683,23 @@
         <v>0</v>
       </c>
       <c r="AM32" t="inlineStr"/>
-      <c r="AN32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR32" t="inlineStr">
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV32" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -5562,7 +5714,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ארנון סמואלוב</t>
+          <t>אורנה רייכמן</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5593,7 +5745,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>smuelof@szmc.org.il</t>
+          <t>oreich@szmc.org.il</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -5606,7 +5758,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
+          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -5616,12 +5768,12 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>ופ' ארנון  סמואלוב רופא בכיר Prof. Arnon  Samueloff התמחות: גינקולוגיה ויילוד תת התמחות: מיילדות וסיבוכי הריון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 02-6666656 מחלקה: 02-6666656 smuelof@szmc.org.il smuelof@szmc.org.il נסיון מקצועי התמחות ברפואת האם והעובר, סן אנטוניו, ארה"ב רופא בכיר, מחלקת נשים ויולדות, המרכז הרפואי הדסה מנהל, מרפאת היריון בסיכון, קופת חולים לאומית מנהל, מרפאת סוכרת, קופת חולים</t>
+          <t xml:space="preserve">אזור אישי רופאים בשערי צדק ד"ר אורנה  רייכמן מנהלת יולדות א' Dr. Orna  Reichman התמחות: גינקולוגיה ויילוד תת התמחות: מחלות שפירות של העריה והלדן הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית משרד 02-6666708 משרד: 02-6666708 oreich@szmc.org.il oreich@szmc.org.il לימודים והכשרה תואר ראשון במדעי החיים באוניברסיטה העברית בירושלים בהצטיינות - 1993 לימודי הרפואה בבית ספר לרפואה של האוניברסיטה העברית הדסה - 1999 ההתמחות במיילדות וגניקולוגיה במרכז </t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>"ארנון סמואלוב"</t>
+          <t>"אורנה רייכמן"</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -5643,36 +5795,36 @@
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-09-04T14:35:26.198949+00:00</t>
+          <t>2026-09-04T13:56:16.031154+00:00</t>
         </is>
       </c>
       <c r="W33" t="n">
         <v>2</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>["https://docsrated.com/doctors/ארנון-סמואלוב", "https://www.infomed.co.il/experts/93587/", "https://www.doctorita.co.il/experts/47319", "https://www.beok.co.il/doctors/Doctors-116451/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A1%D7%9E%D7%95%D7%90%D7%9C%D7%95%D7%91-%D7%90%D7%A8%D7%A0%D7%95%D7%9F/", "https://www.szmc.org.il/doctors/samueloff-arnon/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
+          <t>["https://www.infomed.co.il/experts/149541/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A8%D7%99%D7%99%D7%9B%D7%9E%D7%9F-%D7%90%D7%95%D7%A8%D7%A0%D7%94/", "https://docsrated.com/doctors/אורנה-רייכמן", "https://www.doctorita.co.il/experts/95406", "https://drtor.co.il/doctor/23937", "https://drtor.co.il/cdn-cgi/l/email-protection#8cefe3e2f8edeff8cce8fef8e3fea2efe3a2e5e0", "https://www.beok.co.il/doctors/Doctors-1340/", "https://www.szmc.org.il/doctors/reichman-orna/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://drtor.co.il/cdn-cgi/l/email-protection#3b5854554f5a584f7b5f494f5449155854155257"]</t>
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>1.606459203503928e+16</v>
+        <v>4.819377610511784e+16</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5683,7 +5835,7 @@
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
+          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr"/>
@@ -5693,19 +5845,23 @@
         <v>0</v>
       </c>
       <c r="AM33" t="inlineStr"/>
-      <c r="AN33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR33" t="inlineStr">
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr"/>
+      <c r="AQ33" t="inlineStr"/>
+      <c r="AR33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV33" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -5720,7 +5876,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>גלי פריאנטה</t>
+          <t>ארנון סמואלוב</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5751,7 +5907,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>galipa@bgu.ac.il</t>
+          <t>smuelof@szmc.org.il</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -5764,7 +5920,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
+          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -5774,12 +5930,12 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>ث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان גלי פריאנטה פרופ' גלי פריאנטה Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section galipa@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0001-6484-3769 Orcid Number Cookies Settings</t>
+          <t>ופ' ארנון  סמואלוב רופא בכיר Prof. Arnon  Samueloff התמחות: גינקולוגיה ויילוד תת התמחות: מיילדות וסיבוכי הריון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 02-6666656 מחלקה: 02-6666656 smuelof@szmc.org.il smuelof@szmc.org.il נסיון מקצועי התמחות ברפואת האם והעובר, סן אנטוניו, ארה"ב רופא בכיר, מחלקת נשים ויולדות, המרכז הרפואי הדסה מנהל, מרפאת היריון בסיכון, קופת חולים לאומית מנהל, מרפאת סוכרת, קופת חולים</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>"גלי פריאנטה"</t>
+          <t>"ארנון סמואלוב"</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -5801,36 +5957,36 @@
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-09-03T23:09:10.396904+00:00</t>
+          <t>2026-09-04T14:35:26.198949+00:00</t>
         </is>
       </c>
       <c r="W34" t="n">
         <v>2</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
         <v>6</v>
       </c>
       <c r="Z34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/galipa/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-%D7%92%D7%9C%D7%99/", "https://medpage.co.il/doctors/%D7%92%D7%9C%D7%99-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-25448/", "https://www.doctorita.co.il/experts/131973", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/pariente-g.aspx", "https://www.bgu.ac.il/ar/people/galipa/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://docsrated.com/doctors/ארנון-סמואלוב", "https://www.infomed.co.il/experts/93587/", "https://www.doctorita.co.il/experts/47319", "https://www.beok.co.il/doctors/Doctors-116451/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A1%D7%9E%D7%95%D7%90%D7%9C%D7%95%D7%91-%D7%90%D7%A8%D7%A0%D7%95%D7%9F/", "https://www.szmc.org.il/doctors/samueloff-arnon/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>1.605950830338262e+16</v>
+        <v>4.819377610511784e+16</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5841,7 +5997,7 @@
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
+          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr"/>
@@ -5851,19 +6007,23 @@
         <v>0</v>
       </c>
       <c r="AM34" t="inlineStr"/>
-      <c r="AN34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR34" t="inlineStr">
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr"/>
+      <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV34" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -5878,7 +6038,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ד"ר ברוך יואב</t>
+          <t>גלי פריאנטה</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5898,18 +6058,18 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>ima</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>yoavb@tlvmc.gov.il</t>
+          <t>galipa@bgu.ac.il</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -5922,7 +6082,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
+          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5932,12 +6092,12 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>י לאורוגינקולוגיה ורצפת אגן שטחי התעניינות ועיסוק מיוחדים ניתוחים וגינאליים וזעיר פולשניים לצניחת אברי האגן טיפול תרופתי וכירורגי לדליפת שתן מרפאת ערייה וצוואר הרחם אבחון וטיפול בקונדילומות ונגעים טרום ממאירים יצירת קשר yoavb@tlvmc.gov.il יחידות רפואיות אורוגינקולוגיה ורצפת האגן רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות נעים להכיר, ​ד"ר יואב ברוך איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציונ</t>
+          <t>ث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان גלי פריאנטה פרופ' גלי פריאנטה Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section galipa@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0001-6484-3769 Orcid Number Cookies Settings</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>"ברוך יואב"</t>
+          <t>"גלי פריאנטה"</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -5954,25 +6114,25 @@
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-09-05T00:14:33.719515+00:00</t>
+          <t>2026-09-03T23:09:10.396904+00:00</t>
         </is>
       </c>
       <c r="W35" t="n">
         <v>2</v>
       </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
         <v>6</v>
       </c>
       <c r="Z35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA35" t="n">
         <v>1</v>
@@ -5984,11 +6144,11 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345", "https://soundcloud.com/wx8fnfybplpt", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A-%D7%91%D7%A8%D7%95%D7%9A/pfbid02DHSfATmK3MDpizZrgGTLc9ZAvZHXUsR9pSCjhd6pmWqSMFvq1BwehNeHCARNitMol/", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/pfbid02BMPnQXQYXt6vzctmybagMUp3nWACPxhE1LqhYeJYs1fVgXWA6B1cK2Z9VpRJ8cJRl/", "https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/", "https://pubmed.ncbi.nlm.nih.gov/?term=yoav+baruch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000546", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/61559143005435/", "https://www.infomed.co.il/experts/151203/", "https://www.yoavbaruch.com/", "https://www.yoavbaruch.com/about-6", "https://theindex.co.il/phone/ברוך-יואב-0777573393/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000504"]</t>
+          <t>["https://www.bgu.ac.il/people/galipa/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-%D7%92%D7%9C%D7%99/", "https://medpage.co.il/doctors/%D7%92%D7%9C%D7%99-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-25448/", "https://www.doctorita.co.il/experts/131973", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/pariente-g.aspx", "https://www.bgu.ac.il/ar/people/galipa/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>1.854771251978023e+16</v>
+        <v>4.817852491014786e+16</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -5999,7 +6159,7 @@
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
+          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr"/>
@@ -6009,19 +6169,23 @@
         <v>0</v>
       </c>
       <c r="AM35" t="inlineStr"/>
-      <c r="AN35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR35" t="inlineStr">
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
+      <c r="AP35" t="inlineStr"/>
+      <c r="AQ35" t="inlineStr"/>
+      <c r="AR35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV35" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -6036,7 +6200,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ד"ר צוקר נפתלי</t>
+          <t>ד"ר ברוך יואב</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6056,7 +6220,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -6067,7 +6231,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>drnzuker@arad-medical.co.il</t>
+          <t>yoavb@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -6080,7 +6244,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://www.arad-medical.co.il/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -6090,12 +6254,12 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t xml:space="preserve"> בי"ח אסף הרופא, עבר השתלמות מעמיקה בכירורגיה גניקולוגית ואנדסקופית. כמוכן, גניקולוג בכיר בקופות החולים מכבי ולאומית. קרא עוד עלינו « לפרטים נוספים ולקביעת תור השאר פרטים ונחזור אליך בהקדם! ☎ 077-8037837 | 077-9966036 ✉ drnzuker@arad-medical.co.il שם מלא: מייל: טלפון: שלח © ד"ר נפתלי צוקר — כל הזכויות שמורות אתר זה נבנה ועוצב ע"י קידום פלוס - בניית אתרים</t>
+          <t>י לאורוגינקולוגיה ורצפת אגן שטחי התעניינות ועיסוק מיוחדים ניתוחים וגינאליים וזעיר פולשניים לצניחת אברי האגן טיפול תרופתי וכירורגי לדליפת שתן מרפאת ערייה וצוואר הרחם אבחון וטיפול בקונדילומות ונגעים טרום ממאירים יצירת קשר yoavb@tlvmc.gov.il יחידות רפואיות אורוגינקולוגיה ורצפת האגן רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות נעים להכיר, ​ד"ר יואב ברוך איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציונ</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>"צוקר נפתלי"</t>
+          <t>"ברוך יואב"</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -6112,25 +6276,25 @@
         <v>1</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-09-03T20:26:24.789692+00:00</t>
+          <t>2026-09-05T00:14:33.719515+00:00</t>
         </is>
       </c>
       <c r="W36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X36" t="n">
         <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA36" t="n">
         <v>1</v>
@@ -6142,11 +6306,11 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=JM/xPUEkhEzRgBuX3T9AYqhAJkFmVBaeb30sdIDAjgJqc6t/hlXwF9+305eagC9MR2dwestiB5JmwYwMLOCteQ==", "https://doctors.assuta.co.il/doctor/naftaly-zuker-15805", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=AsbND281GonWNafC65Z5in+5Uof0vMwxuFwCtAAhKp6HNUz+Imt4aFWEpjB1dVuW0TI9YD98xqlKyretPdEuvw==", "https://www.arad-medical.co.il/", "http://www.kidumplus.co.il/", "https://www.arad-medical.co.il/contact", "https://www.arad-medical.co.il/about-us", "https://www.doctorim.co.il/s/doctor-21560/דר-נפתלי-צוקר/מומחה-יילוד-וגניקולוגיה", "https://www.infomed.co.il/experts/83793/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345", "https://soundcloud.com/wx8fnfybplpt", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A-%D7%91%D7%A8%D7%95%D7%9A/pfbid02DHSfATmK3MDpizZrgGTLc9ZAvZHXUsR9pSCjhd6pmWqSMFvq1BwehNeHCARNitMol/", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/pfbid02BMPnQXQYXt6vzctmybagMUp3nWACPxhE1LqhYeJYs1fVgXWA6B1cK2Z9VpRJ8cJRl/", "https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/", "https://pubmed.ncbi.nlm.nih.gov/?term=yoav+baruch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000546", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/61559143005435/", "https://www.infomed.co.il/experts/151203/", "https://www.yoavbaruch.com/", "https://www.yoavbaruch.com/about-6", "https://theindex.co.il/phone/ברוך-יואב-0777573393/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000504"]</t>
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>1.97655486810863e+16</v>
+        <v>5.56431375593407e+16</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6157,7 +6321,7 @@
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>https://www.arad-medical.co.il/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr"/>
@@ -6167,19 +6331,23 @@
         <v>0</v>
       </c>
       <c r="AM36" t="inlineStr"/>
-      <c r="AN36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR36" t="inlineStr">
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr"/>
+      <c r="AQ36" t="inlineStr"/>
+      <c r="AR36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV36" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -6194,7 +6362,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ד"ר רטן גלעד</t>
+          <t>ד"ר צוקר נפתלי</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6214,7 +6382,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -6225,7 +6393,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>giladr@tlvmc.gov.il</t>
+          <t>drnzuker@arad-medical.co.il</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -6238,7 +6406,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
+          <t>https://www.arad-medical.co.il/</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -6248,12 +6416,12 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t xml:space="preserve">ח "ליס" ליולדות ונשים איכילוב צוות איכילוב גלעד רטן בדיקת היסטרוסקופיה - ד"ר גלעד רטן | ליס, איכילוב ד"ר גלעד רטן על תסמונת אשרמן, סטטוסקופ ערוץ 13 פרק 18 | פרופ' יריב יוגב ופרופ' גלעד רטן | בדיקת היסטרוסקופיה יצירת קשר giladr@tlvmc.gov.il יחידות רפואיות היסטרוסקופיה אבחנתית / טיפולית רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א </t>
+          <t xml:space="preserve"> בי"ח אסף הרופא, עבר השתלמות מעמיקה בכירורגיה גניקולוגית ואנדסקופית. כמוכן, גניקולוג בכיר בקופות החולים מכבי ולאומית. קרא עוד עלינו « לפרטים נוספים ולקביעת תור השאר פרטים ונחזור אליך בהקדם! ☎ 077-8037837 | 077-9966036 ✉ drnzuker@arad-medical.co.il שם מלא: מייל: טלפון: שלח © ד"ר נפתלי צוקר — כל הזכויות שמורות אתר זה נבנה ועוצב ע"י קידום פלוס - בניית אתרים</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>"רטן גלעד"</t>
+          <t>"צוקר נפתלי"</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -6275,14 +6443,14 @@
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-09-03T21:08:14.761438+00:00</t>
+          <t>2026-09-03T20:26:24.789692+00:00</t>
         </is>
       </c>
       <c r="W37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
         <v>4</v>
@@ -6300,11 +6468,11 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F/", "https://dr-gilad.infomed.co.il/", "https://www.facebook.com/TLVMDC/posts/%D7%95%D7%95%D7%90%D7%95-%D7%9E%D7%AA%D7%A8%D7%92%D7%A9%D7%99%D7%9D-%D7%9C%D7%94%D7%9B%D7%99%D7%A8-%D7%9C%D7%9B%D7%9D-%D7%90%D7%AA-%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F-%D7%9E%D7%95%D7%9E%D7%97%D7%94-%D7%91%D7%9B%D7%99%D7%A8-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%A8%D7%A4%D7%95%D7%90%D7%99-tlv_medical_center/1344912312574270/", "https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=JM/xPUEkhEzRgBuX3T9AYqhAJkFmVBaeb30sdIDAjgJqc6t/hlXwF9+305eagC9MR2dwestiB5JmwYwMLOCteQ==", "https://doctors.assuta.co.il/doctor/naftaly-zuker-15805", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=AsbND281GonWNafC65Z5in+5Uof0vMwxuFwCtAAhKp6HNUz+Imt4aFWEpjB1dVuW0TI9YD98xqlKyretPdEuvw==", "https://www.arad-medical.co.il/", "http://www.kidumplus.co.il/", "https://www.arad-medical.co.il/contact", "https://www.arad-medical.co.il/about-us", "https://www.doctorim.co.il/s/doctor-21560/דר-נפתלי-צוקר/מומחה-יילוד-וגניקולוגיה", "https://www.infomed.co.il/experts/83793/"]</t>
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>1.605950830338262e+16</v>
+        <v>5.929664604325891e+16</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6315,7 +6483,7 @@
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
+          <t>https://www.arad-medical.co.il/</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr"/>
@@ -6325,19 +6493,23 @@
         <v>0</v>
       </c>
       <c r="AM37" t="inlineStr"/>
-      <c r="AN37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR37" t="inlineStr">
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
+      <c r="AP37" t="inlineStr"/>
+      <c r="AQ37" t="inlineStr"/>
+      <c r="AR37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV37" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -6352,7 +6524,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>דנה ברבינג-גולדשטיין</t>
+          <t>ד"ר רטן גלעד</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6372,18 +6544,18 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>ima</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>danabr2@clalit.org.il</t>
+          <t>giladr@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -6396,7 +6568,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -6406,17 +6578,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>ד"ר דנה ברבינג גולדשטיין | מרכז רפואי רבין ד"ר דנה ברבינג גולדשטיין מיילדות וגינקולוגיה, גנטיקה רפואית שם: ד"ר דנה ברבינג גולדשטיין דוא"ל: danabr2@clalit.org.il יחידה: מכון רפאל רקנאטי לגנטיקה</t>
+          <t xml:space="preserve">ח "ליס" ליולדות ונשים איכילוב צוות איכילוב גלעד רטן בדיקת היסטרוסקופיה - ד"ר גלעד רטן | ליס, איכילוב ד"ר גלעד רטן על תסמונת אשרמן, סטטוסקופ ערוץ 13 פרק 18 | פרופ' יריב יוגב ופרופ' גלעד רטן | בדיקת היסטרוסקופיה יצירת קשר giladr@tlvmc.gov.il יחידות רפואיות היסטרוסקופיה אבחנתית / טיפולית רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א </t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>"דנה ברבינג גולדשטיין" יילוד site:clalit.co.il</t>
+          <t>"רטן גלעד"</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>search_snippet</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -6433,36 +6605,36 @@
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-09-08T13:48:01.035843+00:00</t>
+          <t>2026-09-03T21:08:14.761438+00:00</t>
         </is>
       </c>
       <c r="W38" t="n">
+        <v>2</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
         <v>4</v>
       </c>
-      <c r="X38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1</v>
-      </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA38" t="n">
         <v>1</v>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>ddgs:yahoo+ddgs:bing</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F/", "https://dr-gilad.infomed.co.il/", "https://www.facebook.com/TLVMDC/posts/%D7%95%D7%95%D7%90%D7%95-%D7%9E%D7%AA%D7%A8%D7%92%D7%A9%D7%99%D7%9D-%D7%9C%D7%94%D7%9B%D7%99%D7%A8-%D7%9C%D7%9B%D7%9D-%D7%90%D7%AA-%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F-%D7%9E%D7%95%D7%9E%D7%97%D7%94-%D7%91%D7%9B%D7%99%D7%A8-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%A8%D7%A4%D7%95%D7%90%D7%99-tlv_medical_center/1344912312574270/", "https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>1.606478265601749e+16</v>
+        <v>4.817852491014786e+16</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6473,7 +6645,7 @@
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr"/>
@@ -6483,19 +6655,23 @@
         <v>0</v>
       </c>
       <c r="AM38" t="inlineStr"/>
-      <c r="AN38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR38" t="inlineStr">
+      <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="inlineStr"/>
+      <c r="AP38" t="inlineStr"/>
+      <c r="AQ38" t="inlineStr"/>
+      <c r="AR38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV38" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -6510,7 +6686,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>יעל שולמן</t>
+          <t>דנה ברבינג-גולדשטיין</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6541,7 +6717,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>yaelshu@tlvmc.gov.il</t>
+          <t>danabr2@clalit.org.il</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -6554,7 +6730,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -6564,17 +6740,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>3zgt8o8y2e /search-result/ /api/as/v1/engines/ פתח חיפוש עוד ... זימון תורים אזור אישי כניסה לאיזור האישי AI צ'אט ד"ר יעל שולמן רופאה בכירה במחלקת נשים, ביה"ח 'ליס' ליולדות ונשים איכילוב צוות איכילוב יעל שולמן יצירת קשר yaelshu@tlvmc.gov.il יחידות רפואיות אשפוז נשים - מחלקה רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך ב</t>
+          <t>ד"ר דנה ברבינג גולדשטיין | מרכז רפואי רבין ד"ר דנה ברבינג גולדשטיין מיילדות וגינקולוגיה, גנטיקה רפואית שם: ד"ר דנה ברבינג גולדשטיין דוא"ל: danabr2@clalit.org.il יחידה: מכון רפאל רקנאטי לגנטיקה</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>"יעל שולמן"</t>
+          <t>"דנה ברבינג גולדשטיין" יילוד site:clalit.co.il</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -6591,36 +6767,36 @@
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-09-04T17:01:07.432235+00:00</t>
+          <t>2026-09-08T13:48:01.035843+00:00</t>
         </is>
       </c>
       <c r="W39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>["https://www.agmon-law.co.il/team-member/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/people/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/pfbid02D3uDhLBFvfdSCJScu9afsXcVu6ZWEqNA4AsJgJH4om5Y5hNBNGbDUq3Xyg3nad9hl/", "https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx"]</t>
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>1.524102750666068e+16</v>
+        <v>4.819434796805247e+16</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6631,7 +6807,7 @@
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr"/>
@@ -6641,19 +6817,23 @@
         <v>0</v>
       </c>
       <c r="AM39" t="inlineStr"/>
-      <c r="AN39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR39" t="inlineStr">
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr"/>
+      <c r="AP39" t="inlineStr"/>
+      <c r="AQ39" t="inlineStr"/>
+      <c r="AR39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV39" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -6668,7 +6848,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ישי לוין</t>
+          <t>יעל שולמן</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6699,7 +6879,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>ishail@tlvmc.gov.il</t>
+          <t>yaelshu@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -6712,7 +6892,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -6722,12 +6902,12 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>ריוזיס כנס אונליין אנדומטריאוזיס 2025 | פרופ' יריב יוגב ופרופ' ישי לוין מניעה וגילוי מוקדם של מחלות נשים | ערוץ 10 המכון לפריון - כירורגיה של הפריון | ליס פרופ' ישי לוין על כאבי מחזור חזקים , ערוץ 13, סטטוסקופ יצירת קשר ishail@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה אשפוז נשים - מחלקה אנדומטריוזיס - מרכז רב תחומי המרכז לבריאות האשה-מרפאות מומחים הפלות חוזרות - טיפול בכשל הריוני רופאים בכירים בליס-יולדות ונשים יצירת קשר יחיד</t>
+          <t>3zgt8o8y2e /search-result/ /api/as/v1/engines/ פתח חיפוש עוד ... זימון תורים אזור אישי כניסה לאיזור האישי AI צ'אט ד"ר יעל שולמן רופאה בכירה במחלקת נשים, ביה"ח 'ליס' ליולדות ונשים איכילוב צוות איכילוב יעל שולמן יצירת קשר yaelshu@tlvmc.gov.il יחידות רפואיות אשפוז נשים - מחלקה רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך ב</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>"ישי לוין"</t>
+          <t>"יעל שולמן"</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -6749,7 +6929,7 @@
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-09-04T17:20:48.855691+00:00</t>
+          <t>2026-09-04T17:01:07.432235+00:00</t>
         </is>
       </c>
       <c r="W40" t="n">
@@ -6759,10 +6939,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -6774,11 +6954,11 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>["https://www.ishai-levin.com/", "https://www.ishai-levin.com/about", "https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/", "https://pubmed.ncbi.nlm.nih.gov/?term=Levin%2c%20Ishai%5bFull%20Author%20Name%5d%20OR%20Ishai%2c%20Levin%5bFull%20Author%20Name%5d&amp;cmd=DetailsSearch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.agmon-law.co.il/team-member/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/people/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/pfbid02D3uDhLBFvfdSCJScu9afsXcVu6ZWEqNA4AsJgJH4om5Y5hNBNGbDUq3Xyg3nad9hl/", "https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>1.524102750666068e+16</v>
+        <v>4.572308251998205e+16</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6789,7 +6969,7 @@
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr"/>
@@ -6799,19 +6979,23 @@
         <v>0</v>
       </c>
       <c r="AM40" t="inlineStr"/>
-      <c r="AN40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP40" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ40" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR40" t="inlineStr">
+      <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="inlineStr"/>
+      <c r="AP40" t="inlineStr"/>
+      <c r="AQ40" t="inlineStr"/>
+      <c r="AR40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU40" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV40" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -6826,7 +7010,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>לירן הירש</t>
+          <t>ישי לוין</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6857,7 +7041,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>liranh@tlvmc.gov.il</t>
+          <t>ishail@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -6870,7 +7054,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -6880,12 +7064,12 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>צועיים החברה הישראלית לרפואת האם והעובר החוג הישראלי למיילדות וגינקולוגיה לידה נדירה - תאומים ברחם נפרד פרק 19 | פרופ' יריב יוגב ופרופ' לירן הירש | תאומים פרק 9 | פרופ' יריב יוגב ופרופ' לירן הירש| הריון בסיכון יצירת קשר liranh@tlvmc.gov.il יחידות רפואיות המחלקה לרפואת האם והעובר מניעת לידה מוקדמת - מרפאה מעקב הריונות תאומים רופאים בכירים בליס-יולדות ונשים היריון ולידה יצירת קשר יחידות רפואיות היריון של 1 למיליון עם פרופ' לירן הירש איכיל</t>
+          <t>ריוזיס כנס אונליין אנדומטריאוזיס 2025 | פרופ' יריב יוגב ופרופ' ישי לוין מניעה וגילוי מוקדם של מחלות נשים | ערוץ 10 המכון לפריון - כירורגיה של הפריון | ליס פרופ' ישי לוין על כאבי מחזור חזקים , ערוץ 13, סטטוסקופ יצירת קשר ishail@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה אשפוז נשים - מחלקה אנדומטריוזיס - מרכז רב תחומי המרכז לבריאות האשה-מרפאות מומחים הפלות חוזרות - טיפול בכשל הריוני רופאים בכירים בליס-יולדות ונשים יצירת קשר יחיד</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>"לירן הירש"</t>
+          <t>"ישי לוין"</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -6907,7 +7091,7 @@
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-09-04T17:39:56.947224+00:00</t>
+          <t>2026-09-04T17:20:48.855691+00:00</t>
         </is>
       </c>
       <c r="W41" t="n">
@@ -6932,11 +7116,11 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>["https://www.profhiersch.com/", "https://www.profhiersch.com/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/", "https://pubmed.ncbi.nlm.nih.gov/?term=HIERSCH+L&amp;sort=date", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.ishai-levin.com/", "https://www.ishai-levin.com/about", "https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/", "https://pubmed.ncbi.nlm.nih.gov/?term=Levin%2c%20Ishai%5bFull%20Author%20Name%5d%20OR%20Ishai%2c%20Levin%5bFull%20Author%20Name%5d&amp;cmd=DetailsSearch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>1.524102750666068e+16</v>
+        <v>4.572308251998205e+16</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -6947,7 +7131,7 @@
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr"/>
@@ -6957,19 +7141,23 @@
         <v>0</v>
       </c>
       <c r="AM41" t="inlineStr"/>
-      <c r="AN41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR41" t="inlineStr">
+      <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="inlineStr"/>
+      <c r="AP41" t="inlineStr"/>
+      <c r="AQ41" t="inlineStr"/>
+      <c r="AR41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV41" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -6984,7 +7172,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>נועה גוהר פורטנוי</t>
+          <t>לירן הירש</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7015,7 +7203,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>noago@post.bgu.ac.il</t>
+          <t>liranh@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -7028,7 +7216,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/noago/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -7038,12 +7226,12 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان נועה גוהר פורטנוי נועה גוהר פורטנוי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section noago@post.bgu.ac.il Cookies Settings</t>
+          <t>צועיים החברה הישראלית לרפואת האם והעובר החוג הישראלי למיילדות וגינקולוגיה לידה נדירה - תאומים ברחם נפרד פרק 19 | פרופ' יריב יוגב ופרופ' לירן הירש | תאומים פרק 9 | פרופ' יריב יוגב ופרופ' לירן הירש| הריון בסיכון יצירת קשר liranh@tlvmc.gov.il יחידות רפואיות המחלקה לרפואת האם והעובר מניעת לידה מוקדמת - מרפאה מעקב הריונות תאומים רופאים בכירים בליס-יולדות ונשים היריון ולידה יצירת קשר יחידות רפואיות היריון של 1 למיליון עם פרופ' לירן הירש איכיל</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>"נועה גוהר פורטנוי" יילוד</t>
+          <t>"לירן הירש"</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -7065,14 +7253,14 @@
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-09-08T14:13:12.580343+00:00</t>
+          <t>2026-09-04T17:39:56.947224+00:00</t>
         </is>
       </c>
       <c r="W42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
         <v>2</v>
@@ -7090,11 +7278,11 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>["https://www.doctorita.co.il/experts/126297", "https://www.bgu.ac.il/ar/people/noago/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.profhiersch.com/", "https://www.profhiersch.com/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/", "https://pubmed.ncbi.nlm.nih.gov/?term=HIERSCH+L&amp;sort=date", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>1.487180029392158e+16</v>
+        <v>4.572308251998205e+16</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7105,7 +7293,7 @@
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/noago/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr"/>
@@ -7115,19 +7303,23 @@
         <v>0</v>
       </c>
       <c r="AM42" t="inlineStr"/>
-      <c r="AN42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP42" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ42" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR42" t="inlineStr">
+      <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="inlineStr"/>
+      <c r="AP42" t="inlineStr"/>
+      <c r="AQ42" t="inlineStr"/>
+      <c r="AR42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU42" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV42" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -7142,7 +7334,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>עדי יהודה ווינטראוב</t>
+          <t>נועה גוהר פורטנוי</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7173,7 +7365,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>adiyehud@bgu.ac.il</t>
+          <t>noago@post.bgu.ac.il</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -7186,7 +7378,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
+          <t>https://www.bgu.ac.il/ar/people/noago/</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -7196,12 +7388,12 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>رئيسية جامعة أنشي سيجل في جوريان עדי יהודה ווינטראוב פרופ' עדי יהודה ווינטראוב Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section adiyehud@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0002-4239-8665 Orcid Number Cookies Settings</t>
+          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان נועה גוהר פורטנוי נועה גוהר פורטנוי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section noago@post.bgu.ac.il Cookies Settings</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>"עדי יהודה ווינטראוב"</t>
+          <t>"נועה גוהר פורטנוי" יילוד</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -7218,41 +7410,41 @@
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-09-04T19:20:10.182518+00:00</t>
+          <t>2026-09-08T14:13:12.580343+00:00</t>
         </is>
       </c>
       <c r="W43" t="n">
+        <v>4</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y43" t="n">
         <v>2</v>
       </c>
-      <c r="X43" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>5</v>
-      </c>
       <c r="Z43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/adiyehud/", "https://www.bgu.ac.il/researcher/adi-weintraub/", "https://www.beok.co.il/doctors/Doctors-136810/", "https://cris.bgu.ac.il/en/publications/%D7%94%D7%A1%D7%99%D7%9B%D7%95%D7%9F-%D7%9C%D7%A1%D7%99%D7%91%D7%95%D7%9B%D7%99-%D7%94%D7%99%D7%A8%D7%99%D7%95%D7%9F-%D7%91%D7%A0%D7%A9%D7%99%D7%9D-%D7%A2%D7%9D-%D7%90%D7%A0%D7%93%D7%95%D7%9E%D7%98%D7%A8%D7%99%D7%95%D7%96%D7%99%D7%A1/", "https://www.bgu.ac.il/ar/people/adiyehud/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.doctorita.co.il/experts/126297", "https://www.bgu.ac.il/ar/people/noago/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>1.487160967294354e+16</v>
+        <v>4.461540088176475e+16</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7263,7 +7455,7 @@
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
+          <t>https://www.bgu.ac.il/ar/people/noago/</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr"/>
@@ -7273,19 +7465,23 @@
         <v>0</v>
       </c>
       <c r="AM43" t="inlineStr"/>
-      <c r="AN43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP43" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ43" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR43" t="inlineStr">
+      <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr"/>
+      <c r="AP43" t="inlineStr"/>
+      <c r="AQ43" t="inlineStr"/>
+      <c r="AR43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV43" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -7300,7 +7496,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>עמרי זמשטין</t>
+          <t>עדי יהודה ווינטראוב</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7331,7 +7527,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>omrizam@post.bgu.ac.il</t>
+          <t>adiyehud@bgu.ac.il</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -7344,7 +7540,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
+          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -7354,12 +7550,12 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>ريد البحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان עמרי זמשטין עמרי זמשטין Departments אקדמי לא פעיל הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section omrizam@post.bgu.ac.il Cookies Settings</t>
+          <t>رئيسية جامعة أنشي سيجل في جوريان עדי יהודה ווינטראוב פרופ' עדי יהודה ווינטראוב Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section adiyehud@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0002-4239-8665 Orcid Number Cookies Settings</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>"עמרי זמשטין"</t>
+          <t>"עדי יהודה ווינטראוב"</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -7381,7 +7577,7 @@
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-09-04T19:35:09.971397+00:00</t>
+          <t>2026-09-04T19:20:10.182518+00:00</t>
         </is>
       </c>
       <c r="W44" t="n">
@@ -7391,26 +7587,26 @@
         <v>1</v>
       </c>
       <c r="Y44" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/ar/people/omrizam/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.bgu.ac.il/people/adiyehud/", "https://www.bgu.ac.il/researcher/adi-weintraub/", "https://www.beok.co.il/doctors/Doctors-136810/", "https://cris.bgu.ac.il/en/publications/%D7%94%D7%A1%D7%99%D7%9B%D7%95%D7%9F-%D7%9C%D7%A1%D7%99%D7%91%D7%95%D7%9B%D7%99-%D7%94%D7%99%D7%A8%D7%99%D7%95%D7%9F-%D7%91%D7%A0%D7%A9%D7%99%D7%9D-%D7%A2%D7%9D-%D7%90%D7%A0%D7%93%D7%95%D7%9E%D7%98%D7%A8%D7%99%D7%95%D7%96%D7%99%D7%A1/", "https://www.bgu.ac.il/ar/people/adiyehud/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>1.487160967294354e+16</v>
+        <v>4.461482901883061e+16</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7421,7 +7617,7 @@
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
+          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr"/>
@@ -7431,19 +7627,23 @@
         <v>0</v>
       </c>
       <c r="AM44" t="inlineStr"/>
-      <c r="AN44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR44" t="inlineStr">
+      <c r="AN44" t="inlineStr"/>
+      <c r="AO44" t="inlineStr"/>
+      <c r="AP44" t="inlineStr"/>
+      <c r="AQ44" t="inlineStr"/>
+      <c r="AR44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV44" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -7458,7 +7658,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>רויטל לינדר</t>
+          <t>עמרי זמשטין</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7489,7 +7689,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>revital@drlinder.co.il</t>
+          <t>omrizam@post.bgu.ac.il</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -7502,7 +7702,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://www.drlinder.co.il/</t>
+          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -7512,12 +7712,12 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>בכירה ביחידה הגניקואונקולוגית , בית חולים רמב״ם, חיפה. 4/2014-4/2019 התמחות במיילדות וגניקולוגיה בית חולים רמב״ם,חיפה. לפרטים מלאים חוות דעת יש לך שאלה ? צרי קשר ד״ר רויטל לינדר צפצפה 2 (ישי סנטר) , רמת ישי 058-6918927​ revital@drlinder.co.il הצהרת נגישות © DR. Revital Linder. All rights Reserved , 2023</t>
+          <t>ريد البحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان עמרי זמשטין עמרי זמשטין Departments אקדמי לא פעיל הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section omrizam@post.bgu.ac.il Cookies Settings</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>"רויטל לינדר"</t>
+          <t>"עמרי זמשטין"</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -7534,41 +7734,41 @@
         <v>1</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-09-04T07:14:47.643108+00:00</t>
+          <t>2026-09-04T19:35:09.971397+00:00</t>
         </is>
       </c>
       <c r="W45" t="n">
         <v>2</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>["https://www.rambam.org.il/?catid=%7B9F8D1CC1-1F5C-46F1-A395-E19ED48FE2EE%7D&amp;itemid=%7B4B21BA59-AF68-46CA-9483-9639E61A75A8%7D", "https://www.rambam.org.il/about-rambam/", "https://www.rambam.org.il/about-rambam/careers/", "https://www.rambam.org.il/departmentsandclinics/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/urology/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/orthopedic/", "https://www.drlinder.co.il/"]</t>
+          <t>["https://www.bgu.ac.il/ar/people/omrizam/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>1.486991509572465e+16</v>
+        <v>4.461482901883061e+16</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7579,7 +7779,7 @@
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>https://www.drlinder.co.il/</t>
+          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr"/>
@@ -7589,19 +7789,23 @@
         <v>0</v>
       </c>
       <c r="AM45" t="inlineStr"/>
-      <c r="AN45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR45" t="inlineStr">
+      <c r="AN45" t="inlineStr"/>
+      <c r="AO45" t="inlineStr"/>
+      <c r="AP45" t="inlineStr"/>
+      <c r="AQ45" t="inlineStr"/>
+      <c r="AR45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV45" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -7616,7 +7820,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>רליקה הרשקוביץ</t>
+          <t>רויטל לינדר</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7647,7 +7851,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>ralikah@bgu.ac.il</t>
+          <t>revital@drlinder.co.il</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -7660,7 +7864,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
+          <t>https://www.drlinder.co.il/</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -7670,12 +7874,12 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان רליקה הרשקוביץ פרופ' רליקה הרשקוביץ Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ralikah@bgu.ac.il رابط ملف الأبحاث Cookies Settings</t>
+          <t>בכירה ביחידה הגניקואונקולוגית , בית חולים רמב״ם, חיפה. 4/2014-4/2019 התמחות במיילדות וגניקולוגיה בית חולים רמב״ם,חיפה. לפרטים מלאים חוות דעת יש לך שאלה ? צרי קשר ד״ר רויטל לינדר צפצפה 2 (ישי סנטר) , רמת ישי 058-6918927​ revital@drlinder.co.il הצהרת נגישות © DR. Revital Linder. All rights Reserved , 2023</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>"רליקה הרשקוביץ"</t>
+          <t>"רויטל לינדר"</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -7697,7 +7901,7 @@
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-09-04T07:56:40.372731+00:00</t>
+          <t>2026-09-04T07:14:47.643108+00:00</t>
         </is>
       </c>
       <c r="W46" t="n">
@@ -7707,26 +7911,26 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/ralikah/", "https://www.doctorita.co.il/experts/101245", "https://www.bgu.ac.il/ar/people/ralikah/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.rambam.org.il/?catid=%7B9F8D1CC1-1F5C-46F1-A395-E19ED48FE2EE%7D&amp;itemid=%7B4B21BA59-AF68-46CA-9483-9639E61A75A8%7D", "https://www.rambam.org.il/about-rambam/", "https://www.rambam.org.il/about-rambam/careers/", "https://www.rambam.org.il/departmentsandclinics/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/urology/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/orthopedic/", "https://www.drlinder.co.il/"]</t>
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>1.486991509572465e+16</v>
+        <v>4.460974528717395e+16</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7737,7 +7941,7 @@
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
+          <t>https://www.drlinder.co.il/</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr"/>
@@ -7747,19 +7951,23 @@
         <v>0</v>
       </c>
       <c r="AM46" t="inlineStr"/>
-      <c r="AN46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR46" t="inlineStr">
+      <c r="AN46" t="inlineStr"/>
+      <c r="AO46" t="inlineStr"/>
+      <c r="AP46" t="inlineStr"/>
+      <c r="AQ46" t="inlineStr"/>
+      <c r="AR46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV46" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -7774,7 +7982,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>שקמה בר און</t>
+          <t>רליקה הרשקוביץ</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7805,7 +8013,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>shikmabo@tlvmc.gov.il</t>
+          <t>ralikah@bgu.ac.il</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -7818,7 +8026,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
+          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -7828,12 +8036,12 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>ת לאנדוסקופיה גינקולוגית שטחי התעניינות ועיסוק מיוחדים היסטרוסקופיה עם וללא הרדמה, היסטרוסקופיה ניתוחית ללא הרדמה בשיטת "see and treat" לפרוסקופיות פרק 14 | פרופ' יריב יוגב וד״ר שקמה בר און | מרכז בריאות האישה יצירת קשר shikmabo@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך בהתפתחות ביה"ח איכו</t>
+          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان רליקה הרשקוביץ פרופ' רליקה הרשקוביץ Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ralikah@bgu.ac.il رابط ملف الأبحاث Cookies Settings</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>"שקמה בר און"</t>
+          <t>"רליקה הרשקוביץ"</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -7855,7 +8063,7 @@
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-09-04T10:28:27.702590+00:00</t>
+          <t>2026-09-04T07:56:40.372731+00:00</t>
         </is>
       </c>
       <c r="W47" t="n">
@@ -7865,13 +8073,13 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
@@ -7880,11 +8088,11 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>["https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%A9%D7%A7%D7%9E%D7%94-%D7%91%D7%A8-%D7%90%D7%95%D7%9F/", "https://tlvmedical.com/doctors/דר-שקמה-בר-און/", "https://www.rofim.org.il/minisite/%D7%93%D7%A8_%D7%A9%D7%A7%D7%9E%D7%94_%D7%91%D7%A8_%D7%90%D7%95%D7%9F", "https://www.shidurit-ltd.co.il/", "https://www.rofim.org.il/about", "https://www.rofim.org.il/Contact", "https://www.rofim.org.il/specialityPage/%D7%9E%D7%A8%D7%9B%D7%96_%D7%A8%D7%A4%D7%95%D7%90%D7%99", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%9E%D7%92%D7%90%D7%A8", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%91%D7%99%D7%AA_%D7%92%D7%93%D7%99", "https://www.rofim.org.il/minisite/%D7%90%D7%99%D7%99_%D7%90%D7%9C_%D7%A7%D7%9C%D7%99%D7%A0%D7%99%D7%A7", "https://docsrated.com/doctors/שקמה-בר-און", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2FTLVMDC%2Fphotos%2F%25D7%25A2%25D7%2595%25D7%25A7%25D7%2591%25D7%2595%25D7%25AA-%25D7%2595%25D7%259E%25D7%2598%25D7%2595%25D7%25A4%25D7%259C%25D7%2595%25D7%25AA-%25D7%2590%25D7%25A0%25D7%2595-%25D7%25A9%25D7%259E%25D7%2597%25D7%2599%25D7%259D-%25D7%259C%25D7%2594%25D7%259B%25D7%2599%25D7%25A8-%25D7%259C%25D7%259B%25D7%259F-%25D7%2590%25D7%25AA-%25D7%2593%25D7%25A8-%25D7%25A9%25D7%25A7%25D7%259E%25D7%2594-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F%25D7%2593%25D7%25A8-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F-%25D7%2594%25D7%2599%25D7%2590-%25D7%259E%25D7%25A0%25D7%2594%25D7%259C%25D7%25AA-%25D7%2594%25D7%259E%25D7%25A8%25D7%259B%25D7%2596-%25D7%259C%2F1525276317871201%2F", "https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/", "https://www.ncbi.nlm.nih.gov/pubmed/?term=shikma+bar+on", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.bgu.ac.il/people/ralikah/", "https://www.doctorita.co.il/experts/101245", "https://www.bgu.ac.il/ar/people/ralikah/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>1.48394127057847e+16</v>
+        <v>4.460974528717395e+16</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -7895,7 +8103,7 @@
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
+          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr"/>
@@ -7905,19 +8113,23 @@
         <v>0</v>
       </c>
       <c r="AM47" t="inlineStr"/>
-      <c r="AN47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR47" t="inlineStr">
+      <c r="AN47" t="inlineStr"/>
+      <c r="AO47" t="inlineStr"/>
+      <c r="AP47" t="inlineStr"/>
+      <c r="AQ47" t="inlineStr"/>
+      <c r="AR47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV47" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -7932,7 +8144,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>שרית הלמן</t>
+          <t>שקמה בר און</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7963,7 +8175,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>hsarit@szmc.org.il</t>
+          <t>shikmabo@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -7976,7 +8188,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -7986,12 +8198,12 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t xml:space="preserve"> רופאים בשערי צדק ד"ר שרית  הלמן רופאה בכירה Dr. Sarit  Helman התמחות: גינקולוגיה ויילוד תת התמחות: הריון בסיכון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 026666656 מחלקה: 026666656 hsarit@szmc.org.il hsarit@szmc.org.il נסיון מקצועי Harvard T.H. Chan School of Public Health, Joslin Diabetes Center, Research intern under the supervision of Dr. Florence Brown and Dr. Tamarra James-Todd,     Type 1 Dia</t>
+          <t>ת לאנדוסקופיה גינקולוגית שטחי התעניינות ועיסוק מיוחדים היסטרוסקופיה עם וללא הרדמה, היסטרוסקופיה ניתוחית ללא הרדמה בשיטת "see and treat" לפרוסקופיות פרק 14 | פרופ' יריב יוגב וד״ר שקמה בר און | מרכז בריאות האישה יצירת קשר shikmabo@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך בהתפתחות ביה"ח איכו</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>"שרית הלמן"</t>
+          <t>"שקמה בר און"</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -8008,12 +8220,12 @@
         <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-09-05T00:06:28.339643+00:00</t>
+          <t>2026-09-04T10:28:27.702590+00:00</t>
         </is>
       </c>
       <c r="W48" t="n">
@@ -8026,10 +8238,10 @@
         <v>6</v>
       </c>
       <c r="Z48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
@@ -8038,11 +8250,11 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>["https://www.hamichlol.org.il/שרה_(שרית)_הלמן", "https://behevrat-haadam.org/ram-sara-helman/", "https://behevrat-haadam.org/tag/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/IsrAnthro/posts/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F-%D7%A1%D7%95%D7%A6%D7%99%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA%D7%90%D7%A0%D7%97%D7%A0%D7%95-%D7%A9%D7%9E%D7%97%D7%99%D7%9D-%D7%9C%D7%A9%D7%AA%D7%A3-%D7%91%D7%91%D7%97%D7%91%D7%A8%D7%AA-%D7%94%D7%90%D7%93%D7%9D-%D7%90%D7%AA-%D7%93%D7%91%D7%A8%D7%99%D7%95-%D7%A9%D7%9C-%D7%90%D7%95%D7%A8%D7%99-%D7%A8%D7%9D-%D7%A4%D7%A8%D7%95%D7%A4-%D7%90%D7%9E%D7%A8%D7%99%D7%98%D7%95/4246861638775714/", "https://www.doctorita.co.il/experts/137665", "https://www.szmc.org.il/doctors/helman-sarit/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
+          <t>["https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%A9%D7%A7%D7%9E%D7%94-%D7%91%D7%A8-%D7%90%D7%95%D7%9F/", "https://tlvmedical.com/doctors/דר-שקמה-בר-און/", "https://www.rofim.org.il/minisite/%D7%93%D7%A8_%D7%A9%D7%A7%D7%9E%D7%94_%D7%91%D7%A8_%D7%90%D7%95%D7%9F", "https://www.shidurit-ltd.co.il/", "https://www.rofim.org.il/about", "https://www.rofim.org.il/Contact", "https://www.rofim.org.il/specialityPage/%D7%9E%D7%A8%D7%9B%D7%96_%D7%A8%D7%A4%D7%95%D7%90%D7%99", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%9E%D7%92%D7%90%D7%A8", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%91%D7%99%D7%AA_%D7%92%D7%93%D7%99", "https://www.rofim.org.il/minisite/%D7%90%D7%99%D7%99_%D7%90%D7%9C_%D7%A7%D7%9C%D7%99%D7%A0%D7%99%D7%A7", "https://docsrated.com/doctors/שקמה-בר-און", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2FTLVMDC%2Fphotos%2F%25D7%25A2%25D7%2595%25D7%25A7%25D7%2591%25D7%2595%25D7%25AA-%25D7%2595%25D7%259E%25D7%2598%25D7%2595%25D7%25A4%25D7%259C%25D7%2595%25D7%25AA-%25D7%2590%25D7%25A0%25D7%2595-%25D7%25A9%25D7%259E%25D7%2597%25D7%2599%25D7%259D-%25D7%259C%25D7%2594%25D7%259B%25D7%2599%25D7%25A8-%25D7%259C%25D7%259B%25D7%259F-%25D7%2590%25D7%25AA-%25D7%2593%25D7%25A8-%25D7%25A9%25D7%25A7%25D7%259E%25D7%2594-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F%25D7%2593%25D7%25A8-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F-%25D7%2594%25D7%2599%25D7%2590-%25D7%259E%25D7%25A0%25D7%2594%25D7%259C%25D7%25AA-%25D7%2594%25D7%259E%25D7%25A8%25D7%259B%25D7%2596-%25D7%259C%2F1525276317871201%2F", "https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/", "https://www.ncbi.nlm.nih.gov/pubmed/?term=shikma+bar+on", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>1.483997756485766e+16</v>
+        <v>4.45182381173541e+16</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8053,7 +8265,7 @@
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr"/>
@@ -8063,19 +8275,23 @@
         <v>0</v>
       </c>
       <c r="AM48" t="inlineStr"/>
-      <c r="AN48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR48" t="inlineStr">
+      <c r="AN48" t="inlineStr"/>
+      <c r="AO48" t="inlineStr"/>
+      <c r="AP48" t="inlineStr"/>
+      <c r="AQ48" t="inlineStr"/>
+      <c r="AR48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU48" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV48" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -8090,7 +8306,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ד"ר ארבל אריאל</t>
+          <t>שרית הלמן</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8110,31 +8326,31 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>ima</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>info@eryaveladan.com</t>
+          <t>hsarit@szmc.org.il</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://www.eryaveladan.com/</t>
+          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -8144,12 +8360,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>החזיר את האיזון. קראי עוד השאירי פרטים ונחזור אלייך בהקדם שם מלא טלפון דוא״ל שליחה רופא נשים מומחה מחלות העריה והלדן ​ ד״ר אריאל ארבל לקביעת תור: 077-2311245 כתובת המרפאה: בית למומחים ברפואה - בורוכוב 54, גבעתיים דוא״ל: info@eryaveladan.com bottom of page</t>
+          <t xml:space="preserve"> רופאים בשערי צדק ד"ר שרית  הלמן רופאה בכירה Dr. Sarit  Helman התמחות: גינקולוגיה ויילוד תת התמחות: הריון בסיכון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 026666656 מחלקה: 026666656 hsarit@szmc.org.il hsarit@szmc.org.il נסיון מקצועי Harvard T.H. Chan School of Public Health, Joslin Diabetes Center, Research intern under the supervision of Dr. Florence Brown and Dr. Tamarra James-Todd,     Type 1 Dia</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>"ארבל אריאל"</t>
+          <t>"שרית הלמן"</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -8159,29 +8375,29 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>[{"email": "info@eryaveladan.com", "confidence": 88, "source_url": "https://www.eryaveladan.com/", "identity_url": "https://www.eryaveladan.com/", "evidence": "החזיר את האיזון. קראי עוד השאירי פרטים ונחזור אלייך בהקדם שם מלא טלפון דוא״ל שליחה רופא נשים מומחה מחלות העריה והלדן ​ ד״ר אריאל ארבל לקביעת תור: 077-2311245 כתובת המרפאה: בית למומחים ברפואה - בורוכוב 54, גבעתיים דוא״ל: info@eryaveladan.com bottom of page", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}, {"email": "office@b54.co.il", "confidence": 88, "source_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "identity_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "evidence": "ד\"ר אריאל ארבל - מרפאת מומחים B54, הבית למומחים ברפואה בגבעתיים דילוג לתוכן B54 03-757-8562 office@b54.co.il א׳-ה׳ 8:00-20:00 | ו׳ 08:00-13:00 Facebook-f Youtube Google דף הבית אודות B54 מי אנחנו שכונת בורוכוב מרכז Friendly הנהלת המרפאה שאלות נפוצות הרופאים שלנו קליניקה להשכרה מידע למטופל שאלות ותשובות הורדת טפ", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-09-03T20:23:48.175654+00:00</t>
+          <t>2026-09-05T00:06:28.339643+00:00</t>
         </is>
       </c>
       <c r="W49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X49" t="n">
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z49" t="n">
         <v>5</v>
@@ -8196,11 +8412,11 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598", "https://www.facebook.com/people/%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%90%D7%A8%D7%91%D7%9C/pfbid0NCmi7FZgUyu2EVV5mLJMpBfndXiDQPqseAxUny7KWHsDvucQScUiVnBeMef3ByStl/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%90%D7%A8%D7%91%D7%9C-%D7%90%D7%A8%D7%99%D7%90%D7%9C/", "https://www.eryaveladan.com/", "https://www.eryaveladan.com/%D7%90%D7%95%D7%93%D7%95%D7%AA-1", "https://www.b54.co.il/doctors/dr-arbel-ariel/", "https://www.medreviews.co.il/provider/dr-arbel-ariel", "https://www.b54.co.il/about/", "https://www.b54.co.il/about", "https://www.b54.co.il/about#borohov", "https://www.b54.co.il/about#Friendly", "https://www.b54.co.il/about#management", "https://www.b54.co.il/about#qa", "https://www.medreviews.co.il/provider/dr-arbel-ariel#contact-doctor-section", "https://www.medreviews.co.il/contact-us", "https://www.medreviews.co.il/about", "https://woman.mymc.co.il/doctors/dr-arielarbel/", "https://www.ima.org.il/DoctorsIndex/Default.aspx", "https://www.infomed.co.il/experts/145655/", "https://www.ami.org.il/blog/families/not-the-same-shirley"]</t>
+          <t>["https://www.hamichlol.org.il/שרה_(שרית)_הלמן", "https://behevrat-haadam.org/ram-sara-helman/", "https://behevrat-haadam.org/tag/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/IsrAnthro/posts/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F-%D7%A1%D7%95%D7%A6%D7%99%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA%D7%90%D7%A0%D7%97%D7%A0%D7%95-%D7%A9%D7%9E%D7%97%D7%99%D7%9D-%D7%9C%D7%A9%D7%AA%D7%A3-%D7%91%D7%91%D7%97%D7%91%D7%A8%D7%AA-%D7%94%D7%90%D7%93%D7%9D-%D7%90%D7%AA-%D7%93%D7%91%D7%A8%D7%99%D7%95-%D7%A9%D7%9C-%D7%90%D7%95%D7%A8%D7%99-%D7%A8%D7%9D-%D7%A4%D7%A8%D7%95%D7%A4-%D7%90%D7%9E%D7%A8%D7%99%D7%98%D7%95/4246861638775714/", "https://www.doctorita.co.il/experts/137665", "https://www.szmc.org.il/doctors/helman-sarit/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>1.97655486810863e+16</v>
+        <v>4.451993269457299e+16</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8211,7 +8427,7 @@
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>https://www.eryaveladan.com/</t>
+          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr"/>
@@ -8221,21 +8437,25 @@
         <v>0</v>
       </c>
       <c r="AM49" t="inlineStr"/>
-      <c r="AN49" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP49" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
+      <c r="AN49" t="inlineStr"/>
+      <c r="AO49" t="inlineStr"/>
+      <c r="AP49" t="inlineStr"/>
+      <c r="AQ49" t="inlineStr"/>
+      <c r="AR49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU49" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>PERSON</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8468,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>מאיה שרון וינר</t>
+          <t>ד"ר ארבל אריאל</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8268,18 +8488,18 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>ima</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>clinic@drmayasharonweiner.com</t>
+          <t>info@eryaveladan.com</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -8292,7 +8512,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://www.drmayasharonweiner.com/</t>
+          <t>https://www.eryaveladan.com/</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -8302,12 +8522,12 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>אני איתך במסע הזה. הצעד הראשון שלך מתחיל כאן. ד"ר מאיה שרון-וינר רופאת נשים מומחית בפריון והפריה חוץ גופית מיילדות וגינקולוגיה לקביעת פגישה © 2026 כל הזכויות שמורות לד"ר מאיה שרון-וינר הברזל 9א', רמת החייל ווטסאפ למרפאה clinic@drmayasharonweiner.com פוריות האישה והגבר טיפולי פוריות הפריה חוץ גופית ו-PGD שימור פוריות פוריות לאחר סרטן ובנשאיות BRCA מעקב וליווי הריון גינקולוגיה כללית Menu Close אודות יצירת קשר מדיניות פרטיות הצהרת נגישות M</t>
+          <t>החזיר את האיזון. קראי עוד השאירי פרטים ונחזור אלייך בהקדם שם מלא טלפון דוא״ל שליחה רופא נשים מומחה מחלות העריה והלדן ​ ד״ר אריאל ארבל לקביעת תור: 077-2311245 כתובת המרפאה: בית למומחים ברפואה - בורוכוב 54, גבעתיים דוא״ל: info@eryaveladan.com bottom of page</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>"מאיה שרון וינר"</t>
+          <t>"ארבל אריאל"</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -8317,11 +8537,11 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "info@eryaveladan.com", "confidence": 88, "source_url": "https://www.eryaveladan.com/", "identity_url": "https://www.eryaveladan.com/", "evidence": "החזיר את האיזון. קראי עוד השאירי פרטים ונחזור אלייך בהקדם שם מלא טלפון דוא״ל שליחה רופא נשים מומחה מחלות העריה והלדן ​ ד״ר אריאל ארבל לקביעת תור: 077-2311245 כתובת המרפאה: בית למומחים ברפואה - בורוכוב 54, גבעתיים דוא״ל: info@eryaveladan.com bottom of page", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}, {"email": "office@b54.co.il", "confidence": 88, "source_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "identity_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "evidence": "ד\"ר אריאל ארבל - מרפאת מומחים B54, הבית למומחים ברפואה בגבעתיים דילוג לתוכן B54 03-757-8562 office@b54.co.il א׳-ה׳ 8:00-20:00 | ו׳ 08:00-13:00 Facebook-f Youtube Google דף הבית אודות B54 מי אנחנו שכונת בורוכוב מרכז Friendly הנהלת המרפאה שאלות נפוצות הרופאים שלנו קליניקה להשכרה מידע למטופל שאלות ותשובות הורדת טפ", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}]</t>
         </is>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T50" t="n">
         <v>0</v>
@@ -8329,17 +8549,17 @@
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-09-04T17:43:40.101946+00:00</t>
+          <t>2026-09-03T20:23:48.175654+00:00</t>
         </is>
       </c>
       <c r="W50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z50" t="n">
         <v>5</v>
@@ -8349,16 +8569,16 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>["https://www.drmayasharonweiner.com/", "https://www.drmayasharonweiner.com/about", "https://www.drmayasharonweiner.com/contact", "https://www.medreviews.co.il/provider/dr-sharon-weiner-maya", "https://www.medreviews.co.il/provider/dr-sharon-weiner-maya/treatment", "https://www.doctorita.co.il/experts/119120", "https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr_maya_sharonweiner%2F&amp;is_from_rle", "https://docsrated.com/doctors/מאיה-שרון-וינר"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598", "https://www.facebook.com/people/%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%90%D7%A8%D7%91%D7%9C/pfbid0NCmi7FZgUyu2EVV5mLJMpBfndXiDQPqseAxUny7KWHsDvucQScUiVnBeMef3ByStl/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%90%D7%A8%D7%91%D7%9C-%D7%90%D7%A8%D7%99%D7%90%D7%9C/", "https://www.eryaveladan.com/", "https://www.eryaveladan.com/%D7%90%D7%95%D7%93%D7%95%D7%AA-1", "https://www.b54.co.il/doctors/dr-arbel-ariel/", "https://www.medreviews.co.il/provider/dr-arbel-ariel", "https://www.b54.co.il/about/", "https://www.b54.co.il/about", "https://www.b54.co.il/about#borohov", "https://www.b54.co.il/about#Friendly", "https://www.b54.co.il/about#management", "https://www.b54.co.il/about#qa", "https://www.medreviews.co.il/provider/dr-arbel-ariel#contact-doctor-section", "https://www.medreviews.co.il/contact-us", "https://www.medreviews.co.il/about", "https://woman.mymc.co.il/doctors/dr-arielarbel/", "https://www.ima.org.il/DoctorsIndex/Default.aspx", "https://www.infomed.co.il/experts/145655/", "https://www.ami.org.il/blog/families/not-the-same-shirley"]</t>
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>1.524102750666068e+16</v>
+        <v>5.929664604325891e+16</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8369,7 +8589,7 @@
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>https://www.drmayasharonweiner.com/</t>
+          <t>https://www.eryaveladan.com/</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr"/>
@@ -8379,19 +8599,23 @@
         <v>0</v>
       </c>
       <c r="AM50" t="inlineStr"/>
-      <c r="AN50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP50" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR50" t="inlineStr">
+      <c r="AN50" t="inlineStr"/>
+      <c r="AO50" t="inlineStr"/>
+      <c r="AP50" t="inlineStr"/>
+      <c r="AQ50" t="inlineStr"/>
+      <c r="AR50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV50" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -8406,7 +8630,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>מנחם נוימן</t>
+          <t>מאיה שרון וינר</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8437,7 +8661,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>hello@professorneuman.com</t>
+          <t>clinic@drmayasharonweiner.com</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -8450,7 +8674,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://professorneuman.com/he/</t>
+          <t>https://www.drmayasharonweiner.com/</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -8460,12 +8684,12 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>פרופ׳ מנחם נוימן — אורוגינקולוגיה ורפואת רצפת האגן מגדל סוזוקי, קומה 4, רח׳ יגאל אלון 82, תל אביב 054-644-2060 · hello@professorneuman.com ראשי מידע לרופאים מידע למטופלות מהתקשורת צרי קשר English פרופ׳ מנחם נוימן אורוגינקולוגיה ורפואת רצפת האגן צניחת איברי האגן ודליפת שתן הן מהתופעות השכיחות ביותר בקרב נשים — וגם מהניתנות ביותר לטי</t>
+          <t>אני איתך במסע הזה. הצעד הראשון שלך מתחיל כאן. ד"ר מאיה שרון-וינר רופאת נשים מומחית בפריון והפריה חוץ גופית מיילדות וגינקולוגיה לקביעת פגישה © 2026 כל הזכויות שמורות לד"ר מאיה שרון-וינר הברזל 9א', רמת החייל ווטסאפ למרפאה clinic@drmayasharonweiner.com פוריות האישה והגבר טיפולי פוריות הפריה חוץ גופית ו-PGD שימור פוריות פוריות לאחר סרטן ובנשאיות BRCA מעקב וליווי הריון גינקולוגיה כללית Menu Close אודות יצירת קשר מדיניות פרטיות הצהרת נגישות M</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>"מנחם נוימן"</t>
+          <t>"מאיה שרון וינר"</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -8475,11 +8699,11 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>[{"email": "info@raphaelhospitals.co.il", "confidence": 80, "source_url": "https://www.raphaelhospitals.co.il/en/international-department/about/", "identity_url": "https://www.raphaelhospitals.co.il/doctors/neuman-menahem/", "evidence": "info@raphaelhospitals.co.il", "matched_query": "\"מנחם נוימן\"", "extraction_method": "linked_mailto"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T51" t="n">
         <v>0</v>
@@ -8487,36 +8711,36 @@
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-09-04T18:20:49.705154+00:00</t>
+          <t>2026-09-04T17:43:40.101946+00:00</t>
         </is>
       </c>
       <c r="W51" t="n">
         <v>2</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y51" t="n">
         <v>7</v>
       </c>
       <c r="Z51" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>["https://professorneuman.com/", "https://professorneuman.com/he/", "https://professorneuman.com/he/contact", "https://professorneuman.com/en/contact", "https://www.facebook.com/public/%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/", "https://www.facebook.com/people/%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/pfbid0371mkxMbe96MNN5gS9XHB7KqrSyxJnXyG9AsLfdZV7j8RjCKyjm8cEEVgjSreLhY8l/", "https://chabadpedia.co.il/wiki/%D7%9E%D7%A0%D7%97%D7%9D_%D7%A0%D7%95%D7%99%D7%9E%D7%9F", "https://www.raphaelhospitals.co.il/doctors/neuman-menahem/", "https://www.raphaelhospitals.co.il/about/aboutus/", "https://www.raphaelhospitals.co.il/fields/endoscopic-unit/about/", "https://www.raphaelhospitals.co.il/fields/pain-clinic/about/", "https://www.raphaelhospitals.co.il/en/international-department/about/", "https://www.raphaelhospitals.co.il/fields/heart-catheterization-clinic/about/", "https://www.raphaelhospitals.co.il/en/about/aboutus/", "https://www.raphaelhospitals.co.il/en/contact/"]</t>
+          <t>["https://www.drmayasharonweiner.com/", "https://www.drmayasharonweiner.com/about", "https://www.drmayasharonweiner.com/contact", "https://www.medreviews.co.il/provider/dr-sharon-weiner-maya", "https://www.medreviews.co.il/provider/dr-sharon-weiner-maya/treatment", "https://www.doctorita.co.il/experts/119120", "https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr_maya_sharonweiner%2F&amp;is_from_rle", "https://docsrated.com/doctors/מאיה-שרון-וינר"]</t>
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>1.524102750666068e+16</v>
+        <v>4.572308251998205e+16</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8527,7 +8751,7 @@
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>https://professorneuman.com/he/</t>
+          <t>https://www.drmayasharonweiner.com/</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr"/>
@@ -8537,19 +8761,23 @@
         <v>0</v>
       </c>
       <c r="AM51" t="inlineStr"/>
-      <c r="AN51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP51" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR51" t="inlineStr">
+      <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="inlineStr"/>
+      <c r="AP51" t="inlineStr"/>
+      <c r="AQ51" t="inlineStr"/>
+      <c r="AR51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV51" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -8564,7 +8792,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>נעמה מימון</t>
+          <t>מנחם נוימן</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8595,7 +8823,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>office@medicaltop.co.il</t>
+          <t>hello@professorneuman.com</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -8608,7 +8836,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/</t>
+          <t>https://professorneuman.com/he/</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -8618,12 +8846,12 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t xml:space="preserve">ד"ר נעמה מימון: מומחית ברפואת נשים - MedicalTop Search Close Facebook 073-3310444 סנטר הגליל רחוב האגס 1, שער הרימון, קומה שניה. ראש פינה. office@medicaltop.co.il לקביעת תור דף הבית אודות תחומי פעילות הצוות שלנו יצירת קשר Menu דף הבית אודות תחומי פעילות הצוות שלנו יצירת קשר ד"ר נעמה מימון: מומחית ברפואת נשים דף הבית / רופאים / ד"ר נעמה מימון: מומחית ברפואת </t>
+          <t>פרופ׳ מנחם נוימן — אורוגינקולוגיה ורפואת רצפת האגן מגדל סוזוקי, קומה 4, רח׳ יגאל אלון 82, תל אביב 054-644-2060 · hello@professorneuman.com ראשי מידע לרופאים מידע למטופלות מהתקשורת צרי קשר English פרופ׳ מנחם נוימן אורוגינקולוגיה ורפואת רצפת האגן צניחת איברי האגן ודליפת שתן הן מהתופעות השכיחות ביותר בקרב נשים — וגם מהניתנות ביותר לטי</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>"נעמה מימון"</t>
+          <t>"מנחם נוימן"</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -8633,32 +8861,32 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "info@raphaelhospitals.co.il", "confidence": 80, "source_url": "https://www.raphaelhospitals.co.il/en/international-department/about/", "identity_url": "https://www.raphaelhospitals.co.il/doctors/neuman-menahem/", "evidence": "info@raphaelhospitals.co.il", "matched_query": "\"מנחם נוימן\"", "extraction_method": "linked_mailto"}]</t>
         </is>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-09-04T05:17:30.924388+00:00</t>
+          <t>2026-09-04T18:20:49.705154+00:00</t>
         </is>
       </c>
       <c r="W52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X52" t="n">
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z52" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -8670,14 +8898,14 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>["https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fn.mh.mymwn.2025%2F", "https://www.facebook.com/SNMaesthetic/services/", "https://www.doctorita.co.il/experts/152626", "https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/", "https://medicaltop.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://medicaltop.co.il/%D7%94%D7%A6%D7%95%D7%95%D7%AA-%D7%A9%D7%9C%D7%A0%D7%95/", "https://medicaltop.co.il/wp-content/uploads/2024/04/אודות.jpg"]</t>
+          <t>["https://professorneuman.com/", "https://professorneuman.com/he/", "https://professorneuman.com/he/contact", "https://professorneuman.com/en/contact", "https://www.facebook.com/public/%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/", "https://www.facebook.com/people/%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/pfbid0371mkxMbe96MNN5gS9XHB7KqrSyxJnXyG9AsLfdZV7j8RjCKyjm8cEEVgjSreLhY8l/", "https://chabadpedia.co.il/wiki/%D7%9E%D7%A0%D7%97%D7%9D_%D7%A0%D7%95%D7%99%D7%9E%D7%9F", "https://www.raphaelhospitals.co.il/doctors/neuman-menahem/", "https://www.raphaelhospitals.co.il/about/aboutus/", "https://www.raphaelhospitals.co.il/fields/endoscopic-unit/about/", "https://www.raphaelhospitals.co.il/fields/pain-clinic/about/", "https://www.raphaelhospitals.co.il/en/international-department/about/", "https://www.raphaelhospitals.co.il/fields/heart-catheterization-clinic/about/", "https://www.raphaelhospitals.co.il/en/about/aboutus/", "https://www.raphaelhospitals.co.il/en/contact/"]</t>
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>1.486991509625609e+16</v>
+        <v>4.572308251998205e+16</v>
       </c>
       <c r="AE52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF52" t="n">
         <v>0</v>
@@ -8685,7 +8913,7 @@
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/</t>
+          <t>https://professorneuman.com/he/</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr"/>
@@ -8695,19 +8923,23 @@
         <v>0</v>
       </c>
       <c r="AM52" t="inlineStr"/>
-      <c r="AN52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO52" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP52" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR52" t="inlineStr">
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
+      <c r="AP52" t="inlineStr"/>
+      <c r="AQ52" t="inlineStr"/>
+      <c r="AR52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV52" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -8722,7 +8954,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>תמר גרין</t>
+          <t>נעמה מימון</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8753,7 +8985,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>office@keshet-refua.co.il</t>
+          <t>office@medicaltop.co.il</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -8766,7 +8998,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://keshet-refua.co.il/doctors/dr-tamar-green/</t>
+          <t>https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -8776,17 +9008,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>פיזיותרפיה אסתטיקה פודקסטים קליניקות וססיות להשכרה צור קשר זימון תור ד"ר תמר גרין מומחית לגינקולוגיה ומיילדות מעקב הריון, סקירת הריון מוקדמת ומאוחרת, בדיקות אולטרסאונד אבחנתיות, גיל המעבר ובדיקות גינקולוגיות 073-3214111 office@keshet-refua.co.il לזימון תור &gt; תחומי מומחיות מעקב הריון בדיקות אולטרהסאונד אבחנתיות שקיפות עורפית סקירת מערכות מוקדמת ומאוחרת מעקבי גדילה הדמיית אגן והדמיה תלת מימדית של הרחם טיפולי גינקולוגיה פרטית התקנים תוך רח</t>
+          <t xml:space="preserve">ד"ר נעמה מימון: מומחית ברפואת נשים - MedicalTop Search Close Facebook 073-3310444 סנטר הגליל רחוב האגס 1, שער הרימון, קומה שניה. ראש פינה. office@medicaltop.co.il לקביעת תור דף הבית אודות תחומי פעילות הצוות שלנו יצירת קשר Menu דף הבית אודות תחומי פעילות הצוות שלנו יצירת קשר ד"ר נעמה מימון: מומחית ברפואת נשים דף הבית / רופאים / ד"ר נעמה מימון: מומחית ברפואת </t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>"תמר גרין"</t>
+          <t>"נעמה מימון"</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>official_text</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -8803,39 +9035,39 @@
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-09-05T00:09:39.798497+00:00</t>
+          <t>2026-09-04T05:17:30.924388+00:00</t>
         </is>
       </c>
       <c r="W53" t="n">
+        <v>4</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>["https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fn.mh.mymwn.2025%2F", "https://www.facebook.com/SNMaesthetic/services/", "https://www.doctorita.co.il/experts/152626", "https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/", "https://medicaltop.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://medicaltop.co.il/%D7%94%D7%A6%D7%95%D7%95%D7%AA-%D7%A9%D7%9C%D7%A0%D7%95/", "https://medicaltop.co.il/wp-content/uploads/2024/04/אודות.jpg"]</t>
+        </is>
+      </c>
+      <c r="AD53" t="n">
+        <v>4.460974528876827e+16</v>
+      </c>
+      <c r="AE53" t="n">
         <v>2</v>
-      </c>
-      <c r="X53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>ddgs:bing</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>["https://www.medreviews.co.il/provider/dr-green-tamar", "https://keshet-refua.co.il/doctors/dr-tamar-green/", "https://keshet-refua.co.il/about-us/", "https://keshet-refua.co.il/contact-us/", "https://keshet-refua.co.il/clinics-for-rent-sessional-clinics-for-rent/", "https://keshet-refua.co.il/about-us/#contact-keshet-medical-center", "https://keshet-refua.co.il/areas_of_expertise/child-psychology-clinic/", "https://keshet-refua.co.il/doctors/private-clinical-dietician-jerusalem/", "https://keshet-refua.co.il/contact-us/#contact-keshet-medical-center", "https://keshet-refua.co.il/clinics-for-rent-sessional-clinics-for-rent/#contact-keshet-medical-center", "https://keshet-refua.co.il/doctors/dr-tamar-green-private-gynecologist-in-jerusalem/", "https://wayzee.co.il/", "https://keshet-refua.co.il/treatments/menstrual-arrangement-before-the-wedding-private-womens-clinic-private-gynecologist/", "https://keshet-refua.co.il/areas_of_expertise/child-psychology-clinic/#contact-keshet-medical-center", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2F61558661827898%2F", "https://www.facebook.com/public/%D7%AA%D7%9E%D7%A8-%D7%92%D7%A8%D7%99%D7%9F/", "https://www.medreviews.co.il/provider/dr-green-tamar/treatment/gynecologist-clinic", "https://www.szmc.org.il/doctors/grin-tamar/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
-        </is>
-      </c>
-      <c r="AD53" t="n">
-        <v>1.483997756485766e+16</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>1</v>
       </c>
       <c r="AF53" t="n">
         <v>0</v>
@@ -8843,7 +9075,7 @@
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>https://keshet-refua.co.il/doctors/dr-tamar-green/</t>
+          <t>https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/</t>
         </is>
       </c>
       <c r="AI53" t="inlineStr"/>
@@ -8853,19 +9085,23 @@
         <v>0</v>
       </c>
       <c r="AM53" t="inlineStr"/>
-      <c r="AN53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP53" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR53" t="inlineStr">
+      <c r="AN53" t="inlineStr"/>
+      <c r="AO53" t="inlineStr"/>
+      <c r="AP53" t="inlineStr"/>
+      <c r="AQ53" t="inlineStr"/>
+      <c r="AR53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS53" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT53" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV53" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -8880,7 +9116,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>אבי צפריר</t>
+          <t>תמר גרין</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8911,7 +9147,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>ivfrec@szmc.org.il</t>
+          <t>office@keshet-refua.co.il</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -8920,11 +9156,11 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/tsafrir-avi/</t>
+          <t>https://keshet-refua.co.il/doctors/dr-tamar-green/</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -8934,17 +9170,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t xml:space="preserve">h عربيه Русский צרו קשר צרו קשר אזור אישי אזור אישי רופאים בשערי צדק ד"ר  אבי צפריר רופא בכיר Dr.  Avi Tsafrir התמחות: גינקולוגיה ויילוד תת התמחות: הפריה חוץ גופית תחומים נוספים: שימור פוריות פוריות הגבר פוריות האשה עוד ivfrec@szmc.org.il ivfrec@szmc.org.il נסיון מקצועי מומחה ביילוד ובגינקולוגיה משנת 2005 רופא בכיר להפריה חוץ גופית בשערי צדק משנת 2005 תפקידים ציבוריים חבר ועד האגודה הישראלית לחקר הפוריות משנת 2022 לימודים והכשרה פקולטה </t>
+          <t>פיזיותרפיה אסתטיקה פודקסטים קליניקות וססיות להשכרה צור קשר זימון תור ד"ר תמר גרין מומחית לגינקולוגיה ומיילדות מעקב הריון, סקירת הריון מוקדמת ומאוחרת, בדיקות אולטרסאונד אבחנתיות, גיל המעבר ובדיקות גינקולוגיות 073-3214111 office@keshet-refua.co.il לזימון תור &gt; תחומי מומחיות מעקב הריון בדיקות אולטרהסאונד אבחנתיות שקיפות עורפית סקירת מערכות מוקדמת ומאוחרת מעקבי גדילה הדמיית אגן והדמיה תלת מימדית של הרחם טיפולי גינקולוגיה פרטית התקנים תוך רח</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>"אבי צפריר"</t>
+          <t>"תמר גרין"</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>official_text</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -8961,11 +9197,11 @@
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-09-03T20:26:52.799327+00:00</t>
+          <t>2026-09-05T00:09:39.798497+00:00</t>
         </is>
       </c>
       <c r="W54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X54" t="n">
         <v>0</v>
@@ -8977,7 +9213,7 @@
         <v>6</v>
       </c>
       <c r="AA54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
@@ -8986,14 +9222,14 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>["https://www.infomed.co.il/experts/73913/", "https://he.hadassah.org.il/doctor/dr-avi-tsafrir-gaadaabqaa2aaoiag4adaabyaa======/", "https://www.doctors.co.il/expert/obstetrics-and-gynecologists/80043972/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fbyzpryr%2F", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A6%D7%A4%D7%A8%D7%99%D7%A8-%D7%90%D7%91%D7%99/", "https://drtor.co.il/doctor/3910", "https://www.szmc.org.il/doctors/tsafrir-avi/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.clalit.co.il/he/sefersherut/pages/doctordetails.aspx", "https://docsrated.com/doctors/אבי-צפריר", "https://www.doctorita.co.il/experts/44804"]</t>
+          <t>["https://www.medreviews.co.il/provider/dr-green-tamar", "https://keshet-refua.co.il/doctors/dr-tamar-green/", "https://keshet-refua.co.il/about-us/", "https://keshet-refua.co.il/contact-us/", "https://keshet-refua.co.il/clinics-for-rent-sessional-clinics-for-rent/", "https://keshet-refua.co.il/about-us/#contact-keshet-medical-center", "https://keshet-refua.co.il/areas_of_expertise/child-psychology-clinic/", "https://keshet-refua.co.il/doctors/private-clinical-dietician-jerusalem/", "https://keshet-refua.co.il/contact-us/#contact-keshet-medical-center", "https://keshet-refua.co.il/clinics-for-rent-sessional-clinics-for-rent/#contact-keshet-medical-center", "https://keshet-refua.co.il/doctors/dr-tamar-green-private-gynecologist-in-jerusalem/", "https://wayzee.co.il/", "https://keshet-refua.co.il/treatments/menstrual-arrangement-before-the-wedding-private-womens-clinic-private-gynecologist/", "https://keshet-refua.co.il/areas_of_expertise/child-psychology-clinic/#contact-keshet-medical-center", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2F61558661827898%2F", "https://www.facebook.com/public/%D7%AA%D7%9E%D7%A8-%D7%92%D7%A8%D7%99%D7%9F/", "https://www.medreviews.co.il/provider/dr-green-tamar/treatment/gynecologist-clinic", "https://www.szmc.org.il/doctors/grin-tamar/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>1.976554868161774e+16</v>
+        <v>4.451993269457299e+16</v>
       </c>
       <c r="AE54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF54" t="n">
         <v>0</v>
@@ -9001,7 +9237,7 @@
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/tsafrir-avi/</t>
+          <t>https://keshet-refua.co.il/doctors/dr-tamar-green/</t>
         </is>
       </c>
       <c r="AI54" t="inlineStr"/>
@@ -9011,19 +9247,23 @@
         <v>0</v>
       </c>
       <c r="AM54" t="inlineStr"/>
-      <c r="AN54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO54" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP54" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR54" t="inlineStr">
+      <c r="AN54" t="inlineStr"/>
+      <c r="AO54" t="inlineStr"/>
+      <c r="AP54" t="inlineStr"/>
+      <c r="AQ54" t="inlineStr"/>
+      <c r="AR54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV54" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -9038,17 +9278,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>אירינה דורפמן אלמוג</t>
+          <t>אבי צפריר</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>family_doctor</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -9069,20 +9309,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>dr.irenadorfman@gmail.com</t>
+          <t>ivfrec@szmc.org.il</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
+          <t>https://www.szmc.org.il/doctors/tsafrir-avi/</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -9092,12 +9332,12 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>מוג אירינה כרטיס עסק: ד"ר דורפמן אלמוג אירינה » תחום פעילות: בריאות וספורט » רופא » תאור העסק: רופאת משפחה עצמאית קופת חולים לאומית. » איש קשר: אירנה דורפמן » טלפונים: טלפון: 077-7997456 נייד: 054-4616457 » אתר: » מייל: dr.irenadorfman@gmail.com » כתובת: בן גוריון 123 יהוד, מיקוד: 56209 כלים מחשבונים לעסקים מדריכי ניהול עסק, הקמת עסק נושאי האתר הנהלת חשבונות הפקת חשבוניות חשבונית אלקטרונית ניהול לקוחות שותפים עסקיים אילת סיטי - מדריך הע</t>
+          <t xml:space="preserve">h عربيه Русский צרו קשר צרו קשר אזור אישי אזור אישי רופאים בשערי צדק ד"ר  אבי צפריר רופא בכיר Dr.  Avi Tsafrir התמחות: גינקולוגיה ויילוד תת התמחות: הפריה חוץ גופית תחומים נוספים: שימור פוריות פוריות הגבר פוריות האשה עוד ivfrec@szmc.org.il ivfrec@szmc.org.il נסיון מקצועי מומחה ביילוד ובגינקולוגיה משנת 2005 רופא בכיר להפריה חוץ גופית בשערי צדק משנת 2005 תפקידים ציבוריים חבר ועד האגודה הישראלית לחקר הפוריות משנת 2022 לימודים והכשרה פקולטה </t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>"אירינה דורפמן אלמוג"</t>
+          <t>"אבי צפריר"</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -9107,32 +9347,32 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>[{"email": "info@flex.co.il", "confidence": 80, "source_url": "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "identity_url": "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "evidence": "info@flex.co.il", "matched_query": "\"אירינה דורפמן אלמוג\"", "extraction_method": "linked_mailto"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-09-04T19:17:26.299485+00:00</t>
+          <t>2026-09-03T20:26:52.799327+00:00</t>
         </is>
       </c>
       <c r="W55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z55" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AA55" t="n">
         <v>2</v>
@@ -9144,14 +9384,14 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>["https://www.dunsguide.co.il/C7195b21475cb11a3e5b86def04a3e20c_רופאים/דורפמן_אלמוג_אירינה/", "https://medpage.co.il/doctors/%D7%90%D7%99%D7%A8%D7%A0%D7%94-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-20871/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94/", "https://www.beok.co.il/doctors/Doctors-129241/", "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "https://www.flex.co.il/100_General/005_GeneralPages/006_About.aspx", "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "https://www.flex.co.il/100_General/900_DifferentStuff/900_ForTheCommunity.aspx"]</t>
+          <t>["https://www.infomed.co.il/experts/73913/", "https://he.hadassah.org.il/doctor/dr-avi-tsafrir-gaadaabqaa2aaoiag4adaabyaa======/", "https://www.doctors.co.il/expert/obstetrics-and-gynecologists/80043972/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fbyzpryr%2F", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A6%D7%A4%D7%A8%D7%99%D7%A8-%D7%90%D7%91%D7%99/", "https://drtor.co.il/doctor/3910", "https://www.szmc.org.il/doctors/tsafrir-avi/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.clalit.co.il/he/sefersherut/pages/doctordetails.aspx", "https://docsrated.com/doctors/אבי-צפריר", "https://www.doctorita.co.il/experts/44804"]</t>
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>1.606120288060151e+16</v>
+        <v>5.929664604485323e+16</v>
       </c>
       <c r="AE55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF55" t="n">
         <v>0</v>
@@ -9159,7 +9399,7 @@
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
+          <t>https://www.szmc.org.il/doctors/tsafrir-avi/</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr"/>
@@ -9169,21 +9409,25 @@
         <v>0</v>
       </c>
       <c r="AM55" t="inlineStr"/>
-      <c r="AN55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP55" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ55" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>PERSON</t>
+      <c r="AN55" t="inlineStr"/>
+      <c r="AO55" t="inlineStr"/>
+      <c r="AP55" t="inlineStr"/>
+      <c r="AQ55" t="inlineStr"/>
+      <c r="AR55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS55" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT55" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV55" t="inlineStr">
+        <is>
+          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
       </c>
     </row>
@@ -9196,7 +9440,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>אלון שלב</t>
+          <t>אירינה דורפמן אלמוג</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9227,7 +9471,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>alonshalev31@gmail.com</t>
+          <t>dr.irenadorfman@gmail.com</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -9240,7 +9484,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://pain.coi.co.il/</t>
+          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -9250,12 +9494,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>הודעה לבעלי האתר תקופת הניסיון הסתיימה, יש ליצור מנוי דרך ממשק ניהול האתר. האתר נכנס לרשימת המחיקה ויימחק בקרוב לחץ כאן אם אינך זוכר את כתובת ממשק ניהול האתר שלך. דר אלון שלב - רופא כאב טלפון: 054-6221105 מייל: alonshalev31@gmail.com כתובת: ילדי טהרן 8, ראשון לציון ד"ר אלון שלב מומחה ברפואת המשפחה רופא כאב דף הבית אודות צור קשר אל תחכו - הזמינו תור לרופא עוד היום.. לייעוץ ראשוני ללא עלות והזמנת תורים מלאו פרטים או התקשרו: 05462</t>
+          <t>מוג אירינה כרטיס עסק: ד"ר דורפמן אלמוג אירינה » תחום פעילות: בריאות וספורט » רופא » תאור העסק: רופאת משפחה עצמאית קופת חולים לאומית. » איש קשר: אירנה דורפמן » טלפונים: טלפון: 077-7997456 נייד: 054-4616457 » אתר: » מייל: dr.irenadorfman@gmail.com » כתובת: בן גוריון 123 יהוד, מיקוד: 56209 כלים מחשבונים לעסקים מדריכי ניהול עסק, הקמת עסק נושאי האתר הנהלת חשבונות הפקת חשבוניות חשבונית אלקטרונית ניהול לקוחות שותפים עסקיים אילת סיטי - מדריך הע</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>"אלון שלב"</t>
+          <t>"אירינה דורפמן אלמוג"</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -9265,11 +9509,11 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "info@flex.co.il", "confidence": 80, "source_url": "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "identity_url": "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "evidence": "info@flex.co.il", "matched_query": "\"אירינה דורפמן אלמוג\"", "extraction_method": "linked_mailto"}]</t>
         </is>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T56" t="n">
         <v>0</v>
@@ -9277,23 +9521,23 @@
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-09-04T19:37:15.755041+00:00</t>
+          <t>2026-09-04T19:17:26.299485+00:00</t>
         </is>
       </c>
       <c r="W56" t="n">
         <v>2</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z56" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
@@ -9302,11 +9546,11 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>["https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr.shalev.pain%2F&amp;is_from_rle", "https://www.bgu.ac.il/people/shalevn/", "https://www.bgu.ac.il/en/people/shalevn/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fdr.shalev.pain%2F", "https://www.medreviews.co.il/search/pain-management/center/rishon-lezion", "https://pain.coi.co.il/", "https://pain.coi.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA.htm", "https://pain.coi.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8.htm"]</t>
+          <t>["https://www.dunsguide.co.il/C7195b21475cb11a3e5b86def04a3e20c_רופאים/דורפמן_אלמוג_אירינה/", "https://medpage.co.il/doctors/%D7%90%D7%99%D7%A8%D7%A0%D7%94-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-20871/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94/", "https://www.beok.co.il/doctors/Doctors-129241/", "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "https://www.flex.co.il/100_General/005_GeneralPages/006_About.aspx", "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "https://www.flex.co.il/100_General/900_DifferentStuff/900_ForTheCommunity.aspx"]</t>
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>1.606120288060151e+16</v>
+        <v>4.818360864180453e+16</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9317,7 +9561,7 @@
       <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>https://pain.coi.co.il/</t>
+          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr"/>
@@ -9327,19 +9571,23 @@
         <v>0</v>
       </c>
       <c r="AM56" t="inlineStr"/>
-      <c r="AN56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP56" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ56" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR56" t="inlineStr">
+      <c r="AN56" t="inlineStr"/>
+      <c r="AO56" t="inlineStr"/>
+      <c r="AP56" t="inlineStr"/>
+      <c r="AQ56" t="inlineStr"/>
+      <c r="AR56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU56" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV56" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -9354,7 +9602,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>אמיר צבעוני</t>
+          <t>אלון שלב</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9385,7 +9633,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>healtms@gmail.com</t>
+          <t>alonshalev31@gmail.com</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -9398,7 +9646,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://www.drzivony.co.il/</t>
+          <t>https://pain.coi.co.il/</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -9408,12 +9656,12 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>"ר אמיר צבעוני ד"ר אמיר צבעוני רופא משפחה מומחה העוסק בטיפול בכאב כרוני בגישת גוף-נפש ללא שימוש בתרופות או בפרוצדורות רפואיות. הטיפול מבוסס מחקר בתחום מדעי המח והכאב. ניתן לקרוא עליי עוד ב דף האודות . טלפון: 051-2303120 healtms@gmail.com קליניקה בגבעת עדה (סמוך לבנימינה) ניתן ליצור איתי קשר גם ב דף יצירת הקשר פוסטים אחרונים על הענק הירוק והדחקת רגשות לאותת עם המגבים רגישות יתר לאחר פציעה אזהרת טריגר בקשת סליחה מעצמי חפש: חיפוש בית אודות</t>
+          <t>הודעה לבעלי האתר תקופת הניסיון הסתיימה, יש ליצור מנוי דרך ממשק ניהול האתר. האתר נכנס לרשימת המחיקה ויימחק בקרוב לחץ כאן אם אינך זוכר את כתובת ממשק ניהול האתר שלך. דר אלון שלב - רופא כאב טלפון: 054-6221105 מייל: alonshalev31@gmail.com כתובת: ילדי טהרן 8, ראשון לציון ד"ר אלון שלב מומחה ברפואת המשפחה רופא כאב דף הבית אודות צור קשר אל תחכו - הזמינו תור לרופא עוד היום.. לייעוץ ראשוני ללא עלות והזמנת תורים מלאו פרטים או התקשרו: 05462</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>"אמיר צבעוני"</t>
+          <t>"אלון שלב"</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -9435,7 +9683,7 @@
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-09-03T23:00:56.706890+00:00</t>
+          <t>2026-09-04T19:37:15.755041+00:00</t>
         </is>
       </c>
       <c r="W57" t="n">
@@ -9445,10 +9693,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Z57" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -9460,11 +9708,11 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>["https://www.drzivony.co.il/", "https://www.drzivony.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
+          <t>["https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr.shalev.pain%2F&amp;is_from_rle", "https://www.bgu.ac.il/people/shalevn/", "https://www.bgu.ac.il/en/people/shalevn/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fdr.shalev.pain%2F", "https://www.medreviews.co.il/search/pain-management/center/rishon-lezion", "https://pain.coi.co.il/", "https://pain.coi.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA.htm", "https://pain.coi.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8.htm"]</t>
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>1.605950830338262e+16</v>
+        <v>4.818360864180453e+16</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9475,7 +9723,7 @@
       <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>https://www.drzivony.co.il/</t>
+          <t>https://pain.coi.co.il/</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr"/>
@@ -9485,19 +9733,23 @@
         <v>0</v>
       </c>
       <c r="AM57" t="inlineStr"/>
-      <c r="AN57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP57" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ57" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR57" t="inlineStr">
+      <c r="AN57" t="inlineStr"/>
+      <c r="AO57" t="inlineStr"/>
+      <c r="AP57" t="inlineStr"/>
+      <c r="AQ57" t="inlineStr"/>
+      <c r="AR57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU57" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV57" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -9512,7 +9764,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>בתיה קורנבוים</t>
+          <t>אמיר צבעוני</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9543,7 +9795,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>batyakornboim@gmail.com</t>
+          <t>healtms@gmail.com</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -9556,7 +9808,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://www.dr-batya-kornboim.com/</t>
+          <t>https://www.drzivony.co.il/</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -9566,12 +9818,12 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>שקל בחיפה אודות חוות דעת יצירת קשר כתבות ופרסומים תפריט ד״ר בתיה קורנבוים - מומחית ברפואת משפחה ורפואת השמנה [תיאור המרפאה יתווסף בהמשך] טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו חיפה 3570901 IL 052-567-1100 batyakornboim@gmail.com התמחויות רפואיות עיקריות: [פירוט תחומי הטיפול יתווסף בהמשך] מידע מעשי: יצירת קשר: טלפון 052-567-1100 או וואטסאפ 052-567-1100 מיקום: טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו , חיפה סוג</t>
+          <t>"ר אמיר צבעוני ד"ר אמיר צבעוני רופא משפחה מומחה העוסק בטיפול בכאב כרוני בגישת גוף-נפש ללא שימוש בתרופות או בפרוצדורות רפואיות. הטיפול מבוסס מחקר בתחום מדעי המח והכאב. ניתן לקרוא עליי עוד ב דף האודות . טלפון: 051-2303120 healtms@gmail.com קליניקה בגבעת עדה (סמוך לבנימינה) ניתן ליצור איתי קשר גם ב דף יצירת הקשר פוסטים אחרונים על הענק הירוק והדחקת רגשות לאותת עם המגבים רגישות יתר לאחר פציעה אזהרת טריגר בקשת סליחה מעצמי חפש: חיפוש בית אודות</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>"בתיה קורנבוים"</t>
+          <t>"אמיר צבעוני"</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -9593,7 +9845,7 @@
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-09-03T23:52:50.148875+00:00</t>
+          <t>2026-09-03T23:00:56.706890+00:00</t>
         </is>
       </c>
       <c r="W58" t="n">
@@ -9618,11 +9870,11 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>["https://www.dr-batya-kornboim.com/", "https://www.dr-batya-kornboim.com/#%D7%90%D7%95%D7%93%D7%95%D7%AA"]</t>
+          <t>["https://www.drzivony.co.il/", "https://www.drzivony.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>1.605950830338262e+16</v>
+        <v>4.817852491014786e+16</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9633,7 +9885,7 @@
       <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>https://www.dr-batya-kornboim.com/</t>
+          <t>https://www.drzivony.co.il/</t>
         </is>
       </c>
       <c r="AI58" t="inlineStr"/>
@@ -9643,19 +9895,23 @@
         <v>0</v>
       </c>
       <c r="AM58" t="inlineStr"/>
-      <c r="AN58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP58" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ58" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR58" t="inlineStr">
+      <c r="AN58" t="inlineStr"/>
+      <c r="AO58" t="inlineStr"/>
+      <c r="AP58" t="inlineStr"/>
+      <c r="AQ58" t="inlineStr"/>
+      <c r="AR58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU58" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV58" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -9670,7 +9926,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>שלומית שדמון</t>
+          <t>בתיה קורנבוים</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9701,7 +9957,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>shlomitshadmon@gmail.com</t>
+          <t>batyakornboim@gmail.com</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -9714,7 +9970,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
+          <t>https://www.dr-batya-kornboim.com/</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -9724,12 +9980,12 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>ם ופעילויות כנסים והשתלמויות הרצאות מהכנסים מטפלי.ות איט"ם מטפלי.ות איט"ם פיזיותרפיסטים.ית איט"ם מרפאות ציבוריות הצטרפות והתמחות צור קשר פרטי התקשרות טלפון 054-9145177 כתובת אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אימייל shlomitshadmon@gmail.com שדמון שלומית (MD) – תל אביב מקצוע:  רופאת משפחה, מוסמכת ביעוץ וטיפול מיני. התמחות: מטפלת מינית איזור טיפול: תל אביב אודותי אני רופאת משפחה ותיקה, מדריכה קלינית ומרצה בנושאי בריאות האישה, מיניות ה</t>
+          <t>שקל בחיפה אודות חוות דעת יצירת קשר כתבות ופרסומים תפריט ד״ר בתיה קורנבוים - מומחית ברפואת משפחה ורפואת השמנה [תיאור המרפאה יתווסף בהמשך] טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו חיפה 3570901 IL 052-567-1100 batyakornboim@gmail.com התמחויות רפואיות עיקריות: [פירוט תחומי הטיפול יתווסף בהמשך] מידע מעשי: יצירת קשר: טלפון 052-567-1100 או וואטסאפ 052-567-1100 מיקום: טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו , חיפה סוג</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>"שלומית שדמון"</t>
+          <t>"בתיה קורנבוים"</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -9739,11 +9995,11 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "identity_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "evidence": "mail.com אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"שלומית שדמון\"", "extraction_method": "direct_text"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T59" t="n">
         <v>0</v>
@@ -9751,7 +10007,7 @@
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-09-04T15:25:57.140597+00:00</t>
+          <t>2026-09-03T23:52:50.148875+00:00</t>
         </is>
       </c>
       <c r="W59" t="n">
@@ -9761,10 +10017,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -9776,11 +10032,11 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>["https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA/", "https://moonbellboutique.com/index/%D7%93%D7%A8-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%A9%D7%93%D7%9E%D7%95%D7%9F/", "https://moonbellboutique.com/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/", "https://www.infomed.co.il/experts/145161/", "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
+          <t>["https://www.dr-batya-kornboim.com/", "https://www.dr-batya-kornboim.com/#%D7%90%D7%95%D7%93%D7%95%D7%AA"]</t>
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>1.482924524247139e+16</v>
+        <v>4.817852491014786e+16</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9791,7 +10047,7 @@
       <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
+          <t>https://www.dr-batya-kornboim.com/</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr"/>
@@ -9801,19 +10057,23 @@
         <v>0</v>
       </c>
       <c r="AM59" t="inlineStr"/>
-      <c r="AN59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP59" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ59" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR59" t="inlineStr">
+      <c r="AN59" t="inlineStr"/>
+      <c r="AO59" t="inlineStr"/>
+      <c r="AP59" t="inlineStr"/>
+      <c r="AQ59" t="inlineStr"/>
+      <c r="AR59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU59" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV59" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -9828,7 +10088,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>שרון שלמה קלייטמן</t>
+          <t>שלומית שדמון</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9859,7 +10119,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>sharon.kleitman@gmail.com</t>
+          <t>shlomitshadmon@gmail.com</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -9872,7 +10132,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
+          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -9882,12 +10142,12 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>ש קשר שיתוף שתפו במייל שתפו בפייסבוק שתפו בטוויטר שתפו בלינקדין ד"ר שרון קלייטמן מומחה ברפואת משפחה, MST - Mind Set Technique, רפואה אינטגרטיבית, IMS - דיקור יבש, תזונה אינטגרטיבית. נייד 052-8325580 פקס 08-6560357 דוא"ל sharon.kleitman@gmail.com אתר www.integrative-med.com שלח/י לי sms פייסבוק אודות ד"ר שרון קלייטמן מומחה ברפואת משפחה, סיים את לימודי הרפואה באוניברסיטת בן גוריון, נשוי ואב לארבעה, מתגורר בקיבוץ שדה בוקר. עוסק בפיתוח והקנ</t>
+          <t>ם ופעילויות כנסים והשתלמויות הרצאות מהכנסים מטפלי.ות איט"ם מטפלי.ות איט"ם פיזיותרפיסטים.ית איט"ם מרפאות ציבוריות הצטרפות והתמחות צור קשר פרטי התקשרות טלפון 054-9145177 כתובת אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אימייל shlomitshadmon@gmail.com שדמון שלומית (MD) – תל אביב מקצוע:  רופאת משפחה, מוסמכת ביעוץ וטיפול מיני. התמחות: מטפלת מינית איזור טיפול: תל אביב אודותי אני רופאת משפחה ותיקה, מדריכה קלינית ומרצה בנושאי בריאות האישה, מיניות ה</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>"שרון שלמה קלייטמן"</t>
+          <t>"שלומית שדמון"</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -9897,11 +10157,11 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "identity_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "evidence": "mail.com אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"שלומית שדמון\"", "extraction_method": "direct_text"}]</t>
         </is>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T60" t="n">
         <v>0</v>
@@ -9909,7 +10169,7 @@
       <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-09-04T15:41:54.743203+00:00</t>
+          <t>2026-09-04T15:25:57.140597+00:00</t>
         </is>
       </c>
       <c r="W60" t="n">
@@ -9922,10 +10182,10 @@
         <v>4</v>
       </c>
       <c r="Z60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
@@ -9934,11 +10194,11 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>["https://docsrated.com/doctors/שרון-קלייטמן", "https://www.dunsguide.co.il/Cb6a87819a48606a97ab6b3a3617e9370_רופאים/קלייטמן_שרון_שלמה/", "https://www.facebook.com/sharon.kleitman.md/directory_category/", "https://dns.dibiz.com/sharon-kleitman-md", "https://longevitepalmbeach.com"]</t>
+          <t>["https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA/", "https://moonbellboutique.com/index/%D7%93%D7%A8-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%A9%D7%93%D7%9E%D7%95%D7%9F/", "https://moonbellboutique.com/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/", "https://www.infomed.co.il/experts/145161/", "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>1.482924524247139e+16</v>
+        <v>4.448773572741416e+16</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -9949,7 +10209,7 @@
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
+          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
         </is>
       </c>
       <c r="AI60" t="inlineStr"/>
@@ -9959,19 +10219,23 @@
         <v>0</v>
       </c>
       <c r="AM60" t="inlineStr"/>
-      <c r="AN60" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP60" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ60" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR60" t="inlineStr">
+      <c r="AN60" t="inlineStr"/>
+      <c r="AO60" t="inlineStr"/>
+      <c r="AP60" t="inlineStr"/>
+      <c r="AQ60" t="inlineStr"/>
+      <c r="AR60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU60" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV60" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -9986,7 +10250,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>איה שלם</t>
+          <t>שרון שלמה קלייטמן</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10017,20 +10281,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>info@shrir-sheled.co.il</t>
+          <t>sharon.kleitman@gmail.com</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/</t>
+          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -10040,12 +10304,12 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>ד"ר איה שלם - אינדקס מטפלים ברפואת שריר שלד דלג לתוכן info@shrir-sheled.co.il בית רשימת המטפלים מאמרים מקצועיים אודות מקצוע המטפל רפואת משפחה פיזיותרפיה אוסטיאופתיה כירופרקטיקה אורתופדיה צרו קשר תפריט בית רשימת המטפלים מאמרים מקצועיים אודות מקצוע המטפל רפואת משפחה פיזיותרפי</t>
+          <t>ש קשר שיתוף שתפו במייל שתפו בפייסבוק שתפו בטוויטר שתפו בלינקדין ד"ר שרון קלייטמן מומחה ברפואת משפחה, MST - Mind Set Technique, רפואה אינטגרטיבית, IMS - דיקור יבש, תזונה אינטגרטיבית. נייד 052-8325580 פקס 08-6560357 דוא"ל sharon.kleitman@gmail.com אתר www.integrative-med.com שלח/י לי sms פייסבוק אודות ד"ר שרון קלייטמן מומחה ברפואת משפחה, סיים את לימודי הרפואה באוניברסיטת בן גוריון, נשוי ואב לארבעה, מתגורר בקיבוץ שדה בוקר. עוסק בפיתוח והקנ</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>"איה שלם"</t>
+          <t>"שרון שלמה קלייטמן"</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -10067,7 +10331,7 @@
       <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-09-04T18:58:24.569451+00:00</t>
+          <t>2026-09-04T15:41:54.743203+00:00</t>
         </is>
       </c>
       <c r="W61" t="n">
@@ -10077,13 +10341,13 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z61" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AA61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
@@ -10092,11 +10356,11 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>["https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%9C%D7%9D-%D7%90%D7%99%D7%94/", "https://medpage.co.il/doctors/16196-%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D-8959/", "https://www.doctorita.co.il/experts/124568", "https://drtor.co.il/doctor/19921", "http://me.doctorsonly.co.il/user/2636", "https://www.infomed.co.il/experts/74772/", "https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/", "https://eshkol.media/", "https://shrir-sheled.co.il/about/"]</t>
+          <t>["https://docsrated.com/doctors/שרון-קלייטמן", "https://www.dunsguide.co.il/Cb6a87819a48606a97ab6b3a3617e9370_רופאים/קלייטמן_שרון_שלמה/", "https://www.facebook.com/sharon.kleitman.md/directory_category/", "https://dns.dibiz.com/sharon-kleitman-md", "https://longevitepalmbeach.com"]</t>
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>1.606120288060151e+16</v>
+        <v>4.448773572741416e+16</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10107,7 +10371,7 @@
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/</t>
+          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
         </is>
       </c>
       <c r="AI61" t="inlineStr"/>
@@ -10117,19 +10381,185 @@
         <v>0</v>
       </c>
       <c r="AM61" t="inlineStr"/>
-      <c r="AN61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP61" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR61" t="inlineStr">
+      <c r="AN61" t="inlineStr"/>
+      <c r="AO61" t="inlineStr"/>
+      <c r="AP61" t="inlineStr"/>
+      <c r="AQ61" t="inlineStr"/>
+      <c r="AR61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU61" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV61" t="inlineStr">
+        <is>
+          <t>PERSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>13</v>
+      </c>
+      <c r="B62" t="n">
+        <v>6</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>איה שלם</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>family_doctor</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>moh</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>info@shrir-sheled.co.il</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>CLINIC_OR_ORGANIZATION</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>88</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>ד"ר איה שלם - אינדקס מטפלים ברפואת שריר שלד דלג לתוכן info@shrir-sheled.co.il בית רשימת המטפלים מאמרים מקצועיים אודות מקצוע המטפל רפואת משפחה פיזיותרפיה אוסטיאופתיה כירופרקטיקה אורתופדיה צרו קשר תפריט בית רשימת המטפלים מאמרים מקצועיים אודות מקצוע המטפל רפואת משפחה פיזיותרפי</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>"איה שלם"</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>direct_text</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S62" t="n">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-09-04T18:58:24.569451+00:00</t>
+        </is>
+      </c>
+      <c r="W62" t="n">
+        <v>2</v>
+      </c>
+      <c r="X62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>["https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%9C%D7%9D-%D7%90%D7%99%D7%94/", "https://medpage.co.il/doctors/16196-%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D-8959/", "https://www.doctorita.co.il/experts/124568", "https://drtor.co.il/doctor/19921", "http://me.doctorsonly.co.il/user/2636", "https://www.infomed.co.il/experts/74772/", "https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/", "https://eshkol.media/", "https://shrir-sheled.co.il/about/"]</t>
+        </is>
+      </c>
+      <c r="AD62" t="n">
+        <v>4.818360864180453e+16</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
+      <c r="AL62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM62" t="inlineStr"/>
+      <c r="AN62" t="inlineStr"/>
+      <c r="AO62" t="inlineStr"/>
+      <c r="AP62" t="inlineStr"/>
+      <c r="AQ62" t="inlineStr"/>
+      <c r="AR62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV62" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>

--- a/output/contacts_primary.xlsx
+++ b/output/contacts_primary.xlsx
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>5.943390679798868e+16</v>
+        <v>1.78301720393966e+17</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>5.929664604325891e+16</v>
+        <v>1.778899381297767e+17</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>5.929664604325891e+16</v>
+        <v>1.778899381297767e+17</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>5.563635925046515e+16</v>
+        <v>1.669090777513955e+17</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>4.822485035801138e+16</v>
+        <v>1.446745510740341e+17</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>4.822427849505779e+16</v>
+        <v>1.446728354851734e+17</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>5.945424172461531e+16</v>
+        <v>1.783627251738459e+17</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>4.822485035801146e+16</v>
+        <v>1.446745510740344e+17</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>5.929664604325891e+16</v>
+        <v>1.778899381297767e+17</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>4.822485035801146e+16</v>
+        <v>1.446745510740344e+17</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>4.822427849505779e+16</v>
+        <v>1.446728354851734e+17</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>4.819434796805247e+16</v>
+        <v>1.445830439041574e+17</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -4033,7 +4033,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>4.572308251998205e+16</v>
+        <v>1.371692475599462e+17</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>4.572308251998205e+16</v>
+        <v>1.371692475599462e+17</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4519,7 +4519,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>4.460974528717395e+16</v>
+        <v>1.338292358615219e+17</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>4.460974528717395e+16</v>
+        <v>1.338292358615219e+17</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>4.460974528717395e+16</v>
+        <v>1.338292358615219e+17</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>4.460974528717395e+16</v>
+        <v>1.338292358615219e+17</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5168,7 +5168,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>4.460974528717395e+16</v>
+        <v>1.338292358615219e+17</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>5.943390679798868e+16</v>
+        <v>1.78301720393966e+17</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>4.81943479680715e+16</v>
+        <v>1.445830439042145e+17</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5662,7 +5662,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>4.819377610511784e+16</v>
+        <v>1.445813283153535e+17</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5824,7 +5824,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>4.819377610511784e+16</v>
+        <v>1.445813283153535e+17</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5986,7 +5986,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>4.819377610511784e+16</v>
+        <v>1.445813283153535e+17</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -6148,7 +6148,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6310,7 +6310,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>5.56431375593407e+16</v>
+        <v>1.669294126780221e+17</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6472,7 +6472,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>5.929664604325891e+16</v>
+        <v>1.778899381297767e+17</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6634,7 +6634,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6796,7 +6796,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>4.819434796805247e+16</v>
+        <v>1.445830439041574e+17</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6958,7 +6958,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>4.572308251998205e+16</v>
+        <v>1.371692475599462e+17</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -7120,7 +7120,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>4.572308251998205e+16</v>
+        <v>1.371692475599462e+17</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7282,7 +7282,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>4.572308251998205e+16</v>
+        <v>1.371692475599462e+17</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7444,7 +7444,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>4.461540088176475e+16</v>
+        <v>1.338462026452943e+17</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7606,7 +7606,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>4.461482901883061e+16</v>
+        <v>1.338444870564918e+17</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7768,7 +7768,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>4.461482901883061e+16</v>
+        <v>1.338444870564918e+17</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7930,7 +7930,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>4.460974528717395e+16</v>
+        <v>1.338292358615219e+17</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>4.460974528717395e+16</v>
+        <v>1.338292358615219e+17</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -8254,7 +8254,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>4.45182381173541e+16</v>
+        <v>1.335547143520623e+17</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8416,7 +8416,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>4.451993269457299e+16</v>
+        <v>1.33559798083719e+17</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>5.929664604325891e+16</v>
+        <v>1.778899381297767e+17</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8740,7 +8740,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>4.572308251998205e+16</v>
+        <v>1.371692475599462e+17</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8902,7 +8902,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>4.572308251998205e+16</v>
+        <v>1.371692475599462e+17</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>4.460974528876827e+16</v>
+        <v>1.338292358663048e+17</v>
       </c>
       <c r="AE53" t="n">
         <v>2</v>
@@ -9226,7 +9226,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>4.451993269457299e+16</v>
+        <v>1.33559798083719e+17</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -9388,7 +9388,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>5.929664604485323e+16</v>
+        <v>1.778899381345597e+17</v>
       </c>
       <c r="AE55" t="n">
         <v>2</v>
@@ -9550,7 +9550,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>4.818360864180453e+16</v>
+        <v>1.445508259254136e+17</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9712,7 +9712,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>4.818360864180453e+16</v>
+        <v>1.445508259254136e+17</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9874,7 +9874,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -10036,7 +10036,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -10198,7 +10198,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>4.448773572741416e+16</v>
+        <v>1.334632071822425e+17</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -10360,7 +10360,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>4.448773572741416e+16</v>
+        <v>1.334632071822425e+17</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10522,7 +10522,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>4.818360864180453e+16</v>
+        <v>1.445508259254136e+17</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>

--- a/output/contacts_primary.xlsx
+++ b/output/contacts_primary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV62"/>
+  <dimension ref="A1:AV63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>1.78301720393966e+17</v>
+        <v>5.349051611818981e+17</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>1.445355747304436e+17</v>
+        <v>4.336067241913308e+17</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>1.445355747304436e+17</v>
+        <v>4.336067241913308e+17</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>1.445355747304436e+17</v>
+        <v>4.336067241913308e+17</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>1.445355747304436e+17</v>
+        <v>4.336067241913308e+17</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>1.778899381297767e+17</v>
+        <v>5.336698143893302e+17</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>1.778899381297767e+17</v>
+        <v>5.336698143893302e+17</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>1.669090777513955e+17</v>
+        <v>5.007272332541864e+17</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>1.446745510740341e+17</v>
+        <v>4.340236532221023e+17</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>1.446728354851734e+17</v>
+        <v>4.340185064555201e+17</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>1.783627251738459e+17</v>
+        <v>5.350881755215378e+17</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>1.446745510740344e+17</v>
+        <v>4.340236532221031e+17</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>1.778899381297767e+17</v>
+        <v>5.336698143893302e+17</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>1.445355747304436e+17</v>
+        <v>4.336067241913308e+17</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>1.445355747304436e+17</v>
+        <v>4.336067241913308e+17</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>1.445355747304436e+17</v>
+        <v>4.336067241913308e+17</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>1.446745510740344e+17</v>
+        <v>4.340236532221031e+17</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>1.446728354851734e+17</v>
+        <v>4.340185064555201e+17</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>1.445830439041574e+17</v>
+        <v>4.337491317124723e+17</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>1.445355747304436e+17</v>
+        <v>4.336067241913308e+17</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -4033,7 +4033,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>1.445355747304436e+17</v>
+        <v>4.336067241913308e+17</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>1.371692475599462e+17</v>
+        <v>4.115077426798385e+17</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>1.371692475599462e+17</v>
+        <v>4.115077426798385e+17</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4519,7 +4519,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>1.338292358615219e+17</v>
+        <v>4.014877075845656e+17</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>1.338292358615219e+17</v>
+        <v>4.014877075845656e+17</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>1.338292358615219e+17</v>
+        <v>4.014877075845656e+17</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>1.338292358615219e+17</v>
+        <v>4.014877075845656e+17</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5168,7 +5168,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>1.338292358615219e+17</v>
+        <v>4.014877075845656e+17</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>1.78301720393966e+17</v>
+        <v>5.349051611818981e+17</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5382,12 +5382,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>אוהד חורי</t>
+          <t>רחל דהן</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>ohadho@clalit.org.il</t>
+          <t>racheldahan@hotmail.com</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -5422,11 +5422,11 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
+          <t>https://www.hebpsy.net/showprofile.asp?id=18767</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -5436,17 +5436,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
+          <t>שית בהיפנוזה יועצת גמילה מעישון טיפול בהפרעות שינה, ושינוי הרגלי חיים. רכזת מחקר המחלקה לרפואת משפחה -חיפה מנהלת מרפאת לב הקריה, שירותי בריאות כללית, קרית אתא. טל: 0543130956 אתר אינטרנט http://hypnosis.99k.org ;      : racheldahan@hotmail.com "דוא"ל הפרטים המובאים בכרטיס האישי של רחל דהן, ובכללם פרטים בדבר התואר האקדמי וההכשרה המקצועית נוסחו על ידי רחל דהן ובאחריותו/ה. נצפים ביותר יומנו של עורך וידאו - עדויות מהשבעה באוקטובר / רוני אלפ</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>"אוהד חורי" יילוד site:clalit.co.il</t>
+          <t>"רחל דהן" רפואת משפחה</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>search_snippet</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -5458,12 +5458,12 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-09-09T23:21:42.073181+00:00</t>
+          <t>2026-09-10T13:53:25.006579+00:00</t>
         </is>
       </c>
       <c r="W31" t="n">
@@ -5473,37 +5473,37 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>ddgs:yahoo+ddgs:bing</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx", "https://www.doctorita.co.il/experts/94233", "https://www.ha-makom.co.il/author/vhdcvry/", "https://foody.co.il/author/ohad/", "https://knowmore.co.il/doctors/אוהד-חורי-2/", "https://stage.ha-makom.co.il/author/vhdcvry/", "https://www.facebook.com/YoldotBeilinson/videos/%D7%9E%D7%94-%D7%96%D7%95-%D7%9C%D7%99%D7%93%D7%AA-vbac-%D7%A9%D7%9B%D7%95%D7%9C%D7%9F-%D7%9E%D7%93%D7%91%D7%A8%D7%95%D7%AA-%D7%A2%D7%9C%D7%99%D7%94-%D7%A2%D7%95%D7%A9%D7%99%D7%9D-%D7%9C%D7%9B%D7%9F-%D7%A1%D7%93%D7%A8-%D7%91%D7%9E%D7%95%D7%A9%D7%92%D7%99%D7%9D-%D7%A2%D7%9D-%D7%93%D7%A8-%D7%90%D7%95%D7%94%D7%93-%D7%97%D7%95%D7%A8%D7%99-%D7%A9%D7%9B%D7%90%D7%9F-%D7%9B%D7%93%D7%99/1754039901764363/"]</t>
+          <t>["https://www.doctorita.co.il/experts/141424", "https://www.colbonews.co.il/health/166678/", "https://www.hebpsy.net/showprofile.asp?id=18767", "https://www.hebpsy.net/me.asp?id=72&amp;page=6", "https://www.hebpsy.net/pl.asp?cat=about", "https://www.hebpsy.net/me.asp?id=72", "https://www.hebpsy.net/sysMsg.asp?id=profile_about#p10", "https://www.hebpsy.net/sysMsg.asp?id=profile_about", "https://www.hebpsy.net/showprofile.asp?id=18767#profile", "https://www.hebpsy.net/me.asp?id=72&amp;page=6#contact", "https://www.hebpsy.net/sysMsg.asp?id=profile_promotPL", "https://www.hebpsy.net/me.asp?id=72#contact", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fraceldahan%2F", "https://www.facebook.com/public/%D7%A8%D7%97%D7%9C-%D7%93%D7%94%D7%9F/", "https://www.myheritage.com/names/%D7%A8%D7%97%D7%9C_%D7%93%D7%94%D7%9F", "https://gen.rlzm.co.il/persons/%D7%A8%D7%97%D7%9C-%D7%93%D7%94%D7%9F/"]</t>
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>1.445830439042145e+17</v>
+        <v>4.003947683133098e+17</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
+          <t>https://www.hebpsy.net/showprofile.asp?id=18767</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr"/>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
+          <t>רחל דהן - רופאה רחל דהן - רופאה דלג לתוכן ראשי - מקש קיצור 2 (לחץ Enter) דף הבית - מקש קיצור 1 (לחץ Enter) דלג לתפריט ראשי - מקש קיצור 5 (לחץ Enter) דלג לתיבת חיפוש - מקש קיצור 4 (לחץ Enter) צור קשר - מקש קיצור 9 (לחץ Enter) הצהרת נגישות - מקש קיצור 0 (לחץ Enter) סגור עזרה ראשונה נפשית - בהתנדבות אודות והצטרפות טיפול נפשי מוזל טיפול נפשי בתל אביב מטפלים בהסדר קופת חולים פנויים לקבלת מטופלים חדשים טיפול זוגי טיפול התנהגותי קוגניטיבי - CBT הדרכת הורים טיפול נפשי לילדים אבחון פסיכולוגי לילדים פסיכולוגית בתל אביב פסיכולוגים כניסה רישום צרו קשר חיפוש × × אימייל (דוא"ל) סיסמא שכחת את הסיסמה? הקלידו אימייל ולחצו כאן כניסה אני מסכימ.ה להצטרף לרשימת התפוצה לקבלת עדכונים ומידע שיווקי זכור אותי רישום משתמש חדש ביטול פסיכולוגיה עברית ראשי השער שלי תיבת מסרים כרטיס הביקור שלי הגדרות חשבון אודות פסיכולוגיה עברית שאלות נפוצות יציאה מאמרים המאמרים שלי הגשת טקסט לפרסום נבחרי העורכת אספרגר טיפולי המרה סקס טוב דיו רגשות חינוך מיני תסמונת טורט ניכור הורי רשימות קריאה הכותבים קטגוריות מאמרים מאמרים לפי נושאים ניוזלטר בלוג</t>
         </is>
       </c>
       <c r="AR31" t="n">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>אופיר אלמסי</t>
+          <t>אוהד חורי</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>ofiral@bgu.ac.il</t>
+          <t>ohadho@clalit.org.il</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -5606,17 +5606,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>بحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان אופיר אלמסי ד"ר אופיר אלמסי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ofiral@bgu.ac.il Cookies Settings</t>
+          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>"אופיר אלמסי"</t>
+          <t>"אוהד חורי" יילוד site:clalit.co.il</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -5633,36 +5633,36 @@
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-09-04T13:52:28.665114+00:00</t>
+          <t>2026-09-09T23:21:42.073181+00:00</t>
         </is>
       </c>
       <c r="W32" t="n">
+        <v>8</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA32" t="n">
         <v>2</v>
       </c>
-      <c r="X32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1</v>
-      </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/ofiral/", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/almasi-o.aspx", "https://www.bgu.ac.il/ar/people/ofiral/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx", "https://www.doctorita.co.il/experts/94233", "https://www.ha-makom.co.il/author/vhdcvry/", "https://foody.co.il/author/ohad/", "https://knowmore.co.il/doctors/אוהד-חורי-2/", "https://stage.ha-makom.co.il/author/vhdcvry/", "https://www.facebook.com/YoldotBeilinson/videos/%D7%9E%D7%94-%D7%96%D7%95-%D7%9C%D7%99%D7%93%D7%AA-vbac-%D7%A9%D7%9B%D7%95%D7%9C%D7%9F-%D7%9E%D7%93%D7%91%D7%A8%D7%95%D7%AA-%D7%A2%D7%9C%D7%99%D7%94-%D7%A2%D7%95%D7%A9%D7%99%D7%9D-%D7%9C%D7%9B%D7%9F-%D7%A1%D7%93%D7%A8-%D7%91%D7%9E%D7%95%D7%A9%D7%92%D7%99%D7%9D-%D7%A2%D7%9D-%D7%93%D7%A8-%D7%90%D7%95%D7%94%D7%93-%D7%97%D7%95%D7%A8%D7%99-%D7%A9%D7%9B%D7%90%D7%9F-%D7%9B%D7%93%D7%99/1754039901764363/"]</t>
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>1.445813283153535e+17</v>
+        <v>4.337491317126436e+17</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5673,20 +5673,28 @@
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr"/>
       <c r="AJ32" t="inlineStr"/>
       <c r="AK32" t="inlineStr"/>
-      <c r="AL32" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL32" t="inlineStr"/>
       <c r="AM32" t="inlineStr"/>
-      <c r="AN32" t="inlineStr"/>
-      <c r="AO32" t="inlineStr"/>
-      <c r="AP32" t="inlineStr"/>
-      <c r="AQ32" t="inlineStr"/>
+      <c r="AN32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
+        </is>
+      </c>
       <c r="AR32" t="n">
         <v>1</v>
       </c>
@@ -5714,7 +5722,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>אורנה רייכמן</t>
+          <t>אופיר אלמסי</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5745,7 +5753,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>oreich@szmc.org.il</t>
+          <t>ofiral@bgu.ac.il</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -5758,7 +5766,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
+          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -5768,12 +5776,12 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t xml:space="preserve">אזור אישי רופאים בשערי צדק ד"ר אורנה  רייכמן מנהלת יולדות א' Dr. Orna  Reichman התמחות: גינקולוגיה ויילוד תת התמחות: מחלות שפירות של העריה והלדן הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית משרד 02-6666708 משרד: 02-6666708 oreich@szmc.org.il oreich@szmc.org.il לימודים והכשרה תואר ראשון במדעי החיים באוניברסיטה העברית בירושלים בהצטיינות - 1993 לימודי הרפואה בבית ספר לרפואה של האוניברסיטה העברית הדסה - 1999 ההתמחות במיילדות וגניקולוגיה במרכז </t>
+          <t>بحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان אופיר אלמסי ד"ר אופיר אלמסי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ofiral@bgu.ac.il Cookies Settings</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>"אורנה רייכמן"</t>
+          <t>"אופיר אלמסי"</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -5795,36 +5803,36 @@
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-09-04T13:56:16.031154+00:00</t>
+          <t>2026-09-04T13:52:28.665114+00:00</t>
         </is>
       </c>
       <c r="W33" t="n">
         <v>2</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AA33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>["https://www.infomed.co.il/experts/149541/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A8%D7%99%D7%99%D7%9B%D7%9E%D7%9F-%D7%90%D7%95%D7%A8%D7%A0%D7%94/", "https://docsrated.com/doctors/אורנה-רייכמן", "https://www.doctorita.co.il/experts/95406", "https://drtor.co.il/doctor/23937", "https://drtor.co.il/cdn-cgi/l/email-protection#8cefe3e2f8edeff8cce8fef8e3fea2efe3a2e5e0", "https://www.beok.co.il/doctors/Doctors-1340/", "https://www.szmc.org.il/doctors/reichman-orna/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://drtor.co.il/cdn-cgi/l/email-protection#3b5854554f5a584f7b5f494f5449155854155257"]</t>
+          <t>["https://www.bgu.ac.il/people/ofiral/", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/almasi-o.aspx", "https://www.bgu.ac.il/ar/people/ofiral/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>1.445813283153535e+17</v>
+        <v>4.337439849460605e+17</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5835,7 +5843,7 @@
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
+          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr"/>
@@ -5876,7 +5884,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ארנון סמואלוב</t>
+          <t>אורנה רייכמן</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5907,7 +5915,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>smuelof@szmc.org.il</t>
+          <t>oreich@szmc.org.il</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -5920,7 +5928,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
+          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -5930,12 +5938,12 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>ופ' ארנון  סמואלוב רופא בכיר Prof. Arnon  Samueloff התמחות: גינקולוגיה ויילוד תת התמחות: מיילדות וסיבוכי הריון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 02-6666656 מחלקה: 02-6666656 smuelof@szmc.org.il smuelof@szmc.org.il נסיון מקצועי התמחות ברפואת האם והעובר, סן אנטוניו, ארה"ב רופא בכיר, מחלקת נשים ויולדות, המרכז הרפואי הדסה מנהל, מרפאת היריון בסיכון, קופת חולים לאומית מנהל, מרפאת סוכרת, קופת חולים</t>
+          <t xml:space="preserve">אזור אישי רופאים בשערי צדק ד"ר אורנה  רייכמן מנהלת יולדות א' Dr. Orna  Reichman התמחות: גינקולוגיה ויילוד תת התמחות: מחלות שפירות של העריה והלדן הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית משרד 02-6666708 משרד: 02-6666708 oreich@szmc.org.il oreich@szmc.org.il לימודים והכשרה תואר ראשון במדעי החיים באוניברסיטה העברית בירושלים בהצטיינות - 1993 לימודי הרפואה בבית ספר לרפואה של האוניברסיטה העברית הדסה - 1999 ההתמחות במיילדות וגניקולוגיה במרכז </t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>"ארנון סמואלוב"</t>
+          <t>"אורנה רייכמן"</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -5957,36 +5965,36 @@
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-09-04T14:35:26.198949+00:00</t>
+          <t>2026-09-04T13:56:16.031154+00:00</t>
         </is>
       </c>
       <c r="W34" t="n">
         <v>2</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>["https://docsrated.com/doctors/ארנון-סמואלוב", "https://www.infomed.co.il/experts/93587/", "https://www.doctorita.co.il/experts/47319", "https://www.beok.co.il/doctors/Doctors-116451/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A1%D7%9E%D7%95%D7%90%D7%9C%D7%95%D7%91-%D7%90%D7%A8%D7%A0%D7%95%D7%9F/", "https://www.szmc.org.il/doctors/samueloff-arnon/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
+          <t>["https://www.infomed.co.il/experts/149541/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A8%D7%99%D7%99%D7%9B%D7%9E%D7%9F-%D7%90%D7%95%D7%A8%D7%A0%D7%94/", "https://docsrated.com/doctors/אורנה-רייכמן", "https://www.doctorita.co.il/experts/95406", "https://drtor.co.il/doctor/23937", "https://drtor.co.il/cdn-cgi/l/email-protection#8cefe3e2f8edeff8cce8fef8e3fea2efe3a2e5e0", "https://www.beok.co.il/doctors/Doctors-1340/", "https://www.szmc.org.il/doctors/reichman-orna/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://drtor.co.il/cdn-cgi/l/email-protection#3b5854554f5a584f7b5f494f5449155854155257"]</t>
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>1.445813283153535e+17</v>
+        <v>4.337439849460605e+17</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5997,7 +6005,7 @@
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
+          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr"/>
@@ -6038,7 +6046,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>גלי פריאנטה</t>
+          <t>ארנון סמואלוב</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -6069,7 +6077,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>galipa@bgu.ac.il</t>
+          <t>smuelof@szmc.org.il</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -6082,7 +6090,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
+          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -6092,12 +6100,12 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>ث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان גלי פריאנטה פרופ' גלי פריאנטה Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section galipa@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0001-6484-3769 Orcid Number Cookies Settings</t>
+          <t>ופ' ארנון  סמואלוב רופא בכיר Prof. Arnon  Samueloff התמחות: גינקולוגיה ויילוד תת התמחות: מיילדות וסיבוכי הריון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 02-6666656 מחלקה: 02-6666656 smuelof@szmc.org.il smuelof@szmc.org.il נסיון מקצועי התמחות ברפואת האם והעובר, סן אנטוניו, ארה"ב רופא בכיר, מחלקת נשים ויולדות, המרכז הרפואי הדסה מנהל, מרפאת היריון בסיכון, קופת חולים לאומית מנהל, מרפאת סוכרת, קופת חולים</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>"גלי פריאנטה"</t>
+          <t>"ארנון סמואלוב"</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -6119,36 +6127,36 @@
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-09-03T23:09:10.396904+00:00</t>
+          <t>2026-09-04T14:35:26.198949+00:00</t>
         </is>
       </c>
       <c r="W35" t="n">
         <v>2</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y35" t="n">
         <v>6</v>
       </c>
       <c r="Z35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/galipa/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-%D7%92%D7%9C%D7%99/", "https://medpage.co.il/doctors/%D7%92%D7%9C%D7%99-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-25448/", "https://www.doctorita.co.il/experts/131973", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/pariente-g.aspx", "https://www.bgu.ac.il/ar/people/galipa/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://docsrated.com/doctors/ארנון-סמואלוב", "https://www.infomed.co.il/experts/93587/", "https://www.doctorita.co.il/experts/47319", "https://www.beok.co.il/doctors/Doctors-116451/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A1%D7%9E%D7%95%D7%90%D7%9C%D7%95%D7%91-%D7%90%D7%A8%D7%A0%D7%95%D7%9F/", "https://www.szmc.org.il/doctors/samueloff-arnon/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>1.445355747304436e+17</v>
+        <v>4.337439849460605e+17</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6159,7 +6167,7 @@
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
+          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr"/>
@@ -6200,7 +6208,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ד"ר ברוך יואב</t>
+          <t>גלי פריאנטה</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6220,18 +6228,18 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>ima</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>yoavb@tlvmc.gov.il</t>
+          <t>galipa@bgu.ac.il</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -6244,7 +6252,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
+          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -6254,12 +6262,12 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>י לאורוגינקולוגיה ורצפת אגן שטחי התעניינות ועיסוק מיוחדים ניתוחים וגינאליים וזעיר פולשניים לצניחת אברי האגן טיפול תרופתי וכירורגי לדליפת שתן מרפאת ערייה וצוואר הרחם אבחון וטיפול בקונדילומות ונגעים טרום ממאירים יצירת קשר yoavb@tlvmc.gov.il יחידות רפואיות אורוגינקולוגיה ורצפת האגן רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות נעים להכיר, ​ד"ר יואב ברוך איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציונ</t>
+          <t>ث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان גלי פריאנטה פרופ' גלי פריאנטה Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section galipa@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0001-6484-3769 Orcid Number Cookies Settings</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>"ברוך יואב"</t>
+          <t>"גלי פריאנטה"</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -6276,25 +6284,25 @@
         <v>1</v>
       </c>
       <c r="T36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-09-05T00:14:33.719515+00:00</t>
+          <t>2026-09-03T23:09:10.396904+00:00</t>
         </is>
       </c>
       <c r="W36" t="n">
         <v>2</v>
       </c>
       <c r="X36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
         <v>6</v>
       </c>
       <c r="Z36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA36" t="n">
         <v>1</v>
@@ -6306,11 +6314,11 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345", "https://soundcloud.com/wx8fnfybplpt", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A-%D7%91%D7%A8%D7%95%D7%9A/pfbid02DHSfATmK3MDpizZrgGTLc9ZAvZHXUsR9pSCjhd6pmWqSMFvq1BwehNeHCARNitMol/", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/pfbid02BMPnQXQYXt6vzctmybagMUp3nWACPxhE1LqhYeJYs1fVgXWA6B1cK2Z9VpRJ8cJRl/", "https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/", "https://pubmed.ncbi.nlm.nih.gov/?term=yoav+baruch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000546", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/61559143005435/", "https://www.infomed.co.il/experts/151203/", "https://www.yoavbaruch.com/", "https://www.yoavbaruch.com/about-6", "https://theindex.co.il/phone/ברוך-יואב-0777573393/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000504"]</t>
+          <t>["https://www.bgu.ac.il/people/galipa/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-%D7%92%D7%9C%D7%99/", "https://medpage.co.il/doctors/%D7%92%D7%9C%D7%99-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-25448/", "https://www.doctorita.co.il/experts/131973", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/pariente-g.aspx", "https://www.bgu.ac.il/ar/people/galipa/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>1.669294126780221e+17</v>
+        <v>4.336067241913308e+17</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6321,7 +6329,7 @@
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
+          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr"/>
@@ -6362,7 +6370,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ד"ר צוקר נפתלי</t>
+          <t>ד"ר ברוך יואב</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6382,7 +6390,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -6393,7 +6401,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>drnzuker@arad-medical.co.il</t>
+          <t>yoavb@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -6406,7 +6414,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://www.arad-medical.co.il/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -6416,12 +6424,12 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t xml:space="preserve"> בי"ח אסף הרופא, עבר השתלמות מעמיקה בכירורגיה גניקולוגית ואנדסקופית. כמוכן, גניקולוג בכיר בקופות החולים מכבי ולאומית. קרא עוד עלינו « לפרטים נוספים ולקביעת תור השאר פרטים ונחזור אליך בהקדם! ☎ 077-8037837 | 077-9966036 ✉ drnzuker@arad-medical.co.il שם מלא: מייל: טלפון: שלח © ד"ר נפתלי צוקר — כל הזכויות שמורות אתר זה נבנה ועוצב ע"י קידום פלוס - בניית אתרים</t>
+          <t>י לאורוגינקולוגיה ורצפת אגן שטחי התעניינות ועיסוק מיוחדים ניתוחים וגינאליים וזעיר פולשניים לצניחת אברי האגן טיפול תרופתי וכירורגי לדליפת שתן מרפאת ערייה וצוואר הרחם אבחון וטיפול בקונדילומות ונגעים טרום ממאירים יצירת קשר yoavb@tlvmc.gov.il יחידות רפואיות אורוגינקולוגיה ורצפת האגן רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות נעים להכיר, ​ד"ר יואב ברוך איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציונ</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>"צוקר נפתלי"</t>
+          <t>"ברוך יואב"</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -6438,25 +6446,25 @@
         <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-09-03T20:26:24.789692+00:00</t>
+          <t>2026-09-05T00:14:33.719515+00:00</t>
         </is>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X37" t="n">
         <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z37" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA37" t="n">
         <v>1</v>
@@ -6468,11 +6476,11 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=JM/xPUEkhEzRgBuX3T9AYqhAJkFmVBaeb30sdIDAjgJqc6t/hlXwF9+305eagC9MR2dwestiB5JmwYwMLOCteQ==", "https://doctors.assuta.co.il/doctor/naftaly-zuker-15805", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=AsbND281GonWNafC65Z5in+5Uof0vMwxuFwCtAAhKp6HNUz+Imt4aFWEpjB1dVuW0TI9YD98xqlKyretPdEuvw==", "https://www.arad-medical.co.il/", "http://www.kidumplus.co.il/", "https://www.arad-medical.co.il/contact", "https://www.arad-medical.co.il/about-us", "https://www.doctorim.co.il/s/doctor-21560/דר-נפתלי-צוקר/מומחה-יילוד-וגניקולוגיה", "https://www.infomed.co.il/experts/83793/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345", "https://soundcloud.com/wx8fnfybplpt", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A-%D7%91%D7%A8%D7%95%D7%9A/pfbid02DHSfATmK3MDpizZrgGTLc9ZAvZHXUsR9pSCjhd6pmWqSMFvq1BwehNeHCARNitMol/", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/pfbid02BMPnQXQYXt6vzctmybagMUp3nWACPxhE1LqhYeJYs1fVgXWA6B1cK2Z9VpRJ8cJRl/", "https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/", "https://pubmed.ncbi.nlm.nih.gov/?term=yoav+baruch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000546", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/61559143005435/", "https://www.infomed.co.il/experts/151203/", "https://www.yoavbaruch.com/", "https://www.yoavbaruch.com/about-6", "https://theindex.co.il/phone/ברוך-יואב-0777573393/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000504"]</t>
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>1.778899381297767e+17</v>
+        <v>5.007882380340662e+17</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6483,7 +6491,7 @@
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>https://www.arad-medical.co.il/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr"/>
@@ -6524,7 +6532,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ד"ר רטן גלעד</t>
+          <t>ד"ר צוקר נפתלי</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6544,7 +6552,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -6555,7 +6563,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>giladr@tlvmc.gov.il</t>
+          <t>drnzuker@arad-medical.co.il</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -6568,7 +6576,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
+          <t>https://www.arad-medical.co.il/</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -6578,12 +6586,12 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t xml:space="preserve">ח "ליס" ליולדות ונשים איכילוב צוות איכילוב גלעד רטן בדיקת היסטרוסקופיה - ד"ר גלעד רטן | ליס, איכילוב ד"ר גלעד רטן על תסמונת אשרמן, סטטוסקופ ערוץ 13 פרק 18 | פרופ' יריב יוגב ופרופ' גלעד רטן | בדיקת היסטרוסקופיה יצירת קשר giladr@tlvmc.gov.il יחידות רפואיות היסטרוסקופיה אבחנתית / טיפולית רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א </t>
+          <t xml:space="preserve"> בי"ח אסף הרופא, עבר השתלמות מעמיקה בכירורגיה גניקולוגית ואנדסקופית. כמוכן, גניקולוג בכיר בקופות החולים מכבי ולאומית. קרא עוד עלינו « לפרטים נוספים ולקביעת תור השאר פרטים ונחזור אליך בהקדם! ☎ 077-8037837 | 077-9966036 ✉ drnzuker@arad-medical.co.il שם מלא: מייל: טלפון: שלח © ד"ר נפתלי צוקר — כל הזכויות שמורות אתר זה נבנה ועוצב ע"י קידום פלוס - בניית אתרים</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>"רטן גלעד"</t>
+          <t>"צוקר נפתלי"</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -6605,14 +6613,14 @@
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-09-03T21:08:14.761438+00:00</t>
+          <t>2026-09-03T20:26:24.789692+00:00</t>
         </is>
       </c>
       <c r="W38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y38" t="n">
         <v>4</v>
@@ -6630,11 +6638,11 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F/", "https://dr-gilad.infomed.co.il/", "https://www.facebook.com/TLVMDC/posts/%D7%95%D7%95%D7%90%D7%95-%D7%9E%D7%AA%D7%A8%D7%92%D7%A9%D7%99%D7%9D-%D7%9C%D7%94%D7%9B%D7%99%D7%A8-%D7%9C%D7%9B%D7%9D-%D7%90%D7%AA-%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F-%D7%9E%D7%95%D7%9E%D7%97%D7%94-%D7%91%D7%9B%D7%99%D7%A8-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%A8%D7%A4%D7%95%D7%90%D7%99-tlv_medical_center/1344912312574270/", "https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=JM/xPUEkhEzRgBuX3T9AYqhAJkFmVBaeb30sdIDAjgJqc6t/hlXwF9+305eagC9MR2dwestiB5JmwYwMLOCteQ==", "https://doctors.assuta.co.il/doctor/naftaly-zuker-15805", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=AsbND281GonWNafC65Z5in+5Uof0vMwxuFwCtAAhKp6HNUz+Imt4aFWEpjB1dVuW0TI9YD98xqlKyretPdEuvw==", "https://www.arad-medical.co.il/", "http://www.kidumplus.co.il/", "https://www.arad-medical.co.il/contact", "https://www.arad-medical.co.il/about-us", "https://www.doctorim.co.il/s/doctor-21560/דר-נפתלי-צוקר/מומחה-יילוד-וגניקולוגיה", "https://www.infomed.co.il/experts/83793/"]</t>
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>1.445355747304436e+17</v>
+        <v>5.336698143893302e+17</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6645,7 +6653,7 @@
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
+          <t>https://www.arad-medical.co.il/</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr"/>
@@ -6686,7 +6694,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>דנה ברבינג-גולדשטיין</t>
+          <t>ד"ר רטן גלעד</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6706,18 +6714,18 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>ima</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>danabr2@clalit.org.il</t>
+          <t>giladr@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -6730,7 +6738,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -6740,17 +6748,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>ד"ר דנה ברבינג גולדשטיין | מרכז רפואי רבין ד"ר דנה ברבינג גולדשטיין מיילדות וגינקולוגיה, גנטיקה רפואית שם: ד"ר דנה ברבינג גולדשטיין דוא"ל: danabr2@clalit.org.il יחידה: מכון רפאל רקנאטי לגנטיקה</t>
+          <t xml:space="preserve">ח "ליס" ליולדות ונשים איכילוב צוות איכילוב גלעד רטן בדיקת היסטרוסקופיה - ד"ר גלעד רטן | ליס, איכילוב ד"ר גלעד רטן על תסמונת אשרמן, סטטוסקופ ערוץ 13 פרק 18 | פרופ' יריב יוגב ופרופ' גלעד רטן | בדיקת היסטרוסקופיה יצירת קשר giladr@tlvmc.gov.il יחידות רפואיות היסטרוסקופיה אבחנתית / טיפולית רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א </t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>"דנה ברבינג גולדשטיין" יילוד site:clalit.co.il</t>
+          <t>"רטן גלעד"</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>search_snippet</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -6767,36 +6775,36 @@
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-09-08T13:48:01.035843+00:00</t>
+          <t>2026-09-03T21:08:14.761438+00:00</t>
         </is>
       </c>
       <c r="W39" t="n">
+        <v>2</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
         <v>4</v>
       </c>
-      <c r="X39" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1</v>
-      </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA39" t="n">
         <v>1</v>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>ddgs:yahoo+ddgs:bing</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F/", "https://dr-gilad.infomed.co.il/", "https://www.facebook.com/TLVMDC/posts/%D7%95%D7%95%D7%90%D7%95-%D7%9E%D7%AA%D7%A8%D7%92%D7%A9%D7%99%D7%9D-%D7%9C%D7%94%D7%9B%D7%99%D7%A8-%D7%9C%D7%9B%D7%9D-%D7%90%D7%AA-%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F-%D7%9E%D7%95%D7%9E%D7%97%D7%94-%D7%91%D7%9B%D7%99%D7%A8-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%A8%D7%A4%D7%95%D7%90%D7%99-tlv_medical_center/1344912312574270/", "https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>1.445830439041574e+17</v>
+        <v>4.336067241913308e+17</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6807,7 +6815,7 @@
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr"/>
@@ -6848,7 +6856,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>יעל שולמן</t>
+          <t>דנה ברבינג-גולדשטיין</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6879,7 +6887,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>yaelshu@tlvmc.gov.il</t>
+          <t>danabr2@clalit.org.il</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -6892,7 +6900,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -6902,17 +6910,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>3zgt8o8y2e /search-result/ /api/as/v1/engines/ פתח חיפוש עוד ... זימון תורים אזור אישי כניסה לאיזור האישי AI צ'אט ד"ר יעל שולמן רופאה בכירה במחלקת נשים, ביה"ח 'ליס' ליולדות ונשים איכילוב צוות איכילוב יעל שולמן יצירת קשר yaelshu@tlvmc.gov.il יחידות רפואיות אשפוז נשים - מחלקה רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך ב</t>
+          <t>ד"ר דנה ברבינג גולדשטיין | מרכז רפואי רבין ד"ר דנה ברבינג גולדשטיין מיילדות וגינקולוגיה, גנטיקה רפואית שם: ד"ר דנה ברבינג גולדשטיין דוא"ל: danabr2@clalit.org.il יחידה: מכון רפאל רקנאטי לגנטיקה</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>"יעל שולמן"</t>
+          <t>"דנה ברבינג גולדשטיין" יילוד site:clalit.co.il</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -6929,36 +6937,36 @@
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-09-04T17:01:07.432235+00:00</t>
+          <t>2026-09-08T13:48:01.035843+00:00</t>
         </is>
       </c>
       <c r="W40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>["https://www.agmon-law.co.il/team-member/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/people/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/pfbid02D3uDhLBFvfdSCJScu9afsXcVu6ZWEqNA4AsJgJH4om5Y5hNBNGbDUq3Xyg3nad9hl/", "https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx"]</t>
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>1.371692475599462e+17</v>
+        <v>4.337491317124723e+17</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6969,7 +6977,7 @@
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr"/>
@@ -7010,7 +7018,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ישי לוין</t>
+          <t>יעל שולמן</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -7041,7 +7049,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>ishail@tlvmc.gov.il</t>
+          <t>yaelshu@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -7054,7 +7062,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -7064,12 +7072,12 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>ריוזיס כנס אונליין אנדומטריאוזיס 2025 | פרופ' יריב יוגב ופרופ' ישי לוין מניעה וגילוי מוקדם של מחלות נשים | ערוץ 10 המכון לפריון - כירורגיה של הפריון | ליס פרופ' ישי לוין על כאבי מחזור חזקים , ערוץ 13, סטטוסקופ יצירת קשר ishail@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה אשפוז נשים - מחלקה אנדומטריוזיס - מרכז רב תחומי המרכז לבריאות האשה-מרפאות מומחים הפלות חוזרות - טיפול בכשל הריוני רופאים בכירים בליס-יולדות ונשים יצירת קשר יחיד</t>
+          <t>3zgt8o8y2e /search-result/ /api/as/v1/engines/ פתח חיפוש עוד ... זימון תורים אזור אישי כניסה לאיזור האישי AI צ'אט ד"ר יעל שולמן רופאה בכירה במחלקת נשים, ביה"ח 'ליס' ליולדות ונשים איכילוב צוות איכילוב יעל שולמן יצירת קשר yaelshu@tlvmc.gov.il יחידות רפואיות אשפוז נשים - מחלקה רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך ב</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>"ישי לוין"</t>
+          <t>"יעל שולמן"</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -7091,7 +7099,7 @@
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-09-04T17:20:48.855691+00:00</t>
+          <t>2026-09-04T17:01:07.432235+00:00</t>
         </is>
       </c>
       <c r="W41" t="n">
@@ -7101,10 +7109,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -7116,11 +7124,11 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>["https://www.ishai-levin.com/", "https://www.ishai-levin.com/about", "https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/", "https://pubmed.ncbi.nlm.nih.gov/?term=Levin%2c%20Ishai%5bFull%20Author%20Name%5d%20OR%20Ishai%2c%20Levin%5bFull%20Author%20Name%5d&amp;cmd=DetailsSearch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.agmon-law.co.il/team-member/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/people/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/pfbid02D3uDhLBFvfdSCJScu9afsXcVu6ZWEqNA4AsJgJH4om5Y5hNBNGbDUq3Xyg3nad9hl/", "https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>1.371692475599462e+17</v>
+        <v>4.115077426798385e+17</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7131,7 +7139,7 @@
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr"/>
@@ -7172,7 +7180,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>לירן הירש</t>
+          <t>ישי לוין</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7203,7 +7211,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>liranh@tlvmc.gov.il</t>
+          <t>ishail@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -7216,7 +7224,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -7226,12 +7234,12 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>צועיים החברה הישראלית לרפואת האם והעובר החוג הישראלי למיילדות וגינקולוגיה לידה נדירה - תאומים ברחם נפרד פרק 19 | פרופ' יריב יוגב ופרופ' לירן הירש | תאומים פרק 9 | פרופ' יריב יוגב ופרופ' לירן הירש| הריון בסיכון יצירת קשר liranh@tlvmc.gov.il יחידות רפואיות המחלקה לרפואת האם והעובר מניעת לידה מוקדמת - מרפאה מעקב הריונות תאומים רופאים בכירים בליס-יולדות ונשים היריון ולידה יצירת קשר יחידות רפואיות היריון של 1 למיליון עם פרופ' לירן הירש איכיל</t>
+          <t>ריוזיס כנס אונליין אנדומטריאוזיס 2025 | פרופ' יריב יוגב ופרופ' ישי לוין מניעה וגילוי מוקדם של מחלות נשים | ערוץ 10 המכון לפריון - כירורגיה של הפריון | ליס פרופ' ישי לוין על כאבי מחזור חזקים , ערוץ 13, סטטוסקופ יצירת קשר ishail@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה אשפוז נשים - מחלקה אנדומטריוזיס - מרכז רב תחומי המרכז לבריאות האשה-מרפאות מומחים הפלות חוזרות - טיפול בכשל הריוני רופאים בכירים בליס-יולדות ונשים יצירת קשר יחיד</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>"לירן הירש"</t>
+          <t>"ישי לוין"</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -7253,7 +7261,7 @@
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-09-04T17:39:56.947224+00:00</t>
+          <t>2026-09-04T17:20:48.855691+00:00</t>
         </is>
       </c>
       <c r="W42" t="n">
@@ -7278,11 +7286,11 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>["https://www.profhiersch.com/", "https://www.profhiersch.com/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/", "https://pubmed.ncbi.nlm.nih.gov/?term=HIERSCH+L&amp;sort=date", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.ishai-levin.com/", "https://www.ishai-levin.com/about", "https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/", "https://pubmed.ncbi.nlm.nih.gov/?term=Levin%2c%20Ishai%5bFull%20Author%20Name%5d%20OR%20Ishai%2c%20Levin%5bFull%20Author%20Name%5d&amp;cmd=DetailsSearch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>1.371692475599462e+17</v>
+        <v>4.115077426798385e+17</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7293,7 +7301,7 @@
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr"/>
@@ -7334,7 +7342,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>נועה גוהר פורטנוי</t>
+          <t>לירן הירש</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7365,7 +7373,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>noago@post.bgu.ac.il</t>
+          <t>liranh@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -7378,7 +7386,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/noago/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -7388,12 +7396,12 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان נועה גוהר פורטנוי נועה גוהר פורטנוי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section noago@post.bgu.ac.il Cookies Settings</t>
+          <t>צועיים החברה הישראלית לרפואת האם והעובר החוג הישראלי למיילדות וגינקולוגיה לידה נדירה - תאומים ברחם נפרד פרק 19 | פרופ' יריב יוגב ופרופ' לירן הירש | תאומים פרק 9 | פרופ' יריב יוגב ופרופ' לירן הירש| הריון בסיכון יצירת קשר liranh@tlvmc.gov.il יחידות רפואיות המחלקה לרפואת האם והעובר מניעת לידה מוקדמת - מרפאה מעקב הריונות תאומים רופאים בכירים בליס-יולדות ונשים היריון ולידה יצירת קשר יחידות רפואיות היריון של 1 למיליון עם פרופ' לירן הירש איכיל</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>"נועה גוהר פורטנוי" יילוד</t>
+          <t>"לירן הירש"</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -7415,14 +7423,14 @@
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-09-08T14:13:12.580343+00:00</t>
+          <t>2026-09-04T17:39:56.947224+00:00</t>
         </is>
       </c>
       <c r="W43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
         <v>2</v>
@@ -7440,11 +7448,11 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>["https://www.doctorita.co.il/experts/126297", "https://www.bgu.ac.il/ar/people/noago/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.profhiersch.com/", "https://www.profhiersch.com/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/", "https://pubmed.ncbi.nlm.nih.gov/?term=HIERSCH+L&amp;sort=date", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>1.338462026452943e+17</v>
+        <v>4.115077426798385e+17</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7455,7 +7463,7 @@
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/noago/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr"/>
@@ -7496,7 +7504,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>עדי יהודה ווינטראוב</t>
+          <t>נועה גוהר פורטנוי</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7527,7 +7535,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>adiyehud@bgu.ac.il</t>
+          <t>noago@post.bgu.ac.il</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -7540,7 +7548,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
+          <t>https://www.bgu.ac.il/ar/people/noago/</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -7550,12 +7558,12 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>رئيسية جامعة أنشي سيجل في جوريان עדי יהודה ווינטראוב פרופ' עדי יהודה ווינטראוב Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section adiyehud@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0002-4239-8665 Orcid Number Cookies Settings</t>
+          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان נועה גוהר פורטנוי נועה גוהר פורטנוי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section noago@post.bgu.ac.il Cookies Settings</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>"עדי יהודה ווינטראוב"</t>
+          <t>"נועה גוהר פורטנוי" יילוד</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -7572,41 +7580,41 @@
         <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-09-04T19:20:10.182518+00:00</t>
+          <t>2026-09-08T14:13:12.580343+00:00</t>
         </is>
       </c>
       <c r="W44" t="n">
+        <v>4</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y44" t="n">
         <v>2</v>
       </c>
-      <c r="X44" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>5</v>
-      </c>
       <c r="Z44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/adiyehud/", "https://www.bgu.ac.il/researcher/adi-weintraub/", "https://www.beok.co.il/doctors/Doctors-136810/", "https://cris.bgu.ac.il/en/publications/%D7%94%D7%A1%D7%99%D7%9B%D7%95%D7%9F-%D7%9C%D7%A1%D7%99%D7%91%D7%95%D7%9B%D7%99-%D7%94%D7%99%D7%A8%D7%99%D7%95%D7%9F-%D7%91%D7%A0%D7%A9%D7%99%D7%9D-%D7%A2%D7%9D-%D7%90%D7%A0%D7%93%D7%95%D7%9E%D7%98%D7%A8%D7%99%D7%95%D7%96%D7%99%D7%A1/", "https://www.bgu.ac.il/ar/people/adiyehud/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.doctorita.co.il/experts/126297", "https://www.bgu.ac.il/ar/people/noago/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>1.338444870564918e+17</v>
+        <v>4.015386079358828e+17</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7617,7 +7625,7 @@
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
+          <t>https://www.bgu.ac.il/ar/people/noago/</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr"/>
@@ -7658,7 +7666,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>עמרי זמשטין</t>
+          <t>עדי יהודה ווינטראוב</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7689,7 +7697,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>omrizam@post.bgu.ac.il</t>
+          <t>adiyehud@bgu.ac.il</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -7702,7 +7710,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
+          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -7712,12 +7720,12 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>ريد البحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان עמרי זמשטין עמרי זמשטין Departments אקדמי לא פעיל הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section omrizam@post.bgu.ac.il Cookies Settings</t>
+          <t>رئيسية جامعة أنشي سيجل في جوريان עדי יהודה ווינטראוב פרופ' עדי יהודה ווינטראוב Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section adiyehud@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0002-4239-8665 Orcid Number Cookies Settings</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>"עמרי זמשטין"</t>
+          <t>"עדי יהודה ווינטראוב"</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -7739,7 +7747,7 @@
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-09-04T19:35:09.971397+00:00</t>
+          <t>2026-09-04T19:20:10.182518+00:00</t>
         </is>
       </c>
       <c r="W45" t="n">
@@ -7749,26 +7757,26 @@
         <v>1</v>
       </c>
       <c r="Y45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/ar/people/omrizam/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.bgu.ac.il/people/adiyehud/", "https://www.bgu.ac.il/researcher/adi-weintraub/", "https://www.beok.co.il/doctors/Doctors-136810/", "https://cris.bgu.ac.il/en/publications/%D7%94%D7%A1%D7%99%D7%9B%D7%95%D7%9F-%D7%9C%D7%A1%D7%99%D7%91%D7%95%D7%9B%D7%99-%D7%94%D7%99%D7%A8%D7%99%D7%95%D7%9F-%D7%91%D7%A0%D7%A9%D7%99%D7%9D-%D7%A2%D7%9D-%D7%90%D7%A0%D7%93%D7%95%D7%9E%D7%98%D7%A8%D7%99%D7%95%D7%96%D7%99%D7%A1/", "https://www.bgu.ac.il/ar/people/adiyehud/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>1.338444870564918e+17</v>
+        <v>4.015334611694755e+17</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7779,7 +7787,7 @@
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
+          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr"/>
@@ -7820,7 +7828,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>רויטל לינדר</t>
+          <t>עמרי זמשטין</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7851,7 +7859,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>revital@drlinder.co.il</t>
+          <t>omrizam@post.bgu.ac.il</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -7864,7 +7872,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://www.drlinder.co.il/</t>
+          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -7874,12 +7882,12 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>בכירה ביחידה הגניקואונקולוגית , בית חולים רמב״ם, חיפה. 4/2014-4/2019 התמחות במיילדות וגניקולוגיה בית חולים רמב״ם,חיפה. לפרטים מלאים חוות דעת יש לך שאלה ? צרי קשר ד״ר רויטל לינדר צפצפה 2 (ישי סנטר) , רמת ישי 058-6918927​ revital@drlinder.co.il הצהרת נגישות © DR. Revital Linder. All rights Reserved , 2023</t>
+          <t>ريد البحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان עמרי זמשטין עמרי זמשטין Departments אקדמי לא פעיל הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section omrizam@post.bgu.ac.il Cookies Settings</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>"רויטל לינדר"</t>
+          <t>"עמרי זמשטין"</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -7896,41 +7904,41 @@
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-09-04T07:14:47.643108+00:00</t>
+          <t>2026-09-04T19:35:09.971397+00:00</t>
         </is>
       </c>
       <c r="W46" t="n">
         <v>2</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>["https://www.rambam.org.il/?catid=%7B9F8D1CC1-1F5C-46F1-A395-E19ED48FE2EE%7D&amp;itemid=%7B4B21BA59-AF68-46CA-9483-9639E61A75A8%7D", "https://www.rambam.org.il/about-rambam/", "https://www.rambam.org.il/about-rambam/careers/", "https://www.rambam.org.il/departmentsandclinics/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/urology/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/orthopedic/", "https://www.drlinder.co.il/"]</t>
+          <t>["https://www.bgu.ac.il/ar/people/omrizam/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>1.338292358615219e+17</v>
+        <v>4.015334611694755e+17</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7941,7 +7949,7 @@
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>https://www.drlinder.co.il/</t>
+          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr"/>
@@ -7982,7 +7990,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>רליקה הרשקוביץ</t>
+          <t>רויטל לינדר</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -8013,7 +8021,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>ralikah@bgu.ac.il</t>
+          <t>revital@drlinder.co.il</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -8026,7 +8034,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
+          <t>https://www.drlinder.co.il/</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -8036,12 +8044,12 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان רליקה הרשקוביץ פרופ' רליקה הרשקוביץ Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ralikah@bgu.ac.il رابط ملف الأبحاث Cookies Settings</t>
+          <t>בכירה ביחידה הגניקואונקולוגית , בית חולים רמב״ם, חיפה. 4/2014-4/2019 התמחות במיילדות וגניקולוגיה בית חולים רמב״ם,חיפה. לפרטים מלאים חוות דעת יש לך שאלה ? צרי קשר ד״ר רויטל לינדר צפצפה 2 (ישי סנטר) , רמת ישי 058-6918927​ revital@drlinder.co.il הצהרת נגישות © DR. Revital Linder. All rights Reserved , 2023</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>"רליקה הרשקוביץ"</t>
+          <t>"רויטל לינדר"</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -8063,7 +8071,7 @@
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-09-04T07:56:40.372731+00:00</t>
+          <t>2026-09-04T07:14:47.643108+00:00</t>
         </is>
       </c>
       <c r="W47" t="n">
@@ -8073,26 +8081,26 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/ralikah/", "https://www.doctorita.co.il/experts/101245", "https://www.bgu.ac.il/ar/people/ralikah/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.rambam.org.il/?catid=%7B9F8D1CC1-1F5C-46F1-A395-E19ED48FE2EE%7D&amp;itemid=%7B4B21BA59-AF68-46CA-9483-9639E61A75A8%7D", "https://www.rambam.org.il/about-rambam/", "https://www.rambam.org.il/about-rambam/careers/", "https://www.rambam.org.il/departmentsandclinics/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/urology/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/orthopedic/", "https://www.drlinder.co.il/"]</t>
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>1.338292358615219e+17</v>
+        <v>4.014877075845656e+17</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -8103,7 +8111,7 @@
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
+          <t>https://www.drlinder.co.il/</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr"/>
@@ -8144,7 +8152,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>שקמה בר און</t>
+          <t>רליקה הרשקוביץ</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8175,7 +8183,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>shikmabo@tlvmc.gov.il</t>
+          <t>ralikah@bgu.ac.il</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -8188,7 +8196,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
+          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -8198,12 +8206,12 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>ת לאנדוסקופיה גינקולוגית שטחי התעניינות ועיסוק מיוחדים היסטרוסקופיה עם וללא הרדמה, היסטרוסקופיה ניתוחית ללא הרדמה בשיטת "see and treat" לפרוסקופיות פרק 14 | פרופ' יריב יוגב וד״ר שקמה בר און | מרכז בריאות האישה יצירת קשר shikmabo@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך בהתפתחות ביה"ח איכו</t>
+          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان רליקה הרשקוביץ פרופ' רליקה הרשקוביץ Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ralikah@bgu.ac.il رابط ملف الأبحاث Cookies Settings</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>"שקמה בר און"</t>
+          <t>"רליקה הרשקוביץ"</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -8225,7 +8233,7 @@
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-09-04T10:28:27.702590+00:00</t>
+          <t>2026-09-04T07:56:40.372731+00:00</t>
         </is>
       </c>
       <c r="W48" t="n">
@@ -8235,13 +8243,13 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
@@ -8250,11 +8258,11 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>["https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%A9%D7%A7%D7%9E%D7%94-%D7%91%D7%A8-%D7%90%D7%95%D7%9F/", "https://tlvmedical.com/doctors/דר-שקמה-בר-און/", "https://www.rofim.org.il/minisite/%D7%93%D7%A8_%D7%A9%D7%A7%D7%9E%D7%94_%D7%91%D7%A8_%D7%90%D7%95%D7%9F", "https://www.shidurit-ltd.co.il/", "https://www.rofim.org.il/about", "https://www.rofim.org.il/Contact", "https://www.rofim.org.il/specialityPage/%D7%9E%D7%A8%D7%9B%D7%96_%D7%A8%D7%A4%D7%95%D7%90%D7%99", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%9E%D7%92%D7%90%D7%A8", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%91%D7%99%D7%AA_%D7%92%D7%93%D7%99", "https://www.rofim.org.il/minisite/%D7%90%D7%99%D7%99_%D7%90%D7%9C_%D7%A7%D7%9C%D7%99%D7%A0%D7%99%D7%A7", "https://docsrated.com/doctors/שקמה-בר-און", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2FTLVMDC%2Fphotos%2F%25D7%25A2%25D7%2595%25D7%25A7%25D7%2591%25D7%2595%25D7%25AA-%25D7%2595%25D7%259E%25D7%2598%25D7%2595%25D7%25A4%25D7%259C%25D7%2595%25D7%25AA-%25D7%2590%25D7%25A0%25D7%2595-%25D7%25A9%25D7%259E%25D7%2597%25D7%2599%25D7%259D-%25D7%259C%25D7%2594%25D7%259B%25D7%2599%25D7%25A8-%25D7%259C%25D7%259B%25D7%259F-%25D7%2590%25D7%25AA-%25D7%2593%25D7%25A8-%25D7%25A9%25D7%25A7%25D7%259E%25D7%2594-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F%25D7%2593%25D7%25A8-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F-%25D7%2594%25D7%2599%25D7%2590-%25D7%259E%25D7%25A0%25D7%2594%25D7%259C%25D7%25AA-%25D7%2594%25D7%259E%25D7%25A8%25D7%259B%25D7%2596-%25D7%259C%2F1525276317871201%2F", "https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/", "https://www.ncbi.nlm.nih.gov/pubmed/?term=shikma+bar+on", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.bgu.ac.il/people/ralikah/", "https://www.doctorita.co.il/experts/101245", "https://www.bgu.ac.il/ar/people/ralikah/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>1.335547143520623e+17</v>
+        <v>4.014877075845656e+17</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8265,7 +8273,7 @@
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
+          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr"/>
@@ -8306,7 +8314,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>שרית הלמן</t>
+          <t>שקמה בר און</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8337,7 +8345,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>hsarit@szmc.org.il</t>
+          <t>shikmabo@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -8350,7 +8358,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -8360,12 +8368,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t xml:space="preserve"> רופאים בשערי צדק ד"ר שרית  הלמן רופאה בכירה Dr. Sarit  Helman התמחות: גינקולוגיה ויילוד תת התמחות: הריון בסיכון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 026666656 מחלקה: 026666656 hsarit@szmc.org.il hsarit@szmc.org.il נסיון מקצועי Harvard T.H. Chan School of Public Health, Joslin Diabetes Center, Research intern under the supervision of Dr. Florence Brown and Dr. Tamarra James-Todd,     Type 1 Dia</t>
+          <t>ת לאנדוסקופיה גינקולוגית שטחי התעניינות ועיסוק מיוחדים היסטרוסקופיה עם וללא הרדמה, היסטרוסקופיה ניתוחית ללא הרדמה בשיטת "see and treat" לפרוסקופיות פרק 14 | פרופ' יריב יוגב וד״ר שקמה בר און | מרכז בריאות האישה יצירת קשר shikmabo@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך בהתפתחות ביה"ח איכו</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>"שרית הלמן"</t>
+          <t>"שקמה בר און"</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -8382,12 +8390,12 @@
         <v>1</v>
       </c>
       <c r="T49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-09-05T00:06:28.339643+00:00</t>
+          <t>2026-09-04T10:28:27.702590+00:00</t>
         </is>
       </c>
       <c r="W49" t="n">
@@ -8400,10 +8408,10 @@
         <v>6</v>
       </c>
       <c r="Z49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
@@ -8412,11 +8420,11 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>["https://www.hamichlol.org.il/שרה_(שרית)_הלמן", "https://behevrat-haadam.org/ram-sara-helman/", "https://behevrat-haadam.org/tag/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/IsrAnthro/posts/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F-%D7%A1%D7%95%D7%A6%D7%99%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA%D7%90%D7%A0%D7%97%D7%A0%D7%95-%D7%A9%D7%9E%D7%97%D7%99%D7%9D-%D7%9C%D7%A9%D7%AA%D7%A3-%D7%91%D7%91%D7%97%D7%91%D7%A8%D7%AA-%D7%94%D7%90%D7%93%D7%9D-%D7%90%D7%AA-%D7%93%D7%91%D7%A8%D7%99%D7%95-%D7%A9%D7%9C-%D7%90%D7%95%D7%A8%D7%99-%D7%A8%D7%9D-%D7%A4%D7%A8%D7%95%D7%A4-%D7%90%D7%9E%D7%A8%D7%99%D7%98%D7%95/4246861638775714/", "https://www.doctorita.co.il/experts/137665", "https://www.szmc.org.il/doctors/helman-sarit/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
+          <t>["https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%A9%D7%A7%D7%9E%D7%94-%D7%91%D7%A8-%D7%90%D7%95%D7%9F/", "https://tlvmedical.com/doctors/דר-שקמה-בר-און/", "https://www.rofim.org.il/minisite/%D7%93%D7%A8_%D7%A9%D7%A7%D7%9E%D7%94_%D7%91%D7%A8_%D7%90%D7%95%D7%9F", "https://www.shidurit-ltd.co.il/", "https://www.rofim.org.il/about", "https://www.rofim.org.il/Contact", "https://www.rofim.org.il/specialityPage/%D7%9E%D7%A8%D7%9B%D7%96_%D7%A8%D7%A4%D7%95%D7%90%D7%99", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%9E%D7%92%D7%90%D7%A8", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%91%D7%99%D7%AA_%D7%92%D7%93%D7%99", "https://www.rofim.org.il/minisite/%D7%90%D7%99%D7%99_%D7%90%D7%9C_%D7%A7%D7%9C%D7%99%D7%A0%D7%99%D7%A7", "https://docsrated.com/doctors/שקמה-בר-און", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2FTLVMDC%2Fphotos%2F%25D7%25A2%25D7%2595%25D7%25A7%25D7%2591%25D7%2595%25D7%25AA-%25D7%2595%25D7%259E%25D7%2598%25D7%2595%25D7%25A4%25D7%259C%25D7%2595%25D7%25AA-%25D7%2590%25D7%25A0%25D7%2595-%25D7%25A9%25D7%259E%25D7%2597%25D7%2599%25D7%259D-%25D7%259C%25D7%2594%25D7%259B%25D7%2599%25D7%25A8-%25D7%259C%25D7%259B%25D7%259F-%25D7%2590%25D7%25AA-%25D7%2593%25D7%25A8-%25D7%25A9%25D7%25A7%25D7%259E%25D7%2594-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F%25D7%2593%25D7%25A8-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F-%25D7%2594%25D7%2599%25D7%2590-%25D7%259E%25D7%25A0%25D7%2594%25D7%259C%25D7%25AA-%25D7%2594%25D7%259E%25D7%25A8%25D7%259B%25D7%2596-%25D7%259C%2F1525276317871201%2F", "https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/", "https://www.ncbi.nlm.nih.gov/pubmed/?term=shikma+bar+on", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>1.33559798083719e+17</v>
+        <v>4.006641430561869e+17</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8427,7 +8435,7 @@
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr"/>
@@ -8468,7 +8476,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ד"ר ארבל אריאל</t>
+          <t>שרית הלמן</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8488,31 +8496,31 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>ima</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>info@eryaveladan.com</t>
+          <t>hsarit@szmc.org.il</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://www.eryaveladan.com/</t>
+          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -8522,12 +8530,12 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>החזיר את האיזון. קראי עוד השאירי פרטים ונחזור אלייך בהקדם שם מלא טלפון דוא״ל שליחה רופא נשים מומחה מחלות העריה והלדן ​ ד״ר אריאל ארבל לקביעת תור: 077-2311245 כתובת המרפאה: בית למומחים ברפואה - בורוכוב 54, גבעתיים דוא״ל: info@eryaveladan.com bottom of page</t>
+          <t xml:space="preserve"> רופאים בשערי צדק ד"ר שרית  הלמן רופאה בכירה Dr. Sarit  Helman התמחות: גינקולוגיה ויילוד תת התמחות: הריון בסיכון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 026666656 מחלקה: 026666656 hsarit@szmc.org.il hsarit@szmc.org.il נסיון מקצועי Harvard T.H. Chan School of Public Health, Joslin Diabetes Center, Research intern under the supervision of Dr. Florence Brown and Dr. Tamarra James-Todd,     Type 1 Dia</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>"ארבל אריאל"</t>
+          <t>"שרית הלמן"</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -8537,29 +8545,29 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>[{"email": "info@eryaveladan.com", "confidence": 88, "source_url": "https://www.eryaveladan.com/", "identity_url": "https://www.eryaveladan.com/", "evidence": "החזיר את האיזון. קראי עוד השאירי פרטים ונחזור אלייך בהקדם שם מלא טלפון דוא״ל שליחה רופא נשים מומחה מחלות העריה והלדן ​ ד״ר אריאל ארבל לקביעת תור: 077-2311245 כתובת המרפאה: בית למומחים ברפואה - בורוכוב 54, גבעתיים דוא״ל: info@eryaveladan.com bottom of page", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}, {"email": "office@b54.co.il", "confidence": 88, "source_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "identity_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "evidence": "ד\"ר אריאל ארבל - מרפאת מומחים B54, הבית למומחים ברפואה בגבעתיים דילוג לתוכן B54 03-757-8562 office@b54.co.il א׳-ה׳ 8:00-20:00 | ו׳ 08:00-13:00 Facebook-f Youtube Google דף הבית אודות B54 מי אנחנו שכונת בורוכוב מרכז Friendly הנהלת המרפאה שאלות נפוצות הרופאים שלנו קליניקה להשכרה מידע למטופל שאלות ותשובות הורדת טפ", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-09-03T20:23:48.175654+00:00</t>
+          <t>2026-09-05T00:06:28.339643+00:00</t>
         </is>
       </c>
       <c r="W50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X50" t="n">
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z50" t="n">
         <v>5</v>
@@ -8574,11 +8582,11 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598", "https://www.facebook.com/people/%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%90%D7%A8%D7%91%D7%9C/pfbid0NCmi7FZgUyu2EVV5mLJMpBfndXiDQPqseAxUny7KWHsDvucQScUiVnBeMef3ByStl/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%90%D7%A8%D7%91%D7%9C-%D7%90%D7%A8%D7%99%D7%90%D7%9C/", "https://www.eryaveladan.com/", "https://www.eryaveladan.com/%D7%90%D7%95%D7%93%D7%95%D7%AA-1", "https://www.b54.co.il/doctors/dr-arbel-ariel/", "https://www.medreviews.co.il/provider/dr-arbel-ariel", "https://www.b54.co.il/about/", "https://www.b54.co.il/about", "https://www.b54.co.il/about#borohov", "https://www.b54.co.il/about#Friendly", "https://www.b54.co.il/about#management", "https://www.b54.co.il/about#qa", "https://www.medreviews.co.il/provider/dr-arbel-ariel#contact-doctor-section", "https://www.medreviews.co.il/contact-us", "https://www.medreviews.co.il/about", "https://woman.mymc.co.il/doctors/dr-arielarbel/", "https://www.ima.org.il/DoctorsIndex/Default.aspx", "https://www.infomed.co.il/experts/145655/", "https://www.ami.org.il/blog/families/not-the-same-shirley"]</t>
+          <t>["https://www.hamichlol.org.il/שרה_(שרית)_הלמן", "https://behevrat-haadam.org/ram-sara-helman/", "https://behevrat-haadam.org/tag/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/IsrAnthro/posts/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F-%D7%A1%D7%95%D7%A6%D7%99%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA%D7%90%D7%A0%D7%97%D7%A0%D7%95-%D7%A9%D7%9E%D7%97%D7%99%D7%9D-%D7%9C%D7%A9%D7%AA%D7%A3-%D7%91%D7%91%D7%97%D7%91%D7%A8%D7%AA-%D7%94%D7%90%D7%93%D7%9D-%D7%90%D7%AA-%D7%93%D7%91%D7%A8%D7%99%D7%95-%D7%A9%D7%9C-%D7%90%D7%95%D7%A8%D7%99-%D7%A8%D7%9D-%D7%A4%D7%A8%D7%95%D7%A4-%D7%90%D7%9E%D7%A8%D7%99%D7%98%D7%95/4246861638775714/", "https://www.doctorita.co.il/experts/137665", "https://www.szmc.org.il/doctors/helman-sarit/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>1.778899381297767e+17</v>
+        <v>4.006793942511569e+17</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8589,7 +8597,7 @@
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>https://www.eryaveladan.com/</t>
+          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr"/>
@@ -8604,7 +8612,7 @@
       <c r="AP50" t="inlineStr"/>
       <c r="AQ50" t="inlineStr"/>
       <c r="AR50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS50" t="b">
         <v>0</v>
@@ -8613,11 +8621,11 @@
         <v>1</v>
       </c>
       <c r="AU50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
+          <t>PERSON</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8638,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>מאיה שרון וינר</t>
+          <t>ד"ר ארבל אריאל</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8650,18 +8658,18 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>ima</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>clinic@drmayasharonweiner.com</t>
+          <t>info@eryaveladan.com</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -8674,7 +8682,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://www.drmayasharonweiner.com/</t>
+          <t>https://www.eryaveladan.com/</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -8684,12 +8692,12 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>אני איתך במסע הזה. הצעד הראשון שלך מתחיל כאן. ד"ר מאיה שרון-וינר רופאת נשים מומחית בפריון והפריה חוץ גופית מיילדות וגינקולוגיה לקביעת פגישה © 2026 כל הזכויות שמורות לד"ר מאיה שרון-וינר הברזל 9א', רמת החייל ווטסאפ למרפאה clinic@drmayasharonweiner.com פוריות האישה והגבר טיפולי פוריות הפריה חוץ גופית ו-PGD שימור פוריות פוריות לאחר סרטן ובנשאיות BRCA מעקב וליווי הריון גינקולוגיה כללית Menu Close אודות יצירת קשר מדיניות פרטיות הצהרת נגישות M</t>
+          <t>החזיר את האיזון. קראי עוד השאירי פרטים ונחזור אלייך בהקדם שם מלא טלפון דוא״ל שליחה רופא נשים מומחה מחלות העריה והלדן ​ ד״ר אריאל ארבל לקביעת תור: 077-2311245 כתובת המרפאה: בית למומחים ברפואה - בורוכוב 54, גבעתיים דוא״ל: info@eryaveladan.com bottom of page</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>"מאיה שרון וינר"</t>
+          <t>"ארבל אריאל"</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -8699,11 +8707,11 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "info@eryaveladan.com", "confidence": 88, "source_url": "https://www.eryaveladan.com/", "identity_url": "https://www.eryaveladan.com/", "evidence": "החזיר את האיזון. קראי עוד השאירי פרטים ונחזור אלייך בהקדם שם מלא טלפון דוא״ל שליחה רופא נשים מומחה מחלות העריה והלדן ​ ד״ר אריאל ארבל לקביעת תור: 077-2311245 כתובת המרפאה: בית למומחים ברפואה - בורוכוב 54, גבעתיים דוא״ל: info@eryaveladan.com bottom of page", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}, {"email": "office@b54.co.il", "confidence": 88, "source_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "identity_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "evidence": "ד\"ר אריאל ארבל - מרפאת מומחים B54, הבית למומחים ברפואה בגבעתיים דילוג לתוכן B54 03-757-8562 office@b54.co.il א׳-ה׳ 8:00-20:00 | ו׳ 08:00-13:00 Facebook-f Youtube Google דף הבית אודות B54 מי אנחנו שכונת בורוכוב מרכז Friendly הנהלת המרפאה שאלות נפוצות הרופאים שלנו קליניקה להשכרה מידע למטופל שאלות ותשובות הורדת טפ", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}]</t>
         </is>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T51" t="n">
         <v>0</v>
@@ -8711,17 +8719,17 @@
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-09-04T17:43:40.101946+00:00</t>
+          <t>2026-09-03T20:23:48.175654+00:00</t>
         </is>
       </c>
       <c r="W51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z51" t="n">
         <v>5</v>
@@ -8731,16 +8739,16 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>["https://www.drmayasharonweiner.com/", "https://www.drmayasharonweiner.com/about", "https://www.drmayasharonweiner.com/contact", "https://www.medreviews.co.il/provider/dr-sharon-weiner-maya", "https://www.medreviews.co.il/provider/dr-sharon-weiner-maya/treatment", "https://www.doctorita.co.il/experts/119120", "https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr_maya_sharonweiner%2F&amp;is_from_rle", "https://docsrated.com/doctors/מאיה-שרון-וינר"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598", "https://www.facebook.com/people/%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%90%D7%A8%D7%91%D7%9C/pfbid0NCmi7FZgUyu2EVV5mLJMpBfndXiDQPqseAxUny7KWHsDvucQScUiVnBeMef3ByStl/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%90%D7%A8%D7%91%D7%9C-%D7%90%D7%A8%D7%99%D7%90%D7%9C/", "https://www.eryaveladan.com/", "https://www.eryaveladan.com/%D7%90%D7%95%D7%93%D7%95%D7%AA-1", "https://www.b54.co.il/doctors/dr-arbel-ariel/", "https://www.medreviews.co.il/provider/dr-arbel-ariel", "https://www.b54.co.il/about/", "https://www.b54.co.il/about", "https://www.b54.co.il/about#borohov", "https://www.b54.co.il/about#Friendly", "https://www.b54.co.il/about#management", "https://www.b54.co.il/about#qa", "https://www.medreviews.co.il/provider/dr-arbel-ariel#contact-doctor-section", "https://www.medreviews.co.il/contact-us", "https://www.medreviews.co.il/about", "https://woman.mymc.co.il/doctors/dr-arielarbel/", "https://www.ima.org.il/DoctorsIndex/Default.aspx", "https://www.infomed.co.il/experts/145655/", "https://www.ami.org.il/blog/families/not-the-same-shirley"]</t>
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>1.371692475599462e+17</v>
+        <v>5.336698143893302e+17</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8751,7 +8759,7 @@
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>https://www.drmayasharonweiner.com/</t>
+          <t>https://www.eryaveladan.com/</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr"/>
@@ -8766,7 +8774,7 @@
       <c r="AP51" t="inlineStr"/>
       <c r="AQ51" t="inlineStr"/>
       <c r="AR51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS51" t="b">
         <v>0</v>
@@ -8792,7 +8800,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>מנחם נוימן</t>
+          <t>מאיה שרון וינר</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8823,7 +8831,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>hello@professorneuman.com</t>
+          <t>clinic@drmayasharonweiner.com</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -8836,7 +8844,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://professorneuman.com/he/</t>
+          <t>https://www.drmayasharonweiner.com/</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -8846,12 +8854,12 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>פרופ׳ מנחם נוימן — אורוגינקולוגיה ורפואת רצפת האגן מגדל סוזוקי, קומה 4, רח׳ יגאל אלון 82, תל אביב 054-644-2060 · hello@professorneuman.com ראשי מידע לרופאים מידע למטופלות מהתקשורת צרי קשר English פרופ׳ מנחם נוימן אורוגינקולוגיה ורפואת רצפת האגן צניחת איברי האגן ודליפת שתן הן מהתופעות השכיחות ביותר בקרב נשים — וגם מהניתנות ביותר לטי</t>
+          <t>אני איתך במסע הזה. הצעד הראשון שלך מתחיל כאן. ד"ר מאיה שרון-וינר רופאת נשים מומחית בפריון והפריה חוץ גופית מיילדות וגינקולוגיה לקביעת פגישה © 2026 כל הזכויות שמורות לד"ר מאיה שרון-וינר הברזל 9א', רמת החייל ווטסאפ למרפאה clinic@drmayasharonweiner.com פוריות האישה והגבר טיפולי פוריות הפריה חוץ גופית ו-PGD שימור פוריות פוריות לאחר סרטן ובנשאיות BRCA מעקב וליווי הריון גינקולוגיה כללית Menu Close אודות יצירת קשר מדיניות פרטיות הצהרת נגישות M</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>"מנחם נוימן"</t>
+          <t>"מאיה שרון וינר"</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -8861,11 +8869,11 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>[{"email": "info@raphaelhospitals.co.il", "confidence": 80, "source_url": "https://www.raphaelhospitals.co.il/en/international-department/about/", "identity_url": "https://www.raphaelhospitals.co.il/doctors/neuman-menahem/", "evidence": "info@raphaelhospitals.co.il", "matched_query": "\"מנחם נוימן\"", "extraction_method": "linked_mailto"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T52" t="n">
         <v>0</v>
@@ -8873,36 +8881,36 @@
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-09-04T18:20:49.705154+00:00</t>
+          <t>2026-09-04T17:43:40.101946+00:00</t>
         </is>
       </c>
       <c r="W52" t="n">
         <v>2</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y52" t="n">
         <v>7</v>
       </c>
       <c r="Z52" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>["https://professorneuman.com/", "https://professorneuman.com/he/", "https://professorneuman.com/he/contact", "https://professorneuman.com/en/contact", "https://www.facebook.com/public/%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/", "https://www.facebook.com/people/%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/pfbid0371mkxMbe96MNN5gS9XHB7KqrSyxJnXyG9AsLfdZV7j8RjCKyjm8cEEVgjSreLhY8l/", "https://chabadpedia.co.il/wiki/%D7%9E%D7%A0%D7%97%D7%9D_%D7%A0%D7%95%D7%99%D7%9E%D7%9F", "https://www.raphaelhospitals.co.il/doctors/neuman-menahem/", "https://www.raphaelhospitals.co.il/about/aboutus/", "https://www.raphaelhospitals.co.il/fields/endoscopic-unit/about/", "https://www.raphaelhospitals.co.il/fields/pain-clinic/about/", "https://www.raphaelhospitals.co.il/en/international-department/about/", "https://www.raphaelhospitals.co.il/fields/heart-catheterization-clinic/about/", "https://www.raphaelhospitals.co.il/en/about/aboutus/", "https://www.raphaelhospitals.co.il/en/contact/"]</t>
+          <t>["https://www.drmayasharonweiner.com/", "https://www.drmayasharonweiner.com/about", "https://www.drmayasharonweiner.com/contact", "https://www.medreviews.co.il/provider/dr-sharon-weiner-maya", "https://www.medreviews.co.il/provider/dr-sharon-weiner-maya/treatment", "https://www.doctorita.co.il/experts/119120", "https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr_maya_sharonweiner%2F&amp;is_from_rle", "https://docsrated.com/doctors/מאיה-שרון-וינר"]</t>
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>1.371692475599462e+17</v>
+        <v>4.115077426798385e+17</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8913,7 +8921,7 @@
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>https://professorneuman.com/he/</t>
+          <t>https://www.drmayasharonweiner.com/</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr"/>
@@ -8954,7 +8962,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>נעמה מימון</t>
+          <t>מנחם נוימן</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8985,7 +8993,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>office@medicaltop.co.il</t>
+          <t>hello@professorneuman.com</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -8998,7 +9006,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/</t>
+          <t>https://professorneuman.com/he/</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -9008,12 +9016,12 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t xml:space="preserve">ד"ר נעמה מימון: מומחית ברפואת נשים - MedicalTop Search Close Facebook 073-3310444 סנטר הגליל רחוב האגס 1, שער הרימון, קומה שניה. ראש פינה. office@medicaltop.co.il לקביעת תור דף הבית אודות תחומי פעילות הצוות שלנו יצירת קשר Menu דף הבית אודות תחומי פעילות הצוות שלנו יצירת קשר ד"ר נעמה מימון: מומחית ברפואת נשים דף הבית / רופאים / ד"ר נעמה מימון: מומחית ברפואת </t>
+          <t>פרופ׳ מנחם נוימן — אורוגינקולוגיה ורפואת רצפת האגן מגדל סוזוקי, קומה 4, רח׳ יגאל אלון 82, תל אביב 054-644-2060 · hello@professorneuman.com ראשי מידע לרופאים מידע למטופלות מהתקשורת צרי קשר English פרופ׳ מנחם נוימן אורוגינקולוגיה ורפואת רצפת האגן צניחת איברי האגן ודליפת שתן הן מהתופעות השכיחות ביותר בקרב נשים — וגם מהניתנות ביותר לטי</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>"נעמה מימון"</t>
+          <t>"מנחם נוימן"</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -9023,32 +9031,32 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "info@raphaelhospitals.co.il", "confidence": 80, "source_url": "https://www.raphaelhospitals.co.il/en/international-department/about/", "identity_url": "https://www.raphaelhospitals.co.il/doctors/neuman-menahem/", "evidence": "info@raphaelhospitals.co.il", "matched_query": "\"מנחם נוימן\"", "extraction_method": "linked_mailto"}]</t>
         </is>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-09-04T05:17:30.924388+00:00</t>
+          <t>2026-09-04T18:20:49.705154+00:00</t>
         </is>
       </c>
       <c r="W53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X53" t="n">
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z53" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -9060,14 +9068,14 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>["https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fn.mh.mymwn.2025%2F", "https://www.facebook.com/SNMaesthetic/services/", "https://www.doctorita.co.il/experts/152626", "https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/", "https://medicaltop.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://medicaltop.co.il/%D7%94%D7%A6%D7%95%D7%95%D7%AA-%D7%A9%D7%9C%D7%A0%D7%95/", "https://medicaltop.co.il/wp-content/uploads/2024/04/אודות.jpg"]</t>
+          <t>["https://professorneuman.com/", "https://professorneuman.com/he/", "https://professorneuman.com/he/contact", "https://professorneuman.com/en/contact", "https://www.facebook.com/public/%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/", "https://www.facebook.com/people/%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/pfbid0371mkxMbe96MNN5gS9XHB7KqrSyxJnXyG9AsLfdZV7j8RjCKyjm8cEEVgjSreLhY8l/", "https://chabadpedia.co.il/wiki/%D7%9E%D7%A0%D7%97%D7%9D_%D7%A0%D7%95%D7%99%D7%9E%D7%9F", "https://www.raphaelhospitals.co.il/doctors/neuman-menahem/", "https://www.raphaelhospitals.co.il/about/aboutus/", "https://www.raphaelhospitals.co.il/fields/endoscopic-unit/about/", "https://www.raphaelhospitals.co.il/fields/pain-clinic/about/", "https://www.raphaelhospitals.co.il/en/international-department/about/", "https://www.raphaelhospitals.co.il/fields/heart-catheterization-clinic/about/", "https://www.raphaelhospitals.co.il/en/about/aboutus/", "https://www.raphaelhospitals.co.il/en/contact/"]</t>
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>1.338292358663048e+17</v>
+        <v>4.115077426798385e+17</v>
       </c>
       <c r="AE53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF53" t="n">
         <v>0</v>
@@ -9075,7 +9083,7 @@
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/</t>
+          <t>https://professorneuman.com/he/</t>
         </is>
       </c>
       <c r="AI53" t="inlineStr"/>
@@ -9093,7 +9101,7 @@
         <v>1</v>
       </c>
       <c r="AS53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT53" t="b">
         <v>1</v>
@@ -9116,7 +9124,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>תמר גרין</t>
+          <t>נעמה מימון</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9147,7 +9155,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>office@keshet-refua.co.il</t>
+          <t>office@medicaltop.co.il</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -9160,7 +9168,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://keshet-refua.co.il/doctors/dr-tamar-green/</t>
+          <t>https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -9170,17 +9178,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>פיזיותרפיה אסתטיקה פודקסטים קליניקות וססיות להשכרה צור קשר זימון תור ד"ר תמר גרין מומחית לגינקולוגיה ומיילדות מעקב הריון, סקירת הריון מוקדמת ומאוחרת, בדיקות אולטרסאונד אבחנתיות, גיל המעבר ובדיקות גינקולוגיות 073-3214111 office@keshet-refua.co.il לזימון תור &gt; תחומי מומחיות מעקב הריון בדיקות אולטרהסאונד אבחנתיות שקיפות עורפית סקירת מערכות מוקדמת ומאוחרת מעקבי גדילה הדמיית אגן והדמיה תלת מימדית של הרחם טיפולי גינקולוגיה פרטית התקנים תוך רח</t>
+          <t xml:space="preserve">ד"ר נעמה מימון: מומחית ברפואת נשים - MedicalTop Search Close Facebook 073-3310444 סנטר הגליל רחוב האגס 1, שער הרימון, קומה שניה. ראש פינה. office@medicaltop.co.il לקביעת תור דף הבית אודות תחומי פעילות הצוות שלנו יצירת קשר Menu דף הבית אודות תחומי פעילות הצוות שלנו יצירת קשר ד"ר נעמה מימון: מומחית ברפואת נשים דף הבית / רופאים / ד"ר נעמה מימון: מומחית ברפואת </t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>"תמר גרין"</t>
+          <t>"נעמה מימון"</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>official_text</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -9197,39 +9205,39 @@
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-09-05T00:09:39.798497+00:00</t>
+          <t>2026-09-04T05:17:30.924388+00:00</t>
         </is>
       </c>
       <c r="W54" t="n">
+        <v>4</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>["https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fn.mh.mymwn.2025%2F", "https://www.facebook.com/SNMaesthetic/services/", "https://www.doctorita.co.il/experts/152626", "https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/", "https://medicaltop.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://medicaltop.co.il/%D7%94%D7%A6%D7%95%D7%95%D7%AA-%D7%A9%D7%9C%D7%A0%D7%95/", "https://medicaltop.co.il/wp-content/uploads/2024/04/אודות.jpg"]</t>
+        </is>
+      </c>
+      <c r="AD54" t="n">
+        <v>4.014877075989144e+17</v>
+      </c>
+      <c r="AE54" t="n">
         <v>2</v>
-      </c>
-      <c r="X54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>ddgs:bing</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>["https://www.medreviews.co.il/provider/dr-green-tamar", "https://keshet-refua.co.il/doctors/dr-tamar-green/", "https://keshet-refua.co.il/about-us/", "https://keshet-refua.co.il/contact-us/", "https://keshet-refua.co.il/clinics-for-rent-sessional-clinics-for-rent/", "https://keshet-refua.co.il/about-us/#contact-keshet-medical-center", "https://keshet-refua.co.il/areas_of_expertise/child-psychology-clinic/", "https://keshet-refua.co.il/doctors/private-clinical-dietician-jerusalem/", "https://keshet-refua.co.il/contact-us/#contact-keshet-medical-center", "https://keshet-refua.co.il/clinics-for-rent-sessional-clinics-for-rent/#contact-keshet-medical-center", "https://keshet-refua.co.il/doctors/dr-tamar-green-private-gynecologist-in-jerusalem/", "https://wayzee.co.il/", "https://keshet-refua.co.il/treatments/menstrual-arrangement-before-the-wedding-private-womens-clinic-private-gynecologist/", "https://keshet-refua.co.il/areas_of_expertise/child-psychology-clinic/#contact-keshet-medical-center", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2F61558661827898%2F", "https://www.facebook.com/public/%D7%AA%D7%9E%D7%A8-%D7%92%D7%A8%D7%99%D7%9F/", "https://www.medreviews.co.il/provider/dr-green-tamar/treatment/gynecologist-clinic", "https://www.szmc.org.il/doctors/grin-tamar/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
-        </is>
-      </c>
-      <c r="AD54" t="n">
-        <v>1.33559798083719e+17</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>1</v>
       </c>
       <c r="AF54" t="n">
         <v>0</v>
@@ -9237,7 +9245,7 @@
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>https://keshet-refua.co.il/doctors/dr-tamar-green/</t>
+          <t>https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/</t>
         </is>
       </c>
       <c r="AI54" t="inlineStr"/>
@@ -9255,7 +9263,7 @@
         <v>1</v>
       </c>
       <c r="AS54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT54" t="b">
         <v>1</v>
@@ -9278,7 +9286,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>אבי צפריר</t>
+          <t>תמר גרין</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9309,7 +9317,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>ivfrec@szmc.org.il</t>
+          <t>office@keshet-refua.co.il</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -9318,11 +9326,11 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/tsafrir-avi/</t>
+          <t>https://keshet-refua.co.il/doctors/dr-tamar-green/</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -9332,17 +9340,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t xml:space="preserve">h عربيه Русский צרו קשר צרו קשר אזור אישי אזור אישי רופאים בשערי צדק ד"ר  אבי צפריר רופא בכיר Dr.  Avi Tsafrir התמחות: גינקולוגיה ויילוד תת התמחות: הפריה חוץ גופית תחומים נוספים: שימור פוריות פוריות הגבר פוריות האשה עוד ivfrec@szmc.org.il ivfrec@szmc.org.il נסיון מקצועי מומחה ביילוד ובגינקולוגיה משנת 2005 רופא בכיר להפריה חוץ גופית בשערי צדק משנת 2005 תפקידים ציבוריים חבר ועד האגודה הישראלית לחקר הפוריות משנת 2022 לימודים והכשרה פקולטה </t>
+          <t>פיזיותרפיה אסתטיקה פודקסטים קליניקות וססיות להשכרה צור קשר זימון תור ד"ר תמר גרין מומחית לגינקולוגיה ומיילדות מעקב הריון, סקירת הריון מוקדמת ומאוחרת, בדיקות אולטרסאונד אבחנתיות, גיל המעבר ובדיקות גינקולוגיות 073-3214111 office@keshet-refua.co.il לזימון תור &gt; תחומי מומחיות מעקב הריון בדיקות אולטרהסאונד אבחנתיות שקיפות עורפית סקירת מערכות מוקדמת ומאוחרת מעקבי גדילה הדמיית אגן והדמיה תלת מימדית של הרחם טיפולי גינקולוגיה פרטית התקנים תוך רח</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>"אבי צפריר"</t>
+          <t>"תמר גרין"</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>official_text</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -9359,11 +9367,11 @@
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-09-03T20:26:52.799327+00:00</t>
+          <t>2026-09-05T00:09:39.798497+00:00</t>
         </is>
       </c>
       <c r="W55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X55" t="n">
         <v>0</v>
@@ -9375,7 +9383,7 @@
         <v>6</v>
       </c>
       <c r="AA55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
@@ -9384,14 +9392,14 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>["https://www.infomed.co.il/experts/73913/", "https://he.hadassah.org.il/doctor/dr-avi-tsafrir-gaadaabqaa2aaoiag4adaabyaa======/", "https://www.doctors.co.il/expert/obstetrics-and-gynecologists/80043972/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fbyzpryr%2F", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A6%D7%A4%D7%A8%D7%99%D7%A8-%D7%90%D7%91%D7%99/", "https://drtor.co.il/doctor/3910", "https://www.szmc.org.il/doctors/tsafrir-avi/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.clalit.co.il/he/sefersherut/pages/doctordetails.aspx", "https://docsrated.com/doctors/אבי-צפריר", "https://www.doctorita.co.il/experts/44804"]</t>
+          <t>["https://www.medreviews.co.il/provider/dr-green-tamar", "https://keshet-refua.co.il/doctors/dr-tamar-green/", "https://keshet-refua.co.il/about-us/", "https://keshet-refua.co.il/contact-us/", "https://keshet-refua.co.il/clinics-for-rent-sessional-clinics-for-rent/", "https://keshet-refua.co.il/about-us/#contact-keshet-medical-center", "https://keshet-refua.co.il/areas_of_expertise/child-psychology-clinic/", "https://keshet-refua.co.il/doctors/private-clinical-dietician-jerusalem/", "https://keshet-refua.co.il/contact-us/#contact-keshet-medical-center", "https://keshet-refua.co.il/clinics-for-rent-sessional-clinics-for-rent/#contact-keshet-medical-center", "https://keshet-refua.co.il/doctors/dr-tamar-green-private-gynecologist-in-jerusalem/", "https://wayzee.co.il/", "https://keshet-refua.co.il/treatments/menstrual-arrangement-before-the-wedding-private-womens-clinic-private-gynecologist/", "https://keshet-refua.co.il/areas_of_expertise/child-psychology-clinic/#contact-keshet-medical-center", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2F61558661827898%2F", "https://www.facebook.com/public/%D7%AA%D7%9E%D7%A8-%D7%92%D7%A8%D7%99%D7%9F/", "https://www.medreviews.co.il/provider/dr-green-tamar/treatment/gynecologist-clinic", "https://www.szmc.org.il/doctors/grin-tamar/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>1.778899381345597e+17</v>
+        <v>4.006793942511569e+17</v>
       </c>
       <c r="AE55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF55" t="n">
         <v>0</v>
@@ -9399,7 +9407,7 @@
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/tsafrir-avi/</t>
+          <t>https://keshet-refua.co.il/doctors/dr-tamar-green/</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr"/>
@@ -9417,7 +9425,7 @@
         <v>1</v>
       </c>
       <c r="AS55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT55" t="b">
         <v>1</v>
@@ -9440,17 +9448,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>אירינה דורפמן אלמוג</t>
+          <t>אבי צפריר</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>family_doctor</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -9471,20 +9479,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>dr.irenadorfman@gmail.com</t>
+          <t>ivfrec@szmc.org.il</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
+          <t>https://www.szmc.org.il/doctors/tsafrir-avi/</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -9494,12 +9502,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>מוג אירינה כרטיס עסק: ד"ר דורפמן אלמוג אירינה » תחום פעילות: בריאות וספורט » רופא » תאור העסק: רופאת משפחה עצמאית קופת חולים לאומית. » איש קשר: אירנה דורפמן » טלפונים: טלפון: 077-7997456 נייד: 054-4616457 » אתר: » מייל: dr.irenadorfman@gmail.com » כתובת: בן גוריון 123 יהוד, מיקוד: 56209 כלים מחשבונים לעסקים מדריכי ניהול עסק, הקמת עסק נושאי האתר הנהלת חשבונות הפקת חשבוניות חשבונית אלקטרונית ניהול לקוחות שותפים עסקיים אילת סיטי - מדריך הע</t>
+          <t xml:space="preserve">h عربيه Русский צרו קשר צרו קשר אזור אישי אזור אישי רופאים בשערי צדק ד"ר  אבי צפריר רופא בכיר Dr.  Avi Tsafrir התמחות: גינקולוגיה ויילוד תת התמחות: הפריה חוץ גופית תחומים נוספים: שימור פוריות פוריות הגבר פוריות האשה עוד ivfrec@szmc.org.il ivfrec@szmc.org.il נסיון מקצועי מומחה ביילוד ובגינקולוגיה משנת 2005 רופא בכיר להפריה חוץ גופית בשערי צדק משנת 2005 תפקידים ציבוריים חבר ועד האגודה הישראלית לחקר הפוריות משנת 2022 לימודים והכשרה פקולטה </t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>"אירינה דורפמן אלמוג"</t>
+          <t>"אבי צפריר"</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -9509,32 +9517,32 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>[{"email": "info@flex.co.il", "confidence": 80, "source_url": "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "identity_url": "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "evidence": "info@flex.co.il", "matched_query": "\"אירינה דורפמן אלמוג\"", "extraction_method": "linked_mailto"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-09-04T19:17:26.299485+00:00</t>
+          <t>2026-09-03T20:26:52.799327+00:00</t>
         </is>
       </c>
       <c r="W56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z56" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AA56" t="n">
         <v>2</v>
@@ -9546,14 +9554,14 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>["https://www.dunsguide.co.il/C7195b21475cb11a3e5b86def04a3e20c_רופאים/דורפמן_אלמוג_אירינה/", "https://medpage.co.il/doctors/%D7%90%D7%99%D7%A8%D7%A0%D7%94-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-20871/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94/", "https://www.beok.co.il/doctors/Doctors-129241/", "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "https://www.flex.co.il/100_General/005_GeneralPages/006_About.aspx", "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "https://www.flex.co.il/100_General/900_DifferentStuff/900_ForTheCommunity.aspx"]</t>
+          <t>["https://www.infomed.co.il/experts/73913/", "https://he.hadassah.org.il/doctor/dr-avi-tsafrir-gaadaabqaa2aaoiag4adaabyaa======/", "https://www.doctors.co.il/expert/obstetrics-and-gynecologists/80043972/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fbyzpryr%2F", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A6%D7%A4%D7%A8%D7%99%D7%A8-%D7%90%D7%91%D7%99/", "https://drtor.co.il/doctor/3910", "https://www.szmc.org.il/doctors/tsafrir-avi/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.clalit.co.il/he/sefersherut/pages/doctordetails.aspx", "https://docsrated.com/doctors/אבי-צפריר", "https://www.doctorita.co.il/experts/44804"]</t>
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>1.445508259254136e+17</v>
+        <v>5.336698144036791e+17</v>
       </c>
       <c r="AE56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF56" t="n">
         <v>0</v>
@@ -9561,7 +9569,7 @@
       <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
+          <t>https://www.szmc.org.il/doctors/tsafrir-avi/</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr"/>
@@ -9579,17 +9587,17 @@
         <v>1</v>
       </c>
       <c r="AS56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT56" t="b">
         <v>1</v>
       </c>
       <c r="AU56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>PERSON</t>
+          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
       </c>
     </row>
@@ -9602,7 +9610,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>אלון שלב</t>
+          <t>אירינה דורפמן אלמוג</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9633,7 +9641,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>alonshalev31@gmail.com</t>
+          <t>dr.irenadorfman@gmail.com</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -9646,7 +9654,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://pain.coi.co.il/</t>
+          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -9656,12 +9664,12 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>הודעה לבעלי האתר תקופת הניסיון הסתיימה, יש ליצור מנוי דרך ממשק ניהול האתר. האתר נכנס לרשימת המחיקה ויימחק בקרוב לחץ כאן אם אינך זוכר את כתובת ממשק ניהול האתר שלך. דר אלון שלב - רופא כאב טלפון: 054-6221105 מייל: alonshalev31@gmail.com כתובת: ילדי טהרן 8, ראשון לציון ד"ר אלון שלב מומחה ברפואת המשפחה רופא כאב דף הבית אודות צור קשר אל תחכו - הזמינו תור לרופא עוד היום.. לייעוץ ראשוני ללא עלות והזמנת תורים מלאו פרטים או התקשרו: 05462</t>
+          <t>מוג אירינה כרטיס עסק: ד"ר דורפמן אלמוג אירינה » תחום פעילות: בריאות וספורט » רופא » תאור העסק: רופאת משפחה עצמאית קופת חולים לאומית. » איש קשר: אירנה דורפמן » טלפונים: טלפון: 077-7997456 נייד: 054-4616457 » אתר: » מייל: dr.irenadorfman@gmail.com » כתובת: בן גוריון 123 יהוד, מיקוד: 56209 כלים מחשבונים לעסקים מדריכי ניהול עסק, הקמת עסק נושאי האתר הנהלת חשבונות הפקת חשבוניות חשבונית אלקטרונית ניהול לקוחות שותפים עסקיים אילת סיטי - מדריך הע</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>"אלון שלב"</t>
+          <t>"אירינה דורפמן אלמוג"</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -9671,11 +9679,11 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "info@flex.co.il", "confidence": 80, "source_url": "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "identity_url": "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "evidence": "info@flex.co.il", "matched_query": "\"אירינה דורפמן אלמוג\"", "extraction_method": "linked_mailto"}]</t>
         </is>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T57" t="n">
         <v>0</v>
@@ -9683,23 +9691,23 @@
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-09-04T19:37:15.755041+00:00</t>
+          <t>2026-09-04T19:17:26.299485+00:00</t>
         </is>
       </c>
       <c r="W57" t="n">
         <v>2</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z57" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
@@ -9708,11 +9716,11 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>["https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr.shalev.pain%2F&amp;is_from_rle", "https://www.bgu.ac.il/people/shalevn/", "https://www.bgu.ac.il/en/people/shalevn/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fdr.shalev.pain%2F", "https://www.medreviews.co.il/search/pain-management/center/rishon-lezion", "https://pain.coi.co.il/", "https://pain.coi.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA.htm", "https://pain.coi.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8.htm"]</t>
+          <t>["https://www.dunsguide.co.il/C7195b21475cb11a3e5b86def04a3e20c_רופאים/דורפמן_אלמוג_אירינה/", "https://medpage.co.il/doctors/%D7%90%D7%99%D7%A8%D7%A0%D7%94-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-20871/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94/", "https://www.beok.co.il/doctors/Doctors-129241/", "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "https://www.flex.co.il/100_General/005_GeneralPages/006_About.aspx", "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "https://www.flex.co.il/100_General/900_DifferentStuff/900_ForTheCommunity.aspx"]</t>
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>1.445508259254136e+17</v>
+        <v>4.336524777762407e+17</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9723,7 +9731,7 @@
       <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>https://pain.coi.co.il/</t>
+          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr"/>
@@ -9764,7 +9772,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>אמיר צבעוני</t>
+          <t>אלון שלב</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9795,7 +9803,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>healtms@gmail.com</t>
+          <t>alonshalev31@gmail.com</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -9808,7 +9816,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://www.drzivony.co.il/</t>
+          <t>https://pain.coi.co.il/</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -9818,12 +9826,12 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>"ר אמיר צבעוני ד"ר אמיר צבעוני רופא משפחה מומחה העוסק בטיפול בכאב כרוני בגישת גוף-נפש ללא שימוש בתרופות או בפרוצדורות רפואיות. הטיפול מבוסס מחקר בתחום מדעי המח והכאב. ניתן לקרוא עליי עוד ב דף האודות . טלפון: 051-2303120 healtms@gmail.com קליניקה בגבעת עדה (סמוך לבנימינה) ניתן ליצור איתי קשר גם ב דף יצירת הקשר פוסטים אחרונים על הענק הירוק והדחקת רגשות לאותת עם המגבים רגישות יתר לאחר פציעה אזהרת טריגר בקשת סליחה מעצמי חפש: חיפוש בית אודות</t>
+          <t>הודעה לבעלי האתר תקופת הניסיון הסתיימה, יש ליצור מנוי דרך ממשק ניהול האתר. האתר נכנס לרשימת המחיקה ויימחק בקרוב לחץ כאן אם אינך זוכר את כתובת ממשק ניהול האתר שלך. דר אלון שלב - רופא כאב טלפון: 054-6221105 מייל: alonshalev31@gmail.com כתובת: ילדי טהרן 8, ראשון לציון ד"ר אלון שלב מומחה ברפואת המשפחה רופא כאב דף הבית אודות צור קשר אל תחכו - הזמינו תור לרופא עוד היום.. לייעוץ ראשוני ללא עלות והזמנת תורים מלאו פרטים או התקשרו: 05462</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>"אמיר צבעוני"</t>
+          <t>"אלון שלב"</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -9845,7 +9853,7 @@
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-09-03T23:00:56.706890+00:00</t>
+          <t>2026-09-04T19:37:15.755041+00:00</t>
         </is>
       </c>
       <c r="W58" t="n">
@@ -9855,10 +9863,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Z58" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -9870,11 +9878,11 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>["https://www.drzivony.co.il/", "https://www.drzivony.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
+          <t>["https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr.shalev.pain%2F&amp;is_from_rle", "https://www.bgu.ac.il/people/shalevn/", "https://www.bgu.ac.il/en/people/shalevn/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fdr.shalev.pain%2F", "https://www.medreviews.co.il/search/pain-management/center/rishon-lezion", "https://pain.coi.co.il/", "https://pain.coi.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA.htm", "https://pain.coi.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8.htm"]</t>
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>1.445355747304436e+17</v>
+        <v>4.336524777762407e+17</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9885,7 +9893,7 @@
       <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>https://www.drzivony.co.il/</t>
+          <t>https://pain.coi.co.il/</t>
         </is>
       </c>
       <c r="AI58" t="inlineStr"/>
@@ -9926,7 +9934,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>בתיה קורנבוים</t>
+          <t>אמיר צבעוני</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9957,7 +9965,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>batyakornboim@gmail.com</t>
+          <t>healtms@gmail.com</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -9970,7 +9978,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://www.dr-batya-kornboim.com/</t>
+          <t>https://www.drzivony.co.il/</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -9980,12 +9988,12 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>שקל בחיפה אודות חוות דעת יצירת קשר כתבות ופרסומים תפריט ד״ר בתיה קורנבוים - מומחית ברפואת משפחה ורפואת השמנה [תיאור המרפאה יתווסף בהמשך] טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו חיפה 3570901 IL 052-567-1100 batyakornboim@gmail.com התמחויות רפואיות עיקריות: [פירוט תחומי הטיפול יתווסף בהמשך] מידע מעשי: יצירת קשר: טלפון 052-567-1100 או וואטסאפ 052-567-1100 מיקום: טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו , חיפה סוג</t>
+          <t>"ר אמיר צבעוני ד"ר אמיר צבעוני רופא משפחה מומחה העוסק בטיפול בכאב כרוני בגישת גוף-נפש ללא שימוש בתרופות או בפרוצדורות רפואיות. הטיפול מבוסס מחקר בתחום מדעי המח והכאב. ניתן לקרוא עליי עוד ב דף האודות . טלפון: 051-2303120 healtms@gmail.com קליניקה בגבעת עדה (סמוך לבנימינה) ניתן ליצור איתי קשר גם ב דף יצירת הקשר פוסטים אחרונים על הענק הירוק והדחקת רגשות לאותת עם המגבים רגישות יתר לאחר פציעה אזהרת טריגר בקשת סליחה מעצמי חפש: חיפוש בית אודות</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>"בתיה קורנבוים"</t>
+          <t>"אמיר צבעוני"</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -10007,7 +10015,7 @@
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-09-03T23:52:50.148875+00:00</t>
+          <t>2026-09-03T23:00:56.706890+00:00</t>
         </is>
       </c>
       <c r="W59" t="n">
@@ -10032,11 +10040,11 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>["https://www.dr-batya-kornboim.com/", "https://www.dr-batya-kornboim.com/#%D7%90%D7%95%D7%93%D7%95%D7%AA"]</t>
+          <t>["https://www.drzivony.co.il/", "https://www.drzivony.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>1.445355747304436e+17</v>
+        <v>4.336067241913308e+17</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -10047,7 +10055,7 @@
       <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>https://www.dr-batya-kornboim.com/</t>
+          <t>https://www.drzivony.co.il/</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr"/>
@@ -10088,7 +10096,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>שלומית שדמון</t>
+          <t>בתיה קורנבוים</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10119,7 +10127,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>shlomitshadmon@gmail.com</t>
+          <t>batyakornboim@gmail.com</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -10132,7 +10140,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
+          <t>https://www.dr-batya-kornboim.com/</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -10142,12 +10150,12 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>ם ופעילויות כנסים והשתלמויות הרצאות מהכנסים מטפלי.ות איט"ם מטפלי.ות איט"ם פיזיותרפיסטים.ית איט"ם מרפאות ציבוריות הצטרפות והתמחות צור קשר פרטי התקשרות טלפון 054-9145177 כתובת אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אימייל shlomitshadmon@gmail.com שדמון שלומית (MD) – תל אביב מקצוע:  רופאת משפחה, מוסמכת ביעוץ וטיפול מיני. התמחות: מטפלת מינית איזור טיפול: תל אביב אודותי אני רופאת משפחה ותיקה, מדריכה קלינית ומרצה בנושאי בריאות האישה, מיניות ה</t>
+          <t>שקל בחיפה אודות חוות דעת יצירת קשר כתבות ופרסומים תפריט ד״ר בתיה קורנבוים - מומחית ברפואת משפחה ורפואת השמנה [תיאור המרפאה יתווסף בהמשך] טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו חיפה 3570901 IL 052-567-1100 batyakornboim@gmail.com התמחויות רפואיות עיקריות: [פירוט תחומי הטיפול יתווסף בהמשך] מידע מעשי: יצירת קשר: טלפון 052-567-1100 או וואטסאפ 052-567-1100 מיקום: טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו , חיפה סוג</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>"שלומית שדמון"</t>
+          <t>"בתיה קורנבוים"</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -10157,11 +10165,11 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "identity_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "evidence": "mail.com אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"שלומית שדמון\"", "extraction_method": "direct_text"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T60" t="n">
         <v>0</v>
@@ -10169,7 +10177,7 @@
       <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-09-04T15:25:57.140597+00:00</t>
+          <t>2026-09-03T23:52:50.148875+00:00</t>
         </is>
       </c>
       <c r="W60" t="n">
@@ -10179,10 +10187,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z60" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -10194,11 +10202,11 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>["https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA/", "https://moonbellboutique.com/index/%D7%93%D7%A8-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%A9%D7%93%D7%9E%D7%95%D7%9F/", "https://moonbellboutique.com/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/", "https://www.infomed.co.il/experts/145161/", "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
+          <t>["https://www.dr-batya-kornboim.com/", "https://www.dr-batya-kornboim.com/#%D7%90%D7%95%D7%93%D7%95%D7%AA"]</t>
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>1.334632071822425e+17</v>
+        <v>4.336067241913308e+17</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -10209,7 +10217,7 @@
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
+          <t>https://www.dr-batya-kornboim.com/</t>
         </is>
       </c>
       <c r="AI60" t="inlineStr"/>
@@ -10250,7 +10258,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>שרון שלמה קלייטמן</t>
+          <t>שלומית שדמון</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10281,7 +10289,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>sharon.kleitman@gmail.com</t>
+          <t>shlomitshadmon@gmail.com</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -10294,7 +10302,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
+          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -10304,12 +10312,12 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>ש קשר שיתוף שתפו במייל שתפו בפייסבוק שתפו בטוויטר שתפו בלינקדין ד"ר שרון קלייטמן מומחה ברפואת משפחה, MST - Mind Set Technique, רפואה אינטגרטיבית, IMS - דיקור יבש, תזונה אינטגרטיבית. נייד 052-8325580 פקס 08-6560357 דוא"ל sharon.kleitman@gmail.com אתר www.integrative-med.com שלח/י לי sms פייסבוק אודות ד"ר שרון קלייטמן מומחה ברפואת משפחה, סיים את לימודי הרפואה באוניברסיטת בן גוריון, נשוי ואב לארבעה, מתגורר בקיבוץ שדה בוקר. עוסק בפיתוח והקנ</t>
+          <t>ם ופעילויות כנסים והשתלמויות הרצאות מהכנסים מטפלי.ות איט"ם מטפלי.ות איט"ם פיזיותרפיסטים.ית איט"ם מרפאות ציבוריות הצטרפות והתמחות צור קשר פרטי התקשרות טלפון 054-9145177 כתובת אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אימייל shlomitshadmon@gmail.com שדמון שלומית (MD) – תל אביב מקצוע:  רופאת משפחה, מוסמכת ביעוץ וטיפול מיני. התמחות: מטפלת מינית איזור טיפול: תל אביב אודותי אני רופאת משפחה ותיקה, מדריכה קלינית ומרצה בנושאי בריאות האישה, מיניות ה</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>"שרון שלמה קלייטמן"</t>
+          <t>"שלומית שדמון"</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -10319,11 +10327,11 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "identity_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "evidence": "mail.com אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"שלומית שדמון\"", "extraction_method": "direct_text"}]</t>
         </is>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T61" t="n">
         <v>0</v>
@@ -10331,7 +10339,7 @@
       <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-09-04T15:41:54.743203+00:00</t>
+          <t>2026-09-04T15:25:57.140597+00:00</t>
         </is>
       </c>
       <c r="W61" t="n">
@@ -10344,10 +10352,10 @@
         <v>4</v>
       </c>
       <c r="Z61" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
@@ -10356,11 +10364,11 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>["https://docsrated.com/doctors/שרון-קלייטמן", "https://www.dunsguide.co.il/Cb6a87819a48606a97ab6b3a3617e9370_רופאים/קלייטמן_שרון_שלמה/", "https://www.facebook.com/sharon.kleitman.md/directory_category/", "https://dns.dibiz.com/sharon-kleitman-md", "https://longevitepalmbeach.com"]</t>
+          <t>["https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA/", "https://moonbellboutique.com/index/%D7%93%D7%A8-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%A9%D7%93%D7%9E%D7%95%D7%9F/", "https://moonbellboutique.com/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/", "https://www.infomed.co.il/experts/145161/", "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>1.334632071822425e+17</v>
+        <v>4.003896215467274e+17</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10371,7 +10379,7 @@
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
+          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
         </is>
       </c>
       <c r="AI61" t="inlineStr"/>
@@ -10412,7 +10420,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>איה שלם</t>
+          <t>שרון שלמה קלייטמן</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10443,20 +10451,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>info@shrir-sheled.co.il</t>
+          <t>sharon.kleitman@gmail.com</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/</t>
+          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -10466,12 +10474,12 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>ד"ר איה שלם - אינדקס מטפלים ברפואת שריר שלד דלג לתוכן info@shrir-sheled.co.il בית רשימת המטפלים מאמרים מקצועיים אודות מקצוע המטפל רפואת משפחה פיזיותרפיה אוסטיאופתיה כירופרקטיקה אורתופדיה צרו קשר תפריט בית רשימת המטפלים מאמרים מקצועיים אודות מקצוע המטפל רפואת משפחה פיזיותרפי</t>
+          <t>ש קשר שיתוף שתפו במייל שתפו בפייסבוק שתפו בטוויטר שתפו בלינקדין ד"ר שרון קלייטמן מומחה ברפואת משפחה, MST - Mind Set Technique, רפואה אינטגרטיבית, IMS - דיקור יבש, תזונה אינטגרטיבית. נייד 052-8325580 פקס 08-6560357 דוא"ל sharon.kleitman@gmail.com אתר www.integrative-med.com שלח/י לי sms פייסבוק אודות ד"ר שרון קלייטמן מומחה ברפואת משפחה, סיים את לימודי הרפואה באוניברסיטת בן גוריון, נשוי ואב לארבעה, מתגורר בקיבוץ שדה בוקר. עוסק בפיתוח והקנ</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>"איה שלם"</t>
+          <t>"שרון שלמה קלייטמן"</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -10493,7 +10501,7 @@
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-09-04T18:58:24.569451+00:00</t>
+          <t>2026-09-04T15:41:54.743203+00:00</t>
         </is>
       </c>
       <c r="W62" t="n">
@@ -10503,13 +10511,13 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z62" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AA62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
@@ -10518,11 +10526,11 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>["https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%9C%D7%9D-%D7%90%D7%99%D7%94/", "https://medpage.co.il/doctors/16196-%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D-8959/", "https://www.doctorita.co.il/experts/124568", "https://drtor.co.il/doctor/19921", "http://me.doctorsonly.co.il/user/2636", "https://www.infomed.co.il/experts/74772/", "https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/", "https://eshkol.media/", "https://shrir-sheled.co.il/about/"]</t>
+          <t>["https://docsrated.com/doctors/שרון-קלייטמן", "https://www.dunsguide.co.il/Cb6a87819a48606a97ab6b3a3617e9370_רופאים/קלייטמן_שרון_שלמה/", "https://www.facebook.com/sharon.kleitman.md/directory_category/", "https://dns.dibiz.com/sharon-kleitman-md", "https://longevitepalmbeach.com"]</t>
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>1.445508259254136e+17</v>
+        <v>4.003896215467274e+17</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10533,7 +10541,7 @@
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/</t>
+          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
         </is>
       </c>
       <c r="AI62" t="inlineStr"/>
@@ -10557,9 +10565,171 @@
         <v>1</v>
       </c>
       <c r="AU62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV62" t="inlineStr">
+        <is>
+          <t>PERSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>13</v>
+      </c>
+      <c r="B63" t="n">
+        <v>6</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>איה שלם</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>family_doctor</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>moh</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>info@shrir-sheled.co.il</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>CLINIC_OR_ORGANIZATION</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>88</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>ד"ר איה שלם - אינדקס מטפלים ברפואת שריר שלד דלג לתוכן info@shrir-sheled.co.il בית רשימת המטפלים מאמרים מקצועיים אודות מקצוע המטפל רפואת משפחה פיזיותרפיה אוסטיאופתיה כירופרקטיקה אורתופדיה צרו קשר תפריט בית רשימת המטפלים מאמרים מקצועיים אודות מקצוע המטפל רפואת משפחה פיזיותרפי</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>"איה שלם"</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>direct_text</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S63" t="n">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-09-04T18:58:24.569451+00:00</t>
+        </is>
+      </c>
+      <c r="W63" t="n">
+        <v>2</v>
+      </c>
+      <c r="X63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>["https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%9C%D7%9D-%D7%90%D7%99%D7%94/", "https://medpage.co.il/doctors/16196-%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D-8959/", "https://www.doctorita.co.il/experts/124568", "https://drtor.co.il/doctor/19921", "http://me.doctorsonly.co.il/user/2636", "https://www.infomed.co.il/experts/74772/", "https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/", "https://eshkol.media/", "https://shrir-sheled.co.il/about/"]</t>
+        </is>
+      </c>
+      <c r="AD63" t="n">
+        <v>4.336524777762407e+17</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="inlineStr"/>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr"/>
+      <c r="AJ63" t="inlineStr"/>
+      <c r="AK63" t="inlineStr"/>
+      <c r="AL63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM63" t="inlineStr"/>
+      <c r="AN63" t="inlineStr"/>
+      <c r="AO63" t="inlineStr"/>
+      <c r="AP63" t="inlineStr"/>
+      <c r="AQ63" t="inlineStr"/>
+      <c r="AR63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV63" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>

--- a/output/contacts_primary.xlsx
+++ b/output/contacts_primary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV63"/>
+  <dimension ref="A1:AV66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -616,32 +616,32 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>verification_schema_version</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>identity_name_verified</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>identity_specialty_verified</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>identity_evidence</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
           <t>verification_review_required</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>previous_candidate</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>verification_schema_version</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>identity_name_verified</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>identity_specialty_verified</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>identity_evidence</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>אביטל ורטהיימר</t>
+          <t>אבי גולדברג</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>avital.wer@gmail.com</t>
+          <t>dravigol@gmail.com</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://www.dravitalwertheimer.com/contact</t>
+          <t>https://biobalance.co.il/about-us-https-biobalance-co-il/</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -733,85 +733,93 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>זרעה תוך הרחמית More Use tab to navigate through the menu items. Dr. Avital Wertheimer רופאת נשים מומחית בפריון, מיילדות וגניקולוגיה ד״ר אביטל ורטהיימר כתובת ברודצקי 43, ת״א המרכז לבריאות האישה רמת אביב sec101@bri.co.il avital.wer@gmail.com 03 - 7620620 Mail Phone Mail ד״ר אביטל ורטהיימר ​ רופאת נשיםֿֿ, מומחית בגניקולוגיה ומיילדות ​ ​ ​ ​ כתובת המרפאה ברודצקי 43, ת״א המרכז לבריאות האישה רמת אביב ג׳ © By Roni Rapaport, Wix bottom of page</t>
+          <t>אודות ד"ר אבי גולדברג - Dr. Avi Goldberg - BioBalance 050-6020061 drAviGol@gmail.com Facebook עמוד הבית צוות המרפאה ד”ר אבי גולדברג אורי מנהלת המרפאה שירותי המרפאה תהליך הטיפול מאמרים שאלות ותשובות צרו קשר עמוד הבית צוות המרפאה ד”ר אבי גולדברג אורי מנהלת המרפאה שירותי המרפאה תהליך הטיפ</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>"אביטל ורטהיימר"</t>
+          <t>"אבי גולדברג" רפואת משפחה</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>linked_text</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>[{"email": "sec101@bri.co.il", "confidence": 98, "source_url": "https://www.dravitalwertheimer.com/contact", "identity_url": "https://www.dravitalwertheimer.com/", "evidence": "הפריה חוץ גופית הזרעה תוך הרחמית More Use tab to navigate through the menu items. Dr. Avital Wertheimer רופאת נשים מומחית בפריון, מיילדות וגניקולוגיה ד״ר אביטל ורטהיימר כתובת ברודצקי 43, ת״א המרכז לבריאות האישה רמת אביב sec101@bri.co.il avital.wer@gmail.com 03 - 7620620 Mail Phone Mail ד״ר אביטל ורטהיימר ​ רופאת נשיםֿֿ, מומחית בגניקולוגיה ומיילדות ​ ​ ​ ​ כתובת המרפאה ברודצקי 43, ת״א המרכז לבריאות האישה רמת אביב ג׳ © By Roni Rapaport, W", "matched_query": "אביטל ורטהיימר יילוד", "extraction_method": "linked_text"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S2" t="n">
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-04T04:20:36.746946+00:00</t>
+          <t>2026-09-10T18:34:17.572391+00:00</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Z2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>["https://www.dravitalwertheimer.com/", "https://www.dravitalwertheimer.com/contact", "https://www.dravitalwertheimer.com/about-3", "https://www.dravitalwertheimer.com/about-2", "https://www.dravitalwertheimer.com/about-5"]</t>
+          <t>["https://biobalance.co.il/about-us-https-biobalance-co-il/", "https://biobalance.co.il/%D7%90%D7%95%D7%A8%D7%99-%D7%9E%D7%A0%D7%94%D7%9C%D7%AA-%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94/", "https://biobalance.co.il/%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99-%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94/", "https://biobalance.co.il/contact-us/", "https://avigoldberg.co.il/", "https://avigoldberg.co.il/%D7%A1%D7%99%D7%A4%D7%95%D7%A8-%D7%97%D7%99%D7%99%D7%95/", "https://www.srugim.co.il/1053331-%D7%A6%D7%A4%D7%95-%D7%94%D7%A8%D7%91-%D7%90%D7%91%D7%99-%D7%92%D7%95%D7%9C%D7%93%D7%91%D7%A8%D7%92-%D7%94%D7%99%D7%93-%D7%91%D7%AA%D7%A4%D7%99%D7%9C%D7%94-%D7%9C%D7%A4%D7%A0%D7%99-%D7%94%D7%99", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fbygwldbrg.438538%2F", "https://www.c14.co.il/archive/96776", "https://www.izkor.gov.il/%D7%90%D7%91%D7%A8%D7%94%D7%9D+%D7%99%D7%95%D7%A1%D7%A3+%D7%92%D7%95%D7%9C%D7%93%D7%91%D7%A8%D7%92/en_700097013c53fc0bc9f7dc07a2457af7"]</t>
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>5.349051611818981e+17</v>
+        <v>1.301247395137417e+18</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>https://www.dravitalwertheimer.com/</t>
+          <t>https://biobalance.co.il/about-us-https-biobalance-co-il/</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
+      <c r="AL2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>אודות ד"ר אבי גולדברג - Dr. Avi Goldberg - BioBalance אודות ד"ר אבי גולדברג - Dr. Avi Goldberg - BioBalance 050-6020061 drAviGol@gmail.com Facebook עמוד הבית צוות המרפאה ד”ר אבי גולדברג אורי מנהלת המרפאה שירותי המרפאה תהליך הטיפול מאמרים שאלות ותשובות צרו קשר עמוד הבית צוות המרפאה ד”ר אבי גולדברג אורי מנהלת המרפאה שירותי המרפאה תהליך הטיפול מאמרים שאלות ותשובות צרו קשר אודות ד"ר אבי גולדברג אודות ד"ר אבי גולדברג שמי ד"ר אבי גולדברג, מומחה ברפואת משפחה. את לימודי הרפואה סיימתי בבית הספר לרפואה בהדסה עין כרם. לאחר מסלול מפרך בבית הספר לרפואה, החלטתי שמקומי הוא דווקא בקהילה, ולא בבית החולים, ולכן לאחר שקילת האפשרויות שעומדות בפני, החלטתי להתמחות ברפואת משפחה בקופת חולים מכבי. לאחר סיום ההתמחות בהצלחה עבדתי מספר שנים בקופת חולים כללית, כרופא בית בדיור מוגן ובתור רופא במספר מוקדים רפואיים שונים. במקביל ללימודים, להתמחות ובהמשך לעבודתי, בשל צורך אישי ומשפחתי התחלתי לחקור לעומק מספר תחומים רפואיים אשר בהם ראיתי שיש צורך גדול בטיפול ברמה גבוהה הרבה יותר, גאוט, סוכרת והטיפול ההורמונלי בנשים וגברים. את רזי ואמנות הטיפול ההורמונלי למדתי במספר בתי ספ</t>
+        </is>
+      </c>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
@@ -841,7 +849,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>אלון קדם</t>
+          <t>אביטל ורטהיימר</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -872,7 +880,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>doctorkedem@gmail.com</t>
+          <t>avital.wer@gmail.com</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -885,7 +893,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://www.kedemalon.co.il/</t>
+          <t>https://www.dravitalwertheimer.com/contact</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -895,26 +903,26 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>פרופ' אלון קדם גניקולוגיה | מיילדות | פוריות | IVF 050-7234597 שלם 3, רמת גן (רמת חן) ומדינת היהודים 89, הרצליה פיתוח doctorkedem@gmail.com מדיניות פרטיות | הצהרת נגישות</t>
+          <t>זרעה תוך הרחמית More Use tab to navigate through the menu items. Dr. Avital Wertheimer רופאת נשים מומחית בפריון, מיילדות וגניקולוגיה ד״ר אביטל ורטהיימר כתובת ברודצקי 43, ת״א המרכז לבריאות האישה רמת אביב sec101@bri.co.il avital.wer@gmail.com 03 - 7620620 Mail Phone Mail ד״ר אביטל ורטהיימר ​ רופאת נשיםֿֿ, מומחית בגניקולוגיה ומיילדות ​ ​ ​ ​ כתובת המרפאה ברודצקי 43, ת״א המרכז לבריאות האישה רמת אביב ג׳ © By Roni Rapaport, Wix bottom of page</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>"אלון קדם"</t>
+          <t>"אביטל ורטהיימר"</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>direct_mailto</t>
+          <t>linked_text</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>[{"email": "faceitsd@gmail.com", "confidence": 92, "source_url": "https://www.kedemalon.co.il/contact", "identity_url": "https://www.kedemalon.co.il/", "evidence": "doctorkedem@gmail.com", "matched_query": "\"אלון קדם\"", "extraction_method": "linked_mailto"}]</t>
+          <t>[{"email": "sec101@bri.co.il", "confidence": 98, "source_url": "https://www.dravitalwertheimer.com/contact", "identity_url": "https://www.dravitalwertheimer.com/", "evidence": "הפריה חוץ גופית הזרעה תוך הרחמית More Use tab to navigate through the menu items. Dr. Avital Wertheimer רופאת נשים מומחית בפריון, מיילדות וגניקולוגיה ד״ר אביטל ורטהיימר כתובת ברודצקי 43, ת״א המרכז לבריאות האישה רמת אביב sec101@bri.co.il avital.wer@gmail.com 03 - 7620620 Mail Phone Mail ד״ר אביטל ורטהיימר ​ רופאת נשיםֿֿ, מומחית בגניקולוגיה ומיילדות ​ ​ ​ ​ כתובת המרפאה ברודצקי 43, ת״א המרכז לבריאות האישה רמת אביב ג׳ © By Roni Rapaport, W", "matched_query": "אביטל ורטהיימר יילוד", "extraction_method": "linked_text"}]</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -922,14 +930,14 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-03T22:06:03.406318+00:00</t>
+          <t>2026-09-04T04:20:36.746946+00:00</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
         <v>1</v>
@@ -942,16 +950,16 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>["https://www.kedemalon.co.il/", "https://www.kedemalon.co.il/about", "https://www.kedemalon.co.il/contact"]</t>
+          <t>["https://www.dravitalwertheimer.com/", "https://www.dravitalwertheimer.com/contact", "https://www.dravitalwertheimer.com/about-3", "https://www.dravitalwertheimer.com/about-2", "https://www.dravitalwertheimer.com/about-5"]</t>
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>4.336067241913308e+17</v>
+        <v>1.604715483545694e+18</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -962,19 +970,19 @@
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>https://www.kedemalon.co.il/</t>
+          <t>https://www.dravitalwertheimer.com/</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
+      <c r="AP3" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
         <v>1</v>
@@ -1003,7 +1011,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>אנה פטרוסב</t>
+          <t>אלון קדם</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1034,7 +1042,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>annapetruseva@gmail.com</t>
+          <t>doctorkedem@gmail.com</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1047,7 +1055,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://dr-annapetruseva.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/</t>
+          <t>https://www.kedemalon.co.il/</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1057,26 +1065,26 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ייעוץ ונמצא יחד את הפתרון הנכון ביותר עבורך! זה המקום להשאיר פרטים כדי שנוכל לקבוע שיחת ייעוץ בה תוכלו לקבל תשובות לכל השאלות ולבחור את הטיפול המתאים לכן. Name Phone Email ההסתדרות 55, חיפה, מרפאת שר"פ פלוס 073-2139418 annapetruseva@gmail.com אודות ד"ר אנה פטרוסב, מומחית בגינקולוגיה ובהפרעות הורמונליות לאורך שלבי החיים. מטפלת במחלות העריה, הנרתיק וצוואר הרחם. מבצעת ניתוחים פלסטיים באיברי המין החיצוניים. קישורים אודות המלצות יצירת קשר ה</t>
+          <t>פרופ' אלון קדם גניקולוגיה | מיילדות | פוריות | IVF 050-7234597 שלם 3, רמת גן (רמת חן) ומדינת היהודים 89, הרצליה פיתוח doctorkedem@gmail.com מדיניות פרטיות | הצהרת נגישות</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>"אנה פטרוסב"</t>
+          <t>"אלון קדם"</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>linked_text</t>
+          <t>direct_mailto</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "faceitsd@gmail.com", "confidence": 92, "source_url": "https://www.kedemalon.co.il/contact", "identity_url": "https://www.kedemalon.co.il/", "evidence": "doctorkedem@gmail.com", "matched_query": "\"אלון קדם\"", "extraction_method": "linked_mailto"}]</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1084,7 +1092,7 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:25:40.742527+00:00</t>
+          <t>2026-09-03T22:06:03.406318+00:00</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -1109,11 +1117,11 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>["https://dr-annapetruseva.co.il/", "https://dr-annapetruseva.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://dr-annapetruseva.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/"]</t>
+          <t>["https://www.kedemalon.co.il/", "https://www.kedemalon.co.il/about", "https://www.kedemalon.co.il/contact"]</t>
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>4.336067241913308e+17</v>
+        <v>1.300820172573992e+18</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1124,19 +1132,19 @@
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>https://dr-annapetruseva.co.il/</t>
+          <t>https://www.kedemalon.co.il/</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
+      <c r="AP4" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="n">
         <v>1</v>
@@ -1165,7 +1173,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ג'וניה עאמר-אלשיק</t>
+          <t>אנה פטרוסב</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1196,7 +1204,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>jonia.alshiek@gmail.com</t>
+          <t>annapetruseva@gmail.com</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1209,15 +1217,177 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>https://dr-annapetruseva.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ייעוץ ונמצא יחד את הפתרון הנכון ביותר עבורך! זה המקום להשאיר פרטים כדי שנוכל לקבוע שיחת ייעוץ בה תוכלו לקבל תשובות לכל השאלות ולבחור את הטיפול המתאים לכן. Name Phone Email ההסתדרות 55, חיפה, מרפאת שר"פ פלוס 073-2139418 annapetruseva@gmail.com אודות ד"ר אנה פטרוסב, מומחית בגינקולוגיה ובהפרעות הורמונליות לאורך שלבי החיים. מטפלת במחלות העריה, הנרתיק וצוואר הרחם. מבצעת ניתוחים פלסטיים באיברי המין החיצוניים. קישורים אודות המלצות יצירת קשר ה</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>"אנה פטרוסב"</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>linked_text</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>2026-09-03T22:25:40.742527+00:00</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>["https://dr-annapetruseva.co.il/", "https://dr-annapetruseva.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://dr-annapetruseva.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/"]</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.300820172573992e+18</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>https://dr-annapetruseva.co.il/</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>PERSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ג'וניה עאמר-אלשיק</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>moh</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>jonia.alshiek@gmail.com</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>100</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>https://medicine.biu.ac.il/node/7845</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t xml:space="preserve"> מדיניות הבטיחות והבריאות התעסוקתית מניעת הטרדה מינית חדשות חדשות המחקר תקשורת מעבר לגליל כפר הסטודנטים בעמיעד יצירת קשר English הדפסה פרופ'
   ג'וניה
@@ -1225,172 +1395,9 @@
 הפקול</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>"וניה עאמר אלשיק"</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>direct_text</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>2026-09-03T22:56:01.688904+00:00</t>
-        </is>
-      </c>
-      <c r="W5" t="n">
-        <v>2</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>ddgs:bing</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>["https://medicine.biu.ac.il/node/7845", "https://medicine.biu.ac.il/contact", "https://medicine.biu.ac.il/node/26", "https://medicine.biu.ac.il/pre_clinical", "https://medicine.biu.ac.il/clinical_faculty", "https://medicine.biu.ac.il/node/6861", "https://medicine.biu.ac.il/node/6760"]</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>4.336067241913308e+17</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>https://medicine.biu.ac.il/node/7845</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AU5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>PERSON</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B6" t="n">
-        <v>6</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>גדי בן שטרית</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>gynecologist</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>moh</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>dr.benshitrit@gmail.com</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>PERSONAL_PROFESSIONAL</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>100</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://www.drbenshitrit.co.il/</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>י צוות המרפאה לבדיקות וטיפולים. והתנהלות מול חברות הביטוח. מדריכים רפואים בוידאו שעות פתיחה: ביקורים פרטיים: לפי תיאום מראש. דרכי התקשרות: כתובתינו: רח' הכרמל 20, גני תקווה, מרכז הבמה קומה א'. 
-טלפון: 073-3890435 דוא"ל: dr.benshitrit@gmail.com האם משחות להחלקת הצלוליט אכן עובדות? למעבר לכתבה &gt;&gt; ד"ר בן שטרית נבחר ע"י מגזין פורבס היוקרתי לאחד הרופאים הטובים לשנת 2022 בישראל למעבר לכתבה &gt;&gt; משהו מפריע לך? אל תתביישי להתייעץ עם רופא נשים! שם</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>"גדי בן שטרית"</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1412,7 +1419,7 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-03T22:59:50.505947+00:00</t>
+          <t>2026-09-03T22:56:01.688904+00:00</t>
         </is>
       </c>
       <c r="W6" t="n">
@@ -1437,11 +1444,11 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>["https://www.drbenshitrit.co.il/", "https://www.drbenshitrit.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
+          <t>["https://medicine.biu.ac.il/node/7845", "https://medicine.biu.ac.il/contact", "https://medicine.biu.ac.il/node/26", "https://medicine.biu.ac.il/pre_clinical", "https://medicine.biu.ac.il/clinical_faculty", "https://medicine.biu.ac.il/node/6861", "https://medicine.biu.ac.il/node/6760"]</t>
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>4.336067241913308e+17</v>
+        <v>1.300820172573992e+18</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1452,19 +1459,19 @@
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>https://www.drbenshitrit.co.il/</t>
+          <t>https://medicine.biu.ac.il/node/7845</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
+      <c r="AP6" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="n">
         <v>1</v>
@@ -1493,7 +1500,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ד"ר ארבל אריאל</t>
+          <t>גדי בן שטרית</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1513,18 +1520,18 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ima</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>arbel.ariel.md@gmail.com</t>
+          <t>dr.benshitrit@gmail.com</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1537,7 +1544,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://www.b54.co.il/doctors/dr-arbel-ariel/</t>
+          <t>https://www.drbenshitrit.co.il/</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1547,12 +1554,13 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>מידע למטופל שאלות ותשובות הורדת טפסים מדיניות פרטיות סרטונים צור קשר ד"ר אריאל ארבל לזימון תור ד"ר אריאל ארבל לאתר הרופא/ה לעמוד הפייסבוק לערוץ היוטיוב לזימון תור ד"ר אריאל ארבל התקשר עכשיו יום א', בין השעות 15:00-20:00 arbel.ariel.md@gmail.com 055-9922120 התמחות מומחה ברפואת נשים / OBGYN. מומחה במחלות העריה והלדן / VULVO-VAGINAL DISEASE SPECIALIST. תחומי טיפול מומחה ביילוד גינקולוגיה ופריון, מחלות העריה והלדן תחומי טיפול מחלות עריה ולד</t>
+          <t>י צוות המרפאה לבדיקות וטיפולים. והתנהלות מול חברות הביטוח. מדריכים רפואים בוידאו שעות פתיחה: ביקורים פרטיים: לפי תיאום מראש. דרכי התקשרות: כתובתינו: רח' הכרמל 20, גני תקווה, מרכז הבמה קומה א'. 
+טלפון: 073-3890435 דוא"ל: dr.benshitrit@gmail.com האם משחות להחלקת הצלוליט אכן עובדות? למעבר לכתבה &gt;&gt; ד"ר בן שטרית נבחר ע"י מגזין פורבס היוקרתי לאחד הרופאים הטובים לשנת 2022 בישראל למעבר לכתבה &gt;&gt; משהו מפריע לך? אל תתביישי להתייעץ עם רופא נשים! שם</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>"ארבל אריאל"</t>
+          <t>"גדי בן שטרית"</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1562,11 +1570,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>[{"email": "info@eryaveladan.com", "confidence": 88, "source_url": "https://www.eryaveladan.com/", "identity_url": "https://www.eryaveladan.com/", "evidence": "החזיר את האיזון. קראי עוד השאירי פרטים ונחזור אלייך בהקדם שם מלא טלפון דוא״ל שליחה רופא נשים מומחה מחלות העריה והלדן ​ ד״ר אריאל ארבל לקביעת תור: 077-2311245 כתובת המרפאה: בית למומחים ברפואה - בורוכוב 54, גבעתיים דוא״ל: info@eryaveladan.com bottom of page", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}, {"email": "office@b54.co.il", "confidence": 88, "source_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "identity_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "evidence": "ד\"ר אריאל ארבל - מרפאת מומחים B54, הבית למומחים ברפואה בגבעתיים דילוג לתוכן B54 03-757-8562 office@b54.co.il א׳-ה׳ 8:00-20:00 | ו׳ 08:00-13:00 Facebook-f Youtube Google דף הבית אודות B54 מי אנחנו שכונת בורוכוב מרכז Friendly הנהלת המרפאה שאלות נפוצות הרופאים שלנו קליניקה להשכרה מידע למטופל שאלות ותשובות הורדת טפ", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1574,23 +1582,23 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-03T20:23:48.175654+00:00</t>
+          <t>2026-09-03T22:59:50.505947+00:00</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1599,11 +1607,11 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598", "https://www.facebook.com/people/%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%90%D7%A8%D7%91%D7%9C/pfbid0NCmi7FZgUyu2EVV5mLJMpBfndXiDQPqseAxUny7KWHsDvucQScUiVnBeMef3ByStl/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%90%D7%A8%D7%91%D7%9C-%D7%90%D7%A8%D7%99%D7%90%D7%9C/", "https://www.eryaveladan.com/", "https://www.eryaveladan.com/%D7%90%D7%95%D7%93%D7%95%D7%AA-1", "https://www.b54.co.il/doctors/dr-arbel-ariel/", "https://www.medreviews.co.il/provider/dr-arbel-ariel", "https://www.b54.co.il/about/", "https://www.b54.co.il/about", "https://www.b54.co.il/about#borohov", "https://www.b54.co.il/about#Friendly", "https://www.b54.co.il/about#management", "https://www.b54.co.il/about#qa", "https://www.medreviews.co.il/provider/dr-arbel-ariel#contact-doctor-section", "https://www.medreviews.co.il/contact-us", "https://www.medreviews.co.il/about", "https://woman.mymc.co.il/doctors/dr-arielarbel/", "https://www.ima.org.il/DoctorsIndex/Default.aspx", "https://www.infomed.co.il/experts/145655/", "https://www.ami.org.il/blog/families/not-the-same-shirley"]</t>
+          <t>["https://www.drbenshitrit.co.il/", "https://www.drbenshitrit.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>5.336698143893302e+17</v>
+        <v>1.300820172573992e+18</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1614,19 +1622,19 @@
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>https://www.b54.co.il/doctors/dr-arbel-ariel/</t>
+          <t>https://www.drbenshitrit.co.il/</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
+      <c r="AP7" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="n">
         <v>1</v>
@@ -1655,7 +1663,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ד"ר בלייכר אינה</t>
+          <t>ד"ר ארבל אריאל</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1675,7 +1683,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3930db83-dd31-4cd4-baa4-ffbee4b85ee6</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -1686,7 +1694,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>he.la.medical@gmail.com</t>
+          <t>arbel.ariel.md@gmail.com</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1699,7 +1707,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://www.helaclinic.com/%D7%94%D7%A6%D7%94%D7%A8%D7%AA-%D7%A0%D7%92%D7%99%D7%A9%D7%95%D7%AA</t>
+          <t>https://www.b54.co.il/doctors/dr-arbel-ariel/</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1709,26 +1717,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>א. אנו ממשיכים לשפר את הנגשת האתר על מנת לאפשר בו שימוש רחב לכלל האוכלוסיה לרבות אנשים עם מוגבלויות. במידה וניתקלת באלמנט באתר שאינו נגיש והנך זקוק להתאמתו לנגישות, ניתן לפנות אלינו: בטלפון: 050-2882400 או במייל לכתובת: he.la.medical@gmail.com ​ יצירת קשר צוות המרפאה ד"ר אינה בלייכר מומחית במיילדות וגינקולוגיה ורפואת האם והעובר (הריון בסיכון) ד"ר לילא חדאד מומחית במיילדות וגינקולוגיה ובאולטרסאונד מיילדותי וגינקולוגי, עם ניסיון רב בתחומי</t>
+          <t>מידע למטופל שאלות ותשובות הורדת טפסים מדיניות פרטיות סרטונים צור קשר ד"ר אריאל ארבל לזימון תור ד"ר אריאל ארבל לאתר הרופא/ה לעמוד הפייסבוק לערוץ היוטיוב לזימון תור ד"ר אריאל ארבל התקשר עכשיו יום א', בין השעות 15:00-20:00 arbel.ariel.md@gmail.com 055-9922120 התמחות מומחה ברפואת נשים / OBGYN. מומחה במחלות העריה והלדן / VULVO-VAGINAL DISEASE SPECIALIST. תחומי טיפול מומחה ביילוד גינקולוגיה ופריון, מחלות העריה והלדן תחומי טיפול מחלות עריה ולד</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>"בלייכר אינה"</t>
+          <t>"ארבל אריאל"</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>linked_text</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "info@eryaveladan.com", "confidence": 88, "source_url": "https://www.eryaveladan.com/", "identity_url": "https://www.eryaveladan.com/", "evidence": "החזיר את האיזון. קראי עוד השאירי פרטים ונחזור אלייך בהקדם שם מלא טלפון דוא״ל שליחה רופא נשים מומחה מחלות העריה והלדן ​ ד״ר אריאל ארבל לקביעת תור: 077-2311245 כתובת המרפאה: בית למומחים ברפואה - בורוכוב 54, גבעתיים דוא״ל: info@eryaveladan.com bottom of page", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}, {"email": "office@b54.co.il", "confidence": 88, "source_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "identity_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "evidence": "ד\"ר אריאל ארבל - מרפאת מומחים B54, הבית למומחים ברפואה בגבעתיים דילוג לתוכן B54 03-757-8562 office@b54.co.il א׳-ה׳ 8:00-20:00 | ו׳ 08:00-13:00 Facebook-f Youtube Google דף הבית אודות B54 מי אנחנו שכונת בורוכוב מרכז Friendly הנהלת המרפאה שאלות נפוצות הרופאים שלנו קליניקה להשכרה מידע למטופל שאלות ותשובות הורדת טפ", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}]</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1736,20 +1744,20 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-03T20:24:23.400825+00:00</t>
+          <t>2026-09-03T20:23:48.175654+00:00</t>
         </is>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA8" t="n">
         <v>1</v>
@@ -1761,11 +1769,11 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3930db83-dd31-4cd4-baa4-ffbee4b85ee6", "https://www.medreviews.co.il/provider/dr-bleicher-inna/treatment", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=F4D046F297BAD3648A25E08D58F6A97C27A9F79486CAA0E21C76A59F89CCEEBF&amp;RequestId=00000000-0000-0000-0001-000000000629", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=3&amp;ProviderID=303818454&amp;ProviderProfession=1&amp;docClinic=4002031&amp;Service=1&amp;NewObjectId=70056970&amp;NewObjectType=S&amp;NewPerNr=90012266&amp;ol1=70056970&amp;ol2=S&amp;ol3=90012266&amp;isKosher=1&amp;beginDate=2026-09-03T23:24:04&amp;shaban=false&amp;relative=-2&amp;action_type=1&amp;source=1", "https://www.facebook.com/ina.blicher/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%91%D7%9C%D7%99%D7%99%D7%9B%D7%A8-%D7%90%D7%99%D7%A0%D7%94/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=AB2EF07D4F34EBC58E5E46A0566D6548AE1759D494C6A4CEBACE849A1921D61C&amp;RequestId=00000000-0000-0000-0001-000000000732", "https://www.medreviews.co.il/provider/dr-bleicher-inna", "https://www.helaclinic.com/", "https://www.helaclinic.com/%D7%9E%D7%93%D7%99%D7%A0%D7%99%D7%95%D7%AA-%D7%A4%D7%A8%D7%98%D7%99%D7%95%D7%AA", "https://www.helaclinic.com/%D7%94%D7%A6%D7%94%D7%A8%D7%AA-%D7%A0%D7%92%D7%99%D7%A9%D7%95%D7%AA", "https://www.infomed.co.il/experts/147166/", "https://knowmore.co.il/doctors/אינה-בלייכר/", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=F2E5439F4D7FC4EB4A3BD70F1E153BCC012FCC2B1F7B620D1119D7AA921F32A0&amp;RequestId=00000000-0000-0000-0001-000000000689", "https://www.medreviews.co.il/provider/dr-bleicher-inna/treatment/high-risk-pregnancy-consult", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%90%D7%99%D7%A0%D7%94-%D7%91%D7%9C%D7%99%D7%99%D7%9B%D7%A8/", "https://www.amutatartzi.org/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.amutatartzi.org/%D7%A6%D7%95%D7%95%D7%AA-%D7%95%D7%91%D7%A2%D7%9C%D7%99-%D7%AA%D7%A4%D7%A7%D7%99%D7%93%D7%99%D7%9D/", "https://www.amutatartzi.org/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%90%D7%A8%D7%A6%D7%99/%D7%AA%D7%A7%D7%A0%D7%95%D7%9F-%D7%94%D7%A2%D7%9E%D7%95%D7%AA%D7%94/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598", "https://www.facebook.com/people/%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%90%D7%A8%D7%91%D7%9C/pfbid0NCmi7FZgUyu2EVV5mLJMpBfndXiDQPqseAxUny7KWHsDvucQScUiVnBeMef3ByStl/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%90%D7%A8%D7%91%D7%9C-%D7%90%D7%A8%D7%99%D7%90%D7%9C/", "https://www.eryaveladan.com/", "https://www.eryaveladan.com/%D7%90%D7%95%D7%93%D7%95%D7%AA-1", "https://www.b54.co.il/doctors/dr-arbel-ariel/", "https://www.medreviews.co.il/provider/dr-arbel-ariel", "https://www.b54.co.il/about/", "https://www.b54.co.il/about", "https://www.b54.co.il/about#borohov", "https://www.b54.co.il/about#Friendly", "https://www.b54.co.il/about#management", "https://www.b54.co.il/about#qa", "https://www.medreviews.co.il/provider/dr-arbel-ariel#contact-doctor-section", "https://www.medreviews.co.il/contact-us", "https://www.medreviews.co.il/about", "https://woman.mymc.co.il/doctors/dr-arielarbel/", "https://www.ima.org.il/DoctorsIndex/Default.aspx", "https://www.infomed.co.il/experts/145655/", "https://www.ami.org.il/blog/families/not-the-same-shirley"]</t>
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>5.336698143893302e+17</v>
+        <v>1.601009443167991e+18</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1776,19 +1784,19 @@
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>https://www.medreviews.co.il/provider/dr-bleicher-inna</t>
+          <t>https://www.b54.co.il/doctors/dr-arbel-ariel/</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
+      <c r="AP8" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="n">
         <v>1</v>
@@ -1817,7 +1825,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ד"ר בראל אושרי</t>
+          <t>ד"ר בלייכר אינה</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1837,7 +1845,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3d307898-6be3-4d9e-a284-ee467c2622b0</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3930db83-dd31-4cd4-baa4-ffbee4b85ee6</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1848,7 +1856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>privatepractice.barel@gmail.com</t>
+          <t>he.la.medical@gmail.com</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1861,7 +1869,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://www.droshribarel.com/</t>
+          <t>https://www.helaclinic.com/%D7%94%D7%A6%D7%94%D7%A8%D7%AA-%D7%A0%D7%92%D7%99%D7%A9%D7%95%D7%AA</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1871,17 +1879,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>בחנתית וטיפולית Jul 21, 2018 ניתוחים לפרוסקופים Aug 29, 2016 צרי קשר אסותא רמת החייל - הברזל 20, תל אביב, קומה 2 מתחם גינקולוגיה נס ציונה  - מרפאת לליב, קמפוס יובלים בניין B קומה 3 אסותא כלניות - שד' מנחם בגין 126 אשדוד privatepractice.barel@gmail.com וואטסאפ 054-2592902 Send Your details were sent successfully! ד״ר אושרי בראל רופא מומחה במיילדות, גינקולוגיה וכירורגיה גינקולוגית ליצירת קשר בטלפון או ווטסאפ ליצירת קשר במייל לזימון תור במ</t>
+          <t>א. אנו ממשיכים לשפר את הנגשת האתר על מנת לאפשר בו שימוש רחב לכלל האוכלוסיה לרבות אנשים עם מוגבלויות. במידה וניתקלת באלמנט באתר שאינו נגיש והנך זקוק להתאמתו לנגישות, ניתן לפנות אלינו: בטלפון: 050-2882400 או במייל לכתובת: he.la.medical@gmail.com ​ יצירת קשר צוות המרפאה ד"ר אינה בלייכר מומחית במיילדות וגינקולוגיה ורפואת האם והעובר (הריון בסיכון) ד"ר לילא חדאד מומחית במיילדות וגינקולוגיה ובאולטרסאונד מיילדותי וגינקולוגי, עם ניסיון רב בתחומי</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>"בראל אושרי"</t>
+          <t>"בלייכר אינה"</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>linked_text</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1898,20 +1906,20 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-04T11:17:14.785768+00:00</t>
+          <t>2026-09-03T20:24:23.400825+00:00</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Z9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AA9" t="n">
         <v>1</v>
@@ -1923,11 +1931,11 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3d307898-6be3-4d9e-a284-ee467c2622b0", "https://www.droshribarel.com/", "https://www.droshribarel.com/about", "https://doctors.assuta.co.il/doctor/oshri-barel-32645"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3930db83-dd31-4cd4-baa4-ffbee4b85ee6", "https://www.medreviews.co.il/provider/dr-bleicher-inna/treatment", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=F4D046F297BAD3648A25E08D58F6A97C27A9F79486CAA0E21C76A59F89CCEEBF&amp;RequestId=00000000-0000-0000-0001-000000000629", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=3&amp;ProviderID=303818454&amp;ProviderProfession=1&amp;docClinic=4002031&amp;Service=1&amp;NewObjectId=70056970&amp;NewObjectType=S&amp;NewPerNr=90012266&amp;ol1=70056970&amp;ol2=S&amp;ol3=90012266&amp;isKosher=1&amp;beginDate=2026-09-03T23:24:04&amp;shaban=false&amp;relative=-2&amp;action_type=1&amp;source=1", "https://www.facebook.com/ina.blicher/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%91%D7%9C%D7%99%D7%99%D7%9B%D7%A8-%D7%90%D7%99%D7%A0%D7%94/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=AB2EF07D4F34EBC58E5E46A0566D6548AE1759D494C6A4CEBACE849A1921D61C&amp;RequestId=00000000-0000-0000-0001-000000000732", "https://www.medreviews.co.il/provider/dr-bleicher-inna", "https://www.helaclinic.com/", "https://www.helaclinic.com/%D7%9E%D7%93%D7%99%D7%A0%D7%99%D7%95%D7%AA-%D7%A4%D7%A8%D7%98%D7%99%D7%95%D7%AA", "https://www.helaclinic.com/%D7%94%D7%A6%D7%94%D7%A8%D7%AA-%D7%A0%D7%92%D7%99%D7%A9%D7%95%D7%AA", "https://www.infomed.co.il/experts/147166/", "https://knowmore.co.il/doctors/אינה-בלייכר/", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=F2E5439F4D7FC4EB4A3BD70F1E153BCC012FCC2B1F7B620D1119D7AA921F32A0&amp;RequestId=00000000-0000-0000-0001-000000000689", "https://www.medreviews.co.il/provider/dr-bleicher-inna/treatment/high-risk-pregnancy-consult", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%90%D7%99%D7%A0%D7%94-%D7%91%D7%9C%D7%99%D7%99%D7%9B%D7%A8/", "https://www.amutatartzi.org/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.amutatartzi.org/%D7%A6%D7%95%D7%95%D7%AA-%D7%95%D7%91%D7%A2%D7%9C%D7%99-%D7%AA%D7%A4%D7%A7%D7%99%D7%93%D7%99%D7%9D/", "https://www.amutatartzi.org/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%90%D7%A8%D7%A6%D7%99/%D7%AA%D7%A7%D7%A0%D7%95%D7%9F-%D7%94%D7%A2%D7%9E%D7%95%D7%AA%D7%94/"]</t>
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>5.007272332541864e+17</v>
+        <v>1.601009443167991e+18</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -1938,19 +1946,19 @@
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>https://www.droshribarel.com/</t>
+          <t>https://www.medreviews.co.il/provider/dr-bleicher-inna</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
+      <c r="AP9" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="n">
         <v>1</v>
@@ -1979,7 +1987,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ד"ר גורצק לימור</t>
+          <t>ד"ר בראל אושרי</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1999,7 +2007,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e4863880-ea20-4af5-8f93-9ca81c2181c8</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3d307898-6be3-4d9e-a284-ee467c2622b0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -2010,7 +2018,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>limorgortzak@gmail.com</t>
+          <t>privatepractice.barel@gmail.com</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -2023,7 +2031,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://doctors.assuta.co.il/doctor/limor-gortzak-31448</t>
+          <t>https://www.droshribarel.com/</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -2033,17 +2041,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ד"ר לימור גורצק אוזן | גינקולוגיה ומיילדות | ניתוחיי ... ניתוחיי גינקולוגיה מרפאות אלי כהן 8, רעננה-דוקטור גורצק אוזן לימור רעננה אלי כהן 8 מייל מרפאה : limorgortzak@gmail.com הסדרים ביטוח הראל כלל חברה לביטוח בעמ</t>
+          <t>בחנתית וטיפולית Jul 21, 2018 ניתוחים לפרוסקופים Aug 29, 2016 צרי קשר אסותא רמת החייל - הברזל 20, תל אביב, קומה 2 מתחם גינקולוגיה נס ציונה  - מרפאת לליב, קמפוס יובלים בניין B קומה 3 אסותא כלניות - שד' מנחם בגין 126 אשדוד privatepractice.barel@gmail.com וואטסאפ 054-2592902 Send Your details were sent successfully! ד״ר אושרי בראל רופא מומחה במיילדות, גינקולוגיה וכירורגיה גינקולוגית ליצירת קשר בטלפון או ווטסאפ ליצירת קשר במייל לזימון תור במ</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>"גורצק לימור" יילוד מרפאה</t>
+          <t>"בראל אושרי"</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>search_snippet</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -2060,17 +2068,17 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-08T07:40:03.644359+00:00</t>
+          <t>2026-09-04T11:17:14.785768+00:00</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z10" t="n">
         <v>2</v>
@@ -2080,16 +2088,16 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>ddgs:yahoo+ddgs:bing</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e4863880-ea20-4af5-8f93-9ca81c2181c8", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=3C4EDA09705370ECB68D9C2264B607ED40FF0BE76904B81AEE276453C8369C5C&amp;RequestId=00000000-0000-0000-0001-000000000264", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=8&amp;ProviderID=24990111&amp;ProviderProfession=2&amp;docClinic=67701&amp;Service=1&amp;NewObjectId=70021435&amp;NewObjectType=S&amp;NewPerNr=90005047&amp;ol1=70021435&amp;ol2=S&amp;ol3=90005047&amp;isKosher=1&amp;beginDate=2026-09-08T10:39:13&amp;shaban=false&amp;relative=-2&amp;action_type=1&amp;source=1", "https://doctors.assuta.co.il/doctor/limor-gortzak-31448"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3d307898-6be3-4d9e-a284-ee467c2622b0", "https://www.droshribarel.com/", "https://www.droshribarel.com/about", "https://doctors.assuta.co.il/doctor/oshri-barel-32645"]</t>
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>4.340236532221023e+17</v>
+        <v>1.502181699762559e+18</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2100,19 +2108,19 @@
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>https://doctors.assuta.co.il/doctor/limor-gortzak-31448</t>
+          <t>https://www.droshribarel.com/</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
+      <c r="AP10" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="n">
         <v>1</v>
@@ -2141,7 +2149,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ד"ר הר-טוב יוסף</t>
+          <t>ד"ר גורצק לימור</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2161,7 +2169,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=BBC5ED8B-BCA3-44E9-AD8C-5614970C09B0</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e4863880-ea20-4af5-8f93-9ca81c2181c8</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -2172,7 +2180,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>dr.hartoov@gmail.com</t>
+          <t>limorgortzak@gmail.com</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -2185,7 +2193,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://www.dr-hartoov.co.il/</t>
+          <t>https://doctors.assuta.co.il/doctor/limor-gortzak-31448</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -2195,17 +2203,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>ד"ר יוסי הר-טוב דלג לתוכן כתובת: ויצמן 14, תל אביב, מגדל מרכז ויצמן קומה 19, חדר 1923 אימייל: dr.hartoov@gmail.com שעות פעילות: ​א' - ו' בתיאום מראש 052-8305566 מספר מקשר(?) בית אודות בדיקות גינקולוגיות בדיקת מי שפיר וסיסי שליה סקירת מערכות סקירת מערכות מוקדמת סקירת מערכות מאוחרת סקירת מערכות שלישית מעקבי הריון ש</t>
+          <t>ד"ר לימור גורצק אוזן | גינקולוגיה ומיילדות | ניתוחיי ... ניתוחיי גינקולוגיה מרפאות אלי כהן 8, רעננה-דוקטור גורצק אוזן לימור רעננה אלי כהן 8 מייל מרפאה : limorgortzak@gmail.com הסדרים ביטוח הראל כלל חברה לביטוח בעמ</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>"הר טוב יוסף"</t>
+          <t>"גורצק לימור" יילוד מרפאה</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>official_text</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -2222,36 +2230,36 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-04T11:52:18.314932+00:00</t>
+          <t>2026-09-08T07:40:03.644359+00:00</t>
         </is>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z11" t="n">
         <v>2</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=BBC5ED8B-BCA3-44E9-AD8C-5614970C09B0", "https://www.d.co.il/reviews-80237533-c46500-p1/", "https://www.dr-hartoov.co.il/", "https://www.dr-hartoov.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.dr-hartoov.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e4863880-ea20-4af5-8f93-9ca81c2181c8", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=3C4EDA09705370ECB68D9C2264B607ED40FF0BE76904B81AEE276453C8369C5C&amp;RequestId=00000000-0000-0000-0001-000000000264", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=8&amp;ProviderID=24990111&amp;ProviderProfession=2&amp;docClinic=67701&amp;Service=1&amp;NewObjectId=70021435&amp;NewObjectType=S&amp;NewPerNr=90005047&amp;ol1=70021435&amp;ol2=S&amp;ol3=90005047&amp;isKosher=1&amp;beginDate=2026-09-08T10:39:13&amp;shaban=false&amp;relative=-2&amp;action_type=1&amp;source=1", "https://doctors.assuta.co.il/doctor/limor-gortzak-31448"]</t>
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>4.340185064555201e+17</v>
+        <v>1.302070959666307e+18</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2262,19 +2270,19 @@
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>https://www.dr-hartoov.co.il/</t>
+          <t>https://doctors.assuta.co.il/doctor/limor-gortzak-31448</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
+      <c r="AP11" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="n">
         <v>1</v>
@@ -2303,7 +2311,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ד"ר הראל יעל</t>
+          <t>ד"ר הר-טוב יוסף</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2323,7 +2331,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=1f53d60d-6e05-4854-8a46-954ca448b33c</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=BBC5ED8B-BCA3-44E9-AD8C-5614970C09B0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -2334,7 +2342,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>doc.yaelharel@gmail.com</t>
+          <t>dr.hartoov@gmail.com</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2347,7 +2355,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://dryaelharel.co.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%99/</t>
+          <t>https://www.dr-hartoov.co.il/</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2357,17 +2365,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>גוד הישראלי הישראלי למיילדות וגינקולוגיה החברה לגינקולוגיה של ילדות ומתבגרות החברה הישראלית לקידום, אבחון, טיפול ומניעה של פגיעה מינית קליניקה : רחוב הברזל 9א, קומה 4, תל אביב טלפון : 051-2613697 פקס: 03-7744069 אימייל: Doc.yaelharel@gmail.com © כל הזכויות שמורות לד"ר יעל הראל 2022 הצהרת נגישות Made with 💙 by box גלילה לראש העמוד דילוג לתוכן פתח סרגל נגישות כלי נגישות הגדל טקסט הקטן טקסט גווני אפור ניגודיות גבוהה ניגודיות הפוכה רקע בהיר</t>
+          <t>ד"ר יוסי הר-טוב דלג לתוכן כתובת: ויצמן 14, תל אביב, מגדל מרכז ויצמן קומה 19, חדר 1923 אימייל: dr.hartoov@gmail.com שעות פעילות: ​א' - ו' בתיאום מראש 052-8305566 מספר מקשר(?) בית אודות בדיקות גינקולוגיות בדיקת מי שפיר וסיסי שליה סקירת מערכות סקירת מערכות מוקדמת סקירת מערכות מאוחרת סקירת מערכות שלישית מעקבי הריון ש</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>"הראל יעל"</t>
+          <t>"הר טוב יוסף"</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>official_text</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -2379,25 +2387,25 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-04T19:38:04.257632+00:00</t>
+          <t>2026-09-04T11:52:18.314932+00:00</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2409,11 +2417,11 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=1f53d60d-6e05-4854-8a46-954ca448b33c", "https://www.facebook.com/people/%D7%99%D7%A2%D7%9C-%D7%94%D7%A8%D7%90%D7%9C/100083269862452/", "https://dryaelharel.co.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%99/", "https://dryaelharel.co.il/", "https://dryaelharel.co.il/%D7%99%D7%A2%D7%9C-%D7%94%D7%A8%D7%90%D7%9C/", "https://israel-psychotherapy.org/therapist/%D7%99%D7%A2%D7%9C-%D7%94%D7%A8%D7%90%D7%9C/", "https://upr.co.il/listing/%D7%93%D7%A8-%D7%99%D7%A2%D7%9C-%D7%94%D7%A8%D7%90%D7%9C/", "https://www.prtfl.co.il/archives/writer/%D7%99%D7%A2%D7%9C-%D7%94%D7%A8%D7%90%D7%9C"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=BBC5ED8B-BCA3-44E9-AD8C-5614970C09B0", "https://www.d.co.il/reviews-80237533-c46500-p1/", "https://www.dr-hartoov.co.il/", "https://www.dr-hartoov.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.dr-hartoov.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/"]</t>
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>5.350881755215378e+17</v>
+        <v>1.30205551936656e+18</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2424,19 +2432,19 @@
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>https://dryaelharel.co.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%99/</t>
+          <t>https://www.dr-hartoov.co.il/</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL12" t="inlineStr"/>
       <c r="AM12" t="inlineStr"/>
       <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr"/>
+      <c r="AP12" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ12" t="inlineStr"/>
       <c r="AR12" t="n">
         <v>1</v>
@@ -2465,7 +2473,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ד"ר לוריא מיכל</t>
+          <t>ד"ר הראל יעל</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2485,7 +2493,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=8e800bc1-5c51-41bc-b5cd-3fd5e719dca4</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=1f53d60d-6e05-4854-8a46-954ca448b33c</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -2496,7 +2504,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>mijalluria@gmail.com</t>
+          <t>doc.yaelharel@gmail.com</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2509,7 +2517,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C-%D7%93%D7%A8/</t>
+          <t>https://dryaelharel.co.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%99/</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2519,12 +2527,12 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>יות הרצאות מהכנסים מטפלי.ות איט"ם מטפלי.ות איט"ם פיזיותרפיסטים.ית איט"ם מרפאות ציבוריות הצטרפות והתמחות צור קשר פרטי התקשרות טלפון 072-211-9500 כתובת "מרכז רותם: המרכז הרב תחומי למיניות"  גבעת בית הכרם 3, ירושלים אימייל mijalluria@gmail.com לוריא מיכל (MD) – ירושלים מקצוע: רופאה, מומחית ברפואת נשים, מטפלת מינית מוסמכת התמחות: גינקולוגית איזור טיפול: ירושלים אודותי התמחות: טיפול מיני זוגי ופרטני, פערים בחשק המיני, חוסר הנאה מחיי המין, כא</t>
+          <t>גוד הישראלי הישראלי למיילדות וגינקולוגיה החברה לגינקולוגיה של ילדות ומתבגרות החברה הישראלית לקידום, אבחון, טיפול ומניעה של פגיעה מינית קליניקה : רחוב הברזל 9א, קומה 4, תל אביב טלפון : 051-2613697 פקס: 03-7744069 אימייל: Doc.yaelharel@gmail.com © כל הזכויות שמורות לד"ר יעל הראל 2022 הצהרת נגישות Made with 💙 by box גלילה לראש העמוד דילוג לתוכן פתח סרגל נגישות כלי נגישות הגדל טקסט הקטן טקסט גווני אפור ניגודיות גבוהה ניגודיות הפוכה רקע בהיר</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>"לוריא מיכל" יילוד מרפאה</t>
+          <t>"הראל יעל"</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2534,71 +2542,71 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "identity_url": "https://itam.org.il/therapists/%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C-%D7%93%D7%A8/", "evidence": "ter.rotem.www שעות פעילות: שעות פעילות:\r\nא'-ה' 08.00-22.00 | ו' 8.00-15.00 איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי 052-2528020 מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"לוריא מיכל\" יילוד מרפאה", "extraction_method": "linked_text"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
         <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-08T23:26:20.598402+00:00</t>
+          <t>2026-09-04T19:38:04.257632+00:00</t>
         </is>
       </c>
       <c r="W13" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>ddgs:yahoo</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=8e800bc1-5c51-41bc-b5cd-3fd5e719dca4", "https://www.meuhedet.co.il/poi/Doctors/000250300130100613000000000000_0", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C/", "https://www.doctorita.co.il/experts/72051", "https://itam.org.il/therapists/%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C-%D7%93%D7%A8/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=1f53d60d-6e05-4854-8a46-954ca448b33c", "https://www.facebook.com/people/%D7%99%D7%A2%D7%9C-%D7%94%D7%A8%D7%90%D7%9C/100083269862452/", "https://dryaelharel.co.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%99/", "https://dryaelharel.co.il/", "https://dryaelharel.co.il/%D7%99%D7%A2%D7%9C-%D7%94%D7%A8%D7%90%D7%9C/", "https://israel-psychotherapy.org/therapist/%D7%99%D7%A2%D7%9C-%D7%94%D7%A8%D7%90%D7%9C/", "https://upr.co.il/listing/%D7%93%D7%A8-%D7%99%D7%A2%D7%9C-%D7%94%D7%A8%D7%90%D7%9C/", "https://www.prtfl.co.il/archives/writer/%D7%99%D7%A2%D7%9C-%D7%94%D7%A8%D7%90%D7%9C"]</t>
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>4.340236532221031e+17</v>
+        <v>1.605264526564613e+18</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
       </c>
       <c r="AF13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C-%D7%93%D7%A8/</t>
+          <t>https://dryaelharel.co.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%99/</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL13" t="inlineStr"/>
       <c r="AM13" t="inlineStr"/>
       <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr"/>
+      <c r="AP13" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="n">
         <v>1</v>
@@ -2627,7 +2635,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ד"ר פז מורן</t>
+          <t>ד"ר לוריא מיכל</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2647,7 +2655,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=5eee8cff-ee8c-40c5-807b-acf6f5374dd8</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=8e800bc1-5c51-41bc-b5cd-3fd5e719dca4</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -2658,7 +2666,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>drmoranpaz@gmail.com</t>
+          <t>mijalluria@gmail.com</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2671,7 +2679,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://www.drmoranpaz.com/</t>
+          <t>https://itam.org.il/therapists/%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C-%D7%93%D7%A8/</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2681,12 +2689,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>אליק, ישראל top of page Moran Paz M.D. Obstetrics &amp; Gynaecology Minimally invasive surgery Tel: 050-6265854 058-6265854 ד"ר מורן פז מומחה ברפואת נשים ומיילדות כירורגיה גינקולוגית זער פולשנית טל': 050-6265854 058-6265854 drmoranpaz@gmail.com צרי קשר מיילדות אנדומטריוזיס אמצעי מניעה אמצעי מניעה התקן תוך רחמי גלולות למניעת הריון גינקולוגיה גניקולוגיה הפרשות נרתיקיות פוליפים שרירנים היסטרוסקופיה לפרוסקופיה אודות אודות מכתבי תודה ד"ר מורן פז</t>
+          <t>יות הרצאות מהכנסים מטפלי.ות איט"ם מטפלי.ות איט"ם פיזיותרפיסטים.ית איט"ם מרפאות ציבוריות הצטרפות והתמחות צור קשר פרטי התקשרות טלפון 072-211-9500 כתובת "מרכז רותם: המרכז הרב תחומי למיניות"  גבעת בית הכרם 3, ירושלים אימייל mijalluria@gmail.com לוריא מיכל (MD) – ירושלים מקצוע: רופאה, מומחית ברפואת נשים, מטפלת מינית מוסמכת התמחות: גינקולוגית איזור טיפול: ירושלים אודותי התמחות: טיפול מיני זוגי ופרטני, פערים בחשק המיני, חוסר הנאה מחיי המין, כא</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>"פז מורן"</t>
+          <t>"לוריא מיכל" יילוד מרפאה</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -2696,11 +2704,11 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "identity_url": "https://itam.org.il/therapists/%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C-%D7%93%D7%A8/", "evidence": "ter.rotem.www שעות פעילות: שעות פעילות:\r\nא'-ה' 08.00-22.00 | ו' 8.00-15.00 איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי 052-2528020 מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"לוריא מיכל\" יילוד מרפאה", "extraction_method": "linked_text"}]</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -2708,11 +2716,11 @@
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-03T20:26:18.342248+00:00</t>
+          <t>2026-09-08T23:26:20.598402+00:00</t>
         </is>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -2721,46 +2729,46 @@
         <v>4</v>
       </c>
       <c r="Z14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=5eee8cff-ee8c-40c5-807b-acf6f5374dd8", "https://www.drmoranpaz.com/", "https://www.drmoranpaz.com/blank-1", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A4%D7%96-%D7%9E%D7%95%D7%A8%D7%9F/", "https://docsrated.com/doctors/מורן-פז", "https://www.clalit.co.il/he/sefersherut/pages/doctordetails.aspx?edeptcode=999012319&amp;eservicecode=1722022&amp;employeeid=99B380F756CF96813AEADDED4FF08A8C", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%95%D7%A8%D7%9F-%D7%A4%D7%96/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=8e800bc1-5c51-41bc-b5cd-3fd5e719dca4", "https://www.meuhedet.co.il/poi/Doctors/000250300130100613000000000000_0", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C/", "https://www.doctorita.co.il/experts/72051", "https://itam.org.il/therapists/%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C-%D7%93%D7%A8/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>5.336698143893302e+17</v>
+        <v>1.302070959666309e+18</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>https://www.drmoranpaz.com/</t>
+          <t>https://itam.org.il/therapists/%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C-%D7%93%D7%A8/</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL14" t="inlineStr"/>
       <c r="AM14" t="inlineStr"/>
       <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="inlineStr"/>
+      <c r="AP14" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ14" t="inlineStr"/>
       <c r="AR14" t="n">
         <v>1</v>
@@ -2789,7 +2797,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ד"ר צוקרמן צבי</t>
+          <t>ד"ר פז מורן</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2809,7 +2817,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=ce204428-9658-48fd-9895-62695b31e167</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=5eee8cff-ee8c-40c5-807b-acf6f5374dd8</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -2820,7 +2828,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>zukerman_z@hotmail.com</t>
+          <t>drmoranpaz@gmail.com</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2833,7 +2841,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/</t>
+          <t>https://www.drmoranpaz.com/</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2843,12 +2851,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>עילויות כנסים והשתלמויות הרצאות מהכנסים מטפלי.ות איט"ם מטפלי.ות איט"ם פיזיותרפיסטים.ית איט"ם מרפאות ציבוריות הצטרפות והתמחות צור קשר פרטי התקשרות טלפון 52-2444908 0, פקס': 03-9310870 כתובת ברנדה 4 פתח תקווה 49600 אימייל Zukerman_z@hotmail.com צוקרמן צבי (MD) התמחות: גינקולוגיה איזור טיפול: פתח תקווה אודותי צוקרמן צבי (MD) גינקולוגיה פתח תקווה 52-2444908 0, פקס': 03-9310870 Zukerman_z@hotmail.com ברנדה 4 פתח תקווה 49600 ברנדה 4 פתח תקווה</t>
+          <t>אליק, ישראל top of page Moran Paz M.D. Obstetrics &amp; Gynaecology Minimally invasive surgery Tel: 050-6265854 058-6265854 ד"ר מורן פז מומחה ברפואת נשים ומיילדות כירורגיה גינקולוגית זער פולשנית טל': 050-6265854 058-6265854 drmoranpaz@gmail.com צרי קשר מיילדות אנדומטריוזיס אמצעי מניעה אמצעי מניעה התקן תוך רחמי גלולות למניעת הריון גינקולוגיה גניקולוגיה הפרשות נרתיקיות פוליפים שרירנים היסטרוסקופיה לפרוסקופיה אודות אודות מכתבי תודה ד"ר מורן פז</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>"צוקרמן צבי"</t>
+          <t>"פז מורן"</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2858,11 +2866,11 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/", "identity_url": "https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/", "evidence": "קס': 03-9310870 Zukerman_z@hotmail.com ברנדה 4 פתח תקווה 49600 ברנדה 4 פתח תקווה 49600 איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"צוקרמן צבי\"", "extraction_method": "direct_text"}, {"email": "info@israeli-expert.co.il", "confidence": 80, "source_url": "https://www.israeli-expert.co.il/index2.php?id=5149&amp;lang=HEB", "identity_url": "https://www.israeli-expert.co.il/index2.php?id=13310&amp;lang=HEB", "evidence": "info@israeli-expert.co.il Moriya Av. 105, Haifa 34616 Phone: 04-8244633, Fax: 04-8113444", "matched_query": "\"צוקרמן צבי\"", "extraction_method": "linked_mailto"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -2870,24 +2878,24 @@
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-03T21:00:59.983523+00:00</t>
+          <t>2026-09-03T20:26:18.342248+00:00</t>
         </is>
       </c>
       <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA15" t="n">
         <v>2</v>
       </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
       <c r="AB15" t="inlineStr">
         <is>
           <t>ddgs:bing</t>
@@ -2895,11 +2903,11 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=ce204428-9658-48fd-9895-62695b31e167", "https://www.facebook.com/people/%D7%A6%D7%91%D7%99-%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F/pfbid02E1Nxj3wfhR6MF8D6JXXRW7A6Jhoq792SjPLH1nRCvRmFTDrKUVsZSCxcg5BXdSXDl/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fzby.zwqrmn%2F", "https://benyehuda.org/read/38950", "https://www.israeli-expert.co.il/index2.php?id=13310&amp;lang=HEB", "https://www.interuse.co.il/", "https://www.israeli-expert.co.il/about-en", "https://www.israeli-expert.co.il/index2.php?id=5149&amp;lang=HEB", "https://www.israeli-expert.co.il/about", "https://www.israeli-expert.co.il/index2.php?id=3&amp;lang=HEB", "https://www.palmach.org.il/veterans/veteranpage/?itemId=73755", "https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=5eee8cff-ee8c-40c5-807b-acf6f5374dd8", "https://www.drmoranpaz.com/", "https://www.drmoranpaz.com/blank-1", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A4%D7%96-%D7%9E%D7%95%D7%A8%D7%9F/", "https://docsrated.com/doctors/מורן-פז", "https://www.clalit.co.il/he/sefersherut/pages/doctordetails.aspx?edeptcode=999012319&amp;eservicecode=1722022&amp;employeeid=99B380F756CF96813AEADDED4FF08A8C", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%95%D7%A8%D7%9F-%D7%A4%D7%96/"]</t>
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>4.336067241913308e+17</v>
+        <v>1.601009443167991e+18</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2910,19 +2918,19 @@
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/</t>
+          <t>https://www.drmoranpaz.com/</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="inlineStr"/>
       <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL15" t="inlineStr"/>
       <c r="AM15" t="inlineStr"/>
       <c r="AN15" t="inlineStr"/>
       <c r="AO15" t="inlineStr"/>
-      <c r="AP15" t="inlineStr"/>
+      <c r="AP15" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ15" t="inlineStr"/>
       <c r="AR15" t="n">
         <v>1</v>
@@ -2951,7 +2959,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ד"ר קאופמן יובל</t>
+          <t>ד"ר צוקרמן צבי</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2971,7 +2979,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=87371F6B-AEDA-480B-855B-A665C2A570C0</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=ce204428-9658-48fd-9895-62695b31e167</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -2982,7 +2990,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>mdykaufman@gmail.com</t>
+          <t>zukerman_z@hotmail.com</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2995,7 +3003,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://www.gynsurg.co.il/</t>
+          <t>https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -3005,12 +3013,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t xml:space="preserve">תמחויות לפרוסקופיה היסטרוסקופיה גישה נרתיקית בעיות גניקולוגיות בעיות פוריות פוליפ רחמי שרירנים ברחם ציסטה בשחלה אנדומטריוזיס פרטי התקשרות בית חולים 'אסותא' חיפה, קניון לב המפרץ (קומה ג') שד' ההסתדרות 55 , צ'ק פוסט, חיפה mdykaufman@gmail.com yochi750@gmail.com 03-7644777 050-9500525 © כל הזכויות שמורות ל"ר יובל קאופמן- כירורגיה גניקולוגית מתקדמת | נבנה ע"י ADACTIVE לזימון תורים - לחץ כאן זימון תור טלפון מרפאה סגירת תפריט אנחנו מכבדים את </t>
+          <t>עילויות כנסים והשתלמויות הרצאות מהכנסים מטפלי.ות איט"ם מטפלי.ות איט"ם פיזיותרפיסטים.ית איט"ם מרפאות ציבוריות הצטרפות והתמחות צור קשר פרטי התקשרות טלפון 52-2444908 0, פקס': 03-9310870 כתובת ברנדה 4 פתח תקווה 49600 אימייל Zukerman_z@hotmail.com צוקרמן צבי (MD) התמחות: גינקולוגיה איזור טיפול: פתח תקווה אודותי צוקרמן צבי (MD) גינקולוגיה פתח תקווה 52-2444908 0, פקס': 03-9310870 Zukerman_z@hotmail.com ברנדה 4 פתח תקווה 49600 ברנדה 4 פתח תקווה</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>"קאופמן יובל"</t>
+          <t>"צוקרמן צבי"</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -3020,11 +3028,11 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>[{"email": "yochi750@gmail.com", "confidence": 100, "source_url": "https://www.gynsurg.co.il/", "identity_url": "https://www.gynsurg.co.il/", "evidence": "סטרוסקופיה גישה נרתיקית בעיות גניקולוגיות בעיות פוריות פוליפ רחמי שרירנים ברחם ציסטה בשחלה אנדומטריוזיס פרטי התקשרות בית חולים 'אסותא' חיפה, קניון לב המפרץ (קומה ג') שד' ההסתדרות 55 , צ'ק פוסט, חיפה mdykaufman@gmail.com yochi750@gmail.com 03-7644777 050-9500525 © כל הזכויות שמורות ל\"ר יובל קאופמן- כירורגיה גניקולוגית מתקדמת | נבנה ע\"י ADACTIVE לזימון תורים - לחץ כאן זימון תור טלפון מרפאה סגירת תפריט אנחנו מכבדים את הפרטיות שלך אנחנו משת", "matched_query": "\"קאופמן יובל\"", "extraction_method": "direct_text"}]</t>
+          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/", "identity_url": "https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/", "evidence": "קס': 03-9310870 Zukerman_z@hotmail.com ברנדה 4 פתח תקווה 49600 ברנדה 4 פתח תקווה 49600 איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"צוקרמן צבי\"", "extraction_method": "direct_text"}, {"email": "info@israeli-expert.co.il", "confidence": 80, "source_url": "https://www.israeli-expert.co.il/index2.php?id=5149&amp;lang=HEB", "identity_url": "https://www.israeli-expert.co.il/index2.php?id=13310&amp;lang=HEB", "evidence": "info@israeli-expert.co.il Moriya Av. 105, Haifa 34616 Phone: 04-8244633, Fax: 04-8113444", "matched_query": "\"צוקרמן צבי\"", "extraction_method": "linked_mailto"}]</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -3032,7 +3040,7 @@
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-03T21:01:40.564925+00:00</t>
+          <t>2026-09-03T21:00:59.983523+00:00</t>
         </is>
       </c>
       <c r="W16" t="n">
@@ -3042,10 +3050,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Z16" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -3057,11 +3065,11 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=87371F6B-AEDA-480B-855B-A665C2A570C0", "https://www.gynsurg.co.il/", "https://www.gynsurg.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.gynsurg.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=ce204428-9658-48fd-9895-62695b31e167", "https://www.facebook.com/people/%D7%A6%D7%91%D7%99-%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F/pfbid02E1Nxj3wfhR6MF8D6JXXRW7A6Jhoq792SjPLH1nRCvRmFTDrKUVsZSCxcg5BXdSXDl/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fzby.zwqrmn%2F", "https://benyehuda.org/read/38950", "https://www.israeli-expert.co.il/index2.php?id=13310&amp;lang=HEB", "https://www.interuse.co.il/", "https://www.israeli-expert.co.il/about-en", "https://www.israeli-expert.co.il/index2.php?id=5149&amp;lang=HEB", "https://www.israeli-expert.co.il/about", "https://www.israeli-expert.co.il/index2.php?id=3&amp;lang=HEB", "https://www.palmach.org.il/veterans/veteranpage/?itemId=73755", "https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>4.336067241913308e+17</v>
+        <v>1.300820172573992e+18</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3072,19 +3080,19 @@
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>https://www.gynsurg.co.il/</t>
+          <t>https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="inlineStr"/>
       <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL16" t="inlineStr"/>
       <c r="AM16" t="inlineStr"/>
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="inlineStr"/>
-      <c r="AP16" t="inlineStr"/>
+      <c r="AP16" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ16" t="inlineStr"/>
       <c r="AR16" t="n">
         <v>1</v>
@@ -3144,7 +3152,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>yochi750@gmail.com</t>
+          <t>mdykaufman@gmail.com</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -3167,7 +3175,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>סטרוסקופיה גישה נרתיקית בעיות גניקולוגיות בעיות פוריות פוליפ רחמי שרירנים ברחם ציסטה בשחלה אנדומטריוזיס פרטי התקשרות בית חולים 'אסותא' חיפה, קניון לב המפרץ (קומה ג') שד' ההסתדרות 55 , צ'ק פוסט, חיפה mdykaufman@gmail.com yochi750@gmail.com 03-7644777 050-9500525 © כל הזכויות שמורות ל"ר יובל קאופמן- כירורגיה גניקולוגית מתקדמת | נבנה ע"י ADACTIVE לזימון תורים - לחץ כאן זימון תור טלפון מרפאה סגירת תפריט אנחנו מכבדים את הפרטיות שלך אנחנו משת</t>
+          <t xml:space="preserve">תמחויות לפרוסקופיה היסטרוסקופיה גישה נרתיקית בעיות גניקולוגיות בעיות פוריות פוליפ רחמי שרירנים ברחם ציסטה בשחלה אנדומטריוזיס פרטי התקשרות בית חולים 'אסותא' חיפה, קניון לב המפרץ (קומה ג') שד' ההסתדרות 55 , צ'ק פוסט, חיפה mdykaufman@gmail.com yochi750@gmail.com 03-7644777 050-9500525 © כל הזכויות שמורות ל"ר יובל קאופמן- כירורגיה גניקולוגית מתקדמת | נבנה ע"י ADACTIVE לזימון תורים - לחץ כאן זימון תור טלפון מרפאה סגירת תפריט אנחנו מכבדים את </t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -3223,7 +3231,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>4.336067241913308e+17</v>
+        <v>1.300820172573992e+18</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3240,16 +3248,16 @@
       <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr"/>
       <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL17" t="inlineStr"/>
       <c r="AM17" t="inlineStr"/>
       <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="inlineStr"/>
-      <c r="AP17" t="inlineStr"/>
+      <c r="AP17" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ17" t="inlineStr"/>
       <c r="AR17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS17" t="b">
         <v>0</v>
@@ -3275,7 +3283,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ד"ר קוגן לירון</t>
+          <t>ד"ר קאופמן יובל</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3295,7 +3303,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=874a0be8-2288-4588-8c92-8fd98e173223</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=87371F6B-AEDA-480B-855B-A665C2A570C0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -3306,7 +3314,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>shelach.medical@gmail.com</t>
+          <t>yochi750@gmail.com</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -3319,7 +3327,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://doctors.assuta.co.il/doctor/liron-kogan-83973?readmore=true</t>
+          <t>https://www.gynsurg.co.il/</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -3329,26 +3337,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>ד"ר לירון קוגן | גינקולוגיה ומיילדות | גינקואונקולוגיה | אסותא Jul 16, 2026 · מרפאות החבצלת 1, פתח תקווה-דוקטור קוגן לירון פתח תקווה החבצלת 1 ימי שני 18:00-19:00 מייל מרפאה: shelach.medical@gmail.com</t>
+          <t>סטרוסקופיה גישה נרתיקית בעיות גניקולוגיות בעיות פוריות פוליפ רחמי שרירנים ברחם ציסטה בשחלה אנדומטריוזיס פרטי התקשרות בית חולים 'אסותא' חיפה, קניון לב המפרץ (קומה ג') שד' ההסתדרות 55 , צ'ק פוסט, חיפה mdykaufman@gmail.com yochi750@gmail.com 03-7644777 050-9500525 © כל הזכויות שמורות ל"ר יובל קאופמן- כירורגיה גניקולוגית מתקדמת | נבנה ע"י ADACTIVE לזימון תורים - לחץ כאן זימון תור טלפון מרפאה סגירת תפריט אנחנו מכבדים את הפרטיות שלך אנחנו משת</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>"קוגן לירון" יילוד</t>
+          <t>"קאופמן יובל"</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>search_snippet</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "yochi750@gmail.com", "confidence": 100, "source_url": "https://www.gynsurg.co.il/", "identity_url": "https://www.gynsurg.co.il/", "evidence": "סטרוסקופיה גישה נרתיקית בעיות גניקולוגיות בעיות פוריות פוליפ רחמי שרירנים ברחם ציסטה בשחלה אנדומטריוזיס פרטי התקשרות בית חולים 'אסותא' חיפה, קניון לב המפרץ (קומה ג') שד' ההסתדרות 55 , צ'ק פוסט, חיפה mdykaufman@gmail.com yochi750@gmail.com 03-7644777 050-9500525 © כל הזכויות שמורות ל\"ר יובל קאופמן- כירורגיה גניקולוגית מתקדמת | נבנה ע\"י ADACTIVE לזימון תורים - לחץ כאן זימון תור טלפון מרפאה סגירת תפריט אנחנו מכבדים את הפרטיות שלך אנחנו משת", "matched_query": "\"קאופמן יובל\"", "extraction_method": "direct_text"}]</t>
         </is>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
@@ -3356,62 +3364,62 @@
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-08T23:31:56.357314+00:00</t>
+          <t>2026-09-03T21:01:40.564925+00:00</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>ddgs:yahoo+ddgs:bing</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=874a0be8-2288-4588-8c92-8fd98e173223", "https://www.meuhedet.co.il/poi/Doctors/7070866300000839730000009928_99", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A7%D7%95%D7%92%D7%9F-%D7%9C%D7%99%D7%A8%D7%95%D7%9F/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=4D7994DA1EF011E23924766CCB7D4323448E0FB52729DF77F063BC8E422E0345&amp;RequestId=00000000-0000-0000-0001-000000000518", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=3&amp;ProviderID=32912818&amp;ProviderProfession=W&amp;docClinic=4008135&amp;Service=1&amp;NewObjectId=70064900&amp;NewObjectType=S&amp;NewPerNr=90006758&amp;ol1=70064900&amp;ol2=S&amp;ol3=90006758&amp;isKosher=1&amp;beginDate=2026-09-09T02:30:57&amp;shaban=true&amp;appversion=4.1.3&amp;relative=-2&amp;action_type=1&amp;source=1", "https://doctors.assuta.co.il/doctor/liron-kogan-83973?readmore=true", "https://www.medreviews.co.il/provider/dr-kogan-liron", "https://www.gynonc.co.il/", "https://www.gynonc.co.il/about", "https://doctors.assuta.co.il/doctor/liron-kogan-83973", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fdr.lironkogan%2F", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=3&amp;ProviderID=32912818&amp;ProviderProfession=W&amp;docClinic=4008135&amp;Service=1&amp;NewObjectId=70064900&amp;NewObjectType=S&amp;NewPerNr=90006758&amp;ol1=70064900&amp;ol2=S&amp;ol3=90006758&amp;isKosher=1&amp;beginDate=2026-09-04T00:01:58&amp;shaban=true&amp;appversion=4.1.3&amp;relative=-2&amp;action_type=1&amp;source=1", "https://www.raphaelhospitals.co.il/doctors/liron-kogen/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=87371F6B-AEDA-480B-855B-A665C2A570C0", "https://www.gynsurg.co.il/", "https://www.gynsurg.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.gynsurg.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/"]</t>
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>4.340236532221031e+17</v>
+        <v>1.300820172573992e+18</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
       </c>
       <c r="AF18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>https://doctors.assuta.co.il/doctor/liron-kogan-83973?readmore=true</t>
+          <t>https://www.gynsurg.co.il/</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="inlineStr"/>
       <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL18" t="inlineStr"/>
       <c r="AM18" t="inlineStr"/>
       <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="inlineStr"/>
-      <c r="AP18" t="inlineStr"/>
+      <c r="AP18" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ18" t="inlineStr"/>
       <c r="AR18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS18" t="b">
         <v>0</v>
@@ -3437,7 +3445,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ד"ר רבהון אמיר</t>
+          <t>ד"ר קוגן לירון</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3457,7 +3465,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=73FEFAED-F4B1-412E-801F-0A168B202A07</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=874a0be8-2288-4588-8c92-8fd98e173223</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -3468,12 +3476,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>ravhon.clinic@gmail.com</t>
+          <t>shelach.medical@gmail.com</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -3481,7 +3489,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://www.dr-ravhon.co.il/</t>
+          <t>https://doctors.assuta.co.il/doctor/liron-kogan-83973?readmore=true</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3491,17 +3499,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>ד"ר אמיר רבהון - מומחה במיילדות, גניקולוגיה ובפוריות דלג לתוכן לתיאום תור למרפאה הפרטית התקשרו: 05 4-468-5276 | שלחו מייל: ravhon.clinic@gmail.com Facebook דף בית הצעד הראשון מתי לפנות לטיפולי פוריות למה לצפות כשמצפים לטיפולי פוריות? טיפולים טיפולי פוריות הפריה חוץ גופית – IVF תרומת ביציות הקפאת ביציות צילומי רחם אודות כתבות פורום Infomed יצ</t>
+          <t>ד"ר לירון קוגן | גינקולוגיה ומיילדות | גינקואונקולוגיה | אסותא Jul 16, 2026 · מרפאות החבצלת 1, פתח תקווה-דוקטור קוגן לירון פתח תקווה החבצלת 1 ימי שני 18:00-19:00 מייל מרפאה: shelach.medical@gmail.com</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>"רבהון אמיר"</t>
+          <t>"קוגן לירון" יילוד</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -3518,59 +3526,59 @@
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-04T13:09:47.289882+00:00</t>
+          <t>2026-09-08T23:31:56.357314+00:00</t>
         </is>
       </c>
       <c r="W19" t="n">
+        <v>8</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA19" t="n">
         <v>2</v>
       </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=73FEFAED-F4B1-412E-801F-0A168B202A07", "https://www.dr-ravhon.co.il/", "https://www.dr-ravhon.co.il/about/", "https://www.dr-ravhon.co.il/#contact-area", "https://www.dr-ravhon.co.il/about/#contact-area"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=874a0be8-2288-4588-8c92-8fd98e173223", "https://www.meuhedet.co.il/poi/Doctors/7070866300000839730000009928_99", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A7%D7%95%D7%92%D7%9F-%D7%9C%D7%99%D7%A8%D7%95%D7%9F/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=4D7994DA1EF011E23924766CCB7D4323448E0FB52729DF77F063BC8E422E0345&amp;RequestId=00000000-0000-0000-0001-000000000518", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=3&amp;ProviderID=32912818&amp;ProviderProfession=W&amp;docClinic=4008135&amp;Service=1&amp;NewObjectId=70064900&amp;NewObjectType=S&amp;NewPerNr=90006758&amp;ol1=70064900&amp;ol2=S&amp;ol3=90006758&amp;isKosher=1&amp;beginDate=2026-09-09T02:30:57&amp;shaban=true&amp;appversion=4.1.3&amp;relative=-2&amp;action_type=1&amp;source=1", "https://doctors.assuta.co.il/doctor/liron-kogan-83973?readmore=true", "https://www.medreviews.co.il/provider/dr-kogan-liron", "https://www.gynonc.co.il/", "https://www.gynonc.co.il/about", "https://doctors.assuta.co.il/doctor/liron-kogan-83973", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fdr.lironkogan%2F", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=3&amp;ProviderID=32912818&amp;ProviderProfession=W&amp;docClinic=4008135&amp;Service=1&amp;NewObjectId=70064900&amp;NewObjectType=S&amp;NewPerNr=90006758&amp;ol1=70064900&amp;ol2=S&amp;ol3=90006758&amp;isKosher=1&amp;beginDate=2026-09-04T00:01:58&amp;shaban=true&amp;appversion=4.1.3&amp;relative=-2&amp;action_type=1&amp;source=1", "https://www.raphaelhospitals.co.il/doctors/liron-kogen/"]</t>
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>4.340185064555201e+17</v>
+        <v>1.302070959666309e+18</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>https://www.dr-ravhon.co.il/</t>
+          <t>https://doctors.assuta.co.il/doctor/liron-kogan-83973?readmore=true</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="inlineStr"/>
       <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL19" t="inlineStr"/>
       <c r="AM19" t="inlineStr"/>
       <c r="AN19" t="inlineStr"/>
       <c r="AO19" t="inlineStr"/>
-      <c r="AP19" t="inlineStr"/>
+      <c r="AP19" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ19" t="inlineStr"/>
       <c r="AR19" t="n">
         <v>1</v>
@@ -3582,11 +3590,11 @@
         <v>1</v>
       </c>
       <c r="AU19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
+          <t>PERSON</t>
         </is>
       </c>
     </row>
@@ -3599,12 +3607,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ד"ר שטטר אורנה</t>
+          <t>ד"ר רבהון אמיר</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>family_doctor</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3619,7 +3627,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3029d9ab-24fa-43c3-93a2-29329c1b952c</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=73FEFAED-F4B1-412E-801F-0A168B202A07</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -3630,12 +3638,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>ornastatter@gmail.com</t>
+          <t>ravhon.clinic@gmail.com</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -3643,7 +3651,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://www.fps.org.il/metapel/drornas/</t>
+          <t>https://www.dr-ravhon.co.il/</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3653,12 +3661,12 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>ם והרצאות הרצאות מוקלטות מאמרים חיפוש מטפל/ת אורנה שטטר (ד"ר) דף הבית &gt; מטפלים &gt; אורנה שטטר (ד"ר) פרטי המטפל: אזור טיפול: שפלה ישוב: חולדה (ליד מזכרת בתיה, כ-20 דק מרחובות) נייד: 054-7338883 כתובת המייל של המטפל/מדריך:  ornastatter@gmail.com מידע נוסף: מומחית ברפואת משפחה מטפלת מוסמכת בפסיכותרפיה ממוקדת חברת וועד האגודה הישראלית לפסיכוסומטיקה וועד הסניף הישראלי של acbs אודות האגודה על האגודה חזון ומטרות המייסדים מאפייני טיפול קצר-מועד ה</t>
+          <t>ד"ר אמיר רבהון - מומחה במיילדות, גניקולוגיה ובפוריות דלג לתוכן לתיאום תור למרפאה הפרטית התקשרו: 05 4-468-5276 | שלחו מייל: ravhon.clinic@gmail.com Facebook דף בית הצעד הראשון מתי לפנות לטיפולי פוריות למה לצפות כשמצפים לטיפולי פוריות? טיפולים טיפולי פוריות הפריה חוץ גופית – IVF תרומת ביציות הקפאת ביציות צילומי רחם אודות כתבות פורום Infomed יצ</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>"שטטר אורנה" רפואת משפחה</t>
+          <t>"רבהון אמיר"</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -3668,11 +3676,11 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>[{"email": "fps.israel@gmail.com", "confidence": 92, "source_url": "https://www.fps.org.il/contactus/", "identity_url": "https://www.fps.org.il/metapel/drornas/", "evidence": "Envelope", "matched_query": "\"שטטר אורנה\" רפואת משפחה", "extraction_method": "linked_mailto"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -3680,36 +3688,36 @@
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-08T14:11:08.841786+00:00</t>
+          <t>2026-09-04T13:09:47.289882+00:00</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>ddgs:yahoo+ddgs:bing</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3029d9ab-24fa-43c3-93a2-29329c1b952c", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%98%D7%98%D7%A8-%D7%90%D7%95%D7%A8%D7%A0%D7%94/", "https://www.doctorita.co.il/experts/95407", "https://medpage.co.il/doctors/%D7%90%D7%95%D7%A8%D7%A0%D7%94-%D7%A9%D7%98%D7%98%D7%A8-913/", "https://drtor.co.il/doctor/18797", "https://drtor.co.il/cdn-cgi/l/email-protection#3a5955544e5b594e7a5e484e5548145955145356", "https://www.fps.org.il/metapel/drornas/", "https://www.fps.org.il/contactus/", "https://www.fps.org.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.fps.org.il/about/theassociation/", "https://www.fps.org.il/about/goals/", "https://www.fps.org.il/about/founders/", "https://www.fps.org.il/about/dstterapy/", "https://www.fps.org.il/aguda-members/%D7%90%D7%95%D7%A8%D7%A0%D7%94%D7%A9%D7%98%D7%98%D7%A8/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=73FEFAED-F4B1-412E-801F-0A168B202A07", "https://www.dr-ravhon.co.il/", "https://www.dr-ravhon.co.il/about/", "https://www.dr-ravhon.co.il/#contact-area", "https://www.dr-ravhon.co.il/about/#contact-area"]</t>
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>4.337491317124723e+17</v>
+        <v>1.30205551936656e+18</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3720,19 +3728,19 @@
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>https://www.fps.org.il/metapel/drornas/</t>
+          <t>https://www.dr-ravhon.co.il/</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL20" t="inlineStr"/>
       <c r="AM20" t="inlineStr"/>
       <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="inlineStr"/>
-      <c r="AP20" t="inlineStr"/>
+      <c r="AP20" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ20" t="inlineStr"/>
       <c r="AR20" t="n">
         <v>1</v>
@@ -3744,11 +3752,11 @@
         <v>1</v>
       </c>
       <c r="AU20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>PERSON</t>
+          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
       </c>
     </row>
@@ -3761,12 +3769,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ד"ר שרים גיא</t>
+          <t>ד"ר שטטר אורנה</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3781,7 +3789,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=F9FC3D7F-C0DD-440E-8AA7-DC41A9FCCC00</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3029d9ab-24fa-43c3-93a2-29329c1b952c</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -3792,7 +3800,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>dr.shremguy@gmail.com</t>
+          <t>ornastatter@gmail.com</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3805,7 +3813,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://guyshrem.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
+          <t>https://www.fps.org.il/metapel/drornas/</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3815,12 +3823,12 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>אודות - ד"ר גיא שרים חיפוש חיפוש אודות בירור בעיות פוריות צילום רחם מרכז הידע צרו קשר אודות בירור בעיות פוריות צילום רחם מרכז הידע צרו קשר אודות ד"ר גיא שרים יצירת קשר 077-230-3222 dr.shremguy@gmail.com שדרות ההגשמה 18, חריש לתיאום פגישה: שם טלפון אימייל שליחה אודות ד"ר גיא שרים - מומחה בגינקולוגיה ופוריות ד"ר שרים הינו מומחה באנדוקרינולוגיה של הרביה ואי-פוריות – Reproductive Endocrinology and Infe</t>
+          <t>ם והרצאות הרצאות מוקלטות מאמרים חיפוש מטפל/ת אורנה שטטר (ד"ר) דף הבית &gt; מטפלים &gt; אורנה שטטר (ד"ר) פרטי המטפל: אזור טיפול: שפלה ישוב: חולדה (ליד מזכרת בתיה, כ-20 דק מרחובות) נייד: 054-7338883 כתובת המייל של המטפל/מדריך:  ornastatter@gmail.com מידע נוסף: מומחית ברפואת משפחה מטפלת מוסמכת בפסיכותרפיה ממוקדת חברת וועד האגודה הישראלית לפסיכוסומטיקה וועד הסניף הישראלי של acbs אודות האגודה על האגודה חזון ומטרות המייסדים מאפייני טיפול קצר-מועד ה</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>"שרים גיא"</t>
+          <t>"שטטר אורנה" רפואת משפחה</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -3830,11 +3838,11 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "fps.israel@gmail.com", "confidence": 92, "source_url": "https://www.fps.org.il/contactus/", "identity_url": "https://www.fps.org.il/metapel/drornas/", "evidence": "Envelope", "matched_query": "\"שטטר אורנה\" רפואת משפחה", "extraction_method": "linked_mailto"}]</t>
         </is>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -3842,36 +3850,36 @@
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-03T21:14:53.999772+00:00</t>
+          <t>2026-09-08T14:11:08.841786+00:00</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=F9FC3D7F-C0DD-440E-8AA7-DC41A9FCCC00", "https://medicine.biu.ac.il/node/8582", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fgy.srym%2F", "https://guyshrem.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "http://guyshrem.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3029d9ab-24fa-43c3-93a2-29329c1b952c", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%98%D7%98%D7%A8-%D7%90%D7%95%D7%A8%D7%A0%D7%94/", "https://www.doctorita.co.il/experts/95407", "https://medpage.co.il/doctors/%D7%90%D7%95%D7%A8%D7%A0%D7%94-%D7%A9%D7%98%D7%98%D7%A8-913/", "https://drtor.co.il/doctor/18797", "https://drtor.co.il/cdn-cgi/l/email-protection#3a5955544e5b594e7a5e484e5548145955145356", "https://www.fps.org.il/metapel/drornas/", "https://www.fps.org.il/contactus/", "https://www.fps.org.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.fps.org.il/about/theassociation/", "https://www.fps.org.il/about/goals/", "https://www.fps.org.il/about/founders/", "https://www.fps.org.il/about/dstterapy/", "https://www.fps.org.il/aguda-members/%D7%90%D7%95%D7%A8%D7%A0%D7%94%D7%A9%D7%98%D7%98%D7%A8/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/"]</t>
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>4.336067241913308e+17</v>
+        <v>1.301247395137417e+18</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3882,19 +3890,19 @@
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>https://guyshrem.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
+          <t>https://www.fps.org.il/metapel/drornas/</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr"/>
-      <c r="AL21" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL21" t="inlineStr"/>
       <c r="AM21" t="inlineStr"/>
       <c r="AN21" t="inlineStr"/>
       <c r="AO21" t="inlineStr"/>
-      <c r="AP21" t="inlineStr"/>
+      <c r="AP21" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ21" t="inlineStr"/>
       <c r="AR21" t="n">
         <v>1</v>
@@ -3923,7 +3931,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>דוד גורדון</t>
+          <t>ד"ר שרים גיא</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3943,18 +3951,18 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=F9FC3D7F-C0DD-440E-8AA7-DC41A9FCCC00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>ima</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>davidgordon14@yahoo.com</t>
+          <t>dr.shremguy@gmail.com</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3967,7 +3975,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://www.davidgordon.co.il/</t>
+          <t>https://guyshrem.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3977,12 +3985,12 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>ניחת רחם טיפול בבריחת שתן הערכה אורו-דינמית מדיניות הפרטיות הצהרת נגישות יצירת קשר ותיאם פגישה צרי איתי קשר צוות המרפאה עומד לשרותכם! כתובתנו: מגדל מרכז ויצמן רחוב ויצמן 14, תל אביב טלפון : 03-544-9339 נייד: 052-2411171 davidgordon14@yahoo.com Facebook Google+ Instagram לשיחת יעוץ ותיאום פגישה אני מסכים/ה ל מדיניות הפרטיות ולעיבוד המידע ליצירת קשר Please leave this field empty. Ⓒ  כל הזכויות שמורות ל פרופ' דוד גורדון אורוגניקולוג | טיפו</t>
+          <t>אודות - ד"ר גיא שרים חיפוש חיפוש אודות בירור בעיות פוריות צילום רחם מרכז הידע צרו קשר אודות בירור בעיות פוריות צילום רחם מרכז הידע צרו קשר אודות ד"ר גיא שרים יצירת קשר 077-230-3222 dr.shremguy@gmail.com שדרות ההגשמה 18, חריש לתיאום פגישה: שם טלפון אימייל שליחה אודות ד"ר גיא שרים - מומחה בגינקולוגיה ופוריות ד"ר שרים הינו מומחה באנדוקרינולוגיה של הרביה ואי-פוריות – Reproductive Endocrinology and Infe</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>"דוד גורדון"</t>
+          <t>"שרים גיא"</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -4004,7 +4012,7 @@
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-03T23:18:02.537185+00:00</t>
+          <t>2026-09-03T21:14:53.999772+00:00</t>
         </is>
       </c>
       <c r="W22" t="n">
@@ -4014,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -4029,11 +4037,11 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>["https://www.davidgordon.co.il/", "https://www.davidgordon.co.il/contact/", "https://www.davidgordon.co.il/our-clinic/", "https://www.davidgordon.co.il/our-clinic/faq/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=F9FC3D7F-C0DD-440E-8AA7-DC41A9FCCC00", "https://medicine.biu.ac.il/node/8582", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fgy.srym%2F", "https://guyshrem.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "http://guyshrem.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>4.336067241913308e+17</v>
+        <v>1.300820172573992e+18</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4044,19 +4052,19 @@
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>https://www.davidgordon.co.il/</t>
+          <t>https://guyshrem.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL22" t="inlineStr"/>
       <c r="AM22" t="inlineStr"/>
       <c r="AN22" t="inlineStr"/>
       <c r="AO22" t="inlineStr"/>
-      <c r="AP22" t="inlineStr"/>
+      <c r="AP22" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ22" t="inlineStr"/>
       <c r="AR22" t="n">
         <v>1</v>
@@ -4085,7 +4093,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>יניב צפורי</t>
+          <t>דוד גורדון</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4116,7 +4124,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>zipori.obgyn@gmail.com</t>
+          <t>davidgordon14@yahoo.com</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -4129,7 +4137,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://www.zipori-obgyn.com/</t>
+          <t>https://www.davidgordon.co.il/</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -4139,12 +4147,12 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t xml:space="preserve"> דופלר. פרטי, כללית מושלם, הסדר עם כל חברות הביטוח לקרוא עוד להזמין תור כתובת המרפאה: פרופ' דן שכטמן 10, קניון מול החוף וילג', בניין B קומה 2, חדרה ליצירת קשר וקביעת תורים: 072-3937709 מיטל מזכירה ראשית 📞 ד"ר יניב צפורי zipori.obgyn@gmail.com ©2022 by Doctor Yaniv Zipori bottom of page</t>
+          <t>ניחת רחם טיפול בבריחת שתן הערכה אורו-דינמית מדיניות הפרטיות הצהרת נגישות יצירת קשר ותיאם פגישה צרי איתי קשר צוות המרפאה עומד לשרותכם! כתובתנו: מגדל מרכז ויצמן רחוב ויצמן 14, תל אביב טלפון : 03-544-9339 נייד: 052-2411171 davidgordon14@yahoo.com Facebook Google+ Instagram לשיחת יעוץ ותיאום פגישה אני מסכים/ה ל מדיניות הפרטיות ולעיבוד המידע ליצירת קשר Please leave this field empty. Ⓒ  כל הזכויות שמורות ל פרופ' דוד גורדון אורוגניקולוג | טיפו</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>"יניב צפורי"</t>
+          <t>"דוד גורדון"</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -4166,7 +4174,7 @@
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-04T16:52:16.086371+00:00</t>
+          <t>2026-09-03T23:18:02.537185+00:00</t>
         </is>
       </c>
       <c r="W23" t="n">
@@ -4176,10 +4184,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -4191,11 +4199,11 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>["https://www.doctorita.co.il/experts/65276", "https://www.zipori-obgyn.com/", "https://www.zipori-obgyn.com/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.zipori-obgyn.com/%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99-%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94"]</t>
+          <t>["https://www.davidgordon.co.il/", "https://www.davidgordon.co.il/contact/", "https://www.davidgordon.co.il/our-clinic/", "https://www.davidgordon.co.il/our-clinic/faq/"]</t>
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>4.115077426798385e+17</v>
+        <v>1.300820172573992e+18</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4206,19 +4214,19 @@
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>https://www.zipori-obgyn.com/</t>
+          <t>https://www.davidgordon.co.il/</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr"/>
       <c r="AJ23" t="inlineStr"/>
       <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL23" t="inlineStr"/>
       <c r="AM23" t="inlineStr"/>
       <c r="AN23" t="inlineStr"/>
       <c r="AO23" t="inlineStr"/>
-      <c r="AP23" t="inlineStr"/>
+      <c r="AP23" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ23" t="inlineStr"/>
       <c r="AR23" t="n">
         <v>1</v>
@@ -4247,7 +4255,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>מיכל בראונשטיין</t>
+          <t>יניב צפורי</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4278,12 +4286,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>office.clinica1@gmail.com</t>
+          <t>zipori.obgyn@gmail.com</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -4291,7 +4299,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://drbraunstein.co.il/</t>
+          <t>https://www.zipori-obgyn.com/</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -4301,12 +4309,12 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>שמירת הבריאות של הפות והנרתיק דלקת עור ממגע קנדידה וגינוזיס חיידקי BV וגיניטיס פורלנטית ליכן סקלרוזוס אטרופיה נרתיקית כאב הפות והנרתיק כל מה שרצית לדעת על גז צחוק במרפאה גינקולוגית English Facebook-f Whatsapp 08-9702314 office.clinica1@gmail.com מרפאת "קליניקה", אלי הורוביץ 27, קומה 5, רחובות שלום לכולן, שמי מיכל בראונשטיין, אני רופאת נשים. בצעירותי החלטתי ללמוד רפואה, ובמיוחד גינקולוגיה, מתוך חלום ליצור מרפאה ידידותית ונעימה עבור מטופל</t>
+          <t xml:space="preserve"> דופלר. פרטי, כללית מושלם, הסדר עם כל חברות הביטוח לקרוא עוד להזמין תור כתובת המרפאה: פרופ' דן שכטמן 10, קניון מול החוף וילג', בניין B קומה 2, חדרה ליצירת קשר וקביעת תורים: 072-3937709 מיטל מזכירה ראשית 📞 ד"ר יניב צפורי zipori.obgyn@gmail.com ©2022 by Doctor Yaniv Zipori bottom of page</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>"מיכל בראונשטיין"</t>
+          <t>"יניב צפורי"</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -4328,7 +4336,7 @@
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-09-04T18:07:38.830808+00:00</t>
+          <t>2026-09-04T16:52:16.086371+00:00</t>
         </is>
       </c>
       <c r="W24" t="n">
@@ -4338,10 +4346,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -4353,11 +4361,11 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>["https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2FDr.MichalBraunstein%2F", "https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr.michal.braunstein%2F&amp;is_from_rle", "https://drbraunstein.co.il/", "https://www.shlema.org.il/", "https://drbraunstein.co.il/contact-dermatitis/", "https://drbraunstein.co.il/%D7%92%D7%96-%D7%A6%D7%97%D7%95%D7%A7/", "https://drbraunstein.co.il/#contact"]</t>
+          <t>["https://www.doctorita.co.il/experts/65276", "https://www.zipori-obgyn.com/", "https://www.zipori-obgyn.com/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.zipori-obgyn.com/%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99-%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94"]</t>
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>4.115077426798385e+17</v>
+        <v>1.234523228039515e+18</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4368,19 +4376,19 @@
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>https://drbraunstein.co.il/</t>
+          <t>https://www.zipori-obgyn.com/</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr"/>
       <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL24" t="inlineStr"/>
       <c r="AM24" t="inlineStr"/>
       <c r="AN24" t="inlineStr"/>
       <c r="AO24" t="inlineStr"/>
-      <c r="AP24" t="inlineStr"/>
+      <c r="AP24" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ24" t="inlineStr"/>
       <c r="AR24" t="n">
         <v>1</v>
@@ -4392,11 +4400,11 @@
         <v>1</v>
       </c>
       <c r="AU24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
+          <t>PERSON</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4417,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>נורה גורכד שבסו</t>
+          <t>מיכל בראונשטיין</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4440,12 +4448,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>norashapso@gmail.com</t>
+          <t>office.clinica1@gmail.com</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -4453,7 +4461,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/</t>
+          <t>https://drbraunstein.co.il/</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -4463,12 +4471,12 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Med Ted לחברים בלבד ארצ״י בשטח ארצ״י בתקשורת ארצ"י בכנסת פודקאסט "סדציה להמונים" נוהל כניסה להסדר הצטרפות צרו קשר טופס דיווח שיימינג טופס בקשת סיוע קהילה לזכרם חזרה &gt; חזרה &gt; ד"ר נורה שבסו גינקולוגיה ומיילדות 052-5363267 norashapso@gmail.com ד"ר נורה גורכד שפסו היא מומחית בגינקולוגיה ומיילדות, ובעלת על־התמחות בפוריות ובהפריה חוץ־גופית (IVF). נורה למדה רפואה בטכניון והתמחתה במרכז הרפואי צפון. כיום היא עובדת כרופאה בכירה ביחידת ה- IVF  וכר</t>
+          <t>שמירת הבריאות של הפות והנרתיק דלקת עור ממגע קנדידה וגינוזיס חיידקי BV וגיניטיס פורלנטית ליכן סקלרוזוס אטרופיה נרתיקית כאב הפות והנרתיק כל מה שרצית לדעת על גז צחוק במרפאה גינקולוגית English Facebook-f Whatsapp 08-9702314 office.clinica1@gmail.com מרפאת "קליניקה", אלי הורוביץ 27, קומה 5, רחובות שלום לכולן, שמי מיכל בראונשטיין, אני רופאת נשים. בצעירותי החלטתי ללמוד רפואה, ובמיוחד גינקולוגיה, מתוך חלום ליצור מרפאה ידידותית ונעימה עבור מטופל</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>"נורה גורכד שבסו"</t>
+          <t>"מיכל בראונשטיין"</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -4490,7 +4498,7 @@
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-09-04T04:55:16.280760+00:00</t>
+          <t>2026-09-04T18:07:38.830808+00:00</t>
         </is>
       </c>
       <c r="W25" t="n">
@@ -4500,13 +4508,13 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
@@ -4515,11 +4523,11 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>["https://www.doctorita.co.il/experts/119054", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%92%D7%95%D7%A8%D7%9B%D7%93-%D7%A9%D7%91%D7%A1%D7%95-%D7%A0%D7%95%D7%A8%D7%94/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=72FD73030256FB59999957F3E61E03EABE6A8F724FC86F83B2380B60589F61A5&amp;RequestId=00000000-0000-0000-0001-000000000612", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=CE57634ABBFA154920019C7FAAD7385EAB0BB0D5FD8189978016A2325E1941AE&amp;RequestId=00000000-0000-0000-0001-000000000428", "https://www.beok.co.il/doctors/Doctors-1114057/", "https://medpage.co.il/doctors/%D7%A0%D7%95%D7%A8%D7%94-%D7%92%D7%95%D7%A8%D7%9B%D7%93-%D7%A9%D7%91%D7%A1%D7%95-20898/", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/", "https://www.amutatartzi.org/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.amutatartzi.org/%D7%A6%D7%95%D7%95%D7%AA-%D7%95%D7%91%D7%A2%D7%9C%D7%99-%D7%AA%D7%A4%D7%A7%D7%99%D7%93%D7%99%D7%9D/", "https://www.amutatartzi.org/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%90%D7%A8%D7%A6%D7%99/%D7%AA%D7%A7%D7%A0%D7%95%D7%9F-%D7%94%D7%A2%D7%9E%D7%95%D7%AA%D7%94/", "https://www.amutatartzi.org/דרושים-שותפויות-השכרת-מרפאה/", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%93%D7%B4%D7%A8-%D7%A2%D7%90%D7%99%D7%93%D7%94-%D7%94%D7%99%D7%99%D7%91-%D7%97%D7%9C%D7%99%D7%99%D7%97%D7%9C/", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A4%D7%99%D7%9C%D7%99%D7%A4-%D7%A8%D7%95%D7%96%D7%99%D7%A0%D7%A1%D7%A7%D7%99/", "https://www.amutatartzi.org/team/%D7%93%D7%B4%D7%A8-%D7%A9%D7%9E%D7%A2%D7%95%D7%9F-%D7%90%D7%A8%D7%95%D7%A0%D7%94%D7%99%D7%99%D7%9D/"]</t>
+          <t>["https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2FDr.MichalBraunstein%2F", "https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr.michal.braunstein%2F&amp;is_from_rle", "https://drbraunstein.co.il/", "https://www.shlema.org.il/", "https://drbraunstein.co.il/contact-dermatitis/", "https://drbraunstein.co.il/%D7%92%D7%96-%D7%A6%D7%97%D7%95%D7%A7/", "https://drbraunstein.co.il/#contact"]</t>
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>4.014877075845656e+17</v>
+        <v>1.234523228039515e+18</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4530,19 +4538,19 @@
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/</t>
+          <t>https://drbraunstein.co.il/</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="inlineStr"/>
       <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL25" t="inlineStr"/>
       <c r="AM25" t="inlineStr"/>
       <c r="AN25" t="inlineStr"/>
       <c r="AO25" t="inlineStr"/>
-      <c r="AP25" t="inlineStr"/>
+      <c r="AP25" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ25" t="inlineStr"/>
       <c r="AR25" t="n">
         <v>1</v>
@@ -4554,11 +4562,11 @@
         <v>1</v>
       </c>
       <c r="AU25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>PERSON</t>
+          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4579,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>נעם דומניץ</t>
+          <t>נורה גורכד שבסו</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4602,12 +4610,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>domniz.clinic@gmail.com</t>
+          <t>norashapso@gmail.com</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -4615,7 +4623,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://www.dr-domniz.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/</t>
+          <t>https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -4625,17 +4633,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>ל הדרך גלריה רוצה לשמוע מידע נוסף? קבעי פגישה עם ד"ר נעם דומניץ וקבלי טיפול מותאם אישית. קביעת תור / וואטסאפ פרטי יצירת קשר 0502174994 רוטשילד 54, כפר סבא (בית עמיתים, קומה 1, חדר 6 (מאחורי בית חב״ד)  | רש״י 30, בני ברק domniz.clinic@gmail.com ד"ר דומניץ מומחה בפוריות, מיילדות וגינקולוגיה. תחומי המרפאה בדיקות הריון ייעוץ טרום הריוני הריון בסיכון התקן תוך רחמי אבחון פוריות ‪טיפולי פוריות ‪ייעוץ פוריות ‪בדיקות פוריות תסמיני גיל המעבר משפט</t>
+          <t>Med Ted לחברים בלבד ארצ״י בשטח ארצ״י בתקשורת ארצ"י בכנסת פודקאסט "סדציה להמונים" נוהל כניסה להסדר הצטרפות צרו קשר טופס דיווח שיימינג טופס בקשת סיוע קהילה לזכרם חזרה &gt; חזרה &gt; ד"ר נורה שבסו גינקולוגיה ומיילדות 052-5363267 norashapso@gmail.com ד"ר נורה גורכד שפסו היא מומחית בגינקולוגיה ומיילדות, ובעלת על־התמחות בפוריות ובהפריה חוץ־גופית (IVF). נורה למדה רפואה בטכניון והתמחתה במרכז הרפואי צפון. כיום היא עובדת כרופאה בכירה ביחידת ה- IVF  וכר</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>"נעם דומניץ"</t>
+          <t>"נורה גורכד שבסו"</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>linked_text</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -4652,7 +4660,7 @@
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-09-04T05:13:39.315015+00:00</t>
+          <t>2026-09-04T04:55:16.280760+00:00</t>
         </is>
       </c>
       <c r="W26" t="n">
@@ -4662,13 +4670,13 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Z26" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
@@ -4677,11 +4685,11 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>["https://www.dr-domniz.co.il/", "https://www.dr-domniz.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/"]</t>
+          <t>["https://www.doctorita.co.il/experts/119054", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%92%D7%95%D7%A8%D7%9B%D7%93-%D7%A9%D7%91%D7%A1%D7%95-%D7%A0%D7%95%D7%A8%D7%94/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=72FD73030256FB59999957F3E61E03EABE6A8F724FC86F83B2380B60589F61A5&amp;RequestId=00000000-0000-0000-0001-000000000612", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=CE57634ABBFA154920019C7FAAD7385EAB0BB0D5FD8189978016A2325E1941AE&amp;RequestId=00000000-0000-0000-0001-000000000428", "https://www.beok.co.il/doctors/Doctors-1114057/", "https://medpage.co.il/doctors/%D7%A0%D7%95%D7%A8%D7%94-%D7%92%D7%95%D7%A8%D7%9B%D7%93-%D7%A9%D7%91%D7%A1%D7%95-20898/", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/", "https://www.amutatartzi.org/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.amutatartzi.org/%D7%A6%D7%95%D7%95%D7%AA-%D7%95%D7%91%D7%A2%D7%9C%D7%99-%D7%AA%D7%A4%D7%A7%D7%99%D7%93%D7%99%D7%9D/", "https://www.amutatartzi.org/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%90%D7%A8%D7%A6%D7%99/%D7%AA%D7%A7%D7%A0%D7%95%D7%9F-%D7%94%D7%A2%D7%9E%D7%95%D7%AA%D7%94/", "https://www.amutatartzi.org/דרושים-שותפויות-השכרת-מרפאה/", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%93%D7%B4%D7%A8-%D7%A2%D7%90%D7%99%D7%93%D7%94-%D7%94%D7%99%D7%99%D7%91-%D7%97%D7%9C%D7%99%D7%99%D7%97%D7%9C/", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A4%D7%99%D7%9C%D7%99%D7%A4-%D7%A8%D7%95%D7%96%D7%99%D7%A0%D7%A1%D7%A7%D7%99/", "https://www.amutatartzi.org/team/%D7%93%D7%B4%D7%A8-%D7%A9%D7%9E%D7%A2%D7%95%D7%9F-%D7%90%D7%A8%D7%95%D7%A0%D7%94%D7%99%D7%99%D7%9D/"]</t>
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>4.014877075845656e+17</v>
+        <v>1.204463122753697e+18</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4692,19 +4700,19 @@
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>https://www.dr-domniz.co.il/</t>
+          <t>https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="inlineStr"/>
-      <c r="AL26" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL26" t="inlineStr"/>
       <c r="AM26" t="inlineStr"/>
       <c r="AN26" t="inlineStr"/>
       <c r="AO26" t="inlineStr"/>
-      <c r="AP26" t="inlineStr"/>
+      <c r="AP26" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ26" t="inlineStr"/>
       <c r="AR26" t="n">
         <v>1</v>
@@ -4716,11 +4724,11 @@
         <v>1</v>
       </c>
       <c r="AU26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
+          <t>PERSON</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4741,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>נתנאל אלקבץ</t>
+          <t>נעם דומניץ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4764,7 +4772,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>aimee.medicalclinic@gmail.com</t>
+          <t>domniz.clinic@gmail.com</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -4777,7 +4785,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://www.aimeemedical.co.il/clinical-dietitian/</t>
+          <t>https://www.dr-domniz.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4787,13 +4795,12 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>הריון בסיכון או לצד מחלות רקע-  הוא תהליך אישי, מותאם ומכיל.
-עם ליווי מקצועי של אופק כהן־אלקבץ, דיאטנית קלינית מומחית, תוכלי לשמור על בריאותך ובריאות העובר ולחוות הריון רגוע ומאוזן. לתיאום פגישה אישית עם ד"ר נתנאל אלקבץ aimee.medicalclinic@gmail.com 053-338-8023 ניווט ראשי אודותינו המוצרים שלנו צרו קשר שירותי הקליניקה מעקב הריון והריון בסיכון גבוהה אולטרסאונד מתקדם בירור בעיות פריון אסתטיקה גינקולוגית תפקודית לביופלסטיקה דיטנית קלינית -</t>
+          <t>ל הדרך גלריה רוצה לשמוע מידע נוסף? קבעי פגישה עם ד"ר נעם דומניץ וקבלי טיפול מותאם אישית. קביעת תור / וואטסאפ פרטי יצירת קשר 0502174994 רוטשילד 54, כפר סבא (בית עמיתים, קומה 1, חדר 6 (מאחורי בית חב״ד)  | רש״י 30, בני ברק domniz.clinic@gmail.com ד"ר דומניץ מומחה בפוריות, מיילדות וגינקולוגיה. תחומי המרפאה בדיקות הריון ייעוץ טרום הריוני הריון בסיכון התקן תוך רחמי אבחון פוריות ‪טיפולי פוריות ‪ייעוץ פוריות ‪בדיקות פוריות תסמיני גיל המעבר משפט</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>"נתנאל אלקבץ"</t>
+          <t>"נעם דומניץ"</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -4815,7 +4822,7 @@
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-09-04T05:24:06.061110+00:00</t>
+          <t>2026-09-04T05:13:39.315015+00:00</t>
         </is>
       </c>
       <c r="W27" t="n">
@@ -4825,10 +4832,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -4840,11 +4847,11 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>["https://www.infomed.co.il/experts/152655/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2F61560664132234%2F", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%90%D7%9C%D7%A7%D7%91%D7%A5-%D7%A0%D7%AA%D7%A0%D7%90%D7%9C/", "https://www.medreviews.co.il/provider/dr-elkabetz-netanel", "https://www.aimeemedical.co.il/about-us/", "https://www.aimeemedical.co.il/clinical-dietitian/", "https://www.aimeemedical.co.il/contact/"]</t>
+          <t>["https://www.dr-domniz.co.il/", "https://www.dr-domniz.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/"]</t>
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>4.014877075845656e+17</v>
+        <v>1.204463122753697e+18</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4855,19 +4862,19 @@
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>https://www.medreviews.co.il/provider/dr-elkabetz-netanel</t>
+          <t>https://www.dr-domniz.co.il/</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr"/>
       <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL27" t="inlineStr"/>
       <c r="AM27" t="inlineStr"/>
       <c r="AN27" t="inlineStr"/>
       <c r="AO27" t="inlineStr"/>
-      <c r="AP27" t="inlineStr"/>
+      <c r="AP27" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ27" t="inlineStr"/>
       <c r="AR27" t="n">
         <v>1</v>
@@ -4896,7 +4903,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>עמיחי רוטנשטרייך</t>
+          <t>נתנאל אלקבץ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4927,12 +4934,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>prof.rottenstreich@gmail.com</t>
+          <t>aimee.medicalclinic@gmail.com</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -4940,7 +4947,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://www.prof-rottenstreich.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA</t>
+          <t>https://www.aimeemedical.co.il/clinical-dietitian/</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4950,12 +4957,13 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>פואה פרופסור חבר מטעם האוניברסיטה העברית האגף למיילדות וגינקולוגיה, בית החולים וולפסון, חולון רופא בכיר ומנהל שירות ביחידה להיריון בסיכון Chat Phone פרופ׳ עמיחי רוטנשטרייך מומחה למיילדות גי נ קולוגיה והיריון בסיכון גבוה prof.rottenstreich@gmail.com 055-9787751            , 055-4353787 כל הזכויות שמורות עמיחי רוטנשטרייך 2024 © bottom of page</t>
+          <t>הריון בסיכון או לצד מחלות רקע-  הוא תהליך אישי, מותאם ומכיל.
+עם ליווי מקצועי של אופק כהן־אלקבץ, דיאטנית קלינית מומחית, תוכלי לשמור על בריאותך ובריאות העובר ולחוות הריון רגוע ומאוזן. לתיאום פגישה אישית עם ד"ר נתנאל אלקבץ aimee.medicalclinic@gmail.com 053-338-8023 ניווט ראשי אודותינו המוצרים שלנו צרו קשר שירותי הקליניקה מעקב הריון והריון בסיכון גבוהה אולטרסאונד מתקדם בירור בעיות פריון אסתטיקה גינקולוגית תפקודית לביופלסטיקה דיטנית קלינית -</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>"עמיחי רוטנשטרייך"</t>
+          <t>"נתנאל אלקבץ"</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -4977,7 +4985,7 @@
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-09-04T06:21:38.973409+00:00</t>
+          <t>2026-09-04T05:24:06.061110+00:00</t>
         </is>
       </c>
       <c r="W28" t="n">
@@ -4987,10 +4995,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -5002,11 +5010,11 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>["https://www.prof-rottenstreich.co.il/", "https://www.prof-rottenstreich.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.prof-rottenstreich.co.il/%D7%AA%D7%97%D7%95%D7%9E%D7%99-%D7%A4%D7%A2%D7%99%D7%9C%D7%95%D7%AA"]</t>
+          <t>["https://www.infomed.co.il/experts/152655/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2F61560664132234%2F", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%90%D7%9C%D7%A7%D7%91%D7%A5-%D7%A0%D7%AA%D7%A0%D7%90%D7%9C/", "https://www.medreviews.co.il/provider/dr-elkabetz-netanel", "https://www.aimeemedical.co.il/about-us/", "https://www.aimeemedical.co.il/clinical-dietitian/", "https://www.aimeemedical.co.il/contact/"]</t>
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>4.014877075845656e+17</v>
+        <v>1.204463122753697e+18</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5017,19 +5025,19 @@
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>https://www.prof-rottenstreich.co.il/</t>
+          <t>https://www.medreviews.co.il/provider/dr-elkabetz-netanel</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr"/>
       <c r="AJ28" t="inlineStr"/>
       <c r="AK28" t="inlineStr"/>
-      <c r="AL28" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL28" t="inlineStr"/>
       <c r="AM28" t="inlineStr"/>
       <c r="AN28" t="inlineStr"/>
       <c r="AO28" t="inlineStr"/>
-      <c r="AP28" t="inlineStr"/>
+      <c r="AP28" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ28" t="inlineStr"/>
       <c r="AR28" t="n">
         <v>1</v>
@@ -5041,11 +5049,11 @@
         <v>1</v>
       </c>
       <c r="AU28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>PERSON</t>
+          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5066,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ערן ברזילי</t>
+          <t>עמיחי רוטנשטרייך</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5089,7 +5097,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>prof.eran.barzilay@gmail.com</t>
+          <t>prof.rottenstreich@gmail.com</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -5102,7 +5110,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
+          <t>https://www.prof-rottenstreich.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -5112,17 +5120,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>ת ה- MD-PhD היוקרתית של הפקולטה לרפואה באוניברסיטת תל אביב, בהצטיינות. עמודים דף הבית אודות אולטרסאונד בהריון ממצאים לא תקינים אולטרסאונד גניקולוגי צור קשר צור קשר ברודצקי 43, כניסה ב', רמת אביב, תל אביב יפו 073-7815218 prof.eran.barzilay@gmail.com פרופ' ערן ברזילי באינפומד © כל הזכויות שמורות לאינפומד בע"מ פרטיות המבקרים באתר חשובה לנו כדי לשפר את חוויית הגלישה, אתר זה משתמש בקבצי עוגיות  (Cookies), המשך גלישה באתר מהווה הסכמתך לכך. מד</t>
+          <t>פואה פרופסור חבר מטעם האוניברסיטה העברית האגף למיילדות וגינקולוגיה, בית החולים וולפסון, חולון רופא בכיר ומנהל שירות ביחידה להיריון בסיכון Chat Phone פרופ׳ עמיחי רוטנשטרייך מומחה למיילדות גי נ קולוגיה והיריון בסיכון גבוה prof.rottenstreich@gmail.com 055-9787751            , 055-4353787 כל הזכויות שמורות עמיחי רוטנשטרייך 2024 © bottom of page</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>"ערן ברזילי"</t>
+          <t>"עמיחי רוטנשטרייך"</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>linked_text</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -5139,7 +5147,7 @@
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-04T06:36:53.022308+00:00</t>
+          <t>2026-09-04T06:21:38.973409+00:00</t>
         </is>
       </c>
       <c r="W29" t="n">
@@ -5149,13 +5157,13 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
@@ -5164,11 +5172,11 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>["https://www.instagram.com/proferanbarzilay/", "https://www.bgu.ac.il/people/barzilae/", "https://www.bgu.ac.il/en/people/barzilae/", "https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://dr-barzilay.com/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/"]</t>
+          <t>["https://www.prof-rottenstreich.co.il/", "https://www.prof-rottenstreich.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.prof-rottenstreich.co.il/%D7%AA%D7%97%D7%95%D7%9E%D7%99-%D7%A4%D7%A2%D7%99%D7%9C%D7%95%D7%AA"]</t>
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>4.014877075845656e+17</v>
+        <v>1.204463122753697e+18</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5179,19 +5187,19 @@
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
+          <t>https://www.prof-rottenstreich.co.il/</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr"/>
       <c r="AJ29" t="inlineStr"/>
       <c r="AK29" t="inlineStr"/>
-      <c r="AL29" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL29" t="inlineStr"/>
       <c r="AM29" t="inlineStr"/>
       <c r="AN29" t="inlineStr"/>
       <c r="AO29" t="inlineStr"/>
-      <c r="AP29" t="inlineStr"/>
+      <c r="AP29" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ29" t="inlineStr"/>
       <c r="AR29" t="n">
         <v>1</v>
@@ -5220,7 +5228,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>פרופ' משען נדב</t>
+          <t>ערן ברזילי</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5240,18 +5248,18 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=26deea29-fa58-44cd-a7ba-96d9df718414</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>ima</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>drnadavmic@gmail.com</t>
+          <t>prof.eran.barzilay@gmail.com</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -5264,7 +5272,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://www.dr-mishan.co.il/</t>
+          <t>https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -5274,12 +5282,12 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>פרופ' נדב משען ✅️ קבעי כעת ביקור בקליניקה הפרטית ✔️ דלג לתוכן 052-4322732 03-5716996 drnadavmic@gmail.com רחוב רמב"ם 26, גבעתיים בית – פרופ' נדב משען אודות שירותי המרפאה סרטן הרחם סרטן צוואר הרחם סרטן שחלות סרטן הערייה (vulva) בדיקת פאפ בדיקת קולפוסקופיה נשאיות של BRCA קוניזציה גניקולוגיה כללית מחקר רפוא</t>
+          <t>ת ה- MD-PhD היוקרתית של הפקולטה לרפואה באוניברסיטת תל אביב, בהצטיינות. עמודים דף הבית אודות אולטרסאונד בהריון ממצאים לא תקינים אולטרסאונד גניקולוגי צור קשר צור קשר ברודצקי 43, כניסה ב', רמת אביב, תל אביב יפו 073-7815218 prof.eran.barzilay@gmail.com פרופ' ערן ברזילי באינפומד © כל הזכויות שמורות לאינפומד בע"מ פרטיות המבקרים באתר חשובה לנו כדי לשפר את חוויית הגלישה, אתר זה משתמש בקבצי עוגיות  (Cookies), המשך גלישה באתר מהווה הסכמתך לכך. מד</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>"משען נדב"</t>
+          <t>"ערן ברזילי"</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -5301,11 +5309,11 @@
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-09-04T04:19:53.405262+00:00</t>
+          <t>2026-09-04T06:36:53.022308+00:00</t>
         </is>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
@@ -5314,7 +5322,7 @@
         <v>4</v>
       </c>
       <c r="Z30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AA30" t="n">
         <v>1</v>
@@ -5326,11 +5334,11 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=26deea29-fa58-44cd-a7ba-96d9df718414", "https://doctors.assuta.co.il/doctor/nadav-michaan-80431?readmore=true", "https://www.dr-mishan.co.il/", "https://md-digital.co.il/", "https://www.dr-mishan.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.infomed.co.il/experts/144408/", "https://medpage.co.il/doctors/%D7%A0%D7%93%D7%91-%D7%9E%D7%A9%D7%A2%D7%9F-20445/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%A0%D7%93%D7%91-%D7%9E%D7%A9%D7%A2%D7%9F/", "https://www.danielly.co.il/doctors/view/%D7%93%D7%A8-%D7%A0%D7%93%D7%91-%D7%9E%D7%A9%D7%A2%D7%9F-%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92", "https://www.danielly.co.il/contact/index", "https://www.danielly.co.il/contact", "https://www.danielly.co.il/about", "https://www.danielly.co.il/contact?apt=1&amp;doctor_id=668"]</t>
+          <t>["https://www.instagram.com/proferanbarzilay/", "https://www.bgu.ac.il/people/barzilae/", "https://www.bgu.ac.il/en/people/barzilae/", "https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://dr-barzilay.com/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/"]</t>
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>5.349051611818981e+17</v>
+        <v>1.204463122753697e+18</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5341,19 +5349,19 @@
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>https://www.dr-mishan.co.il/</t>
+          <t>https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr"/>
       <c r="AJ30" t="inlineStr"/>
       <c r="AK30" t="inlineStr"/>
-      <c r="AL30" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL30" t="inlineStr"/>
       <c r="AM30" t="inlineStr"/>
       <c r="AN30" t="inlineStr"/>
       <c r="AO30" t="inlineStr"/>
-      <c r="AP30" t="inlineStr"/>
+      <c r="AP30" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ30" t="inlineStr"/>
       <c r="AR30" t="n">
         <v>1</v>
@@ -5382,12 +5390,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>רחל דהן</t>
+          <t>פרופ' משען נדב</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>family_doctor</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -5402,18 +5410,18 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=26deea29-fa58-44cd-a7ba-96d9df718414</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>ima</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>racheldahan@hotmail.com</t>
+          <t>drnadavmic@gmail.com</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -5426,7 +5434,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://www.hebpsy.net/showprofile.asp?id=18767</t>
+          <t>https://www.dr-mishan.co.il/</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -5436,12 +5444,12 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>שית בהיפנוזה יועצת גמילה מעישון טיפול בהפרעות שינה, ושינוי הרגלי חיים. רכזת מחקר המחלקה לרפואת משפחה -חיפה מנהלת מרפאת לב הקריה, שירותי בריאות כללית, קרית אתא. טל: 0543130956 אתר אינטרנט http://hypnosis.99k.org ;      : racheldahan@hotmail.com "דוא"ל הפרטים המובאים בכרטיס האישי של רחל דהן, ובכללם פרטים בדבר התואר האקדמי וההכשרה המקצועית נוסחו על ידי רחל דהן ובאחריותו/ה. נצפים ביותר יומנו של עורך וידאו - עדויות מהשבעה באוקטובר / רוני אלפ</t>
+          <t>פרופ' נדב משען ✅️ קבעי כעת ביקור בקליניקה הפרטית ✔️ דלג לתוכן 052-4322732 03-5716996 drnadavmic@gmail.com רחוב רמב"ם 26, גבעתיים בית – פרופ' נדב משען אודות שירותי המרפאה סרטן הרחם סרטן צוואר הרחם סרטן שחלות סרטן הערייה (vulva) בדיקת פאפ בדיקת קולפוסקופיה נשאיות של BRCA קוניזציה גניקולוגיה כללית מחקר רפוא</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>"רחל דהן" רפואת משפחה</t>
+          <t>"משען נדב"</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -5458,16 +5466,16 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-09-10T13:53:25.006579+00:00</t>
+          <t>2026-09-04T04:19:53.405262+00:00</t>
         </is>
       </c>
       <c r="W31" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -5476,7 +5484,7 @@
         <v>4</v>
       </c>
       <c r="Z31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA31" t="n">
         <v>1</v>
@@ -5488,22 +5496,22 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>["https://www.doctorita.co.il/experts/141424", "https://www.colbonews.co.il/health/166678/", "https://www.hebpsy.net/showprofile.asp?id=18767", "https://www.hebpsy.net/me.asp?id=72&amp;page=6", "https://www.hebpsy.net/pl.asp?cat=about", "https://www.hebpsy.net/me.asp?id=72", "https://www.hebpsy.net/sysMsg.asp?id=profile_about#p10", "https://www.hebpsy.net/sysMsg.asp?id=profile_about", "https://www.hebpsy.net/showprofile.asp?id=18767#profile", "https://www.hebpsy.net/me.asp?id=72&amp;page=6#contact", "https://www.hebpsy.net/sysMsg.asp?id=profile_promotPL", "https://www.hebpsy.net/me.asp?id=72#contact", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fraceldahan%2F", "https://www.facebook.com/public/%D7%A8%D7%97%D7%9C-%D7%93%D7%94%D7%9F/", "https://www.myheritage.com/names/%D7%A8%D7%97%D7%9C_%D7%93%D7%94%D7%9F", "https://gen.rlzm.co.il/persons/%D7%A8%D7%97%D7%9C-%D7%93%D7%94%D7%9F/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=26deea29-fa58-44cd-a7ba-96d9df718414", "https://doctors.assuta.co.il/doctor/nadav-michaan-80431?readmore=true", "https://www.dr-mishan.co.il/", "https://md-digital.co.il/", "https://www.dr-mishan.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.infomed.co.il/experts/144408/", "https://medpage.co.il/doctors/%D7%A0%D7%93%D7%91-%D7%9E%D7%A9%D7%A2%D7%9F-20445/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%A0%D7%93%D7%91-%D7%9E%D7%A9%D7%A2%D7%9F/", "https://www.danielly.co.il/doctors/view/%D7%93%D7%A8-%D7%A0%D7%93%D7%91-%D7%9E%D7%A9%D7%A2%D7%9F-%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92", "https://www.danielly.co.il/contact/index", "https://www.danielly.co.il/contact", "https://www.danielly.co.il/about", "https://www.danielly.co.il/contact?apt=1&amp;doctor_id=668"]</t>
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>4.003947683133098e+17</v>
+        <v>1.604715483545694e+18</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
       </c>
       <c r="AF31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>https://www.hebpsy.net/showprofile.asp?id=18767</t>
+          <t>https://www.dr-mishan.co.il/</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr"/>
@@ -5511,20 +5519,12 @@
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="inlineStr"/>
       <c r="AM31" t="inlineStr"/>
-      <c r="AN31" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO31" t="b">
-        <v>1</v>
-      </c>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
       <c r="AP31" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ31" t="inlineStr">
-        <is>
-          <t>רחל דהן - רופאה רחל דהן - רופאה דלג לתוכן ראשי - מקש קיצור 2 (לחץ Enter) דף הבית - מקש קיצור 1 (לחץ Enter) דלג לתפריט ראשי - מקש קיצור 5 (לחץ Enter) דלג לתיבת חיפוש - מקש קיצור 4 (לחץ Enter) צור קשר - מקש קיצור 9 (לחץ Enter) הצהרת נגישות - מקש קיצור 0 (לחץ Enter) סגור עזרה ראשונה נפשית - בהתנדבות אודות והצטרפות טיפול נפשי מוזל טיפול נפשי בתל אביב מטפלים בהסדר קופת חולים פנויים לקבלת מטופלים חדשים טיפול זוגי טיפול התנהגותי קוגניטיבי - CBT הדרכת הורים טיפול נפשי לילדים אבחון פסיכולוגי לילדים פסיכולוגית בתל אביב פסיכולוגים כניסה רישום צרו קשר חיפוש × × אימייל (דוא"ל) סיסמא שכחת את הסיסמה? הקלידו אימייל ולחצו כאן כניסה אני מסכימ.ה להצטרף לרשימת התפוצה לקבלת עדכונים ומידע שיווקי זכור אותי רישום משתמש חדש ביטול פסיכולוגיה עברית ראשי השער שלי תיבת מסרים כרטיס הביקור שלי הגדרות חשבון אודות פסיכולוגיה עברית שאלות נפוצות יציאה מאמרים המאמרים שלי הגשת טקסט לפרסום נבחרי העורכת אספרגר טיפולי המרה סקס טוב דיו רגשות חינוך מיני תסמונת טורט ניכור הורי רשימות קריאה הכותבים קטגוריות מאמרים מאמרים לפי נושאים ניוזלטר בלוג</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="inlineStr"/>
       <c r="AR31" t="n">
         <v>1</v>
       </c>
@@ -5552,12 +5552,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>אוהד חורי</t>
+          <t>רחל דהן</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>ohadho@clalit.org.il</t>
+          <t>racheldahan@hotmail.com</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -5592,11 +5592,11 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
+          <t>https://www.hebpsy.net/showprofile.asp?id=18767</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -5606,17 +5606,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
+          <t>שית בהיפנוזה יועצת גמילה מעישון טיפול בהפרעות שינה, ושינוי הרגלי חיים. רכזת מחקר המחלקה לרפואת משפחה -חיפה מנהלת מרפאת לב הקריה, שירותי בריאות כללית, קרית אתא. טל: 0543130956 אתר אינטרנט http://hypnosis.99k.org ;      : racheldahan@hotmail.com "דוא"ל הפרטים המובאים בכרטיס האישי של רחל דהן, ובכללם פרטים בדבר התואר האקדמי וההכשרה המקצועית נוסחו על ידי רחל דהן ובאחריותו/ה. נצפים ביותר יומנו של עורך וידאו - עדויות מהשבעה באוקטובר / רוני אלפ</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>"אוהד חורי" יילוד site:clalit.co.il</t>
+          <t>"רחל דהן" רפואת משפחה</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>search_snippet</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -5628,12 +5628,12 @@
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-09-09T23:21:42.073181+00:00</t>
+          <t>2026-09-10T13:53:25.006579+00:00</t>
         </is>
       </c>
       <c r="W32" t="n">
@@ -5643,58 +5643,58 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>ddgs:yahoo+ddgs:bing</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx", "https://www.doctorita.co.il/experts/94233", "https://www.ha-makom.co.il/author/vhdcvry/", "https://foody.co.il/author/ohad/", "https://knowmore.co.il/doctors/אוהד-חורי-2/", "https://stage.ha-makom.co.il/author/vhdcvry/", "https://www.facebook.com/YoldotBeilinson/videos/%D7%9E%D7%94-%D7%96%D7%95-%D7%9C%D7%99%D7%93%D7%AA-vbac-%D7%A9%D7%9B%D7%95%D7%9C%D7%9F-%D7%9E%D7%93%D7%91%D7%A8%D7%95%D7%AA-%D7%A2%D7%9C%D7%99%D7%94-%D7%A2%D7%95%D7%A9%D7%99%D7%9D-%D7%9C%D7%9B%D7%9F-%D7%A1%D7%93%D7%A8-%D7%91%D7%9E%D7%95%D7%A9%D7%92%D7%99%D7%9D-%D7%A2%D7%9D-%D7%93%D7%A8-%D7%90%D7%95%D7%94%D7%93-%D7%97%D7%95%D7%A8%D7%99-%D7%A9%D7%9B%D7%90%D7%9F-%D7%9B%D7%93%D7%99/1754039901764363/"]</t>
+          <t>["https://www.doctorita.co.il/experts/141424", "https://www.colbonews.co.il/health/166678/", "https://www.hebpsy.net/showprofile.asp?id=18767", "https://www.hebpsy.net/me.asp?id=72&amp;page=6", "https://www.hebpsy.net/pl.asp?cat=about", "https://www.hebpsy.net/me.asp?id=72", "https://www.hebpsy.net/sysMsg.asp?id=profile_about#p10", "https://www.hebpsy.net/sysMsg.asp?id=profile_about", "https://www.hebpsy.net/showprofile.asp?id=18767#profile", "https://www.hebpsy.net/me.asp?id=72&amp;page=6#contact", "https://www.hebpsy.net/sysMsg.asp?id=profile_promotPL", "https://www.hebpsy.net/me.asp?id=72#contact", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fraceldahan%2F", "https://www.facebook.com/public/%D7%A8%D7%97%D7%9C-%D7%93%D7%94%D7%9F/", "https://www.myheritage.com/names/%D7%A8%D7%97%D7%9C_%D7%93%D7%94%D7%9F", "https://gen.rlzm.co.il/persons/%D7%A8%D7%97%D7%9C-%D7%93%D7%94%D7%9F/"]</t>
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>4.337491317126436e+17</v>
+        <v>1.201184304939929e+18</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
+          <t>https://www.hebpsy.net/showprofile.asp?id=18767</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr"/>
       <c r="AJ32" t="inlineStr"/>
       <c r="AK32" t="inlineStr"/>
-      <c r="AL32" t="inlineStr"/>
-      <c r="AM32" t="inlineStr"/>
-      <c r="AN32" t="n">
+      <c r="AL32" t="n">
         <v>3</v>
       </c>
-      <c r="AO32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ32" t="inlineStr">
-        <is>
-          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
-        </is>
-      </c>
+      <c r="AM32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>רחל דהן - רופאה רחל דהן - רופאה דלג לתוכן ראשי - מקש קיצור 2 (לחץ Enter) דף הבית - מקש קיצור 1 (לחץ Enter) דלג לתפריט ראשי - מקש קיצור 5 (לחץ Enter) דלג לתיבת חיפוש - מקש קיצור 4 (לחץ Enter) צור קשר - מקש קיצור 9 (לחץ Enter) הצהרת נגישות - מקש קיצור 0 (לחץ Enter) סגור עזרה ראשונה נפשית - בהתנדבות אודות והצטרפות טיפול נפשי מוזל טיפול נפשי בתל אביב מטפלים בהסדר קופת חולים פנויים לקבלת מטופלים חדשים טיפול זוגי טיפול התנהגותי קוגניטיבי - CBT הדרכת הורים טיפול נפשי לילדים אבחון פסיכולוגי לילדים פסיכולוגית בתל אביב פסיכולוגים כניסה רישום צרו קשר חיפוש × × אימייל (דוא"ל) סיסמא שכחת את הסיסמה? הקלידו אימייל ולחצו כאן כניסה אני מסכימ.ה להצטרף לרשימת התפוצה לקבלת עדכונים ומידע שיווקי זכור אותי רישום משתמש חדש ביטול פסיכולוגיה עברית ראשי השער שלי תיבת מסרים כרטיס הביקור שלי הגדרות חשבון אודות פסיכולוגיה עברית שאלות נפוצות יציאה מאמרים המאמרים שלי הגשת טקסט לפרסום נבחרי העורכת אספרגר טיפולי המרה סקס טוב דיו רגשות חינוך מיני תסמונת טורט ניכור הורי רשימות קריאה הכותבים קטגוריות מאמרים מאמרים לפי נושאים ניוזלטר בלוג</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr"/>
       <c r="AR32" t="n">
         <v>1</v>
       </c>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>אופיר אלמסי</t>
+          <t>אוהד חורי</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>ofiral@bgu.ac.il</t>
+          <t>ohadho@clalit.org.il</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -5776,17 +5776,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>بحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان אופיר אלמסי ד"ר אופיר אלמסי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ofiral@bgu.ac.il Cookies Settings</t>
+          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>"אופיר אלמסי"</t>
+          <t>"אוהד חורי" יילוד site:clalit.co.il</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -5803,36 +5803,36 @@
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-09-04T13:52:28.665114+00:00</t>
+          <t>2026-09-09T23:21:42.073181+00:00</t>
         </is>
       </c>
       <c r="W33" t="n">
+        <v>8</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA33" t="n">
         <v>2</v>
       </c>
-      <c r="X33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1</v>
-      </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/ofiral/", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/almasi-o.aspx", "https://www.bgu.ac.il/ar/people/ofiral/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx", "https://www.doctorita.co.il/experts/94233", "https://www.ha-makom.co.il/author/vhdcvry/", "https://foody.co.il/author/ohad/", "https://knowmore.co.il/doctors/אוהד-חורי-2/", "https://stage.ha-makom.co.il/author/vhdcvry/", "https://www.facebook.com/YoldotBeilinson/videos/%D7%9E%D7%94-%D7%96%D7%95-%D7%9C%D7%99%D7%93%D7%AA-vbac-%D7%A9%D7%9B%D7%95%D7%9C%D7%9F-%D7%9E%D7%93%D7%91%D7%A8%D7%95%D7%AA-%D7%A2%D7%9C%D7%99%D7%94-%D7%A2%D7%95%D7%A9%D7%99%D7%9D-%D7%9C%D7%9B%D7%9F-%D7%A1%D7%93%D7%A8-%D7%91%D7%9E%D7%95%D7%A9%D7%92%D7%99%D7%9D-%D7%A2%D7%9D-%D7%93%D7%A8-%D7%90%D7%95%D7%94%D7%93-%D7%97%D7%95%D7%A8%D7%99-%D7%A9%D7%9B%D7%90%D7%9F-%D7%9B%D7%93%D7%99/1754039901764363/"]</t>
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>4.337439849460605e+17</v>
+        <v>1.301247395137931e+18</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5843,18 +5843,26 @@
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr"/>
       <c r="AJ33" t="inlineStr"/>
       <c r="AK33" t="inlineStr"/>
-      <c r="AL33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM33" t="inlineStr"/>
-      <c r="AN33" t="inlineStr"/>
-      <c r="AO33" t="inlineStr"/>
+      <c r="AL33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
+        </is>
+      </c>
       <c r="AP33" t="inlineStr"/>
       <c r="AQ33" t="inlineStr"/>
       <c r="AR33" t="n">
@@ -5884,7 +5892,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>אורנה רייכמן</t>
+          <t>אופיר אלמסי</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5915,7 +5923,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>oreich@szmc.org.il</t>
+          <t>ofiral@bgu.ac.il</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -5928,7 +5936,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
+          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -5938,12 +5946,12 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t xml:space="preserve">אזור אישי רופאים בשערי צדק ד"ר אורנה  רייכמן מנהלת יולדות א' Dr. Orna  Reichman התמחות: גינקולוגיה ויילוד תת התמחות: מחלות שפירות של העריה והלדן הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית משרד 02-6666708 משרד: 02-6666708 oreich@szmc.org.il oreich@szmc.org.il לימודים והכשרה תואר ראשון במדעי החיים באוניברסיטה העברית בירושלים בהצטיינות - 1993 לימודי הרפואה בבית ספר לרפואה של האוניברסיטה העברית הדסה - 1999 ההתמחות במיילדות וגניקולוגיה במרכז </t>
+          <t>بحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان אופיר אלמסי ד"ר אופיר אלמסי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ofiral@bgu.ac.il Cookies Settings</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>"אורנה רייכמן"</t>
+          <t>"אופיר אלמסי"</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -5965,36 +5973,36 @@
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-09-04T13:56:16.031154+00:00</t>
+          <t>2026-09-04T13:52:28.665114+00:00</t>
         </is>
       </c>
       <c r="W34" t="n">
         <v>2</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AA34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>["https://www.infomed.co.il/experts/149541/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A8%D7%99%D7%99%D7%9B%D7%9E%D7%9F-%D7%90%D7%95%D7%A8%D7%A0%D7%94/", "https://docsrated.com/doctors/אורנה-רייכמן", "https://www.doctorita.co.il/experts/95406", "https://drtor.co.il/doctor/23937", "https://drtor.co.il/cdn-cgi/l/email-protection#8cefe3e2f8edeff8cce8fef8e3fea2efe3a2e5e0", "https://www.beok.co.il/doctors/Doctors-1340/", "https://www.szmc.org.il/doctors/reichman-orna/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://drtor.co.il/cdn-cgi/l/email-protection#3b5854554f5a584f7b5f494f5449155854155257"]</t>
+          <t>["https://www.bgu.ac.il/people/ofiral/", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/almasi-o.aspx", "https://www.bgu.ac.il/ar/people/ofiral/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>4.337439849460605e+17</v>
+        <v>1.301231954838182e+18</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -6005,19 +6013,19 @@
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
+          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr"/>
       <c r="AJ34" t="inlineStr"/>
       <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL34" t="inlineStr"/>
       <c r="AM34" t="inlineStr"/>
       <c r="AN34" t="inlineStr"/>
       <c r="AO34" t="inlineStr"/>
-      <c r="AP34" t="inlineStr"/>
+      <c r="AP34" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ34" t="inlineStr"/>
       <c r="AR34" t="n">
         <v>1</v>
@@ -6046,7 +6054,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ארנון סמואלוב</t>
+          <t>אורנה רייכמן</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -6077,7 +6085,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>smuelof@szmc.org.il</t>
+          <t>oreich@szmc.org.il</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -6090,7 +6098,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
+          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -6100,12 +6108,12 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>ופ' ארנון  סמואלוב רופא בכיר Prof. Arnon  Samueloff התמחות: גינקולוגיה ויילוד תת התמחות: מיילדות וסיבוכי הריון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 02-6666656 מחלקה: 02-6666656 smuelof@szmc.org.il smuelof@szmc.org.il נסיון מקצועי התמחות ברפואת האם והעובר, סן אנטוניו, ארה"ב רופא בכיר, מחלקת נשים ויולדות, המרכז הרפואי הדסה מנהל, מרפאת היריון בסיכון, קופת חולים לאומית מנהל, מרפאת סוכרת, קופת חולים</t>
+          <t xml:space="preserve">אזור אישי רופאים בשערי צדק ד"ר אורנה  רייכמן מנהלת יולדות א' Dr. Orna  Reichman התמחות: גינקולוגיה ויילוד תת התמחות: מחלות שפירות של העריה והלדן הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית משרד 02-6666708 משרד: 02-6666708 oreich@szmc.org.il oreich@szmc.org.il לימודים והכשרה תואר ראשון במדעי החיים באוניברסיטה העברית בירושלים בהצטיינות - 1993 לימודי הרפואה בבית ספר לרפואה של האוניברסיטה העברית הדסה - 1999 ההתמחות במיילדות וגניקולוגיה במרכז </t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>"ארנון סמואלוב"</t>
+          <t>"אורנה רייכמן"</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -6127,36 +6135,36 @@
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-09-04T14:35:26.198949+00:00</t>
+          <t>2026-09-04T13:56:16.031154+00:00</t>
         </is>
       </c>
       <c r="W35" t="n">
         <v>2</v>
       </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>["https://docsrated.com/doctors/ארנון-סמואלוב", "https://www.infomed.co.il/experts/93587/", "https://www.doctorita.co.il/experts/47319", "https://www.beok.co.il/doctors/Doctors-116451/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A1%D7%9E%D7%95%D7%90%D7%9C%D7%95%D7%91-%D7%90%D7%A8%D7%A0%D7%95%D7%9F/", "https://www.szmc.org.il/doctors/samueloff-arnon/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
+          <t>["https://www.infomed.co.il/experts/149541/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A8%D7%99%D7%99%D7%9B%D7%9E%D7%9F-%D7%90%D7%95%D7%A8%D7%A0%D7%94/", "https://docsrated.com/doctors/אורנה-רייכמן", "https://www.doctorita.co.il/experts/95406", "https://drtor.co.il/doctor/23937", "https://drtor.co.il/cdn-cgi/l/email-protection#8cefe3e2f8edeff8cce8fef8e3fea2efe3a2e5e0", "https://www.beok.co.il/doctors/Doctors-1340/", "https://www.szmc.org.il/doctors/reichman-orna/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://drtor.co.il/cdn-cgi/l/email-protection#3b5854554f5a584f7b5f494f5449155854155257"]</t>
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>4.337439849460605e+17</v>
+        <v>1.301231954838182e+18</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6167,19 +6175,19 @@
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
+          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr"/>
       <c r="AJ35" t="inlineStr"/>
       <c r="AK35" t="inlineStr"/>
-      <c r="AL35" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL35" t="inlineStr"/>
       <c r="AM35" t="inlineStr"/>
       <c r="AN35" t="inlineStr"/>
       <c r="AO35" t="inlineStr"/>
-      <c r="AP35" t="inlineStr"/>
+      <c r="AP35" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ35" t="inlineStr"/>
       <c r="AR35" t="n">
         <v>1</v>
@@ -6208,7 +6216,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>גלי פריאנטה</t>
+          <t>ארנון סמואלוב</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6239,7 +6247,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>galipa@bgu.ac.il</t>
+          <t>smuelof@szmc.org.il</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -6252,7 +6260,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
+          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -6262,12 +6270,12 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>ث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان גלי פריאנטה פרופ' גלי פריאנטה Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section galipa@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0001-6484-3769 Orcid Number Cookies Settings</t>
+          <t>ופ' ארנון  סמואלוב רופא בכיר Prof. Arnon  Samueloff התמחות: גינקולוגיה ויילוד תת התמחות: מיילדות וסיבוכי הריון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 02-6666656 מחלקה: 02-6666656 smuelof@szmc.org.il smuelof@szmc.org.il נסיון מקצועי התמחות ברפואת האם והעובר, סן אנטוניו, ארה"ב רופא בכיר, מחלקת נשים ויולדות, המרכז הרפואי הדסה מנהל, מרפאת היריון בסיכון, קופת חולים לאומית מנהל, מרפאת סוכרת, קופת חולים</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>"גלי פריאנטה"</t>
+          <t>"ארנון סמואלוב"</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -6289,36 +6297,36 @@
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-09-03T23:09:10.396904+00:00</t>
+          <t>2026-09-04T14:35:26.198949+00:00</t>
         </is>
       </c>
       <c r="W36" t="n">
         <v>2</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
         <v>6</v>
       </c>
       <c r="Z36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/galipa/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-%D7%92%D7%9C%D7%99/", "https://medpage.co.il/doctors/%D7%92%D7%9C%D7%99-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-25448/", "https://www.doctorita.co.il/experts/131973", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/pariente-g.aspx", "https://www.bgu.ac.il/ar/people/galipa/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://docsrated.com/doctors/ארנון-סמואלוב", "https://www.infomed.co.il/experts/93587/", "https://www.doctorita.co.il/experts/47319", "https://www.beok.co.il/doctors/Doctors-116451/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A1%D7%9E%D7%95%D7%90%D7%9C%D7%95%D7%91-%D7%90%D7%A8%D7%A0%D7%95%D7%9F/", "https://www.szmc.org.il/doctors/samueloff-arnon/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>4.336067241913308e+17</v>
+        <v>1.301231954838182e+18</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6329,19 +6337,19 @@
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
+          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr"/>
       <c r="AJ36" t="inlineStr"/>
       <c r="AK36" t="inlineStr"/>
-      <c r="AL36" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL36" t="inlineStr"/>
       <c r="AM36" t="inlineStr"/>
       <c r="AN36" t="inlineStr"/>
       <c r="AO36" t="inlineStr"/>
-      <c r="AP36" t="inlineStr"/>
+      <c r="AP36" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ36" t="inlineStr"/>
       <c r="AR36" t="n">
         <v>1</v>
@@ -6370,7 +6378,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ד"ר ברוך יואב</t>
+          <t>גלי פריאנטה</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6390,18 +6398,18 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>ima</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>yoavb@tlvmc.gov.il</t>
+          <t>galipa@bgu.ac.il</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -6414,7 +6422,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
+          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -6424,12 +6432,12 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>י לאורוגינקולוגיה ורצפת אגן שטחי התעניינות ועיסוק מיוחדים ניתוחים וגינאליים וזעיר פולשניים לצניחת אברי האגן טיפול תרופתי וכירורגי לדליפת שתן מרפאת ערייה וצוואר הרחם אבחון וטיפול בקונדילומות ונגעים טרום ממאירים יצירת קשר yoavb@tlvmc.gov.il יחידות רפואיות אורוגינקולוגיה ורצפת האגן רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות נעים להכיר, ​ד"ר יואב ברוך איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציונ</t>
+          <t>ث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان גלי פריאנטה פרופ' גלי פריאנטה Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section galipa@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0001-6484-3769 Orcid Number Cookies Settings</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>"ברוך יואב"</t>
+          <t>"גלי פריאנטה"</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -6446,25 +6454,25 @@
         <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-09-05T00:14:33.719515+00:00</t>
+          <t>2026-09-03T23:09:10.396904+00:00</t>
         </is>
       </c>
       <c r="W37" t="n">
         <v>2</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
         <v>6</v>
       </c>
       <c r="Z37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA37" t="n">
         <v>1</v>
@@ -6476,11 +6484,11 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345", "https://soundcloud.com/wx8fnfybplpt", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A-%D7%91%D7%A8%D7%95%D7%9A/pfbid02DHSfATmK3MDpizZrgGTLc9ZAvZHXUsR9pSCjhd6pmWqSMFvq1BwehNeHCARNitMol/", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/pfbid02BMPnQXQYXt6vzctmybagMUp3nWACPxhE1LqhYeJYs1fVgXWA6B1cK2Z9VpRJ8cJRl/", "https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/", "https://pubmed.ncbi.nlm.nih.gov/?term=yoav+baruch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000546", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/61559143005435/", "https://www.infomed.co.il/experts/151203/", "https://www.yoavbaruch.com/", "https://www.yoavbaruch.com/about-6", "https://theindex.co.il/phone/ברוך-יואב-0777573393/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000504"]</t>
+          <t>["https://www.bgu.ac.il/people/galipa/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-%D7%92%D7%9C%D7%99/", "https://medpage.co.il/doctors/%D7%92%D7%9C%D7%99-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-25448/", "https://www.doctorita.co.il/experts/131973", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/pariente-g.aspx", "https://www.bgu.ac.il/ar/people/galipa/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>5.007882380340662e+17</v>
+        <v>1.300820172573992e+18</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6491,19 +6499,19 @@
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
+          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr"/>
       <c r="AJ37" t="inlineStr"/>
       <c r="AK37" t="inlineStr"/>
-      <c r="AL37" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL37" t="inlineStr"/>
       <c r="AM37" t="inlineStr"/>
       <c r="AN37" t="inlineStr"/>
       <c r="AO37" t="inlineStr"/>
-      <c r="AP37" t="inlineStr"/>
+      <c r="AP37" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ37" t="inlineStr"/>
       <c r="AR37" t="n">
         <v>1</v>
@@ -6532,7 +6540,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ד"ר צוקר נפתלי</t>
+          <t>ד"ר ברוך יואב</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6552,7 +6560,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -6563,7 +6571,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>drnzuker@arad-medical.co.il</t>
+          <t>yoavb@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -6576,7 +6584,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://www.arad-medical.co.il/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -6586,12 +6594,12 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t xml:space="preserve"> בי"ח אסף הרופא, עבר השתלמות מעמיקה בכירורגיה גניקולוגית ואנדסקופית. כמוכן, גניקולוג בכיר בקופות החולים מכבי ולאומית. קרא עוד עלינו « לפרטים נוספים ולקביעת תור השאר פרטים ונחזור אליך בהקדם! ☎ 077-8037837 | 077-9966036 ✉ drnzuker@arad-medical.co.il שם מלא: מייל: טלפון: שלח © ד"ר נפתלי צוקר — כל הזכויות שמורות אתר זה נבנה ועוצב ע"י קידום פלוס - בניית אתרים</t>
+          <t>י לאורוגינקולוגיה ורצפת אגן שטחי התעניינות ועיסוק מיוחדים ניתוחים וגינאליים וזעיר פולשניים לצניחת אברי האגן טיפול תרופתי וכירורגי לדליפת שתן מרפאת ערייה וצוואר הרחם אבחון וטיפול בקונדילומות ונגעים טרום ממאירים יצירת קשר yoavb@tlvmc.gov.il יחידות רפואיות אורוגינקולוגיה ורצפת האגן רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות נעים להכיר, ​ד"ר יואב ברוך איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציונ</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>"צוקר נפתלי"</t>
+          <t>"ברוך יואב"</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -6608,25 +6616,25 @@
         <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-09-03T20:26:24.789692+00:00</t>
+          <t>2026-09-05T00:14:33.719515+00:00</t>
         </is>
       </c>
       <c r="W38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X38" t="n">
         <v>1</v>
       </c>
       <c r="Y38" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z38" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA38" t="n">
         <v>1</v>
@@ -6638,11 +6646,11 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=JM/xPUEkhEzRgBuX3T9AYqhAJkFmVBaeb30sdIDAjgJqc6t/hlXwF9+305eagC9MR2dwestiB5JmwYwMLOCteQ==", "https://doctors.assuta.co.il/doctor/naftaly-zuker-15805", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=AsbND281GonWNafC65Z5in+5Uof0vMwxuFwCtAAhKp6HNUz+Imt4aFWEpjB1dVuW0TI9YD98xqlKyretPdEuvw==", "https://www.arad-medical.co.il/", "http://www.kidumplus.co.il/", "https://www.arad-medical.co.il/contact", "https://www.arad-medical.co.il/about-us", "https://www.doctorim.co.il/s/doctor-21560/דר-נפתלי-צוקר/מומחה-יילוד-וגניקולוגיה", "https://www.infomed.co.il/experts/83793/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345", "https://soundcloud.com/wx8fnfybplpt", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A-%D7%91%D7%A8%D7%95%D7%9A/pfbid02DHSfATmK3MDpizZrgGTLc9ZAvZHXUsR9pSCjhd6pmWqSMFvq1BwehNeHCARNitMol/", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/pfbid02BMPnQXQYXt6vzctmybagMUp3nWACPxhE1LqhYeJYs1fVgXWA6B1cK2Z9VpRJ8cJRl/", "https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/", "https://pubmed.ncbi.nlm.nih.gov/?term=yoav+baruch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000546", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/61559143005435/", "https://www.infomed.co.il/experts/151203/", "https://www.yoavbaruch.com/", "https://www.yoavbaruch.com/about-6", "https://theindex.co.il/phone/ברוך-יואב-0777573393/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000504"]</t>
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>5.336698143893302e+17</v>
+        <v>1.502364714102199e+18</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6653,19 +6661,19 @@
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>https://www.arad-medical.co.il/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr"/>
       <c r="AJ38" t="inlineStr"/>
       <c r="AK38" t="inlineStr"/>
-      <c r="AL38" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL38" t="inlineStr"/>
       <c r="AM38" t="inlineStr"/>
       <c r="AN38" t="inlineStr"/>
       <c r="AO38" t="inlineStr"/>
-      <c r="AP38" t="inlineStr"/>
+      <c r="AP38" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ38" t="inlineStr"/>
       <c r="AR38" t="n">
         <v>1</v>
@@ -6694,7 +6702,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ד"ר רטן גלעד</t>
+          <t>ד"ר צוקר נפתלי</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6714,7 +6722,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -6725,7 +6733,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>giladr@tlvmc.gov.il</t>
+          <t>drnzuker@arad-medical.co.il</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -6738,7 +6746,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
+          <t>https://www.arad-medical.co.il/</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -6748,12 +6756,12 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t xml:space="preserve">ח "ליס" ליולדות ונשים איכילוב צוות איכילוב גלעד רטן בדיקת היסטרוסקופיה - ד"ר גלעד רטן | ליס, איכילוב ד"ר גלעד רטן על תסמונת אשרמן, סטטוסקופ ערוץ 13 פרק 18 | פרופ' יריב יוגב ופרופ' גלעד רטן | בדיקת היסטרוסקופיה יצירת קשר giladr@tlvmc.gov.il יחידות רפואיות היסטרוסקופיה אבחנתית / טיפולית רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א </t>
+          <t xml:space="preserve"> בי"ח אסף הרופא, עבר השתלמות מעמיקה בכירורגיה גניקולוגית ואנדסקופית. כמוכן, גניקולוג בכיר בקופות החולים מכבי ולאומית. קרא עוד עלינו « לפרטים נוספים ולקביעת תור השאר פרטים ונחזור אליך בהקדם! ☎ 077-8037837 | 077-9966036 ✉ drnzuker@arad-medical.co.il שם מלא: מייל: טלפון: שלח © ד"ר נפתלי צוקר — כל הזכויות שמורות אתר זה נבנה ועוצב ע"י קידום פלוס - בניית אתרים</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>"רטן גלעד"</t>
+          <t>"צוקר נפתלי"</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -6775,14 +6783,14 @@
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-09-03T21:08:14.761438+00:00</t>
+          <t>2026-09-03T20:26:24.789692+00:00</t>
         </is>
       </c>
       <c r="W39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y39" t="n">
         <v>4</v>
@@ -6800,11 +6808,11 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F/", "https://dr-gilad.infomed.co.il/", "https://www.facebook.com/TLVMDC/posts/%D7%95%D7%95%D7%90%D7%95-%D7%9E%D7%AA%D7%A8%D7%92%D7%A9%D7%99%D7%9D-%D7%9C%D7%94%D7%9B%D7%99%D7%A8-%D7%9C%D7%9B%D7%9D-%D7%90%D7%AA-%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F-%D7%9E%D7%95%D7%9E%D7%97%D7%94-%D7%91%D7%9B%D7%99%D7%A8-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%A8%D7%A4%D7%95%D7%90%D7%99-tlv_medical_center/1344912312574270/", "https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=JM/xPUEkhEzRgBuX3T9AYqhAJkFmVBaeb30sdIDAjgJqc6t/hlXwF9+305eagC9MR2dwestiB5JmwYwMLOCteQ==", "https://doctors.assuta.co.il/doctor/naftaly-zuker-15805", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=AsbND281GonWNafC65Z5in+5Uof0vMwxuFwCtAAhKp6HNUz+Imt4aFWEpjB1dVuW0TI9YD98xqlKyretPdEuvw==", "https://www.arad-medical.co.il/", "http://www.kidumplus.co.il/", "https://www.arad-medical.co.il/contact", "https://www.arad-medical.co.il/about-us", "https://www.doctorim.co.il/s/doctor-21560/דר-נפתלי-צוקר/מומחה-יילוד-וגניקולוגיה", "https://www.infomed.co.il/experts/83793/"]</t>
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>4.336067241913308e+17</v>
+        <v>1.601009443167991e+18</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6815,19 +6823,19 @@
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
+          <t>https://www.arad-medical.co.il/</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr"/>
       <c r="AJ39" t="inlineStr"/>
       <c r="AK39" t="inlineStr"/>
-      <c r="AL39" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL39" t="inlineStr"/>
       <c r="AM39" t="inlineStr"/>
       <c r="AN39" t="inlineStr"/>
       <c r="AO39" t="inlineStr"/>
-      <c r="AP39" t="inlineStr"/>
+      <c r="AP39" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ39" t="inlineStr"/>
       <c r="AR39" t="n">
         <v>1</v>
@@ -6856,7 +6864,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>דנה ברבינג-גולדשטיין</t>
+          <t>ד"ר רטן גלעד</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6876,18 +6884,18 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>ima</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>danabr2@clalit.org.il</t>
+          <t>giladr@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -6900,7 +6908,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -6910,17 +6918,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>ד"ר דנה ברבינג גולדשטיין | מרכז רפואי רבין ד"ר דנה ברבינג גולדשטיין מיילדות וגינקולוגיה, גנטיקה רפואית שם: ד"ר דנה ברבינג גולדשטיין דוא"ל: danabr2@clalit.org.il יחידה: מכון רפאל רקנאטי לגנטיקה</t>
+          <t xml:space="preserve">ח "ליס" ליולדות ונשים איכילוב צוות איכילוב גלעד רטן בדיקת היסטרוסקופיה - ד"ר גלעד רטן | ליס, איכילוב ד"ר גלעד רטן על תסמונת אשרמן, סטטוסקופ ערוץ 13 פרק 18 | פרופ' יריב יוגב ופרופ' גלעד רטן | בדיקת היסטרוסקופיה יצירת קשר giladr@tlvmc.gov.il יחידות רפואיות היסטרוסקופיה אבחנתית / טיפולית רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א </t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>"דנה ברבינג גולדשטיין" יילוד site:clalit.co.il</t>
+          <t>"רטן גלעד"</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>search_snippet</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -6937,36 +6945,36 @@
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-09-08T13:48:01.035843+00:00</t>
+          <t>2026-09-03T21:08:14.761438+00:00</t>
         </is>
       </c>
       <c r="W40" t="n">
+        <v>2</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
         <v>4</v>
       </c>
-      <c r="X40" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1</v>
-      </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA40" t="n">
         <v>1</v>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>ddgs:yahoo+ddgs:bing</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F/", "https://dr-gilad.infomed.co.il/", "https://www.facebook.com/TLVMDC/posts/%D7%95%D7%95%D7%90%D7%95-%D7%9E%D7%AA%D7%A8%D7%92%D7%A9%D7%99%D7%9D-%D7%9C%D7%94%D7%9B%D7%99%D7%A8-%D7%9C%D7%9B%D7%9D-%D7%90%D7%AA-%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F-%D7%9E%D7%95%D7%9E%D7%97%D7%94-%D7%91%D7%9B%D7%99%D7%A8-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%A8%D7%A4%D7%95%D7%90%D7%99-tlv_medical_center/1344912312574270/", "https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>4.337491317124723e+17</v>
+        <v>1.300820172573992e+18</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6977,19 +6985,19 @@
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr"/>
       <c r="AJ40" t="inlineStr"/>
       <c r="AK40" t="inlineStr"/>
-      <c r="AL40" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL40" t="inlineStr"/>
       <c r="AM40" t="inlineStr"/>
       <c r="AN40" t="inlineStr"/>
       <c r="AO40" t="inlineStr"/>
-      <c r="AP40" t="inlineStr"/>
+      <c r="AP40" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ40" t="inlineStr"/>
       <c r="AR40" t="n">
         <v>1</v>
@@ -7018,7 +7026,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>יעל שולמן</t>
+          <t>דנה ברבינג-גולדשטיין</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -7049,7 +7057,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>yaelshu@tlvmc.gov.il</t>
+          <t>danabr2@clalit.org.il</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -7062,7 +7070,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -7072,17 +7080,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>3zgt8o8y2e /search-result/ /api/as/v1/engines/ פתח חיפוש עוד ... זימון תורים אזור אישי כניסה לאיזור האישי AI צ'אט ד"ר יעל שולמן רופאה בכירה במחלקת נשים, ביה"ח 'ליס' ליולדות ונשים איכילוב צוות איכילוב יעל שולמן יצירת קשר yaelshu@tlvmc.gov.il יחידות רפואיות אשפוז נשים - מחלקה רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך ב</t>
+          <t>ד"ר דנה ברבינג גולדשטיין | מרכז רפואי רבין ד"ר דנה ברבינג גולדשטיין מיילדות וגינקולוגיה, גנטיקה רפואית שם: ד"ר דנה ברבינג גולדשטיין דוא"ל: danabr2@clalit.org.il יחידה: מכון רפאל רקנאטי לגנטיקה</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>"יעל שולמן"</t>
+          <t>"דנה ברבינג גולדשטיין" יילוד site:clalit.co.il</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -7099,36 +7107,36 @@
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-09-04T17:01:07.432235+00:00</t>
+          <t>2026-09-08T13:48:01.035843+00:00</t>
         </is>
       </c>
       <c r="W41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>["https://www.agmon-law.co.il/team-member/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/people/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/pfbid02D3uDhLBFvfdSCJScu9afsXcVu6ZWEqNA4AsJgJH4om5Y5hNBNGbDUq3Xyg3nad9hl/", "https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx"]</t>
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>4.115077426798385e+17</v>
+        <v>1.301247395137417e+18</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7139,19 +7147,19 @@
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr"/>
       <c r="AJ41" t="inlineStr"/>
       <c r="AK41" t="inlineStr"/>
-      <c r="AL41" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL41" t="inlineStr"/>
       <c r="AM41" t="inlineStr"/>
       <c r="AN41" t="inlineStr"/>
       <c r="AO41" t="inlineStr"/>
-      <c r="AP41" t="inlineStr"/>
+      <c r="AP41" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ41" t="inlineStr"/>
       <c r="AR41" t="n">
         <v>1</v>
@@ -7180,7 +7188,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ישי לוין</t>
+          <t>יעל שולמן</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7211,7 +7219,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>ishail@tlvmc.gov.il</t>
+          <t>yaelshu@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -7224,7 +7232,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -7234,12 +7242,12 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>ריוזיס כנס אונליין אנדומטריאוזיס 2025 | פרופ' יריב יוגב ופרופ' ישי לוין מניעה וגילוי מוקדם של מחלות נשים | ערוץ 10 המכון לפריון - כירורגיה של הפריון | ליס פרופ' ישי לוין על כאבי מחזור חזקים , ערוץ 13, סטטוסקופ יצירת קשר ishail@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה אשפוז נשים - מחלקה אנדומטריוזיס - מרכז רב תחומי המרכז לבריאות האשה-מרפאות מומחים הפלות חוזרות - טיפול בכשל הריוני רופאים בכירים בליס-יולדות ונשים יצירת קשר יחיד</t>
+          <t>3zgt8o8y2e /search-result/ /api/as/v1/engines/ פתח חיפוש עוד ... זימון תורים אזור אישי כניסה לאיזור האישי AI צ'אט ד"ר יעל שולמן רופאה בכירה במחלקת נשים, ביה"ח 'ליס' ליולדות ונשים איכילוב צוות איכילוב יעל שולמן יצירת קשר yaelshu@tlvmc.gov.il יחידות רפואיות אשפוז נשים - מחלקה רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך ב</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>"ישי לוין"</t>
+          <t>"יעל שולמן"</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -7261,7 +7269,7 @@
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-09-04T17:20:48.855691+00:00</t>
+          <t>2026-09-04T17:01:07.432235+00:00</t>
         </is>
       </c>
       <c r="W42" t="n">
@@ -7271,10 +7279,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -7286,11 +7294,11 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>["https://www.ishai-levin.com/", "https://www.ishai-levin.com/about", "https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/", "https://pubmed.ncbi.nlm.nih.gov/?term=Levin%2c%20Ishai%5bFull%20Author%20Name%5d%20OR%20Ishai%2c%20Levin%5bFull%20Author%20Name%5d&amp;cmd=DetailsSearch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.agmon-law.co.il/team-member/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/people/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/pfbid02D3uDhLBFvfdSCJScu9afsXcVu6ZWEqNA4AsJgJH4om5Y5hNBNGbDUq3Xyg3nad9hl/", "https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>4.115077426798385e+17</v>
+        <v>1.234523228039515e+18</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7301,19 +7309,19 @@
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr"/>
       <c r="AJ42" t="inlineStr"/>
       <c r="AK42" t="inlineStr"/>
-      <c r="AL42" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL42" t="inlineStr"/>
       <c r="AM42" t="inlineStr"/>
       <c r="AN42" t="inlineStr"/>
       <c r="AO42" t="inlineStr"/>
-      <c r="AP42" t="inlineStr"/>
+      <c r="AP42" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ42" t="inlineStr"/>
       <c r="AR42" t="n">
         <v>1</v>
@@ -7342,7 +7350,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>לירן הירש</t>
+          <t>ישי לוין</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7373,7 +7381,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>liranh@tlvmc.gov.il</t>
+          <t>ishail@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -7386,7 +7394,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -7396,12 +7404,12 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>צועיים החברה הישראלית לרפואת האם והעובר החוג הישראלי למיילדות וגינקולוגיה לידה נדירה - תאומים ברחם נפרד פרק 19 | פרופ' יריב יוגב ופרופ' לירן הירש | תאומים פרק 9 | פרופ' יריב יוגב ופרופ' לירן הירש| הריון בסיכון יצירת קשר liranh@tlvmc.gov.il יחידות רפואיות המחלקה לרפואת האם והעובר מניעת לידה מוקדמת - מרפאה מעקב הריונות תאומים רופאים בכירים בליס-יולדות ונשים היריון ולידה יצירת קשר יחידות רפואיות היריון של 1 למיליון עם פרופ' לירן הירש איכיל</t>
+          <t>ריוזיס כנס אונליין אנדומטריאוזיס 2025 | פרופ' יריב יוגב ופרופ' ישי לוין מניעה וגילוי מוקדם של מחלות נשים | ערוץ 10 המכון לפריון - כירורגיה של הפריון | ליס פרופ' ישי לוין על כאבי מחזור חזקים , ערוץ 13, סטטוסקופ יצירת קשר ishail@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה אשפוז נשים - מחלקה אנדומטריוזיס - מרכז רב תחומי המרכז לבריאות האשה-מרפאות מומחים הפלות חוזרות - טיפול בכשל הריוני רופאים בכירים בליס-יולדות ונשים יצירת קשר יחיד</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>"לירן הירש"</t>
+          <t>"ישי לוין"</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -7423,7 +7431,7 @@
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-09-04T17:39:56.947224+00:00</t>
+          <t>2026-09-04T17:20:48.855691+00:00</t>
         </is>
       </c>
       <c r="W43" t="n">
@@ -7448,11 +7456,11 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>["https://www.profhiersch.com/", "https://www.profhiersch.com/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/", "https://pubmed.ncbi.nlm.nih.gov/?term=HIERSCH+L&amp;sort=date", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.ishai-levin.com/", "https://www.ishai-levin.com/about", "https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/", "https://pubmed.ncbi.nlm.nih.gov/?term=Levin%2c%20Ishai%5bFull%20Author%20Name%5d%20OR%20Ishai%2c%20Levin%5bFull%20Author%20Name%5d&amp;cmd=DetailsSearch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>4.115077426798385e+17</v>
+        <v>1.234523228039515e+18</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7463,19 +7471,19 @@
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr"/>
       <c r="AJ43" t="inlineStr"/>
       <c r="AK43" t="inlineStr"/>
-      <c r="AL43" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL43" t="inlineStr"/>
       <c r="AM43" t="inlineStr"/>
       <c r="AN43" t="inlineStr"/>
       <c r="AO43" t="inlineStr"/>
-      <c r="AP43" t="inlineStr"/>
+      <c r="AP43" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ43" t="inlineStr"/>
       <c r="AR43" t="n">
         <v>1</v>
@@ -7504,7 +7512,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>נועה גוהר פורטנוי</t>
+          <t>לירן הירש</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7535,7 +7543,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>noago@post.bgu.ac.il</t>
+          <t>liranh@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -7548,7 +7556,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/noago/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -7558,12 +7566,12 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان נועה גוהר פורטנוי נועה גוהר פורטנוי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section noago@post.bgu.ac.il Cookies Settings</t>
+          <t>צועיים החברה הישראלית לרפואת האם והעובר החוג הישראלי למיילדות וגינקולוגיה לידה נדירה - תאומים ברחם נפרד פרק 19 | פרופ' יריב יוגב ופרופ' לירן הירש | תאומים פרק 9 | פרופ' יריב יוגב ופרופ' לירן הירש| הריון בסיכון יצירת קשר liranh@tlvmc.gov.il יחידות רפואיות המחלקה לרפואת האם והעובר מניעת לידה מוקדמת - מרפאה מעקב הריונות תאומים רופאים בכירים בליס-יולדות ונשים היריון ולידה יצירת קשר יחידות רפואיות היריון של 1 למיליון עם פרופ' לירן הירש איכיל</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>"נועה גוהר פורטנוי" יילוד</t>
+          <t>"לירן הירש"</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -7585,14 +7593,14 @@
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-09-08T14:13:12.580343+00:00</t>
+          <t>2026-09-04T17:39:56.947224+00:00</t>
         </is>
       </c>
       <c r="W44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
         <v>2</v>
@@ -7610,11 +7618,11 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>["https://www.doctorita.co.il/experts/126297", "https://www.bgu.ac.il/ar/people/noago/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.profhiersch.com/", "https://www.profhiersch.com/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/", "https://pubmed.ncbi.nlm.nih.gov/?term=HIERSCH+L&amp;sort=date", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>4.015386079358828e+17</v>
+        <v>1.234523228039515e+18</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7625,19 +7633,19 @@
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/noago/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr"/>
       <c r="AJ44" t="inlineStr"/>
       <c r="AK44" t="inlineStr"/>
-      <c r="AL44" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL44" t="inlineStr"/>
       <c r="AM44" t="inlineStr"/>
       <c r="AN44" t="inlineStr"/>
       <c r="AO44" t="inlineStr"/>
-      <c r="AP44" t="inlineStr"/>
+      <c r="AP44" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ44" t="inlineStr"/>
       <c r="AR44" t="n">
         <v>1</v>
@@ -7666,7 +7674,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>עדי יהודה ווינטראוב</t>
+          <t>נועה גוהר פורטנוי</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7697,7 +7705,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>adiyehud@bgu.ac.il</t>
+          <t>noago@post.bgu.ac.il</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -7710,7 +7718,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
+          <t>https://www.bgu.ac.il/ar/people/noago/</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -7720,12 +7728,12 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>رئيسية جامعة أنشي سيجل في جوريان עדי יהודה ווינטראוב פרופ' עדי יהודה ווינטראוב Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section adiyehud@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0002-4239-8665 Orcid Number Cookies Settings</t>
+          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان נועה גוהר פורטנוי נועה גוהר פורטנוי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section noago@post.bgu.ac.il Cookies Settings</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>"עדי יהודה ווינטראוב"</t>
+          <t>"נועה גוהר פורטנוי" יילוד</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -7742,41 +7750,41 @@
         <v>1</v>
       </c>
       <c r="T45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-09-04T19:20:10.182518+00:00</t>
+          <t>2026-09-08T14:13:12.580343+00:00</t>
         </is>
       </c>
       <c r="W45" t="n">
+        <v>4</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y45" t="n">
         <v>2</v>
       </c>
-      <c r="X45" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>5</v>
-      </c>
       <c r="Z45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/adiyehud/", "https://www.bgu.ac.il/researcher/adi-weintraub/", "https://www.beok.co.il/doctors/Doctors-136810/", "https://cris.bgu.ac.il/en/publications/%D7%94%D7%A1%D7%99%D7%9B%D7%95%D7%9F-%D7%9C%D7%A1%D7%99%D7%91%D7%95%D7%9B%D7%99-%D7%94%D7%99%D7%A8%D7%99%D7%95%D7%9F-%D7%91%D7%A0%D7%A9%D7%99%D7%9D-%D7%A2%D7%9D-%D7%90%D7%A0%D7%93%D7%95%D7%9E%D7%98%D7%A8%D7%99%D7%95%D7%96%D7%99%D7%A1/", "https://www.bgu.ac.il/ar/people/adiyehud/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.doctorita.co.il/experts/126297", "https://www.bgu.ac.il/ar/people/noago/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>4.015334611694755e+17</v>
+        <v>1.204615823807648e+18</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7787,19 +7795,19 @@
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
+          <t>https://www.bgu.ac.il/ar/people/noago/</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr"/>
       <c r="AJ45" t="inlineStr"/>
       <c r="AK45" t="inlineStr"/>
-      <c r="AL45" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL45" t="inlineStr"/>
       <c r="AM45" t="inlineStr"/>
       <c r="AN45" t="inlineStr"/>
       <c r="AO45" t="inlineStr"/>
-      <c r="AP45" t="inlineStr"/>
+      <c r="AP45" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ45" t="inlineStr"/>
       <c r="AR45" t="n">
         <v>1</v>
@@ -7828,7 +7836,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>עמרי זמשטין</t>
+          <t>עדי יהודה ווינטראוב</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7859,7 +7867,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>omrizam@post.bgu.ac.il</t>
+          <t>adiyehud@bgu.ac.il</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -7872,7 +7880,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
+          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -7882,12 +7890,12 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>ريد البحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان עמרי זמשטין עמרי זמשטין Departments אקדמי לא פעיל הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section omrizam@post.bgu.ac.il Cookies Settings</t>
+          <t>رئيسية جامعة أنشي سيجل في جوريان עדי יהודה ווינטראוב פרופ' עדי יהודה ווינטראוב Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section adiyehud@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0002-4239-8665 Orcid Number Cookies Settings</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>"עמרי זמשטין"</t>
+          <t>"עדי יהודה ווינטראוב"</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -7909,7 +7917,7 @@
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-09-04T19:35:09.971397+00:00</t>
+          <t>2026-09-04T19:20:10.182518+00:00</t>
         </is>
       </c>
       <c r="W46" t="n">
@@ -7919,26 +7927,26 @@
         <v>1</v>
       </c>
       <c r="Y46" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/ar/people/omrizam/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.bgu.ac.il/people/adiyehud/", "https://www.bgu.ac.il/researcher/adi-weintraub/", "https://www.beok.co.il/doctors/Doctors-136810/", "https://cris.bgu.ac.il/en/publications/%D7%94%D7%A1%D7%99%D7%9B%D7%95%D7%9F-%D7%9C%D7%A1%D7%99%D7%91%D7%95%D7%9B%D7%99-%D7%94%D7%99%D7%A8%D7%99%D7%95%D7%9F-%D7%91%D7%A0%D7%A9%D7%99%D7%9D-%D7%A2%D7%9D-%D7%90%D7%A0%D7%93%D7%95%D7%9E%D7%98%D7%A8%D7%99%D7%95%D7%96%D7%99%D7%A1/", "https://www.bgu.ac.il/ar/people/adiyehud/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>4.015334611694755e+17</v>
+        <v>1.204600383508426e+18</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7949,19 +7957,19 @@
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
+          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr"/>
       <c r="AJ46" t="inlineStr"/>
       <c r="AK46" t="inlineStr"/>
-      <c r="AL46" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL46" t="inlineStr"/>
       <c r="AM46" t="inlineStr"/>
       <c r="AN46" t="inlineStr"/>
       <c r="AO46" t="inlineStr"/>
-      <c r="AP46" t="inlineStr"/>
+      <c r="AP46" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ46" t="inlineStr"/>
       <c r="AR46" t="n">
         <v>1</v>
@@ -7990,7 +7998,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>רויטל לינדר</t>
+          <t>עמרי זמשטין</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -8021,7 +8029,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>revital@drlinder.co.il</t>
+          <t>omrizam@post.bgu.ac.il</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -8034,7 +8042,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://www.drlinder.co.il/</t>
+          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -8044,12 +8052,12 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>בכירה ביחידה הגניקואונקולוגית , בית חולים רמב״ם, חיפה. 4/2014-4/2019 התמחות במיילדות וגניקולוגיה בית חולים רמב״ם,חיפה. לפרטים מלאים חוות דעת יש לך שאלה ? צרי קשר ד״ר רויטל לינדר צפצפה 2 (ישי סנטר) , רמת ישי 058-6918927​ revital@drlinder.co.il הצהרת נגישות © DR. Revital Linder. All rights Reserved , 2023</t>
+          <t>ريد البحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان עמרי זמשטין עמרי זמשטין Departments אקדמי לא פעיל הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section omrizam@post.bgu.ac.il Cookies Settings</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>"רויטל לינדר"</t>
+          <t>"עמרי זמשטין"</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -8066,41 +8074,41 @@
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-09-04T07:14:47.643108+00:00</t>
+          <t>2026-09-04T19:35:09.971397+00:00</t>
         </is>
       </c>
       <c r="W47" t="n">
         <v>2</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>["https://www.rambam.org.il/?catid=%7B9F8D1CC1-1F5C-46F1-A395-E19ED48FE2EE%7D&amp;itemid=%7B4B21BA59-AF68-46CA-9483-9639E61A75A8%7D", "https://www.rambam.org.il/about-rambam/", "https://www.rambam.org.il/about-rambam/careers/", "https://www.rambam.org.il/departmentsandclinics/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/urology/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/orthopedic/", "https://www.drlinder.co.il/"]</t>
+          <t>["https://www.bgu.ac.il/ar/people/omrizam/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>4.014877075845656e+17</v>
+        <v>1.204600383508426e+18</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -8111,19 +8119,19 @@
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>https://www.drlinder.co.il/</t>
+          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr"/>
       <c r="AJ47" t="inlineStr"/>
       <c r="AK47" t="inlineStr"/>
-      <c r="AL47" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL47" t="inlineStr"/>
       <c r="AM47" t="inlineStr"/>
       <c r="AN47" t="inlineStr"/>
       <c r="AO47" t="inlineStr"/>
-      <c r="AP47" t="inlineStr"/>
+      <c r="AP47" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ47" t="inlineStr"/>
       <c r="AR47" t="n">
         <v>1</v>
@@ -8152,7 +8160,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>רליקה הרשקוביץ</t>
+          <t>רויטל לינדר</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8183,7 +8191,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>ralikah@bgu.ac.il</t>
+          <t>revital@drlinder.co.il</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -8196,7 +8204,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
+          <t>https://www.drlinder.co.il/</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -8206,12 +8214,12 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان רליקה הרשקוביץ פרופ' רליקה הרשקוביץ Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ralikah@bgu.ac.il رابط ملف الأبحاث Cookies Settings</t>
+          <t>בכירה ביחידה הגניקואונקולוגית , בית חולים רמב״ם, חיפה. 4/2014-4/2019 התמחות במיילדות וגניקולוגיה בית חולים רמב״ם,חיפה. לפרטים מלאים חוות דעת יש לך שאלה ? צרי קשר ד״ר רויטל לינדר צפצפה 2 (ישי סנטר) , רמת ישי 058-6918927​ revital@drlinder.co.il הצהרת נגישות © DR. Revital Linder. All rights Reserved , 2023</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>"רליקה הרשקוביץ"</t>
+          <t>"רויטל לינדר"</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -8233,7 +8241,7 @@
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-09-04T07:56:40.372731+00:00</t>
+          <t>2026-09-04T07:14:47.643108+00:00</t>
         </is>
       </c>
       <c r="W48" t="n">
@@ -8243,26 +8251,26 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/ralikah/", "https://www.doctorita.co.il/experts/101245", "https://www.bgu.ac.il/ar/people/ralikah/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.rambam.org.il/?catid=%7B9F8D1CC1-1F5C-46F1-A395-E19ED48FE2EE%7D&amp;itemid=%7B4B21BA59-AF68-46CA-9483-9639E61A75A8%7D", "https://www.rambam.org.il/about-rambam/", "https://www.rambam.org.il/about-rambam/careers/", "https://www.rambam.org.il/departmentsandclinics/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/urology/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/orthopedic/", "https://www.drlinder.co.il/"]</t>
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>4.014877075845656e+17</v>
+        <v>1.204463122753697e+18</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8273,19 +8281,19 @@
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
+          <t>https://www.drlinder.co.il/</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr"/>
       <c r="AJ48" t="inlineStr"/>
       <c r="AK48" t="inlineStr"/>
-      <c r="AL48" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL48" t="inlineStr"/>
       <c r="AM48" t="inlineStr"/>
       <c r="AN48" t="inlineStr"/>
       <c r="AO48" t="inlineStr"/>
-      <c r="AP48" t="inlineStr"/>
+      <c r="AP48" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ48" t="inlineStr"/>
       <c r="AR48" t="n">
         <v>1</v>
@@ -8314,7 +8322,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>שקמה בר און</t>
+          <t>רליקה הרשקוביץ</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8345,7 +8353,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>shikmabo@tlvmc.gov.il</t>
+          <t>ralikah@bgu.ac.il</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -8358,7 +8366,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
+          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -8368,12 +8376,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>ת לאנדוסקופיה גינקולוגית שטחי התעניינות ועיסוק מיוחדים היסטרוסקופיה עם וללא הרדמה, היסטרוסקופיה ניתוחית ללא הרדמה בשיטת "see and treat" לפרוסקופיות פרק 14 | פרופ' יריב יוגב וד״ר שקמה בר און | מרכז בריאות האישה יצירת קשר shikmabo@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך בהתפתחות ביה"ח איכו</t>
+          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان רליקה הרשקוביץ פרופ' רליקה הרשקוביץ Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ralikah@bgu.ac.il رابط ملف الأبحاث Cookies Settings</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>"שקמה בר און"</t>
+          <t>"רליקה הרשקוביץ"</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -8395,7 +8403,7 @@
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-09-04T10:28:27.702590+00:00</t>
+          <t>2026-09-04T07:56:40.372731+00:00</t>
         </is>
       </c>
       <c r="W49" t="n">
@@ -8405,13 +8413,13 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
@@ -8420,11 +8428,11 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>["https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%A9%D7%A7%D7%9E%D7%94-%D7%91%D7%A8-%D7%90%D7%95%D7%9F/", "https://tlvmedical.com/doctors/דר-שקמה-בר-און/", "https://www.rofim.org.il/minisite/%D7%93%D7%A8_%D7%A9%D7%A7%D7%9E%D7%94_%D7%91%D7%A8_%D7%90%D7%95%D7%9F", "https://www.shidurit-ltd.co.il/", "https://www.rofim.org.il/about", "https://www.rofim.org.il/Contact", "https://www.rofim.org.il/specialityPage/%D7%9E%D7%A8%D7%9B%D7%96_%D7%A8%D7%A4%D7%95%D7%90%D7%99", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%9E%D7%92%D7%90%D7%A8", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%91%D7%99%D7%AA_%D7%92%D7%93%D7%99", "https://www.rofim.org.il/minisite/%D7%90%D7%99%D7%99_%D7%90%D7%9C_%D7%A7%D7%9C%D7%99%D7%A0%D7%99%D7%A7", "https://docsrated.com/doctors/שקמה-בר-און", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2FTLVMDC%2Fphotos%2F%25D7%25A2%25D7%2595%25D7%25A7%25D7%2591%25D7%2595%25D7%25AA-%25D7%2595%25D7%259E%25D7%2598%25D7%2595%25D7%25A4%25D7%259C%25D7%2595%25D7%25AA-%25D7%2590%25D7%25A0%25D7%2595-%25D7%25A9%25D7%259E%25D7%2597%25D7%2599%25D7%259D-%25D7%259C%25D7%2594%25D7%259B%25D7%2599%25D7%25A8-%25D7%259C%25D7%259B%25D7%259F-%25D7%2590%25D7%25AA-%25D7%2593%25D7%25A8-%25D7%25A9%25D7%25A7%25D7%259E%25D7%2594-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F%25D7%2593%25D7%25A8-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F-%25D7%2594%25D7%2599%25D7%2590-%25D7%259E%25D7%25A0%25D7%2594%25D7%259C%25D7%25AA-%25D7%2594%25D7%259E%25D7%25A8%25D7%259B%25D7%2596-%25D7%259C%2F1525276317871201%2F", "https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/", "https://www.ncbi.nlm.nih.gov/pubmed/?term=shikma+bar+on", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.bgu.ac.il/people/ralikah/", "https://www.doctorita.co.il/experts/101245", "https://www.bgu.ac.il/ar/people/ralikah/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>4.006641430561869e+17</v>
+        <v>1.204463122753697e+18</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8435,19 +8443,19 @@
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
+          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr"/>
       <c r="AJ49" t="inlineStr"/>
       <c r="AK49" t="inlineStr"/>
-      <c r="AL49" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL49" t="inlineStr"/>
       <c r="AM49" t="inlineStr"/>
       <c r="AN49" t="inlineStr"/>
       <c r="AO49" t="inlineStr"/>
-      <c r="AP49" t="inlineStr"/>
+      <c r="AP49" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ49" t="inlineStr"/>
       <c r="AR49" t="n">
         <v>1</v>
@@ -8476,7 +8484,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>שרית הלמן</t>
+          <t>שקמה בר און</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8507,7 +8515,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>hsarit@szmc.org.il</t>
+          <t>shikmabo@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -8520,7 +8528,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -8530,12 +8538,12 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t xml:space="preserve"> רופאים בשערי צדק ד"ר שרית  הלמן רופאה בכירה Dr. Sarit  Helman התמחות: גינקולוגיה ויילוד תת התמחות: הריון בסיכון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 026666656 מחלקה: 026666656 hsarit@szmc.org.il hsarit@szmc.org.il נסיון מקצועי Harvard T.H. Chan School of Public Health, Joslin Diabetes Center, Research intern under the supervision of Dr. Florence Brown and Dr. Tamarra James-Todd,     Type 1 Dia</t>
+          <t>ת לאנדוסקופיה גינקולוגית שטחי התעניינות ועיסוק מיוחדים היסטרוסקופיה עם וללא הרדמה, היסטרוסקופיה ניתוחית ללא הרדמה בשיטת "see and treat" לפרוסקופיות פרק 14 | פרופ' יריב יוגב וד״ר שקמה בר און | מרכז בריאות האישה יצירת קשר shikmabo@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך בהתפתחות ביה"ח איכו</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>"שרית הלמן"</t>
+          <t>"שקמה בר און"</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -8552,12 +8560,12 @@
         <v>1</v>
       </c>
       <c r="T50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-09-05T00:06:28.339643+00:00</t>
+          <t>2026-09-04T10:28:27.702590+00:00</t>
         </is>
       </c>
       <c r="W50" t="n">
@@ -8570,10 +8578,10 @@
         <v>6</v>
       </c>
       <c r="Z50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
@@ -8582,11 +8590,11 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>["https://www.hamichlol.org.il/שרה_(שרית)_הלמן", "https://behevrat-haadam.org/ram-sara-helman/", "https://behevrat-haadam.org/tag/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/IsrAnthro/posts/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F-%D7%A1%D7%95%D7%A6%D7%99%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA%D7%90%D7%A0%D7%97%D7%A0%D7%95-%D7%A9%D7%9E%D7%97%D7%99%D7%9D-%D7%9C%D7%A9%D7%AA%D7%A3-%D7%91%D7%91%D7%97%D7%91%D7%A8%D7%AA-%D7%94%D7%90%D7%93%D7%9D-%D7%90%D7%AA-%D7%93%D7%91%D7%A8%D7%99%D7%95-%D7%A9%D7%9C-%D7%90%D7%95%D7%A8%D7%99-%D7%A8%D7%9D-%D7%A4%D7%A8%D7%95%D7%A4-%D7%90%D7%9E%D7%A8%D7%99%D7%98%D7%95/4246861638775714/", "https://www.doctorita.co.il/experts/137665", "https://www.szmc.org.il/doctors/helman-sarit/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
+          <t>["https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%A9%D7%A7%D7%9E%D7%94-%D7%91%D7%A8-%D7%90%D7%95%D7%9F/", "https://tlvmedical.com/doctors/דר-שקמה-בר-און/", "https://www.rofim.org.il/minisite/%D7%93%D7%A8_%D7%A9%D7%A7%D7%9E%D7%94_%D7%91%D7%A8_%D7%90%D7%95%D7%9F", "https://www.shidurit-ltd.co.il/", "https://www.rofim.org.il/about", "https://www.rofim.org.il/Contact", "https://www.rofim.org.il/specialityPage/%D7%9E%D7%A8%D7%9B%D7%96_%D7%A8%D7%A4%D7%95%D7%90%D7%99", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%9E%D7%92%D7%90%D7%A8", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%91%D7%99%D7%AA_%D7%92%D7%93%D7%99", "https://www.rofim.org.il/minisite/%D7%90%D7%99%D7%99_%D7%90%D7%9C_%D7%A7%D7%9C%D7%99%D7%A0%D7%99%D7%A7", "https://docsrated.com/doctors/שקמה-בר-און", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2FTLVMDC%2Fphotos%2F%25D7%25A2%25D7%2595%25D7%25A7%25D7%2591%25D7%2595%25D7%25AA-%25D7%2595%25D7%259E%25D7%2598%25D7%2595%25D7%25A4%25D7%259C%25D7%2595%25D7%25AA-%25D7%2590%25D7%25A0%25D7%2595-%25D7%25A9%25D7%259E%25D7%2597%25D7%2599%25D7%259D-%25D7%259C%25D7%2594%25D7%259B%25D7%2599%25D7%25A8-%25D7%259C%25D7%259B%25D7%259F-%25D7%2590%25D7%25AA-%25D7%2593%25D7%25A8-%25D7%25A9%25D7%25A7%25D7%259E%25D7%2594-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F%25D7%2593%25D7%25A8-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F-%25D7%2594%25D7%2599%25D7%2590-%25D7%259E%25D7%25A0%25D7%2594%25D7%259C%25D7%25AA-%25D7%2594%25D7%259E%25D7%25A8%25D7%259B%25D7%2596-%25D7%259C%2F1525276317871201%2F", "https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/", "https://www.ncbi.nlm.nih.gov/pubmed/?term=shikma+bar+on", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>4.006793942511569e+17</v>
+        <v>1.201992429168561e+18</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8597,19 +8605,19 @@
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr"/>
       <c r="AJ50" t="inlineStr"/>
       <c r="AK50" t="inlineStr"/>
-      <c r="AL50" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL50" t="inlineStr"/>
       <c r="AM50" t="inlineStr"/>
       <c r="AN50" t="inlineStr"/>
       <c r="AO50" t="inlineStr"/>
-      <c r="AP50" t="inlineStr"/>
+      <c r="AP50" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ50" t="inlineStr"/>
       <c r="AR50" t="n">
         <v>1</v>
@@ -8638,7 +8646,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ד"ר ארבל אריאל</t>
+          <t>שרית הלמן</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8658,31 +8666,31 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>ima</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>info@eryaveladan.com</t>
+          <t>hsarit@szmc.org.il</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://www.eryaveladan.com/</t>
+          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -8692,12 +8700,12 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>החזיר את האיזון. קראי עוד השאירי פרטים ונחזור אלייך בהקדם שם מלא טלפון דוא״ל שליחה רופא נשים מומחה מחלות העריה והלדן ​ ד״ר אריאל ארבל לקביעת תור: 077-2311245 כתובת המרפאה: בית למומחים ברפואה - בורוכוב 54, גבעתיים דוא״ל: info@eryaveladan.com bottom of page</t>
+          <t xml:space="preserve"> רופאים בשערי צדק ד"ר שרית  הלמן רופאה בכירה Dr. Sarit  Helman התמחות: גינקולוגיה ויילוד תת התמחות: הריון בסיכון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 026666656 מחלקה: 026666656 hsarit@szmc.org.il hsarit@szmc.org.il נסיון מקצועי Harvard T.H. Chan School of Public Health, Joslin Diabetes Center, Research intern under the supervision of Dr. Florence Brown and Dr. Tamarra James-Todd,     Type 1 Dia</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>"ארבל אריאל"</t>
+          <t>"שרית הלמן"</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -8707,29 +8715,29 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>[{"email": "info@eryaveladan.com", "confidence": 88, "source_url": "https://www.eryaveladan.com/", "identity_url": "https://www.eryaveladan.com/", "evidence": "החזיר את האיזון. קראי עוד השאירי פרטים ונחזור אלייך בהקדם שם מלא טלפון דוא״ל שליחה רופא נשים מומחה מחלות העריה והלדן ​ ד״ר אריאל ארבל לקביעת תור: 077-2311245 כתובת המרפאה: בית למומחים ברפואה - בורוכוב 54, גבעתיים דוא״ל: info@eryaveladan.com bottom of page", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}, {"email": "office@b54.co.il", "confidence": 88, "source_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "identity_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "evidence": "ד\"ר אריאל ארבל - מרפאת מומחים B54, הבית למומחים ברפואה בגבעתיים דילוג לתוכן B54 03-757-8562 office@b54.co.il א׳-ה׳ 8:00-20:00 | ו׳ 08:00-13:00 Facebook-f Youtube Google דף הבית אודות B54 מי אנחנו שכונת בורוכוב מרכז Friendly הנהלת המרפאה שאלות נפוצות הרופאים שלנו קליניקה להשכרה מידע למטופל שאלות ותשובות הורדת טפ", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-09-03T20:23:48.175654+00:00</t>
+          <t>2026-09-05T00:06:28.339643+00:00</t>
         </is>
       </c>
       <c r="W51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X51" t="n">
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z51" t="n">
         <v>5</v>
@@ -8744,11 +8752,11 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598", "https://www.facebook.com/people/%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%90%D7%A8%D7%91%D7%9C/pfbid0NCmi7FZgUyu2EVV5mLJMpBfndXiDQPqseAxUny7KWHsDvucQScUiVnBeMef3ByStl/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%90%D7%A8%D7%91%D7%9C-%D7%90%D7%A8%D7%99%D7%90%D7%9C/", "https://www.eryaveladan.com/", "https://www.eryaveladan.com/%D7%90%D7%95%D7%93%D7%95%D7%AA-1", "https://www.b54.co.il/doctors/dr-arbel-ariel/", "https://www.medreviews.co.il/provider/dr-arbel-ariel", "https://www.b54.co.il/about/", "https://www.b54.co.il/about", "https://www.b54.co.il/about#borohov", "https://www.b54.co.il/about#Friendly", "https://www.b54.co.il/about#management", "https://www.b54.co.il/about#qa", "https://www.medreviews.co.il/provider/dr-arbel-ariel#contact-doctor-section", "https://www.medreviews.co.il/contact-us", "https://www.medreviews.co.il/about", "https://woman.mymc.co.il/doctors/dr-arielarbel/", "https://www.ima.org.il/DoctorsIndex/Default.aspx", "https://www.infomed.co.il/experts/145655/", "https://www.ami.org.il/blog/families/not-the-same-shirley"]</t>
+          <t>["https://www.hamichlol.org.il/שרה_(שרית)_הלמן", "https://behevrat-haadam.org/ram-sara-helman/", "https://behevrat-haadam.org/tag/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/IsrAnthro/posts/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F-%D7%A1%D7%95%D7%A6%D7%99%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA%D7%90%D7%A0%D7%97%D7%A0%D7%95-%D7%A9%D7%9E%D7%97%D7%99%D7%9D-%D7%9C%D7%A9%D7%AA%D7%A3-%D7%91%D7%91%D7%97%D7%91%D7%A8%D7%AA-%D7%94%D7%90%D7%93%D7%9D-%D7%90%D7%AA-%D7%93%D7%91%D7%A8%D7%99%D7%95-%D7%A9%D7%9C-%D7%90%D7%95%D7%A8%D7%99-%D7%A8%D7%9D-%D7%A4%D7%A8%D7%95%D7%A4-%D7%90%D7%9E%D7%A8%D7%99%D7%98%D7%95/4246861638775714/", "https://www.doctorita.co.il/experts/137665", "https://www.szmc.org.il/doctors/helman-sarit/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>5.336698143893302e+17</v>
+        <v>1.202038182753471e+18</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8759,22 +8767,22 @@
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>https://www.eryaveladan.com/</t>
+          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr"/>
       <c r="AJ51" t="inlineStr"/>
       <c r="AK51" t="inlineStr"/>
-      <c r="AL51" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL51" t="inlineStr"/>
       <c r="AM51" t="inlineStr"/>
       <c r="AN51" t="inlineStr"/>
       <c r="AO51" t="inlineStr"/>
-      <c r="AP51" t="inlineStr"/>
+      <c r="AP51" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ51" t="inlineStr"/>
       <c r="AR51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS51" t="b">
         <v>0</v>
@@ -8783,11 +8791,11 @@
         <v>1</v>
       </c>
       <c r="AU51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
+          <t>PERSON</t>
         </is>
       </c>
     </row>
@@ -8800,12 +8808,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>מאיה שרון וינר</t>
+          <t>דלית דרימן-מדינה</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -8831,20 +8839,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>clinic@drmayasharonweiner.com</t>
+          <t>dalit@drdreman.co.il</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://www.drmayasharonweiner.com/</t>
+          <t>https://www.drdreman.co.il/%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%9E%D7%98%D7%91%D7%95%D7%9C%D7%99%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -8854,17 +8862,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>אני איתך במסע הזה. הצעד הראשון שלך מתחיל כאן. ד"ר מאיה שרון-וינר רופאת נשים מומחית בפריון והפריה חוץ גופית מיילדות וגינקולוגיה לקביעת פגישה © 2026 כל הזכויות שמורות לד"ר מאיה שרון-וינר הברזל 9א', רמת החייל ווטסאפ למרפאה clinic@drmayasharonweiner.com פוריות האישה והגבר טיפולי פוריות הפריה חוץ גופית ו-PGD שימור פוריות פוריות לאחר סרטן ובנשאיות BRCA מעקב וליווי הריון גינקולוגיה כללית Menu Close אודות יצירת קשר מדיניות פרטיות הצהרת נגישות M</t>
+          <t>drdremandalit@gmail.com</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>"מאיה שרון וינר"</t>
+          <t>"דלית דרימן מדינה" רפואת משפחה (מרפאה OR "צור קשר" OR email OR מייל)</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>direct_mailto</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -8876,41 +8884,41 @@
         <v>1</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-09-04T17:43:40.101946+00:00</t>
+          <t>2026-09-10T18:44:56.180135+00:00</t>
         </is>
       </c>
       <c r="W52" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="X52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
         <v>7</v>
       </c>
       <c r="Z52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>["https://www.drmayasharonweiner.com/", "https://www.drmayasharonweiner.com/about", "https://www.drmayasharonweiner.com/contact", "https://www.medreviews.co.il/provider/dr-sharon-weiner-maya", "https://www.medreviews.co.il/provider/dr-sharon-weiner-maya/treatment", "https://www.doctorita.co.il/experts/119120", "https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr_maya_sharonweiner%2F&amp;is_from_rle", "https://docsrated.com/doctors/מאיה-שרון-וינר"]</t>
+          <t>["https://www.drdreman.co.il/מחלות-מטבוליות/", "https://www.drdreman.co.il/%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%9E%D7%98%D7%91%D7%95%D7%9C%D7%99%D7%95%D7%AA/", "https://www.drdreman.co.il/about/", "https://www.drdreman.co.il/contact/", "https://www.drdreman.co.il/", "https://www.doctorita.co.il/experts/52215", "https://www.drdreman.co.il/%D7%93%D7%A3-%D7%91%D7%99%D7%AA/", "https://www.other-medicine.co.il/author/dalitdrdreman-co-il/", "https://www.izi.co.il/site/6f2c026c8d", "https://www.infomed.co.il/experts/78145/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%93%D7%A8%D7%99%D7%9E%D7%9F-%D7%9E%D7%93%D7%99%D7%A0%D7%94-%D7%93%D7%9C%D7%99%D7%AA/", "https://www.findglocal.com/IL/Unknown/106988607393615/ד״ר-דלית-דרימן-רפואה-פונקציונלית-ואינטגרטיבית"]</t>
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>4.115077426798385e+17</v>
+        <v>1.234264146800576e+18</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8921,18 +8929,27 @@
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>https://www.drmayasharonweiner.com/</t>
+          <t>https://www.drdreman.co.il/%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%9E%D7%98%D7%91%D7%95%D7%9C%D7%99%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr"/>
       <c r="AJ52" t="inlineStr"/>
       <c r="AK52" t="inlineStr"/>
-      <c r="AL52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM52" t="inlineStr"/>
-      <c r="AN52" t="inlineStr"/>
-      <c r="AO52" t="inlineStr"/>
+      <c r="AL52" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM52" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN52" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>מחלות מטבוליות - ד"ר דלית דרימן-מדינה מחלות מטבוליות - ד"ר דלית דרימן-מדינה דלג לתוכן אודות כיצד נוכל לעזור במה אנחנו מטפלים מפגשים ועלויות שאלות ותשובות מאמרים סרטונים מהתקשורת צור קשר אודות כיצד נוכל לעזור במה אנחנו מטפלים מפגשים ועלויות שאלות ותשובות מאמרים סרטונים מהתקשורת צור קשר 0546033755 חיפוש חיפוש אודות כיצד נוכל לעזור במה אנחנו מטפלים מפגשים ועלויות שאלות ותשובות מאמרים סרטונים מהתקשורת צור קשר אודות כיצד נוכל לעזור במה אנחנו מטפלים מפגשים ועלויות שאלות ותשובות מאמרים סרטונים מהתקשורת צור קשר חיפוש חיפוש מחלות מטבוליות הפרעות מטבוליות, עודף משקל, סוכרת בחירות מזון גרועות, העדר מרכיבי מזון חיוניים, רעלנים, מתח נפשי, ודלקת כרונית גורמים לחוסר איזון מטבולי ולמחלות שמהוות את מרבית המחלות הכרוניות כיום. במה אנו מטפלים? מחלות לב יתר לחץ דם עודף משקל והשמנה תסמונת מטבולית סוכרת הפרעות בכולסטרול ושומני הדם איך זה עובד? אנחנו עורכים למטופלים שלנו בירור נרחב ע״י בדיקות מעבדה מתקדמות כולל בדיקות מיוחדות לשומני הדם שאינן מבוצעות באופן סטנדרטי בקופות החולים.
+בטיפול שלנו אנו מתבססים על המזון ומרכיבי התזונה ככלים הטיפוליים הרא</t>
+        </is>
+      </c>
       <c r="AP52" t="inlineStr"/>
       <c r="AQ52" t="inlineStr"/>
       <c r="AR52" t="n">
@@ -8962,7 +8979,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>מנחם נוימן</t>
+          <t>ד"ר ארבל אריאל</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8982,18 +8999,18 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>ima</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>hello@professorneuman.com</t>
+          <t>info@eryaveladan.com</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -9006,7 +9023,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://professorneuman.com/he/</t>
+          <t>https://www.eryaveladan.com/</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -9016,12 +9033,12 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>פרופ׳ מנחם נוימן — אורוגינקולוגיה ורפואת רצפת האגן מגדל סוזוקי, קומה 4, רח׳ יגאל אלון 82, תל אביב 054-644-2060 · hello@professorneuman.com ראשי מידע לרופאים מידע למטופלות מהתקשורת צרי קשר English פרופ׳ מנחם נוימן אורוגינקולוגיה ורפואת רצפת האגן צניחת איברי האגן ודליפת שתן הן מהתופעות השכיחות ביותר בקרב נשים — וגם מהניתנות ביותר לטי</t>
+          <t>החזיר את האיזון. קראי עוד השאירי פרטים ונחזור אלייך בהקדם שם מלא טלפון דוא״ל שליחה רופא נשים מומחה מחלות העריה והלדן ​ ד״ר אריאל ארבל לקביעת תור: 077-2311245 כתובת המרפאה: בית למומחים ברפואה - בורוכוב 54, גבעתיים דוא״ל: info@eryaveladan.com bottom of page</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>"מנחם נוימן"</t>
+          <t>"ארבל אריאל"</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -9031,11 +9048,11 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>[{"email": "info@raphaelhospitals.co.il", "confidence": 80, "source_url": "https://www.raphaelhospitals.co.il/en/international-department/about/", "identity_url": "https://www.raphaelhospitals.co.il/doctors/neuman-menahem/", "evidence": "info@raphaelhospitals.co.il", "matched_query": "\"מנחם נוימן\"", "extraction_method": "linked_mailto"}]</t>
+          <t>[{"email": "info@eryaveladan.com", "confidence": 88, "source_url": "https://www.eryaveladan.com/", "identity_url": "https://www.eryaveladan.com/", "evidence": "החזיר את האיזון. קראי עוד השאירי פרטים ונחזור אלייך בהקדם שם מלא טלפון דוא״ל שליחה רופא נשים מומחה מחלות העריה והלדן ​ ד״ר אריאל ארבל לקביעת תור: 077-2311245 כתובת המרפאה: בית למומחים ברפואה - בורוכוב 54, גבעתיים דוא״ל: info@eryaveladan.com bottom of page", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}, {"email": "office@b54.co.il", "confidence": 88, "source_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "identity_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "evidence": "ד\"ר אריאל ארבל - מרפאת מומחים B54, הבית למומחים ברפואה בגבעתיים דילוג לתוכן B54 03-757-8562 office@b54.co.il א׳-ה׳ 8:00-20:00 | ו׳ 08:00-13:00 Facebook-f Youtube Google דף הבית אודות B54 מי אנחנו שכונת בורוכוב מרכז Friendly הנהלת המרפאה שאלות נפוצות הרופאים שלנו קליניקה להשכרה מידע למטופל שאלות ותשובות הורדת טפ", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}]</t>
         </is>
       </c>
       <c r="S53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T53" t="n">
         <v>0</v>
@@ -9043,23 +9060,23 @@
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-09-04T18:20:49.705154+00:00</t>
+          <t>2026-09-03T20:23:48.175654+00:00</t>
         </is>
       </c>
       <c r="W53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X53" t="n">
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z53" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
@@ -9068,11 +9085,11 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>["https://professorneuman.com/", "https://professorneuman.com/he/", "https://professorneuman.com/he/contact", "https://professorneuman.com/en/contact", "https://www.facebook.com/public/%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/", "https://www.facebook.com/people/%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/pfbid0371mkxMbe96MNN5gS9XHB7KqrSyxJnXyG9AsLfdZV7j8RjCKyjm8cEEVgjSreLhY8l/", "https://chabadpedia.co.il/wiki/%D7%9E%D7%A0%D7%97%D7%9D_%D7%A0%D7%95%D7%99%D7%9E%D7%9F", "https://www.raphaelhospitals.co.il/doctors/neuman-menahem/", "https://www.raphaelhospitals.co.il/about/aboutus/", "https://www.raphaelhospitals.co.il/fields/endoscopic-unit/about/", "https://www.raphaelhospitals.co.il/fields/pain-clinic/about/", "https://www.raphaelhospitals.co.il/en/international-department/about/", "https://www.raphaelhospitals.co.il/fields/heart-catheterization-clinic/about/", "https://www.raphaelhospitals.co.il/en/about/aboutus/", "https://www.raphaelhospitals.co.il/en/contact/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598", "https://www.facebook.com/people/%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%90%D7%A8%D7%91%D7%9C/pfbid0NCmi7FZgUyu2EVV5mLJMpBfndXiDQPqseAxUny7KWHsDvucQScUiVnBeMef3ByStl/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%90%D7%A8%D7%91%D7%9C-%D7%90%D7%A8%D7%99%D7%90%D7%9C/", "https://www.eryaveladan.com/", "https://www.eryaveladan.com/%D7%90%D7%95%D7%93%D7%95%D7%AA-1", "https://www.b54.co.il/doctors/dr-arbel-ariel/", "https://www.medreviews.co.il/provider/dr-arbel-ariel", "https://www.b54.co.il/about/", "https://www.b54.co.il/about", "https://www.b54.co.il/about#borohov", "https://www.b54.co.il/about#Friendly", "https://www.b54.co.il/about#management", "https://www.b54.co.il/about#qa", "https://www.medreviews.co.il/provider/dr-arbel-ariel#contact-doctor-section", "https://www.medreviews.co.il/contact-us", "https://www.medreviews.co.il/about", "https://woman.mymc.co.il/doctors/dr-arielarbel/", "https://www.ima.org.il/DoctorsIndex/Default.aspx", "https://www.infomed.co.il/experts/145655/", "https://www.ami.org.il/blog/families/not-the-same-shirley"]</t>
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>4.115077426798385e+17</v>
+        <v>1.601009443167991e+18</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -9083,22 +9100,22 @@
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>https://professorneuman.com/he/</t>
+          <t>https://www.eryaveladan.com/</t>
         </is>
       </c>
       <c r="AI53" t="inlineStr"/>
       <c r="AJ53" t="inlineStr"/>
       <c r="AK53" t="inlineStr"/>
-      <c r="AL53" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL53" t="inlineStr"/>
       <c r="AM53" t="inlineStr"/>
       <c r="AN53" t="inlineStr"/>
       <c r="AO53" t="inlineStr"/>
-      <c r="AP53" t="inlineStr"/>
+      <c r="AP53" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ53" t="inlineStr"/>
       <c r="AR53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS53" t="b">
         <v>0</v>
@@ -9124,7 +9141,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>נעמה מימון</t>
+          <t>יעל כהן</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9155,7 +9172,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>office@medicaltop.co.il</t>
+          <t>office@elitemed.co.il</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -9168,7 +9185,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/</t>
+          <t>https://elitemed.co.il/doctors/dr-yael-cohen-hebrew/</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -9178,12 +9195,12 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t xml:space="preserve">ד"ר נעמה מימון: מומחית ברפואת נשים - MedicalTop Search Close Facebook 073-3310444 סנטר הגליל רחוב האגס 1, שער הרימון, קומה שניה. ראש פינה. office@medicaltop.co.il לקביעת תור דף הבית אודות תחומי פעילות הצוות שלנו יצירת קשר Menu דף הבית אודות תחומי פעילות הצוות שלנו יצירת קשר ד"ר נעמה מימון: מומחית ברפואת נשים דף הבית / רופאים / ד"ר נעמה מימון: מומחית ברפואת </t>
+          <t>ד"ר יעל כהן - elitemed.co.il דלג לתוכן Facebook Instagram Whatsapp Office@elitemed.co.il 073-321-4181 בית אודות רופאים שירותים רפואיים אולטרסאונד וביופסיות אוסטאופתיה אורולוגיה אורתופדיה אלרגיה ואימונולגיה אנדוקרינולוגיה סוכרת וירידה במשקל אסתטיקה אף אוזן גרון גינקולוגיה ובריאות האישה ג</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>"נעמה מימון"</t>
+          <t>"יעל כהן" יילוד</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -9205,65 +9222,73 @@
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-09-04T05:17:30.924388+00:00</t>
+          <t>2026-09-10T18:33:08.486465+00:00</t>
         </is>
       </c>
       <c r="W54" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="X54" t="n">
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Z54" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>["https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fn.mh.mymwn.2025%2F", "https://www.facebook.com/SNMaesthetic/services/", "https://www.doctorita.co.il/experts/152626", "https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/", "https://medicaltop.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://medicaltop.co.il/%D7%94%D7%A6%D7%95%D7%95%D7%AA-%D7%A9%D7%9C%D7%A0%D7%95/", "https://medicaltop.co.il/wp-content/uploads/2024/04/אודות.jpg"]</t>
+          <t>["https://elitemed.co.il/doctors/dr-yael-cohen-hebrew/", "https://elitemed.co.il/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%A4%D7%95%D7%90%D7%99-%D7%A4%D7%A8%D7%98%D7%99-%D7%91%D7%9E%D7%95%D7%93%D7%99%D7%A2%D7%99%D7%9F/", "https://elitemed.co.il/pain-clinic-modiin/", "https://elitemed.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://elitemed.co.il/%d7%90%d7%95%d6%b9%d7%93%d7%95%d6%b9%d7%aa/", "https://medpage.co.il/doctors/יעל-כהן-23202/", "https://medpage.co.il/doctors/%D7%99%D7%A2%D7%9C-%D7%9B%D7%94%D7%9F-23202/", "https://www.facebook.com/ichilovmedical/posts/תכירו-את-פרופ-יעל-כהןמנהלת-יחידת-המיאלומה-במערך-ההמטולוגי-של-איכילוב-ואחת-מהרופא/1288268913309017/", "https://www.facebook.com/ichilovmedical/videos/%D7%AA%D7%9B%D7%99%D7%A8%D7%95-%D7%90%D7%AA-%D7%A4%D7%A8%D7%95%D7%A4-%D7%99%D7%A2%D7%9C-%D7%9B%D7%94%D7%9F%D7%9E%D7%A0%D7%94%D7%9C%D7%AA-%D7%99%D7%97%D7%99%D7%93%D7%AA-%D7%94%D7%9E%D7%99%D7%90%D7%9C%D7%95%D7%9E%D7%94-%D7%91%D7%9E%D7%A2%D7%A8%D7%9A-%D7%94%D7%94%D7%9E%D7%98%D7%95%D7%9C%D7%95%D7%92%D7%99-%D7%A9%D7%9C-%D7%90%D7%99%D7%9B%D7%99%D7%9C%D7%95%D7%91-%D7%95%D7%90%D7%97%D7%AA-%D7%9E%D7%94%D7%A8%D7%95%D7%A4%D7%90/981973987039095/", "https://www.medico.co.il/doctors/פרופ-יעל-כהן/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%99%D7%A2%D7%9C-%D7%9B%D7%94%D7%9F/", "https://www.medico.co.il/doctors/", "https://www.medico.co.il/doctors/%d7%a4%d7%a8%d7%95%d7%a4-%d7%99%d7%a2%d7%9c-%d7%9b%d7%94%d7%9f/", "https://www.tasmc.org.il/doctorssearch/dr/cohen-yael/", "https://www.szmc.org.il/doctors/cohen-yael/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.vimed.co.il/users/0918fba4-bd6a-4310-ab8f-b51cab0b8f80", "https://www.meuhedet.co.il/poi/ParamedicalDoctors/000189680918100097000000000000_0", "https://www.medreviews.co.il/provider/dr-cohen-yael"]</t>
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>4.014877075989144e+17</v>
+        <v>1.234538668338751e+18</v>
       </c>
       <c r="AE54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/</t>
+          <t>https://elitemed.co.il/doctors/dr-yael-cohen-hebrew/</t>
         </is>
       </c>
       <c r="AI54" t="inlineStr"/>
       <c r="AJ54" t="inlineStr"/>
       <c r="AK54" t="inlineStr"/>
-      <c r="AL54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM54" t="inlineStr"/>
-      <c r="AN54" t="inlineStr"/>
-      <c r="AO54" t="inlineStr"/>
+      <c r="AL54" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM54" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN54" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>ד"ר יעל כהן - elitemed.co.il ד"ר יעל כהן - elitemed.co.il דלג לתוכן Facebook Instagram Whatsapp Office@elitemed.co.il 073-321-4181 בית אודות רופאים שירותים רפואיים אולטרסאונד וביופסיות אוסטאופתיה אורולוגיה אורתופדיה אלרגיה ואימונולגיה אנדוקרינולוגיה סוכרת וירידה במשקל אסתטיקה אף אוזן גרון גינקולוגיה ובריאות האישה גסטרואנטרולוגיה גֵרִיאַטרִיָה דרמטולגיה המטולוגיה כלי דם ורדיולוגיה פולשנית התמחויות טיפוליות ושיקומיות כירורגיה כירורגיה פלסטית מרפאת כאב נוירולוגיה, קשב וריכוז והתפתחות הילד נפרולוגיה ויתר לחץ דם סקירות מערכות ואקו לב עובר עיניים פודיאטריה כירורגית וכף רגל פולמונולוגיה ורפואת שינה פסיכיאטריה פרוקטולוגיה וכירורגיה קולורקטלית קרדיולוגיה ואלקטרופיזיולוגיה ראומטולוגיה רפואת ילדים מומחית רפואת ספורט ופיזיותרפיה רפואה תעסוקתית תזונה קלינית ודיאטה תור דחוף  24-48 שעות צור קשר השכרת קליניקה במודיעין שירות VIP שירותים מידע רפואי בית אודות רופאים שירותים רפואיים אולטרסאונד וביופסיות אוסטאופתיה אורולוגיה אורתופדיה אלרגיה ואימונולגיה אנדוקרינולוגיה סוכרת וירידה במשקל אסתטיקה אף אוזן גרון גינקולוגיה ובריאות האישה גס</t>
+        </is>
+      </c>
       <c r="AP54" t="inlineStr"/>
       <c r="AQ54" t="inlineStr"/>
       <c r="AR54" t="n">
         <v>1</v>
       </c>
       <c r="AS54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT54" t="b">
         <v>1</v>
@@ -9286,7 +9311,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>תמר גרין</t>
+          <t>מאיה שרון וינר</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9317,7 +9342,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>office@keshet-refua.co.il</t>
+          <t>clinic@drmayasharonweiner.com</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -9330,7 +9355,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://keshet-refua.co.il/doctors/dr-tamar-green/</t>
+          <t>https://www.drmayasharonweiner.com/</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -9340,17 +9365,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>פיזיותרפיה אסתטיקה פודקסטים קליניקות וססיות להשכרה צור קשר זימון תור ד"ר תמר גרין מומחית לגינקולוגיה ומיילדות מעקב הריון, סקירת הריון מוקדמת ומאוחרת, בדיקות אולטרסאונד אבחנתיות, גיל המעבר ובדיקות גינקולוגיות 073-3214111 office@keshet-refua.co.il לזימון תור &gt; תחומי מומחיות מעקב הריון בדיקות אולטרהסאונד אבחנתיות שקיפות עורפית סקירת מערכות מוקדמת ומאוחרת מעקבי גדילה הדמיית אגן והדמיה תלת מימדית של הרחם טיפולי גינקולוגיה פרטית התקנים תוך רח</t>
+          <t>אני איתך במסע הזה. הצעד הראשון שלך מתחיל כאן. ד"ר מאיה שרון-וינר רופאת נשים מומחית בפריון והפריה חוץ גופית מיילדות וגינקולוגיה לקביעת פגישה © 2026 כל הזכויות שמורות לד"ר מאיה שרון-וינר הברזל 9א', רמת החייל ווטסאפ למרפאה clinic@drmayasharonweiner.com פוריות האישה והגבר טיפולי פוריות הפריה חוץ גופית ו-PGD שימור פוריות פוריות לאחר סרטן ובנשאיות BRCA מעקב וליווי הריון גינקולוגיה כללית Menu Close אודות יצירת קשר מדיניות פרטיות הצהרת נגישות M</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>"תמר גרין"</t>
+          <t>"מאיה שרון וינר"</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>official_text</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -9362,41 +9387,41 @@
         <v>1</v>
       </c>
       <c r="T55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-09-05T00:09:39.798497+00:00</t>
+          <t>2026-09-04T17:43:40.101946+00:00</t>
         </is>
       </c>
       <c r="W55" t="n">
         <v>2</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y55" t="n">
         <v>7</v>
       </c>
       <c r="Z55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>["https://www.medreviews.co.il/provider/dr-green-tamar", "https://keshet-refua.co.il/doctors/dr-tamar-green/", "https://keshet-refua.co.il/about-us/", "https://keshet-refua.co.il/contact-us/", "https://keshet-refua.co.il/clinics-for-rent-sessional-clinics-for-rent/", "https://keshet-refua.co.il/about-us/#contact-keshet-medical-center", "https://keshet-refua.co.il/areas_of_expertise/child-psychology-clinic/", "https://keshet-refua.co.il/doctors/private-clinical-dietician-jerusalem/", "https://keshet-refua.co.il/contact-us/#contact-keshet-medical-center", "https://keshet-refua.co.il/clinics-for-rent-sessional-clinics-for-rent/#contact-keshet-medical-center", "https://keshet-refua.co.il/doctors/dr-tamar-green-private-gynecologist-in-jerusalem/", "https://wayzee.co.il/", "https://keshet-refua.co.il/treatments/menstrual-arrangement-before-the-wedding-private-womens-clinic-private-gynecologist/", "https://keshet-refua.co.il/areas_of_expertise/child-psychology-clinic/#contact-keshet-medical-center", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2F61558661827898%2F", "https://www.facebook.com/public/%D7%AA%D7%9E%D7%A8-%D7%92%D7%A8%D7%99%D7%9F/", "https://www.medreviews.co.il/provider/dr-green-tamar/treatment/gynecologist-clinic", "https://www.szmc.org.il/doctors/grin-tamar/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
+          <t>["https://www.drmayasharonweiner.com/", "https://www.drmayasharonweiner.com/about", "https://www.drmayasharonweiner.com/contact", "https://www.medreviews.co.il/provider/dr-sharon-weiner-maya", "https://www.medreviews.co.il/provider/dr-sharon-weiner-maya/treatment", "https://www.doctorita.co.il/experts/119120", "https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr_maya_sharonweiner%2F&amp;is_from_rle", "https://docsrated.com/doctors/מאיה-שרון-וינר"]</t>
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>4.006793942511569e+17</v>
+        <v>1.234523228039515e+18</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9407,19 +9432,19 @@
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>https://keshet-refua.co.il/doctors/dr-tamar-green/</t>
+          <t>https://www.drmayasharonweiner.com/</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr"/>
       <c r="AJ55" t="inlineStr"/>
       <c r="AK55" t="inlineStr"/>
-      <c r="AL55" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL55" t="inlineStr"/>
       <c r="AM55" t="inlineStr"/>
       <c r="AN55" t="inlineStr"/>
       <c r="AO55" t="inlineStr"/>
-      <c r="AP55" t="inlineStr"/>
+      <c r="AP55" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ55" t="inlineStr"/>
       <c r="AR55" t="n">
         <v>1</v>
@@ -9448,7 +9473,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>אבי צפריר</t>
+          <t>מנחם נוימן</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9479,7 +9504,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>ivfrec@szmc.org.il</t>
+          <t>hello@professorneuman.com</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -9488,11 +9513,11 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/tsafrir-avi/</t>
+          <t>https://professorneuman.com/he/</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -9502,12 +9527,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t xml:space="preserve">h عربيه Русский צרו קשר צרו קשר אזור אישי אזור אישי רופאים בשערי צדק ד"ר  אבי צפריר רופא בכיר Dr.  Avi Tsafrir התמחות: גינקולוגיה ויילוד תת התמחות: הפריה חוץ גופית תחומים נוספים: שימור פוריות פוריות הגבר פוריות האשה עוד ivfrec@szmc.org.il ivfrec@szmc.org.il נסיון מקצועי מומחה ביילוד ובגינקולוגיה משנת 2005 רופא בכיר להפריה חוץ גופית בשערי צדק משנת 2005 תפקידים ציבוריים חבר ועד האגודה הישראלית לחקר הפוריות משנת 2022 לימודים והכשרה פקולטה </t>
+          <t>פרופ׳ מנחם נוימן — אורוגינקולוגיה ורפואת רצפת האגן מגדל סוזוקי, קומה 4, רח׳ יגאל אלון 82, תל אביב 054-644-2060 · hello@professorneuman.com ראשי מידע לרופאים מידע למטופלות מהתקשורת צרי קשר English פרופ׳ מנחם נוימן אורוגינקולוגיה ורפואת רצפת האגן צניחת איברי האגן ודליפת שתן הן מהתופעות השכיחות ביותר בקרב נשים — וגם מהניתנות ביותר לטי</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>"אבי צפריר"</t>
+          <t>"מנחם נוימן"</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -9517,23 +9542,23 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "info@raphaelhospitals.co.il", "confidence": 80, "source_url": "https://www.raphaelhospitals.co.il/en/international-department/about/", "identity_url": "https://www.raphaelhospitals.co.il/doctors/neuman-menahem/", "evidence": "info@raphaelhospitals.co.il", "matched_query": "\"מנחם נוימן\"", "extraction_method": "linked_mailto"}]</t>
         </is>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-09-03T20:26:52.799327+00:00</t>
+          <t>2026-09-04T18:20:49.705154+00:00</t>
         </is>
       </c>
       <c r="W56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X56" t="n">
         <v>0</v>
@@ -9542,10 +9567,10 @@
         <v>7</v>
       </c>
       <c r="Z56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
@@ -9554,14 +9579,14 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>["https://www.infomed.co.il/experts/73913/", "https://he.hadassah.org.il/doctor/dr-avi-tsafrir-gaadaabqaa2aaoiag4adaabyaa======/", "https://www.doctors.co.il/expert/obstetrics-and-gynecologists/80043972/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fbyzpryr%2F", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A6%D7%A4%D7%A8%D7%99%D7%A8-%D7%90%D7%91%D7%99/", "https://drtor.co.il/doctor/3910", "https://www.szmc.org.il/doctors/tsafrir-avi/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.clalit.co.il/he/sefersherut/pages/doctordetails.aspx", "https://docsrated.com/doctors/אבי-צפריר", "https://www.doctorita.co.il/experts/44804"]</t>
+          <t>["https://professorneuman.com/", "https://professorneuman.com/he/", "https://professorneuman.com/he/contact", "https://professorneuman.com/en/contact", "https://www.facebook.com/public/%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/", "https://www.facebook.com/people/%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/pfbid0371mkxMbe96MNN5gS9XHB7KqrSyxJnXyG9AsLfdZV7j8RjCKyjm8cEEVgjSreLhY8l/", "https://chabadpedia.co.il/wiki/%D7%9E%D7%A0%D7%97%D7%9D_%D7%A0%D7%95%D7%99%D7%9E%D7%9F", "https://www.raphaelhospitals.co.il/doctors/neuman-menahem/", "https://www.raphaelhospitals.co.il/about/aboutus/", "https://www.raphaelhospitals.co.il/fields/endoscopic-unit/about/", "https://www.raphaelhospitals.co.il/fields/pain-clinic/about/", "https://www.raphaelhospitals.co.il/en/international-department/about/", "https://www.raphaelhospitals.co.il/fields/heart-catheterization-clinic/about/", "https://www.raphaelhospitals.co.il/en/about/aboutus/", "https://www.raphaelhospitals.co.il/en/contact/"]</t>
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>5.336698144036791e+17</v>
+        <v>1.234523228039515e+18</v>
       </c>
       <c r="AE56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF56" t="n">
         <v>0</v>
@@ -9569,25 +9594,25 @@
       <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/tsafrir-avi/</t>
+          <t>https://professorneuman.com/he/</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr"/>
       <c r="AJ56" t="inlineStr"/>
       <c r="AK56" t="inlineStr"/>
-      <c r="AL56" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL56" t="inlineStr"/>
       <c r="AM56" t="inlineStr"/>
       <c r="AN56" t="inlineStr"/>
       <c r="AO56" t="inlineStr"/>
-      <c r="AP56" t="inlineStr"/>
+      <c r="AP56" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ56" t="inlineStr"/>
       <c r="AR56" t="n">
         <v>1</v>
       </c>
       <c r="AS56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT56" t="b">
         <v>1</v>
@@ -9610,17 +9635,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>אירינה דורפמן אלמוג</t>
+          <t>נעמה מימון</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>family_doctor</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -9641,20 +9666,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>dr.irenadorfman@gmail.com</t>
+          <t>office@medicaltop.co.il</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
+          <t>https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -9664,12 +9689,12 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>מוג אירינה כרטיס עסק: ד"ר דורפמן אלמוג אירינה » תחום פעילות: בריאות וספורט » רופא » תאור העסק: רופאת משפחה עצמאית קופת חולים לאומית. » איש קשר: אירנה דורפמן » טלפונים: טלפון: 077-7997456 נייד: 054-4616457 » אתר: » מייל: dr.irenadorfman@gmail.com » כתובת: בן גוריון 123 יהוד, מיקוד: 56209 כלים מחשבונים לעסקים מדריכי ניהול עסק, הקמת עסק נושאי האתר הנהלת חשבונות הפקת חשבוניות חשבונית אלקטרונית ניהול לקוחות שותפים עסקיים אילת סיטי - מדריך הע</t>
+          <t xml:space="preserve">ד"ר נעמה מימון: מומחית ברפואת נשים - MedicalTop Search Close Facebook 073-3310444 סנטר הגליל רחוב האגס 1, שער הרימון, קומה שניה. ראש פינה. office@medicaltop.co.il לקביעת תור דף הבית אודות תחומי פעילות הצוות שלנו יצירת קשר Menu דף הבית אודות תחומי פעילות הצוות שלנו יצירת קשר ד"ר נעמה מימון: מומחית ברפואת נשים דף הבית / רופאים / ד"ר נעמה מימון: מומחית ברפואת </t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>"אירינה דורפמן אלמוג"</t>
+          <t>"נעמה מימון"</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -9679,51 +9704,51 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>[{"email": "info@flex.co.il", "confidence": 80, "source_url": "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "identity_url": "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "evidence": "info@flex.co.il", "matched_query": "\"אירינה דורפמן אלמוג\"", "extraction_method": "linked_mailto"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-09-04T19:17:26.299485+00:00</t>
+          <t>2026-09-04T05:17:30.924388+00:00</t>
         </is>
       </c>
       <c r="W57" t="n">
+        <v>4</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>["https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fn.mh.mymwn.2025%2F", "https://www.facebook.com/SNMaesthetic/services/", "https://www.doctorita.co.il/experts/152626", "https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/", "https://medicaltop.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://medicaltop.co.il/%D7%94%D7%A6%D7%95%D7%95%D7%AA-%D7%A9%D7%9C%D7%A0%D7%95/", "https://medicaltop.co.il/wp-content/uploads/2024/04/אודות.jpg"]</t>
+        </is>
+      </c>
+      <c r="AD57" t="n">
+        <v>1.204463122796743e+18</v>
+      </c>
+      <c r="AE57" t="n">
         <v>2</v>
-      </c>
-      <c r="X57" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>ddgs:bing</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>["https://www.dunsguide.co.il/C7195b21475cb11a3e5b86def04a3e20c_רופאים/דורפמן_אלמוג_אירינה/", "https://medpage.co.il/doctors/%D7%90%D7%99%D7%A8%D7%A0%D7%94-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-20871/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94/", "https://www.beok.co.il/doctors/Doctors-129241/", "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "https://www.flex.co.il/100_General/005_GeneralPages/006_About.aspx", "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "https://www.flex.co.il/100_General/900_DifferentStuff/900_ForTheCommunity.aspx"]</t>
-        </is>
-      </c>
-      <c r="AD57" t="n">
-        <v>4.336524777762407e+17</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>1</v>
       </c>
       <c r="AF57" t="n">
         <v>0</v>
@@ -9731,35 +9756,35 @@
       <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
+          <t>https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr"/>
       <c r="AJ57" t="inlineStr"/>
       <c r="AK57" t="inlineStr"/>
-      <c r="AL57" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL57" t="inlineStr"/>
       <c r="AM57" t="inlineStr"/>
       <c r="AN57" t="inlineStr"/>
       <c r="AO57" t="inlineStr"/>
-      <c r="AP57" t="inlineStr"/>
+      <c r="AP57" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ57" t="inlineStr"/>
       <c r="AR57" t="n">
         <v>1</v>
       </c>
       <c r="AS57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT57" t="b">
         <v>1</v>
       </c>
       <c r="AU57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>PERSON</t>
+          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
       </c>
     </row>
@@ -9772,17 +9797,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>אלון שלב</t>
+          <t>תמר גרין</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>family_doctor</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -9803,20 +9828,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>alonshalev31@gmail.com</t>
+          <t>office@keshet-refua.co.il</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://pain.coi.co.il/</t>
+          <t>https://keshet-refua.co.il/doctors/dr-tamar-green/</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -9826,17 +9851,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>הודעה לבעלי האתר תקופת הניסיון הסתיימה, יש ליצור מנוי דרך ממשק ניהול האתר. האתר נכנס לרשימת המחיקה ויימחק בקרוב לחץ כאן אם אינך זוכר את כתובת ממשק ניהול האתר שלך. דר אלון שלב - רופא כאב טלפון: 054-6221105 מייל: alonshalev31@gmail.com כתובת: ילדי טהרן 8, ראשון לציון ד"ר אלון שלב מומחה ברפואת המשפחה רופא כאב דף הבית אודות צור קשר אל תחכו - הזמינו תור לרופא עוד היום.. לייעוץ ראשוני ללא עלות והזמנת תורים מלאו פרטים או התקשרו: 05462</t>
+          <t>פיזיותרפיה אסתטיקה פודקסטים קליניקות וססיות להשכרה צור קשר זימון תור ד"ר תמר גרין מומחית לגינקולוגיה ומיילדות מעקב הריון, סקירת הריון מוקדמת ומאוחרת, בדיקות אולטרסאונד אבחנתיות, גיל המעבר ובדיקות גינקולוגיות 073-3214111 office@keshet-refua.co.il לזימון תור &gt; תחומי מומחיות מעקב הריון בדיקות אולטרהסאונד אבחנתיות שקיפות עורפית סקירת מערכות מוקדמת ומאוחרת מעקבי גדילה הדמיית אגן והדמיה תלת מימדית של הרחם טיפולי גינקולוגיה פרטית התקנים תוך רח</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>"אלון שלב"</t>
+          <t>"תמר גרין"</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>official_text</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -9848,12 +9873,12 @@
         <v>1</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-09-04T19:37:15.755041+00:00</t>
+          <t>2026-09-05T00:09:39.798497+00:00</t>
         </is>
       </c>
       <c r="W58" t="n">
@@ -9863,7 +9888,7 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z58" t="n">
         <v>6</v>
@@ -9878,11 +9903,11 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>["https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr.shalev.pain%2F&amp;is_from_rle", "https://www.bgu.ac.il/people/shalevn/", "https://www.bgu.ac.il/en/people/shalevn/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fdr.shalev.pain%2F", "https://www.medreviews.co.il/search/pain-management/center/rishon-lezion", "https://pain.coi.co.il/", "https://pain.coi.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA.htm", "https://pain.coi.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8.htm"]</t>
+          <t>["https://www.medreviews.co.il/provider/dr-green-tamar", "https://keshet-refua.co.il/doctors/dr-tamar-green/", "https://keshet-refua.co.il/about-us/", "https://keshet-refua.co.il/contact-us/", "https://keshet-refua.co.il/clinics-for-rent-sessional-clinics-for-rent/", "https://keshet-refua.co.il/about-us/#contact-keshet-medical-center", "https://keshet-refua.co.il/areas_of_expertise/child-psychology-clinic/", "https://keshet-refua.co.il/doctors/private-clinical-dietician-jerusalem/", "https://keshet-refua.co.il/contact-us/#contact-keshet-medical-center", "https://keshet-refua.co.il/clinics-for-rent-sessional-clinics-for-rent/#contact-keshet-medical-center", "https://keshet-refua.co.il/doctors/dr-tamar-green-private-gynecologist-in-jerusalem/", "https://wayzee.co.il/", "https://keshet-refua.co.il/treatments/menstrual-arrangement-before-the-wedding-private-womens-clinic-private-gynecologist/", "https://keshet-refua.co.il/areas_of_expertise/child-psychology-clinic/#contact-keshet-medical-center", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2F61558661827898%2F", "https://www.facebook.com/public/%D7%AA%D7%9E%D7%A8-%D7%92%D7%A8%D7%99%D7%9F/", "https://www.medreviews.co.il/provider/dr-green-tamar/treatment/gynecologist-clinic", "https://www.szmc.org.il/doctors/grin-tamar/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>4.336524777762407e+17</v>
+        <v>1.202038182753471e+18</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9893,19 +9918,19 @@
       <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>https://pain.coi.co.il/</t>
+          <t>https://keshet-refua.co.il/doctors/dr-tamar-green/</t>
         </is>
       </c>
       <c r="AI58" t="inlineStr"/>
       <c r="AJ58" t="inlineStr"/>
       <c r="AK58" t="inlineStr"/>
-      <c r="AL58" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL58" t="inlineStr"/>
       <c r="AM58" t="inlineStr"/>
       <c r="AN58" t="inlineStr"/>
       <c r="AO58" t="inlineStr"/>
-      <c r="AP58" t="inlineStr"/>
+      <c r="AP58" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ58" t="inlineStr"/>
       <c r="AR58" t="n">
         <v>1</v>
@@ -9917,11 +9942,11 @@
         <v>1</v>
       </c>
       <c r="AU58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>PERSON</t>
+          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
       </c>
     </row>
@@ -9934,17 +9959,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>אמיר צבעוני</t>
+          <t>אבי צפריר</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>family_doctor</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -9965,20 +9990,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>healtms@gmail.com</t>
+          <t>ivfrec@szmc.org.il</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://www.drzivony.co.il/</t>
+          <t>https://www.szmc.org.il/doctors/tsafrir-avi/</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -9988,12 +10013,12 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>"ר אמיר צבעוני ד"ר אמיר צבעוני רופא משפחה מומחה העוסק בטיפול בכאב כרוני בגישת גוף-נפש ללא שימוש בתרופות או בפרוצדורות רפואיות. הטיפול מבוסס מחקר בתחום מדעי המח והכאב. ניתן לקרוא עליי עוד ב דף האודות . טלפון: 051-2303120 healtms@gmail.com קליניקה בגבעת עדה (סמוך לבנימינה) ניתן ליצור איתי קשר גם ב דף יצירת הקשר פוסטים אחרונים על הענק הירוק והדחקת רגשות לאותת עם המגבים רגישות יתר לאחר פציעה אזהרת טריגר בקשת סליחה מעצמי חפש: חיפוש בית אודות</t>
+          <t xml:space="preserve">h عربيه Русский צרו קשר צרו קשר אזור אישי אזור אישי רופאים בשערי צדק ד"ר  אבי צפריר רופא בכיר Dr.  Avi Tsafrir התמחות: גינקולוגיה ויילוד תת התמחות: הפריה חוץ גופית תחומים נוספים: שימור פוריות פוריות הגבר פוריות האשה עוד ivfrec@szmc.org.il ivfrec@szmc.org.il נסיון מקצועי מומחה ביילוד ובגינקולוגיה משנת 2005 רופא בכיר להפריה חוץ גופית בשערי צדק משנת 2005 תפקידים ציבוריים חבר ועד האגודה הישראלית לחקר הפוריות משנת 2022 לימודים והכשרה פקולטה </t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>"אמיר צבעוני"</t>
+          <t>"אבי צפריר"</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -10010,29 +10035,29 @@
         <v>1</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-09-03T23:00:56.706890+00:00</t>
+          <t>2026-09-03T20:26:52.799327+00:00</t>
         </is>
       </c>
       <c r="W59" t="n">
+        <v>4</v>
+      </c>
+      <c r="X59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA59" t="n">
         <v>2</v>
       </c>
-      <c r="X59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>0</v>
-      </c>
       <c r="AB59" t="inlineStr">
         <is>
           <t>ddgs:bing</t>
@@ -10040,14 +10065,14 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>["https://www.drzivony.co.il/", "https://www.drzivony.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
+          <t>["https://www.infomed.co.il/experts/73913/", "https://he.hadassah.org.il/doctor/dr-avi-tsafrir-gaadaabqaa2aaoiag4adaabyaa======/", "https://www.doctors.co.il/expert/obstetrics-and-gynecologists/80043972/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fbyzpryr%2F", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A6%D7%A4%D7%A8%D7%99%D7%A8-%D7%90%D7%91%D7%99/", "https://drtor.co.il/doctor/3910", "https://www.szmc.org.il/doctors/tsafrir-avi/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.clalit.co.il/he/sefersherut/pages/doctordetails.aspx", "https://docsrated.com/doctors/אבי-צפריר", "https://www.doctorita.co.il/experts/44804"]</t>
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>4.336067241913308e+17</v>
+        <v>1.601009443211037e+18</v>
       </c>
       <c r="AE59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF59" t="n">
         <v>0</v>
@@ -10055,35 +10080,35 @@
       <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>https://www.drzivony.co.il/</t>
+          <t>https://www.szmc.org.il/doctors/tsafrir-avi/</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr"/>
       <c r="AJ59" t="inlineStr"/>
       <c r="AK59" t="inlineStr"/>
-      <c r="AL59" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL59" t="inlineStr"/>
       <c r="AM59" t="inlineStr"/>
       <c r="AN59" t="inlineStr"/>
       <c r="AO59" t="inlineStr"/>
-      <c r="AP59" t="inlineStr"/>
+      <c r="AP59" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ59" t="inlineStr"/>
       <c r="AR59" t="n">
         <v>1</v>
       </c>
       <c r="AS59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT59" t="b">
         <v>1</v>
       </c>
       <c r="AU59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>PERSON</t>
+          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
       </c>
     </row>
@@ -10096,7 +10121,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>בתיה קורנבוים</t>
+          <t>אירינה דורפמן אלמוג</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10127,7 +10152,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>batyakornboim@gmail.com</t>
+          <t>dr.irenadorfman@gmail.com</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -10140,7 +10165,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://www.dr-batya-kornboim.com/</t>
+          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -10150,12 +10175,12 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>שקל בחיפה אודות חוות דעת יצירת קשר כתבות ופרסומים תפריט ד״ר בתיה קורנבוים - מומחית ברפואת משפחה ורפואת השמנה [תיאור המרפאה יתווסף בהמשך] טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו חיפה 3570901 IL 052-567-1100 batyakornboim@gmail.com התמחויות רפואיות עיקריות: [פירוט תחומי הטיפול יתווסף בהמשך] מידע מעשי: יצירת קשר: טלפון 052-567-1100 או וואטסאפ 052-567-1100 מיקום: טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו , חיפה סוג</t>
+          <t>מוג אירינה כרטיס עסק: ד"ר דורפמן אלמוג אירינה » תחום פעילות: בריאות וספורט » רופא » תאור העסק: רופאת משפחה עצמאית קופת חולים לאומית. » איש קשר: אירנה דורפמן » טלפונים: טלפון: 077-7997456 נייד: 054-4616457 » אתר: » מייל: dr.irenadorfman@gmail.com » כתובת: בן גוריון 123 יהוד, מיקוד: 56209 כלים מחשבונים לעסקים מדריכי ניהול עסק, הקמת עסק נושאי האתר הנהלת חשבונות הפקת חשבוניות חשבונית אלקטרונית ניהול לקוחות שותפים עסקיים אילת סיטי - מדריך הע</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>"בתיה קורנבוים"</t>
+          <t>"אירינה דורפמן אלמוג"</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -10165,11 +10190,11 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "info@flex.co.il", "confidence": 80, "source_url": "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "identity_url": "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "evidence": "info@flex.co.il", "matched_query": "\"אירינה דורפמן אלמוג\"", "extraction_method": "linked_mailto"}]</t>
         </is>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T60" t="n">
         <v>0</v>
@@ -10177,23 +10202,23 @@
       <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-09-03T23:52:50.148875+00:00</t>
+          <t>2026-09-04T19:17:26.299485+00:00</t>
         </is>
       </c>
       <c r="W60" t="n">
         <v>2</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y60" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
@@ -10202,11 +10227,11 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>["https://www.dr-batya-kornboim.com/", "https://www.dr-batya-kornboim.com/#%D7%90%D7%95%D7%93%D7%95%D7%AA"]</t>
+          <t>["https://www.dunsguide.co.il/C7195b21475cb11a3e5b86def04a3e20c_רופאים/דורפמן_אלמוג_אירינה/", "https://medpage.co.il/doctors/%D7%90%D7%99%D7%A8%D7%A0%D7%94-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-20871/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94/", "https://www.beok.co.il/doctors/Doctors-129241/", "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "https://www.flex.co.il/100_General/005_GeneralPages/006_About.aspx", "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "https://www.flex.co.il/100_General/900_DifferentStuff/900_ForTheCommunity.aspx"]</t>
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>4.336067241913308e+17</v>
+        <v>1.300957433328722e+18</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -10217,19 +10242,19 @@
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>https://www.dr-batya-kornboim.com/</t>
+          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
         </is>
       </c>
       <c r="AI60" t="inlineStr"/>
       <c r="AJ60" t="inlineStr"/>
       <c r="AK60" t="inlineStr"/>
-      <c r="AL60" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL60" t="inlineStr"/>
       <c r="AM60" t="inlineStr"/>
       <c r="AN60" t="inlineStr"/>
       <c r="AO60" t="inlineStr"/>
-      <c r="AP60" t="inlineStr"/>
+      <c r="AP60" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ60" t="inlineStr"/>
       <c r="AR60" t="n">
         <v>1</v>
@@ -10258,7 +10283,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>שלומית שדמון</t>
+          <t>אלון שלב</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10289,7 +10314,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>shlomitshadmon@gmail.com</t>
+          <t>alonshalev31@gmail.com</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -10302,7 +10327,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
+          <t>https://pain.coi.co.il/</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -10312,12 +10337,12 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>ם ופעילויות כנסים והשתלמויות הרצאות מהכנסים מטפלי.ות איט"ם מטפלי.ות איט"ם פיזיותרפיסטים.ית איט"ם מרפאות ציבוריות הצטרפות והתמחות צור קשר פרטי התקשרות טלפון 054-9145177 כתובת אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אימייל shlomitshadmon@gmail.com שדמון שלומית (MD) – תל אביב מקצוע:  רופאת משפחה, מוסמכת ביעוץ וטיפול מיני. התמחות: מטפלת מינית איזור טיפול: תל אביב אודותי אני רופאת משפחה ותיקה, מדריכה קלינית ומרצה בנושאי בריאות האישה, מיניות ה</t>
+          <t>הודעה לבעלי האתר תקופת הניסיון הסתיימה, יש ליצור מנוי דרך ממשק ניהול האתר. האתר נכנס לרשימת המחיקה ויימחק בקרוב לחץ כאן אם אינך זוכר את כתובת ממשק ניהול האתר שלך. דר אלון שלב - רופא כאב טלפון: 054-6221105 מייל: alonshalev31@gmail.com כתובת: ילדי טהרן 8, ראשון לציון ד"ר אלון שלב מומחה ברפואת המשפחה רופא כאב דף הבית אודות צור קשר אל תחכו - הזמינו תור לרופא עוד היום.. לייעוץ ראשוני ללא עלות והזמנת תורים מלאו פרטים או התקשרו: 05462</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>"שלומית שדמון"</t>
+          <t>"אלון שלב"</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -10327,11 +10352,11 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "identity_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "evidence": "mail.com אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"שלומית שדמון\"", "extraction_method": "direct_text"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T61" t="n">
         <v>0</v>
@@ -10339,7 +10364,7 @@
       <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-09-04T15:25:57.140597+00:00</t>
+          <t>2026-09-04T19:37:15.755041+00:00</t>
         </is>
       </c>
       <c r="W61" t="n">
@@ -10349,10 +10374,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z61" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -10364,11 +10389,11 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>["https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA/", "https://moonbellboutique.com/index/%D7%93%D7%A8-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%A9%D7%93%D7%9E%D7%95%D7%9F/", "https://moonbellboutique.com/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/", "https://www.infomed.co.il/experts/145161/", "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
+          <t>["https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr.shalev.pain%2F&amp;is_from_rle", "https://www.bgu.ac.il/people/shalevn/", "https://www.bgu.ac.il/en/people/shalevn/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fdr.shalev.pain%2F", "https://www.medreviews.co.il/search/pain-management/center/rishon-lezion", "https://pain.coi.co.il/", "https://pain.coi.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA.htm", "https://pain.coi.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8.htm"]</t>
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>4.003896215467274e+17</v>
+        <v>1.300957433328722e+18</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10379,19 +10404,19 @@
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
+          <t>https://pain.coi.co.il/</t>
         </is>
       </c>
       <c r="AI61" t="inlineStr"/>
       <c r="AJ61" t="inlineStr"/>
       <c r="AK61" t="inlineStr"/>
-      <c r="AL61" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL61" t="inlineStr"/>
       <c r="AM61" t="inlineStr"/>
       <c r="AN61" t="inlineStr"/>
       <c r="AO61" t="inlineStr"/>
-      <c r="AP61" t="inlineStr"/>
+      <c r="AP61" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ61" t="inlineStr"/>
       <c r="AR61" t="n">
         <v>1</v>
@@ -10420,7 +10445,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>שרון שלמה קלייטמן</t>
+          <t>אמיר צבעוני</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10451,7 +10476,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>sharon.kleitman@gmail.com</t>
+          <t>healtms@gmail.com</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -10464,7 +10489,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
+          <t>https://www.drzivony.co.il/</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -10474,12 +10499,12 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>ש קשר שיתוף שתפו במייל שתפו בפייסבוק שתפו בטוויטר שתפו בלינקדין ד"ר שרון קלייטמן מומחה ברפואת משפחה, MST - Mind Set Technique, רפואה אינטגרטיבית, IMS - דיקור יבש, תזונה אינטגרטיבית. נייד 052-8325580 פקס 08-6560357 דוא"ל sharon.kleitman@gmail.com אתר www.integrative-med.com שלח/י לי sms פייסבוק אודות ד"ר שרון קלייטמן מומחה ברפואת משפחה, סיים את לימודי הרפואה באוניברסיטת בן גוריון, נשוי ואב לארבעה, מתגורר בקיבוץ שדה בוקר. עוסק בפיתוח והקנ</t>
+          <t>"ר אמיר צבעוני ד"ר אמיר צבעוני רופא משפחה מומחה העוסק בטיפול בכאב כרוני בגישת גוף-נפש ללא שימוש בתרופות או בפרוצדורות רפואיות. הטיפול מבוסס מחקר בתחום מדעי המח והכאב. ניתן לקרוא עליי עוד ב דף האודות . טלפון: 051-2303120 healtms@gmail.com קליניקה בגבעת עדה (סמוך לבנימינה) ניתן ליצור איתי קשר גם ב דף יצירת הקשר פוסטים אחרונים על הענק הירוק והדחקת רגשות לאותת עם המגבים רגישות יתר לאחר פציעה אזהרת טריגר בקשת סליחה מעצמי חפש: חיפוש בית אודות</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>"שרון שלמה קלייטמן"</t>
+          <t>"אמיר צבעוני"</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -10501,7 +10526,7 @@
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-09-04T15:41:54.743203+00:00</t>
+          <t>2026-09-03T23:00:56.706890+00:00</t>
         </is>
       </c>
       <c r="W62" t="n">
@@ -10511,13 +10536,13 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
@@ -10526,11 +10551,11 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>["https://docsrated.com/doctors/שרון-קלייטמן", "https://www.dunsguide.co.il/Cb6a87819a48606a97ab6b3a3617e9370_רופאים/קלייטמן_שרון_שלמה/", "https://www.facebook.com/sharon.kleitman.md/directory_category/", "https://dns.dibiz.com/sharon-kleitman-md", "https://longevitepalmbeach.com"]</t>
+          <t>["https://www.drzivony.co.il/", "https://www.drzivony.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>4.003896215467274e+17</v>
+        <v>1.300820172573992e+18</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10541,19 +10566,19 @@
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
+          <t>https://www.drzivony.co.il/</t>
         </is>
       </c>
       <c r="AI62" t="inlineStr"/>
       <c r="AJ62" t="inlineStr"/>
       <c r="AK62" t="inlineStr"/>
-      <c r="AL62" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL62" t="inlineStr"/>
       <c r="AM62" t="inlineStr"/>
       <c r="AN62" t="inlineStr"/>
       <c r="AO62" t="inlineStr"/>
-      <c r="AP62" t="inlineStr"/>
+      <c r="AP62" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ62" t="inlineStr"/>
       <c r="AR62" t="n">
         <v>1</v>
@@ -10582,7 +10607,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>איה שלם</t>
+          <t>בתיה קורנבוים</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10613,20 +10638,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>info@shrir-sheled.co.il</t>
+          <t>batyakornboim@gmail.com</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/</t>
+          <t>https://www.dr-batya-kornboim.com/</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -10636,12 +10661,12 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>ד"ר איה שלם - אינדקס מטפלים ברפואת שריר שלד דלג לתוכן info@shrir-sheled.co.il בית רשימת המטפלים מאמרים מקצועיים אודות מקצוע המטפל רפואת משפחה פיזיותרפיה אוסטיאופתיה כירופרקטיקה אורתופדיה צרו קשר תפריט בית רשימת המטפלים מאמרים מקצועיים אודות מקצוע המטפל רפואת משפחה פיזיותרפי</t>
+          <t>שקל בחיפה אודות חוות דעת יצירת קשר כתבות ופרסומים תפריט ד״ר בתיה קורנבוים - מומחית ברפואת משפחה ורפואת השמנה [תיאור המרפאה יתווסף בהמשך] טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו חיפה 3570901 IL 052-567-1100 batyakornboim@gmail.com התמחויות רפואיות עיקריות: [פירוט תחומי הטיפול יתווסף בהמשך] מידע מעשי: יצירת קשר: טלפון 052-567-1100 או וואטסאפ 052-567-1100 מיקום: טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו , חיפה סוג</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>"איה שלם"</t>
+          <t>"בתיה קורנבוים"</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -10663,7 +10688,7 @@
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-09-04T18:58:24.569451+00:00</t>
+          <t>2026-09-03T23:52:50.148875+00:00</t>
         </is>
       </c>
       <c r="W63" t="n">
@@ -10673,13 +10698,13 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Z63" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
@@ -10688,11 +10713,11 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>["https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%9C%D7%9D-%D7%90%D7%99%D7%94/", "https://medpage.co.il/doctors/16196-%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D-8959/", "https://www.doctorita.co.il/experts/124568", "https://drtor.co.il/doctor/19921", "http://me.doctorsonly.co.il/user/2636", "https://www.infomed.co.il/experts/74772/", "https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/", "https://eshkol.media/", "https://shrir-sheled.co.il/about/"]</t>
+          <t>["https://www.dr-batya-kornboim.com/", "https://www.dr-batya-kornboim.com/#%D7%90%D7%95%D7%93%D7%95%D7%AA"]</t>
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>4.336524777762407e+17</v>
+        <v>1.300820172573992e+18</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10703,19 +10728,19 @@
       <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/</t>
+          <t>https://www.dr-batya-kornboim.com/</t>
         </is>
       </c>
       <c r="AI63" t="inlineStr"/>
       <c r="AJ63" t="inlineStr"/>
       <c r="AK63" t="inlineStr"/>
-      <c r="AL63" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL63" t="inlineStr"/>
       <c r="AM63" t="inlineStr"/>
       <c r="AN63" t="inlineStr"/>
       <c r="AO63" t="inlineStr"/>
-      <c r="AP63" t="inlineStr"/>
+      <c r="AP63" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ63" t="inlineStr"/>
       <c r="AR63" t="n">
         <v>1</v>
@@ -10727,9 +10752,495 @@
         <v>1</v>
       </c>
       <c r="AU63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV63" t="inlineStr">
+        <is>
+          <t>PERSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>13</v>
+      </c>
+      <c r="B64" t="n">
+        <v>6</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>שלומית שדמון</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>family_doctor</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>moh</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>shlomitshadmon@gmail.com</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>100</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>ם ופעילויות כנסים והשתלמויות הרצאות מהכנסים מטפלי.ות איט"ם מטפלי.ות איט"ם פיזיותרפיסטים.ית איט"ם מרפאות ציבוריות הצטרפות והתמחות צור קשר פרטי התקשרות טלפון 054-9145177 כתובת אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אימייל shlomitshadmon@gmail.com שדמון שלומית (MD) – תל אביב מקצוע:  רופאת משפחה, מוסמכת ביעוץ וטיפול מיני. התמחות: מטפלת מינית איזור טיפול: תל אביב אודותי אני רופאת משפחה ותיקה, מדריכה קלינית ומרצה בנושאי בריאות האישה, מיניות ה</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>"שלומית שדמון"</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>direct_text</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "identity_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "evidence": "mail.com אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"שלומית שדמון\"", "extraction_method": "direct_text"}]</t>
+        </is>
+      </c>
+      <c r="S64" t="n">
+        <v>2</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-09-04T15:25:57.140597+00:00</t>
+        </is>
+      </c>
+      <c r="W64" t="n">
+        <v>2</v>
+      </c>
+      <c r="X64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>["https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA/", "https://moonbellboutique.com/index/%D7%93%D7%A8-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%A9%D7%93%D7%9E%D7%95%D7%9F/", "https://moonbellboutique.com/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/", "https://www.infomed.co.il/experts/145161/", "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="AD64" t="n">
+        <v>1.201168864640182e+18</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="inlineStr"/>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr"/>
+      <c r="AJ64" t="inlineStr"/>
+      <c r="AK64" t="inlineStr"/>
+      <c r="AL64" t="inlineStr"/>
+      <c r="AM64" t="inlineStr"/>
+      <c r="AN64" t="inlineStr"/>
+      <c r="AO64" t="inlineStr"/>
+      <c r="AP64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ64" t="inlineStr"/>
+      <c r="AR64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU64" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV64" t="inlineStr">
+        <is>
+          <t>PERSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>13</v>
+      </c>
+      <c r="B65" t="n">
+        <v>6</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>שרון שלמה קלייטמן</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>family_doctor</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>moh</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>sharon.kleitman@gmail.com</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>100</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>ש קשר שיתוף שתפו במייל שתפו בפייסבוק שתפו בטוויטר שתפו בלינקדין ד"ר שרון קלייטמן מומחה ברפואת משפחה, MST - Mind Set Technique, רפואה אינטגרטיבית, IMS - דיקור יבש, תזונה אינטגרטיבית. נייד 052-8325580 פקס 08-6560357 דוא"ל sharon.kleitman@gmail.com אתר www.integrative-med.com שלח/י לי sms פייסבוק אודות ד"ר שרון קלייטמן מומחה ברפואת משפחה, סיים את לימודי הרפואה באוניברסיטת בן גוריון, נשוי ואב לארבעה, מתגורר בקיבוץ שדה בוקר. עוסק בפיתוח והקנ</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>"שרון שלמה קלייטמן"</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>direct_text</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S65" t="n">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-09-04T15:41:54.743203+00:00</t>
+        </is>
+      </c>
+      <c r="W65" t="n">
+        <v>2</v>
+      </c>
+      <c r="X65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>["https://docsrated.com/doctors/שרון-קלייטמן", "https://www.dunsguide.co.il/Cb6a87819a48606a97ab6b3a3617e9370_רופאים/קלייטמן_שרון_שלמה/", "https://www.facebook.com/sharon.kleitman.md/directory_category/", "https://dns.dibiz.com/sharon-kleitman-md", "https://longevitepalmbeach.com"]</t>
+        </is>
+      </c>
+      <c r="AD65" t="n">
+        <v>1.201168864640182e+18</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="inlineStr"/>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr"/>
+      <c r="AJ65" t="inlineStr"/>
+      <c r="AK65" t="inlineStr"/>
+      <c r="AL65" t="inlineStr"/>
+      <c r="AM65" t="inlineStr"/>
+      <c r="AN65" t="inlineStr"/>
+      <c r="AO65" t="inlineStr"/>
+      <c r="AP65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ65" t="inlineStr"/>
+      <c r="AR65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU65" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV65" t="inlineStr">
+        <is>
+          <t>PERSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>13</v>
+      </c>
+      <c r="B66" t="n">
+        <v>6</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>איה שלם</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>family_doctor</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>moh</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>info@shrir-sheled.co.il</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>CLINIC_OR_ORGANIZATION</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>88</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>ד"ר איה שלם - אינדקס מטפלים ברפואת שריר שלד דלג לתוכן info@shrir-sheled.co.il בית רשימת המטפלים מאמרים מקצועיים אודות מקצוע המטפל רפואת משפחה פיזיותרפיה אוסטיאופתיה כירופרקטיקה אורתופדיה צרו קשר תפריט בית רשימת המטפלים מאמרים מקצועיים אודות מקצוע המטפל רפואת משפחה פיזיותרפי</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>"איה שלם"</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>direct_text</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S66" t="n">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-09-04T18:58:24.569451+00:00</t>
+        </is>
+      </c>
+      <c r="W66" t="n">
+        <v>2</v>
+      </c>
+      <c r="X66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>["https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%9C%D7%9D-%D7%90%D7%99%D7%94/", "https://medpage.co.il/doctors/16196-%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D-8959/", "https://www.doctorita.co.il/experts/124568", "https://drtor.co.il/doctor/19921", "http://me.doctorsonly.co.il/user/2636", "https://www.infomed.co.il/experts/74772/", "https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/", "https://eshkol.media/", "https://shrir-sheled.co.il/about/"]</t>
+        </is>
+      </c>
+      <c r="AD66" t="n">
+        <v>1.300957433328722e+18</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="inlineStr"/>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr"/>
+      <c r="AJ66" t="inlineStr"/>
+      <c r="AK66" t="inlineStr"/>
+      <c r="AL66" t="inlineStr"/>
+      <c r="AM66" t="inlineStr"/>
+      <c r="AN66" t="inlineStr"/>
+      <c r="AO66" t="inlineStr"/>
+      <c r="AP66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ66" t="inlineStr"/>
+      <c r="AR66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV66" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>

--- a/output/contacts_primary.xlsx
+++ b/output/contacts_primary.xlsx
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>1.301247395137417e+18</v>
+        <v>3.903742185412251e+18</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>1.604715483545694e+18</v>
+        <v>4.814146450637083e+18</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>1.601009443167991e+18</v>
+        <v>4.803028329503972e+18</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>1.601009443167991e+18</v>
+        <v>4.803028329503972e+18</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>1.502181699762559e+18</v>
+        <v>4.506545099287677e+18</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>1.302070959666307e+18</v>
+        <v>3.906212878998921e+18</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>1.30205551936656e+18</v>
+        <v>3.906166558099681e+18</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>1.605264526564613e+18</v>
+        <v>4.81579357969384e+18</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>1.302070959666309e+18</v>
+        <v>3.906212878998928e+18</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>1.601009443167991e+18</v>
+        <v>4.803028329503972e+18</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -3069,7 +3069,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3393,7 +3393,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>1.302070959666309e+18</v>
+        <v>3.906212878998928e+18</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>1.30205551936656e+18</v>
+        <v>3.906166558099681e+18</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3879,7 +3879,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>1.301247395137417e+18</v>
+        <v>3.90374218541225e+18</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>1.234523228039515e+18</v>
+        <v>3.703569684118546e+18</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>1.234523228039515e+18</v>
+        <v>3.703569684118546e+18</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4689,7 +4689,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>1.204463122753697e+18</v>
+        <v>3.61338936826109e+18</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>1.204463122753697e+18</v>
+        <v>3.61338936826109e+18</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -5014,7 +5014,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>1.204463122753697e+18</v>
+        <v>3.61338936826109e+18</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>1.204463122753697e+18</v>
+        <v>3.61338936826109e+18</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5338,7 +5338,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>1.204463122753697e+18</v>
+        <v>3.61338936826109e+18</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5500,7 +5500,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>1.604715483545694e+18</v>
+        <v>4.814146450637083e+18</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5662,7 +5662,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>1.201184304939929e+18</v>
+        <v>3.603552914819788e+18</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>1.301247395137931e+18</v>
+        <v>3.903742185413792e+18</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>1.301231954838182e+18</v>
+        <v>3.903695864514545e+18</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -6164,7 +6164,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>1.301231954838182e+18</v>
+        <v>3.903695864514545e+18</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6326,7 +6326,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>1.301231954838182e+18</v>
+        <v>3.903695864514545e+18</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6488,7 +6488,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>1.502364714102199e+18</v>
+        <v>4.507094142306596e+18</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6812,7 +6812,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>1.601009443167991e+18</v>
+        <v>4.803028329503972e+18</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -7136,7 +7136,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>1.301247395137417e+18</v>
+        <v>3.90374218541225e+18</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7298,7 +7298,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>1.234523228039515e+18</v>
+        <v>3.703569684118546e+18</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>1.234523228039515e+18</v>
+        <v>3.703569684118546e+18</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7622,7 +7622,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>1.234523228039515e+18</v>
+        <v>3.703569684118546e+18</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7784,7 +7784,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>1.204615823807648e+18</v>
+        <v>3.613847471422945e+18</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7946,7 +7946,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>1.204600383508426e+18</v>
+        <v>3.613801150525279e+18</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -8108,7 +8108,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>1.204600383508426e+18</v>
+        <v>3.613801150525279e+18</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -8270,7 +8270,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>1.204463122753697e+18</v>
+        <v>3.61338936826109e+18</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8432,7 +8432,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>1.204463122753697e+18</v>
+        <v>3.61338936826109e+18</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8594,7 +8594,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>1.201992429168561e+18</v>
+        <v>3.605977287505682e+18</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8756,7 +8756,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>1.202038182753471e+18</v>
+        <v>3.606114548260412e+18</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>1.234264146800576e+18</v>
+        <v>3.702792440401727e+18</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>1.601009443167991e+18</v>
+        <v>4.803028329503972e+18</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -9251,7 +9251,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>1.234538668338751e+18</v>
+        <v>3.703616005016253e+18</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -9421,7 +9421,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>1.234523228039515e+18</v>
+        <v>3.703569684118546e+18</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9583,7 +9583,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>1.234523228039515e+18</v>
+        <v>3.703569684118546e+18</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9745,7 +9745,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>1.204463122796743e+18</v>
+        <v>3.61338936839023e+18</v>
       </c>
       <c r="AE57" t="n">
         <v>2</v>
@@ -9907,7 +9907,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>1.202038182753471e+18</v>
+        <v>3.606114548260412e+18</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -10069,7 +10069,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>1.601009443211037e+18</v>
+        <v>4.803028329633112e+18</v>
       </c>
       <c r="AE59" t="n">
         <v>2</v>
@@ -10231,7 +10231,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>1.300957433328722e+18</v>
+        <v>3.902872299986166e+18</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -10393,7 +10393,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>1.300957433328722e+18</v>
+        <v>3.902872299986166e+18</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10555,7 +10555,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10717,7 +10717,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>1.201168864640182e+18</v>
+        <v>3.603506593920547e+18</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -11041,7 +11041,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>1.201168864640182e+18</v>
+        <v>3.603506593920547e+18</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -11203,7 +11203,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>1.300957433328722e+18</v>
+        <v>3.902872299986166e+18</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>

--- a/output/contacts_primary.xlsx
+++ b/output/contacts_primary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV66"/>
+  <dimension ref="A1:AV67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>3.903742185412251e+18</v>
+        <v>1.171122655623675e+19</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>4.814146450637083e+18</v>
+        <v>1.444243935191125e+19</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>3.902460517721977e+18</v>
+        <v>1.170738155316593e+19</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>3.902460517721977e+18</v>
+        <v>1.170738155316593e+19</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>3.902460517721977e+18</v>
+        <v>1.170738155316593e+19</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>3.902460517721977e+18</v>
+        <v>1.170738155316593e+19</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>4.803028329503972e+18</v>
+        <v>1.440908498851192e+19</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>4.803028329503972e+18</v>
+        <v>1.440908498851192e+19</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>4.506545099287677e+18</v>
+        <v>1.351963529786303e+19</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>3.906212878998921e+18</v>
+        <v>1.171863863699676e+19</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>3.906166558099681e+18</v>
+        <v>1.171849967429904e+19</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>4.81579357969384e+18</v>
+        <v>1.444738073908152e+19</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>3.906212878998928e+18</v>
+        <v>1.171863863699678e+19</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>4.803028329503972e+18</v>
+        <v>1.440908498851192e+19</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -3069,7 +3069,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>3.902460517721977e+18</v>
+        <v>1.170738155316593e+19</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>3.902460517721977e+18</v>
+        <v>1.170738155316593e+19</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3393,7 +3393,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>3.902460517721977e+18</v>
+        <v>1.170738155316593e+19</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>3.906212878998928e+18</v>
+        <v>1.171863863699678e+19</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>3.906166558099681e+18</v>
+        <v>1.171849967429904e+19</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3879,7 +3879,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>3.90374218541225e+18</v>
+        <v>1.171122655623675e+19</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>3.902460517721977e+18</v>
+        <v>1.170738155316593e+19</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>3.902460517721977e+18</v>
+        <v>1.170738155316593e+19</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>3.703569684118546e+18</v>
+        <v>1.111070905235564e+19</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>3.703569684118546e+18</v>
+        <v>1.111070905235564e+19</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4689,7 +4689,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>3.61338936826109e+18</v>
+        <v>1.084016810478327e+19</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>3.61338936826109e+18</v>
+        <v>1.084016810478327e+19</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -5014,7 +5014,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>3.61338936826109e+18</v>
+        <v>1.084016810478327e+19</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>3.61338936826109e+18</v>
+        <v>1.084016810478327e+19</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5338,7 +5338,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>3.61338936826109e+18</v>
+        <v>1.084016810478327e+19</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5500,7 +5500,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>4.814146450637083e+18</v>
+        <v>1.444243935191125e+19</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5662,7 +5662,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>3.603552914819788e+18</v>
+        <v>1.081065874445936e+19</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>3.903742185413792e+18</v>
+        <v>1.171122655624138e+19</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>3.903695864514545e+18</v>
+        <v>1.171108759354363e+19</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -6164,7 +6164,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>3.903695864514545e+18</v>
+        <v>1.171108759354363e+19</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6326,7 +6326,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>3.903695864514545e+18</v>
+        <v>1.171108759354363e+19</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6488,7 +6488,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>3.902460517721977e+18</v>
+        <v>1.170738155316593e+19</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>4.507094142306596e+18</v>
+        <v>1.352128242691979e+19</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6812,7 +6812,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>4.803028329503972e+18</v>
+        <v>1.440908498851192e+19</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>3.902460517721977e+18</v>
+        <v>1.170738155316593e+19</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -7136,7 +7136,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>3.90374218541225e+18</v>
+        <v>1.171122655623675e+19</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7298,7 +7298,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>3.703569684118546e+18</v>
+        <v>1.111070905235564e+19</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>3.703569684118546e+18</v>
+        <v>1.111070905235564e+19</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7622,7 +7622,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>3.703569684118546e+18</v>
+        <v>1.111070905235564e+19</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7784,7 +7784,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>3.613847471422945e+18</v>
+        <v>1.084154241426883e+19</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7946,7 +7946,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>3.613801150525279e+18</v>
+        <v>1.084140345157584e+19</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -8108,7 +8108,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>3.613801150525279e+18</v>
+        <v>1.084140345157584e+19</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -8270,7 +8270,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>3.61338936826109e+18</v>
+        <v>1.084016810478327e+19</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8432,7 +8432,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>3.61338936826109e+18</v>
+        <v>1.084016810478327e+19</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8594,7 +8594,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>3.605977287505682e+18</v>
+        <v>1.081793186251705e+19</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8756,7 +8756,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>3.606114548260412e+18</v>
+        <v>1.081834364478124e+19</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>דלית דרימן-מדינה</t>
+          <t>ניצן נבות אבישר</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>dalit@drdreman.co.il</t>
+          <t>doctor.nitzan@gmail.com</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -8848,11 +8848,11 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://www.drdreman.co.il/%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%9E%D7%98%D7%91%D7%95%D7%9C%D7%99%D7%95%D7%AA/</t>
+          <t>https://drnitzan.com/#about</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -8862,17 +8862,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>drdremandalit@gmail.com</t>
+          <t>doctor.nitzan@gmail.com</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>"דלית דרימן מדינה" רפואת משפחה (מרפאה OR "צור קשר" OR email OR מייל)</t>
+          <t>"ניצן נבות אבישר" רפואת משפחה</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>direct_mailto</t>
+          <t>linked_mailto</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -8889,47 +8889,47 @@
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-09-10T18:44:56.180135+00:00</t>
+          <t>2026-09-11T08:10:09.398703+00:00</t>
         </is>
       </c>
       <c r="W52" t="n">
         <v>8</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y52" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Z52" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AA52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>["https://www.drdreman.co.il/מחלות-מטבוליות/", "https://www.drdreman.co.il/%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%9E%D7%98%D7%91%D7%95%D7%9C%D7%99%D7%95%D7%AA/", "https://www.drdreman.co.il/about/", "https://www.drdreman.co.il/contact/", "https://www.drdreman.co.il/", "https://www.doctorita.co.il/experts/52215", "https://www.drdreman.co.il/%D7%93%D7%A3-%D7%91%D7%99%D7%AA/", "https://www.other-medicine.co.il/author/dalitdrdreman-co-il/", "https://www.izi.co.il/site/6f2c026c8d", "https://www.infomed.co.il/experts/78145/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%93%D7%A8%D7%99%D7%9E%D7%9F-%D7%9E%D7%93%D7%99%D7%A0%D7%94-%D7%93%D7%9C%D7%99%D7%AA/", "https://www.findglocal.com/IL/Unknown/106988607393615/ד״ר-דלית-דרימן-רפואה-פונקציונלית-ואינטגרטיבית"]</t>
+          <t>["https://drnitzan.com/", "https://drnitzan.com/#about", "https://drnitzan.com/#contact"]</t>
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>3.702792440401727e+18</v>
+        <v>1.081807082521478e+19</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>https://www.drdreman.co.il/%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%9E%D7%98%D7%91%D7%95%D7%9C%D7%99%D7%95%D7%AA/</t>
+          <t>https://drnitzan.com/</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr"/>
@@ -8946,8 +8946,7 @@
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>מחלות מטבוליות - ד"ר דלית דרימן-מדינה מחלות מטבוליות - ד"ר דלית דרימן-מדינה דלג לתוכן אודות כיצד נוכל לעזור במה אנחנו מטפלים מפגשים ועלויות שאלות ותשובות מאמרים סרטונים מהתקשורת צור קשר אודות כיצד נוכל לעזור במה אנחנו מטפלים מפגשים ועלויות שאלות ותשובות מאמרים סרטונים מהתקשורת צור קשר 0546033755 חיפוש חיפוש אודות כיצד נוכל לעזור במה אנחנו מטפלים מפגשים ועלויות שאלות ותשובות מאמרים סרטונים מהתקשורת צור קשר אודות כיצד נוכל לעזור במה אנחנו מטפלים מפגשים ועלויות שאלות ותשובות מאמרים סרטונים מהתקשורת צור קשר חיפוש חיפוש מחלות מטבוליות הפרעות מטבוליות, עודף משקל, סוכרת בחירות מזון גרועות, העדר מרכיבי מזון חיוניים, רעלנים, מתח נפשי, ודלקת כרונית גורמים לחוסר איזון מטבולי ולמחלות שמהוות את מרבית המחלות הכרוניות כיום. במה אנו מטפלים? מחלות לב יתר לחץ דם עודף משקל והשמנה תסמונת מטבולית סוכרת הפרעות בכולסטרול ושומני הדם איך זה עובד? אנחנו עורכים למטופלים שלנו בירור נרחב ע״י בדיקות מעבדה מתקדמות כולל בדיקות מיוחדות לשומני הדם שאינן מבוצעות באופן סטנדרטי בקופות החולים.
-בטיפול שלנו אנו מתבססים על המזון ומרכיבי התזונה ככלים הטיפוליים הרא</t>
+          <t>ד"ר ניצן נבות אבישר | ליווי וטיפול רפואי בהשמנה ומחלות מטבוליות – שוהם ד"ר ניצן נבות אבישר | ליווי וטיפול רפואי בהשמנה ומחלות מטבוליות – שוהם בית הסבר תהליך עלינו צור קשר לתיאום ייעוץ בית הסבר תהליך עלינו צור קשר לתיאום ייעוץ ד"ר ניצן נבות אבישר · מומחית ברפואת משפחה ליווי וטיפול בהשמנה ומחלות מטבוליות אבחון, טיפול וליווי מותאם אישית, בלי שיפוטיות ובלי סודות. שילוב של ידע מדעי, הקשבה ורגישות. לתיאום ייעוץ הגישה שלי המיקוד הוא בך הזמן שלך לשינוי, המקום שלך בחיים אם הגעת לכאן, אני מאמינה שפינית מקום בלב להתמקד בעצמך ולהעניק לעצמך את המתנה החשובה ביותר – הבריאות שלך. הגעת למקום בחיים שבו הבריאות והצרכים שלך נמצאים במרכז. אני מאמינה שטיפול בהשמנה ובאיזון מטבולי אינו מסתכם בנוסחאות פשוטות של מספרים או קלוריות. מדובר בתהליך רפואי עמוק ומורכב, שחייב להתאים באופן מדויק לשגרת החיים, לפיזיולוגיה וליעדים האישיים שלך. אני כאן כדי להעניק לך מענה מקצועי ומקיף המבוסס על ידע קליני עדכני וניסיון רב שנים, לצד הקשבה עמוקה ורגישות. ההתמקדות היא בך. המענה הרפואי בקליניקה אבחון ואיזון מטבולי מקיף בדיקות והסתכלות רחבה על כל התמונה הבריאותית שלך, כדי להבין מה באמת משפיע על המשקל</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr"/>
@@ -8979,12 +8978,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ד"ר ארבל אריאל</t>
+          <t>דלית דרימן-מדינה</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -8999,31 +8998,31 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>ima</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>info@eryaveladan.com</t>
+          <t>dalit@drdreman.co.il</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://www.eryaveladan.com/</t>
+          <t>https://www.drdreman.co.il/%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%9E%D7%98%D7%91%D7%95%D7%9C%D7%99%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -9033,50 +9032,50 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>החזיר את האיזון. קראי עוד השאירי פרטים ונחזור אלייך בהקדם שם מלא טלפון דוא״ל שליחה רופא נשים מומחה מחלות העריה והלדן ​ ד״ר אריאל ארבל לקביעת תור: 077-2311245 כתובת המרפאה: בית למומחים ברפואה - בורוכוב 54, גבעתיים דוא״ל: info@eryaveladan.com bottom of page</t>
+          <t>drdremandalit@gmail.com</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>"ארבל אריאל"</t>
+          <t>"דלית דרימן מדינה" רפואת משפחה (מרפאה OR "צור קשר" OR email OR מייל)</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>direct_mailto</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>[{"email": "info@eryaveladan.com", "confidence": 88, "source_url": "https://www.eryaveladan.com/", "identity_url": "https://www.eryaveladan.com/", "evidence": "החזיר את האיזון. קראי עוד השאירי פרטים ונחזור אלייך בהקדם שם מלא טלפון דוא״ל שליחה רופא נשים מומחה מחלות העריה והלדן ​ ד״ר אריאל ארבל לקביעת תור: 077-2311245 כתובת המרפאה: בית למומחים ברפואה - בורוכוב 54, גבעתיים דוא״ל: info@eryaveladan.com bottom of page", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}, {"email": "office@b54.co.il", "confidence": 88, "source_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "identity_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "evidence": "ד\"ר אריאל ארבל - מרפאת מומחים B54, הבית למומחים ברפואה בגבעתיים דילוג לתוכן B54 03-757-8562 office@b54.co.il א׳-ה׳ 8:00-20:00 | ו׳ 08:00-13:00 Facebook-f Youtube Google דף הבית אודות B54 מי אנחנו שכונת בורוכוב מרכז Friendly הנהלת המרפאה שאלות נפוצות הרופאים שלנו קליניקה להשכרה מידע למטופל שאלות ותשובות הורדת טפ", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-09-03T20:23:48.175654+00:00</t>
+          <t>2026-09-10T18:44:56.180135+00:00</t>
         </is>
       </c>
       <c r="W53" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X53" t="n">
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
@@ -9085,11 +9084,11 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598", "https://www.facebook.com/people/%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%90%D7%A8%D7%91%D7%9C/pfbid0NCmi7FZgUyu2EVV5mLJMpBfndXiDQPqseAxUny7KWHsDvucQScUiVnBeMef3ByStl/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%90%D7%A8%D7%91%D7%9C-%D7%90%D7%A8%D7%99%D7%90%D7%9C/", "https://www.eryaveladan.com/", "https://www.eryaveladan.com/%D7%90%D7%95%D7%93%D7%95%D7%AA-1", "https://www.b54.co.il/doctors/dr-arbel-ariel/", "https://www.medreviews.co.il/provider/dr-arbel-ariel", "https://www.b54.co.il/about/", "https://www.b54.co.il/about", "https://www.b54.co.il/about#borohov", "https://www.b54.co.il/about#Friendly", "https://www.b54.co.il/about#management", "https://www.b54.co.il/about#qa", "https://www.medreviews.co.il/provider/dr-arbel-ariel#contact-doctor-section", "https://www.medreviews.co.il/contact-us", "https://www.medreviews.co.il/about", "https://woman.mymc.co.il/doctors/dr-arielarbel/", "https://www.ima.org.il/DoctorsIndex/Default.aspx", "https://www.infomed.co.il/experts/145655/", "https://www.ami.org.il/blog/families/not-the-same-shirley"]</t>
+          <t>["https://www.drdreman.co.il/מחלות-מטבוליות/", "https://www.drdreman.co.il/%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%9E%D7%98%D7%91%D7%95%D7%9C%D7%99%D7%95%D7%AA/", "https://www.drdreman.co.il/about/", "https://www.drdreman.co.il/contact/", "https://www.drdreman.co.il/", "https://www.doctorita.co.il/experts/52215", "https://www.drdreman.co.il/%D7%93%D7%A3-%D7%91%D7%99%D7%AA/", "https://www.other-medicine.co.il/author/dalitdrdreman-co-il/", "https://www.izi.co.il/site/6f2c026c8d", "https://www.infomed.co.il/experts/78145/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%93%D7%A8%D7%99%D7%9E%D7%9F-%D7%9E%D7%93%D7%99%D7%A0%D7%94-%D7%93%D7%9C%D7%99%D7%AA/", "https://www.findglocal.com/IL/Unknown/106988607393615/ד״ר-דלית-דרימן-רפואה-פונקציונלית-ואינטגרטיבית"]</t>
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>4.803028329503972e+18</v>
+        <v>1.110837732120518e+19</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -9100,22 +9099,31 @@
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>https://www.eryaveladan.com/</t>
+          <t>https://www.drdreman.co.il/%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%9E%D7%98%D7%91%D7%95%D7%9C%D7%99%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="AI53" t="inlineStr"/>
       <c r="AJ53" t="inlineStr"/>
       <c r="AK53" t="inlineStr"/>
-      <c r="AL53" t="inlineStr"/>
-      <c r="AM53" t="inlineStr"/>
-      <c r="AN53" t="inlineStr"/>
-      <c r="AO53" t="inlineStr"/>
-      <c r="AP53" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL53" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM53" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN53" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>מחלות מטבוליות - ד"ר דלית דרימן-מדינה מחלות מטבוליות - ד"ר דלית דרימן-מדינה דלג לתוכן אודות כיצד נוכל לעזור במה אנחנו מטפלים מפגשים ועלויות שאלות ותשובות מאמרים סרטונים מהתקשורת צור קשר אודות כיצד נוכל לעזור במה אנחנו מטפלים מפגשים ועלויות שאלות ותשובות מאמרים סרטונים מהתקשורת צור קשר 0546033755 חיפוש חיפוש אודות כיצד נוכל לעזור במה אנחנו מטפלים מפגשים ועלויות שאלות ותשובות מאמרים סרטונים מהתקשורת צור קשר אודות כיצד נוכל לעזור במה אנחנו מטפלים מפגשים ועלויות שאלות ותשובות מאמרים סרטונים מהתקשורת צור קשר חיפוש חיפוש מחלות מטבוליות הפרעות מטבוליות, עודף משקל, סוכרת בחירות מזון גרועות, העדר מרכיבי מזון חיוניים, רעלנים, מתח נפשי, ודלקת כרונית גורמים לחוסר איזון מטבולי ולמחלות שמהוות את מרבית המחלות הכרוניות כיום. במה אנו מטפלים? מחלות לב יתר לחץ דם עודף משקל והשמנה תסמונת מטבולית סוכרת הפרעות בכולסטרול ושומני הדם איך זה עובד? אנחנו עורכים למטופלים שלנו בירור נרחב ע״י בדיקות מעבדה מתקדמות כולל בדיקות מיוחדות לשומני הדם שאינן מבוצעות באופן סטנדרטי בקופות החולים.
+בטיפול שלנו אנו מתבססים על המזון ומרכיבי התזונה ככלים הטיפוליים הרא</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr"/>
       <c r="AQ53" t="inlineStr"/>
       <c r="AR53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS53" t="b">
         <v>0</v>
@@ -9141,7 +9149,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>יעל כהן</t>
+          <t>ד"ר ארבל אריאל</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9161,18 +9169,18 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>ima</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>office@elitemed.co.il</t>
+          <t>info@eryaveladan.com</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -9185,7 +9193,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://elitemed.co.il/doctors/dr-yael-cohen-hebrew/</t>
+          <t>https://www.eryaveladan.com/</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -9195,12 +9203,12 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>ד"ר יעל כהן - elitemed.co.il דלג לתוכן Facebook Instagram Whatsapp Office@elitemed.co.il 073-321-4181 בית אודות רופאים שירותים רפואיים אולטרסאונד וביופסיות אוסטאופתיה אורולוגיה אורתופדיה אלרגיה ואימונולגיה אנדוקרינולוגיה סוכרת וירידה במשקל אסתטיקה אף אוזן גרון גינקולוגיה ובריאות האישה ג</t>
+          <t>החזיר את האיזון. קראי עוד השאירי פרטים ונחזור אלייך בהקדם שם מלא טלפון דוא״ל שליחה רופא נשים מומחה מחלות העריה והלדן ​ ד״ר אריאל ארבל לקביעת תור: 077-2311245 כתובת המרפאה: בית למומחים ברפואה - בורוכוב 54, גבעתיים דוא״ל: info@eryaveladan.com bottom of page</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>"יעל כהן" יילוד</t>
+          <t>"ארבל אריאל"</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -9210,82 +9218,74 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "info@eryaveladan.com", "confidence": 88, "source_url": "https://www.eryaveladan.com/", "identity_url": "https://www.eryaveladan.com/", "evidence": "החזיר את האיזון. קראי עוד השאירי פרטים ונחזור אלייך בהקדם שם מלא טלפון דוא״ל שליחה רופא נשים מומחה מחלות העריה והלדן ​ ד״ר אריאל ארבל לקביעת תור: 077-2311245 כתובת המרפאה: בית למומחים ברפואה - בורוכוב 54, גבעתיים דוא״ל: info@eryaveladan.com bottom of page", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}, {"email": "office@b54.co.il", "confidence": 88, "source_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "identity_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "evidence": "ד\"ר אריאל ארבל - מרפאת מומחים B54, הבית למומחים ברפואה בגבעתיים דילוג לתוכן B54 03-757-8562 office@b54.co.il א׳-ה׳ 8:00-20:00 | ו׳ 08:00-13:00 Facebook-f Youtube Google דף הבית אודות B54 מי אנחנו שכונת בורוכוב מרכז Friendly הנהלת המרפאה שאלות נפוצות הרופאים שלנו קליניקה להשכרה מידע למטופל שאלות ותשובות הורדת טפ", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}]</t>
         </is>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-09-10T18:33:08.486465+00:00</t>
+          <t>2026-09-03T20:23:48.175654+00:00</t>
         </is>
       </c>
       <c r="W54" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="X54" t="n">
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Z54" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>ddgs:yahoo+ddgs:bing</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>["https://elitemed.co.il/doctors/dr-yael-cohen-hebrew/", "https://elitemed.co.il/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%A4%D7%95%D7%90%D7%99-%D7%A4%D7%A8%D7%98%D7%99-%D7%91%D7%9E%D7%95%D7%93%D7%99%D7%A2%D7%99%D7%9F/", "https://elitemed.co.il/pain-clinic-modiin/", "https://elitemed.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://elitemed.co.il/%d7%90%d7%95%d6%b9%d7%93%d7%95%d6%b9%d7%aa/", "https://medpage.co.il/doctors/יעל-כהן-23202/", "https://medpage.co.il/doctors/%D7%99%D7%A2%D7%9C-%D7%9B%D7%94%D7%9F-23202/", "https://www.facebook.com/ichilovmedical/posts/תכירו-את-פרופ-יעל-כהןמנהלת-יחידת-המיאלומה-במערך-ההמטולוגי-של-איכילוב-ואחת-מהרופא/1288268913309017/", "https://www.facebook.com/ichilovmedical/videos/%D7%AA%D7%9B%D7%99%D7%A8%D7%95-%D7%90%D7%AA-%D7%A4%D7%A8%D7%95%D7%A4-%D7%99%D7%A2%D7%9C-%D7%9B%D7%94%D7%9F%D7%9E%D7%A0%D7%94%D7%9C%D7%AA-%D7%99%D7%97%D7%99%D7%93%D7%AA-%D7%94%D7%9E%D7%99%D7%90%D7%9C%D7%95%D7%9E%D7%94-%D7%91%D7%9E%D7%A2%D7%A8%D7%9A-%D7%94%D7%94%D7%9E%D7%98%D7%95%D7%9C%D7%95%D7%92%D7%99-%D7%A9%D7%9C-%D7%90%D7%99%D7%9B%D7%99%D7%9C%D7%95%D7%91-%D7%95%D7%90%D7%97%D7%AA-%D7%9E%D7%94%D7%A8%D7%95%D7%A4%D7%90/981973987039095/", "https://www.medico.co.il/doctors/פרופ-יעל-כהן/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%99%D7%A2%D7%9C-%D7%9B%D7%94%D7%9F/", "https://www.medico.co.il/doctors/", "https://www.medico.co.il/doctors/%d7%a4%d7%a8%d7%95%d7%a4-%d7%99%d7%a2%d7%9c-%d7%9b%d7%94%d7%9f/", "https://www.tasmc.org.il/doctorssearch/dr/cohen-yael/", "https://www.szmc.org.il/doctors/cohen-yael/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.vimed.co.il/users/0918fba4-bd6a-4310-ab8f-b51cab0b8f80", "https://www.meuhedet.co.il/poi/ParamedicalDoctors/000189680918100097000000000000_0", "https://www.medreviews.co.il/provider/dr-cohen-yael"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598", "https://www.facebook.com/people/%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%90%D7%A8%D7%91%D7%9C/pfbid0NCmi7FZgUyu2EVV5mLJMpBfndXiDQPqseAxUny7KWHsDvucQScUiVnBeMef3ByStl/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%90%D7%A8%D7%91%D7%9C-%D7%90%D7%A8%D7%99%D7%90%D7%9C/", "https://www.eryaveladan.com/", "https://www.eryaveladan.com/%D7%90%D7%95%D7%93%D7%95%D7%AA-1", "https://www.b54.co.il/doctors/dr-arbel-ariel/", "https://www.medreviews.co.il/provider/dr-arbel-ariel", "https://www.b54.co.il/about/", "https://www.b54.co.il/about", "https://www.b54.co.il/about#borohov", "https://www.b54.co.il/about#Friendly", "https://www.b54.co.il/about#management", "https://www.b54.co.il/about#qa", "https://www.medreviews.co.il/provider/dr-arbel-ariel#contact-doctor-section", "https://www.medreviews.co.il/contact-us", "https://www.medreviews.co.il/about", "https://woman.mymc.co.il/doctors/dr-arielarbel/", "https://www.ima.org.il/DoctorsIndex/Default.aspx", "https://www.infomed.co.il/experts/145655/", "https://www.ami.org.il/blog/families/not-the-same-shirley"]</t>
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>3.703616005016253e+18</v>
+        <v>1.440908498851192e+19</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
       </c>
       <c r="AF54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>https://elitemed.co.il/doctors/dr-yael-cohen-hebrew/</t>
+          <t>https://www.eryaveladan.com/</t>
         </is>
       </c>
       <c r="AI54" t="inlineStr"/>
       <c r="AJ54" t="inlineStr"/>
       <c r="AK54" t="inlineStr"/>
-      <c r="AL54" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM54" t="b">
-        <v>1</v>
-      </c>
-      <c r="AN54" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>ד"ר יעל כהן - elitemed.co.il ד"ר יעל כהן - elitemed.co.il דלג לתוכן Facebook Instagram Whatsapp Office@elitemed.co.il 073-321-4181 בית אודות רופאים שירותים רפואיים אולטרסאונד וביופסיות אוסטאופתיה אורולוגיה אורתופדיה אלרגיה ואימונולגיה אנדוקרינולוגיה סוכרת וירידה במשקל אסתטיקה אף אוזן גרון גינקולוגיה ובריאות האישה גסטרואנטרולוגיה גֵרִיאַטרִיָה דרמטולגיה המטולוגיה כלי דם ורדיולוגיה פולשנית התמחויות טיפוליות ושיקומיות כירורגיה כירורגיה פלסטית מרפאת כאב נוירולוגיה, קשב וריכוז והתפתחות הילד נפרולוגיה ויתר לחץ דם סקירות מערכות ואקו לב עובר עיניים פודיאטריה כירורגית וכף רגל פולמונולוגיה ורפואת שינה פסיכיאטריה פרוקטולוגיה וכירורגיה קולורקטלית קרדיולוגיה ואלקטרופיזיולוגיה ראומטולוגיה רפואת ילדים מומחית רפואת ספורט ופיזיותרפיה רפואה תעסוקתית תזונה קלינית ודיאטה תור דחוף  24-48 שעות צור קשר השכרת קליניקה במודיעין שירות VIP שירותים מידע רפואי בית אודות רופאים שירותים רפואיים אולטרסאונד וביופסיות אוסטאופתיה אורולוגיה אורתופדיה אלרגיה ואימונולגיה אנדוקרינולוגיה סוכרת וירידה במשקל אסתטיקה אף אוזן גרון גינקולוגיה ובריאות האישה גס</t>
-        </is>
-      </c>
-      <c r="AP54" t="inlineStr"/>
+      <c r="AL54" t="inlineStr"/>
+      <c r="AM54" t="inlineStr"/>
+      <c r="AN54" t="inlineStr"/>
+      <c r="AO54" t="inlineStr"/>
+      <c r="AP54" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ54" t="inlineStr"/>
       <c r="AR54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS54" t="b">
         <v>0</v>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>מאיה שרון וינר</t>
+          <t>יעל כהן</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9342,7 +9342,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>clinic@drmayasharonweiner.com</t>
+          <t>office@elitemed.co.il</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://www.drmayasharonweiner.com/</t>
+          <t>https://elitemed.co.il/doctors/dr-yael-cohen-hebrew/</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -9365,12 +9365,12 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>אני איתך במסע הזה. הצעד הראשון שלך מתחיל כאן. ד"ר מאיה שרון-וינר רופאת נשים מומחית בפריון והפריה חוץ גופית מיילדות וגינקולוגיה לקביעת פגישה © 2026 כל הזכויות שמורות לד"ר מאיה שרון-וינר הברזל 9א', רמת החייל ווטסאפ למרפאה clinic@drmayasharonweiner.com פוריות האישה והגבר טיפולי פוריות הפריה חוץ גופית ו-PGD שימור פוריות פוריות לאחר סרטן ובנשאיות BRCA מעקב וליווי הריון גינקולוגיה כללית Menu Close אודות יצירת קשר מדיניות פרטיות הצהרת נגישות M</t>
+          <t>ד"ר יעל כהן - elitemed.co.il דלג לתוכן Facebook Instagram Whatsapp Office@elitemed.co.il 073-321-4181 בית אודות רופאים שירותים רפואיים אולטרסאונד וביופסיות אוסטאופתיה אורולוגיה אורתופדיה אלרגיה ואימונולגיה אנדוקרינולוגיה סוכרת וירידה במשקל אסתטיקה אף אוזן גרון גינקולוגיה ובריאות האישה ג</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>"מאיה שרון וינר"</t>
+          <t>"יעל כהן" יילוד</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -9387,64 +9387,72 @@
         <v>1</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-09-04T17:43:40.101946+00:00</t>
+          <t>2026-09-10T18:33:08.486465+00:00</t>
         </is>
       </c>
       <c r="W55" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="X55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z55" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>["https://www.drmayasharonweiner.com/", "https://www.drmayasharonweiner.com/about", "https://www.drmayasharonweiner.com/contact", "https://www.medreviews.co.il/provider/dr-sharon-weiner-maya", "https://www.medreviews.co.il/provider/dr-sharon-weiner-maya/treatment", "https://www.doctorita.co.il/experts/119120", "https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr_maya_sharonweiner%2F&amp;is_from_rle", "https://docsrated.com/doctors/מאיה-שרון-וינר"]</t>
+          <t>["https://elitemed.co.il/doctors/dr-yael-cohen-hebrew/", "https://elitemed.co.il/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%A4%D7%95%D7%90%D7%99-%D7%A4%D7%A8%D7%98%D7%99-%D7%91%D7%9E%D7%95%D7%93%D7%99%D7%A2%D7%99%D7%9F/", "https://elitemed.co.il/pain-clinic-modiin/", "https://elitemed.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://elitemed.co.il/%d7%90%d7%95%d6%b9%d7%93%d7%95%d6%b9%d7%aa/", "https://medpage.co.il/doctors/יעל-כהן-23202/", "https://medpage.co.il/doctors/%D7%99%D7%A2%D7%9C-%D7%9B%D7%94%D7%9F-23202/", "https://www.facebook.com/ichilovmedical/posts/תכירו-את-פרופ-יעל-כהןמנהלת-יחידת-המיאלומה-במערך-ההמטולוגי-של-איכילוב-ואחת-מהרופא/1288268913309017/", "https://www.facebook.com/ichilovmedical/videos/%D7%AA%D7%9B%D7%99%D7%A8%D7%95-%D7%90%D7%AA-%D7%A4%D7%A8%D7%95%D7%A4-%D7%99%D7%A2%D7%9C-%D7%9B%D7%94%D7%9F%D7%9E%D7%A0%D7%94%D7%9C%D7%AA-%D7%99%D7%97%D7%99%D7%93%D7%AA-%D7%94%D7%9E%D7%99%D7%90%D7%9C%D7%95%D7%9E%D7%94-%D7%91%D7%9E%D7%A2%D7%A8%D7%9A-%D7%94%D7%94%D7%9E%D7%98%D7%95%D7%9C%D7%95%D7%92%D7%99-%D7%A9%D7%9C-%D7%90%D7%99%D7%9B%D7%99%D7%9C%D7%95%D7%91-%D7%95%D7%90%D7%97%D7%AA-%D7%9E%D7%94%D7%A8%D7%95%D7%A4%D7%90/981973987039095/", "https://www.medico.co.il/doctors/פרופ-יעל-כהן/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%99%D7%A2%D7%9C-%D7%9B%D7%94%D7%9F/", "https://www.medico.co.il/doctors/", "https://www.medico.co.il/doctors/%d7%a4%d7%a8%d7%95%d7%a4-%d7%99%d7%a2%d7%9c-%d7%9b%d7%94%d7%9f/", "https://www.tasmc.org.il/doctorssearch/dr/cohen-yael/", "https://www.szmc.org.il/doctors/cohen-yael/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.vimed.co.il/users/0918fba4-bd6a-4310-ab8f-b51cab0b8f80", "https://www.meuhedet.co.il/poi/ParamedicalDoctors/000189680918100097000000000000_0", "https://www.medreviews.co.il/provider/dr-cohen-yael"]</t>
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>3.703569684118546e+18</v>
+        <v>1.111084801504876e+19</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>https://www.drmayasharonweiner.com/</t>
+          <t>https://elitemed.co.il/doctors/dr-yael-cohen-hebrew/</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr"/>
       <c r="AJ55" t="inlineStr"/>
       <c r="AK55" t="inlineStr"/>
-      <c r="AL55" t="inlineStr"/>
-      <c r="AM55" t="inlineStr"/>
-      <c r="AN55" t="inlineStr"/>
-      <c r="AO55" t="inlineStr"/>
-      <c r="AP55" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL55" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM55" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN55" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>ד"ר יעל כהן - elitemed.co.il ד"ר יעל כהן - elitemed.co.il דלג לתוכן Facebook Instagram Whatsapp Office@elitemed.co.il 073-321-4181 בית אודות רופאים שירותים רפואיים אולטרסאונד וביופסיות אוסטאופתיה אורולוגיה אורתופדיה אלרגיה ואימונולגיה אנדוקרינולוגיה סוכרת וירידה במשקל אסתטיקה אף אוזן גרון גינקולוגיה ובריאות האישה גסטרואנטרולוגיה גֵרִיאַטרִיָה דרמטולגיה המטולוגיה כלי דם ורדיולוגיה פולשנית התמחויות טיפוליות ושיקומיות כירורגיה כירורגיה פלסטית מרפאת כאב נוירולוגיה, קשב וריכוז והתפתחות הילד נפרולוגיה ויתר לחץ דם סקירות מערכות ואקו לב עובר עיניים פודיאטריה כירורגית וכף רגל פולמונולוגיה ורפואת שינה פסיכיאטריה פרוקטולוגיה וכירורגיה קולורקטלית קרדיולוגיה ואלקטרופיזיולוגיה ראומטולוגיה רפואת ילדים מומחית רפואת ספורט ופיזיותרפיה רפואה תעסוקתית תזונה קלינית ודיאטה תור דחוף  24-48 שעות צור קשר השכרת קליניקה במודיעין שירות VIP שירותים מידע רפואי בית אודות רופאים שירותים רפואיים אולטרסאונד וביופסיות אוסטאופתיה אורולוגיה אורתופדיה אלרגיה ואימונולגיה אנדוקרינולוגיה סוכרת וירידה במשקל אסתטיקה אף אוזן גרון גינקולוגיה ובריאות האישה גס</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr"/>
       <c r="AQ55" t="inlineStr"/>
       <c r="AR55" t="n">
         <v>1</v>
@@ -9473,7 +9481,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>מנחם נוימן</t>
+          <t>מאיה שרון וינר</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9504,7 +9512,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>hello@professorneuman.com</t>
+          <t>clinic@drmayasharonweiner.com</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -9517,7 +9525,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://professorneuman.com/he/</t>
+          <t>https://www.drmayasharonweiner.com/</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -9527,12 +9535,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>פרופ׳ מנחם נוימן — אורוגינקולוגיה ורפואת רצפת האגן מגדל סוזוקי, קומה 4, רח׳ יגאל אלון 82, תל אביב 054-644-2060 · hello@professorneuman.com ראשי מידע לרופאים מידע למטופלות מהתקשורת צרי קשר English פרופ׳ מנחם נוימן אורוגינקולוגיה ורפואת רצפת האגן צניחת איברי האגן ודליפת שתן הן מהתופעות השכיחות ביותר בקרב נשים — וגם מהניתנות ביותר לטי</t>
+          <t>אני איתך במסע הזה. הצעד הראשון שלך מתחיל כאן. ד"ר מאיה שרון-וינר רופאת נשים מומחית בפריון והפריה חוץ גופית מיילדות וגינקולוגיה לקביעת פגישה © 2026 כל הזכויות שמורות לד"ר מאיה שרון-וינר הברזל 9א', רמת החייל ווטסאפ למרפאה clinic@drmayasharonweiner.com פוריות האישה והגבר טיפולי פוריות הפריה חוץ גופית ו-PGD שימור פוריות פוריות לאחר סרטן ובנשאיות BRCA מעקב וליווי הריון גינקולוגיה כללית Menu Close אודות יצירת קשר מדיניות פרטיות הצהרת נגישות M</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>"מנחם נוימן"</t>
+          <t>"מאיה שרון וינר"</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -9542,11 +9550,11 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>[{"email": "info@raphaelhospitals.co.il", "confidence": 80, "source_url": "https://www.raphaelhospitals.co.il/en/international-department/about/", "identity_url": "https://www.raphaelhospitals.co.il/doctors/neuman-menahem/", "evidence": "info@raphaelhospitals.co.il", "matched_query": "\"מנחם נוימן\"", "extraction_method": "linked_mailto"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T56" t="n">
         <v>0</v>
@@ -9554,36 +9562,36 @@
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-09-04T18:20:49.705154+00:00</t>
+          <t>2026-09-04T17:43:40.101946+00:00</t>
         </is>
       </c>
       <c r="W56" t="n">
         <v>2</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y56" t="n">
         <v>7</v>
       </c>
       <c r="Z56" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>["https://professorneuman.com/", "https://professorneuman.com/he/", "https://professorneuman.com/he/contact", "https://professorneuman.com/en/contact", "https://www.facebook.com/public/%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/", "https://www.facebook.com/people/%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/pfbid0371mkxMbe96MNN5gS9XHB7KqrSyxJnXyG9AsLfdZV7j8RjCKyjm8cEEVgjSreLhY8l/", "https://chabadpedia.co.il/wiki/%D7%9E%D7%A0%D7%97%D7%9D_%D7%A0%D7%95%D7%99%D7%9E%D7%9F", "https://www.raphaelhospitals.co.il/doctors/neuman-menahem/", "https://www.raphaelhospitals.co.il/about/aboutus/", "https://www.raphaelhospitals.co.il/fields/endoscopic-unit/about/", "https://www.raphaelhospitals.co.il/fields/pain-clinic/about/", "https://www.raphaelhospitals.co.il/en/international-department/about/", "https://www.raphaelhospitals.co.il/fields/heart-catheterization-clinic/about/", "https://www.raphaelhospitals.co.il/en/about/aboutus/", "https://www.raphaelhospitals.co.il/en/contact/"]</t>
+          <t>["https://www.drmayasharonweiner.com/", "https://www.drmayasharonweiner.com/about", "https://www.drmayasharonweiner.com/contact", "https://www.medreviews.co.il/provider/dr-sharon-weiner-maya", "https://www.medreviews.co.il/provider/dr-sharon-weiner-maya/treatment", "https://www.doctorita.co.il/experts/119120", "https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr_maya_sharonweiner%2F&amp;is_from_rle", "https://docsrated.com/doctors/מאיה-שרון-וינר"]</t>
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>3.703569684118546e+18</v>
+        <v>1.111070905235564e+19</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9594,7 +9602,7 @@
       <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>https://professorneuman.com/he/</t>
+          <t>https://www.drmayasharonweiner.com/</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr"/>
@@ -9635,7 +9643,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>נעמה מימון</t>
+          <t>מנחם נוימן</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9666,7 +9674,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>office@medicaltop.co.il</t>
+          <t>hello@professorneuman.com</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -9679,7 +9687,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/</t>
+          <t>https://professorneuman.com/he/</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -9689,12 +9697,12 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t xml:space="preserve">ד"ר נעמה מימון: מומחית ברפואת נשים - MedicalTop Search Close Facebook 073-3310444 סנטר הגליל רחוב האגס 1, שער הרימון, קומה שניה. ראש פינה. office@medicaltop.co.il לקביעת תור דף הבית אודות תחומי פעילות הצוות שלנו יצירת קשר Menu דף הבית אודות תחומי פעילות הצוות שלנו יצירת קשר ד"ר נעמה מימון: מומחית ברפואת נשים דף הבית / רופאים / ד"ר נעמה מימון: מומחית ברפואת </t>
+          <t>פרופ׳ מנחם נוימן — אורוגינקולוגיה ורפואת רצפת האגן מגדל סוזוקי, קומה 4, רח׳ יגאל אלון 82, תל אביב 054-644-2060 · hello@professorneuman.com ראשי מידע לרופאים מידע למטופלות מהתקשורת צרי קשר English פרופ׳ מנחם נוימן אורוגינקולוגיה ורפואת רצפת האגן צניחת איברי האגן ודליפת שתן הן מהתופעות השכיחות ביותר בקרב נשים — וגם מהניתנות ביותר לטי</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>"נעמה מימון"</t>
+          <t>"מנחם נוימן"</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -9704,32 +9712,32 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "info@raphaelhospitals.co.il", "confidence": 80, "source_url": "https://www.raphaelhospitals.co.il/en/international-department/about/", "identity_url": "https://www.raphaelhospitals.co.il/doctors/neuman-menahem/", "evidence": "info@raphaelhospitals.co.il", "matched_query": "\"מנחם נוימן\"", "extraction_method": "linked_mailto"}]</t>
         </is>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-09-04T05:17:30.924388+00:00</t>
+          <t>2026-09-04T18:20:49.705154+00:00</t>
         </is>
       </c>
       <c r="W57" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X57" t="n">
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z57" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -9741,14 +9749,14 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>["https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fn.mh.mymwn.2025%2F", "https://www.facebook.com/SNMaesthetic/services/", "https://www.doctorita.co.il/experts/152626", "https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/", "https://medicaltop.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://medicaltop.co.il/%D7%94%D7%A6%D7%95%D7%95%D7%AA-%D7%A9%D7%9C%D7%A0%D7%95/", "https://medicaltop.co.il/wp-content/uploads/2024/04/אודות.jpg"]</t>
+          <t>["https://professorneuman.com/", "https://professorneuman.com/he/", "https://professorneuman.com/he/contact", "https://professorneuman.com/en/contact", "https://www.facebook.com/public/%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/", "https://www.facebook.com/people/%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/pfbid0371mkxMbe96MNN5gS9XHB7KqrSyxJnXyG9AsLfdZV7j8RjCKyjm8cEEVgjSreLhY8l/", "https://chabadpedia.co.il/wiki/%D7%9E%D7%A0%D7%97%D7%9D_%D7%A0%D7%95%D7%99%D7%9E%D7%9F", "https://www.raphaelhospitals.co.il/doctors/neuman-menahem/", "https://www.raphaelhospitals.co.il/about/aboutus/", "https://www.raphaelhospitals.co.il/fields/endoscopic-unit/about/", "https://www.raphaelhospitals.co.il/fields/pain-clinic/about/", "https://www.raphaelhospitals.co.il/en/international-department/about/", "https://www.raphaelhospitals.co.il/fields/heart-catheterization-clinic/about/", "https://www.raphaelhospitals.co.il/en/about/aboutus/", "https://www.raphaelhospitals.co.il/en/contact/"]</t>
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>3.61338936839023e+18</v>
+        <v>1.111070905235564e+19</v>
       </c>
       <c r="AE57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF57" t="n">
         <v>0</v>
@@ -9756,7 +9764,7 @@
       <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/</t>
+          <t>https://professorneuman.com/he/</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr"/>
@@ -9774,7 +9782,7 @@
         <v>1</v>
       </c>
       <c r="AS57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT57" t="b">
         <v>1</v>
@@ -9797,7 +9805,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>תמר גרין</t>
+          <t>נעמה מימון</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9828,7 +9836,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>office@keshet-refua.co.il</t>
+          <t>office@medicaltop.co.il</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -9841,7 +9849,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://keshet-refua.co.il/doctors/dr-tamar-green/</t>
+          <t>https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -9851,17 +9859,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>פיזיותרפיה אסתטיקה פודקסטים קליניקות וססיות להשכרה צור קשר זימון תור ד"ר תמר גרין מומחית לגינקולוגיה ומיילדות מעקב הריון, סקירת הריון מוקדמת ומאוחרת, בדיקות אולטרסאונד אבחנתיות, גיל המעבר ובדיקות גינקולוגיות 073-3214111 office@keshet-refua.co.il לזימון תור &gt; תחומי מומחיות מעקב הריון בדיקות אולטרהסאונד אבחנתיות שקיפות עורפית סקירת מערכות מוקדמת ומאוחרת מעקבי גדילה הדמיית אגן והדמיה תלת מימדית של הרחם טיפולי גינקולוגיה פרטית התקנים תוך רח</t>
+          <t xml:space="preserve">ד"ר נעמה מימון: מומחית ברפואת נשים - MedicalTop Search Close Facebook 073-3310444 סנטר הגליל רחוב האגס 1, שער הרימון, קומה שניה. ראש פינה. office@medicaltop.co.il לקביעת תור דף הבית אודות תחומי פעילות הצוות שלנו יצירת קשר Menu דף הבית אודות תחומי פעילות הצוות שלנו יצירת קשר ד"ר נעמה מימון: מומחית ברפואת נשים דף הבית / רופאים / ד"ר נעמה מימון: מומחית ברפואת </t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>"תמר גרין"</t>
+          <t>"נעמה מימון"</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>official_text</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -9878,39 +9886,39 @@
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-09-05T00:09:39.798497+00:00</t>
+          <t>2026-09-04T05:17:30.924388+00:00</t>
         </is>
       </c>
       <c r="W58" t="n">
+        <v>4</v>
+      </c>
+      <c r="X58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>["https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fn.mh.mymwn.2025%2F", "https://www.facebook.com/SNMaesthetic/services/", "https://www.doctorita.co.il/experts/152626", "https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/", "https://medicaltop.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://medicaltop.co.il/%D7%94%D7%A6%D7%95%D7%95%D7%AA-%D7%A9%D7%9C%D7%A0%D7%95/", "https://medicaltop.co.il/wp-content/uploads/2024/04/אודות.jpg"]</t>
+        </is>
+      </c>
+      <c r="AD58" t="n">
+        <v>1.084016810517069e+19</v>
+      </c>
+      <c r="AE58" t="n">
         <v>2</v>
-      </c>
-      <c r="X58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>ddgs:bing</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>["https://www.medreviews.co.il/provider/dr-green-tamar", "https://keshet-refua.co.il/doctors/dr-tamar-green/", "https://keshet-refua.co.il/about-us/", "https://keshet-refua.co.il/contact-us/", "https://keshet-refua.co.il/clinics-for-rent-sessional-clinics-for-rent/", "https://keshet-refua.co.il/about-us/#contact-keshet-medical-center", "https://keshet-refua.co.il/areas_of_expertise/child-psychology-clinic/", "https://keshet-refua.co.il/doctors/private-clinical-dietician-jerusalem/", "https://keshet-refua.co.il/contact-us/#contact-keshet-medical-center", "https://keshet-refua.co.il/clinics-for-rent-sessional-clinics-for-rent/#contact-keshet-medical-center", "https://keshet-refua.co.il/doctors/dr-tamar-green-private-gynecologist-in-jerusalem/", "https://wayzee.co.il/", "https://keshet-refua.co.il/treatments/menstrual-arrangement-before-the-wedding-private-womens-clinic-private-gynecologist/", "https://keshet-refua.co.il/areas_of_expertise/child-psychology-clinic/#contact-keshet-medical-center", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2F61558661827898%2F", "https://www.facebook.com/public/%D7%AA%D7%9E%D7%A8-%D7%92%D7%A8%D7%99%D7%9F/", "https://www.medreviews.co.il/provider/dr-green-tamar/treatment/gynecologist-clinic", "https://www.szmc.org.il/doctors/grin-tamar/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
-        </is>
-      </c>
-      <c r="AD58" t="n">
-        <v>3.606114548260412e+18</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>1</v>
       </c>
       <c r="AF58" t="n">
         <v>0</v>
@@ -9918,7 +9926,7 @@
       <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>https://keshet-refua.co.il/doctors/dr-tamar-green/</t>
+          <t>https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/</t>
         </is>
       </c>
       <c r="AI58" t="inlineStr"/>
@@ -9936,7 +9944,7 @@
         <v>1</v>
       </c>
       <c r="AS58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT58" t="b">
         <v>1</v>
@@ -9959,7 +9967,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>אבי צפריר</t>
+          <t>תמר גרין</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9990,7 +9998,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>ivfrec@szmc.org.il</t>
+          <t>office@keshet-refua.co.il</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -9999,11 +10007,11 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/tsafrir-avi/</t>
+          <t>https://keshet-refua.co.il/doctors/dr-tamar-green/</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -10013,17 +10021,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t xml:space="preserve">h عربيه Русский צרו קשר צרו קשר אזור אישי אזור אישי רופאים בשערי צדק ד"ר  אבי צפריר רופא בכיר Dr.  Avi Tsafrir התמחות: גינקולוגיה ויילוד תת התמחות: הפריה חוץ גופית תחומים נוספים: שימור פוריות פוריות הגבר פוריות האשה עוד ivfrec@szmc.org.il ivfrec@szmc.org.il נסיון מקצועי מומחה ביילוד ובגינקולוגיה משנת 2005 רופא בכיר להפריה חוץ גופית בשערי צדק משנת 2005 תפקידים ציבוריים חבר ועד האגודה הישראלית לחקר הפוריות משנת 2022 לימודים והכשרה פקולטה </t>
+          <t>פיזיותרפיה אסתטיקה פודקסטים קליניקות וססיות להשכרה צור קשר זימון תור ד"ר תמר גרין מומחית לגינקולוגיה ומיילדות מעקב הריון, סקירת הריון מוקדמת ומאוחרת, בדיקות אולטרסאונד אבחנתיות, גיל המעבר ובדיקות גינקולוגיות 073-3214111 office@keshet-refua.co.il לזימון תור &gt; תחומי מומחיות מעקב הריון בדיקות אולטרהסאונד אבחנתיות שקיפות עורפית סקירת מערכות מוקדמת ומאוחרת מעקבי גדילה הדמיית אגן והדמיה תלת מימדית של הרחם טיפולי גינקולוגיה פרטית התקנים תוך רח</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>"אבי צפריר"</t>
+          <t>"תמר גרין"</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>official_text</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -10040,11 +10048,11 @@
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-09-03T20:26:52.799327+00:00</t>
+          <t>2026-09-05T00:09:39.798497+00:00</t>
         </is>
       </c>
       <c r="W59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X59" t="n">
         <v>0</v>
@@ -10056,7 +10064,7 @@
         <v>6</v>
       </c>
       <c r="AA59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
@@ -10065,14 +10073,14 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>["https://www.infomed.co.il/experts/73913/", "https://he.hadassah.org.il/doctor/dr-avi-tsafrir-gaadaabqaa2aaoiag4adaabyaa======/", "https://www.doctors.co.il/expert/obstetrics-and-gynecologists/80043972/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fbyzpryr%2F", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A6%D7%A4%D7%A8%D7%99%D7%A8-%D7%90%D7%91%D7%99/", "https://drtor.co.il/doctor/3910", "https://www.szmc.org.il/doctors/tsafrir-avi/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.clalit.co.il/he/sefersherut/pages/doctordetails.aspx", "https://docsrated.com/doctors/אבי-צפריר", "https://www.doctorita.co.il/experts/44804"]</t>
+          <t>["https://www.medreviews.co.il/provider/dr-green-tamar", "https://keshet-refua.co.il/doctors/dr-tamar-green/", "https://keshet-refua.co.il/about-us/", "https://keshet-refua.co.il/contact-us/", "https://keshet-refua.co.il/clinics-for-rent-sessional-clinics-for-rent/", "https://keshet-refua.co.il/about-us/#contact-keshet-medical-center", "https://keshet-refua.co.il/areas_of_expertise/child-psychology-clinic/", "https://keshet-refua.co.il/doctors/private-clinical-dietician-jerusalem/", "https://keshet-refua.co.il/contact-us/#contact-keshet-medical-center", "https://keshet-refua.co.il/clinics-for-rent-sessional-clinics-for-rent/#contact-keshet-medical-center", "https://keshet-refua.co.il/doctors/dr-tamar-green-private-gynecologist-in-jerusalem/", "https://wayzee.co.il/", "https://keshet-refua.co.il/treatments/menstrual-arrangement-before-the-wedding-private-womens-clinic-private-gynecologist/", "https://keshet-refua.co.il/areas_of_expertise/child-psychology-clinic/#contact-keshet-medical-center", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2F61558661827898%2F", "https://www.facebook.com/public/%D7%AA%D7%9E%D7%A8-%D7%92%D7%A8%D7%99%D7%9F/", "https://www.medreviews.co.il/provider/dr-green-tamar/treatment/gynecologist-clinic", "https://www.szmc.org.il/doctors/grin-tamar/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>4.803028329633112e+18</v>
+        <v>1.081834364478124e+19</v>
       </c>
       <c r="AE59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF59" t="n">
         <v>0</v>
@@ -10080,7 +10088,7 @@
       <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/tsafrir-avi/</t>
+          <t>https://keshet-refua.co.il/doctors/dr-tamar-green/</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr"/>
@@ -10098,7 +10106,7 @@
         <v>1</v>
       </c>
       <c r="AS59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT59" t="b">
         <v>1</v>
@@ -10121,17 +10129,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>אירינה דורפמן אלמוג</t>
+          <t>אבי צפריר</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>family_doctor</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -10152,20 +10160,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>dr.irenadorfman@gmail.com</t>
+          <t>ivfrec@szmc.org.il</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
+          <t>https://www.szmc.org.il/doctors/tsafrir-avi/</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -10175,12 +10183,12 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>מוג אירינה כרטיס עסק: ד"ר דורפמן אלמוג אירינה » תחום פעילות: בריאות וספורט » רופא » תאור העסק: רופאת משפחה עצמאית קופת חולים לאומית. » איש קשר: אירנה דורפמן » טלפונים: טלפון: 077-7997456 נייד: 054-4616457 » אתר: » מייל: dr.irenadorfman@gmail.com » כתובת: בן גוריון 123 יהוד, מיקוד: 56209 כלים מחשבונים לעסקים מדריכי ניהול עסק, הקמת עסק נושאי האתר הנהלת חשבונות הפקת חשבוניות חשבונית אלקטרונית ניהול לקוחות שותפים עסקיים אילת סיטי - מדריך הע</t>
+          <t xml:space="preserve">h عربيه Русский צרו קשר צרו קשר אזור אישי אזור אישי רופאים בשערי צדק ד"ר  אבי צפריר רופא בכיר Dr.  Avi Tsafrir התמחות: גינקולוגיה ויילוד תת התמחות: הפריה חוץ גופית תחומים נוספים: שימור פוריות פוריות הגבר פוריות האשה עוד ivfrec@szmc.org.il ivfrec@szmc.org.il נסיון מקצועי מומחה ביילוד ובגינקולוגיה משנת 2005 רופא בכיר להפריה חוץ גופית בשערי צדק משנת 2005 תפקידים ציבוריים חבר ועד האגודה הישראלית לחקר הפוריות משנת 2022 לימודים והכשרה פקולטה </t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>"אירינה דורפמן אלמוג"</t>
+          <t>"אבי צפריר"</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -10190,32 +10198,32 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>[{"email": "info@flex.co.il", "confidence": 80, "source_url": "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "identity_url": "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "evidence": "info@flex.co.il", "matched_query": "\"אירינה דורפמן אלמוג\"", "extraction_method": "linked_mailto"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-09-04T19:17:26.299485+00:00</t>
+          <t>2026-09-03T20:26:52.799327+00:00</t>
         </is>
       </c>
       <c r="W60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z60" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AA60" t="n">
         <v>2</v>
@@ -10227,14 +10235,14 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>["https://www.dunsguide.co.il/C7195b21475cb11a3e5b86def04a3e20c_רופאים/דורפמן_אלמוג_אירינה/", "https://medpage.co.il/doctors/%D7%90%D7%99%D7%A8%D7%A0%D7%94-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-20871/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94/", "https://www.beok.co.il/doctors/Doctors-129241/", "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "https://www.flex.co.il/100_General/005_GeneralPages/006_About.aspx", "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "https://www.flex.co.il/100_General/900_DifferentStuff/900_ForTheCommunity.aspx"]</t>
+          <t>["https://www.infomed.co.il/experts/73913/", "https://he.hadassah.org.il/doctor/dr-avi-tsafrir-gaadaabqaa2aaoiag4adaabyaa======/", "https://www.doctors.co.il/expert/obstetrics-and-gynecologists/80043972/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fbyzpryr%2F", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A6%D7%A4%D7%A8%D7%99%D7%A8-%D7%90%D7%91%D7%99/", "https://drtor.co.il/doctor/3910", "https://www.szmc.org.il/doctors/tsafrir-avi/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.clalit.co.il/he/sefersherut/pages/doctordetails.aspx", "https://docsrated.com/doctors/אבי-צפריר", "https://www.doctorita.co.il/experts/44804"]</t>
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>3.902872299986166e+18</v>
+        <v>1.440908498889934e+19</v>
       </c>
       <c r="AE60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF60" t="n">
         <v>0</v>
@@ -10242,7 +10250,7 @@
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
+          <t>https://www.szmc.org.il/doctors/tsafrir-avi/</t>
         </is>
       </c>
       <c r="AI60" t="inlineStr"/>
@@ -10260,17 +10268,17 @@
         <v>1</v>
       </c>
       <c r="AS60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT60" t="b">
         <v>1</v>
       </c>
       <c r="AU60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>PERSON</t>
+          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10291,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>אלון שלב</t>
+          <t>אירינה דורפמן אלמוג</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10314,7 +10322,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>alonshalev31@gmail.com</t>
+          <t>dr.irenadorfman@gmail.com</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -10327,7 +10335,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://pain.coi.co.il/</t>
+          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -10337,12 +10345,12 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>הודעה לבעלי האתר תקופת הניסיון הסתיימה, יש ליצור מנוי דרך ממשק ניהול האתר. האתר נכנס לרשימת המחיקה ויימחק בקרוב לחץ כאן אם אינך זוכר את כתובת ממשק ניהול האתר שלך. דר אלון שלב - רופא כאב טלפון: 054-6221105 מייל: alonshalev31@gmail.com כתובת: ילדי טהרן 8, ראשון לציון ד"ר אלון שלב מומחה ברפואת המשפחה רופא כאב דף הבית אודות צור קשר אל תחכו - הזמינו תור לרופא עוד היום.. לייעוץ ראשוני ללא עלות והזמנת תורים מלאו פרטים או התקשרו: 05462</t>
+          <t>מוג אירינה כרטיס עסק: ד"ר דורפמן אלמוג אירינה » תחום פעילות: בריאות וספורט » רופא » תאור העסק: רופאת משפחה עצמאית קופת חולים לאומית. » איש קשר: אירנה דורפמן » טלפונים: טלפון: 077-7997456 נייד: 054-4616457 » אתר: » מייל: dr.irenadorfman@gmail.com » כתובת: בן גוריון 123 יהוד, מיקוד: 56209 כלים מחשבונים לעסקים מדריכי ניהול עסק, הקמת עסק נושאי האתר הנהלת חשבונות הפקת חשבוניות חשבונית אלקטרונית ניהול לקוחות שותפים עסקיים אילת סיטי - מדריך הע</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>"אלון שלב"</t>
+          <t>"אירינה דורפמן אלמוג"</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -10352,11 +10360,11 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "info@flex.co.il", "confidence": 80, "source_url": "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "identity_url": "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "evidence": "info@flex.co.il", "matched_query": "\"אירינה דורפמן אלמוג\"", "extraction_method": "linked_mailto"}]</t>
         </is>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T61" t="n">
         <v>0</v>
@@ -10364,23 +10372,23 @@
       <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-09-04T19:37:15.755041+00:00</t>
+          <t>2026-09-04T19:17:26.299485+00:00</t>
         </is>
       </c>
       <c r="W61" t="n">
         <v>2</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z61" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
@@ -10389,11 +10397,11 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>["https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr.shalev.pain%2F&amp;is_from_rle", "https://www.bgu.ac.il/people/shalevn/", "https://www.bgu.ac.il/en/people/shalevn/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fdr.shalev.pain%2F", "https://www.medreviews.co.il/search/pain-management/center/rishon-lezion", "https://pain.coi.co.il/", "https://pain.coi.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA.htm", "https://pain.coi.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8.htm"]</t>
+          <t>["https://www.dunsguide.co.il/C7195b21475cb11a3e5b86def04a3e20c_רופאים/דורפמן_אלמוג_אירינה/", "https://medpage.co.il/doctors/%D7%90%D7%99%D7%A8%D7%A0%D7%94-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-20871/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94/", "https://www.beok.co.il/doctors/Doctors-129241/", "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "https://www.flex.co.il/100_General/005_GeneralPages/006_About.aspx", "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "https://www.flex.co.il/100_General/900_DifferentStuff/900_ForTheCommunity.aspx"]</t>
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>3.902872299986166e+18</v>
+        <v>1.17086168999585e+19</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10404,7 +10412,7 @@
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>https://pain.coi.co.il/</t>
+          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
         </is>
       </c>
       <c r="AI61" t="inlineStr"/>
@@ -10445,7 +10453,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>אמיר צבעוני</t>
+          <t>אלון שלב</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10476,7 +10484,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>healtms@gmail.com</t>
+          <t>alonshalev31@gmail.com</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -10489,7 +10497,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://www.drzivony.co.il/</t>
+          <t>https://pain.coi.co.il/</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -10499,12 +10507,12 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>"ר אמיר צבעוני ד"ר אמיר צבעוני רופא משפחה מומחה העוסק בטיפול בכאב כרוני בגישת גוף-נפש ללא שימוש בתרופות או בפרוצדורות רפואיות. הטיפול מבוסס מחקר בתחום מדעי המח והכאב. ניתן לקרוא עליי עוד ב דף האודות . טלפון: 051-2303120 healtms@gmail.com קליניקה בגבעת עדה (סמוך לבנימינה) ניתן ליצור איתי קשר גם ב דף יצירת הקשר פוסטים אחרונים על הענק הירוק והדחקת רגשות לאותת עם המגבים רגישות יתר לאחר פציעה אזהרת טריגר בקשת סליחה מעצמי חפש: חיפוש בית אודות</t>
+          <t>הודעה לבעלי האתר תקופת הניסיון הסתיימה, יש ליצור מנוי דרך ממשק ניהול האתר. האתר נכנס לרשימת המחיקה ויימחק בקרוב לחץ כאן אם אינך זוכר את כתובת ממשק ניהול האתר שלך. דר אלון שלב - רופא כאב טלפון: 054-6221105 מייל: alonshalev31@gmail.com כתובת: ילדי טהרן 8, ראשון לציון ד"ר אלון שלב מומחה ברפואת המשפחה רופא כאב דף הבית אודות צור קשר אל תחכו - הזמינו תור לרופא עוד היום.. לייעוץ ראשוני ללא עלות והזמנת תורים מלאו פרטים או התקשרו: 05462</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>"אמיר צבעוני"</t>
+          <t>"אלון שלב"</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -10526,7 +10534,7 @@
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-09-03T23:00:56.706890+00:00</t>
+          <t>2026-09-04T19:37:15.755041+00:00</t>
         </is>
       </c>
       <c r="W62" t="n">
@@ -10536,10 +10544,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Z62" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -10551,11 +10559,11 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>["https://www.drzivony.co.il/", "https://www.drzivony.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
+          <t>["https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr.shalev.pain%2F&amp;is_from_rle", "https://www.bgu.ac.il/people/shalevn/", "https://www.bgu.ac.il/en/people/shalevn/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fdr.shalev.pain%2F", "https://www.medreviews.co.il/search/pain-management/center/rishon-lezion", "https://pain.coi.co.il/", "https://pain.coi.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA.htm", "https://pain.coi.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8.htm"]</t>
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>3.902460517721977e+18</v>
+        <v>1.17086168999585e+19</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10566,7 +10574,7 @@
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>https://www.drzivony.co.il/</t>
+          <t>https://pain.coi.co.il/</t>
         </is>
       </c>
       <c r="AI62" t="inlineStr"/>
@@ -10607,7 +10615,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>בתיה קורנבוים</t>
+          <t>אמיר צבעוני</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10638,7 +10646,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>batyakornboim@gmail.com</t>
+          <t>healtms@gmail.com</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -10651,7 +10659,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://www.dr-batya-kornboim.com/</t>
+          <t>https://www.drzivony.co.il/</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -10661,12 +10669,12 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>שקל בחיפה אודות חוות דעת יצירת קשר כתבות ופרסומים תפריט ד״ר בתיה קורנבוים - מומחית ברפואת משפחה ורפואת השמנה [תיאור המרפאה יתווסף בהמשך] טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו חיפה 3570901 IL 052-567-1100 batyakornboim@gmail.com התמחויות רפואיות עיקריות: [פירוט תחומי הטיפול יתווסף בהמשך] מידע מעשי: יצירת קשר: טלפון 052-567-1100 או וואטסאפ 052-567-1100 מיקום: טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו , חיפה סוג</t>
+          <t>"ר אמיר צבעוני ד"ר אמיר צבעוני רופא משפחה מומחה העוסק בטיפול בכאב כרוני בגישת גוף-נפש ללא שימוש בתרופות או בפרוצדורות רפואיות. הטיפול מבוסס מחקר בתחום מדעי המח והכאב. ניתן לקרוא עליי עוד ב דף האודות . טלפון: 051-2303120 healtms@gmail.com קליניקה בגבעת עדה (סמוך לבנימינה) ניתן ליצור איתי קשר גם ב דף יצירת הקשר פוסטים אחרונים על הענק הירוק והדחקת רגשות לאותת עם המגבים רגישות יתר לאחר פציעה אזהרת טריגר בקשת סליחה מעצמי חפש: חיפוש בית אודות</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>"בתיה קורנבוים"</t>
+          <t>"אמיר צבעוני"</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -10688,7 +10696,7 @@
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-09-03T23:52:50.148875+00:00</t>
+          <t>2026-09-03T23:00:56.706890+00:00</t>
         </is>
       </c>
       <c r="W63" t="n">
@@ -10713,11 +10721,11 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>["https://www.dr-batya-kornboim.com/", "https://www.dr-batya-kornboim.com/#%D7%90%D7%95%D7%93%D7%95%D7%AA"]</t>
+          <t>["https://www.drzivony.co.il/", "https://www.drzivony.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>3.902460517721977e+18</v>
+        <v>1.170738155316593e+19</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10728,7 +10736,7 @@
       <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>https://www.dr-batya-kornboim.com/</t>
+          <t>https://www.drzivony.co.il/</t>
         </is>
       </c>
       <c r="AI63" t="inlineStr"/>
@@ -10769,7 +10777,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>שלומית שדמון</t>
+          <t>בתיה קורנבוים</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10800,7 +10808,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>shlomitshadmon@gmail.com</t>
+          <t>batyakornboim@gmail.com</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -10813,7 +10821,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
+          <t>https://www.dr-batya-kornboim.com/</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -10823,12 +10831,12 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>ם ופעילויות כנסים והשתלמויות הרצאות מהכנסים מטפלי.ות איט"ם מטפלי.ות איט"ם פיזיותרפיסטים.ית איט"ם מרפאות ציבוריות הצטרפות והתמחות צור קשר פרטי התקשרות טלפון 054-9145177 כתובת אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אימייל shlomitshadmon@gmail.com שדמון שלומית (MD) – תל אביב מקצוע:  רופאת משפחה, מוסמכת ביעוץ וטיפול מיני. התמחות: מטפלת מינית איזור טיפול: תל אביב אודותי אני רופאת משפחה ותיקה, מדריכה קלינית ומרצה בנושאי בריאות האישה, מיניות ה</t>
+          <t>שקל בחיפה אודות חוות דעת יצירת קשר כתבות ופרסומים תפריט ד״ר בתיה קורנבוים - מומחית ברפואת משפחה ורפואת השמנה [תיאור המרפאה יתווסף בהמשך] טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו חיפה 3570901 IL 052-567-1100 batyakornboim@gmail.com התמחויות רפואיות עיקריות: [פירוט תחומי הטיפול יתווסף בהמשך] מידע מעשי: יצירת קשר: טלפון 052-567-1100 או וואטסאפ 052-567-1100 מיקום: טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו , חיפה סוג</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>"שלומית שדמון"</t>
+          <t>"בתיה קורנבוים"</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -10838,11 +10846,11 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "identity_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "evidence": "mail.com אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"שלומית שדמון\"", "extraction_method": "direct_text"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T64" t="n">
         <v>0</v>
@@ -10850,7 +10858,7 @@
       <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-09-04T15:25:57.140597+00:00</t>
+          <t>2026-09-03T23:52:50.148875+00:00</t>
         </is>
       </c>
       <c r="W64" t="n">
@@ -10860,10 +10868,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z64" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -10875,11 +10883,11 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>["https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA/", "https://moonbellboutique.com/index/%D7%93%D7%A8-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%A9%D7%93%D7%9E%D7%95%D7%9F/", "https://moonbellboutique.com/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/", "https://www.infomed.co.il/experts/145161/", "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
+          <t>["https://www.dr-batya-kornboim.com/", "https://www.dr-batya-kornboim.com/#%D7%90%D7%95%D7%93%D7%95%D7%AA"]</t>
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>3.603506593920547e+18</v>
+        <v>1.170738155316593e+19</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10890,7 +10898,7 @@
       <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
+          <t>https://www.dr-batya-kornboim.com/</t>
         </is>
       </c>
       <c r="AI64" t="inlineStr"/>
@@ -10931,7 +10939,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>שרון שלמה קלייטמן</t>
+          <t>שלומית שדמון</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10962,7 +10970,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>sharon.kleitman@gmail.com</t>
+          <t>shlomitshadmon@gmail.com</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -10975,7 +10983,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
+          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -10985,12 +10993,12 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>ש קשר שיתוף שתפו במייל שתפו בפייסבוק שתפו בטוויטר שתפו בלינקדין ד"ר שרון קלייטמן מומחה ברפואת משפחה, MST - Mind Set Technique, רפואה אינטגרטיבית, IMS - דיקור יבש, תזונה אינטגרטיבית. נייד 052-8325580 פקס 08-6560357 דוא"ל sharon.kleitman@gmail.com אתר www.integrative-med.com שלח/י לי sms פייסבוק אודות ד"ר שרון קלייטמן מומחה ברפואת משפחה, סיים את לימודי הרפואה באוניברסיטת בן גוריון, נשוי ואב לארבעה, מתגורר בקיבוץ שדה בוקר. עוסק בפיתוח והקנ</t>
+          <t>ם ופעילויות כנסים והשתלמויות הרצאות מהכנסים מטפלי.ות איט"ם מטפלי.ות איט"ם פיזיותרפיסטים.ית איט"ם מרפאות ציבוריות הצטרפות והתמחות צור קשר פרטי התקשרות טלפון 054-9145177 כתובת אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אימייל shlomitshadmon@gmail.com שדמון שלומית (MD) – תל אביב מקצוע:  רופאת משפחה, מוסמכת ביעוץ וטיפול מיני. התמחות: מטפלת מינית איזור טיפול: תל אביב אודותי אני רופאת משפחה ותיקה, מדריכה קלינית ומרצה בנושאי בריאות האישה, מיניות ה</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>"שרון שלמה קלייטמן"</t>
+          <t>"שלומית שדמון"</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -11000,11 +11008,11 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "identity_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "evidence": "mail.com אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"שלומית שדמון\"", "extraction_method": "direct_text"}]</t>
         </is>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T65" t="n">
         <v>0</v>
@@ -11012,7 +11020,7 @@
       <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-09-04T15:41:54.743203+00:00</t>
+          <t>2026-09-04T15:25:57.140597+00:00</t>
         </is>
       </c>
       <c r="W65" t="n">
@@ -11025,10 +11033,10 @@
         <v>4</v>
       </c>
       <c r="Z65" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
@@ -11037,11 +11045,11 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>["https://docsrated.com/doctors/שרון-קלייטמן", "https://www.dunsguide.co.il/Cb6a87819a48606a97ab6b3a3617e9370_רופאים/קלייטמן_שרון_שלמה/", "https://www.facebook.com/sharon.kleitman.md/directory_category/", "https://dns.dibiz.com/sharon-kleitman-md", "https://longevitepalmbeach.com"]</t>
+          <t>["https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA/", "https://moonbellboutique.com/index/%D7%93%D7%A8-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%A9%D7%93%D7%9E%D7%95%D7%9F/", "https://moonbellboutique.com/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/", "https://www.infomed.co.il/experts/145161/", "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>3.603506593920547e+18</v>
+        <v>1.081051978176164e+19</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -11052,7 +11060,7 @@
       <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
+          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
         </is>
       </c>
       <c r="AI65" t="inlineStr"/>
@@ -11093,7 +11101,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>איה שלם</t>
+          <t>שרון שלמה קלייטמן</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11124,20 +11132,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>info@shrir-sheled.co.il</t>
+          <t>sharon.kleitman@gmail.com</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/</t>
+          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -11147,12 +11155,12 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>ד"ר איה שלם - אינדקס מטפלים ברפואת שריר שלד דלג לתוכן info@shrir-sheled.co.il בית רשימת המטפלים מאמרים מקצועיים אודות מקצוע המטפל רפואת משפחה פיזיותרפיה אוסטיאופתיה כירופרקטיקה אורתופדיה צרו קשר תפריט בית רשימת המטפלים מאמרים מקצועיים אודות מקצוע המטפל רפואת משפחה פיזיותרפי</t>
+          <t>ש קשר שיתוף שתפו במייל שתפו בפייסבוק שתפו בטוויטר שתפו בלינקדין ד"ר שרון קלייטמן מומחה ברפואת משפחה, MST - Mind Set Technique, רפואה אינטגרטיבית, IMS - דיקור יבש, תזונה אינטגרטיבית. נייד 052-8325580 פקס 08-6560357 דוא"ל sharon.kleitman@gmail.com אתר www.integrative-med.com שלח/י לי sms פייסבוק אודות ד"ר שרון קלייטמן מומחה ברפואת משפחה, סיים את לימודי הרפואה באוניברסיטת בן גוריון, נשוי ואב לארבעה, מתגורר בקיבוץ שדה בוקר. עוסק בפיתוח והקנ</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>"איה שלם"</t>
+          <t>"שרון שלמה קלייטמן"</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -11174,7 +11182,7 @@
       <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-09-04T18:58:24.569451+00:00</t>
+          <t>2026-09-04T15:41:54.743203+00:00</t>
         </is>
       </c>
       <c r="W66" t="n">
@@ -11184,13 +11192,13 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z66" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AA66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
@@ -11199,11 +11207,11 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>["https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%9C%D7%9D-%D7%90%D7%99%D7%94/", "https://medpage.co.il/doctors/16196-%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D-8959/", "https://www.doctorita.co.il/experts/124568", "https://drtor.co.il/doctor/19921", "http://me.doctorsonly.co.il/user/2636", "https://www.infomed.co.il/experts/74772/", "https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/", "https://eshkol.media/", "https://shrir-sheled.co.il/about/"]</t>
+          <t>["https://docsrated.com/doctors/שרון-קלייטמן", "https://www.dunsguide.co.il/Cb6a87819a48606a97ab6b3a3617e9370_רופאים/קלייטמן_שרון_שלמה/", "https://www.facebook.com/sharon.kleitman.md/directory_category/", "https://dns.dibiz.com/sharon-kleitman-md", "https://longevitepalmbeach.com"]</t>
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>3.902872299986166e+18</v>
+        <v>1.081051978176164e+19</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -11214,7 +11222,7 @@
       <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/</t>
+          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
         </is>
       </c>
       <c r="AI66" t="inlineStr"/>
@@ -11238,9 +11246,171 @@
         <v>1</v>
       </c>
       <c r="AU66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV66" t="inlineStr">
+        <is>
+          <t>PERSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>13</v>
+      </c>
+      <c r="B67" t="n">
+        <v>6</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>איה שלם</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>family_doctor</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>moh</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>info@shrir-sheled.co.il</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>CLINIC_OR_ORGANIZATION</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>88</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>ד"ר איה שלם - אינדקס מטפלים ברפואת שריר שלד דלג לתוכן info@shrir-sheled.co.il בית רשימת המטפלים מאמרים מקצועיים אודות מקצוע המטפל רפואת משפחה פיזיותרפיה אוסטיאופתיה כירופרקטיקה אורתופדיה צרו קשר תפריט בית רשימת המטפלים מאמרים מקצועיים אודות מקצוע המטפל רפואת משפחה פיזיותרפי</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>"איה שלם"</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>direct_text</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S67" t="n">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-09-04T18:58:24.569451+00:00</t>
+        </is>
+      </c>
+      <c r="W67" t="n">
+        <v>2</v>
+      </c>
+      <c r="X67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>["https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%9C%D7%9D-%D7%90%D7%99%D7%94/", "https://medpage.co.il/doctors/16196-%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D-8959/", "https://www.doctorita.co.il/experts/124568", "https://drtor.co.il/doctor/19921", "http://me.doctorsonly.co.il/user/2636", "https://www.infomed.co.il/experts/74772/", "https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/", "https://eshkol.media/", "https://shrir-sheled.co.il/about/"]</t>
+        </is>
+      </c>
+      <c r="AD67" t="n">
+        <v>1.17086168999585e+19</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="inlineStr"/>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr"/>
+      <c r="AJ67" t="inlineStr"/>
+      <c r="AK67" t="inlineStr"/>
+      <c r="AL67" t="inlineStr"/>
+      <c r="AM67" t="inlineStr"/>
+      <c r="AN67" t="inlineStr"/>
+      <c r="AO67" t="inlineStr"/>
+      <c r="AP67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ67" t="inlineStr"/>
+      <c r="AR67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV67" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>

--- a/output/contacts_primary.xlsx
+++ b/output/contacts_primary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV67"/>
+  <dimension ref="A1:AV68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>1.171122655623675e+19</v>
+        <v>3.513367966871026e+19</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>1.444243935191125e+19</v>
+        <v>4.332731805573375e+19</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>1.170738155316593e+19</v>
+        <v>3.51221446594978e+19</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>1.170738155316593e+19</v>
+        <v>3.51221446594978e+19</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>1.170738155316593e+19</v>
+        <v>3.51221446594978e+19</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>1.170738155316593e+19</v>
+        <v>3.51221446594978e+19</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>1.440908498851192e+19</v>
+        <v>4.322725496553574e+19</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>1.440908498851192e+19</v>
+        <v>4.322725496553574e+19</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>1.351963529786303e+19</v>
+        <v>4.05589058935891e+19</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>1.171863863699676e+19</v>
+        <v>3.515591591099029e+19</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>1.171849967429904e+19</v>
+        <v>3.515549902289713e+19</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>1.444738073908152e+19</v>
+        <v>4.334214221724456e+19</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ד"ר לוריא מיכל</t>
+          <t>ד"ר הרן גבי</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=8e800bc1-5c51-41bc-b5cd-3fd5e719dca4</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=18aa957a-0f78-4228-8bdf-8ebacc279f5a</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>mijalluria@gmail.com</t>
+          <t>haran.clinic@gmail.com</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C-%D7%93%D7%A8/</t>
+          <t>https://doctors.assuta.co.il/doctor/gabi-haran-88606?readmore=true</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2689,63 +2689,63 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>יות הרצאות מהכנסים מטפלי.ות איט"ם מטפלי.ות איט"ם פיזיותרפיסטים.ית איט"ם מרפאות ציבוריות הצטרפות והתמחות צור קשר פרטי התקשרות טלפון 072-211-9500 כתובת "מרכז רותם: המרכז הרב תחומי למיניות"  גבעת בית הכרם 3, ירושלים אימייל mijalluria@gmail.com לוריא מיכל (MD) – ירושלים מקצוע: רופאה, מומחית ברפואת נשים, מטפלת מינית מוסמכת התמחות: גינקולוגית איזור טיפול: ירושלים אודותי התמחות: טיפול מיני זוגי ופרטני, פערים בחשק המיני, חוסר הנאה מחיי המין, כא</t>
+          <t>ד"ר גבי הרן | גינקולוגיה ומיילדות | גינקואונקולוגיה | אסותא 2 days ago · מרפאות מרפאת ארליך דוקטור הרן גבי תל אביב הברזל 15 קומה: 2 מייל מרפאה: haran.clinic@gmail.com</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>"לוריא מיכל" יילוד מרפאה</t>
+          <t>"הרן גבי" יילוד</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "identity_url": "https://itam.org.il/therapists/%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C-%D7%93%D7%A8/", "evidence": "ter.rotem.www שעות פעילות: שעות פעילות:\r\nא'-ה' 08.00-22.00 | ו' 8.00-15.00 איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי 052-2528020 מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"לוריא מיכל\" יילוד מרפאה", "extraction_method": "linked_text"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
         <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-08T23:26:20.598402+00:00</t>
+          <t>2026-09-11T13:38:16.718852+00:00</t>
         </is>
       </c>
       <c r="W14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>ddgs:yahoo</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=8e800bc1-5c51-41bc-b5cd-3fd5e719dca4", "https://www.meuhedet.co.il/poi/Doctors/000250300130100613000000000000_0", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C/", "https://www.doctorita.co.il/experts/72051", "https://itam.org.il/therapists/%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C-%D7%93%D7%A8/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=18aa957a-0f78-4228-8bdf-8ebacc279f5a", "https://doctorindex.co.il/דוקטור-הרן-גבי/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%94%D7%A8%D7%9F-%D7%92%D7%91%D7%99/", "https://doctors.assuta.co.il/doctor/gabi-haran-88606?readmore=true"]</t>
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>1.171863863699678e+19</v>
+        <v>7293</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2756,19 +2756,27 @@
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C-%D7%93%D7%A8/</t>
+          <t>https://doctors.assuta.co.il/doctor/gabi-haran-88606?readmore=true</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>ד"ר גבי הרן | גינקולוגיה ומיילדות | גינקואונקולוגיה | אסותא ד"ר גבי הרן | גינקולוגיה ומיילדות | גינקואונקולוגיה | אסותא 2 days ago · מרפאות מרפאת ארליך דוקטור הרן גבי תל אביב הברזל 15 קומה: 2 מייל מרפאה: haran.clinic@gmail.com</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr"/>
       <c r="AR14" t="n">
         <v>1</v>
@@ -2780,11 +2788,11 @@
         <v>1</v>
       </c>
       <c r="AU14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>PERSON</t>
+          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2805,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ד"ר פז מורן</t>
+          <t>ד"ר לוריא מיכל</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2817,7 +2825,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=5eee8cff-ee8c-40c5-807b-acf6f5374dd8</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=8e800bc1-5c51-41bc-b5cd-3fd5e719dca4</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -2828,7 +2836,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>drmoranpaz@gmail.com</t>
+          <t>mijalluria@gmail.com</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2841,7 +2849,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://www.drmoranpaz.com/</t>
+          <t>https://itam.org.il/therapists/%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C-%D7%93%D7%A8/</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2851,12 +2859,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>אליק, ישראל top of page Moran Paz M.D. Obstetrics &amp; Gynaecology Minimally invasive surgery Tel: 050-6265854 058-6265854 ד"ר מורן פז מומחה ברפואת נשים ומיילדות כירורגיה גינקולוגית זער פולשנית טל': 050-6265854 058-6265854 drmoranpaz@gmail.com צרי קשר מיילדות אנדומטריוזיס אמצעי מניעה אמצעי מניעה התקן תוך רחמי גלולות למניעת הריון גינקולוגיה גניקולוגיה הפרשות נרתיקיות פוליפים שרירנים היסטרוסקופיה לפרוסקופיה אודות אודות מכתבי תודה ד"ר מורן פז</t>
+          <t>יות הרצאות מהכנסים מטפלי.ות איט"ם מטפלי.ות איט"ם פיזיותרפיסטים.ית איט"ם מרפאות ציבוריות הצטרפות והתמחות צור קשר פרטי התקשרות טלפון 072-211-9500 כתובת "מרכז רותם: המרכז הרב תחומי למיניות"  גבעת בית הכרם 3, ירושלים אימייל mijalluria@gmail.com לוריא מיכל (MD) – ירושלים מקצוע: רופאה, מומחית ברפואת נשים, מטפלת מינית מוסמכת התמחות: גינקולוגית איזור טיפול: ירושלים אודותי התמחות: טיפול מיני זוגי ופרטני, פערים בחשק המיני, חוסר הנאה מחיי המין, כא</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>"פז מורן"</t>
+          <t>"לוריא מיכל" יילוד מרפאה</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2866,11 +2874,11 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "identity_url": "https://itam.org.il/therapists/%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C-%D7%93%D7%A8/", "evidence": "ter.rotem.www שעות פעילות: שעות פעילות:\r\nא'-ה' 08.00-22.00 | ו' 8.00-15.00 איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי 052-2528020 מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"לוריא מיכל\" יילוד מרפאה", "extraction_method": "linked_text"}]</t>
         </is>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -2878,11 +2886,11 @@
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-03T20:26:18.342248+00:00</t>
+          <t>2026-09-08T23:26:20.598402+00:00</t>
         </is>
       </c>
       <c r="W15" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -2891,34 +2899,34 @@
         <v>4</v>
       </c>
       <c r="Z15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=5eee8cff-ee8c-40c5-807b-acf6f5374dd8", "https://www.drmoranpaz.com/", "https://www.drmoranpaz.com/blank-1", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A4%D7%96-%D7%9E%D7%95%D7%A8%D7%9F/", "https://docsrated.com/doctors/מורן-פז", "https://www.clalit.co.il/he/sefersherut/pages/doctordetails.aspx?edeptcode=999012319&amp;eservicecode=1722022&amp;employeeid=99B380F756CF96813AEADDED4FF08A8C", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%95%D7%A8%D7%9F-%D7%A4%D7%96/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=8e800bc1-5c51-41bc-b5cd-3fd5e719dca4", "https://www.meuhedet.co.il/poi/Doctors/000250300130100613000000000000_0", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C/", "https://www.doctorita.co.il/experts/72051", "https://itam.org.il/therapists/%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C-%D7%93%D7%A8/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>1.440908498851192e+19</v>
+        <v>3.515591591099035e+19</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>https://www.drmoranpaz.com/</t>
+          <t>https://itam.org.il/therapists/%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C-%D7%93%D7%A8/</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr"/>
@@ -2959,7 +2967,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ד"ר צוקרמן צבי</t>
+          <t>ד"ר פז מורן</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2979,7 +2987,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=ce204428-9658-48fd-9895-62695b31e167</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=5eee8cff-ee8c-40c5-807b-acf6f5374dd8</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -2990,7 +2998,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>zukerman_z@hotmail.com</t>
+          <t>drmoranpaz@gmail.com</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -3003,7 +3011,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/</t>
+          <t>https://www.drmoranpaz.com/</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -3013,12 +3021,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>עילויות כנסים והשתלמויות הרצאות מהכנסים מטפלי.ות איט"ם מטפלי.ות איט"ם פיזיותרפיסטים.ית איט"ם מרפאות ציבוריות הצטרפות והתמחות צור קשר פרטי התקשרות טלפון 52-2444908 0, פקס': 03-9310870 כתובת ברנדה 4 פתח תקווה 49600 אימייל Zukerman_z@hotmail.com צוקרמן צבי (MD) התמחות: גינקולוגיה איזור טיפול: פתח תקווה אודותי צוקרמן צבי (MD) גינקולוגיה פתח תקווה 52-2444908 0, פקס': 03-9310870 Zukerman_z@hotmail.com ברנדה 4 פתח תקווה 49600 ברנדה 4 פתח תקווה</t>
+          <t>אליק, ישראל top of page Moran Paz M.D. Obstetrics &amp; Gynaecology Minimally invasive surgery Tel: 050-6265854 058-6265854 ד"ר מורן פז מומחה ברפואת נשים ומיילדות כירורגיה גינקולוגית זער פולשנית טל': 050-6265854 058-6265854 drmoranpaz@gmail.com צרי קשר מיילדות אנדומטריוזיס אמצעי מניעה אמצעי מניעה התקן תוך רחמי גלולות למניעת הריון גינקולוגיה גניקולוגיה הפרשות נרתיקיות פוליפים שרירנים היסטרוסקופיה לפרוסקופיה אודות אודות מכתבי תודה ד"ר מורן פז</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>"צוקרמן צבי"</t>
+          <t>"פז מורן"</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -3028,11 +3036,11 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/", "identity_url": "https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/", "evidence": "קס': 03-9310870 Zukerman_z@hotmail.com ברנדה 4 פתח תקווה 49600 ברנדה 4 פתח תקווה 49600 איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"צוקרמן צבי\"", "extraction_method": "direct_text"}, {"email": "info@israeli-expert.co.il", "confidence": 80, "source_url": "https://www.israeli-expert.co.il/index2.php?id=5149&amp;lang=HEB", "identity_url": "https://www.israeli-expert.co.il/index2.php?id=13310&amp;lang=HEB", "evidence": "info@israeli-expert.co.il Moriya Av. 105, Haifa 34616 Phone: 04-8244633, Fax: 04-8113444", "matched_query": "\"צוקרמן צבי\"", "extraction_method": "linked_mailto"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -3040,24 +3048,24 @@
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-03T21:00:59.983523+00:00</t>
+          <t>2026-09-03T20:26:18.342248+00:00</t>
         </is>
       </c>
       <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA16" t="n">
         <v>2</v>
       </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
       <c r="AB16" t="inlineStr">
         <is>
           <t>ddgs:bing</t>
@@ -3065,11 +3073,11 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=ce204428-9658-48fd-9895-62695b31e167", "https://www.facebook.com/people/%D7%A6%D7%91%D7%99-%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F/pfbid02E1Nxj3wfhR6MF8D6JXXRW7A6Jhoq792SjPLH1nRCvRmFTDrKUVsZSCxcg5BXdSXDl/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fzby.zwqrmn%2F", "https://benyehuda.org/read/38950", "https://www.israeli-expert.co.il/index2.php?id=13310&amp;lang=HEB", "https://www.interuse.co.il/", "https://www.israeli-expert.co.il/about-en", "https://www.israeli-expert.co.il/index2.php?id=5149&amp;lang=HEB", "https://www.israeli-expert.co.il/about", "https://www.israeli-expert.co.il/index2.php?id=3&amp;lang=HEB", "https://www.palmach.org.il/veterans/veteranpage/?itemId=73755", "https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=5eee8cff-ee8c-40c5-807b-acf6f5374dd8", "https://www.drmoranpaz.com/", "https://www.drmoranpaz.com/blank-1", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A4%D7%96-%D7%9E%D7%95%D7%A8%D7%9F/", "https://docsrated.com/doctors/מורן-פז", "https://www.clalit.co.il/he/sefersherut/pages/doctordetails.aspx?edeptcode=999012319&amp;eservicecode=1722022&amp;employeeid=99B380F756CF96813AEADDED4FF08A8C", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%95%D7%A8%D7%9F-%D7%A4%D7%96/"]</t>
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>1.170738155316593e+19</v>
+        <v>4.322725496553574e+19</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3080,7 +3088,7 @@
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/</t>
+          <t>https://www.drmoranpaz.com/</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr"/>
@@ -3121,7 +3129,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ד"ר קאופמן יובל</t>
+          <t>ד"ר צוקרמן צבי</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3141,7 +3149,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=87371F6B-AEDA-480B-855B-A665C2A570C0</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=ce204428-9658-48fd-9895-62695b31e167</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -3152,7 +3160,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>mdykaufman@gmail.com</t>
+          <t>zukerman_z@hotmail.com</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -3165,7 +3173,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://www.gynsurg.co.il/</t>
+          <t>https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -3175,12 +3183,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t xml:space="preserve">תמחויות לפרוסקופיה היסטרוסקופיה גישה נרתיקית בעיות גניקולוגיות בעיות פוריות פוליפ רחמי שרירנים ברחם ציסטה בשחלה אנדומטריוזיס פרטי התקשרות בית חולים 'אסותא' חיפה, קניון לב המפרץ (קומה ג') שד' ההסתדרות 55 , צ'ק פוסט, חיפה mdykaufman@gmail.com yochi750@gmail.com 03-7644777 050-9500525 © כל הזכויות שמורות ל"ר יובל קאופמן- כירורגיה גניקולוגית מתקדמת | נבנה ע"י ADACTIVE לזימון תורים - לחץ כאן זימון תור טלפון מרפאה סגירת תפריט אנחנו מכבדים את </t>
+          <t>עילויות כנסים והשתלמויות הרצאות מהכנסים מטפלי.ות איט"ם מטפלי.ות איט"ם פיזיותרפיסטים.ית איט"ם מרפאות ציבוריות הצטרפות והתמחות צור קשר פרטי התקשרות טלפון 52-2444908 0, פקס': 03-9310870 כתובת ברנדה 4 פתח תקווה 49600 אימייל Zukerman_z@hotmail.com צוקרמן צבי (MD) התמחות: גינקולוגיה איזור טיפול: פתח תקווה אודותי צוקרמן צבי (MD) גינקולוגיה פתח תקווה 52-2444908 0, פקס': 03-9310870 Zukerman_z@hotmail.com ברנדה 4 פתח תקווה 49600 ברנדה 4 פתח תקווה</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>"קאופמן יובל"</t>
+          <t>"צוקרמן צבי"</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -3190,11 +3198,11 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>[{"email": "yochi750@gmail.com", "confidence": 100, "source_url": "https://www.gynsurg.co.il/", "identity_url": "https://www.gynsurg.co.il/", "evidence": "סטרוסקופיה גישה נרתיקית בעיות גניקולוגיות בעיות פוריות פוליפ רחמי שרירנים ברחם ציסטה בשחלה אנדומטריוזיס פרטי התקשרות בית חולים 'אסותא' חיפה, קניון לב המפרץ (קומה ג') שד' ההסתדרות 55 , צ'ק פוסט, חיפה mdykaufman@gmail.com yochi750@gmail.com 03-7644777 050-9500525 © כל הזכויות שמורות ל\"ר יובל קאופמן- כירורגיה גניקולוגית מתקדמת | נבנה ע\"י ADACTIVE לזימון תורים - לחץ כאן זימון תור טלפון מרפאה סגירת תפריט אנחנו מכבדים את הפרטיות שלך אנחנו משת", "matched_query": "\"קאופמן יובל\"", "extraction_method": "direct_text"}]</t>
+          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/", "identity_url": "https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/", "evidence": "קס': 03-9310870 Zukerman_z@hotmail.com ברנדה 4 פתח תקווה 49600 ברנדה 4 פתח תקווה 49600 איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"צוקרמן צבי\"", "extraction_method": "direct_text"}, {"email": "info@israeli-expert.co.il", "confidence": 80, "source_url": "https://www.israeli-expert.co.il/index2.php?id=5149&amp;lang=HEB", "identity_url": "https://www.israeli-expert.co.il/index2.php?id=13310&amp;lang=HEB", "evidence": "info@israeli-expert.co.il Moriya Av. 105, Haifa 34616 Phone: 04-8244633, Fax: 04-8113444", "matched_query": "\"צוקרמן צבי\"", "extraction_method": "linked_mailto"}]</t>
         </is>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -3202,7 +3210,7 @@
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-03T21:01:40.564925+00:00</t>
+          <t>2026-09-03T21:00:59.983523+00:00</t>
         </is>
       </c>
       <c r="W17" t="n">
@@ -3212,10 +3220,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Z17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -3227,11 +3235,11 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=87371F6B-AEDA-480B-855B-A665C2A570C0", "https://www.gynsurg.co.il/", "https://www.gynsurg.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.gynsurg.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=ce204428-9658-48fd-9895-62695b31e167", "https://www.facebook.com/people/%D7%A6%D7%91%D7%99-%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F/pfbid02E1Nxj3wfhR6MF8D6JXXRW7A6Jhoq792SjPLH1nRCvRmFTDrKUVsZSCxcg5BXdSXDl/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fzby.zwqrmn%2F", "https://benyehuda.org/read/38950", "https://www.israeli-expert.co.il/index2.php?id=13310&amp;lang=HEB", "https://www.interuse.co.il/", "https://www.israeli-expert.co.il/about-en", "https://www.israeli-expert.co.il/index2.php?id=5149&amp;lang=HEB", "https://www.israeli-expert.co.il/about", "https://www.israeli-expert.co.il/index2.php?id=3&amp;lang=HEB", "https://www.palmach.org.il/veterans/veteranpage/?itemId=73755", "https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>1.170738155316593e+19</v>
+        <v>3.51221446594978e+19</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3242,7 +3250,7 @@
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>https://www.gynsurg.co.il/</t>
+          <t>https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr"/>
@@ -3314,7 +3322,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>yochi750@gmail.com</t>
+          <t>mdykaufman@gmail.com</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -3337,7 +3345,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>סטרוסקופיה גישה נרתיקית בעיות גניקולוגיות בעיות פוריות פוליפ רחמי שרירנים ברחם ציסטה בשחלה אנדומטריוזיס פרטי התקשרות בית חולים 'אסותא' חיפה, קניון לב המפרץ (קומה ג') שד' ההסתדרות 55 , צ'ק פוסט, חיפה mdykaufman@gmail.com yochi750@gmail.com 03-7644777 050-9500525 © כל הזכויות שמורות ל"ר יובל קאופמן- כירורגיה גניקולוגית מתקדמת | נבנה ע"י ADACTIVE לזימון תורים - לחץ כאן זימון תור טלפון מרפאה סגירת תפריט אנחנו מכבדים את הפרטיות שלך אנחנו משת</t>
+          <t xml:space="preserve">תמחויות לפרוסקופיה היסטרוסקופיה גישה נרתיקית בעיות גניקולוגיות בעיות פוריות פוליפ רחמי שרירנים ברחם ציסטה בשחלה אנדומטריוזיס פרטי התקשרות בית חולים 'אסותא' חיפה, קניון לב המפרץ (קומה ג') שד' ההסתדרות 55 , צ'ק פוסט, חיפה mdykaufman@gmail.com yochi750@gmail.com 03-7644777 050-9500525 © כל הזכויות שמורות ל"ר יובל קאופמן- כירורגיה גניקולוגית מתקדמת | נבנה ע"י ADACTIVE לזימון תורים - לחץ כאן זימון תור טלפון מרפאה סגירת תפריט אנחנו מכבדים את </t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -3393,7 +3401,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>1.170738155316593e+19</v>
+        <v>3.51221446594978e+19</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3419,7 +3427,7 @@
       </c>
       <c r="AQ18" t="inlineStr"/>
       <c r="AR18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS18" t="b">
         <v>0</v>
@@ -3445,7 +3453,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ד"ר קוגן לירון</t>
+          <t>ד"ר קאופמן יובל</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3465,7 +3473,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=874a0be8-2288-4588-8c92-8fd98e173223</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=87371F6B-AEDA-480B-855B-A665C2A570C0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -3476,7 +3484,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>shelach.medical@gmail.com</t>
+          <t>yochi750@gmail.com</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -3489,7 +3497,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://doctors.assuta.co.il/doctor/liron-kogan-83973?readmore=true</t>
+          <t>https://www.gynsurg.co.il/</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3499,26 +3507,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>ד"ר לירון קוגן | גינקולוגיה ומיילדות | גינקואונקולוגיה | אסותא Jul 16, 2026 · מרפאות החבצלת 1, פתח תקווה-דוקטור קוגן לירון פתח תקווה החבצלת 1 ימי שני 18:00-19:00 מייל מרפאה: shelach.medical@gmail.com</t>
+          <t>סטרוסקופיה גישה נרתיקית בעיות גניקולוגיות בעיות פוריות פוליפ רחמי שרירנים ברחם ציסטה בשחלה אנדומטריוזיס פרטי התקשרות בית חולים 'אסותא' חיפה, קניון לב המפרץ (קומה ג') שד' ההסתדרות 55 , צ'ק פוסט, חיפה mdykaufman@gmail.com yochi750@gmail.com 03-7644777 050-9500525 © כל הזכויות שמורות ל"ר יובל קאופמן- כירורגיה גניקולוגית מתקדמת | נבנה ע"י ADACTIVE לזימון תורים - לחץ כאן זימון תור טלפון מרפאה סגירת תפריט אנחנו מכבדים את הפרטיות שלך אנחנו משת</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>"קוגן לירון" יילוד</t>
+          <t>"קאופמן יובל"</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>search_snippet</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "yochi750@gmail.com", "confidence": 100, "source_url": "https://www.gynsurg.co.il/", "identity_url": "https://www.gynsurg.co.il/", "evidence": "סטרוסקופיה גישה נרתיקית בעיות גניקולוגיות בעיות פוריות פוליפ רחמי שרירנים ברחם ציסטה בשחלה אנדומטריוזיס פרטי התקשרות בית חולים 'אסותא' חיפה, קניון לב המפרץ (קומה ג') שד' ההסתדרות 55 , צ'ק פוסט, חיפה mdykaufman@gmail.com yochi750@gmail.com 03-7644777 050-9500525 © כל הזכויות שמורות ל\"ר יובל קאופמן- כירורגיה גניקולוגית מתקדמת | נבנה ע\"י ADACTIVE לזימון תורים - לחץ כאן זימון תור טלפון מרפאה סגירת תפריט אנחנו מכבדים את הפרטיות שלך אנחנו משת", "matched_query": "\"קאופמן יובל\"", "extraction_method": "direct_text"}]</t>
         </is>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -3526,47 +3534,47 @@
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-08T23:31:56.357314+00:00</t>
+          <t>2026-09-03T21:01:40.564925+00:00</t>
         </is>
       </c>
       <c r="W19" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>ddgs:yahoo+ddgs:bing</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=874a0be8-2288-4588-8c92-8fd98e173223", "https://www.meuhedet.co.il/poi/Doctors/7070866300000839730000009928_99", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A7%D7%95%D7%92%D7%9F-%D7%9C%D7%99%D7%A8%D7%95%D7%9F/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=4D7994DA1EF011E23924766CCB7D4323448E0FB52729DF77F063BC8E422E0345&amp;RequestId=00000000-0000-0000-0001-000000000518", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=3&amp;ProviderID=32912818&amp;ProviderProfession=W&amp;docClinic=4008135&amp;Service=1&amp;NewObjectId=70064900&amp;NewObjectType=S&amp;NewPerNr=90006758&amp;ol1=70064900&amp;ol2=S&amp;ol3=90006758&amp;isKosher=1&amp;beginDate=2026-09-09T02:30:57&amp;shaban=true&amp;appversion=4.1.3&amp;relative=-2&amp;action_type=1&amp;source=1", "https://doctors.assuta.co.il/doctor/liron-kogan-83973?readmore=true", "https://www.medreviews.co.il/provider/dr-kogan-liron", "https://www.gynonc.co.il/", "https://www.gynonc.co.il/about", "https://doctors.assuta.co.il/doctor/liron-kogan-83973", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fdr.lironkogan%2F", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=3&amp;ProviderID=32912818&amp;ProviderProfession=W&amp;docClinic=4008135&amp;Service=1&amp;NewObjectId=70064900&amp;NewObjectType=S&amp;NewPerNr=90006758&amp;ol1=70064900&amp;ol2=S&amp;ol3=90006758&amp;isKosher=1&amp;beginDate=2026-09-04T00:01:58&amp;shaban=true&amp;appversion=4.1.3&amp;relative=-2&amp;action_type=1&amp;source=1", "https://www.raphaelhospitals.co.il/doctors/liron-kogen/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=87371F6B-AEDA-480B-855B-A665C2A570C0", "https://www.gynsurg.co.il/", "https://www.gynsurg.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.gynsurg.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/"]</t>
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>1.171863863699678e+19</v>
+        <v>3.51221446594978e+19</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
       </c>
       <c r="AF19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>https://doctors.assuta.co.il/doctor/liron-kogan-83973?readmore=true</t>
+          <t>https://www.gynsurg.co.il/</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr"/>
@@ -3581,7 +3589,7 @@
       </c>
       <c r="AQ19" t="inlineStr"/>
       <c r="AR19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS19" t="b">
         <v>0</v>
@@ -3607,7 +3615,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ד"ר רבהון אמיר</t>
+          <t>ד"ר קוגן לירון</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3627,7 +3635,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=73FEFAED-F4B1-412E-801F-0A168B202A07</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=874a0be8-2288-4588-8c92-8fd98e173223</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -3638,12 +3646,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>ravhon.clinic@gmail.com</t>
+          <t>shelach.medical@gmail.com</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -3651,7 +3659,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://www.dr-ravhon.co.il/</t>
+          <t>https://doctors.assuta.co.il/doctor/liron-kogan-83973?readmore=true</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3661,17 +3669,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>ד"ר אמיר רבהון - מומחה במיילדות, גניקולוגיה ובפוריות דלג לתוכן לתיאום תור למרפאה הפרטית התקשרו: 05 4-468-5276 | שלחו מייל: ravhon.clinic@gmail.com Facebook דף בית הצעד הראשון מתי לפנות לטיפולי פוריות למה לצפות כשמצפים לטיפולי פוריות? טיפולים טיפולי פוריות הפריה חוץ גופית – IVF תרומת ביציות הקפאת ביציות צילומי רחם אודות כתבות פורום Infomed יצ</t>
+          <t>ד"ר לירון קוגן | גינקולוגיה ומיילדות | גינקואונקולוגיה | אסותא Jul 16, 2026 · מרפאות החבצלת 1, פתח תקווה-דוקטור קוגן לירון פתח תקווה החבצלת 1 ימי שני 18:00-19:00 מייל מרפאה: shelach.medical@gmail.com</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>"רבהון אמיר"</t>
+          <t>"קוגן לירון" יילוד</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -3688,47 +3696,47 @@
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-04T13:09:47.289882+00:00</t>
+          <t>2026-09-08T23:31:56.357314+00:00</t>
         </is>
       </c>
       <c r="W20" t="n">
+        <v>8</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA20" t="n">
         <v>2</v>
       </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=73FEFAED-F4B1-412E-801F-0A168B202A07", "https://www.dr-ravhon.co.il/", "https://www.dr-ravhon.co.il/about/", "https://www.dr-ravhon.co.il/#contact-area", "https://www.dr-ravhon.co.il/about/#contact-area"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=874a0be8-2288-4588-8c92-8fd98e173223", "https://www.meuhedet.co.il/poi/Doctors/7070866300000839730000009928_99", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A7%D7%95%D7%92%D7%9F-%D7%9C%D7%99%D7%A8%D7%95%D7%9F/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=4D7994DA1EF011E23924766CCB7D4323448E0FB52729DF77F063BC8E422E0345&amp;RequestId=00000000-0000-0000-0001-000000000518", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=3&amp;ProviderID=32912818&amp;ProviderProfession=W&amp;docClinic=4008135&amp;Service=1&amp;NewObjectId=70064900&amp;NewObjectType=S&amp;NewPerNr=90006758&amp;ol1=70064900&amp;ol2=S&amp;ol3=90006758&amp;isKosher=1&amp;beginDate=2026-09-09T02:30:57&amp;shaban=true&amp;appversion=4.1.3&amp;relative=-2&amp;action_type=1&amp;source=1", "https://doctors.assuta.co.il/doctor/liron-kogan-83973?readmore=true", "https://www.medreviews.co.il/provider/dr-kogan-liron", "https://www.gynonc.co.il/", "https://www.gynonc.co.il/about", "https://doctors.assuta.co.il/doctor/liron-kogan-83973", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fdr.lironkogan%2F", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=3&amp;ProviderID=32912818&amp;ProviderProfession=W&amp;docClinic=4008135&amp;Service=1&amp;NewObjectId=70064900&amp;NewObjectType=S&amp;NewPerNr=90006758&amp;ol1=70064900&amp;ol2=S&amp;ol3=90006758&amp;isKosher=1&amp;beginDate=2026-09-04T00:01:58&amp;shaban=true&amp;appversion=4.1.3&amp;relative=-2&amp;action_type=1&amp;source=1", "https://www.raphaelhospitals.co.il/doctors/liron-kogen/"]</t>
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>1.171849967429904e+19</v>
+        <v>3.515591591099035e+19</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>https://www.dr-ravhon.co.il/</t>
+          <t>https://doctors.assuta.co.il/doctor/liron-kogan-83973?readmore=true</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr"/>
@@ -3752,11 +3760,11 @@
         <v>1</v>
       </c>
       <c r="AU20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
+          <t>PERSON</t>
         </is>
       </c>
     </row>
@@ -3769,12 +3777,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ד"ר שטטר אורנה</t>
+          <t>ד"ר רבהון אמיר</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>family_doctor</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3789,7 +3797,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3029d9ab-24fa-43c3-93a2-29329c1b952c</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=73FEFAED-F4B1-412E-801F-0A168B202A07</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -3800,12 +3808,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>ornastatter@gmail.com</t>
+          <t>ravhon.clinic@gmail.com</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -3813,7 +3821,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://www.fps.org.il/metapel/drornas/</t>
+          <t>https://www.dr-ravhon.co.il/</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3823,12 +3831,12 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>ם והרצאות הרצאות מוקלטות מאמרים חיפוש מטפל/ת אורנה שטטר (ד"ר) דף הבית &gt; מטפלים &gt; אורנה שטטר (ד"ר) פרטי המטפל: אזור טיפול: שפלה ישוב: חולדה (ליד מזכרת בתיה, כ-20 דק מרחובות) נייד: 054-7338883 כתובת המייל של המטפל/מדריך:  ornastatter@gmail.com מידע נוסף: מומחית ברפואת משפחה מטפלת מוסמכת בפסיכותרפיה ממוקדת חברת וועד האגודה הישראלית לפסיכוסומטיקה וועד הסניף הישראלי של acbs אודות האגודה על האגודה חזון ומטרות המייסדים מאפייני טיפול קצר-מועד ה</t>
+          <t>ד"ר אמיר רבהון - מומחה במיילדות, גניקולוגיה ובפוריות דלג לתוכן לתיאום תור למרפאה הפרטית התקשרו: 05 4-468-5276 | שלחו מייל: ravhon.clinic@gmail.com Facebook דף בית הצעד הראשון מתי לפנות לטיפולי פוריות למה לצפות כשמצפים לטיפולי פוריות? טיפולים טיפולי פוריות הפריה חוץ גופית – IVF תרומת ביציות הקפאת ביציות צילומי רחם אודות כתבות פורום Infomed יצ</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>"שטטר אורנה" רפואת משפחה</t>
+          <t>"רבהון אמיר"</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -3838,11 +3846,11 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>[{"email": "fps.israel@gmail.com", "confidence": 92, "source_url": "https://www.fps.org.il/contactus/", "identity_url": "https://www.fps.org.il/metapel/drornas/", "evidence": "Envelope", "matched_query": "\"שטטר אורנה\" רפואת משפחה", "extraction_method": "linked_mailto"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -3850,36 +3858,36 @@
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-08T14:11:08.841786+00:00</t>
+          <t>2026-09-04T13:09:47.289882+00:00</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>ddgs:yahoo+ddgs:bing</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3029d9ab-24fa-43c3-93a2-29329c1b952c", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%98%D7%98%D7%A8-%D7%90%D7%95%D7%A8%D7%A0%D7%94/", "https://www.doctorita.co.il/experts/95407", "https://medpage.co.il/doctors/%D7%90%D7%95%D7%A8%D7%A0%D7%94-%D7%A9%D7%98%D7%98%D7%A8-913/", "https://drtor.co.il/doctor/18797", "https://drtor.co.il/cdn-cgi/l/email-protection#3a5955544e5b594e7a5e484e5548145955145356", "https://www.fps.org.il/metapel/drornas/", "https://www.fps.org.il/contactus/", "https://www.fps.org.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.fps.org.il/about/theassociation/", "https://www.fps.org.il/about/goals/", "https://www.fps.org.il/about/founders/", "https://www.fps.org.il/about/dstterapy/", "https://www.fps.org.il/aguda-members/%D7%90%D7%95%D7%A8%D7%A0%D7%94%D7%A9%D7%98%D7%98%D7%A8/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=73FEFAED-F4B1-412E-801F-0A168B202A07", "https://www.dr-ravhon.co.il/", "https://www.dr-ravhon.co.il/about/", "https://www.dr-ravhon.co.il/#contact-area", "https://www.dr-ravhon.co.il/about/#contact-area"]</t>
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>1.171122655623675e+19</v>
+        <v>3.515549902289713e+19</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3890,7 +3898,7 @@
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>https://www.fps.org.il/metapel/drornas/</t>
+          <t>https://www.dr-ravhon.co.il/</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr"/>
@@ -3914,11 +3922,11 @@
         <v>1</v>
       </c>
       <c r="AU21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>PERSON</t>
+          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
       </c>
     </row>
@@ -3931,12 +3939,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ד"ר שרים גיא</t>
+          <t>ד"ר שטטר אורנה</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3951,7 +3959,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=F9FC3D7F-C0DD-440E-8AA7-DC41A9FCCC00</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3029d9ab-24fa-43c3-93a2-29329c1b952c</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -3962,7 +3970,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>dr.shremguy@gmail.com</t>
+          <t>ornastatter@gmail.com</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3975,7 +3983,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://guyshrem.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
+          <t>https://www.fps.org.il/metapel/drornas/</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3985,12 +3993,12 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>אודות - ד"ר גיא שרים חיפוש חיפוש אודות בירור בעיות פוריות צילום רחם מרכז הידע צרו קשר אודות בירור בעיות פוריות צילום רחם מרכז הידע צרו קשר אודות ד"ר גיא שרים יצירת קשר 077-230-3222 dr.shremguy@gmail.com שדרות ההגשמה 18, חריש לתיאום פגישה: שם טלפון אימייל שליחה אודות ד"ר גיא שרים - מומחה בגינקולוגיה ופוריות ד"ר שרים הינו מומחה באנדוקרינולוגיה של הרביה ואי-פוריות – Reproductive Endocrinology and Infe</t>
+          <t>ם והרצאות הרצאות מוקלטות מאמרים חיפוש מטפל/ת אורנה שטטר (ד"ר) דף הבית &gt; מטפלים &gt; אורנה שטטר (ד"ר) פרטי המטפל: אזור טיפול: שפלה ישוב: חולדה (ליד מזכרת בתיה, כ-20 דק מרחובות) נייד: 054-7338883 כתובת המייל של המטפל/מדריך:  ornastatter@gmail.com מידע נוסף: מומחית ברפואת משפחה מטפלת מוסמכת בפסיכותרפיה ממוקדת חברת וועד האגודה הישראלית לפסיכוסומטיקה וועד הסניף הישראלי של acbs אודות האגודה על האגודה חזון ומטרות המייסדים מאפייני טיפול קצר-מועד ה</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>"שרים גיא"</t>
+          <t>"שטטר אורנה" רפואת משפחה</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -4000,11 +4008,11 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "fps.israel@gmail.com", "confidence": 92, "source_url": "https://www.fps.org.il/contactus/", "identity_url": "https://www.fps.org.il/metapel/drornas/", "evidence": "Envelope", "matched_query": "\"שטטר אורנה\" רפואת משפחה", "extraction_method": "linked_mailto"}]</t>
         </is>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -4012,36 +4020,36 @@
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-03T21:14:53.999772+00:00</t>
+          <t>2026-09-08T14:11:08.841786+00:00</t>
         </is>
       </c>
       <c r="W22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=F9FC3D7F-C0DD-440E-8AA7-DC41A9FCCC00", "https://medicine.biu.ac.il/node/8582", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fgy.srym%2F", "https://guyshrem.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "http://guyshrem.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3029d9ab-24fa-43c3-93a2-29329c1b952c", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%98%D7%98%D7%A8-%D7%90%D7%95%D7%A8%D7%A0%D7%94/", "https://www.doctorita.co.il/experts/95407", "https://medpage.co.il/doctors/%D7%90%D7%95%D7%A8%D7%A0%D7%94-%D7%A9%D7%98%D7%98%D7%A8-913/", "https://drtor.co.il/doctor/18797", "https://drtor.co.il/cdn-cgi/l/email-protection#3a5955544e5b594e7a5e484e5548145955145356", "https://www.fps.org.il/metapel/drornas/", "https://www.fps.org.il/contactus/", "https://www.fps.org.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.fps.org.il/about/theassociation/", "https://www.fps.org.il/about/goals/", "https://www.fps.org.il/about/founders/", "https://www.fps.org.il/about/dstterapy/", "https://www.fps.org.il/aguda-members/%D7%90%D7%95%D7%A8%D7%A0%D7%94%D7%A9%D7%98%D7%98%D7%A8/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/"]</t>
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>1.170738155316593e+19</v>
+        <v>3.513367966871025e+19</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4052,7 +4060,7 @@
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>https://guyshrem.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
+          <t>https://www.fps.org.il/metapel/drornas/</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr"/>
@@ -4093,7 +4101,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>דוד גורדון</t>
+          <t>ד"ר שרים גיא</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4113,18 +4121,18 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=F9FC3D7F-C0DD-440E-8AA7-DC41A9FCCC00</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>ima</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>davidgordon14@yahoo.com</t>
+          <t>dr.shremguy@gmail.com</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -4137,7 +4145,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://www.davidgordon.co.il/</t>
+          <t>https://guyshrem.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -4147,12 +4155,12 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>ניחת רחם טיפול בבריחת שתן הערכה אורו-דינמית מדיניות הפרטיות הצהרת נגישות יצירת קשר ותיאם פגישה צרי איתי קשר צוות המרפאה עומד לשרותכם! כתובתנו: מגדל מרכז ויצמן רחוב ויצמן 14, תל אביב טלפון : 03-544-9339 נייד: 052-2411171 davidgordon14@yahoo.com Facebook Google+ Instagram לשיחת יעוץ ותיאום פגישה אני מסכים/ה ל מדיניות הפרטיות ולעיבוד המידע ליצירת קשר Please leave this field empty. Ⓒ  כל הזכויות שמורות ל פרופ' דוד גורדון אורוגניקולוג | טיפו</t>
+          <t>אודות - ד"ר גיא שרים חיפוש חיפוש אודות בירור בעיות פוריות צילום רחם מרכז הידע צרו קשר אודות בירור בעיות פוריות צילום רחם מרכז הידע צרו קשר אודות ד"ר גיא שרים יצירת קשר 077-230-3222 dr.shremguy@gmail.com שדרות ההגשמה 18, חריש לתיאום פגישה: שם טלפון אימייל שליחה אודות ד"ר גיא שרים - מומחה בגינקולוגיה ופוריות ד"ר שרים הינו מומחה באנדוקרינולוגיה של הרביה ואי-פוריות – Reproductive Endocrinology and Infe</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>"דוד גורדון"</t>
+          <t>"שרים גיא"</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -4174,7 +4182,7 @@
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-03T23:18:02.537185+00:00</t>
+          <t>2026-09-03T21:14:53.999772+00:00</t>
         </is>
       </c>
       <c r="W23" t="n">
@@ -4184,10 +4192,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -4199,11 +4207,11 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>["https://www.davidgordon.co.il/", "https://www.davidgordon.co.il/contact/", "https://www.davidgordon.co.il/our-clinic/", "https://www.davidgordon.co.il/our-clinic/faq/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=F9FC3D7F-C0DD-440E-8AA7-DC41A9FCCC00", "https://medicine.biu.ac.il/node/8582", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fgy.srym%2F", "https://guyshrem.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "http://guyshrem.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>1.170738155316593e+19</v>
+        <v>3.51221446594978e+19</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4214,7 +4222,7 @@
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>https://www.davidgordon.co.il/</t>
+          <t>https://guyshrem.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr"/>
@@ -4255,7 +4263,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>יניב צפורי</t>
+          <t>דוד גורדון</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4286,7 +4294,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>zipori.obgyn@gmail.com</t>
+          <t>davidgordon14@yahoo.com</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -4299,7 +4307,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://www.zipori-obgyn.com/</t>
+          <t>https://www.davidgordon.co.il/</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -4309,12 +4317,12 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t xml:space="preserve"> דופלר. פרטי, כללית מושלם, הסדר עם כל חברות הביטוח לקרוא עוד להזמין תור כתובת המרפאה: פרופ' דן שכטמן 10, קניון מול החוף וילג', בניין B קומה 2, חדרה ליצירת קשר וקביעת תורים: 072-3937709 מיטל מזכירה ראשית 📞 ד"ר יניב צפורי zipori.obgyn@gmail.com ©2022 by Doctor Yaniv Zipori bottom of page</t>
+          <t>ניחת רחם טיפול בבריחת שתן הערכה אורו-דינמית מדיניות הפרטיות הצהרת נגישות יצירת קשר ותיאם פגישה צרי איתי קשר צוות המרפאה עומד לשרותכם! כתובתנו: מגדל מרכז ויצמן רחוב ויצמן 14, תל אביב טלפון : 03-544-9339 נייד: 052-2411171 davidgordon14@yahoo.com Facebook Google+ Instagram לשיחת יעוץ ותיאום פגישה אני מסכים/ה ל מדיניות הפרטיות ולעיבוד המידע ליצירת קשר Please leave this field empty. Ⓒ  כל הזכויות שמורות ל פרופ' דוד גורדון אורוגניקולוג | טיפו</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>"יניב צפורי"</t>
+          <t>"דוד גורדון"</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -4336,7 +4344,7 @@
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-09-04T16:52:16.086371+00:00</t>
+          <t>2026-09-03T23:18:02.537185+00:00</t>
         </is>
       </c>
       <c r="W24" t="n">
@@ -4346,10 +4354,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -4361,11 +4369,11 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>["https://www.doctorita.co.il/experts/65276", "https://www.zipori-obgyn.com/", "https://www.zipori-obgyn.com/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.zipori-obgyn.com/%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99-%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94"]</t>
+          <t>["https://www.davidgordon.co.il/", "https://www.davidgordon.co.il/contact/", "https://www.davidgordon.co.il/our-clinic/", "https://www.davidgordon.co.il/our-clinic/faq/"]</t>
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>1.111070905235564e+19</v>
+        <v>3.51221446594978e+19</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4376,7 +4384,7 @@
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>https://www.zipori-obgyn.com/</t>
+          <t>https://www.davidgordon.co.il/</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr"/>
@@ -4417,7 +4425,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>מיכל בראונשטיין</t>
+          <t>יניב צפורי</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4448,12 +4456,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>office.clinica1@gmail.com</t>
+          <t>zipori.obgyn@gmail.com</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -4461,7 +4469,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://drbraunstein.co.il/</t>
+          <t>https://www.zipori-obgyn.com/</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -4471,12 +4479,12 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>שמירת הבריאות של הפות והנרתיק דלקת עור ממגע קנדידה וגינוזיס חיידקי BV וגיניטיס פורלנטית ליכן סקלרוזוס אטרופיה נרתיקית כאב הפות והנרתיק כל מה שרצית לדעת על גז צחוק במרפאה גינקולוגית English Facebook-f Whatsapp 08-9702314 office.clinica1@gmail.com מרפאת "קליניקה", אלי הורוביץ 27, קומה 5, רחובות שלום לכולן, שמי מיכל בראונשטיין, אני רופאת נשים. בצעירותי החלטתי ללמוד רפואה, ובמיוחד גינקולוגיה, מתוך חלום ליצור מרפאה ידידותית ונעימה עבור מטופל</t>
+          <t xml:space="preserve"> דופלר. פרטי, כללית מושלם, הסדר עם כל חברות הביטוח לקרוא עוד להזמין תור כתובת המרפאה: פרופ' דן שכטמן 10, קניון מול החוף וילג', בניין B קומה 2, חדרה ליצירת קשר וקביעת תורים: 072-3937709 מיטל מזכירה ראשית 📞 ד"ר יניב צפורי zipori.obgyn@gmail.com ©2022 by Doctor Yaniv Zipori bottom of page</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>"מיכל בראונשטיין"</t>
+          <t>"יניב צפורי"</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -4498,7 +4506,7 @@
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-09-04T18:07:38.830808+00:00</t>
+          <t>2026-09-04T16:52:16.086371+00:00</t>
         </is>
       </c>
       <c r="W25" t="n">
@@ -4508,10 +4516,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -4523,11 +4531,11 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>["https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2FDr.MichalBraunstein%2F", "https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr.michal.braunstein%2F&amp;is_from_rle", "https://drbraunstein.co.il/", "https://www.shlema.org.il/", "https://drbraunstein.co.il/contact-dermatitis/", "https://drbraunstein.co.il/%D7%92%D7%96-%D7%A6%D7%97%D7%95%D7%A7/", "https://drbraunstein.co.il/#contact"]</t>
+          <t>["https://www.doctorita.co.il/experts/65276", "https://www.zipori-obgyn.com/", "https://www.zipori-obgyn.com/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.zipori-obgyn.com/%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99-%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94"]</t>
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>1.111070905235564e+19</v>
+        <v>3.333212715706692e+19</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4538,7 +4546,7 @@
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>https://drbraunstein.co.il/</t>
+          <t>https://www.zipori-obgyn.com/</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr"/>
@@ -4562,11 +4570,11 @@
         <v>1</v>
       </c>
       <c r="AU25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
+          <t>PERSON</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4587,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>נורה גורכד שבסו</t>
+          <t>מיכל בראונשטיין</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4610,12 +4618,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>norashapso@gmail.com</t>
+          <t>office.clinica1@gmail.com</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -4623,7 +4631,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/</t>
+          <t>https://drbraunstein.co.il/</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -4633,12 +4641,12 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Med Ted לחברים בלבד ארצ״י בשטח ארצ״י בתקשורת ארצ"י בכנסת פודקאסט "סדציה להמונים" נוהל כניסה להסדר הצטרפות צרו קשר טופס דיווח שיימינג טופס בקשת סיוע קהילה לזכרם חזרה &gt; חזרה &gt; ד"ר נורה שבסו גינקולוגיה ומיילדות 052-5363267 norashapso@gmail.com ד"ר נורה גורכד שפסו היא מומחית בגינקולוגיה ומיילדות, ובעלת על־התמחות בפוריות ובהפריה חוץ־גופית (IVF). נורה למדה רפואה בטכניון והתמחתה במרכז הרפואי צפון. כיום היא עובדת כרופאה בכירה ביחידת ה- IVF  וכר</t>
+          <t>שמירת הבריאות של הפות והנרתיק דלקת עור ממגע קנדידה וגינוזיס חיידקי BV וגיניטיס פורלנטית ליכן סקלרוזוס אטרופיה נרתיקית כאב הפות והנרתיק כל מה שרצית לדעת על גז צחוק במרפאה גינקולוגית English Facebook-f Whatsapp 08-9702314 office.clinica1@gmail.com מרפאת "קליניקה", אלי הורוביץ 27, קומה 5, רחובות שלום לכולן, שמי מיכל בראונשטיין, אני רופאת נשים. בצעירותי החלטתי ללמוד רפואה, ובמיוחד גינקולוגיה, מתוך חלום ליצור מרפאה ידידותית ונעימה עבור מטופל</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>"נורה גורכד שבסו"</t>
+          <t>"מיכל בראונשטיין"</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -4660,7 +4668,7 @@
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-09-04T04:55:16.280760+00:00</t>
+          <t>2026-09-04T18:07:38.830808+00:00</t>
         </is>
       </c>
       <c r="W26" t="n">
@@ -4670,13 +4678,13 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
@@ -4685,11 +4693,11 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>["https://www.doctorita.co.il/experts/119054", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%92%D7%95%D7%A8%D7%9B%D7%93-%D7%A9%D7%91%D7%A1%D7%95-%D7%A0%D7%95%D7%A8%D7%94/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=72FD73030256FB59999957F3E61E03EABE6A8F724FC86F83B2380B60589F61A5&amp;RequestId=00000000-0000-0000-0001-000000000612", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=CE57634ABBFA154920019C7FAAD7385EAB0BB0D5FD8189978016A2325E1941AE&amp;RequestId=00000000-0000-0000-0001-000000000428", "https://www.beok.co.il/doctors/Doctors-1114057/", "https://medpage.co.il/doctors/%D7%A0%D7%95%D7%A8%D7%94-%D7%92%D7%95%D7%A8%D7%9B%D7%93-%D7%A9%D7%91%D7%A1%D7%95-20898/", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/", "https://www.amutatartzi.org/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.amutatartzi.org/%D7%A6%D7%95%D7%95%D7%AA-%D7%95%D7%91%D7%A2%D7%9C%D7%99-%D7%AA%D7%A4%D7%A7%D7%99%D7%93%D7%99%D7%9D/", "https://www.amutatartzi.org/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%90%D7%A8%D7%A6%D7%99/%D7%AA%D7%A7%D7%A0%D7%95%D7%9F-%D7%94%D7%A2%D7%9E%D7%95%D7%AA%D7%94/", "https://www.amutatartzi.org/דרושים-שותפויות-השכרת-מרפאה/", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%93%D7%B4%D7%A8-%D7%A2%D7%90%D7%99%D7%93%D7%94-%D7%94%D7%99%D7%99%D7%91-%D7%97%D7%9C%D7%99%D7%99%D7%97%D7%9C/", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A4%D7%99%D7%9C%D7%99%D7%A4-%D7%A8%D7%95%D7%96%D7%99%D7%A0%D7%A1%D7%A7%D7%99/", "https://www.amutatartzi.org/team/%D7%93%D7%B4%D7%A8-%D7%A9%D7%9E%D7%A2%D7%95%D7%9F-%D7%90%D7%A8%D7%95%D7%A0%D7%94%D7%99%D7%99%D7%9D/"]</t>
+          <t>["https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2FDr.MichalBraunstein%2F", "https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr.michal.braunstein%2F&amp;is_from_rle", "https://drbraunstein.co.il/", "https://www.shlema.org.il/", "https://drbraunstein.co.il/contact-dermatitis/", "https://drbraunstein.co.il/%D7%92%D7%96-%D7%A6%D7%97%D7%95%D7%A7/", "https://drbraunstein.co.il/#contact"]</t>
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>1.084016810478327e+19</v>
+        <v>3.333212715706692e+19</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4700,7 +4708,7 @@
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/</t>
+          <t>https://drbraunstein.co.il/</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr"/>
@@ -4724,11 +4732,11 @@
         <v>1</v>
       </c>
       <c r="AU26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>PERSON</t>
+          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4749,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>נעם דומניץ</t>
+          <t>נורה גורכד שבסו</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4772,12 +4780,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>domniz.clinic@gmail.com</t>
+          <t>norashapso@gmail.com</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -4785,7 +4793,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://www.dr-domniz.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/</t>
+          <t>https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4795,17 +4803,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>ל הדרך גלריה רוצה לשמוע מידע נוסף? קבעי פגישה עם ד"ר נעם דומניץ וקבלי טיפול מותאם אישית. קביעת תור / וואטסאפ פרטי יצירת קשר 0502174994 רוטשילד 54, כפר סבא (בית עמיתים, קומה 1, חדר 6 (מאחורי בית חב״ד)  | רש״י 30, בני ברק domniz.clinic@gmail.com ד"ר דומניץ מומחה בפוריות, מיילדות וגינקולוגיה. תחומי המרפאה בדיקות הריון ייעוץ טרום הריוני הריון בסיכון התקן תוך רחמי אבחון פוריות ‪טיפולי פוריות ‪ייעוץ פוריות ‪בדיקות פוריות תסמיני גיל המעבר משפט</t>
+          <t>Med Ted לחברים בלבד ארצ״י בשטח ארצ״י בתקשורת ארצ"י בכנסת פודקאסט "סדציה להמונים" נוהל כניסה להסדר הצטרפות צרו קשר טופס דיווח שיימינג טופס בקשת סיוע קהילה לזכרם חזרה &gt; חזרה &gt; ד"ר נורה שבסו גינקולוגיה ומיילדות 052-5363267 norashapso@gmail.com ד"ר נורה גורכד שפסו היא מומחית בגינקולוגיה ומיילדות, ובעלת על־התמחות בפוריות ובהפריה חוץ־גופית (IVF). נורה למדה רפואה בטכניון והתמחתה במרכז הרפואי צפון. כיום היא עובדת כרופאה בכירה ביחידת ה- IVF  וכר</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>"נעם דומניץ"</t>
+          <t>"נורה גורכד שבסו"</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>linked_text</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -4822,7 +4830,7 @@
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-09-04T05:13:39.315015+00:00</t>
+          <t>2026-09-04T04:55:16.280760+00:00</t>
         </is>
       </c>
       <c r="W27" t="n">
@@ -4832,13 +4840,13 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Z27" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
@@ -4847,11 +4855,11 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>["https://www.dr-domniz.co.il/", "https://www.dr-domniz.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/"]</t>
+          <t>["https://www.doctorita.co.il/experts/119054", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%92%D7%95%D7%A8%D7%9B%D7%93-%D7%A9%D7%91%D7%A1%D7%95-%D7%A0%D7%95%D7%A8%D7%94/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=72FD73030256FB59999957F3E61E03EABE6A8F724FC86F83B2380B60589F61A5&amp;RequestId=00000000-0000-0000-0001-000000000612", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=CE57634ABBFA154920019C7FAAD7385EAB0BB0D5FD8189978016A2325E1941AE&amp;RequestId=00000000-0000-0000-0001-000000000428", "https://www.beok.co.il/doctors/Doctors-1114057/", "https://medpage.co.il/doctors/%D7%A0%D7%95%D7%A8%D7%94-%D7%92%D7%95%D7%A8%D7%9B%D7%93-%D7%A9%D7%91%D7%A1%D7%95-20898/", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/", "https://www.amutatartzi.org/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.amutatartzi.org/%D7%A6%D7%95%D7%95%D7%AA-%D7%95%D7%91%D7%A2%D7%9C%D7%99-%D7%AA%D7%A4%D7%A7%D7%99%D7%93%D7%99%D7%9D/", "https://www.amutatartzi.org/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%90%D7%A8%D7%A6%D7%99/%D7%AA%D7%A7%D7%A0%D7%95%D7%9F-%D7%94%D7%A2%D7%9E%D7%95%D7%AA%D7%94/", "https://www.amutatartzi.org/דרושים-שותפויות-השכרת-מרפאה/", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%93%D7%B4%D7%A8-%D7%A2%D7%90%D7%99%D7%93%D7%94-%D7%94%D7%99%D7%99%D7%91-%D7%97%D7%9C%D7%99%D7%99%D7%97%D7%9C/", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A4%D7%99%D7%9C%D7%99%D7%A4-%D7%A8%D7%95%D7%96%D7%99%D7%A0%D7%A1%D7%A7%D7%99/", "https://www.amutatartzi.org/team/%D7%93%D7%B4%D7%A8-%D7%A9%D7%9E%D7%A2%D7%95%D7%9F-%D7%90%D7%A8%D7%95%D7%A0%D7%94%D7%99%D7%99%D7%9D/"]</t>
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>1.084016810478327e+19</v>
+        <v>3.252050431434981e+19</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4862,7 +4870,7 @@
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>https://www.dr-domniz.co.il/</t>
+          <t>https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr"/>
@@ -4886,11 +4894,11 @@
         <v>1</v>
       </c>
       <c r="AU27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
+          <t>PERSON</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4911,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>נתנאל אלקבץ</t>
+          <t>נעם דומניץ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4934,7 +4942,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>aimee.medicalclinic@gmail.com</t>
+          <t>domniz.clinic@gmail.com</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -4947,7 +4955,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://www.aimeemedical.co.il/clinical-dietitian/</t>
+          <t>https://www.dr-domniz.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4957,13 +4965,12 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>הריון בסיכון או לצד מחלות רקע-  הוא תהליך אישי, מותאם ומכיל.
-עם ליווי מקצועי של אופק כהן־אלקבץ, דיאטנית קלינית מומחית, תוכלי לשמור על בריאותך ובריאות העובר ולחוות הריון רגוע ומאוזן. לתיאום פגישה אישית עם ד"ר נתנאל אלקבץ aimee.medicalclinic@gmail.com 053-338-8023 ניווט ראשי אודותינו המוצרים שלנו צרו קשר שירותי הקליניקה מעקב הריון והריון בסיכון גבוהה אולטרסאונד מתקדם בירור בעיות פריון אסתטיקה גינקולוגית תפקודית לביופלסטיקה דיטנית קלינית -</t>
+          <t>ל הדרך גלריה רוצה לשמוע מידע נוסף? קבעי פגישה עם ד"ר נעם דומניץ וקבלי טיפול מותאם אישית. קביעת תור / וואטסאפ פרטי יצירת קשר 0502174994 רוטשילד 54, כפר סבא (בית עמיתים, קומה 1, חדר 6 (מאחורי בית חב״ד)  | רש״י 30, בני ברק domniz.clinic@gmail.com ד"ר דומניץ מומחה בפוריות, מיילדות וגינקולוגיה. תחומי המרפאה בדיקות הריון ייעוץ טרום הריוני הריון בסיכון התקן תוך רחמי אבחון פוריות ‪טיפולי פוריות ‪ייעוץ פוריות ‪בדיקות פוריות תסמיני גיל המעבר משפט</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>"נתנאל אלקבץ"</t>
+          <t>"נעם דומניץ"</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -4985,7 +4992,7 @@
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-09-04T05:24:06.061110+00:00</t>
+          <t>2026-09-04T05:13:39.315015+00:00</t>
         </is>
       </c>
       <c r="W28" t="n">
@@ -4995,10 +5002,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -5010,11 +5017,11 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>["https://www.infomed.co.il/experts/152655/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2F61560664132234%2F", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%90%D7%9C%D7%A7%D7%91%D7%A5-%D7%A0%D7%AA%D7%A0%D7%90%D7%9C/", "https://www.medreviews.co.il/provider/dr-elkabetz-netanel", "https://www.aimeemedical.co.il/about-us/", "https://www.aimeemedical.co.il/clinical-dietitian/", "https://www.aimeemedical.co.il/contact/"]</t>
+          <t>["https://www.dr-domniz.co.il/", "https://www.dr-domniz.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/"]</t>
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>1.084016810478327e+19</v>
+        <v>3.252050431434981e+19</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5025,7 +5032,7 @@
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>https://www.medreviews.co.il/provider/dr-elkabetz-netanel</t>
+          <t>https://www.dr-domniz.co.il/</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr"/>
@@ -5066,7 +5073,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>עמיחי רוטנשטרייך</t>
+          <t>נתנאל אלקבץ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5097,12 +5104,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>prof.rottenstreich@gmail.com</t>
+          <t>aimee.medicalclinic@gmail.com</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -5110,7 +5117,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://www.prof-rottenstreich.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA</t>
+          <t>https://www.aimeemedical.co.il/clinical-dietitian/</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -5120,12 +5127,13 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>פואה פרופסור חבר מטעם האוניברסיטה העברית האגף למיילדות וגינקולוגיה, בית החולים וולפסון, חולון רופא בכיר ומנהל שירות ביחידה להיריון בסיכון Chat Phone פרופ׳ עמיחי רוטנשטרייך מומחה למיילדות גי נ קולוגיה והיריון בסיכון גבוה prof.rottenstreich@gmail.com 055-9787751            , 055-4353787 כל הזכויות שמורות עמיחי רוטנשטרייך 2024 © bottom of page</t>
+          <t>הריון בסיכון או לצד מחלות רקע-  הוא תהליך אישי, מותאם ומכיל.
+עם ליווי מקצועי של אופק כהן־אלקבץ, דיאטנית קלינית מומחית, תוכלי לשמור על בריאותך ובריאות העובר ולחוות הריון רגוע ומאוזן. לתיאום פגישה אישית עם ד"ר נתנאל אלקבץ aimee.medicalclinic@gmail.com 053-338-8023 ניווט ראשי אודותינו המוצרים שלנו צרו קשר שירותי הקליניקה מעקב הריון והריון בסיכון גבוהה אולטרסאונד מתקדם בירור בעיות פריון אסתטיקה גינקולוגית תפקודית לביופלסטיקה דיטנית קלינית -</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>"עמיחי רוטנשטרייך"</t>
+          <t>"נתנאל אלקבץ"</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -5147,7 +5155,7 @@
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-04T06:21:38.973409+00:00</t>
+          <t>2026-09-04T05:24:06.061110+00:00</t>
         </is>
       </c>
       <c r="W29" t="n">
@@ -5157,10 +5165,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -5172,11 +5180,11 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>["https://www.prof-rottenstreich.co.il/", "https://www.prof-rottenstreich.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.prof-rottenstreich.co.il/%D7%AA%D7%97%D7%95%D7%9E%D7%99-%D7%A4%D7%A2%D7%99%D7%9C%D7%95%D7%AA"]</t>
+          <t>["https://www.infomed.co.il/experts/152655/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2F61560664132234%2F", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%90%D7%9C%D7%A7%D7%91%D7%A5-%D7%A0%D7%AA%D7%A0%D7%90%D7%9C/", "https://www.medreviews.co.il/provider/dr-elkabetz-netanel", "https://www.aimeemedical.co.il/about-us/", "https://www.aimeemedical.co.il/clinical-dietitian/", "https://www.aimeemedical.co.il/contact/"]</t>
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>1.084016810478327e+19</v>
+        <v>3.252050431434981e+19</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5187,7 +5195,7 @@
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>https://www.prof-rottenstreich.co.il/</t>
+          <t>https://www.medreviews.co.il/provider/dr-elkabetz-netanel</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr"/>
@@ -5211,11 +5219,11 @@
         <v>1</v>
       </c>
       <c r="AU29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>PERSON</t>
+          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5236,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ערן ברזילי</t>
+          <t>עמיחי רוטנשטרייך</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5259,7 +5267,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>prof.eran.barzilay@gmail.com</t>
+          <t>prof.rottenstreich@gmail.com</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -5272,7 +5280,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
+          <t>https://www.prof-rottenstreich.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -5282,17 +5290,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>ת ה- MD-PhD היוקרתית של הפקולטה לרפואה באוניברסיטת תל אביב, בהצטיינות. עמודים דף הבית אודות אולטרסאונד בהריון ממצאים לא תקינים אולטרסאונד גניקולוגי צור קשר צור קשר ברודצקי 43, כניסה ב', רמת אביב, תל אביב יפו 073-7815218 prof.eran.barzilay@gmail.com פרופ' ערן ברזילי באינפומד © כל הזכויות שמורות לאינפומד בע"מ פרטיות המבקרים באתר חשובה לנו כדי לשפר את חוויית הגלישה, אתר זה משתמש בקבצי עוגיות  (Cookies), המשך גלישה באתר מהווה הסכמתך לכך. מד</t>
+          <t>פואה פרופסור חבר מטעם האוניברסיטה העברית האגף למיילדות וגינקולוגיה, בית החולים וולפסון, חולון רופא בכיר ומנהל שירות ביחידה להיריון בסיכון Chat Phone פרופ׳ עמיחי רוטנשטרייך מומחה למיילדות גי נ קולוגיה והיריון בסיכון גבוה prof.rottenstreich@gmail.com 055-9787751            , 055-4353787 כל הזכויות שמורות עמיחי רוטנשטרייך 2024 © bottom of page</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>"ערן ברזילי"</t>
+          <t>"עמיחי רוטנשטרייך"</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>linked_text</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -5309,7 +5317,7 @@
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-09-04T06:36:53.022308+00:00</t>
+          <t>2026-09-04T06:21:38.973409+00:00</t>
         </is>
       </c>
       <c r="W30" t="n">
@@ -5319,13 +5327,13 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
@@ -5334,11 +5342,11 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>["https://www.instagram.com/proferanbarzilay/", "https://www.bgu.ac.il/people/barzilae/", "https://www.bgu.ac.il/en/people/barzilae/", "https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://dr-barzilay.com/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/"]</t>
+          <t>["https://www.prof-rottenstreich.co.il/", "https://www.prof-rottenstreich.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.prof-rottenstreich.co.il/%D7%AA%D7%97%D7%95%D7%9E%D7%99-%D7%A4%D7%A2%D7%99%D7%9C%D7%95%D7%AA"]</t>
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>1.084016810478327e+19</v>
+        <v>3.252050431434981e+19</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5349,7 +5357,7 @@
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
+          <t>https://www.prof-rottenstreich.co.il/</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr"/>
@@ -5390,7 +5398,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>פרופ' משען נדב</t>
+          <t>ערן ברזילי</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5410,18 +5418,18 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=26deea29-fa58-44cd-a7ba-96d9df718414</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ima</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>drnadavmic@gmail.com</t>
+          <t>prof.eran.barzilay@gmail.com</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -5434,7 +5442,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://www.dr-mishan.co.il/</t>
+          <t>https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -5444,12 +5452,12 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>פרופ' נדב משען ✅️ קבעי כעת ביקור בקליניקה הפרטית ✔️ דלג לתוכן 052-4322732 03-5716996 drnadavmic@gmail.com רחוב רמב"ם 26, גבעתיים בית – פרופ' נדב משען אודות שירותי המרפאה סרטן הרחם סרטן צוואר הרחם סרטן שחלות סרטן הערייה (vulva) בדיקת פאפ בדיקת קולפוסקופיה נשאיות של BRCA קוניזציה גניקולוגיה כללית מחקר רפוא</t>
+          <t>ת ה- MD-PhD היוקרתית של הפקולטה לרפואה באוניברסיטת תל אביב, בהצטיינות. עמודים דף הבית אודות אולטרסאונד בהריון ממצאים לא תקינים אולטרסאונד גניקולוגי צור קשר צור קשר ברודצקי 43, כניסה ב', רמת אביב, תל אביב יפו 073-7815218 prof.eran.barzilay@gmail.com פרופ' ערן ברזילי באינפומד © כל הזכויות שמורות לאינפומד בע"מ פרטיות המבקרים באתר חשובה לנו כדי לשפר את חוויית הגלישה, אתר זה משתמש בקבצי עוגיות  (Cookies), המשך גלישה באתר מהווה הסכמתך לכך. מד</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>"משען נדב"</t>
+          <t>"ערן ברזילי"</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -5471,11 +5479,11 @@
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-09-04T04:19:53.405262+00:00</t>
+          <t>2026-09-04T06:36:53.022308+00:00</t>
         </is>
       </c>
       <c r="W31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -5484,7 +5492,7 @@
         <v>4</v>
       </c>
       <c r="Z31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AA31" t="n">
         <v>1</v>
@@ -5496,11 +5504,11 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=26deea29-fa58-44cd-a7ba-96d9df718414", "https://doctors.assuta.co.il/doctor/nadav-michaan-80431?readmore=true", "https://www.dr-mishan.co.il/", "https://md-digital.co.il/", "https://www.dr-mishan.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.infomed.co.il/experts/144408/", "https://medpage.co.il/doctors/%D7%A0%D7%93%D7%91-%D7%9E%D7%A9%D7%A2%D7%9F-20445/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%A0%D7%93%D7%91-%D7%9E%D7%A9%D7%A2%D7%9F/", "https://www.danielly.co.il/doctors/view/%D7%93%D7%A8-%D7%A0%D7%93%D7%91-%D7%9E%D7%A9%D7%A2%D7%9F-%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92", "https://www.danielly.co.il/contact/index", "https://www.danielly.co.il/contact", "https://www.danielly.co.il/about", "https://www.danielly.co.il/contact?apt=1&amp;doctor_id=668"]</t>
+          <t>["https://www.instagram.com/proferanbarzilay/", "https://www.bgu.ac.il/people/barzilae/", "https://www.bgu.ac.il/en/people/barzilae/", "https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://dr-barzilay.com/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/"]</t>
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>1.444243935191125e+19</v>
+        <v>3.252050431434981e+19</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5511,7 +5519,7 @@
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>https://www.dr-mishan.co.il/</t>
+          <t>https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr"/>
@@ -5552,12 +5560,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>רחל דהן</t>
+          <t>פרופ' משען נדב</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>family_doctor</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -5572,18 +5580,18 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=26deea29-fa58-44cd-a7ba-96d9df718414</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>ima</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>racheldahan@hotmail.com</t>
+          <t>drnadavmic@gmail.com</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -5596,7 +5604,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://www.hebpsy.net/showprofile.asp?id=18767</t>
+          <t>https://www.dr-mishan.co.il/</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -5606,12 +5614,12 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>שית בהיפנוזה יועצת גמילה מעישון טיפול בהפרעות שינה, ושינוי הרגלי חיים. רכזת מחקר המחלקה לרפואת משפחה -חיפה מנהלת מרפאת לב הקריה, שירותי בריאות כללית, קרית אתא. טל: 0543130956 אתר אינטרנט http://hypnosis.99k.org ;      : racheldahan@hotmail.com "דוא"ל הפרטים המובאים בכרטיס האישי של רחל דהן, ובכללם פרטים בדבר התואר האקדמי וההכשרה המקצועית נוסחו על ידי רחל דהן ובאחריותו/ה. נצפים ביותר יומנו של עורך וידאו - עדויות מהשבעה באוקטובר / רוני אלפ</t>
+          <t>פרופ' נדב משען ✅️ קבעי כעת ביקור בקליניקה הפרטית ✔️ דלג לתוכן 052-4322732 03-5716996 drnadavmic@gmail.com רחוב רמב"ם 26, גבעתיים בית – פרופ' נדב משען אודות שירותי המרפאה סרטן הרחם סרטן צוואר הרחם סרטן שחלות סרטן הערייה (vulva) בדיקת פאפ בדיקת קולפוסקופיה נשאיות של BRCA קוניזציה גניקולוגיה כללית מחקר רפוא</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>"רחל דהן" רפואת משפחה</t>
+          <t>"משען נדב"</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -5628,16 +5636,16 @@
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-09-10T13:53:25.006579+00:00</t>
+          <t>2026-09-04T04:19:53.405262+00:00</t>
         </is>
       </c>
       <c r="W32" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
@@ -5646,7 +5654,7 @@
         <v>4</v>
       </c>
       <c r="Z32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA32" t="n">
         <v>1</v>
@@ -5658,42 +5666,34 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>["https://www.doctorita.co.il/experts/141424", "https://www.colbonews.co.il/health/166678/", "https://www.hebpsy.net/showprofile.asp?id=18767", "https://www.hebpsy.net/me.asp?id=72&amp;page=6", "https://www.hebpsy.net/pl.asp?cat=about", "https://www.hebpsy.net/me.asp?id=72", "https://www.hebpsy.net/sysMsg.asp?id=profile_about#p10", "https://www.hebpsy.net/sysMsg.asp?id=profile_about", "https://www.hebpsy.net/showprofile.asp?id=18767#profile", "https://www.hebpsy.net/me.asp?id=72&amp;page=6#contact", "https://www.hebpsy.net/sysMsg.asp?id=profile_promotPL", "https://www.hebpsy.net/me.asp?id=72#contact", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fraceldahan%2F", "https://www.facebook.com/public/%D7%A8%D7%97%D7%9C-%D7%93%D7%94%D7%9F/", "https://www.myheritage.com/names/%D7%A8%D7%97%D7%9C_%D7%93%D7%94%D7%9F", "https://gen.rlzm.co.il/persons/%D7%A8%D7%97%D7%9C-%D7%93%D7%94%D7%9F/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=26deea29-fa58-44cd-a7ba-96d9df718414", "https://doctors.assuta.co.il/doctor/nadav-michaan-80431?readmore=true", "https://www.dr-mishan.co.il/", "https://md-digital.co.il/", "https://www.dr-mishan.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.infomed.co.il/experts/144408/", "https://medpage.co.il/doctors/%D7%A0%D7%93%D7%91-%D7%9E%D7%A9%D7%A2%D7%9F-20445/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%A0%D7%93%D7%91-%D7%9E%D7%A9%D7%A2%D7%9F/", "https://www.danielly.co.il/doctors/view/%D7%93%D7%A8-%D7%A0%D7%93%D7%91-%D7%9E%D7%A9%D7%A2%D7%9F-%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92", "https://www.danielly.co.il/contact/index", "https://www.danielly.co.il/contact", "https://www.danielly.co.il/about", "https://www.danielly.co.il/contact?apt=1&amp;doctor_id=668"]</t>
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>1.081065874445936e+19</v>
+        <v>4.332731805573375e+19</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
       </c>
       <c r="AF32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>https://www.hebpsy.net/showprofile.asp?id=18767</t>
+          <t>https://www.dr-mishan.co.il/</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr"/>
       <c r="AJ32" t="inlineStr"/>
       <c r="AK32" t="inlineStr"/>
-      <c r="AL32" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AN32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>רחל דהן - רופאה רחל דהן - רופאה דלג לתוכן ראשי - מקש קיצור 2 (לחץ Enter) דף הבית - מקש קיצור 1 (לחץ Enter) דלג לתפריט ראשי - מקש קיצור 5 (לחץ Enter) דלג לתיבת חיפוש - מקש קיצור 4 (לחץ Enter) צור קשר - מקש קיצור 9 (לחץ Enter) הצהרת נגישות - מקש קיצור 0 (לחץ Enter) סגור עזרה ראשונה נפשית - בהתנדבות אודות והצטרפות טיפול נפשי מוזל טיפול נפשי בתל אביב מטפלים בהסדר קופת חולים פנויים לקבלת מטופלים חדשים טיפול זוגי טיפול התנהגותי קוגניטיבי - CBT הדרכת הורים טיפול נפשי לילדים אבחון פסיכולוגי לילדים פסיכולוגית בתל אביב פסיכולוגים כניסה רישום צרו קשר חיפוש × × אימייל (דוא"ל) סיסמא שכחת את הסיסמה? הקלידו אימייל ולחצו כאן כניסה אני מסכימ.ה להצטרף לרשימת התפוצה לקבלת עדכונים ומידע שיווקי זכור אותי רישום משתמש חדש ביטול פסיכולוגיה עברית ראשי השער שלי תיבת מסרים כרטיס הביקור שלי הגדרות חשבון אודות פסיכולוגיה עברית שאלות נפוצות יציאה מאמרים המאמרים שלי הגשת טקסט לפרסום נבחרי העורכת אספרגר טיפולי המרה סקס טוב דיו רגשות חינוך מיני תסמונת טורט ניכור הורי רשימות קריאה הכותבים קטגוריות מאמרים מאמרים לפי נושאים ניוזלטר בלוג</t>
-        </is>
-      </c>
-      <c r="AP32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ32" t="inlineStr"/>
       <c r="AR32" t="n">
         <v>1</v>
@@ -5722,12 +5722,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>אוהד חורי</t>
+          <t>רחל דהן</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>ohadho@clalit.org.il</t>
+          <t>racheldahan@hotmail.com</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -5762,11 +5762,11 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
+          <t>https://www.hebpsy.net/showprofile.asp?id=18767</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -5776,17 +5776,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
+          <t>שית בהיפנוזה יועצת גמילה מעישון טיפול בהפרעות שינה, ושינוי הרגלי חיים. רכזת מחקר המחלקה לרפואת משפחה -חיפה מנהלת מרפאת לב הקריה, שירותי בריאות כללית, קרית אתא. טל: 0543130956 אתר אינטרנט http://hypnosis.99k.org ;      : racheldahan@hotmail.com "דוא"ל הפרטים המובאים בכרטיס האישי של רחל דהן, ובכללם פרטים בדבר התואר האקדמי וההכשרה המקצועית נוסחו על ידי רחל דהן ובאחריותו/ה. נצפים ביותר יומנו של עורך וידאו - עדויות מהשבעה באוקטובר / רוני אלפ</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>"אוהד חורי" יילוד site:clalit.co.il</t>
+          <t>"רחל דהן" רפואת משפחה</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>search_snippet</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -5798,12 +5798,12 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-09-09T23:21:42.073181+00:00</t>
+          <t>2026-09-10T13:53:25.006579+00:00</t>
         </is>
       </c>
       <c r="W33" t="n">
@@ -5813,37 +5813,37 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>ddgs:yahoo+ddgs:bing</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx", "https://www.doctorita.co.il/experts/94233", "https://www.ha-makom.co.il/author/vhdcvry/", "https://foody.co.il/author/ohad/", "https://knowmore.co.il/doctors/אוהד-חורי-2/", "https://stage.ha-makom.co.il/author/vhdcvry/", "https://www.facebook.com/YoldotBeilinson/videos/%D7%9E%D7%94-%D7%96%D7%95-%D7%9C%D7%99%D7%93%D7%AA-vbac-%D7%A9%D7%9B%D7%95%D7%9C%D7%9F-%D7%9E%D7%93%D7%91%D7%A8%D7%95%D7%AA-%D7%A2%D7%9C%D7%99%D7%94-%D7%A2%D7%95%D7%A9%D7%99%D7%9D-%D7%9C%D7%9B%D7%9F-%D7%A1%D7%93%D7%A8-%D7%91%D7%9E%D7%95%D7%A9%D7%92%D7%99%D7%9D-%D7%A2%D7%9D-%D7%93%D7%A8-%D7%90%D7%95%D7%94%D7%93-%D7%97%D7%95%D7%A8%D7%99-%D7%A9%D7%9B%D7%90%D7%9F-%D7%9B%D7%93%D7%99/1754039901764363/"]</t>
+          <t>["https://www.doctorita.co.il/experts/141424", "https://www.colbonews.co.il/health/166678/", "https://www.hebpsy.net/showprofile.asp?id=18767", "https://www.hebpsy.net/me.asp?id=72&amp;page=6", "https://www.hebpsy.net/pl.asp?cat=about", "https://www.hebpsy.net/me.asp?id=72", "https://www.hebpsy.net/sysMsg.asp?id=profile_about#p10", "https://www.hebpsy.net/sysMsg.asp?id=profile_about", "https://www.hebpsy.net/showprofile.asp?id=18767#profile", "https://www.hebpsy.net/me.asp?id=72&amp;page=6#contact", "https://www.hebpsy.net/sysMsg.asp?id=profile_promotPL", "https://www.hebpsy.net/me.asp?id=72#contact", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fraceldahan%2F", "https://www.facebook.com/public/%D7%A8%D7%97%D7%9C-%D7%93%D7%94%D7%9F/", "https://www.myheritage.com/names/%D7%A8%D7%97%D7%9C_%D7%93%D7%94%D7%9F", "https://gen.rlzm.co.il/persons/%D7%A8%D7%97%D7%9C-%D7%93%D7%94%D7%9F/"]</t>
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>1.171122655624138e+19</v>
+        <v>3.243197623337809e+19</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
+          <t>https://www.hebpsy.net/showprofile.asp?id=18767</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr"/>
@@ -5860,7 +5860,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
+          <t>רחל דהן - רופאה רחל דהן - רופאה דלג לתוכן ראשי - מקש קיצור 2 (לחץ Enter) דף הבית - מקש קיצור 1 (לחץ Enter) דלג לתפריט ראשי - מקש קיצור 5 (לחץ Enter) דלג לתיבת חיפוש - מקש קיצור 4 (לחץ Enter) צור קשר - מקש קיצור 9 (לחץ Enter) הצהרת נגישות - מקש קיצור 0 (לחץ Enter) סגור עזרה ראשונה נפשית - בהתנדבות אודות והצטרפות טיפול נפשי מוזל טיפול נפשי בתל אביב מטפלים בהסדר קופת חולים פנויים לקבלת מטופלים חדשים טיפול זוגי טיפול התנהגותי קוגניטיבי - CBT הדרכת הורים טיפול נפשי לילדים אבחון פסיכולוגי לילדים פסיכולוגית בתל אביב פסיכולוגים כניסה רישום צרו קשר חיפוש × × אימייל (דוא"ל) סיסמא שכחת את הסיסמה? הקלידו אימייל ולחצו כאן כניסה אני מסכימ.ה להצטרף לרשימת התפוצה לקבלת עדכונים ומידע שיווקי זכור אותי רישום משתמש חדש ביטול פסיכולוגיה עברית ראשי השער שלי תיבת מסרים כרטיס הביקור שלי הגדרות חשבון אודות פסיכולוגיה עברית שאלות נפוצות יציאה מאמרים המאמרים שלי הגשת טקסט לפרסום נבחרי העורכת אספרגר טיפולי המרה סקס טוב דיו רגשות חינוך מיני תסמונת טורט ניכור הורי רשימות קריאה הכותבים קטגוריות מאמרים מאמרים לפי נושאים ניוזלטר בלוג</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr"/>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>אופיר אלמסי</t>
+          <t>אוהד חורי</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>ofiral@bgu.ac.il</t>
+          <t>ohadho@clalit.org.il</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>بحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان אופיר אלמסי ד"ר אופיר אלמסי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ofiral@bgu.ac.il Cookies Settings</t>
+          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>"אופיר אלמסי"</t>
+          <t>"אוהד חורי" יילוד site:clalit.co.il</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -5973,36 +5973,36 @@
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-09-04T13:52:28.665114+00:00</t>
+          <t>2026-09-09T23:21:42.073181+00:00</t>
         </is>
       </c>
       <c r="W34" t="n">
+        <v>8</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA34" t="n">
         <v>2</v>
       </c>
-      <c r="X34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1</v>
-      </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/ofiral/", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/almasi-o.aspx", "https://www.bgu.ac.il/ar/people/ofiral/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx", "https://www.doctorita.co.il/experts/94233", "https://www.ha-makom.co.il/author/vhdcvry/", "https://foody.co.il/author/ohad/", "https://knowmore.co.il/doctors/אוהד-חורי-2/", "https://stage.ha-makom.co.il/author/vhdcvry/", "https://www.facebook.com/YoldotBeilinson/videos/%D7%9E%D7%94-%D7%96%D7%95-%D7%9C%D7%99%D7%93%D7%AA-vbac-%D7%A9%D7%9B%D7%95%D7%9C%D7%9F-%D7%9E%D7%93%D7%91%D7%A8%D7%95%D7%AA-%D7%A2%D7%9C%D7%99%D7%94-%D7%A2%D7%95%D7%A9%D7%99%D7%9D-%D7%9C%D7%9B%D7%9F-%D7%A1%D7%93%D7%A8-%D7%91%D7%9E%D7%95%D7%A9%D7%92%D7%99%D7%9D-%D7%A2%D7%9D-%D7%93%D7%A8-%D7%90%D7%95%D7%94%D7%93-%D7%97%D7%95%D7%A8%D7%99-%D7%A9%D7%9B%D7%90%D7%9F-%D7%9B%D7%93%D7%99/1754039901764363/"]</t>
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>1.171108759354363e+19</v>
+        <v>3.513367966872413e+19</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -6013,19 +6013,27 @@
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr"/>
       <c r="AJ34" t="inlineStr"/>
       <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="inlineStr"/>
-      <c r="AN34" t="inlineStr"/>
-      <c r="AO34" t="inlineStr"/>
-      <c r="AP34" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr"/>
       <c r="AQ34" t="inlineStr"/>
       <c r="AR34" t="n">
         <v>1</v>
@@ -6054,7 +6062,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>אורנה רייכמן</t>
+          <t>אופיר אלמסי</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -6085,7 +6093,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>oreich@szmc.org.il</t>
+          <t>ofiral@bgu.ac.il</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -6098,7 +6106,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
+          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -6108,12 +6116,12 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t xml:space="preserve">אזור אישי רופאים בשערי צדק ד"ר אורנה  רייכמן מנהלת יולדות א' Dr. Orna  Reichman התמחות: גינקולוגיה ויילוד תת התמחות: מחלות שפירות של העריה והלדן הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית משרד 02-6666708 משרד: 02-6666708 oreich@szmc.org.il oreich@szmc.org.il לימודים והכשרה תואר ראשון במדעי החיים באוניברסיטה העברית בירושלים בהצטיינות - 1993 לימודי הרפואה בבית ספר לרפואה של האוניברסיטה העברית הדסה - 1999 ההתמחות במיילדות וגניקולוגיה במרכז </t>
+          <t>بحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان אופיר אלמסי ד"ר אופיר אלמסי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ofiral@bgu.ac.il Cookies Settings</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>"אורנה רייכמן"</t>
+          <t>"אופיר אלמסי"</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -6135,36 +6143,36 @@
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-09-04T13:56:16.031154+00:00</t>
+          <t>2026-09-04T13:52:28.665114+00:00</t>
         </is>
       </c>
       <c r="W35" t="n">
         <v>2</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y35" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AA35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>["https://www.infomed.co.il/experts/149541/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A8%D7%99%D7%99%D7%9B%D7%9E%D7%9F-%D7%90%D7%95%D7%A8%D7%A0%D7%94/", "https://docsrated.com/doctors/אורנה-רייכמן", "https://www.doctorita.co.il/experts/95406", "https://drtor.co.il/doctor/23937", "https://drtor.co.il/cdn-cgi/l/email-protection#8cefe3e2f8edeff8cce8fef8e3fea2efe3a2e5e0", "https://www.beok.co.il/doctors/Doctors-1340/", "https://www.szmc.org.il/doctors/reichman-orna/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://drtor.co.il/cdn-cgi/l/email-protection#3b5854554f5a584f7b5f494f5449155854155257"]</t>
+          <t>["https://www.bgu.ac.il/people/ofiral/", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/almasi-o.aspx", "https://www.bgu.ac.il/ar/people/ofiral/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>1.171108759354363e+19</v>
+        <v>3.51332627806309e+19</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6175,7 +6183,7 @@
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
+          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr"/>
@@ -6216,7 +6224,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ארנון סמואלוב</t>
+          <t>אורנה רייכמן</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6247,7 +6255,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>smuelof@szmc.org.il</t>
+          <t>oreich@szmc.org.il</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -6260,7 +6268,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
+          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -6270,12 +6278,12 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>ופ' ארנון  סמואלוב רופא בכיר Prof. Arnon  Samueloff התמחות: גינקולוגיה ויילוד תת התמחות: מיילדות וסיבוכי הריון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 02-6666656 מחלקה: 02-6666656 smuelof@szmc.org.il smuelof@szmc.org.il נסיון מקצועי התמחות ברפואת האם והעובר, סן אנטוניו, ארה"ב רופא בכיר, מחלקת נשים ויולדות, המרכז הרפואי הדסה מנהל, מרפאת היריון בסיכון, קופת חולים לאומית מנהל, מרפאת סוכרת, קופת חולים</t>
+          <t xml:space="preserve">אזור אישי רופאים בשערי צדק ד"ר אורנה  רייכמן מנהלת יולדות א' Dr. Orna  Reichman התמחות: גינקולוגיה ויילוד תת התמחות: מחלות שפירות של העריה והלדן הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית משרד 02-6666708 משרד: 02-6666708 oreich@szmc.org.il oreich@szmc.org.il לימודים והכשרה תואר ראשון במדעי החיים באוניברסיטה העברית בירושלים בהצטיינות - 1993 לימודי הרפואה בבית ספר לרפואה של האוניברסיטה העברית הדסה - 1999 ההתמחות במיילדות וגניקולוגיה במרכז </t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>"ארנון סמואלוב"</t>
+          <t>"אורנה רייכמן"</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -6297,36 +6305,36 @@
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-09-04T14:35:26.198949+00:00</t>
+          <t>2026-09-04T13:56:16.031154+00:00</t>
         </is>
       </c>
       <c r="W36" t="n">
         <v>2</v>
       </c>
       <c r="X36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>["https://docsrated.com/doctors/ארנון-סמואלוב", "https://www.infomed.co.il/experts/93587/", "https://www.doctorita.co.il/experts/47319", "https://www.beok.co.il/doctors/Doctors-116451/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A1%D7%9E%D7%95%D7%90%D7%9C%D7%95%D7%91-%D7%90%D7%A8%D7%A0%D7%95%D7%9F/", "https://www.szmc.org.il/doctors/samueloff-arnon/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
+          <t>["https://www.infomed.co.il/experts/149541/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A8%D7%99%D7%99%D7%9B%D7%9E%D7%9F-%D7%90%D7%95%D7%A8%D7%A0%D7%94/", "https://docsrated.com/doctors/אורנה-רייכמן", "https://www.doctorita.co.il/experts/95406", "https://drtor.co.il/doctor/23937", "https://drtor.co.il/cdn-cgi/l/email-protection#8cefe3e2f8edeff8cce8fef8e3fea2efe3a2e5e0", "https://www.beok.co.il/doctors/Doctors-1340/", "https://www.szmc.org.il/doctors/reichman-orna/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://drtor.co.il/cdn-cgi/l/email-protection#3b5854554f5a584f7b5f494f5449155854155257"]</t>
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>1.171108759354363e+19</v>
+        <v>3.51332627806309e+19</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6337,7 +6345,7 @@
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
+          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr"/>
@@ -6378,7 +6386,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>גלי פריאנטה</t>
+          <t>ארנון סמואלוב</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6409,7 +6417,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>galipa@bgu.ac.il</t>
+          <t>smuelof@szmc.org.il</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -6422,7 +6430,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
+          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -6432,12 +6440,12 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>ث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان גלי פריאנטה פרופ' גלי פריאנטה Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section galipa@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0001-6484-3769 Orcid Number Cookies Settings</t>
+          <t>ופ' ארנון  סמואלוב רופא בכיר Prof. Arnon  Samueloff התמחות: גינקולוגיה ויילוד תת התמחות: מיילדות וסיבוכי הריון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 02-6666656 מחלקה: 02-6666656 smuelof@szmc.org.il smuelof@szmc.org.il נסיון מקצועי התמחות ברפואת האם והעובר, סן אנטוניו, ארה"ב רופא בכיר, מחלקת נשים ויולדות, המרכז הרפואי הדסה מנהל, מרפאת היריון בסיכון, קופת חולים לאומית מנהל, מרפאת סוכרת, קופת חולים</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>"גלי פריאנטה"</t>
+          <t>"ארנון סמואלוב"</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -6459,36 +6467,36 @@
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-09-03T23:09:10.396904+00:00</t>
+          <t>2026-09-04T14:35:26.198949+00:00</t>
         </is>
       </c>
       <c r="W37" t="n">
         <v>2</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
         <v>6</v>
       </c>
       <c r="Z37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/galipa/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-%D7%92%D7%9C%D7%99/", "https://medpage.co.il/doctors/%D7%92%D7%9C%D7%99-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-25448/", "https://www.doctorita.co.il/experts/131973", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/pariente-g.aspx", "https://www.bgu.ac.il/ar/people/galipa/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://docsrated.com/doctors/ארנון-סמואלוב", "https://www.infomed.co.il/experts/93587/", "https://www.doctorita.co.il/experts/47319", "https://www.beok.co.il/doctors/Doctors-116451/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A1%D7%9E%D7%95%D7%90%D7%9C%D7%95%D7%91-%D7%90%D7%A8%D7%A0%D7%95%D7%9F/", "https://www.szmc.org.il/doctors/samueloff-arnon/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>1.170738155316593e+19</v>
+        <v>3.51332627806309e+19</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6499,7 +6507,7 @@
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
+          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr"/>
@@ -6540,7 +6548,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ד"ר ברוך יואב</t>
+          <t>גלי פריאנטה</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6560,18 +6568,18 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>ima</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>yoavb@tlvmc.gov.il</t>
+          <t>galipa@bgu.ac.il</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -6584,7 +6592,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
+          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -6594,12 +6602,12 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>י לאורוגינקולוגיה ורצפת אגן שטחי התעניינות ועיסוק מיוחדים ניתוחים וגינאליים וזעיר פולשניים לצניחת אברי האגן טיפול תרופתי וכירורגי לדליפת שתן מרפאת ערייה וצוואר הרחם אבחון וטיפול בקונדילומות ונגעים טרום ממאירים יצירת קשר yoavb@tlvmc.gov.il יחידות רפואיות אורוגינקולוגיה ורצפת האגן רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות נעים להכיר, ​ד"ר יואב ברוך איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציונ</t>
+          <t>ث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان גלי פריאנטה פרופ' גלי פריאנטה Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section galipa@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0001-6484-3769 Orcid Number Cookies Settings</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>"ברוך יואב"</t>
+          <t>"גלי פריאנטה"</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -6616,25 +6624,25 @@
         <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-09-05T00:14:33.719515+00:00</t>
+          <t>2026-09-03T23:09:10.396904+00:00</t>
         </is>
       </c>
       <c r="W38" t="n">
         <v>2</v>
       </c>
       <c r="X38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
         <v>6</v>
       </c>
       <c r="Z38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA38" t="n">
         <v>1</v>
@@ -6646,11 +6654,11 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345", "https://soundcloud.com/wx8fnfybplpt", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A-%D7%91%D7%A8%D7%95%D7%9A/pfbid02DHSfATmK3MDpizZrgGTLc9ZAvZHXUsR9pSCjhd6pmWqSMFvq1BwehNeHCARNitMol/", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/pfbid02BMPnQXQYXt6vzctmybagMUp3nWACPxhE1LqhYeJYs1fVgXWA6B1cK2Z9VpRJ8cJRl/", "https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/", "https://pubmed.ncbi.nlm.nih.gov/?term=yoav+baruch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000546", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/61559143005435/", "https://www.infomed.co.il/experts/151203/", "https://www.yoavbaruch.com/", "https://www.yoavbaruch.com/about-6", "https://theindex.co.il/phone/ברוך-יואב-0777573393/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000504"]</t>
+          <t>["https://www.bgu.ac.il/people/galipa/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-%D7%92%D7%9C%D7%99/", "https://medpage.co.il/doctors/%D7%92%D7%9C%D7%99-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-25448/", "https://www.doctorita.co.il/experts/131973", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/pariente-g.aspx", "https://www.bgu.ac.il/ar/people/galipa/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>1.352128242691979e+19</v>
+        <v>3.51221446594978e+19</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6661,7 +6669,7 @@
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
+          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr"/>
@@ -6702,7 +6710,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ד"ר צוקר נפתלי</t>
+          <t>ד"ר ברוך יואב</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6722,7 +6730,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -6733,7 +6741,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>drnzuker@arad-medical.co.il</t>
+          <t>yoavb@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -6746,7 +6754,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://www.arad-medical.co.il/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -6756,12 +6764,12 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> בי"ח אסף הרופא, עבר השתלמות מעמיקה בכירורגיה גניקולוגית ואנדסקופית. כמוכן, גניקולוג בכיר בקופות החולים מכבי ולאומית. קרא עוד עלינו « לפרטים נוספים ולקביעת תור השאר פרטים ונחזור אליך בהקדם! ☎ 077-8037837 | 077-9966036 ✉ drnzuker@arad-medical.co.il שם מלא: מייל: טלפון: שלח © ד"ר נפתלי צוקר — כל הזכויות שמורות אתר זה נבנה ועוצב ע"י קידום פלוס - בניית אתרים</t>
+          <t>י לאורוגינקולוגיה ורצפת אגן שטחי התעניינות ועיסוק מיוחדים ניתוחים וגינאליים וזעיר פולשניים לצניחת אברי האגן טיפול תרופתי וכירורגי לדליפת שתן מרפאת ערייה וצוואר הרחם אבחון וטיפול בקונדילומות ונגעים טרום ממאירים יצירת קשר yoavb@tlvmc.gov.il יחידות רפואיות אורוגינקולוגיה ורצפת האגן רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות נעים להכיר, ​ד"ר יואב ברוך איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציונ</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>"צוקר נפתלי"</t>
+          <t>"ברוך יואב"</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -6778,25 +6786,25 @@
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-09-03T20:26:24.789692+00:00</t>
+          <t>2026-09-05T00:14:33.719515+00:00</t>
         </is>
       </c>
       <c r="W39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X39" t="n">
         <v>1</v>
       </c>
       <c r="Y39" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z39" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA39" t="n">
         <v>1</v>
@@ -6808,11 +6816,11 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=JM/xPUEkhEzRgBuX3T9AYqhAJkFmVBaeb30sdIDAjgJqc6t/hlXwF9+305eagC9MR2dwestiB5JmwYwMLOCteQ==", "https://doctors.assuta.co.il/doctor/naftaly-zuker-15805", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=AsbND281GonWNafC65Z5in+5Uof0vMwxuFwCtAAhKp6HNUz+Imt4aFWEpjB1dVuW0TI9YD98xqlKyretPdEuvw==", "https://www.arad-medical.co.il/", "http://www.kidumplus.co.il/", "https://www.arad-medical.co.il/contact", "https://www.arad-medical.co.il/about-us", "https://www.doctorim.co.il/s/doctor-21560/דר-נפתלי-צוקר/מומחה-יילוד-וגניקולוגיה", "https://www.infomed.co.il/experts/83793/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345", "https://soundcloud.com/wx8fnfybplpt", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A-%D7%91%D7%A8%D7%95%D7%9A/pfbid02DHSfATmK3MDpizZrgGTLc9ZAvZHXUsR9pSCjhd6pmWqSMFvq1BwehNeHCARNitMol/", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/pfbid02BMPnQXQYXt6vzctmybagMUp3nWACPxhE1LqhYeJYs1fVgXWA6B1cK2Z9VpRJ8cJRl/", "https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/", "https://pubmed.ncbi.nlm.nih.gov/?term=yoav+baruch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000546", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/61559143005435/", "https://www.infomed.co.il/experts/151203/", "https://www.yoavbaruch.com/", "https://www.yoavbaruch.com/about-6", "https://theindex.co.il/phone/ברוך-יואב-0777573393/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000504"]</t>
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>1.440908498851192e+19</v>
+        <v>4.056384728075937e+19</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6823,7 +6831,7 @@
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>https://www.arad-medical.co.il/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr"/>
@@ -6864,7 +6872,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ד"ר רטן גלעד</t>
+          <t>ד"ר צוקר נפתלי</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6884,7 +6892,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -6895,7 +6903,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>giladr@tlvmc.gov.il</t>
+          <t>drnzuker@arad-medical.co.il</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -6908,7 +6916,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
+          <t>https://www.arad-medical.co.il/</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -6918,12 +6926,12 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t xml:space="preserve">ח "ליס" ליולדות ונשים איכילוב צוות איכילוב גלעד רטן בדיקת היסטרוסקופיה - ד"ר גלעד רטן | ליס, איכילוב ד"ר גלעד רטן על תסמונת אשרמן, סטטוסקופ ערוץ 13 פרק 18 | פרופ' יריב יוגב ופרופ' גלעד רטן | בדיקת היסטרוסקופיה יצירת קשר giladr@tlvmc.gov.il יחידות רפואיות היסטרוסקופיה אבחנתית / טיפולית רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א </t>
+          <t xml:space="preserve"> בי"ח אסף הרופא, עבר השתלמות מעמיקה בכירורגיה גניקולוגית ואנדסקופית. כמוכן, גניקולוג בכיר בקופות החולים מכבי ולאומית. קרא עוד עלינו « לפרטים נוספים ולקביעת תור השאר פרטים ונחזור אליך בהקדם! ☎ 077-8037837 | 077-9966036 ✉ drnzuker@arad-medical.co.il שם מלא: מייל: טלפון: שלח © ד"ר נפתלי צוקר — כל הזכויות שמורות אתר זה נבנה ועוצב ע"י קידום פלוס - בניית אתרים</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>"רטן גלעד"</t>
+          <t>"צוקר נפתלי"</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -6945,14 +6953,14 @@
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-09-03T21:08:14.761438+00:00</t>
+          <t>2026-09-03T20:26:24.789692+00:00</t>
         </is>
       </c>
       <c r="W40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="n">
         <v>4</v>
@@ -6970,11 +6978,11 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F/", "https://dr-gilad.infomed.co.il/", "https://www.facebook.com/TLVMDC/posts/%D7%95%D7%95%D7%90%D7%95-%D7%9E%D7%AA%D7%A8%D7%92%D7%A9%D7%99%D7%9D-%D7%9C%D7%94%D7%9B%D7%99%D7%A8-%D7%9C%D7%9B%D7%9D-%D7%90%D7%AA-%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F-%D7%9E%D7%95%D7%9E%D7%97%D7%94-%D7%91%D7%9B%D7%99%D7%A8-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%A8%D7%A4%D7%95%D7%90%D7%99-tlv_medical_center/1344912312574270/", "https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=JM/xPUEkhEzRgBuX3T9AYqhAJkFmVBaeb30sdIDAjgJqc6t/hlXwF9+305eagC9MR2dwestiB5JmwYwMLOCteQ==", "https://doctors.assuta.co.il/doctor/naftaly-zuker-15805", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=AsbND281GonWNafC65Z5in+5Uof0vMwxuFwCtAAhKp6HNUz+Imt4aFWEpjB1dVuW0TI9YD98xqlKyretPdEuvw==", "https://www.arad-medical.co.il/", "http://www.kidumplus.co.il/", "https://www.arad-medical.co.il/contact", "https://www.arad-medical.co.il/about-us", "https://www.doctorim.co.il/s/doctor-21560/דר-נפתלי-צוקר/מומחה-יילוד-וגניקולוגיה", "https://www.infomed.co.il/experts/83793/"]</t>
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>1.170738155316593e+19</v>
+        <v>4.322725496553574e+19</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6985,7 +6993,7 @@
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
+          <t>https://www.arad-medical.co.il/</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr"/>
@@ -7026,7 +7034,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>דנה ברבינג-גולדשטיין</t>
+          <t>ד"ר רטן גלעד</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -7046,18 +7054,18 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>ima</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>danabr2@clalit.org.il</t>
+          <t>giladr@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -7070,7 +7078,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -7080,17 +7088,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>ד"ר דנה ברבינג גולדשטיין | מרכז רפואי רבין ד"ר דנה ברבינג גולדשטיין מיילדות וגינקולוגיה, גנטיקה רפואית שם: ד"ר דנה ברבינג גולדשטיין דוא"ל: danabr2@clalit.org.il יחידה: מכון רפאל רקנאטי לגנטיקה</t>
+          <t xml:space="preserve">ח "ליס" ליולדות ונשים איכילוב צוות איכילוב גלעד רטן בדיקת היסטרוסקופיה - ד"ר גלעד רטן | ליס, איכילוב ד"ר גלעד רטן על תסמונת אשרמן, סטטוסקופ ערוץ 13 פרק 18 | פרופ' יריב יוגב ופרופ' גלעד רטן | בדיקת היסטרוסקופיה יצירת קשר giladr@tlvmc.gov.il יחידות רפואיות היסטרוסקופיה אבחנתית / טיפולית רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א </t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>"דנה ברבינג גולדשטיין" יילוד site:clalit.co.il</t>
+          <t>"רטן גלעד"</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>search_snippet</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -7107,36 +7115,36 @@
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-09-08T13:48:01.035843+00:00</t>
+          <t>2026-09-03T21:08:14.761438+00:00</t>
         </is>
       </c>
       <c r="W41" t="n">
+        <v>2</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
         <v>4</v>
       </c>
-      <c r="X41" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1</v>
-      </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA41" t="n">
         <v>1</v>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>ddgs:yahoo+ddgs:bing</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F/", "https://dr-gilad.infomed.co.il/", "https://www.facebook.com/TLVMDC/posts/%D7%95%D7%95%D7%90%D7%95-%D7%9E%D7%AA%D7%A8%D7%92%D7%A9%D7%99%D7%9D-%D7%9C%D7%94%D7%9B%D7%99%D7%A8-%D7%9C%D7%9B%D7%9D-%D7%90%D7%AA-%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F-%D7%9E%D7%95%D7%9E%D7%97%D7%94-%D7%91%D7%9B%D7%99%D7%A8-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%A8%D7%A4%D7%95%D7%90%D7%99-tlv_medical_center/1344912312574270/", "https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>1.171122655623675e+19</v>
+        <v>3.51221446594978e+19</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7147,7 +7155,7 @@
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr"/>
@@ -7188,7 +7196,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>יעל שולמן</t>
+          <t>דנה ברבינג-גולדשטיין</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7219,7 +7227,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>yaelshu@tlvmc.gov.il</t>
+          <t>danabr2@clalit.org.il</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -7232,7 +7240,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -7242,17 +7250,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>3zgt8o8y2e /search-result/ /api/as/v1/engines/ פתח חיפוש עוד ... זימון תורים אזור אישי כניסה לאיזור האישי AI צ'אט ד"ר יעל שולמן רופאה בכירה במחלקת נשים, ביה"ח 'ליס' ליולדות ונשים איכילוב צוות איכילוב יעל שולמן יצירת קשר yaelshu@tlvmc.gov.il יחידות רפואיות אשפוז נשים - מחלקה רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך ב</t>
+          <t>ד"ר דנה ברבינג גולדשטיין | מרכז רפואי רבין ד"ר דנה ברבינג גולדשטיין מיילדות וגינקולוגיה, גנטיקה רפואית שם: ד"ר דנה ברבינג גולדשטיין דוא"ל: danabr2@clalit.org.il יחידה: מכון רפאל רקנאטי לגנטיקה</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>"יעל שולמן"</t>
+          <t>"דנה ברבינג גולדשטיין" יילוד site:clalit.co.il</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -7269,36 +7277,36 @@
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-09-04T17:01:07.432235+00:00</t>
+          <t>2026-09-08T13:48:01.035843+00:00</t>
         </is>
       </c>
       <c r="W42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>["https://www.agmon-law.co.il/team-member/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/people/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/pfbid02D3uDhLBFvfdSCJScu9afsXcVu6ZWEqNA4AsJgJH4om5Y5hNBNGbDUq3Xyg3nad9hl/", "https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx"]</t>
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>1.111070905235564e+19</v>
+        <v>3.513367966871025e+19</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7309,7 +7317,7 @@
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr"/>
@@ -7350,7 +7358,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ישי לוין</t>
+          <t>יעל שולמן</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7381,7 +7389,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>ishail@tlvmc.gov.il</t>
+          <t>yaelshu@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -7394,7 +7402,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -7404,12 +7412,12 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>ריוזיס כנס אונליין אנדומטריאוזיס 2025 | פרופ' יריב יוגב ופרופ' ישי לוין מניעה וגילוי מוקדם של מחלות נשים | ערוץ 10 המכון לפריון - כירורגיה של הפריון | ליס פרופ' ישי לוין על כאבי מחזור חזקים , ערוץ 13, סטטוסקופ יצירת קשר ishail@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה אשפוז נשים - מחלקה אנדומטריוזיס - מרכז רב תחומי המרכז לבריאות האשה-מרפאות מומחים הפלות חוזרות - טיפול בכשל הריוני רופאים בכירים בליס-יולדות ונשים יצירת קשר יחיד</t>
+          <t>3zgt8o8y2e /search-result/ /api/as/v1/engines/ פתח חיפוש עוד ... זימון תורים אזור אישי כניסה לאיזור האישי AI צ'אט ד"ר יעל שולמן רופאה בכירה במחלקת נשים, ביה"ח 'ליס' ליולדות ונשים איכילוב צוות איכילוב יעל שולמן יצירת קשר yaelshu@tlvmc.gov.il יחידות רפואיות אשפוז נשים - מחלקה רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך ב</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>"ישי לוין"</t>
+          <t>"יעל שולמן"</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -7431,7 +7439,7 @@
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-09-04T17:20:48.855691+00:00</t>
+          <t>2026-09-04T17:01:07.432235+00:00</t>
         </is>
       </c>
       <c r="W43" t="n">
@@ -7441,10 +7449,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -7456,11 +7464,11 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>["https://www.ishai-levin.com/", "https://www.ishai-levin.com/about", "https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/", "https://pubmed.ncbi.nlm.nih.gov/?term=Levin%2c%20Ishai%5bFull%20Author%20Name%5d%20OR%20Ishai%2c%20Levin%5bFull%20Author%20Name%5d&amp;cmd=DetailsSearch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.agmon-law.co.il/team-member/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/people/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/pfbid02D3uDhLBFvfdSCJScu9afsXcVu6ZWEqNA4AsJgJH4om5Y5hNBNGbDUq3Xyg3nad9hl/", "https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>1.111070905235564e+19</v>
+        <v>3.333212715706692e+19</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7471,7 +7479,7 @@
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr"/>
@@ -7512,7 +7520,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>לירן הירש</t>
+          <t>ישי לוין</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7543,7 +7551,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>liranh@tlvmc.gov.il</t>
+          <t>ishail@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -7556,7 +7564,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -7566,12 +7574,12 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>צועיים החברה הישראלית לרפואת האם והעובר החוג הישראלי למיילדות וגינקולוגיה לידה נדירה - תאומים ברחם נפרד פרק 19 | פרופ' יריב יוגב ופרופ' לירן הירש | תאומים פרק 9 | פרופ' יריב יוגב ופרופ' לירן הירש| הריון בסיכון יצירת קשר liranh@tlvmc.gov.il יחידות רפואיות המחלקה לרפואת האם והעובר מניעת לידה מוקדמת - מרפאה מעקב הריונות תאומים רופאים בכירים בליס-יולדות ונשים היריון ולידה יצירת קשר יחידות רפואיות היריון של 1 למיליון עם פרופ' לירן הירש איכיל</t>
+          <t>ריוזיס כנס אונליין אנדומטריאוזיס 2025 | פרופ' יריב יוגב ופרופ' ישי לוין מניעה וגילוי מוקדם של מחלות נשים | ערוץ 10 המכון לפריון - כירורגיה של הפריון | ליס פרופ' ישי לוין על כאבי מחזור חזקים , ערוץ 13, סטטוסקופ יצירת קשר ishail@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה אשפוז נשים - מחלקה אנדומטריוזיס - מרכז רב תחומי המרכז לבריאות האשה-מרפאות מומחים הפלות חוזרות - טיפול בכשל הריוני רופאים בכירים בליס-יולדות ונשים יצירת קשר יחיד</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>"לירן הירש"</t>
+          <t>"ישי לוין"</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -7593,7 +7601,7 @@
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-09-04T17:39:56.947224+00:00</t>
+          <t>2026-09-04T17:20:48.855691+00:00</t>
         </is>
       </c>
       <c r="W44" t="n">
@@ -7618,11 +7626,11 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>["https://www.profhiersch.com/", "https://www.profhiersch.com/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/", "https://pubmed.ncbi.nlm.nih.gov/?term=HIERSCH+L&amp;sort=date", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.ishai-levin.com/", "https://www.ishai-levin.com/about", "https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/", "https://pubmed.ncbi.nlm.nih.gov/?term=Levin%2c%20Ishai%5bFull%20Author%20Name%5d%20OR%20Ishai%2c%20Levin%5bFull%20Author%20Name%5d&amp;cmd=DetailsSearch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>1.111070905235564e+19</v>
+        <v>3.333212715706692e+19</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7633,7 +7641,7 @@
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr"/>
@@ -7674,7 +7682,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>נועה גוהר פורטנוי</t>
+          <t>לירן הירש</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7705,7 +7713,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>noago@post.bgu.ac.il</t>
+          <t>liranh@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -7718,7 +7726,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/noago/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -7728,12 +7736,12 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان נועה גוהר פורטנוי נועה גוהר פורטנוי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section noago@post.bgu.ac.il Cookies Settings</t>
+          <t>צועיים החברה הישראלית לרפואת האם והעובר החוג הישראלי למיילדות וגינקולוגיה לידה נדירה - תאומים ברחם נפרד פרק 19 | פרופ' יריב יוגב ופרופ' לירן הירש | תאומים פרק 9 | פרופ' יריב יוגב ופרופ' לירן הירש| הריון בסיכון יצירת קשר liranh@tlvmc.gov.il יחידות רפואיות המחלקה לרפואת האם והעובר מניעת לידה מוקדמת - מרפאה מעקב הריונות תאומים רופאים בכירים בליס-יולדות ונשים היריון ולידה יצירת קשר יחידות רפואיות היריון של 1 למיליון עם פרופ' לירן הירש איכיל</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>"נועה גוהר פורטנוי" יילוד</t>
+          <t>"לירן הירש"</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -7755,14 +7763,14 @@
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-09-08T14:13:12.580343+00:00</t>
+          <t>2026-09-04T17:39:56.947224+00:00</t>
         </is>
       </c>
       <c r="W45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
         <v>2</v>
@@ -7780,11 +7788,11 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>["https://www.doctorita.co.il/experts/126297", "https://www.bgu.ac.il/ar/people/noago/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.profhiersch.com/", "https://www.profhiersch.com/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/", "https://pubmed.ncbi.nlm.nih.gov/?term=HIERSCH+L&amp;sort=date", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>1.084154241426883e+19</v>
+        <v>3.333212715706692e+19</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7795,7 +7803,7 @@
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/noago/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr"/>
@@ -7836,7 +7844,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>עדי יהודה ווינטראוב</t>
+          <t>נועה גוהר פורטנוי</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7867,7 +7875,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>adiyehud@bgu.ac.il</t>
+          <t>noago@post.bgu.ac.il</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -7880,7 +7888,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
+          <t>https://www.bgu.ac.il/ar/people/noago/</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -7890,12 +7898,12 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>رئيسية جامعة أنشي سيجل في جوريان עדי יהודה ווינטראוב פרופ' עדי יהודה ווינטראוב Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section adiyehud@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0002-4239-8665 Orcid Number Cookies Settings</t>
+          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان נועה גוהר פורטנוי נועה גוהר פורטנוי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section noago@post.bgu.ac.il Cookies Settings</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>"עדי יהודה ווינטראוב"</t>
+          <t>"נועה גוהר פורטנוי" יילוד</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -7912,41 +7920,41 @@
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-09-04T19:20:10.182518+00:00</t>
+          <t>2026-09-08T14:13:12.580343+00:00</t>
         </is>
       </c>
       <c r="W46" t="n">
+        <v>4</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y46" t="n">
         <v>2</v>
       </c>
-      <c r="X46" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>5</v>
-      </c>
       <c r="Z46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/adiyehud/", "https://www.bgu.ac.il/researcher/adi-weintraub/", "https://www.beok.co.il/doctors/Doctors-136810/", "https://cris.bgu.ac.il/en/publications/%D7%94%D7%A1%D7%99%D7%9B%D7%95%D7%9F-%D7%9C%D7%A1%D7%99%D7%91%D7%95%D7%9B%D7%99-%D7%94%D7%99%D7%A8%D7%99%D7%95%D7%9F-%D7%91%D7%A0%D7%A9%D7%99%D7%9D-%D7%A2%D7%9D-%D7%90%D7%A0%D7%93%D7%95%D7%9E%D7%98%D7%A8%D7%99%D7%95%D7%96%D7%99%D7%A1/", "https://www.bgu.ac.il/ar/people/adiyehud/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.doctorita.co.il/experts/126297", "https://www.bgu.ac.il/ar/people/noago/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>1.084140345157584e+19</v>
+        <v>3.252462724280651e+19</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7957,7 +7965,7 @@
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
+          <t>https://www.bgu.ac.il/ar/people/noago/</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr"/>
@@ -7998,7 +8006,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>עמרי זמשטין</t>
+          <t>עדי יהודה ווינטראוב</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -8029,7 +8037,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>omrizam@post.bgu.ac.il</t>
+          <t>adiyehud@bgu.ac.il</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -8042,7 +8050,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
+          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -8052,12 +8060,12 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>ريد البحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان עמרי זמשטין עמרי זמשטין Departments אקדמי לא פעיל הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section omrizam@post.bgu.ac.il Cookies Settings</t>
+          <t>رئيسية جامعة أنشي سيجل في جوريان עדי יהודה ווינטראוב פרופ' עדי יהודה ווינטראוב Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section adiyehud@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0002-4239-8665 Orcid Number Cookies Settings</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>"עמרי זמשטין"</t>
+          <t>"עדי יהודה ווינטראוב"</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -8079,7 +8087,7 @@
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-09-04T19:35:09.971397+00:00</t>
+          <t>2026-09-04T19:20:10.182518+00:00</t>
         </is>
       </c>
       <c r="W47" t="n">
@@ -8089,26 +8097,26 @@
         <v>1</v>
       </c>
       <c r="Y47" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/ar/people/omrizam/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.bgu.ac.il/people/adiyehud/", "https://www.bgu.ac.il/researcher/adi-weintraub/", "https://www.beok.co.il/doctors/Doctors-136810/", "https://cris.bgu.ac.il/en/publications/%D7%94%D7%A1%D7%99%D7%9B%D7%95%D7%9F-%D7%9C%D7%A1%D7%99%D7%91%D7%95%D7%9B%D7%99-%D7%94%D7%99%D7%A8%D7%99%D7%95%D7%9F-%D7%91%D7%A0%D7%A9%D7%99%D7%9D-%D7%A2%D7%9D-%D7%90%D7%A0%D7%93%D7%95%D7%9E%D7%98%D7%A8%D7%99%D7%95%D7%96%D7%99%D7%A1/", "https://www.bgu.ac.il/ar/people/adiyehud/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>1.084140345157584e+19</v>
+        <v>3.252421035472751e+19</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -8119,7 +8127,7 @@
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
+          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr"/>
@@ -8160,7 +8168,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>רויטל לינדר</t>
+          <t>עמרי זמשטין</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8191,7 +8199,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>revital@drlinder.co.il</t>
+          <t>omrizam@post.bgu.ac.il</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -8204,7 +8212,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://www.drlinder.co.il/</t>
+          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -8214,12 +8222,12 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>בכירה ביחידה הגניקואונקולוגית , בית חולים רמב״ם, חיפה. 4/2014-4/2019 התמחות במיילדות וגניקולוגיה בית חולים רמב״ם,חיפה. לפרטים מלאים חוות דעת יש לך שאלה ? צרי קשר ד״ר רויטל לינדר צפצפה 2 (ישי סנטר) , רמת ישי 058-6918927​ revital@drlinder.co.il הצהרת נגישות © DR. Revital Linder. All rights Reserved , 2023</t>
+          <t>ريد البحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان עמרי זמשטין עמרי זמשטין Departments אקדמי לא פעיל הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section omrizam@post.bgu.ac.il Cookies Settings</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>"רויטל לינדר"</t>
+          <t>"עמרי זמשטין"</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -8236,41 +8244,41 @@
         <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-09-04T07:14:47.643108+00:00</t>
+          <t>2026-09-04T19:35:09.971397+00:00</t>
         </is>
       </c>
       <c r="W48" t="n">
         <v>2</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>["https://www.rambam.org.il/?catid=%7B9F8D1CC1-1F5C-46F1-A395-E19ED48FE2EE%7D&amp;itemid=%7B4B21BA59-AF68-46CA-9483-9639E61A75A8%7D", "https://www.rambam.org.il/about-rambam/", "https://www.rambam.org.il/about-rambam/careers/", "https://www.rambam.org.il/departmentsandclinics/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/urology/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/orthopedic/", "https://www.drlinder.co.il/"]</t>
+          <t>["https://www.bgu.ac.il/ar/people/omrizam/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>1.084016810478327e+19</v>
+        <v>3.252421035472751e+19</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8281,7 +8289,7 @@
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>https://www.drlinder.co.il/</t>
+          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr"/>
@@ -8322,7 +8330,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>רליקה הרשקוביץ</t>
+          <t>רויטל לינדר</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8353,7 +8361,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>ralikah@bgu.ac.il</t>
+          <t>revital@drlinder.co.il</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -8366,7 +8374,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
+          <t>https://www.drlinder.co.il/</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -8376,12 +8384,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان רליקה הרשקוביץ פרופ' רליקה הרשקוביץ Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ralikah@bgu.ac.il رابط ملف الأبحاث Cookies Settings</t>
+          <t>בכירה ביחידה הגניקואונקולוגית , בית חולים רמב״ם, חיפה. 4/2014-4/2019 התמחות במיילדות וגניקולוגיה בית חולים רמב״ם,חיפה. לפרטים מלאים חוות דעת יש לך שאלה ? צרי קשר ד״ר רויטל לינדר צפצפה 2 (ישי סנטר) , רמת ישי 058-6918927​ revital@drlinder.co.il הצהרת נגישות © DR. Revital Linder. All rights Reserved , 2023</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>"רליקה הרשקוביץ"</t>
+          <t>"רויטל לינדר"</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -8403,7 +8411,7 @@
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-09-04T07:56:40.372731+00:00</t>
+          <t>2026-09-04T07:14:47.643108+00:00</t>
         </is>
       </c>
       <c r="W49" t="n">
@@ -8413,26 +8421,26 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/ralikah/", "https://www.doctorita.co.il/experts/101245", "https://www.bgu.ac.il/ar/people/ralikah/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.rambam.org.il/?catid=%7B9F8D1CC1-1F5C-46F1-A395-E19ED48FE2EE%7D&amp;itemid=%7B4B21BA59-AF68-46CA-9483-9639E61A75A8%7D", "https://www.rambam.org.il/about-rambam/", "https://www.rambam.org.il/about-rambam/careers/", "https://www.rambam.org.il/departmentsandclinics/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/urology/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/orthopedic/", "https://www.drlinder.co.il/"]</t>
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>1.084016810478327e+19</v>
+        <v>3.252050431434981e+19</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8443,7 +8451,7 @@
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
+          <t>https://www.drlinder.co.il/</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr"/>
@@ -8484,7 +8492,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>שקמה בר און</t>
+          <t>רליקה הרשקוביץ</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8515,7 +8523,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>shikmabo@tlvmc.gov.il</t>
+          <t>ralikah@bgu.ac.il</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -8528,7 +8536,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
+          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -8538,12 +8546,12 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>ת לאנדוסקופיה גינקולוגית שטחי התעניינות ועיסוק מיוחדים היסטרוסקופיה עם וללא הרדמה, היסטרוסקופיה ניתוחית ללא הרדמה בשיטת "see and treat" לפרוסקופיות פרק 14 | פרופ' יריב יוגב וד״ר שקמה בר און | מרכז בריאות האישה יצירת קשר shikmabo@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך בהתפתחות ביה"ח איכו</t>
+          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان רליקה הרשקוביץ פרופ' רליקה הרשקוביץ Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ralikah@bgu.ac.il رابط ملف الأبحاث Cookies Settings</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>"שקמה בר און"</t>
+          <t>"רליקה הרשקוביץ"</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -8565,7 +8573,7 @@
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-09-04T10:28:27.702590+00:00</t>
+          <t>2026-09-04T07:56:40.372731+00:00</t>
         </is>
       </c>
       <c r="W50" t="n">
@@ -8575,13 +8583,13 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
@@ -8590,11 +8598,11 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>["https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%A9%D7%A7%D7%9E%D7%94-%D7%91%D7%A8-%D7%90%D7%95%D7%9F/", "https://tlvmedical.com/doctors/דר-שקמה-בר-און/", "https://www.rofim.org.il/minisite/%D7%93%D7%A8_%D7%A9%D7%A7%D7%9E%D7%94_%D7%91%D7%A8_%D7%90%D7%95%D7%9F", "https://www.shidurit-ltd.co.il/", "https://www.rofim.org.il/about", "https://www.rofim.org.il/Contact", "https://www.rofim.org.il/specialityPage/%D7%9E%D7%A8%D7%9B%D7%96_%D7%A8%D7%A4%D7%95%D7%90%D7%99", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%9E%D7%92%D7%90%D7%A8", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%91%D7%99%D7%AA_%D7%92%D7%93%D7%99", "https://www.rofim.org.il/minisite/%D7%90%D7%99%D7%99_%D7%90%D7%9C_%D7%A7%D7%9C%D7%99%D7%A0%D7%99%D7%A7", "https://docsrated.com/doctors/שקמה-בר-און", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2FTLVMDC%2Fphotos%2F%25D7%25A2%25D7%2595%25D7%25A7%25D7%2591%25D7%2595%25D7%25AA-%25D7%2595%25D7%259E%25D7%2598%25D7%2595%25D7%25A4%25D7%259C%25D7%2595%25D7%25AA-%25D7%2590%25D7%25A0%25D7%2595-%25D7%25A9%25D7%259E%25D7%2597%25D7%2599%25D7%259D-%25D7%259C%25D7%2594%25D7%259B%25D7%2599%25D7%25A8-%25D7%259C%25D7%259B%25D7%259F-%25D7%2590%25D7%25AA-%25D7%2593%25D7%25A8-%25D7%25A9%25D7%25A7%25D7%259E%25D7%2594-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F%25D7%2593%25D7%25A8-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F-%25D7%2594%25D7%2599%25D7%2590-%25D7%259E%25D7%25A0%25D7%2594%25D7%259C%25D7%25AA-%25D7%2594%25D7%259E%25D7%25A8%25D7%259B%25D7%2596-%25D7%259C%2F1525276317871201%2F", "https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/", "https://www.ncbi.nlm.nih.gov/pubmed/?term=shikma+bar+on", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.bgu.ac.il/people/ralikah/", "https://www.doctorita.co.il/experts/101245", "https://www.bgu.ac.il/ar/people/ralikah/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>1.081793186251705e+19</v>
+        <v>3.252050431434981e+19</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8605,7 +8613,7 @@
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
+          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr"/>
@@ -8646,7 +8654,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>שרית הלמן</t>
+          <t>שקמה בר און</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8677,7 +8685,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>hsarit@szmc.org.il</t>
+          <t>shikmabo@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -8690,7 +8698,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -8700,12 +8708,12 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t xml:space="preserve"> רופאים בשערי צדק ד"ר שרית  הלמן רופאה בכירה Dr. Sarit  Helman התמחות: גינקולוגיה ויילוד תת התמחות: הריון בסיכון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 026666656 מחלקה: 026666656 hsarit@szmc.org.il hsarit@szmc.org.il נסיון מקצועי Harvard T.H. Chan School of Public Health, Joslin Diabetes Center, Research intern under the supervision of Dr. Florence Brown and Dr. Tamarra James-Todd,     Type 1 Dia</t>
+          <t>ת לאנדוסקופיה גינקולוגית שטחי התעניינות ועיסוק מיוחדים היסטרוסקופיה עם וללא הרדמה, היסטרוסקופיה ניתוחית ללא הרדמה בשיטת "see and treat" לפרוסקופיות פרק 14 | פרופ' יריב יוגב וד״ר שקמה בר און | מרכז בריאות האישה יצירת קשר shikmabo@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך בהתפתחות ביה"ח איכו</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>"שרית הלמן"</t>
+          <t>"שקמה בר און"</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -8722,12 +8730,12 @@
         <v>1</v>
       </c>
       <c r="T51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-09-05T00:06:28.339643+00:00</t>
+          <t>2026-09-04T10:28:27.702590+00:00</t>
         </is>
       </c>
       <c r="W51" t="n">
@@ -8740,10 +8748,10 @@
         <v>6</v>
       </c>
       <c r="Z51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
@@ -8752,11 +8760,11 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>["https://www.hamichlol.org.il/שרה_(שרית)_הלמן", "https://behevrat-haadam.org/ram-sara-helman/", "https://behevrat-haadam.org/tag/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/IsrAnthro/posts/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F-%D7%A1%D7%95%D7%A6%D7%99%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA%D7%90%D7%A0%D7%97%D7%A0%D7%95-%D7%A9%D7%9E%D7%97%D7%99%D7%9D-%D7%9C%D7%A9%D7%AA%D7%A3-%D7%91%D7%91%D7%97%D7%91%D7%A8%D7%AA-%D7%94%D7%90%D7%93%D7%9D-%D7%90%D7%AA-%D7%93%D7%91%D7%A8%D7%99%D7%95-%D7%A9%D7%9C-%D7%90%D7%95%D7%A8%D7%99-%D7%A8%D7%9D-%D7%A4%D7%A8%D7%95%D7%A4-%D7%90%D7%9E%D7%A8%D7%99%D7%98%D7%95/4246861638775714/", "https://www.doctorita.co.il/experts/137665", "https://www.szmc.org.il/doctors/helman-sarit/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
+          <t>["https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%A9%D7%A7%D7%9E%D7%94-%D7%91%D7%A8-%D7%90%D7%95%D7%9F/", "https://tlvmedical.com/doctors/דר-שקמה-בר-און/", "https://www.rofim.org.il/minisite/%D7%93%D7%A8_%D7%A9%D7%A7%D7%9E%D7%94_%D7%91%D7%A8_%D7%90%D7%95%D7%9F", "https://www.shidurit-ltd.co.il/", "https://www.rofim.org.il/about", "https://www.rofim.org.il/Contact", "https://www.rofim.org.il/specialityPage/%D7%9E%D7%A8%D7%9B%D7%96_%D7%A8%D7%A4%D7%95%D7%90%D7%99", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%9E%D7%92%D7%90%D7%A8", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%91%D7%99%D7%AA_%D7%92%D7%93%D7%99", "https://www.rofim.org.il/minisite/%D7%90%D7%99%D7%99_%D7%90%D7%9C_%D7%A7%D7%9C%D7%99%D7%A0%D7%99%D7%A7", "https://docsrated.com/doctors/שקמה-בר-און", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2FTLVMDC%2Fphotos%2F%25D7%25A2%25D7%2595%25D7%25A7%25D7%2591%25D7%2595%25D7%25AA-%25D7%2595%25D7%259E%25D7%2598%25D7%2595%25D7%25A4%25D7%259C%25D7%2595%25D7%25AA-%25D7%2590%25D7%25A0%25D7%2595-%25D7%25A9%25D7%259E%25D7%2597%25D7%2599%25D7%259D-%25D7%259C%25D7%2594%25D7%259B%25D7%2599%25D7%25A8-%25D7%259C%25D7%259B%25D7%259F-%25D7%2590%25D7%25AA-%25D7%2593%25D7%25A8-%25D7%25A9%25D7%25A7%25D7%259E%25D7%2594-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F%25D7%2593%25D7%25A8-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F-%25D7%2594%25D7%2599%25D7%2590-%25D7%259E%25D7%25A0%25D7%2594%25D7%259C%25D7%25AA-%25D7%2594%25D7%259E%25D7%25A8%25D7%259B%25D7%2596-%25D7%259C%2F1525276317871201%2F", "https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/", "https://www.ncbi.nlm.nih.gov/pubmed/?term=shikma+bar+on", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>1.081834364478124e+19</v>
+        <v>3.245379558755114e+19</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8767,7 +8775,7 @@
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr"/>
@@ -8808,12 +8816,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ניצן נבות אבישר</t>
+          <t>שרית הלמן</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>family_doctor</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -8839,7 +8847,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>doctor.nitzan@gmail.com</t>
+          <t>hsarit@szmc.org.il</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -8848,11 +8856,11 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://drnitzan.com/#about</t>
+          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -8862,17 +8870,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>doctor.nitzan@gmail.com</t>
+          <t xml:space="preserve"> רופאים בשערי צדק ד"ר שרית  הלמן רופאה בכירה Dr. Sarit  Helman התמחות: גינקולוגיה ויילוד תת התמחות: הריון בסיכון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 026666656 מחלקה: 026666656 hsarit@szmc.org.il hsarit@szmc.org.il נסיון מקצועי Harvard T.H. Chan School of Public Health, Joslin Diabetes Center, Research intern under the supervision of Dr. Florence Brown and Dr. Tamarra James-Todd,     Type 1 Dia</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>"ניצן נבות אבישר" רפואת משפחה</t>
+          <t>"שרית הלמן"</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>linked_mailto</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -8889,67 +8897,59 @@
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-09-11T08:10:09.398703+00:00</t>
+          <t>2026-09-05T00:06:28.339643+00:00</t>
         </is>
       </c>
       <c r="W52" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="X52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Z52" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>ddgs:yahoo+ddgs:bing</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>["https://drnitzan.com/", "https://drnitzan.com/#about", "https://drnitzan.com/#contact"]</t>
+          <t>["https://www.hamichlol.org.il/שרה_(שרית)_הלמן", "https://behevrat-haadam.org/ram-sara-helman/", "https://behevrat-haadam.org/tag/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/IsrAnthro/posts/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F-%D7%A1%D7%95%D7%A6%D7%99%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA%D7%90%D7%A0%D7%97%D7%A0%D7%95-%D7%A9%D7%9E%D7%97%D7%99%D7%9D-%D7%9C%D7%A9%D7%AA%D7%A3-%D7%91%D7%91%D7%97%D7%91%D7%A8%D7%AA-%D7%94%D7%90%D7%93%D7%9D-%D7%90%D7%AA-%D7%93%D7%91%D7%A8%D7%99%D7%95-%D7%A9%D7%9C-%D7%90%D7%95%D7%A8%D7%99-%D7%A8%D7%9D-%D7%A4%D7%A8%D7%95%D7%A4-%D7%90%D7%9E%D7%A8%D7%99%D7%98%D7%95/4246861638775714/", "https://www.doctorita.co.il/experts/137665", "https://www.szmc.org.il/doctors/helman-sarit/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>1.081807082521478e+19</v>
+        <v>3.245503093434371e+19</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
       </c>
       <c r="AF52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>https://drnitzan.com/</t>
+          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr"/>
       <c r="AJ52" t="inlineStr"/>
       <c r="AK52" t="inlineStr"/>
-      <c r="AL52" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM52" t="b">
-        <v>1</v>
-      </c>
-      <c r="AN52" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>ד"ר ניצן נבות אבישר | ליווי וטיפול רפואי בהשמנה ומחלות מטבוליות – שוהם ד"ר ניצן נבות אבישר | ליווי וטיפול רפואי בהשמנה ומחלות מטבוליות – שוהם בית הסבר תהליך עלינו צור קשר לתיאום ייעוץ בית הסבר תהליך עלינו צור קשר לתיאום ייעוץ ד"ר ניצן נבות אבישר · מומחית ברפואת משפחה ליווי וטיפול בהשמנה ומחלות מטבוליות אבחון, טיפול וליווי מותאם אישית, בלי שיפוטיות ובלי סודות. שילוב של ידע מדעי, הקשבה ורגישות. לתיאום ייעוץ הגישה שלי המיקוד הוא בך הזמן שלך לשינוי, המקום שלך בחיים אם הגעת לכאן, אני מאמינה שפינית מקום בלב להתמקד בעצמך ולהעניק לעצמך את המתנה החשובה ביותר – הבריאות שלך. הגעת למקום בחיים שבו הבריאות והצרכים שלך נמצאים במרכז. אני מאמינה שטיפול בהשמנה ובאיזון מטבולי אינו מסתכם בנוסחאות פשוטות של מספרים או קלוריות. מדובר בתהליך רפואי עמוק ומורכב, שחייב להתאים באופן מדויק לשגרת החיים, לפיזיולוגיה וליעדים האישיים שלך. אני כאן כדי להעניק לך מענה מקצועי ומקיף המבוסס על ידע קליני עדכני וניסיון רב שנים, לצד הקשבה עמוקה ורגישות. ההתמקדות היא בך. המענה הרפואי בקליניקה אבחון ואיזון מטבולי מקיף בדיקות והסתכלות רחבה על כל התמונה הבריאותית שלך, כדי להבין מה באמת משפיע על המשקל</t>
-        </is>
-      </c>
-      <c r="AP52" t="inlineStr"/>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
+      <c r="AP52" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ52" t="inlineStr"/>
       <c r="AR52" t="n">
         <v>1</v>
@@ -8961,11 +8961,11 @@
         <v>1</v>
       </c>
       <c r="AU52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
+          <t>PERSON</t>
         </is>
       </c>
     </row>
@@ -8978,7 +8978,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>דלית דרימן-מדינה</t>
+          <t>ניצן נבות אבישר</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -9009,7 +9009,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>dalit@drdreman.co.il</t>
+          <t>doctor.nitzan@gmail.com</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -9018,11 +9018,11 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://www.drdreman.co.il/%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%9E%D7%98%D7%91%D7%95%D7%9C%D7%99%D7%95%D7%AA/</t>
+          <t>https://drnitzan.com/#about</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -9032,17 +9032,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>drdremandalit@gmail.com</t>
+          <t>doctor.nitzan@gmail.com</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>"דלית דרימן מדינה" רפואת משפחה (מרפאה OR "צור קשר" OR email OR מייל)</t>
+          <t>"ניצן נבות אבישר" רפואת משפחה</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>direct_mailto</t>
+          <t>linked_mailto</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -9059,47 +9059,47 @@
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-09-10T18:44:56.180135+00:00</t>
+          <t>2026-09-11T08:10:09.398703+00:00</t>
         </is>
       </c>
       <c r="W53" t="n">
         <v>8</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y53" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Z53" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AA53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>["https://www.drdreman.co.il/מחלות-מטבוליות/", "https://www.drdreman.co.il/%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%9E%D7%98%D7%91%D7%95%D7%9C%D7%99%D7%95%D7%AA/", "https://www.drdreman.co.il/about/", "https://www.drdreman.co.il/contact/", "https://www.drdreman.co.il/", "https://www.doctorita.co.il/experts/52215", "https://www.drdreman.co.il/%D7%93%D7%A3-%D7%91%D7%99%D7%AA/", "https://www.other-medicine.co.il/author/dalitdrdreman-co-il/", "https://www.izi.co.il/site/6f2c026c8d", "https://www.infomed.co.il/experts/78145/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%93%D7%A8%D7%99%D7%9E%D7%9F-%D7%9E%D7%93%D7%99%D7%A0%D7%94-%D7%93%D7%9C%D7%99%D7%AA/", "https://www.findglocal.com/IL/Unknown/106988607393615/ד״ר-דלית-דרימן-רפואה-פונקציונלית-ואינטגרטיבית"]</t>
+          <t>["https://drnitzan.com/", "https://drnitzan.com/#about", "https://drnitzan.com/#contact"]</t>
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>1.110837732120518e+19</v>
+        <v>3.245421247564433e+19</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>https://www.drdreman.co.il/%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%9E%D7%98%D7%91%D7%95%D7%9C%D7%99%D7%95%D7%AA/</t>
+          <t>https://drnitzan.com/</t>
         </is>
       </c>
       <c r="AI53" t="inlineStr"/>
@@ -9116,8 +9116,7 @@
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>מחלות מטבוליות - ד"ר דלית דרימן-מדינה מחלות מטבוליות - ד"ר דלית דרימן-מדינה דלג לתוכן אודות כיצד נוכל לעזור במה אנחנו מטפלים מפגשים ועלויות שאלות ותשובות מאמרים סרטונים מהתקשורת צור קשר אודות כיצד נוכל לעזור במה אנחנו מטפלים מפגשים ועלויות שאלות ותשובות מאמרים סרטונים מהתקשורת צור קשר 0546033755 חיפוש חיפוש אודות כיצד נוכל לעזור במה אנחנו מטפלים מפגשים ועלויות שאלות ותשובות מאמרים סרטונים מהתקשורת צור קשר אודות כיצד נוכל לעזור במה אנחנו מטפלים מפגשים ועלויות שאלות ותשובות מאמרים סרטונים מהתקשורת צור קשר חיפוש חיפוש מחלות מטבוליות הפרעות מטבוליות, עודף משקל, סוכרת בחירות מזון גרועות, העדר מרכיבי מזון חיוניים, רעלנים, מתח נפשי, ודלקת כרונית גורמים לחוסר איזון מטבולי ולמחלות שמהוות את מרבית המחלות הכרוניות כיום. במה אנו מטפלים? מחלות לב יתר לחץ דם עודף משקל והשמנה תסמונת מטבולית סוכרת הפרעות בכולסטרול ושומני הדם איך זה עובד? אנחנו עורכים למטופלים שלנו בירור נרחב ע״י בדיקות מעבדה מתקדמות כולל בדיקות מיוחדות לשומני הדם שאינן מבוצעות באופן סטנדרטי בקופות החולים.
-בטיפול שלנו אנו מתבססים על המזון ומרכיבי התזונה ככלים הטיפוליים הרא</t>
+          <t>ד"ר ניצן נבות אבישר | ליווי וטיפול רפואי בהשמנה ומחלות מטבוליות – שוהם ד"ר ניצן נבות אבישר | ליווי וטיפול רפואי בהשמנה ומחלות מטבוליות – שוהם בית הסבר תהליך עלינו צור קשר לתיאום ייעוץ בית הסבר תהליך עלינו צור קשר לתיאום ייעוץ ד"ר ניצן נבות אבישר · מומחית ברפואת משפחה ליווי וטיפול בהשמנה ומחלות מטבוליות אבחון, טיפול וליווי מותאם אישית, בלי שיפוטיות ובלי סודות. שילוב של ידע מדעי, הקשבה ורגישות. לתיאום ייעוץ הגישה שלי המיקוד הוא בך הזמן שלך לשינוי, המקום שלך בחיים אם הגעת לכאן, אני מאמינה שפינית מקום בלב להתמקד בעצמך ולהעניק לעצמך את המתנה החשובה ביותר – הבריאות שלך. הגעת למקום בחיים שבו הבריאות והצרכים שלך נמצאים במרכז. אני מאמינה שטיפול בהשמנה ובאיזון מטבולי אינו מסתכם בנוסחאות פשוטות של מספרים או קלוריות. מדובר בתהליך רפואי עמוק ומורכב, שחייב להתאים באופן מדויק לשגרת החיים, לפיזיולוגיה וליעדים האישיים שלך. אני כאן כדי להעניק לך מענה מקצועי ומקיף המבוסס על ידע קליני עדכני וניסיון רב שנים, לצד הקשבה עמוקה ורגישות. ההתמקדות היא בך. המענה הרפואי בקליניקה אבחון ואיזון מטבולי מקיף בדיקות והסתכלות רחבה על כל התמונה הבריאותית שלך, כדי להבין מה באמת משפיע על המשקל</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr"/>
@@ -9149,12 +9148,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ד"ר ארבל אריאל</t>
+          <t>דלית דרימן-מדינה</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -9169,31 +9168,31 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ima</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>info@eryaveladan.com</t>
+          <t>dalit@drdreman.co.il</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://www.eryaveladan.com/</t>
+          <t>https://www.drdreman.co.il/%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%9E%D7%98%D7%91%D7%95%D7%9C%D7%99%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -9203,50 +9202,50 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>החזיר את האיזון. קראי עוד השאירי פרטים ונחזור אלייך בהקדם שם מלא טלפון דוא״ל שליחה רופא נשים מומחה מחלות העריה והלדן ​ ד״ר אריאל ארבל לקביעת תור: 077-2311245 כתובת המרפאה: בית למומחים ברפואה - בורוכוב 54, גבעתיים דוא״ל: info@eryaveladan.com bottom of page</t>
+          <t>drdremandalit@gmail.com</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>"ארבל אריאל"</t>
+          <t>"דלית דרימן מדינה" רפואת משפחה (מרפאה OR "צור קשר" OR email OR מייל)</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>direct_mailto</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>[{"email": "info@eryaveladan.com", "confidence": 88, "source_url": "https://www.eryaveladan.com/", "identity_url": "https://www.eryaveladan.com/", "evidence": "החזיר את האיזון. קראי עוד השאירי פרטים ונחזור אלייך בהקדם שם מלא טלפון דוא״ל שליחה רופא נשים מומחה מחלות העריה והלדן ​ ד״ר אריאל ארבל לקביעת תור: 077-2311245 כתובת המרפאה: בית למומחים ברפואה - בורוכוב 54, גבעתיים דוא״ל: info@eryaveladan.com bottom of page", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}, {"email": "office@b54.co.il", "confidence": 88, "source_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "identity_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "evidence": "ד\"ר אריאל ארבל - מרפאת מומחים B54, הבית למומחים ברפואה בגבעתיים דילוג לתוכן B54 03-757-8562 office@b54.co.il א׳-ה׳ 8:00-20:00 | ו׳ 08:00-13:00 Facebook-f Youtube Google דף הבית אודות B54 מי אנחנו שכונת בורוכוב מרכז Friendly הנהלת המרפאה שאלות נפוצות הרופאים שלנו קליניקה להשכרה מידע למטופל שאלות ותשובות הורדת טפ", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-09-03T20:23:48.175654+00:00</t>
+          <t>2026-09-10T18:44:56.180135+00:00</t>
         </is>
       </c>
       <c r="W54" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X54" t="n">
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
@@ -9255,11 +9254,11 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598", "https://www.facebook.com/people/%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%90%D7%A8%D7%91%D7%9C/pfbid0NCmi7FZgUyu2EVV5mLJMpBfndXiDQPqseAxUny7KWHsDvucQScUiVnBeMef3ByStl/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%90%D7%A8%D7%91%D7%9C-%D7%90%D7%A8%D7%99%D7%90%D7%9C/", "https://www.eryaveladan.com/", "https://www.eryaveladan.com/%D7%90%D7%95%D7%93%D7%95%D7%AA-1", "https://www.b54.co.il/doctors/dr-arbel-ariel/", "https://www.medreviews.co.il/provider/dr-arbel-ariel", "https://www.b54.co.il/about/", "https://www.b54.co.il/about", "https://www.b54.co.il/about#borohov", "https://www.b54.co.il/about#Friendly", "https://www.b54.co.il/about#management", "https://www.b54.co.il/about#qa", "https://www.medreviews.co.il/provider/dr-arbel-ariel#contact-doctor-section", "https://www.medreviews.co.il/contact-us", "https://www.medreviews.co.il/about", "https://woman.mymc.co.il/doctors/dr-arielarbel/", "https://www.ima.org.il/DoctorsIndex/Default.aspx", "https://www.infomed.co.il/experts/145655/", "https://www.ami.org.il/blog/families/not-the-same-shirley"]</t>
+          <t>["https://www.drdreman.co.il/מחלות-מטבוליות/", "https://www.drdreman.co.il/%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%9E%D7%98%D7%91%D7%95%D7%9C%D7%99%D7%95%D7%AA/", "https://www.drdreman.co.il/about/", "https://www.drdreman.co.il/contact/", "https://www.drdreman.co.il/", "https://www.doctorita.co.il/experts/52215", "https://www.drdreman.co.il/%D7%93%D7%A3-%D7%91%D7%99%D7%AA/", "https://www.other-medicine.co.il/author/dalitdrdreman-co-il/", "https://www.izi.co.il/site/6f2c026c8d", "https://www.infomed.co.il/experts/78145/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%93%D7%A8%D7%99%D7%9E%D7%9F-%D7%9E%D7%93%D7%99%D7%A0%D7%94-%D7%93%D7%9C%D7%99%D7%AA/", "https://www.findglocal.com/IL/Unknown/106988607393615/ד״ר-דלית-דרימן-רפואה-פונקציונלית-ואינטגרטיבית"]</t>
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>1.440908498851192e+19</v>
+        <v>3.332513196361554e+19</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -9270,22 +9269,31 @@
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>https://www.eryaveladan.com/</t>
+          <t>https://www.drdreman.co.il/%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%9E%D7%98%D7%91%D7%95%D7%9C%D7%99%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="AI54" t="inlineStr"/>
       <c r="AJ54" t="inlineStr"/>
       <c r="AK54" t="inlineStr"/>
-      <c r="AL54" t="inlineStr"/>
-      <c r="AM54" t="inlineStr"/>
-      <c r="AN54" t="inlineStr"/>
-      <c r="AO54" t="inlineStr"/>
-      <c r="AP54" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL54" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM54" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN54" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>מחלות מטבוליות - ד"ר דלית דרימן-מדינה מחלות מטבוליות - ד"ר דלית דרימן-מדינה דלג לתוכן אודות כיצד נוכל לעזור במה אנחנו מטפלים מפגשים ועלויות שאלות ותשובות מאמרים סרטונים מהתקשורת צור קשר אודות כיצד נוכל לעזור במה אנחנו מטפלים מפגשים ועלויות שאלות ותשובות מאמרים סרטונים מהתקשורת צור קשר 0546033755 חיפוש חיפוש אודות כיצד נוכל לעזור במה אנחנו מטפלים מפגשים ועלויות שאלות ותשובות מאמרים סרטונים מהתקשורת צור קשר אודות כיצד נוכל לעזור במה אנחנו מטפלים מפגשים ועלויות שאלות ותשובות מאמרים סרטונים מהתקשורת צור קשר חיפוש חיפוש מחלות מטבוליות הפרעות מטבוליות, עודף משקל, סוכרת בחירות מזון גרועות, העדר מרכיבי מזון חיוניים, רעלנים, מתח נפשי, ודלקת כרונית גורמים לחוסר איזון מטבולי ולמחלות שמהוות את מרבית המחלות הכרוניות כיום. במה אנו מטפלים? מחלות לב יתר לחץ דם עודף משקל והשמנה תסמונת מטבולית סוכרת הפרעות בכולסטרול ושומני הדם איך זה עובד? אנחנו עורכים למטופלים שלנו בירור נרחב ע״י בדיקות מעבדה מתקדמות כולל בדיקות מיוחדות לשומני הדם שאינן מבוצעות באופן סטנדרטי בקופות החולים.
+בטיפול שלנו אנו מתבססים על המזון ומרכיבי התזונה ככלים הטיפוליים הרא</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr"/>
       <c r="AQ54" t="inlineStr"/>
       <c r="AR54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS54" t="b">
         <v>0</v>
@@ -9311,7 +9319,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>יעל כהן</t>
+          <t>ד"ר ארבל אריאל</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9331,18 +9339,18 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>ima</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>office@elitemed.co.il</t>
+          <t>info@eryaveladan.com</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -9355,7 +9363,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://elitemed.co.il/doctors/dr-yael-cohen-hebrew/</t>
+          <t>https://www.eryaveladan.com/</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -9365,12 +9373,12 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>ד"ר יעל כהן - elitemed.co.il דלג לתוכן Facebook Instagram Whatsapp Office@elitemed.co.il 073-321-4181 בית אודות רופאים שירותים רפואיים אולטרסאונד וביופסיות אוסטאופתיה אורולוגיה אורתופדיה אלרגיה ואימונולגיה אנדוקרינולוגיה סוכרת וירידה במשקל אסתטיקה אף אוזן גרון גינקולוגיה ובריאות האישה ג</t>
+          <t>החזיר את האיזון. קראי עוד השאירי פרטים ונחזור אלייך בהקדם שם מלא טלפון דוא״ל שליחה רופא נשים מומחה מחלות העריה והלדן ​ ד״ר אריאל ארבל לקביעת תור: 077-2311245 כתובת המרפאה: בית למומחים ברפואה - בורוכוב 54, גבעתיים דוא״ל: info@eryaveladan.com bottom of page</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>"יעל כהן" יילוד</t>
+          <t>"ארבל אריאל"</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -9380,82 +9388,74 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "info@eryaveladan.com", "confidence": 88, "source_url": "https://www.eryaveladan.com/", "identity_url": "https://www.eryaveladan.com/", "evidence": "החזיר את האיזון. קראי עוד השאירי פרטים ונחזור אלייך בהקדם שם מלא טלפון דוא״ל שליחה רופא נשים מומחה מחלות העריה והלדן ​ ד״ר אריאל ארבל לקביעת תור: 077-2311245 כתובת המרפאה: בית למומחים ברפואה - בורוכוב 54, גבעתיים דוא״ל: info@eryaveladan.com bottom of page", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}, {"email": "office@b54.co.il", "confidence": 88, "source_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "identity_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "evidence": "ד\"ר אריאל ארבל - מרפאת מומחים B54, הבית למומחים ברפואה בגבעתיים דילוג לתוכן B54 03-757-8562 office@b54.co.il א׳-ה׳ 8:00-20:00 | ו׳ 08:00-13:00 Facebook-f Youtube Google דף הבית אודות B54 מי אנחנו שכונת בורוכוב מרכז Friendly הנהלת המרפאה שאלות נפוצות הרופאים שלנו קליניקה להשכרה מידע למטופל שאלות ותשובות הורדת טפ", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}]</t>
         </is>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-09-10T18:33:08.486465+00:00</t>
+          <t>2026-09-03T20:23:48.175654+00:00</t>
         </is>
       </c>
       <c r="W55" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="X55" t="n">
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Z55" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>ddgs:yahoo+ddgs:bing</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>["https://elitemed.co.il/doctors/dr-yael-cohen-hebrew/", "https://elitemed.co.il/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%A4%D7%95%D7%90%D7%99-%D7%A4%D7%A8%D7%98%D7%99-%D7%91%D7%9E%D7%95%D7%93%D7%99%D7%A2%D7%99%D7%9F/", "https://elitemed.co.il/pain-clinic-modiin/", "https://elitemed.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://elitemed.co.il/%d7%90%d7%95%d6%b9%d7%93%d7%95%d6%b9%d7%aa/", "https://medpage.co.il/doctors/יעל-כהן-23202/", "https://medpage.co.il/doctors/%D7%99%D7%A2%D7%9C-%D7%9B%D7%94%D7%9F-23202/", "https://www.facebook.com/ichilovmedical/posts/תכירו-את-פרופ-יעל-כהןמנהלת-יחידת-המיאלומה-במערך-ההמטולוגי-של-איכילוב-ואחת-מהרופא/1288268913309017/", "https://www.facebook.com/ichilovmedical/videos/%D7%AA%D7%9B%D7%99%D7%A8%D7%95-%D7%90%D7%AA-%D7%A4%D7%A8%D7%95%D7%A4-%D7%99%D7%A2%D7%9C-%D7%9B%D7%94%D7%9F%D7%9E%D7%A0%D7%94%D7%9C%D7%AA-%D7%99%D7%97%D7%99%D7%93%D7%AA-%D7%94%D7%9E%D7%99%D7%90%D7%9C%D7%95%D7%9E%D7%94-%D7%91%D7%9E%D7%A2%D7%A8%D7%9A-%D7%94%D7%94%D7%9E%D7%98%D7%95%D7%9C%D7%95%D7%92%D7%99-%D7%A9%D7%9C-%D7%90%D7%99%D7%9B%D7%99%D7%9C%D7%95%D7%91-%D7%95%D7%90%D7%97%D7%AA-%D7%9E%D7%94%D7%A8%D7%95%D7%A4%D7%90/981973987039095/", "https://www.medico.co.il/doctors/פרופ-יעל-כהן/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%99%D7%A2%D7%9C-%D7%9B%D7%94%D7%9F/", "https://www.medico.co.il/doctors/", "https://www.medico.co.il/doctors/%d7%a4%d7%a8%d7%95%d7%a4-%d7%99%d7%a2%d7%9c-%d7%9b%d7%94%d7%9f/", "https://www.tasmc.org.il/doctorssearch/dr/cohen-yael/", "https://www.szmc.org.il/doctors/cohen-yael/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.vimed.co.il/users/0918fba4-bd6a-4310-ab8f-b51cab0b8f80", "https://www.meuhedet.co.il/poi/ParamedicalDoctors/000189680918100097000000000000_0", "https://www.medreviews.co.il/provider/dr-cohen-yael"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598", "https://www.facebook.com/people/%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%90%D7%A8%D7%91%D7%9C/pfbid0NCmi7FZgUyu2EVV5mLJMpBfndXiDQPqseAxUny7KWHsDvucQScUiVnBeMef3ByStl/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%90%D7%A8%D7%91%D7%9C-%D7%90%D7%A8%D7%99%D7%90%D7%9C/", "https://www.eryaveladan.com/", "https://www.eryaveladan.com/%D7%90%D7%95%D7%93%D7%95%D7%AA-1", "https://www.b54.co.il/doctors/dr-arbel-ariel/", "https://www.medreviews.co.il/provider/dr-arbel-ariel", "https://www.b54.co.il/about/", "https://www.b54.co.il/about", "https://www.b54.co.il/about#borohov", "https://www.b54.co.il/about#Friendly", "https://www.b54.co.il/about#management", "https://www.b54.co.il/about#qa", "https://www.medreviews.co.il/provider/dr-arbel-ariel#contact-doctor-section", "https://www.medreviews.co.il/contact-us", "https://www.medreviews.co.il/about", "https://woman.mymc.co.il/doctors/dr-arielarbel/", "https://www.ima.org.il/DoctorsIndex/Default.aspx", "https://www.infomed.co.il/experts/145655/", "https://www.ami.org.il/blog/families/not-the-same-shirley"]</t>
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>1.111084801504876e+19</v>
+        <v>4.322725496553574e+19</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
       </c>
       <c r="AF55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>https://elitemed.co.il/doctors/dr-yael-cohen-hebrew/</t>
+          <t>https://www.eryaveladan.com/</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr"/>
       <c r="AJ55" t="inlineStr"/>
       <c r="AK55" t="inlineStr"/>
-      <c r="AL55" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM55" t="b">
-        <v>1</v>
-      </c>
-      <c r="AN55" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>ד"ר יעל כהן - elitemed.co.il ד"ר יעל כהן - elitemed.co.il דלג לתוכן Facebook Instagram Whatsapp Office@elitemed.co.il 073-321-4181 בית אודות רופאים שירותים רפואיים אולטרסאונד וביופסיות אוסטאופתיה אורולוגיה אורתופדיה אלרגיה ואימונולגיה אנדוקרינולוגיה סוכרת וירידה במשקל אסתטיקה אף אוזן גרון גינקולוגיה ובריאות האישה גסטרואנטרולוגיה גֵרִיאַטרִיָה דרמטולגיה המטולוגיה כלי דם ורדיולוגיה פולשנית התמחויות טיפוליות ושיקומיות כירורגיה כירורגיה פלסטית מרפאת כאב נוירולוגיה, קשב וריכוז והתפתחות הילד נפרולוגיה ויתר לחץ דם סקירות מערכות ואקו לב עובר עיניים פודיאטריה כירורגית וכף רגל פולמונולוגיה ורפואת שינה פסיכיאטריה פרוקטולוגיה וכירורגיה קולורקטלית קרדיולוגיה ואלקטרופיזיולוגיה ראומטולוגיה רפואת ילדים מומחית רפואת ספורט ופיזיותרפיה רפואה תעסוקתית תזונה קלינית ודיאטה תור דחוף  24-48 שעות צור קשר השכרת קליניקה במודיעין שירות VIP שירותים מידע רפואי בית אודות רופאים שירותים רפואיים אולטרסאונד וביופסיות אוסטאופתיה אורולוגיה אורתופדיה אלרגיה ואימונולגיה אנדוקרינולוגיה סוכרת וירידה במשקל אסתטיקה אף אוזן גרון גינקולוגיה ובריאות האישה גס</t>
-        </is>
-      </c>
-      <c r="AP55" t="inlineStr"/>
+      <c r="AL55" t="inlineStr"/>
+      <c r="AM55" t="inlineStr"/>
+      <c r="AN55" t="inlineStr"/>
+      <c r="AO55" t="inlineStr"/>
+      <c r="AP55" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ55" t="inlineStr"/>
       <c r="AR55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS55" t="b">
         <v>0</v>
@@ -9481,7 +9481,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>מאיה שרון וינר</t>
+          <t>יעל כהן</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>clinic@drmayasharonweiner.com</t>
+          <t>office@elitemed.co.il</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://www.drmayasharonweiner.com/</t>
+          <t>https://elitemed.co.il/doctors/dr-yael-cohen-hebrew/</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -9535,12 +9535,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>אני איתך במסע הזה. הצעד הראשון שלך מתחיל כאן. ד"ר מאיה שרון-וינר רופאת נשים מומחית בפריון והפריה חוץ גופית מיילדות וגינקולוגיה לקביעת פגישה © 2026 כל הזכויות שמורות לד"ר מאיה שרון-וינר הברזל 9א', רמת החייל ווטסאפ למרפאה clinic@drmayasharonweiner.com פוריות האישה והגבר טיפולי פוריות הפריה חוץ גופית ו-PGD שימור פוריות פוריות לאחר סרטן ובנשאיות BRCA מעקב וליווי הריון גינקולוגיה כללית Menu Close אודות יצירת קשר מדיניות פרטיות הצהרת נגישות M</t>
+          <t>ד"ר יעל כהן - elitemed.co.il דלג לתוכן Facebook Instagram Whatsapp Office@elitemed.co.il 073-321-4181 בית אודות רופאים שירותים רפואיים אולטרסאונד וביופסיות אוסטאופתיה אורולוגיה אורתופדיה אלרגיה ואימונולגיה אנדוקרינולוגיה סוכרת וירידה במשקל אסתטיקה אף אוזן גרון גינקולוגיה ובריאות האישה ג</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>"מאיה שרון וינר"</t>
+          <t>"יעל כהן" יילוד</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -9557,64 +9557,72 @@
         <v>1</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-09-04T17:43:40.101946+00:00</t>
+          <t>2026-09-10T18:33:08.486465+00:00</t>
         </is>
       </c>
       <c r="W56" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="X56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z56" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>["https://www.drmayasharonweiner.com/", "https://www.drmayasharonweiner.com/about", "https://www.drmayasharonweiner.com/contact", "https://www.medreviews.co.il/provider/dr-sharon-weiner-maya", "https://www.medreviews.co.il/provider/dr-sharon-weiner-maya/treatment", "https://www.doctorita.co.il/experts/119120", "https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr_maya_sharonweiner%2F&amp;is_from_rle", "https://docsrated.com/doctors/מאיה-שרון-וינר"]</t>
+          <t>["https://elitemed.co.il/doctors/dr-yael-cohen-hebrew/", "https://elitemed.co.il/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%A4%D7%95%D7%90%D7%99-%D7%A4%D7%A8%D7%98%D7%99-%D7%91%D7%9E%D7%95%D7%93%D7%99%D7%A2%D7%99%D7%9F/", "https://elitemed.co.il/pain-clinic-modiin/", "https://elitemed.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://elitemed.co.il/%d7%90%d7%95%d6%b9%d7%93%d7%95%d6%b9%d7%aa/", "https://medpage.co.il/doctors/יעל-כהן-23202/", "https://medpage.co.il/doctors/%D7%99%D7%A2%D7%9C-%D7%9B%D7%94%D7%9F-23202/", "https://www.facebook.com/ichilovmedical/posts/תכירו-את-פרופ-יעל-כהןמנהלת-יחידת-המיאלומה-במערך-ההמטולוגי-של-איכילוב-ואחת-מהרופא/1288268913309017/", "https://www.facebook.com/ichilovmedical/videos/%D7%AA%D7%9B%D7%99%D7%A8%D7%95-%D7%90%D7%AA-%D7%A4%D7%A8%D7%95%D7%A4-%D7%99%D7%A2%D7%9C-%D7%9B%D7%94%D7%9F%D7%9E%D7%A0%D7%94%D7%9C%D7%AA-%D7%99%D7%97%D7%99%D7%93%D7%AA-%D7%94%D7%9E%D7%99%D7%90%D7%9C%D7%95%D7%9E%D7%94-%D7%91%D7%9E%D7%A2%D7%A8%D7%9A-%D7%94%D7%94%D7%9E%D7%98%D7%95%D7%9C%D7%95%D7%92%D7%99-%D7%A9%D7%9C-%D7%90%D7%99%D7%9B%D7%99%D7%9C%D7%95%D7%91-%D7%95%D7%90%D7%97%D7%AA-%D7%9E%D7%94%D7%A8%D7%95%D7%A4%D7%90/981973987039095/", "https://www.medico.co.il/doctors/פרופ-יעל-כהן/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%99%D7%A2%D7%9C-%D7%9B%D7%94%D7%9F/", "https://www.medico.co.il/doctors/", "https://www.medico.co.il/doctors/%d7%a4%d7%a8%d7%95%d7%a4-%d7%99%d7%a2%d7%9c-%d7%9b%d7%94%d7%9f/", "https://www.tasmc.org.il/doctorssearch/dr/cohen-yael/", "https://www.szmc.org.il/doctors/cohen-yael/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.vimed.co.il/users/0918fba4-bd6a-4310-ab8f-b51cab0b8f80", "https://www.meuhedet.co.il/poi/ParamedicalDoctors/000189680918100097000000000000_0", "https://www.medreviews.co.il/provider/dr-cohen-yael"]</t>
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>1.111070905235564e+19</v>
+        <v>3.333254404514628e+19</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>https://www.drmayasharonweiner.com/</t>
+          <t>https://elitemed.co.il/doctors/dr-yael-cohen-hebrew/</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr"/>
       <c r="AJ56" t="inlineStr"/>
       <c r="AK56" t="inlineStr"/>
-      <c r="AL56" t="inlineStr"/>
-      <c r="AM56" t="inlineStr"/>
-      <c r="AN56" t="inlineStr"/>
-      <c r="AO56" t="inlineStr"/>
-      <c r="AP56" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL56" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM56" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN56" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>ד"ר יעל כהן - elitemed.co.il ד"ר יעל כהן - elitemed.co.il דלג לתוכן Facebook Instagram Whatsapp Office@elitemed.co.il 073-321-4181 בית אודות רופאים שירותים רפואיים אולטרסאונד וביופסיות אוסטאופתיה אורולוגיה אורתופדיה אלרגיה ואימונולגיה אנדוקרינולוגיה סוכרת וירידה במשקל אסתטיקה אף אוזן גרון גינקולוגיה ובריאות האישה גסטרואנטרולוגיה גֵרִיאַטרִיָה דרמטולגיה המטולוגיה כלי דם ורדיולוגיה פולשנית התמחויות טיפוליות ושיקומיות כירורגיה כירורגיה פלסטית מרפאת כאב נוירולוגיה, קשב וריכוז והתפתחות הילד נפרולוגיה ויתר לחץ דם סקירות מערכות ואקו לב עובר עיניים פודיאטריה כירורגית וכף רגל פולמונולוגיה ורפואת שינה פסיכיאטריה פרוקטולוגיה וכירורגיה קולורקטלית קרדיולוגיה ואלקטרופיזיולוגיה ראומטולוגיה רפואת ילדים מומחית רפואת ספורט ופיזיותרפיה רפואה תעסוקתית תזונה קלינית ודיאטה תור דחוף  24-48 שעות צור קשר השכרת קליניקה במודיעין שירות VIP שירותים מידע רפואי בית אודות רופאים שירותים רפואיים אולטרסאונד וביופסיות אוסטאופתיה אורולוגיה אורתופדיה אלרגיה ואימונולגיה אנדוקרינולוגיה סוכרת וירידה במשקל אסתטיקה אף אוזן גרון גינקולוגיה ובריאות האישה גס</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr"/>
       <c r="AQ56" t="inlineStr"/>
       <c r="AR56" t="n">
         <v>1</v>
@@ -9643,7 +9651,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>מנחם נוימן</t>
+          <t>מאיה שרון וינר</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9674,7 +9682,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>hello@professorneuman.com</t>
+          <t>clinic@drmayasharonweiner.com</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -9687,7 +9695,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://professorneuman.com/he/</t>
+          <t>https://www.drmayasharonweiner.com/</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -9697,12 +9705,12 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>פרופ׳ מנחם נוימן — אורוגינקולוגיה ורפואת רצפת האגן מגדל סוזוקי, קומה 4, רח׳ יגאל אלון 82, תל אביב 054-644-2060 · hello@professorneuman.com ראשי מידע לרופאים מידע למטופלות מהתקשורת צרי קשר English פרופ׳ מנחם נוימן אורוגינקולוגיה ורפואת רצפת האגן צניחת איברי האגן ודליפת שתן הן מהתופעות השכיחות ביותר בקרב נשים — וגם מהניתנות ביותר לטי</t>
+          <t>אני איתך במסע הזה. הצעד הראשון שלך מתחיל כאן. ד"ר מאיה שרון-וינר רופאת נשים מומחית בפריון והפריה חוץ גופית מיילדות וגינקולוגיה לקביעת פגישה © 2026 כל הזכויות שמורות לד"ר מאיה שרון-וינר הברזל 9א', רמת החייל ווטסאפ למרפאה clinic@drmayasharonweiner.com פוריות האישה והגבר טיפולי פוריות הפריה חוץ גופית ו-PGD שימור פוריות פוריות לאחר סרטן ובנשאיות BRCA מעקב וליווי הריון גינקולוגיה כללית Menu Close אודות יצירת קשר מדיניות פרטיות הצהרת נגישות M</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>"מנחם נוימן"</t>
+          <t>"מאיה שרון וינר"</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -9712,11 +9720,11 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>[{"email": "info@raphaelhospitals.co.il", "confidence": 80, "source_url": "https://www.raphaelhospitals.co.il/en/international-department/about/", "identity_url": "https://www.raphaelhospitals.co.il/doctors/neuman-menahem/", "evidence": "info@raphaelhospitals.co.il", "matched_query": "\"מנחם נוימן\"", "extraction_method": "linked_mailto"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T57" t="n">
         <v>0</v>
@@ -9724,36 +9732,36 @@
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-09-04T18:20:49.705154+00:00</t>
+          <t>2026-09-04T17:43:40.101946+00:00</t>
         </is>
       </c>
       <c r="W57" t="n">
         <v>2</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y57" t="n">
         <v>7</v>
       </c>
       <c r="Z57" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>["https://professorneuman.com/", "https://professorneuman.com/he/", "https://professorneuman.com/he/contact", "https://professorneuman.com/en/contact", "https://www.facebook.com/public/%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/", "https://www.facebook.com/people/%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/pfbid0371mkxMbe96MNN5gS9XHB7KqrSyxJnXyG9AsLfdZV7j8RjCKyjm8cEEVgjSreLhY8l/", "https://chabadpedia.co.il/wiki/%D7%9E%D7%A0%D7%97%D7%9D_%D7%A0%D7%95%D7%99%D7%9E%D7%9F", "https://www.raphaelhospitals.co.il/doctors/neuman-menahem/", "https://www.raphaelhospitals.co.il/about/aboutus/", "https://www.raphaelhospitals.co.il/fields/endoscopic-unit/about/", "https://www.raphaelhospitals.co.il/fields/pain-clinic/about/", "https://www.raphaelhospitals.co.il/en/international-department/about/", "https://www.raphaelhospitals.co.il/fields/heart-catheterization-clinic/about/", "https://www.raphaelhospitals.co.il/en/about/aboutus/", "https://www.raphaelhospitals.co.il/en/contact/"]</t>
+          <t>["https://www.drmayasharonweiner.com/", "https://www.drmayasharonweiner.com/about", "https://www.drmayasharonweiner.com/contact", "https://www.medreviews.co.il/provider/dr-sharon-weiner-maya", "https://www.medreviews.co.il/provider/dr-sharon-weiner-maya/treatment", "https://www.doctorita.co.il/experts/119120", "https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr_maya_sharonweiner%2F&amp;is_from_rle", "https://docsrated.com/doctors/מאיה-שרון-וינר"]</t>
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>1.111070905235564e+19</v>
+        <v>3.333212715706692e+19</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9764,7 +9772,7 @@
       <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>https://professorneuman.com/he/</t>
+          <t>https://www.drmayasharonweiner.com/</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr"/>
@@ -9805,7 +9813,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>נעמה מימון</t>
+          <t>מנחם נוימן</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9836,7 +9844,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>office@medicaltop.co.il</t>
+          <t>hello@professorneuman.com</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -9849,7 +9857,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/</t>
+          <t>https://professorneuman.com/he/</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -9859,12 +9867,12 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t xml:space="preserve">ד"ר נעמה מימון: מומחית ברפואת נשים - MedicalTop Search Close Facebook 073-3310444 סנטר הגליל רחוב האגס 1, שער הרימון, קומה שניה. ראש פינה. office@medicaltop.co.il לקביעת תור דף הבית אודות תחומי פעילות הצוות שלנו יצירת קשר Menu דף הבית אודות תחומי פעילות הצוות שלנו יצירת קשר ד"ר נעמה מימון: מומחית ברפואת נשים דף הבית / רופאים / ד"ר נעמה מימון: מומחית ברפואת </t>
+          <t>פרופ׳ מנחם נוימן — אורוגינקולוגיה ורפואת רצפת האגן מגדל סוזוקי, קומה 4, רח׳ יגאל אלון 82, תל אביב 054-644-2060 · hello@professorneuman.com ראשי מידע לרופאים מידע למטופלות מהתקשורת צרי קשר English פרופ׳ מנחם נוימן אורוגינקולוגיה ורפואת רצפת האגן צניחת איברי האגן ודליפת שתן הן מהתופעות השכיחות ביותר בקרב נשים — וגם מהניתנות ביותר לטי</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>"נעמה מימון"</t>
+          <t>"מנחם נוימן"</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -9874,32 +9882,32 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "info@raphaelhospitals.co.il", "confidence": 80, "source_url": "https://www.raphaelhospitals.co.il/en/international-department/about/", "identity_url": "https://www.raphaelhospitals.co.il/doctors/neuman-menahem/", "evidence": "info@raphaelhospitals.co.il", "matched_query": "\"מנחם נוימן\"", "extraction_method": "linked_mailto"}]</t>
         </is>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-09-04T05:17:30.924388+00:00</t>
+          <t>2026-09-04T18:20:49.705154+00:00</t>
         </is>
       </c>
       <c r="W58" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X58" t="n">
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z58" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -9911,14 +9919,14 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>["https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fn.mh.mymwn.2025%2F", "https://www.facebook.com/SNMaesthetic/services/", "https://www.doctorita.co.il/experts/152626", "https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/", "https://medicaltop.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://medicaltop.co.il/%D7%94%D7%A6%D7%95%D7%95%D7%AA-%D7%A9%D7%9C%D7%A0%D7%95/", "https://medicaltop.co.il/wp-content/uploads/2024/04/אודות.jpg"]</t>
+          <t>["https://professorneuman.com/", "https://professorneuman.com/he/", "https://professorneuman.com/he/contact", "https://professorneuman.com/en/contact", "https://www.facebook.com/public/%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/", "https://www.facebook.com/people/%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/pfbid0371mkxMbe96MNN5gS9XHB7KqrSyxJnXyG9AsLfdZV7j8RjCKyjm8cEEVgjSreLhY8l/", "https://chabadpedia.co.il/wiki/%D7%9E%D7%A0%D7%97%D7%9D_%D7%A0%D7%95%D7%99%D7%9E%D7%9F", "https://www.raphaelhospitals.co.il/doctors/neuman-menahem/", "https://www.raphaelhospitals.co.il/about/aboutus/", "https://www.raphaelhospitals.co.il/fields/endoscopic-unit/about/", "https://www.raphaelhospitals.co.il/fields/pain-clinic/about/", "https://www.raphaelhospitals.co.il/en/international-department/about/", "https://www.raphaelhospitals.co.il/fields/heart-catheterization-clinic/about/", "https://www.raphaelhospitals.co.il/en/about/aboutus/", "https://www.raphaelhospitals.co.il/en/contact/"]</t>
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>1.084016810517069e+19</v>
+        <v>3.333212715706692e+19</v>
       </c>
       <c r="AE58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF58" t="n">
         <v>0</v>
@@ -9926,7 +9934,7 @@
       <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/</t>
+          <t>https://professorneuman.com/he/</t>
         </is>
       </c>
       <c r="AI58" t="inlineStr"/>
@@ -9944,7 +9952,7 @@
         <v>1</v>
       </c>
       <c r="AS58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT58" t="b">
         <v>1</v>
@@ -9967,7 +9975,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>תמר גרין</t>
+          <t>נעמה מימון</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9998,7 +10006,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>office@keshet-refua.co.il</t>
+          <t>office@medicaltop.co.il</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -10011,7 +10019,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://keshet-refua.co.il/doctors/dr-tamar-green/</t>
+          <t>https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -10021,17 +10029,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>פיזיותרפיה אסתטיקה פודקסטים קליניקות וססיות להשכרה צור קשר זימון תור ד"ר תמר גרין מומחית לגינקולוגיה ומיילדות מעקב הריון, סקירת הריון מוקדמת ומאוחרת, בדיקות אולטרסאונד אבחנתיות, גיל המעבר ובדיקות גינקולוגיות 073-3214111 office@keshet-refua.co.il לזימון תור &gt; תחומי מומחיות מעקב הריון בדיקות אולטרהסאונד אבחנתיות שקיפות עורפית סקירת מערכות מוקדמת ומאוחרת מעקבי גדילה הדמיית אגן והדמיה תלת מימדית של הרחם טיפולי גינקולוגיה פרטית התקנים תוך רח</t>
+          <t xml:space="preserve">ד"ר נעמה מימון: מומחית ברפואת נשים - MedicalTop Search Close Facebook 073-3310444 סנטר הגליל רחוב האגס 1, שער הרימון, קומה שניה. ראש פינה. office@medicaltop.co.il לקביעת תור דף הבית אודות תחומי פעילות הצוות שלנו יצירת קשר Menu דף הבית אודות תחומי פעילות הצוות שלנו יצירת קשר ד"ר נעמה מימון: מומחית ברפואת נשים דף הבית / רופאים / ד"ר נעמה מימון: מומחית ברפואת </t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>"תמר גרין"</t>
+          <t>"נעמה מימון"</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>official_text</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -10048,39 +10056,39 @@
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-09-05T00:09:39.798497+00:00</t>
+          <t>2026-09-04T05:17:30.924388+00:00</t>
         </is>
       </c>
       <c r="W59" t="n">
+        <v>4</v>
+      </c>
+      <c r="X59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>["https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fn.mh.mymwn.2025%2F", "https://www.facebook.com/SNMaesthetic/services/", "https://www.doctorita.co.il/experts/152626", "https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/", "https://medicaltop.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://medicaltop.co.il/%D7%94%D7%A6%D7%95%D7%95%D7%AA-%D7%A9%D7%9C%D7%A0%D7%95/", "https://medicaltop.co.il/wp-content/uploads/2024/04/אודות.jpg"]</t>
+        </is>
+      </c>
+      <c r="AD59" t="n">
+        <v>3.252050431551207e+19</v>
+      </c>
+      <c r="AE59" t="n">
         <v>2</v>
-      </c>
-      <c r="X59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>ddgs:bing</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>["https://www.medreviews.co.il/provider/dr-green-tamar", "https://keshet-refua.co.il/doctors/dr-tamar-green/", "https://keshet-refua.co.il/about-us/", "https://keshet-refua.co.il/contact-us/", "https://keshet-refua.co.il/clinics-for-rent-sessional-clinics-for-rent/", "https://keshet-refua.co.il/about-us/#contact-keshet-medical-center", "https://keshet-refua.co.il/areas_of_expertise/child-psychology-clinic/", "https://keshet-refua.co.il/doctors/private-clinical-dietician-jerusalem/", "https://keshet-refua.co.il/contact-us/#contact-keshet-medical-center", "https://keshet-refua.co.il/clinics-for-rent-sessional-clinics-for-rent/#contact-keshet-medical-center", "https://keshet-refua.co.il/doctors/dr-tamar-green-private-gynecologist-in-jerusalem/", "https://wayzee.co.il/", "https://keshet-refua.co.il/treatments/menstrual-arrangement-before-the-wedding-private-womens-clinic-private-gynecologist/", "https://keshet-refua.co.il/areas_of_expertise/child-psychology-clinic/#contact-keshet-medical-center", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2F61558661827898%2F", "https://www.facebook.com/public/%D7%AA%D7%9E%D7%A8-%D7%92%D7%A8%D7%99%D7%9F/", "https://www.medreviews.co.il/provider/dr-green-tamar/treatment/gynecologist-clinic", "https://www.szmc.org.il/doctors/grin-tamar/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
-        </is>
-      </c>
-      <c r="AD59" t="n">
-        <v>1.081834364478124e+19</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>1</v>
       </c>
       <c r="AF59" t="n">
         <v>0</v>
@@ -10088,7 +10096,7 @@
       <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>https://keshet-refua.co.il/doctors/dr-tamar-green/</t>
+          <t>https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr"/>
@@ -10106,7 +10114,7 @@
         <v>1</v>
       </c>
       <c r="AS59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT59" t="b">
         <v>1</v>
@@ -10129,7 +10137,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>אבי צפריר</t>
+          <t>תמר גרין</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10160,7 +10168,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>ivfrec@szmc.org.il</t>
+          <t>office@keshet-refua.co.il</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -10169,11 +10177,11 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/tsafrir-avi/</t>
+          <t>https://keshet-refua.co.il/doctors/dr-tamar-green/</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -10183,17 +10191,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t xml:space="preserve">h عربيه Русский צרו קשר צרו קשר אזור אישי אזור אישי רופאים בשערי צדק ד"ר  אבי צפריר רופא בכיר Dr.  Avi Tsafrir התמחות: גינקולוגיה ויילוד תת התמחות: הפריה חוץ גופית תחומים נוספים: שימור פוריות פוריות הגבר פוריות האשה עוד ivfrec@szmc.org.il ivfrec@szmc.org.il נסיון מקצועי מומחה ביילוד ובגינקולוגיה משנת 2005 רופא בכיר להפריה חוץ גופית בשערי צדק משנת 2005 תפקידים ציבוריים חבר ועד האגודה הישראלית לחקר הפוריות משנת 2022 לימודים והכשרה פקולטה </t>
+          <t>פיזיותרפיה אסתטיקה פודקסטים קליניקות וססיות להשכרה צור קשר זימון תור ד"ר תמר גרין מומחית לגינקולוגיה ומיילדות מעקב הריון, סקירת הריון מוקדמת ומאוחרת, בדיקות אולטרסאונד אבחנתיות, גיל המעבר ובדיקות גינקולוגיות 073-3214111 office@keshet-refua.co.il לזימון תור &gt; תחומי מומחיות מעקב הריון בדיקות אולטרהסאונד אבחנתיות שקיפות עורפית סקירת מערכות מוקדמת ומאוחרת מעקבי גדילה הדמיית אגן והדמיה תלת מימדית של הרחם טיפולי גינקולוגיה פרטית התקנים תוך רח</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>"אבי צפריר"</t>
+          <t>"תמר גרין"</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>official_text</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -10210,11 +10218,11 @@
       <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-09-03T20:26:52.799327+00:00</t>
+          <t>2026-09-05T00:09:39.798497+00:00</t>
         </is>
       </c>
       <c r="W60" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X60" t="n">
         <v>0</v>
@@ -10226,7 +10234,7 @@
         <v>6</v>
       </c>
       <c r="AA60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
@@ -10235,14 +10243,14 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>["https://www.infomed.co.il/experts/73913/", "https://he.hadassah.org.il/doctor/dr-avi-tsafrir-gaadaabqaa2aaoiag4adaabyaa======/", "https://www.doctors.co.il/expert/obstetrics-and-gynecologists/80043972/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fbyzpryr%2F", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A6%D7%A4%D7%A8%D7%99%D7%A8-%D7%90%D7%91%D7%99/", "https://drtor.co.il/doctor/3910", "https://www.szmc.org.il/doctors/tsafrir-avi/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.clalit.co.il/he/sefersherut/pages/doctordetails.aspx", "https://docsrated.com/doctors/אבי-צפריר", "https://www.doctorita.co.il/experts/44804"]</t>
+          <t>["https://www.medreviews.co.il/provider/dr-green-tamar", "https://keshet-refua.co.il/doctors/dr-tamar-green/", "https://keshet-refua.co.il/about-us/", "https://keshet-refua.co.il/contact-us/", "https://keshet-refua.co.il/clinics-for-rent-sessional-clinics-for-rent/", "https://keshet-refua.co.il/about-us/#contact-keshet-medical-center", "https://keshet-refua.co.il/areas_of_expertise/child-psychology-clinic/", "https://keshet-refua.co.il/doctors/private-clinical-dietician-jerusalem/", "https://keshet-refua.co.il/contact-us/#contact-keshet-medical-center", "https://keshet-refua.co.il/clinics-for-rent-sessional-clinics-for-rent/#contact-keshet-medical-center", "https://keshet-refua.co.il/doctors/dr-tamar-green-private-gynecologist-in-jerusalem/", "https://wayzee.co.il/", "https://keshet-refua.co.il/treatments/menstrual-arrangement-before-the-wedding-private-womens-clinic-private-gynecologist/", "https://keshet-refua.co.il/areas_of_expertise/child-psychology-clinic/#contact-keshet-medical-center", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2F61558661827898%2F", "https://www.facebook.com/public/%D7%AA%D7%9E%D7%A8-%D7%92%D7%A8%D7%99%D7%9F/", "https://www.medreviews.co.il/provider/dr-green-tamar/treatment/gynecologist-clinic", "https://www.szmc.org.il/doctors/grin-tamar/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>1.440908498889934e+19</v>
+        <v>3.245503093434371e+19</v>
       </c>
       <c r="AE60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF60" t="n">
         <v>0</v>
@@ -10250,7 +10258,7 @@
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/tsafrir-avi/</t>
+          <t>https://keshet-refua.co.il/doctors/dr-tamar-green/</t>
         </is>
       </c>
       <c r="AI60" t="inlineStr"/>
@@ -10268,7 +10276,7 @@
         <v>1</v>
       </c>
       <c r="AS60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT60" t="b">
         <v>1</v>
@@ -10291,17 +10299,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>אירינה דורפמן אלמוג</t>
+          <t>אבי צפריר</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>family_doctor</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -10322,20 +10330,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>dr.irenadorfman@gmail.com</t>
+          <t>ivfrec@szmc.org.il</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
+          <t>https://www.szmc.org.il/doctors/tsafrir-avi/</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -10345,12 +10353,12 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>מוג אירינה כרטיס עסק: ד"ר דורפמן אלמוג אירינה » תחום פעילות: בריאות וספורט » רופא » תאור העסק: רופאת משפחה עצמאית קופת חולים לאומית. » איש קשר: אירנה דורפמן » טלפונים: טלפון: 077-7997456 נייד: 054-4616457 » אתר: » מייל: dr.irenadorfman@gmail.com » כתובת: בן גוריון 123 יהוד, מיקוד: 56209 כלים מחשבונים לעסקים מדריכי ניהול עסק, הקמת עסק נושאי האתר הנהלת חשבונות הפקת חשבוניות חשבונית אלקטרונית ניהול לקוחות שותפים עסקיים אילת סיטי - מדריך הע</t>
+          <t xml:space="preserve">h عربيه Русский צרו קשר צרו קשר אזור אישי אזור אישי רופאים בשערי צדק ד"ר  אבי צפריר רופא בכיר Dr.  Avi Tsafrir התמחות: גינקולוגיה ויילוד תת התמחות: הפריה חוץ גופית תחומים נוספים: שימור פוריות פוריות הגבר פוריות האשה עוד ivfrec@szmc.org.il ivfrec@szmc.org.il נסיון מקצועי מומחה ביילוד ובגינקולוגיה משנת 2005 רופא בכיר להפריה חוץ גופית בשערי צדק משנת 2005 תפקידים ציבוריים חבר ועד האגודה הישראלית לחקר הפוריות משנת 2022 לימודים והכשרה פקולטה </t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>"אירינה דורפמן אלמוג"</t>
+          <t>"אבי צפריר"</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -10360,32 +10368,32 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>[{"email": "info@flex.co.il", "confidence": 80, "source_url": "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "identity_url": "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "evidence": "info@flex.co.il", "matched_query": "\"אירינה דורפמן אלמוג\"", "extraction_method": "linked_mailto"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-09-04T19:17:26.299485+00:00</t>
+          <t>2026-09-03T20:26:52.799327+00:00</t>
         </is>
       </c>
       <c r="W61" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z61" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AA61" t="n">
         <v>2</v>
@@ -10397,14 +10405,14 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>["https://www.dunsguide.co.il/C7195b21475cb11a3e5b86def04a3e20c_רופאים/דורפמן_אלמוג_אירינה/", "https://medpage.co.il/doctors/%D7%90%D7%99%D7%A8%D7%A0%D7%94-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-20871/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94/", "https://www.beok.co.il/doctors/Doctors-129241/", "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "https://www.flex.co.il/100_General/005_GeneralPages/006_About.aspx", "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "https://www.flex.co.il/100_General/900_DifferentStuff/900_ForTheCommunity.aspx"]</t>
+          <t>["https://www.infomed.co.il/experts/73913/", "https://he.hadassah.org.il/doctor/dr-avi-tsafrir-gaadaabqaa2aaoiag4adaabyaa======/", "https://www.doctors.co.il/expert/obstetrics-and-gynecologists/80043972/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fbyzpryr%2F", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A6%D7%A4%D7%A8%D7%99%D7%A8-%D7%90%D7%91%D7%99/", "https://drtor.co.il/doctor/3910", "https://www.szmc.org.il/doctors/tsafrir-avi/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.clalit.co.il/he/sefersherut/pages/doctordetails.aspx", "https://docsrated.com/doctors/אבי-צפריר", "https://www.doctorita.co.il/experts/44804"]</t>
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>1.17086168999585e+19</v>
+        <v>4.322725496669801e+19</v>
       </c>
       <c r="AE61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF61" t="n">
         <v>0</v>
@@ -10412,7 +10420,7 @@
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
+          <t>https://www.szmc.org.il/doctors/tsafrir-avi/</t>
         </is>
       </c>
       <c r="AI61" t="inlineStr"/>
@@ -10430,17 +10438,17 @@
         <v>1</v>
       </c>
       <c r="AS61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT61" t="b">
         <v>1</v>
       </c>
       <c r="AU61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>PERSON</t>
+          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
       </c>
     </row>
@@ -10453,7 +10461,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>אלון שלב</t>
+          <t>אירינה דורפמן אלמוג</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10484,7 +10492,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>alonshalev31@gmail.com</t>
+          <t>dr.irenadorfman@gmail.com</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -10497,7 +10505,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://pain.coi.co.il/</t>
+          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -10507,12 +10515,12 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>הודעה לבעלי האתר תקופת הניסיון הסתיימה, יש ליצור מנוי דרך ממשק ניהול האתר. האתר נכנס לרשימת המחיקה ויימחק בקרוב לחץ כאן אם אינך זוכר את כתובת ממשק ניהול האתר שלך. דר אלון שלב - רופא כאב טלפון: 054-6221105 מייל: alonshalev31@gmail.com כתובת: ילדי טהרן 8, ראשון לציון ד"ר אלון שלב מומחה ברפואת המשפחה רופא כאב דף הבית אודות צור קשר אל תחכו - הזמינו תור לרופא עוד היום.. לייעוץ ראשוני ללא עלות והזמנת תורים מלאו פרטים או התקשרו: 05462</t>
+          <t>מוג אירינה כרטיס עסק: ד"ר דורפמן אלמוג אירינה » תחום פעילות: בריאות וספורט » רופא » תאור העסק: רופאת משפחה עצמאית קופת חולים לאומית. » איש קשר: אירנה דורפמן » טלפונים: טלפון: 077-7997456 נייד: 054-4616457 » אתר: » מייל: dr.irenadorfman@gmail.com » כתובת: בן גוריון 123 יהוד, מיקוד: 56209 כלים מחשבונים לעסקים מדריכי ניהול עסק, הקמת עסק נושאי האתר הנהלת חשבונות הפקת חשבוניות חשבונית אלקטרונית ניהול לקוחות שותפים עסקיים אילת סיטי - מדריך הע</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>"אלון שלב"</t>
+          <t>"אירינה דורפמן אלמוג"</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -10522,11 +10530,11 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "info@flex.co.il", "confidence": 80, "source_url": "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "identity_url": "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "evidence": "info@flex.co.il", "matched_query": "\"אירינה דורפמן אלמוג\"", "extraction_method": "linked_mailto"}]</t>
         </is>
       </c>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T62" t="n">
         <v>0</v>
@@ -10534,23 +10542,23 @@
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-09-04T19:37:15.755041+00:00</t>
+          <t>2026-09-04T19:17:26.299485+00:00</t>
         </is>
       </c>
       <c r="W62" t="n">
         <v>2</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z62" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
@@ -10559,11 +10567,11 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>["https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr.shalev.pain%2F&amp;is_from_rle", "https://www.bgu.ac.il/people/shalevn/", "https://www.bgu.ac.il/en/people/shalevn/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fdr.shalev.pain%2F", "https://www.medreviews.co.il/search/pain-management/center/rishon-lezion", "https://pain.coi.co.il/", "https://pain.coi.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA.htm", "https://pain.coi.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8.htm"]</t>
+          <t>["https://www.dunsguide.co.il/C7195b21475cb11a3e5b86def04a3e20c_רופאים/דורפמן_אלמוג_אירינה/", "https://medpage.co.il/doctors/%D7%90%D7%99%D7%A8%D7%A0%D7%94-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-20871/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94/", "https://www.beok.co.il/doctors/Doctors-129241/", "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "https://www.flex.co.il/100_General/005_GeneralPages/006_About.aspx", "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "https://www.flex.co.il/100_General/900_DifferentStuff/900_ForTheCommunity.aspx"]</t>
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>1.17086168999585e+19</v>
+        <v>3.51258506998755e+19</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10574,7 +10582,7 @@
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>https://pain.coi.co.il/</t>
+          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
         </is>
       </c>
       <c r="AI62" t="inlineStr"/>
@@ -10615,7 +10623,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>אמיר צבעוני</t>
+          <t>אלון שלב</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10646,7 +10654,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>healtms@gmail.com</t>
+          <t>alonshalev31@gmail.com</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -10659,7 +10667,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://www.drzivony.co.il/</t>
+          <t>https://pain.coi.co.il/</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -10669,12 +10677,12 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>"ר אמיר צבעוני ד"ר אמיר צבעוני רופא משפחה מומחה העוסק בטיפול בכאב כרוני בגישת גוף-נפש ללא שימוש בתרופות או בפרוצדורות רפואיות. הטיפול מבוסס מחקר בתחום מדעי המח והכאב. ניתן לקרוא עליי עוד ב דף האודות . טלפון: 051-2303120 healtms@gmail.com קליניקה בגבעת עדה (סמוך לבנימינה) ניתן ליצור איתי קשר גם ב דף יצירת הקשר פוסטים אחרונים על הענק הירוק והדחקת רגשות לאותת עם המגבים רגישות יתר לאחר פציעה אזהרת טריגר בקשת סליחה מעצמי חפש: חיפוש בית אודות</t>
+          <t>הודעה לבעלי האתר תקופת הניסיון הסתיימה, יש ליצור מנוי דרך ממשק ניהול האתר. האתר נכנס לרשימת המחיקה ויימחק בקרוב לחץ כאן אם אינך זוכר את כתובת ממשק ניהול האתר שלך. דר אלון שלב - רופא כאב טלפון: 054-6221105 מייל: alonshalev31@gmail.com כתובת: ילדי טהרן 8, ראשון לציון ד"ר אלון שלב מומחה ברפואת המשפחה רופא כאב דף הבית אודות צור קשר אל תחכו - הזמינו תור לרופא עוד היום.. לייעוץ ראשוני ללא עלות והזמנת תורים מלאו פרטים או התקשרו: 05462</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>"אמיר צבעוני"</t>
+          <t>"אלון שלב"</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -10696,7 +10704,7 @@
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-09-03T23:00:56.706890+00:00</t>
+          <t>2026-09-04T19:37:15.755041+00:00</t>
         </is>
       </c>
       <c r="W63" t="n">
@@ -10706,10 +10714,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Z63" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -10721,11 +10729,11 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>["https://www.drzivony.co.il/", "https://www.drzivony.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
+          <t>["https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr.shalev.pain%2F&amp;is_from_rle", "https://www.bgu.ac.il/people/shalevn/", "https://www.bgu.ac.il/en/people/shalevn/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fdr.shalev.pain%2F", "https://www.medreviews.co.il/search/pain-management/center/rishon-lezion", "https://pain.coi.co.il/", "https://pain.coi.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA.htm", "https://pain.coi.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8.htm"]</t>
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>1.170738155316593e+19</v>
+        <v>3.51258506998755e+19</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10736,7 +10744,7 @@
       <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>https://www.drzivony.co.il/</t>
+          <t>https://pain.coi.co.il/</t>
         </is>
       </c>
       <c r="AI63" t="inlineStr"/>
@@ -10777,7 +10785,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>בתיה קורנבוים</t>
+          <t>אמיר צבעוני</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10808,7 +10816,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>batyakornboim@gmail.com</t>
+          <t>healtms@gmail.com</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -10821,7 +10829,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>https://www.dr-batya-kornboim.com/</t>
+          <t>https://www.drzivony.co.il/</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -10831,12 +10839,12 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>שקל בחיפה אודות חוות דעת יצירת קשר כתבות ופרסומים תפריט ד״ר בתיה קורנבוים - מומחית ברפואת משפחה ורפואת השמנה [תיאור המרפאה יתווסף בהמשך] טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו חיפה 3570901 IL 052-567-1100 batyakornboim@gmail.com התמחויות רפואיות עיקריות: [פירוט תחומי הטיפול יתווסף בהמשך] מידע מעשי: יצירת קשר: טלפון 052-567-1100 או וואטסאפ 052-567-1100 מיקום: טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו , חיפה סוג</t>
+          <t>"ר אמיר צבעוני ד"ר אמיר צבעוני רופא משפחה מומחה העוסק בטיפול בכאב כרוני בגישת גוף-נפש ללא שימוש בתרופות או בפרוצדורות רפואיות. הטיפול מבוסס מחקר בתחום מדעי המח והכאב. ניתן לקרוא עליי עוד ב דף האודות . טלפון: 051-2303120 healtms@gmail.com קליניקה בגבעת עדה (סמוך לבנימינה) ניתן ליצור איתי קשר גם ב דף יצירת הקשר פוסטים אחרונים על הענק הירוק והדחקת רגשות לאותת עם המגבים רגישות יתר לאחר פציעה אזהרת טריגר בקשת סליחה מעצמי חפש: חיפוש בית אודות</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>"בתיה קורנבוים"</t>
+          <t>"אמיר צבעוני"</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -10858,7 +10866,7 @@
       <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-09-03T23:52:50.148875+00:00</t>
+          <t>2026-09-03T23:00:56.706890+00:00</t>
         </is>
       </c>
       <c r="W64" t="n">
@@ -10883,11 +10891,11 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>["https://www.dr-batya-kornboim.com/", "https://www.dr-batya-kornboim.com/#%D7%90%D7%95%D7%93%D7%95%D7%AA"]</t>
+          <t>["https://www.drzivony.co.il/", "https://www.drzivony.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>1.170738155316593e+19</v>
+        <v>3.51221446594978e+19</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10898,7 +10906,7 @@
       <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>https://www.dr-batya-kornboim.com/</t>
+          <t>https://www.drzivony.co.il/</t>
         </is>
       </c>
       <c r="AI64" t="inlineStr"/>
@@ -10939,7 +10947,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>שלומית שדמון</t>
+          <t>בתיה קורנבוים</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10970,7 +10978,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>shlomitshadmon@gmail.com</t>
+          <t>batyakornboim@gmail.com</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -10983,7 +10991,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
+          <t>https://www.dr-batya-kornboim.com/</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -10993,12 +11001,12 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>ם ופעילויות כנסים והשתלמויות הרצאות מהכנסים מטפלי.ות איט"ם מטפלי.ות איט"ם פיזיותרפיסטים.ית איט"ם מרפאות ציבוריות הצטרפות והתמחות צור קשר פרטי התקשרות טלפון 054-9145177 כתובת אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אימייל shlomitshadmon@gmail.com שדמון שלומית (MD) – תל אביב מקצוע:  רופאת משפחה, מוסמכת ביעוץ וטיפול מיני. התמחות: מטפלת מינית איזור טיפול: תל אביב אודותי אני רופאת משפחה ותיקה, מדריכה קלינית ומרצה בנושאי בריאות האישה, מיניות ה</t>
+          <t>שקל בחיפה אודות חוות דעת יצירת קשר כתבות ופרסומים תפריט ד״ר בתיה קורנבוים - מומחית ברפואת משפחה ורפואת השמנה [תיאור המרפאה יתווסף בהמשך] טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו חיפה 3570901 IL 052-567-1100 batyakornboim@gmail.com התמחויות רפואיות עיקריות: [פירוט תחומי הטיפול יתווסף בהמשך] מידע מעשי: יצירת קשר: טלפון 052-567-1100 או וואטסאפ 052-567-1100 מיקום: טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו , חיפה סוג</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>"שלומית שדמון"</t>
+          <t>"בתיה קורנבוים"</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -11008,11 +11016,11 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "identity_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "evidence": "mail.com אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"שלומית שדמון\"", "extraction_method": "direct_text"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T65" t="n">
         <v>0</v>
@@ -11020,7 +11028,7 @@
       <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-09-04T15:25:57.140597+00:00</t>
+          <t>2026-09-03T23:52:50.148875+00:00</t>
         </is>
       </c>
       <c r="W65" t="n">
@@ -11030,10 +11038,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z65" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -11045,11 +11053,11 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>["https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA/", "https://moonbellboutique.com/index/%D7%93%D7%A8-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%A9%D7%93%D7%9E%D7%95%D7%9F/", "https://moonbellboutique.com/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/", "https://www.infomed.co.il/experts/145161/", "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
+          <t>["https://www.dr-batya-kornboim.com/", "https://www.dr-batya-kornboim.com/#%D7%90%D7%95%D7%93%D7%95%D7%AA"]</t>
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>1.081051978176164e+19</v>
+        <v>3.51221446594978e+19</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -11060,7 +11068,7 @@
       <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
+          <t>https://www.dr-batya-kornboim.com/</t>
         </is>
       </c>
       <c r="AI65" t="inlineStr"/>
@@ -11101,7 +11109,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>שרון שלמה קלייטמן</t>
+          <t>שלומית שדמון</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11132,7 +11140,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>sharon.kleitman@gmail.com</t>
+          <t>shlomitshadmon@gmail.com</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -11145,7 +11153,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
+          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -11155,12 +11163,12 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>ש קשר שיתוף שתפו במייל שתפו בפייסבוק שתפו בטוויטר שתפו בלינקדין ד"ר שרון קלייטמן מומחה ברפואת משפחה, MST - Mind Set Technique, רפואה אינטגרטיבית, IMS - דיקור יבש, תזונה אינטגרטיבית. נייד 052-8325580 פקס 08-6560357 דוא"ל sharon.kleitman@gmail.com אתר www.integrative-med.com שלח/י לי sms פייסבוק אודות ד"ר שרון קלייטמן מומחה ברפואת משפחה, סיים את לימודי הרפואה באוניברסיטת בן גוריון, נשוי ואב לארבעה, מתגורר בקיבוץ שדה בוקר. עוסק בפיתוח והקנ</t>
+          <t>ם ופעילויות כנסים והשתלמויות הרצאות מהכנסים מטפלי.ות איט"ם מטפלי.ות איט"ם פיזיותרפיסטים.ית איט"ם מרפאות ציבוריות הצטרפות והתמחות צור קשר פרטי התקשרות טלפון 054-9145177 כתובת אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אימייל shlomitshadmon@gmail.com שדמון שלומית (MD) – תל אביב מקצוע:  רופאת משפחה, מוסמכת ביעוץ וטיפול מיני. התמחות: מטפלת מינית איזור טיפול: תל אביב אודותי אני רופאת משפחה ותיקה, מדריכה קלינית ומרצה בנושאי בריאות האישה, מיניות ה</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>"שרון שלמה קלייטמן"</t>
+          <t>"שלומית שדמון"</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -11170,11 +11178,11 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "identity_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "evidence": "mail.com אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"שלומית שדמון\"", "extraction_method": "direct_text"}]</t>
         </is>
       </c>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T66" t="n">
         <v>0</v>
@@ -11182,7 +11190,7 @@
       <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-09-04T15:41:54.743203+00:00</t>
+          <t>2026-09-04T15:25:57.140597+00:00</t>
         </is>
       </c>
       <c r="W66" t="n">
@@ -11195,10 +11203,10 @@
         <v>4</v>
       </c>
       <c r="Z66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
@@ -11207,11 +11215,11 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>["https://docsrated.com/doctors/שרון-קלייטמן", "https://www.dunsguide.co.il/Cb6a87819a48606a97ab6b3a3617e9370_רופאים/קלייטמן_שרון_שלמה/", "https://www.facebook.com/sharon.kleitman.md/directory_category/", "https://dns.dibiz.com/sharon-kleitman-md", "https://longevitepalmbeach.com"]</t>
+          <t>["https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA/", "https://moonbellboutique.com/index/%D7%93%D7%A8-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%A9%D7%93%D7%9E%D7%95%D7%9F/", "https://moonbellboutique.com/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/", "https://www.infomed.co.il/experts/145161/", "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>1.081051978176164e+19</v>
+        <v>3.243155934528492e+19</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -11222,7 +11230,7 @@
       <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
+          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
         </is>
       </c>
       <c r="AI66" t="inlineStr"/>
@@ -11263,7 +11271,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>איה שלם</t>
+          <t>שרון שלמה קלייטמן</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11294,20 +11302,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>info@shrir-sheled.co.il</t>
+          <t>sharon.kleitman@gmail.com</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/</t>
+          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -11317,12 +11325,12 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>ד"ר איה שלם - אינדקס מטפלים ברפואת שריר שלד דלג לתוכן info@shrir-sheled.co.il בית רשימת המטפלים מאמרים מקצועיים אודות מקצוע המטפל רפואת משפחה פיזיותרפיה אוסטיאופתיה כירופרקטיקה אורתופדיה צרו קשר תפריט בית רשימת המטפלים מאמרים מקצועיים אודות מקצוע המטפל רפואת משפחה פיזיותרפי</t>
+          <t>ש קשר שיתוף שתפו במייל שתפו בפייסבוק שתפו בטוויטר שתפו בלינקדין ד"ר שרון קלייטמן מומחה ברפואת משפחה, MST - Mind Set Technique, רפואה אינטגרטיבית, IMS - דיקור יבש, תזונה אינטגרטיבית. נייד 052-8325580 פקס 08-6560357 דוא"ל sharon.kleitman@gmail.com אתר www.integrative-med.com שלח/י לי sms פייסבוק אודות ד"ר שרון קלייטמן מומחה ברפואת משפחה, סיים את לימודי הרפואה באוניברסיטת בן גוריון, נשוי ואב לארבעה, מתגורר בקיבוץ שדה בוקר. עוסק בפיתוח והקנ</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>"איה שלם"</t>
+          <t>"שרון שלמה קלייטמן"</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -11344,7 +11352,7 @@
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-09-04T18:58:24.569451+00:00</t>
+          <t>2026-09-04T15:41:54.743203+00:00</t>
         </is>
       </c>
       <c r="W67" t="n">
@@ -11354,13 +11362,13 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z67" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AA67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
@@ -11369,11 +11377,11 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>["https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%9C%D7%9D-%D7%90%D7%99%D7%94/", "https://medpage.co.il/doctors/16196-%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D-8959/", "https://www.doctorita.co.il/experts/124568", "https://drtor.co.il/doctor/19921", "http://me.doctorsonly.co.il/user/2636", "https://www.infomed.co.il/experts/74772/", "https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/", "https://eshkol.media/", "https://shrir-sheled.co.il/about/"]</t>
+          <t>["https://docsrated.com/doctors/שרון-קלייטמן", "https://www.dunsguide.co.il/Cb6a87819a48606a97ab6b3a3617e9370_רופאים/קלייטמן_שרון_שלמה/", "https://www.facebook.com/sharon.kleitman.md/directory_category/", "https://dns.dibiz.com/sharon-kleitman-md", "https://longevitepalmbeach.com"]</t>
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>1.17086168999585e+19</v>
+        <v>3.243155934528492e+19</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -11384,7 +11392,7 @@
       <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/</t>
+          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
         </is>
       </c>
       <c r="AI67" t="inlineStr"/>
@@ -11408,9 +11416,171 @@
         <v>1</v>
       </c>
       <c r="AU67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV67" t="inlineStr">
+        <is>
+          <t>PERSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>13</v>
+      </c>
+      <c r="B68" t="n">
+        <v>6</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>איה שלם</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>family_doctor</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>moh</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>info@shrir-sheled.co.il</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>CLINIC_OR_ORGANIZATION</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>88</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>ד"ר איה שלם - אינדקס מטפלים ברפואת שריר שלד דלג לתוכן info@shrir-sheled.co.il בית רשימת המטפלים מאמרים מקצועיים אודות מקצוע המטפל רפואת משפחה פיזיותרפיה אוסטיאופתיה כירופרקטיקה אורתופדיה צרו קשר תפריט בית רשימת המטפלים מאמרים מקצועיים אודות מקצוע המטפל רפואת משפחה פיזיותרפי</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>"איה שלם"</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>direct_text</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S68" t="n">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-09-04T18:58:24.569451+00:00</t>
+        </is>
+      </c>
+      <c r="W68" t="n">
+        <v>2</v>
+      </c>
+      <c r="X68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>["https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%9C%D7%9D-%D7%90%D7%99%D7%94/", "https://medpage.co.il/doctors/16196-%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D-8959/", "https://www.doctorita.co.il/experts/124568", "https://drtor.co.il/doctor/19921", "http://me.doctorsonly.co.il/user/2636", "https://www.infomed.co.il/experts/74772/", "https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/", "https://eshkol.media/", "https://shrir-sheled.co.il/about/"]</t>
+        </is>
+      </c>
+      <c r="AD68" t="n">
+        <v>3.51258506998755e+19</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="inlineStr"/>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr"/>
+      <c r="AJ68" t="inlineStr"/>
+      <c r="AK68" t="inlineStr"/>
+      <c r="AL68" t="inlineStr"/>
+      <c r="AM68" t="inlineStr"/>
+      <c r="AN68" t="inlineStr"/>
+      <c r="AO68" t="inlineStr"/>
+      <c r="AP68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ68" t="inlineStr"/>
+      <c r="AR68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV68" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>

--- a/output/contacts_primary.xlsx
+++ b/output/contacts_primary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV68"/>
+  <dimension ref="A1:AV79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>3.513367966871026e+19</v>
+        <v>1.054010390061308e+20</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>4.332731805573375e+19</v>
+        <v>1.299819541672012e+20</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>3.51221446594978e+19</v>
+        <v>1.053664339784934e+20</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>3.51221446594978e+19</v>
+        <v>1.053664339784934e+20</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>3.51221446594978e+19</v>
+        <v>1.053664339784934e+20</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>3.51221446594978e+19</v>
+        <v>1.053664339784934e+20</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>4.322725496553574e+19</v>
+        <v>1.296817648966072e+20</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>4.322725496553574e+19</v>
+        <v>1.296817648966072e+20</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>4.05589058935891e+19</v>
+        <v>1.216767176807673e+20</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>3.515591591099029e+19</v>
+        <v>1.054677477329709e+20</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>3.515549902289713e+19</v>
+        <v>1.054664970686914e+20</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>4.334214221724456e+19</v>
+        <v>1.300264266517337e+20</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>7293</v>
+        <v>21879</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>3.515591591099035e+19</v>
+        <v>1.05467747732971e+20</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>4.322725496553574e+19</v>
+        <v>1.296817648966072e+20</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>3.51221446594978e+19</v>
+        <v>1.053664339784934e+20</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>3.51221446594978e+19</v>
+        <v>1.053664339784934e+20</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3563,7 +3563,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>3.51221446594978e+19</v>
+        <v>1.053664339784934e+20</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>3.515591591099035e+19</v>
+        <v>1.05467747732971e+20</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>3.515549902289713e+19</v>
+        <v>1.054664970686914e+20</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -4049,7 +4049,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>3.513367966871025e+19</v>
+        <v>1.054010390061307e+20</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4211,7 +4211,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>3.51221446594978e+19</v>
+        <v>1.053664339784934e+20</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>3.51221446594978e+19</v>
+        <v>1.053664339784934e+20</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4535,7 +4535,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>3.333212715706692e+19</v>
+        <v>9.999638147120076e+19</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4587,12 +4587,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>מיכל בראונשטיין</t>
+          <t>לילך מלצקי</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>office.clinica1@gmail.com</t>
+          <t>ms.lilach@gmail.com</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://drbraunstein.co.il/</t>
+          <t>https://medicine.biu.ac.il/node/2836</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -4641,12 +4641,14 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>שמירת הבריאות של הפות והנרתיק דלקת עור ממגע קנדידה וגינוזיס חיידקי BV וגיניטיס פורלנטית ליכן סקלרוזוס אטרופיה נרתיקית כאב הפות והנרתיק כל מה שרצית לדעת על גז צחוק במרפאה גינקולוגית English Facebook-f Whatsapp 08-9702314 office.clinica1@gmail.com מרפאת "קליניקה", אלי הורוביץ 27, קומה 5, רחובות שלום לכולן, שמי מיכל בראונשטיין, אני רופאת נשים. בצעירותי החלטתי ללמוד רפואה, ובמיוחד גינקולוגיה, מתוך חלום ליצור מרפאה ידידותית ונעימה עבור מטופל</t>
+          <t>פשי קמפוס בטוח מדיניות הבטיחות והבריאות התעסוקתית מניעת הטרדה מינית חדשות חדשות המחקר תקשורת מעבר לגליל כפר הסטודנטים בעמיעד יצירת קשר English הדפסה ד"ר
+  לילך
+  מלצקי מרצה בכירה קליני Clinical Senior Lecturer דוא"ל ms.lilach@gmail.com דוא"ל בר-אילן lilach.malatskey@biu.ac.il תחום הוראה רפואת המשפחה תחומי מחקר Lifestyle Medicine מרכזי מחקר הפקולטה לרפואה ע"ש עזריאלי, אוניברסיטת בר-אילן, צפת מחלקה משפחה מרפאה שירותי בריאות כללית, מחו</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>"מיכל בראונשטיין"</t>
+          <t>"לילך מלצקי" רפואת משפחה</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -4656,71 +4658,79 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "lilach.malatskey@biu.ac.il", "confidence": 90, "source_url": "https://medicine.biu.ac.il/node/2836", "identity_url": "https://medicine.biu.ac.il/node/2836", "evidence": "ריאות התעסוקתית מניעת הטרדה מינית חדשות חדשות המחקר תקשורת מעבר לגליל כפר הסטודנטים בעמיעד יצירת קשר English הדפסה ד\"ר\n \n  לילך\n \n  מלצקי מרצה בכירה קליני Clinical Senior Lecturer דוא\"ל ms.lilach@gmail.com דוא\"ל בר-אילן lilach.malatskey@biu.ac.il תחום הוראה רפואת המשפחה תחומי מחקר Lifestyle Medicine מרכזי מחקר הפקולטה לרפואה ע\"ש עזריאלי, אוניברסיטת בר-אילן, צפת מחלקה משפחה מרפאה שירותי בריאות כללית, מחוז שרון\\שומרון תאריך עדכון אחרון : ", "matched_query": "\"לילך מלצקי\" רפואת משפחה", "extraction_method": "direct_text", "verification_schema_version": 3, "identity_name_verified": true, "identity_specialty_verified": true, "identity_evidence": "מלצקי לילך | הפקולטה לרפואה בגליל ע״ש עזריאלי מלצקי לילך | הפקולטה לרפואה בגליל ע״ש עזריאלי דילוג לתוכן העיקרי דילוג לתפריט ניווט ראשי תפריט משני ניוזלטר אוגוסט 2026 גלריית תמונות דרושים אירועים צור קשר אוניברסיטת בר-אילן English תפריט הפקולטה לרפואה בגליל ע״ש עזריאלי פייסבוק טוויטר tiktok יוטיוב Linkedin Instagram חיפוש חיפוש חיפוש אודות מי אנחנו חזון הפקולטה מרכזי רפואה מסונפים לפקולטה בקהילה \"פרחי רפואה\" תוכנית עבודות הגמר של גליליום תוכנית כוכבי הצפון הכירו את הבוגרים/ות שלנו לזכרם וזכרן In Memoriam ארכיון ניוזלטר לזכרם של אהרון ורחל דהאן הסגל הנהלת הפקולטה סגל אקדמי מחקרי סגל אקדמי קליני מינויים וקידומים אקדמיים קליניים סגל מינהלי הנהלת החינוך הרפואי והמחקר בעלי תפקידים מחקר ספריה תחום מומחיות מרכזי מחקר בפקולטה מכוני המחקר בבתי החולים טכנולוגיה ומכשור צוות היחידה ציוד היחידה המרכז הגנומי מאמרים Academic Publications לימודי רפואה M.D. לימודים לתואר דוקטור ברפואה (M.D.) - התכנית השש שנתית לימודים לתואר דוקטור ברפואה (M.D.) - התכנית הארבע שנתית לימודים לתואר דוקטור ברפואה (M.D.) - התכנית התלת שנתית תוכנית MD-PhD רום-גליל (רפואת"}]</t>
         </is>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-09-04T18:07:38.830808+00:00</t>
+          <t>2026-09-11T18:38:12.718732+00:00</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>["https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2FDr.MichalBraunstein%2F", "https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr.michal.braunstein%2F&amp;is_from_rle", "https://drbraunstein.co.il/", "https://www.shlema.org.il/", "https://drbraunstein.co.il/contact-dermatitis/", "https://drbraunstein.co.il/%D7%92%D7%96-%D7%A6%D7%97%D7%95%D7%A7/", "https://drbraunstein.co.il/#contact"]</t>
+          <t>["https://www.ima.org.il/MainSiteNew/StaticPage.aspx?Page=13564", "https://www.ima.org.il/Main/ViewContent.aspx?CategoryId=19239", "https://doctorindex.co.il/דוקטור-מלצקי-לילך/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%9E%D7%9C%D7%A6%D7%A7%D7%99-%D7%9C%D7%99%D7%9C%D7%9A/", "https://family.mednet.co.il/writer/דר-לילך-מלצקי/", "https://www.rofim.org.il/minisite/דר_לילך_מלצקי", "https://www.rofim.org.il/minisite/%D7%93%D7%A8_%D7%9C%D7%99%D7%9C%D7%9A_%D7%9E%D7%9C%D7%A6%D7%A7%D7%99", "https://www.shidurit-ltd.co.il/", "https://www.rofim.org.il/about", "https://www.rofim.org.il/Contact", "https://www.rofim.org.il/specialityPage/%D7%9E%D7%A8%D7%9B%D7%96_%D7%A8%D7%A4%D7%95%D7%90%D7%99", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%9E%D7%92%D7%90%D7%A8", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%91%D7%99%D7%AA_%D7%92%D7%93%D7%99", "https://www.rofim.org.il/minisite/%D7%90%D7%99%D7%99_%D7%90%D7%9C_%D7%A7%D7%9C%D7%99%D7%A0%D7%99%D7%A7", "https://medpage.co.il/doctors/לילך-מלצקי-978/", "https://medpage.co.il/doctors/%D7%9C%D7%99%D7%9C%D7%9A-%D7%9E%D7%9C%D7%A6%D7%A7%D7%99-978/", "https://medicine.biu.ac.il/node/2836", "https://medicine.biu.ac.il/contact", "https://medicine.biu.ac.il/node/26", "https://medicine.biu.ac.il/pre_clinical", "https://medicine.biu.ac.il/clinical_faculty", "https://medicine.biu.ac.il/node/6861", "https://medicine.biu.ac.il/node/6760"]</t>
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>3.333212715706692e+19</v>
+        <v>20415</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>https://drbraunstein.co.il/</t>
+          <t>https://medicine.biu.ac.il/node/2836</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="inlineStr"/>
-      <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="inlineStr"/>
-      <c r="AN26" t="inlineStr"/>
-      <c r="AO26" t="inlineStr"/>
-      <c r="AP26" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>מלצקי לילך | הפקולטה לרפואה בגליל ע״ש עזריאלי מלצקי לילך | הפקולטה לרפואה בגליל ע״ש עזריאלי דילוג לתוכן העיקרי דילוג לתפריט ניווט ראשי תפריט משני ניוזלטר אוגוסט 2026 גלריית תמונות דרושים אירועים צור קשר אוניברסיטת בר-אילן English תפריט הפקולטה לרפואה בגליל ע״ש עזריאלי פייסבוק טוויטר tiktok יוטיוב Linkedin Instagram חיפוש חיפוש חיפוש אודות מי אנחנו חזון הפקולטה מרכזי רפואה מסונפים לפקולטה בקהילה "פרחי רפואה" תוכנית עבודות הגמר של גליליום תוכנית כוכבי הצפון הכירו את הבוגרים/ות שלנו לזכרם וזכרן In Memoriam ארכיון ניוזלטר לזכרם של אהרון ורחל דהאן הסגל הנהלת הפקולטה סגל אקדמי מחקרי סגל אקדמי קליני מינויים וקידומים אקדמיים קליניים סגל מינהלי הנהלת החינוך הרפואי והמחקר בעלי תפקידים מחקר ספריה תחום מומחיות מרכזי מחקר בפקולטה מכוני המחקר בבתי החולים טכנולוגיה ומכשור צוות היחידה ציוד היחידה המרכז הגנומי מאמרים Academic Publications לימודי רפואה M.D. לימודים לתואר דוקטור ברפואה (M.D.) - התכנית השש שנתית לימודים לתואר דוקטור ברפואה (M.D.) - התכנית הארבע שנתית לימודים לתואר דוקטור ברפואה (M.D.) - התכנית התלת שנתית תוכנית MD-PhD רום-גליל (רפואת</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr"/>
       <c r="AR26" t="n">
         <v>1</v>
@@ -4732,11 +4742,11 @@
         <v>1</v>
       </c>
       <c r="AU26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
+          <t>PERSON</t>
         </is>
       </c>
     </row>
@@ -4749,12 +4759,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>נורה גורכד שבסו</t>
+          <t>מאמון הייב</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4780,7 +4790,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>norashapso@gmail.com</t>
+          <t>maamon.haib@gmail.com</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -4793,7 +4803,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/</t>
+          <t>https://medicine.biu.ac.il/node/6715</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4803,12 +4813,16 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Med Ted לחברים בלבד ארצ״י בשטח ארצ״י בתקשורת ארצ"י בכנסת פודקאסט "סדציה להמונים" נוהל כניסה להסדר הצטרפות צרו קשר טופס דיווח שיימינג טופס בקשת סיוע קהילה לזכרם חזרה &gt; חזרה &gt; ד"ר נורה שבסו גינקולוגיה ומיילדות 052-5363267 norashapso@gmail.com ד"ר נורה גורכד שפסו היא מומחית בגינקולוגיה ומיילדות, ובעלת על־התמחות בפוריות ובהפריה חוץ־גופית (IVF). נורה למדה רפואה בטכניון והתמחתה במרכז הרפואי צפון. כיום היא עובדת כרופאה בכירה ביחידת ה- IVF  וכר</t>
+          <t xml:space="preserve">דע אישי לסטודנט אגודת הסטודנטים סיוע נפשי קמפוס בטוח מדיניות הבטיחות והבריאות התעסוקתית מניעת הטרדה מינית חדשות חדשות המחקר תקשורת מעבר לגליל כפר הסטודנטים בעמיעד יצירת קשר הדפסה ד"ר
+  הייב
+  מאמון מדריך קליני דוא"ל maamon.haib@gmail.com מחלקה רפואת המשפחה מרפאה שירותי בריאות כללית, מחוז צפון תאריך עדכון אחרון : 20/04/2026 כניסה לעורכי האתר כל הזכויות שמורות:
+הפקולטה לרפואה בגליל ע״ש עזריאלי | אוניברסיטת בר-אילן | יצירת קשר לימודי
+</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>"נורה גורכד שבסו"</t>
+          <t>"מאמון הייב" רפואת משפחה</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -4825,64 +4839,72 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-09-04T04:55:16.280760+00:00</t>
+          <t>2026-09-11T18:38:09.730192+00:00</t>
         </is>
       </c>
       <c r="W27" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z27" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AA27" t="n">
         <v>1</v>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>["https://www.doctorita.co.il/experts/119054", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%92%D7%95%D7%A8%D7%9B%D7%93-%D7%A9%D7%91%D7%A1%D7%95-%D7%A0%D7%95%D7%A8%D7%94/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=72FD73030256FB59999957F3E61E03EABE6A8F724FC86F83B2380B60589F61A5&amp;RequestId=00000000-0000-0000-0001-000000000612", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=CE57634ABBFA154920019C7FAAD7385EAB0BB0D5FD8189978016A2325E1941AE&amp;RequestId=00000000-0000-0000-0001-000000000428", "https://www.beok.co.il/doctors/Doctors-1114057/", "https://medpage.co.il/doctors/%D7%A0%D7%95%D7%A8%D7%94-%D7%92%D7%95%D7%A8%D7%9B%D7%93-%D7%A9%D7%91%D7%A1%D7%95-20898/", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/", "https://www.amutatartzi.org/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.amutatartzi.org/%D7%A6%D7%95%D7%95%D7%AA-%D7%95%D7%91%D7%A2%D7%9C%D7%99-%D7%AA%D7%A4%D7%A7%D7%99%D7%93%D7%99%D7%9D/", "https://www.amutatartzi.org/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%90%D7%A8%D7%A6%D7%99/%D7%AA%D7%A7%D7%A0%D7%95%D7%9F-%D7%94%D7%A2%D7%9E%D7%95%D7%AA%D7%94/", "https://www.amutatartzi.org/דרושים-שותפויות-השכרת-מרפאה/", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%93%D7%B4%D7%A8-%D7%A2%D7%90%D7%99%D7%93%D7%94-%D7%94%D7%99%D7%99%D7%91-%D7%97%D7%9C%D7%99%D7%99%D7%97%D7%9C/", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A4%D7%99%D7%9C%D7%99%D7%A4-%D7%A8%D7%95%D7%96%D7%99%D7%A0%D7%A1%D7%A7%D7%99/", "https://www.amutatartzi.org/team/%D7%93%D7%B4%D7%A8-%D7%A9%D7%9E%D7%A2%D7%95%D7%9F-%D7%90%D7%A8%D7%95%D7%A0%D7%94%D7%99%D7%99%D7%9D/"]</t>
+          <t>["https://www.doctorita.co.il/experts/69492", "https://drtor.co.il/doctor/16532", "https://drtor.co.il/cdn-cgi/l/email-protection#fe9d91908a9f9d8abe9a8c8a918cd09d91d09792", "https://docsrated.com/doctors/מאמון-הייב", "https://medicine.biu.ac.il/node/6715", "https://medicine.biu.ac.il/contact", "https://medicine.biu.ac.il/node/26", "https://medicine.biu.ac.il/pre_clinical", "https://medicine.biu.ac.il/clinical_faculty", "https://medicine.biu.ac.il/node/6861", "https://medicine.biu.ac.il/node/6760"]</t>
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>3.252050431434981e+19</v>
+        <v>20415</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/</t>
+          <t>https://medicine.biu.ac.il/node/6715</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr"/>
       <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="inlineStr"/>
-      <c r="AM27" t="inlineStr"/>
-      <c r="AN27" t="inlineStr"/>
-      <c r="AO27" t="inlineStr"/>
-      <c r="AP27" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>מאמון הייב | הפקולטה לרפואה בגליל ע״ש עזריאלי מאמון הייב | הפקולטה לרפואה בגליל ע״ש עזריאלי דילוג לתוכן העיקרי דילוג לתפריט ניווט ראשי תפריט משני ניוזלטר אוגוסט 2026 גלריית תמונות דרושים אירועים צור קשר אוניברסיטת בר-אילן English תפריט הפקולטה לרפואה בגליל ע״ש עזריאלי פייסבוק טוויטר tiktok יוטיוב Linkedin Instagram חיפוש חיפוש חיפוש אודות מי אנחנו חזון הפקולטה מרכזי רפואה מסונפים לפקולטה בקהילה "פרחי רפואה" תוכנית עבודות הגמר של גליליום תוכנית כוכבי הצפון הכירו את הבוגרים/ות שלנו לזכרם וזכרן In Memoriam ארכיון ניוזלטר לזכרם של אהרון ורחל דהאן הסגל הנהלת הפקולטה סגל אקדמי מחקרי סגל אקדמי קליני מינויים וקידומים אקדמיים קליניים סגל מינהלי הנהלת החינוך הרפואי והמחקר בעלי תפקידים מחקר ספריה תחום מומחיות מרכזי מחקר בפקולטה מכוני המחקר בבתי החולים טכנולוגיה ומכשור צוות היחידה ציוד היחידה המרכז הגנומי מאמרים Academic Publications לימודי רפואה M.D. לימודים לתואר דוקטור ברפואה (M.D.) - התכנית השש שנתית לימודים לתואר דוקטור ברפואה (M.D.) - התכנית הארבע שנתית לימודים לתואר דוקטור ברפואה (M.D.) - התכנית התלת שנתית תוכנית MD-PhD רום-גליל (רפואת</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr"/>
       <c r="AR27" t="n">
         <v>1</v>
@@ -4911,7 +4933,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>נעם דומניץ</t>
+          <t>מיכל בראונשטיין</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4942,7 +4964,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>domniz.clinic@gmail.com</t>
+          <t>office.clinica1@gmail.com</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -4955,7 +4977,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://www.dr-domniz.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/</t>
+          <t>https://drbraunstein.co.il/</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4965,17 +4987,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>ל הדרך גלריה רוצה לשמוע מידע נוסף? קבעי פגישה עם ד"ר נעם דומניץ וקבלי טיפול מותאם אישית. קביעת תור / וואטסאפ פרטי יצירת קשר 0502174994 רוטשילד 54, כפר סבא (בית עמיתים, קומה 1, חדר 6 (מאחורי בית חב״ד)  | רש״י 30, בני ברק domniz.clinic@gmail.com ד"ר דומניץ מומחה בפוריות, מיילדות וגינקולוגיה. תחומי המרפאה בדיקות הריון ייעוץ טרום הריוני הריון בסיכון התקן תוך רחמי אבחון פוריות ‪טיפולי פוריות ‪ייעוץ פוריות ‪בדיקות פוריות תסמיני גיל המעבר משפט</t>
+          <t>שמירת הבריאות של הפות והנרתיק דלקת עור ממגע קנדידה וגינוזיס חיידקי BV וגיניטיס פורלנטית ליכן סקלרוזוס אטרופיה נרתיקית כאב הפות והנרתיק כל מה שרצית לדעת על גז צחוק במרפאה גינקולוגית English Facebook-f Whatsapp 08-9702314 office.clinica1@gmail.com מרפאת "קליניקה", אלי הורוביץ 27, קומה 5, רחובות שלום לכולן, שמי מיכל בראונשטיין, אני רופאת נשים. בצעירותי החלטתי ללמוד רפואה, ובמיוחד גינקולוגיה, מתוך חלום ליצור מרפאה ידידותית ונעימה עבור מטופל</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>"נעם דומניץ"</t>
+          <t>"מיכל בראונשטיין"</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>linked_text</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -4992,7 +5014,7 @@
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-09-04T05:13:39.315015+00:00</t>
+          <t>2026-09-04T18:07:38.830808+00:00</t>
         </is>
       </c>
       <c r="W28" t="n">
@@ -5002,10 +5024,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -5017,11 +5039,11 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>["https://www.dr-domniz.co.il/", "https://www.dr-domniz.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/"]</t>
+          <t>["https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2FDr.MichalBraunstein%2F", "https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr.michal.braunstein%2F&amp;is_from_rle", "https://drbraunstein.co.il/", "https://www.shlema.org.il/", "https://drbraunstein.co.il/contact-dermatitis/", "https://drbraunstein.co.il/%D7%92%D7%96-%D7%A6%D7%97%D7%95%D7%A7/", "https://drbraunstein.co.il/#contact"]</t>
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>3.252050431434981e+19</v>
+        <v>9.999638147120076e+19</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5032,7 +5054,7 @@
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>https://www.dr-domniz.co.il/</t>
+          <t>https://drbraunstein.co.il/</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr"/>
@@ -5073,7 +5095,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>נתנאל אלקבץ</t>
+          <t>נורה גורכד שבסו</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5104,12 +5126,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>aimee.medicalclinic@gmail.com</t>
+          <t>norashapso@gmail.com</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -5117,7 +5139,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://www.aimeemedical.co.il/clinical-dietitian/</t>
+          <t>https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -5127,18 +5149,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>הריון בסיכון או לצד מחלות רקע-  הוא תהליך אישי, מותאם ומכיל.
-עם ליווי מקצועי של אופק כהן־אלקבץ, דיאטנית קלינית מומחית, תוכלי לשמור על בריאותך ובריאות העובר ולחוות הריון רגוע ומאוזן. לתיאום פגישה אישית עם ד"ר נתנאל אלקבץ aimee.medicalclinic@gmail.com 053-338-8023 ניווט ראשי אודותינו המוצרים שלנו צרו קשר שירותי הקליניקה מעקב הריון והריון בסיכון גבוהה אולטרסאונד מתקדם בירור בעיות פריון אסתטיקה גינקולוגית תפקודית לביופלסטיקה דיטנית קלינית -</t>
+          <t>Med Ted לחברים בלבד ארצ״י בשטח ארצ״י בתקשורת ארצ"י בכנסת פודקאסט "סדציה להמונים" נוהל כניסה להסדר הצטרפות צרו קשר טופס דיווח שיימינג טופס בקשת סיוע קהילה לזכרם חזרה &gt; חזרה &gt; ד"ר נורה שבסו גינקולוגיה ומיילדות 052-5363267 norashapso@gmail.com ד"ר נורה גורכד שפסו היא מומחית בגינקולוגיה ומיילדות, ובעלת על־התמחות בפוריות ובהפריה חוץ־גופית (IVF). נורה למדה רפואה בטכניון והתמחתה במרכז הרפואי צפון. כיום היא עובדת כרופאה בכירה ביחידת ה- IVF  וכר</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>"נתנאל אלקבץ"</t>
+          <t>"נורה גורכד שבסו"</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>linked_text</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -5155,7 +5176,7 @@
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-04T05:24:06.061110+00:00</t>
+          <t>2026-09-04T04:55:16.280760+00:00</t>
         </is>
       </c>
       <c r="W29" t="n">
@@ -5165,13 +5186,13 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
@@ -5180,11 +5201,11 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>["https://www.infomed.co.il/experts/152655/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2F61560664132234%2F", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%90%D7%9C%D7%A7%D7%91%D7%A5-%D7%A0%D7%AA%D7%A0%D7%90%D7%9C/", "https://www.medreviews.co.il/provider/dr-elkabetz-netanel", "https://www.aimeemedical.co.il/about-us/", "https://www.aimeemedical.co.il/clinical-dietitian/", "https://www.aimeemedical.co.il/contact/"]</t>
+          <t>["https://www.doctorita.co.il/experts/119054", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%92%D7%95%D7%A8%D7%9B%D7%93-%D7%A9%D7%91%D7%A1%D7%95-%D7%A0%D7%95%D7%A8%D7%94/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=72FD73030256FB59999957F3E61E03EABE6A8F724FC86F83B2380B60589F61A5&amp;RequestId=00000000-0000-0000-0001-000000000612", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=CE57634ABBFA154920019C7FAAD7385EAB0BB0D5FD8189978016A2325E1941AE&amp;RequestId=00000000-0000-0000-0001-000000000428", "https://www.beok.co.il/doctors/Doctors-1114057/", "https://medpage.co.il/doctors/%D7%A0%D7%95%D7%A8%D7%94-%D7%92%D7%95%D7%A8%D7%9B%D7%93-%D7%A9%D7%91%D7%A1%D7%95-20898/", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/", "https://www.amutatartzi.org/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.amutatartzi.org/%D7%A6%D7%95%D7%95%D7%AA-%D7%95%D7%91%D7%A2%D7%9C%D7%99-%D7%AA%D7%A4%D7%A7%D7%99%D7%93%D7%99%D7%9D/", "https://www.amutatartzi.org/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%90%D7%A8%D7%A6%D7%99/%D7%AA%D7%A7%D7%A0%D7%95%D7%9F-%D7%94%D7%A2%D7%9E%D7%95%D7%AA%D7%94/", "https://www.amutatartzi.org/דרושים-שותפויות-השכרת-מרפאה/", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%93%D7%B4%D7%A8-%D7%A2%D7%90%D7%99%D7%93%D7%94-%D7%94%D7%99%D7%99%D7%91-%D7%97%D7%9C%D7%99%D7%99%D7%97%D7%9C/", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A4%D7%99%D7%9C%D7%99%D7%A4-%D7%A8%D7%95%D7%96%D7%99%D7%A0%D7%A1%D7%A7%D7%99/", "https://www.amutatartzi.org/team/%D7%93%D7%B4%D7%A8-%D7%A9%D7%9E%D7%A2%D7%95%D7%9F-%D7%90%D7%A8%D7%95%D7%A0%D7%94%D7%99%D7%99%D7%9D/"]</t>
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>3.252050431434981e+19</v>
+        <v>9.756151294304942e+19</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5195,7 +5216,7 @@
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>https://www.medreviews.co.il/provider/dr-elkabetz-netanel</t>
+          <t>https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr"/>
@@ -5219,11 +5240,11 @@
         <v>1</v>
       </c>
       <c r="AU29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
+          <t>PERSON</t>
         </is>
       </c>
     </row>
@@ -5236,7 +5257,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>עמיחי רוטנשטרייך</t>
+          <t>נעם דומניץ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5267,12 +5288,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>prof.rottenstreich@gmail.com</t>
+          <t>domniz.clinic@gmail.com</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -5280,7 +5301,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://www.prof-rottenstreich.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA</t>
+          <t>https://www.dr-domniz.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -5290,12 +5311,12 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>פואה פרופסור חבר מטעם האוניברסיטה העברית האגף למיילדות וגינקולוגיה, בית החולים וולפסון, חולון רופא בכיר ומנהל שירות ביחידה להיריון בסיכון Chat Phone פרופ׳ עמיחי רוטנשטרייך מומחה למיילדות גי נ קולוגיה והיריון בסיכון גבוה prof.rottenstreich@gmail.com 055-9787751            , 055-4353787 כל הזכויות שמורות עמיחי רוטנשטרייך 2024 © bottom of page</t>
+          <t>ל הדרך גלריה רוצה לשמוע מידע נוסף? קבעי פגישה עם ד"ר נעם דומניץ וקבלי טיפול מותאם אישית. קביעת תור / וואטסאפ פרטי יצירת קשר 0502174994 רוטשילד 54, כפר סבא (בית עמיתים, קומה 1, חדר 6 (מאחורי בית חב״ד)  | רש״י 30, בני ברק domniz.clinic@gmail.com ד"ר דומניץ מומחה בפוריות, מיילדות וגינקולוגיה. תחומי המרפאה בדיקות הריון ייעוץ טרום הריוני הריון בסיכון התקן תוך רחמי אבחון פוריות ‪טיפולי פוריות ‪ייעוץ פוריות ‪בדיקות פוריות תסמיני גיל המעבר משפט</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>"עמיחי רוטנשטרייך"</t>
+          <t>"נעם דומניץ"</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -5317,7 +5338,7 @@
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-09-04T06:21:38.973409+00:00</t>
+          <t>2026-09-04T05:13:39.315015+00:00</t>
         </is>
       </c>
       <c r="W30" t="n">
@@ -5342,11 +5363,11 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>["https://www.prof-rottenstreich.co.il/", "https://www.prof-rottenstreich.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.prof-rottenstreich.co.il/%D7%AA%D7%97%D7%95%D7%9E%D7%99-%D7%A4%D7%A2%D7%99%D7%9C%D7%95%D7%AA"]</t>
+          <t>["https://www.dr-domniz.co.il/", "https://www.dr-domniz.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/"]</t>
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>3.252050431434981e+19</v>
+        <v>9.756151294304942e+19</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5357,7 +5378,7 @@
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>https://www.prof-rottenstreich.co.il/</t>
+          <t>https://www.dr-domniz.co.il/</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr"/>
@@ -5381,11 +5402,11 @@
         <v>1</v>
       </c>
       <c r="AU30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>PERSON</t>
+          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5419,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ערן ברזילי</t>
+          <t>נתנאל אלקבץ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5429,12 +5450,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>prof.eran.barzilay@gmail.com</t>
+          <t>aimee.medicalclinic@gmail.com</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -5442,7 +5463,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
+          <t>https://www.aimeemedical.co.il/clinical-dietitian/</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -5452,17 +5473,18 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>ת ה- MD-PhD היוקרתית של הפקולטה לרפואה באוניברסיטת תל אביב, בהצטיינות. עמודים דף הבית אודות אולטרסאונד בהריון ממצאים לא תקינים אולטרסאונד גניקולוגי צור קשר צור קשר ברודצקי 43, כניסה ב', רמת אביב, תל אביב יפו 073-7815218 prof.eran.barzilay@gmail.com פרופ' ערן ברזילי באינפומד © כל הזכויות שמורות לאינפומד בע"מ פרטיות המבקרים באתר חשובה לנו כדי לשפר את חוויית הגלישה, אתר זה משתמש בקבצי עוגיות  (Cookies), המשך גלישה באתר מהווה הסכמתך לכך. מד</t>
+          <t>הריון בסיכון או לצד מחלות רקע-  הוא תהליך אישי, מותאם ומכיל.
+עם ליווי מקצועי של אופק כהן־אלקבץ, דיאטנית קלינית מומחית, תוכלי לשמור על בריאותך ובריאות העובר ולחוות הריון רגוע ומאוזן. לתיאום פגישה אישית עם ד"ר נתנאל אלקבץ aimee.medicalclinic@gmail.com 053-338-8023 ניווט ראשי אודותינו המוצרים שלנו צרו קשר שירותי הקליניקה מעקב הריון והריון בסיכון גבוהה אולטרסאונד מתקדם בירור בעיות פריון אסתטיקה גינקולוגית תפקודית לביופלסטיקה דיטנית קלינית -</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>"ערן ברזילי"</t>
+          <t>"נתנאל אלקבץ"</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>linked_text</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -5479,7 +5501,7 @@
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-09-04T06:36:53.022308+00:00</t>
+          <t>2026-09-04T05:24:06.061110+00:00</t>
         </is>
       </c>
       <c r="W31" t="n">
@@ -5492,10 +5514,10 @@
         <v>4</v>
       </c>
       <c r="Z31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
@@ -5504,11 +5526,11 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>["https://www.instagram.com/proferanbarzilay/", "https://www.bgu.ac.il/people/barzilae/", "https://www.bgu.ac.il/en/people/barzilae/", "https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://dr-barzilay.com/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/"]</t>
+          <t>["https://www.infomed.co.il/experts/152655/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2F61560664132234%2F", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%90%D7%9C%D7%A7%D7%91%D7%A5-%D7%A0%D7%AA%D7%A0%D7%90%D7%9C/", "https://www.medreviews.co.il/provider/dr-elkabetz-netanel", "https://www.aimeemedical.co.il/about-us/", "https://www.aimeemedical.co.il/clinical-dietitian/", "https://www.aimeemedical.co.il/contact/"]</t>
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>3.252050431434981e+19</v>
+        <v>9.756151294304942e+19</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5519,7 +5541,7 @@
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
+          <t>https://www.medreviews.co.il/provider/dr-elkabetz-netanel</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr"/>
@@ -5543,11 +5565,11 @@
         <v>1</v>
       </c>
       <c r="AU31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>PERSON</t>
+          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
       </c>
     </row>
@@ -5560,7 +5582,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>פרופ' משען נדב</t>
+          <t>עמיחי רוטנשטרייך</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5580,18 +5602,18 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=26deea29-fa58-44cd-a7ba-96d9df718414</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>ima</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>drnadavmic@gmail.com</t>
+          <t>prof.rottenstreich@gmail.com</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -5604,7 +5626,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://www.dr-mishan.co.il/</t>
+          <t>https://www.prof-rottenstreich.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -5614,17 +5636,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>פרופ' נדב משען ✅️ קבעי כעת ביקור בקליניקה הפרטית ✔️ דלג לתוכן 052-4322732 03-5716996 drnadavmic@gmail.com רחוב רמב"ם 26, גבעתיים בית – פרופ' נדב משען אודות שירותי המרפאה סרטן הרחם סרטן צוואר הרחם סרטן שחלות סרטן הערייה (vulva) בדיקת פאפ בדיקת קולפוסקופיה נשאיות של BRCA קוניזציה גניקולוגיה כללית מחקר רפוא</t>
+          <t>פואה פרופסור חבר מטעם האוניברסיטה העברית האגף למיילדות וגינקולוגיה, בית החולים וולפסון, חולון רופא בכיר ומנהל שירות ביחידה להיריון בסיכון Chat Phone פרופ׳ עמיחי רוטנשטרייך מומחה למיילדות גי נ קולוגיה והיריון בסיכון גבוה prof.rottenstreich@gmail.com 055-9787751            , 055-4353787 כל הזכויות שמורות עמיחי רוטנשטרייך 2024 © bottom of page</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>"משען נדב"</t>
+          <t>"עמיחי רוטנשטרייך"</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>linked_text</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -5641,23 +5663,23 @@
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-09-04T04:19:53.405262+00:00</t>
+          <t>2026-09-04T06:21:38.973409+00:00</t>
         </is>
       </c>
       <c r="W32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
@@ -5666,11 +5688,11 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=26deea29-fa58-44cd-a7ba-96d9df718414", "https://doctors.assuta.co.il/doctor/nadav-michaan-80431?readmore=true", "https://www.dr-mishan.co.il/", "https://md-digital.co.il/", "https://www.dr-mishan.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.infomed.co.il/experts/144408/", "https://medpage.co.il/doctors/%D7%A0%D7%93%D7%91-%D7%9E%D7%A9%D7%A2%D7%9F-20445/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%A0%D7%93%D7%91-%D7%9E%D7%A9%D7%A2%D7%9F/", "https://www.danielly.co.il/doctors/view/%D7%93%D7%A8-%D7%A0%D7%93%D7%91-%D7%9E%D7%A9%D7%A2%D7%9F-%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92", "https://www.danielly.co.il/contact/index", "https://www.danielly.co.il/contact", "https://www.danielly.co.il/about", "https://www.danielly.co.il/contact?apt=1&amp;doctor_id=668"]</t>
+          <t>["https://www.prof-rottenstreich.co.il/", "https://www.prof-rottenstreich.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.prof-rottenstreich.co.il/%D7%AA%D7%97%D7%95%D7%9E%D7%99-%D7%A4%D7%A2%D7%99%D7%9C%D7%95%D7%AA"]</t>
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>4.332731805573375e+19</v>
+        <v>9.756151294304942e+19</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5681,7 +5703,7 @@
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>https://www.dr-mishan.co.il/</t>
+          <t>https://www.prof-rottenstreich.co.il/</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr"/>
@@ -5722,12 +5744,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>רחל דהן</t>
+          <t>ערן ברזילי</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>family_doctor</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -5753,7 +5775,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>racheldahan@hotmail.com</t>
+          <t>prof.eran.barzilay@gmail.com</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -5766,7 +5788,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://www.hebpsy.net/showprofile.asp?id=18767</t>
+          <t>https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -5776,12 +5798,12 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>שית בהיפנוזה יועצת גמילה מעישון טיפול בהפרעות שינה, ושינוי הרגלי חיים. רכזת מחקר המחלקה לרפואת משפחה -חיפה מנהלת מרפאת לב הקריה, שירותי בריאות כללית, קרית אתא. טל: 0543130956 אתר אינטרנט http://hypnosis.99k.org ;      : racheldahan@hotmail.com "דוא"ל הפרטים המובאים בכרטיס האישי של רחל דהן, ובכללם פרטים בדבר התואר האקדמי וההכשרה המקצועית נוסחו על ידי רחל דהן ובאחריותו/ה. נצפים ביותר יומנו של עורך וידאו - עדויות מהשבעה באוקטובר / רוני אלפ</t>
+          <t>ת ה- MD-PhD היוקרתית של הפקולטה לרפואה באוניברסיטת תל אביב, בהצטיינות. עמודים דף הבית אודות אולטרסאונד בהריון ממצאים לא תקינים אולטרסאונד גניקולוגי צור קשר צור קשר ברודצקי 43, כניסה ב', רמת אביב, תל אביב יפו 073-7815218 prof.eran.barzilay@gmail.com פרופ' ערן ברזילי באינפומד © כל הזכויות שמורות לאינפומד בע"מ פרטיות המבקרים באתר חשובה לנו כדי לשפר את חוויית הגלישה, אתר זה משתמש בקבצי עוגיות  (Cookies), המשך גלישה באתר מהווה הסכמתך לכך. מד</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>"רחל דהן" רפואת משפחה</t>
+          <t>"ערן ברזילי"</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -5798,16 +5820,16 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-09-10T13:53:25.006579+00:00</t>
+          <t>2026-09-04T06:36:53.022308+00:00</t>
         </is>
       </c>
       <c r="W33" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -5816,7 +5838,7 @@
         <v>4</v>
       </c>
       <c r="Z33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA33" t="n">
         <v>1</v>
@@ -5828,42 +5850,34 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>["https://www.doctorita.co.il/experts/141424", "https://www.colbonews.co.il/health/166678/", "https://www.hebpsy.net/showprofile.asp?id=18767", "https://www.hebpsy.net/me.asp?id=72&amp;page=6", "https://www.hebpsy.net/pl.asp?cat=about", "https://www.hebpsy.net/me.asp?id=72", "https://www.hebpsy.net/sysMsg.asp?id=profile_about#p10", "https://www.hebpsy.net/sysMsg.asp?id=profile_about", "https://www.hebpsy.net/showprofile.asp?id=18767#profile", "https://www.hebpsy.net/me.asp?id=72&amp;page=6#contact", "https://www.hebpsy.net/sysMsg.asp?id=profile_promotPL", "https://www.hebpsy.net/me.asp?id=72#contact", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fraceldahan%2F", "https://www.facebook.com/public/%D7%A8%D7%97%D7%9C-%D7%93%D7%94%D7%9F/", "https://www.myheritage.com/names/%D7%A8%D7%97%D7%9C_%D7%93%D7%94%D7%9F", "https://gen.rlzm.co.il/persons/%D7%A8%D7%97%D7%9C-%D7%93%D7%94%D7%9F/"]</t>
+          <t>["https://www.instagram.com/proferanbarzilay/", "https://www.bgu.ac.il/people/barzilae/", "https://www.bgu.ac.il/en/people/barzilae/", "https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://dr-barzilay.com/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/"]</t>
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>3.243197623337809e+19</v>
+        <v>9.756151294304942e+19</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
       </c>
       <c r="AF33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>https://www.hebpsy.net/showprofile.asp?id=18767</t>
+          <t>https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr"/>
       <c r="AJ33" t="inlineStr"/>
       <c r="AK33" t="inlineStr"/>
-      <c r="AL33" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AN33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>רחל דהן - רופאה רחל דהן - רופאה דלג לתוכן ראשי - מקש קיצור 2 (לחץ Enter) דף הבית - מקש קיצור 1 (לחץ Enter) דלג לתפריט ראשי - מקש קיצור 5 (לחץ Enter) דלג לתיבת חיפוש - מקש קיצור 4 (לחץ Enter) צור קשר - מקש קיצור 9 (לחץ Enter) הצהרת נגישות - מקש קיצור 0 (לחץ Enter) סגור עזרה ראשונה נפשית - בהתנדבות אודות והצטרפות טיפול נפשי מוזל טיפול נפשי בתל אביב מטפלים בהסדר קופת חולים פנויים לקבלת מטופלים חדשים טיפול זוגי טיפול התנהגותי קוגניטיבי - CBT הדרכת הורים טיפול נפשי לילדים אבחון פסיכולוגי לילדים פסיכולוגית בתל אביב פסיכולוגים כניסה רישום צרו קשר חיפוש × × אימייל (דוא"ל) סיסמא שכחת את הסיסמה? הקלידו אימייל ולחצו כאן כניסה אני מסכימ.ה להצטרף לרשימת התפוצה לקבלת עדכונים ומידע שיווקי זכור אותי רישום משתמש חדש ביטול פסיכולוגיה עברית ראשי השער שלי תיבת מסרים כרטיס הביקור שלי הגדרות חשבון אודות פסיכולוגיה עברית שאלות נפוצות יציאה מאמרים המאמרים שלי הגשת טקסט לפרסום נבחרי העורכת אספרגר טיפולי המרה סקס טוב דיו רגשות חינוך מיני תסמונת טורט ניכור הורי רשימות קריאה הכותבים קטגוריות מאמרים מאמרים לפי נושאים ניוזלטר בלוג</t>
-        </is>
-      </c>
-      <c r="AP33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ33" t="inlineStr"/>
       <c r="AR33" t="n">
         <v>1</v>
@@ -5892,7 +5906,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>אוהד חורי</t>
+          <t>פרופ' משען נדב</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5912,18 +5926,18 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=26deea29-fa58-44cd-a7ba-96d9df718414</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>ima</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>ohadho@clalit.org.il</t>
+          <t>drnadavmic@gmail.com</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -5932,11 +5946,11 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
+          <t>https://www.dr-mishan.co.il/</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -5946,17 +5960,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
+          <t>פרופ' נדב משען ✅️ קבעי כעת ביקור בקליניקה הפרטית ✔️ דלג לתוכן 052-4322732 03-5716996 drnadavmic@gmail.com רחוב רמב"ם 26, גבעתיים בית – פרופ' נדב משען אודות שירותי המרפאה סרטן הרחם סרטן צוואר הרחם סרטן שחלות סרטן הערייה (vulva) בדיקת פאפ בדיקת קולפוסקופיה נשאיות של BRCA קוניזציה גניקולוגיה כללית מחקר רפוא</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>"אוהד חורי" יילוד site:clalit.co.il</t>
+          <t>"משען נדב"</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>search_snippet</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -5973,36 +5987,36 @@
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-09-09T23:21:42.073181+00:00</t>
+          <t>2026-09-04T04:19:53.405262+00:00</t>
         </is>
       </c>
       <c r="W34" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z34" t="n">
         <v>5</v>
       </c>
       <c r="AA34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>ddgs:yahoo+ddgs:bing</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx", "https://www.doctorita.co.il/experts/94233", "https://www.ha-makom.co.il/author/vhdcvry/", "https://foody.co.il/author/ohad/", "https://knowmore.co.il/doctors/אוהד-חורי-2/", "https://stage.ha-makom.co.il/author/vhdcvry/", "https://www.facebook.com/YoldotBeilinson/videos/%D7%9E%D7%94-%D7%96%D7%95-%D7%9C%D7%99%D7%93%D7%AA-vbac-%D7%A9%D7%9B%D7%95%D7%9C%D7%9F-%D7%9E%D7%93%D7%91%D7%A8%D7%95%D7%AA-%D7%A2%D7%9C%D7%99%D7%94-%D7%A2%D7%95%D7%A9%D7%99%D7%9D-%D7%9C%D7%9B%D7%9F-%D7%A1%D7%93%D7%A8-%D7%91%D7%9E%D7%95%D7%A9%D7%92%D7%99%D7%9D-%D7%A2%D7%9D-%D7%93%D7%A8-%D7%90%D7%95%D7%94%D7%93-%D7%97%D7%95%D7%A8%D7%99-%D7%A9%D7%9B%D7%90%D7%9F-%D7%9B%D7%93%D7%99/1754039901764363/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=26deea29-fa58-44cd-a7ba-96d9df718414", "https://doctors.assuta.co.il/doctor/nadav-michaan-80431?readmore=true", "https://www.dr-mishan.co.il/", "https://md-digital.co.il/", "https://www.dr-mishan.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.infomed.co.il/experts/144408/", "https://medpage.co.il/doctors/%D7%A0%D7%93%D7%91-%D7%9E%D7%A9%D7%A2%D7%9F-20445/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%A0%D7%93%D7%91-%D7%9E%D7%A9%D7%A2%D7%9F/", "https://www.danielly.co.il/doctors/view/%D7%93%D7%A8-%D7%A0%D7%93%D7%91-%D7%9E%D7%A9%D7%A2%D7%9F-%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92", "https://www.danielly.co.il/contact/index", "https://www.danielly.co.il/contact", "https://www.danielly.co.il/about", "https://www.danielly.co.il/contact?apt=1&amp;doctor_id=668"]</t>
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>3.513367966872413e+19</v>
+        <v>1.299819541672012e+20</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -6013,27 +6027,19 @@
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
+          <t>https://www.dr-mishan.co.il/</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr"/>
       <c r="AJ34" t="inlineStr"/>
       <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AN34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
-        </is>
-      </c>
-      <c r="AP34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ34" t="inlineStr"/>
       <c r="AR34" t="n">
         <v>1</v>
@@ -6062,12 +6068,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>אופיר אלמסי</t>
+          <t>רחל דהן</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -6093,7 +6099,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>ofiral@bgu.ac.il</t>
+          <t>racheldahan@hotmail.com</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -6102,11 +6108,11 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
+          <t>https://www.hebpsy.net/showprofile.asp?id=18767</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -6116,12 +6122,12 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>بحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان אופיר אלמסי ד"ר אופיר אלמסי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ofiral@bgu.ac.il Cookies Settings</t>
+          <t>שית בהיפנוזה יועצת גמילה מעישון טיפול בהפרעות שינה, ושינוי הרגלי חיים. רכזת מחקר המחלקה לרפואת משפחה -חיפה מנהלת מרפאת לב הקריה, שירותי בריאות כללית, קרית אתא. טל: 0543130956 אתר אינטרנט http://hypnosis.99k.org ;      : racheldahan@hotmail.com "דוא"ל הפרטים המובאים בכרטיס האישי של רחל דהן, ובכללם פרטים בדבר התואר האקדמי וההכשרה המקצועית נוסחו על ידי רחל דהן ובאחריותו/ה. נצפים ביותר יומנו של עורך וידאו - עדויות מהשבעה באוקטובר / רוני אלפ</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>"אופיר אלמסי"</t>
+          <t>"רחל דהן" רפואת משפחה</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -6138,64 +6144,72 @@
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-09-04T13:52:28.665114+00:00</t>
+          <t>2026-09-10T13:53:25.006579+00:00</t>
         </is>
       </c>
       <c r="W35" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA35" t="n">
         <v>1</v>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/ofiral/", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/almasi-o.aspx", "https://www.bgu.ac.il/ar/people/ofiral/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.doctorita.co.il/experts/141424", "https://www.colbonews.co.il/health/166678/", "https://www.hebpsy.net/showprofile.asp?id=18767", "https://www.hebpsy.net/me.asp?id=72&amp;page=6", "https://www.hebpsy.net/pl.asp?cat=about", "https://www.hebpsy.net/me.asp?id=72", "https://www.hebpsy.net/sysMsg.asp?id=profile_about#p10", "https://www.hebpsy.net/sysMsg.asp?id=profile_about", "https://www.hebpsy.net/showprofile.asp?id=18767#profile", "https://www.hebpsy.net/me.asp?id=72&amp;page=6#contact", "https://www.hebpsy.net/sysMsg.asp?id=profile_promotPL", "https://www.hebpsy.net/me.asp?id=72#contact", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fraceldahan%2F", "https://www.facebook.com/public/%D7%A8%D7%97%D7%9C-%D7%93%D7%94%D7%9F/", "https://www.myheritage.com/names/%D7%A8%D7%97%D7%9C_%D7%93%D7%94%D7%9F", "https://gen.rlzm.co.il/persons/%D7%A8%D7%97%D7%9C-%D7%93%D7%94%D7%9F/"]</t>
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>3.51332627806309e+19</v>
+        <v>9.729592870013428e+19</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
+          <t>https://www.hebpsy.net/showprofile.asp?id=18767</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr"/>
       <c r="AJ35" t="inlineStr"/>
       <c r="AK35" t="inlineStr"/>
-      <c r="AL35" t="inlineStr"/>
-      <c r="AM35" t="inlineStr"/>
-      <c r="AN35" t="inlineStr"/>
-      <c r="AO35" t="inlineStr"/>
-      <c r="AP35" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL35" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>רחל דהן - רופאה רחל דהן - רופאה דלג לתוכן ראשי - מקש קיצור 2 (לחץ Enter) דף הבית - מקש קיצור 1 (לחץ Enter) דלג לתפריט ראשי - מקש קיצור 5 (לחץ Enter) דלג לתיבת חיפוש - מקש קיצור 4 (לחץ Enter) צור קשר - מקש קיצור 9 (לחץ Enter) הצהרת נגישות - מקש קיצור 0 (לחץ Enter) סגור עזרה ראשונה נפשית - בהתנדבות אודות והצטרפות טיפול נפשי מוזל טיפול נפשי בתל אביב מטפלים בהסדר קופת חולים פנויים לקבלת מטופלים חדשים טיפול זוגי טיפול התנהגותי קוגניטיבי - CBT הדרכת הורים טיפול נפשי לילדים אבחון פסיכולוגי לילדים פסיכולוגית בתל אביב פסיכולוגים כניסה רישום צרו קשר חיפוש × × אימייל (דוא"ל) סיסמא שכחת את הסיסמה? הקלידו אימייל ולחצו כאן כניסה אני מסכימ.ה להצטרף לרשימת התפוצה לקבלת עדכונים ומידע שיווקי זכור אותי רישום משתמש חדש ביטול פסיכולוגיה עברית ראשי השער שלי תיבת מסרים כרטיס הביקור שלי הגדרות חשבון אודות פסיכולוגיה עברית שאלות נפוצות יציאה מאמרים המאמרים שלי הגשת טקסט לפרסום נבחרי העורכת אספרגר טיפולי המרה סקס טוב דיו רגשות חינוך מיני תסמונת טורט ניכור הורי רשימות קריאה הכותבים קטגוריות מאמרים מאמרים לפי נושאים ניוזלטר בלוג</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr"/>
       <c r="AQ35" t="inlineStr"/>
       <c r="AR35" t="n">
         <v>1</v>
@@ -6224,12 +6238,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>אורנה רייכמן</t>
+          <t>שירי רון ברצ'ילון</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -6255,7 +6269,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>oreich@szmc.org.il</t>
+          <t>dr.shiribarchilon@gmail.com</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -6264,11 +6278,11 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
+          <t>https://dr-shiribarchilon.co.il/</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -6278,12 +6292,13 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t xml:space="preserve">אזור אישי רופאים בשערי צדק ד"ר אורנה  רייכמן מנהלת יולדות א' Dr. Orna  Reichman התמחות: גינקולוגיה ויילוד תת התמחות: מחלות שפירות של העריה והלדן הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית משרד 02-6666708 משרד: 02-6666708 oreich@szmc.org.il oreich@szmc.org.il לימודים והכשרה תואר ראשון במדעי החיים באוניברסיטה העברית בירושלים בהצטיינות - 1993 לימודי הרפואה בבית ספר לרפואה של האוניברסיטה העברית הדסה - 1999 ההתמחות במיילדות וגניקולוגיה במרכז </t>
+          <t>לינט, חוג באלינט ישראל. ביקורי הבית מאפשרים הערכה גריאטרית מקיפה בסביבתו הטבעית של המטופל,
+                        ובתנאים הנוחים לו. המפגשים נעשים ברגישות, אמפתיה ומקצועיות. אין כמו בבית. איזור השרון והמרכז 050-8334003 dr.shiribarchilon@gmail.com ד"ר שירי רון ברצ'ילון מומחית ברפואה גריאטרית אם חיפשתם את ד״ר ברצ׳ילון, אורתופד מנתח - לחצו כאן עיצוב-יאיר דיגיטל</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>"אורנה רייכמן"</t>
+          <t>"שירי רון ברצ ילון" רפואת משפחה</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -6300,64 +6315,73 @@
         <v>1</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-09-04T13:56:16.031154+00:00</t>
+          <t>2026-09-11T18:42:01.466130+00:00</t>
         </is>
       </c>
       <c r="W36" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z36" t="n">
         <v>5</v>
       </c>
       <c r="AA36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>["https://www.infomed.co.il/experts/149541/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A8%D7%99%D7%99%D7%9B%D7%9E%D7%9F-%D7%90%D7%95%D7%A8%D7%A0%D7%94/", "https://docsrated.com/doctors/אורנה-רייכמן", "https://www.doctorita.co.il/experts/95406", "https://drtor.co.il/doctor/23937", "https://drtor.co.il/cdn-cgi/l/email-protection#8cefe3e2f8edeff8cce8fef8e3fea2efe3a2e5e0", "https://www.beok.co.il/doctors/Doctors-1340/", "https://www.szmc.org.il/doctors/reichman-orna/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://drtor.co.il/cdn-cgi/l/email-protection#3b5854554f5a584f7b5f494f5449155854155257"]</t>
+          <t>["https://doctorindex.co.il/דוקטור-רון-ברצילון-שירי/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A8%D7%95%D7%9F-%D7%91%D7%A8%D7%A6%D7%99%D7%9C%D7%95%D7%9F-%D7%A9%D7%99%D7%A8%D7%99/", "https://dr-shiribarchilon.co.il/", "https://dr-shiribarchilon.co.il/#odot", "https://medpage.co.il/doctors/%D7%A9%D7%99%D7%A8%D7%99-%D7%A8%D7%95%D7%9F-%D7%91%D7%A8%D7%A6%D7%99%D7%9C%D7%95%D7%9F-17881/", "https://www.medreviews.co.il/provider/dr-ron-barchilon-shiri/page/2", "https://www.medreviews.co.il/provider/dr-ron-barchilon-shiri/treatment"]</t>
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>3.51332627806309e+19</v>
+        <v>9.729592870009283e+19</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
+          <t>https://dr-shiribarchilon.co.il/</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr"/>
       <c r="AJ36" t="inlineStr"/>
       <c r="AK36" t="inlineStr"/>
-      <c r="AL36" t="inlineStr"/>
-      <c r="AM36" t="inlineStr"/>
-      <c r="AN36" t="inlineStr"/>
-      <c r="AO36" t="inlineStr"/>
-      <c r="AP36" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL36" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>ד”ר שירי רון ברצ'ילון ד”ר שירי רון ברצ'ילון ד"ר שירי רון ברצ'ילון רופאה מומחית בגריאטריה אודות אין כמו בבית הערכה גריאטרית בבית המטופל יצירת קשר יצירת קשר הערכה תפקודית הערכה קוגניטיבית איזון נפשי סידור תרופות ירידה בזכרון ודמנציה כשירות לייפוי כח וצוואה ד"ר שירי רון ברצ'ילון מומחית ברפואה גריאטרית מנהלת יחידת הייעוץ הגריאטרי בבית החולים לניאדו. מומחית ברפואת המשפחה ורפואה גריאטרית. תואר MD מבית הספר לרפואה של אוניברסיטת תל-אביב משנת 2000. מנחת קבוצות, בוגרת התכנית להכשרת מנחי קבוצות, אוניברסיטת בר אילן. מרצה בבית הספר לרפואה, אוניברסיטת תל-אביב. מדריכת באלינט, חוג באלינט ישראל. ביקורי הבית מאפשרים הערכה גריאטרית מקיפה בסביבתו הטבעית של המטופל,
+                        ובתנאים הנוחים לו. המפגשים נעשים ברגישות, אמפתיה ומקצועיות. אין כמו בבית. איזור השרון והמרכז 050-8334003 dr.shiribarchilon@gmail.com ד"ר שירי רון ברצ'ילון מומחית ברפואה גריאטרית אם חיפשתם את ד״ר ברצ׳ילון, אורתופד מנתח - לחצו כאן עיצוב-יאיר דיגיטל</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr"/>
       <c r="AQ36" t="inlineStr"/>
       <c r="AR36" t="n">
         <v>1</v>
@@ -6386,7 +6410,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ארנון סמואלוב</t>
+          <t>אוהד חורי</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6417,7 +6441,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>smuelof@szmc.org.il</t>
+          <t>ohadho@clalit.org.il</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -6430,7 +6454,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -6440,17 +6464,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>ופ' ארנון  סמואלוב רופא בכיר Prof. Arnon  Samueloff התמחות: גינקולוגיה ויילוד תת התמחות: מיילדות וסיבוכי הריון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 02-6666656 מחלקה: 02-6666656 smuelof@szmc.org.il smuelof@szmc.org.il נסיון מקצועי התמחות ברפואת האם והעובר, סן אנטוניו, ארה"ב רופא בכיר, מחלקת נשים ויולדות, המרכז הרפואי הדסה מנהל, מרפאת היריון בסיכון, קופת חולים לאומית מנהל, מרפאת סוכרת, קופת חולים</t>
+          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>"ארנון סמואלוב"</t>
+          <t>"אוהד חורי" יילוד site:clalit.co.il</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -6467,36 +6491,36 @@
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-09-04T14:35:26.198949+00:00</t>
+          <t>2026-09-09T23:21:42.073181+00:00</t>
         </is>
       </c>
       <c r="W37" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA37" t="n">
         <v>2</v>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>["https://docsrated.com/doctors/ארנון-סמואלוב", "https://www.infomed.co.il/experts/93587/", "https://www.doctorita.co.il/experts/47319", "https://www.beok.co.il/doctors/Doctors-116451/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A1%D7%9E%D7%95%D7%90%D7%9C%D7%95%D7%91-%D7%90%D7%A8%D7%A0%D7%95%D7%9F/", "https://www.szmc.org.il/doctors/samueloff-arnon/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
+          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx", "https://www.doctorita.co.il/experts/94233", "https://www.ha-makom.co.il/author/vhdcvry/", "https://foody.co.il/author/ohad/", "https://knowmore.co.il/doctors/אוהד-חורי-2/", "https://stage.ha-makom.co.il/author/vhdcvry/", "https://www.facebook.com/YoldotBeilinson/videos/%D7%9E%D7%94-%D7%96%D7%95-%D7%9C%D7%99%D7%93%D7%AA-vbac-%D7%A9%D7%9B%D7%95%D7%9C%D7%9F-%D7%9E%D7%93%D7%91%D7%A8%D7%95%D7%AA-%D7%A2%D7%9C%D7%99%D7%94-%D7%A2%D7%95%D7%A9%D7%99%D7%9D-%D7%9C%D7%9B%D7%9F-%D7%A1%D7%93%D7%A8-%D7%91%D7%9E%D7%95%D7%A9%D7%92%D7%99%D7%9D-%D7%A2%D7%9D-%D7%93%D7%A8-%D7%90%D7%95%D7%94%D7%93-%D7%97%D7%95%D7%A8%D7%99-%D7%A9%D7%9B%D7%90%D7%9F-%D7%9B%D7%93%D7%99/1754039901764363/"]</t>
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>3.51332627806309e+19</v>
+        <v>1.054010390061724e+20</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6507,19 +6531,27 @@
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr"/>
       <c r="AJ37" t="inlineStr"/>
       <c r="AK37" t="inlineStr"/>
-      <c r="AL37" t="inlineStr"/>
-      <c r="AM37" t="inlineStr"/>
-      <c r="AN37" t="inlineStr"/>
-      <c r="AO37" t="inlineStr"/>
-      <c r="AP37" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL37" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr"/>
       <c r="AQ37" t="inlineStr"/>
       <c r="AR37" t="n">
         <v>1</v>
@@ -6548,7 +6580,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>גלי פריאנטה</t>
+          <t>אופיר אלמסי</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6579,7 +6611,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>galipa@bgu.ac.il</t>
+          <t>ofiral@bgu.ac.il</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -6592,7 +6624,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
+          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -6602,12 +6634,12 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>ث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان גלי פריאנטה פרופ' גלי פריאנטה Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section galipa@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0001-6484-3769 Orcid Number Cookies Settings</t>
+          <t>بحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان אופיר אלמסי ד"ר אופיר אלמסי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ofiral@bgu.ac.il Cookies Settings</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>"גלי פריאנטה"</t>
+          <t>"אופיר אלמסי"</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -6629,36 +6661,36 @@
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-09-03T23:09:10.396904+00:00</t>
+          <t>2026-09-04T13:52:28.665114+00:00</t>
         </is>
       </c>
       <c r="W38" t="n">
         <v>2</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y38" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z38" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AA38" t="n">
         <v>1</v>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/galipa/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-%D7%92%D7%9C%D7%99/", "https://medpage.co.il/doctors/%D7%92%D7%9C%D7%99-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-25448/", "https://www.doctorita.co.il/experts/131973", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/pariente-g.aspx", "https://www.bgu.ac.il/ar/people/galipa/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.bgu.ac.il/people/ofiral/", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/almasi-o.aspx", "https://www.bgu.ac.il/ar/people/ofiral/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>3.51221446594978e+19</v>
+        <v>1.053997883418927e+20</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6669,7 +6701,7 @@
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
+          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr"/>
@@ -6710,7 +6742,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ד"ר ברוך יואב</t>
+          <t>אורנה רייכמן</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6730,18 +6762,18 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>ima</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>yoavb@tlvmc.gov.il</t>
+          <t>oreich@szmc.org.il</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -6754,7 +6786,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
+          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -6764,12 +6796,12 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>י לאורוגינקולוגיה ורצפת אגן שטחי התעניינות ועיסוק מיוחדים ניתוחים וגינאליים וזעיר פולשניים לצניחת אברי האגן טיפול תרופתי וכירורגי לדליפת שתן מרפאת ערייה וצוואר הרחם אבחון וטיפול בקונדילומות ונגעים טרום ממאירים יצירת קשר yoavb@tlvmc.gov.il יחידות רפואיות אורוגינקולוגיה ורצפת האגן רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות נעים להכיר, ​ד"ר יואב ברוך איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציונ</t>
+          <t xml:space="preserve">אזור אישי רופאים בשערי צדק ד"ר אורנה  רייכמן מנהלת יולדות א' Dr. Orna  Reichman התמחות: גינקולוגיה ויילוד תת התמחות: מחלות שפירות של העריה והלדן הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית משרד 02-6666708 משרד: 02-6666708 oreich@szmc.org.il oreich@szmc.org.il לימודים והכשרה תואר ראשון במדעי החיים באוניברסיטה העברית בירושלים בהצטיינות - 1993 לימודי הרפואה בבית ספר לרפואה של האוניברסיטה העברית הדסה - 1999 ההתמחות במיילדות וגניקולוגיה במרכז </t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>"ברוך יואב"</t>
+          <t>"אורנה רייכמן"</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -6786,28 +6818,28 @@
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-09-05T00:14:33.719515+00:00</t>
+          <t>2026-09-04T13:56:16.031154+00:00</t>
         </is>
       </c>
       <c r="W39" t="n">
         <v>2</v>
       </c>
       <c r="X39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
@@ -6816,11 +6848,11 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345", "https://soundcloud.com/wx8fnfybplpt", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A-%D7%91%D7%A8%D7%95%D7%9A/pfbid02DHSfATmK3MDpizZrgGTLc9ZAvZHXUsR9pSCjhd6pmWqSMFvq1BwehNeHCARNitMol/", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/pfbid02BMPnQXQYXt6vzctmybagMUp3nWACPxhE1LqhYeJYs1fVgXWA6B1cK2Z9VpRJ8cJRl/", "https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/", "https://pubmed.ncbi.nlm.nih.gov/?term=yoav+baruch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000546", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/61559143005435/", "https://www.infomed.co.il/experts/151203/", "https://www.yoavbaruch.com/", "https://www.yoavbaruch.com/about-6", "https://theindex.co.il/phone/ברוך-יואב-0777573393/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000504"]</t>
+          <t>["https://www.infomed.co.il/experts/149541/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A8%D7%99%D7%99%D7%9B%D7%9E%D7%9F-%D7%90%D7%95%D7%A8%D7%A0%D7%94/", "https://docsrated.com/doctors/אורנה-רייכמן", "https://www.doctorita.co.il/experts/95406", "https://drtor.co.il/doctor/23937", "https://drtor.co.il/cdn-cgi/l/email-protection#8cefe3e2f8edeff8cce8fef8e3fea2efe3a2e5e0", "https://www.beok.co.il/doctors/Doctors-1340/", "https://www.szmc.org.il/doctors/reichman-orna/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://drtor.co.il/cdn-cgi/l/email-protection#3b5854554f5a584f7b5f494f5449155854155257"]</t>
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>4.056384728075937e+19</v>
+        <v>1.053997883418927e+20</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6831,7 +6863,7 @@
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
+          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr"/>
@@ -6872,7 +6904,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ד"ר צוקר נפתלי</t>
+          <t>ארנון סמואלוב</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6892,18 +6924,18 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>ima</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>drnzuker@arad-medical.co.il</t>
+          <t>smuelof@szmc.org.il</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -6916,7 +6948,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://www.arad-medical.co.il/</t>
+          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -6926,12 +6958,12 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t xml:space="preserve"> בי"ח אסף הרופא, עבר השתלמות מעמיקה בכירורגיה גניקולוגית ואנדסקופית. כמוכן, גניקולוג בכיר בקופות החולים מכבי ולאומית. קרא עוד עלינו « לפרטים נוספים ולקביעת תור השאר פרטים ונחזור אליך בהקדם! ☎ 077-8037837 | 077-9966036 ✉ drnzuker@arad-medical.co.il שם מלא: מייל: טלפון: שלח © ד"ר נפתלי צוקר — כל הזכויות שמורות אתר זה נבנה ועוצב ע"י קידום פלוס - בניית אתרים</t>
+          <t>ופ' ארנון  סמואלוב רופא בכיר Prof. Arnon  Samueloff התמחות: גינקולוגיה ויילוד תת התמחות: מיילדות וסיבוכי הריון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 02-6666656 מחלקה: 02-6666656 smuelof@szmc.org.il smuelof@szmc.org.il נסיון מקצועי התמחות ברפואת האם והעובר, סן אנטוניו, ארה"ב רופא בכיר, מחלקת נשים ויולדות, המרכז הרפואי הדסה מנהל, מרפאת היריון בסיכון, קופת חולים לאומית מנהל, מרפאת סוכרת, קופת חולים</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>"צוקר נפתלי"</t>
+          <t>"ארנון סמואלוב"</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -6953,36 +6985,36 @@
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-09-03T20:26:24.789692+00:00</t>
+          <t>2026-09-04T14:35:26.198949+00:00</t>
         </is>
       </c>
       <c r="W40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X40" t="n">
         <v>1</v>
       </c>
       <c r="Y40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z40" t="n">
         <v>4</v>
       </c>
       <c r="AA40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=JM/xPUEkhEzRgBuX3T9AYqhAJkFmVBaeb30sdIDAjgJqc6t/hlXwF9+305eagC9MR2dwestiB5JmwYwMLOCteQ==", "https://doctors.assuta.co.il/doctor/naftaly-zuker-15805", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=AsbND281GonWNafC65Z5in+5Uof0vMwxuFwCtAAhKp6HNUz+Imt4aFWEpjB1dVuW0TI9YD98xqlKyretPdEuvw==", "https://www.arad-medical.co.il/", "http://www.kidumplus.co.il/", "https://www.arad-medical.co.il/contact", "https://www.arad-medical.co.il/about-us", "https://www.doctorim.co.il/s/doctor-21560/דר-נפתלי-צוקר/מומחה-יילוד-וגניקולוגיה", "https://www.infomed.co.il/experts/83793/"]</t>
+          <t>["https://docsrated.com/doctors/ארנון-סמואלוב", "https://www.infomed.co.il/experts/93587/", "https://www.doctorita.co.il/experts/47319", "https://www.beok.co.il/doctors/Doctors-116451/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A1%D7%9E%D7%95%D7%90%D7%9C%D7%95%D7%91-%D7%90%D7%A8%D7%A0%D7%95%D7%9F/", "https://www.szmc.org.il/doctors/samueloff-arnon/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>4.322725496553574e+19</v>
+        <v>1.053997883418927e+20</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6993,7 +7025,7 @@
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>https://www.arad-medical.co.il/</t>
+          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr"/>
@@ -7034,7 +7066,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ד"ר רטן גלעד</t>
+          <t>גלי פריאנטה</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -7054,18 +7086,18 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>ima</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>giladr@tlvmc.gov.il</t>
+          <t>galipa@bgu.ac.il</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -7078,7 +7110,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
+          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -7088,12 +7120,12 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t xml:space="preserve">ח "ליס" ליולדות ונשים איכילוב צוות איכילוב גלעד רטן בדיקת היסטרוסקופיה - ד"ר גלעד רטן | ליס, איכילוב ד"ר גלעד רטן על תסמונת אשרמן, סטטוסקופ ערוץ 13 פרק 18 | פרופ' יריב יוגב ופרופ' גלעד רטן | בדיקת היסטרוסקופיה יצירת קשר giladr@tlvmc.gov.il יחידות רפואיות היסטרוסקופיה אבחנתית / טיפולית רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א </t>
+          <t>ث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان גלי פריאנטה פרופ' גלי פריאנטה Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section galipa@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0001-6484-3769 Orcid Number Cookies Settings</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>"רטן גלעד"</t>
+          <t>"גלי פריאנטה"</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -7115,7 +7147,7 @@
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-09-03T21:08:14.761438+00:00</t>
+          <t>2026-09-03T23:09:10.396904+00:00</t>
         </is>
       </c>
       <c r="W41" t="n">
@@ -7125,10 +7157,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA41" t="n">
         <v>1</v>
@@ -7140,11 +7172,11 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F/", "https://dr-gilad.infomed.co.il/", "https://www.facebook.com/TLVMDC/posts/%D7%95%D7%95%D7%90%D7%95-%D7%9E%D7%AA%D7%A8%D7%92%D7%A9%D7%99%D7%9D-%D7%9C%D7%94%D7%9B%D7%99%D7%A8-%D7%9C%D7%9B%D7%9D-%D7%90%D7%AA-%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F-%D7%9E%D7%95%D7%9E%D7%97%D7%94-%D7%91%D7%9B%D7%99%D7%A8-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%A8%D7%A4%D7%95%D7%90%D7%99-tlv_medical_center/1344912312574270/", "https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.bgu.ac.il/people/galipa/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-%D7%92%D7%9C%D7%99/", "https://medpage.co.il/doctors/%D7%92%D7%9C%D7%99-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-25448/", "https://www.doctorita.co.il/experts/131973", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/pariente-g.aspx", "https://www.bgu.ac.il/ar/people/galipa/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>3.51221446594978e+19</v>
+        <v>1.053664339784934e+20</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7155,7 +7187,7 @@
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
+          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr"/>
@@ -7196,7 +7228,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>דנה ברבינג-גולדשטיין</t>
+          <t>ד"ר ברוך יואב</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7216,18 +7248,18 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>ima</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>danabr2@clalit.org.il</t>
+          <t>yoavb@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -7240,7 +7272,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -7250,17 +7282,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>ד"ר דנה ברבינג גולדשטיין | מרכז רפואי רבין ד"ר דנה ברבינג גולדשטיין מיילדות וגינקולוגיה, גנטיקה רפואית שם: ד"ר דנה ברבינג גולדשטיין דוא"ל: danabr2@clalit.org.il יחידה: מכון רפאל רקנאטי לגנטיקה</t>
+          <t>י לאורוגינקולוגיה ורצפת אגן שטחי התעניינות ועיסוק מיוחדים ניתוחים וגינאליים וזעיר פולשניים לצניחת אברי האגן טיפול תרופתי וכירורגי לדליפת שתן מרפאת ערייה וצוואר הרחם אבחון וטיפול בקונדילומות ונגעים טרום ממאירים יצירת קשר yoavb@tlvmc.gov.il יחידות רפואיות אורוגינקולוגיה ורצפת האגן רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות נעים להכיר, ​ד"ר יואב ברוך איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציונ</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>"דנה ברבינג גולדשטיין" יילוד site:clalit.co.il</t>
+          <t>"ברוך יואב"</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>search_snippet</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -7272,41 +7304,41 @@
         <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-09-08T13:48:01.035843+00:00</t>
+          <t>2026-09-05T00:14:33.719515+00:00</t>
         </is>
       </c>
       <c r="W42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X42" t="n">
         <v>1</v>
       </c>
       <c r="Y42" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA42" t="n">
         <v>1</v>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>ddgs:yahoo+ddgs:bing</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345", "https://soundcloud.com/wx8fnfybplpt", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A-%D7%91%D7%A8%D7%95%D7%9A/pfbid02DHSfATmK3MDpizZrgGTLc9ZAvZHXUsR9pSCjhd6pmWqSMFvq1BwehNeHCARNitMol/", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/pfbid02BMPnQXQYXt6vzctmybagMUp3nWACPxhE1LqhYeJYs1fVgXWA6B1cK2Z9VpRJ8cJRl/", "https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/", "https://pubmed.ncbi.nlm.nih.gov/?term=yoav+baruch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000546", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/61559143005435/", "https://www.infomed.co.il/experts/151203/", "https://www.yoavbaruch.com/", "https://www.yoavbaruch.com/about-6", "https://theindex.co.il/phone/ברוך-יואב-0777573393/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000504"]</t>
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>3.513367966871025e+19</v>
+        <v>1.216915418422781e+20</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7317,7 +7349,7 @@
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr"/>
@@ -7358,7 +7390,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>יעל שולמן</t>
+          <t>ד"ר צוקר נפתלי</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7378,18 +7410,18 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>ima</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>yaelshu@tlvmc.gov.il</t>
+          <t>drnzuker@arad-medical.co.il</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -7402,7 +7434,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
+          <t>https://www.arad-medical.co.il/</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -7412,12 +7444,12 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>3zgt8o8y2e /search-result/ /api/as/v1/engines/ פתח חיפוש עוד ... זימון תורים אזור אישי כניסה לאיזור האישי AI צ'אט ד"ר יעל שולמן רופאה בכירה במחלקת נשים, ביה"ח 'ליס' ליולדות ונשים איכילוב צוות איכילוב יעל שולמן יצירת קשר yaelshu@tlvmc.gov.il יחידות רפואיות אשפוז נשים - מחלקה רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך ב</t>
+          <t xml:space="preserve"> בי"ח אסף הרופא, עבר השתלמות מעמיקה בכירורגיה גניקולוגית ואנדסקופית. כמוכן, גניקולוג בכיר בקופות החולים מכבי ולאומית. קרא עוד עלינו « לפרטים נוספים ולקביעת תור השאר פרטים ונחזור אליך בהקדם! ☎ 077-8037837 | 077-9966036 ✉ drnzuker@arad-medical.co.il שם מלא: מייל: טלפון: שלח © ד"ר נפתלי צוקר — כל הזכויות שמורות אתר זה נבנה ועוצב ע"י קידום פלוס - בניית אתרים</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>"יעל שולמן"</t>
+          <t>"צוקר נפתלי"</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -7439,23 +7471,23 @@
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-09-04T17:01:07.432235+00:00</t>
+          <t>2026-09-03T20:26:24.789692+00:00</t>
         </is>
       </c>
       <c r="W43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
@@ -7464,11 +7496,11 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>["https://www.agmon-law.co.il/team-member/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/people/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/pfbid02D3uDhLBFvfdSCJScu9afsXcVu6ZWEqNA4AsJgJH4om5Y5hNBNGbDUq3Xyg3nad9hl/", "https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=JM/xPUEkhEzRgBuX3T9AYqhAJkFmVBaeb30sdIDAjgJqc6t/hlXwF9+305eagC9MR2dwestiB5JmwYwMLOCteQ==", "https://doctors.assuta.co.il/doctor/naftaly-zuker-15805", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=AsbND281GonWNafC65Z5in+5Uof0vMwxuFwCtAAhKp6HNUz+Imt4aFWEpjB1dVuW0TI9YD98xqlKyretPdEuvw==", "https://www.arad-medical.co.il/", "http://www.kidumplus.co.il/", "https://www.arad-medical.co.il/contact", "https://www.arad-medical.co.il/about-us", "https://www.doctorim.co.il/s/doctor-21560/דר-נפתלי-צוקר/מומחה-יילוד-וגניקולוגיה", "https://www.infomed.co.il/experts/83793/"]</t>
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>3.333212715706692e+19</v>
+        <v>1.296817648966072e+20</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7479,7 +7511,7 @@
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
+          <t>https://www.arad-medical.co.il/</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr"/>
@@ -7520,7 +7552,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ישי לוין</t>
+          <t>ד"ר רטן גלעד</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7540,18 +7572,18 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>ima</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>ishail@tlvmc.gov.il</t>
+          <t>giladr@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -7564,7 +7596,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -7574,12 +7606,12 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>ריוזיס כנס אונליין אנדומטריאוזיס 2025 | פרופ' יריב יוגב ופרופ' ישי לוין מניעה וגילוי מוקדם של מחלות נשים | ערוץ 10 המכון לפריון - כירורגיה של הפריון | ליס פרופ' ישי לוין על כאבי מחזור חזקים , ערוץ 13, סטטוסקופ יצירת קשר ishail@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה אשפוז נשים - מחלקה אנדומטריוזיס - מרכז רב תחומי המרכז לבריאות האשה-מרפאות מומחים הפלות חוזרות - טיפול בכשל הריוני רופאים בכירים בליס-יולדות ונשים יצירת קשר יחיד</t>
+          <t xml:space="preserve">ח "ליס" ליולדות ונשים איכילוב צוות איכילוב גלעד רטן בדיקת היסטרוסקופיה - ד"ר גלעד רטן | ליס, איכילוב ד"ר גלעד רטן על תסמונת אשרמן, סטטוסקופ ערוץ 13 פרק 18 | פרופ' יריב יוגב ופרופ' גלעד רטן | בדיקת היסטרוסקופיה יצירת קשר giladr@tlvmc.gov.il יחידות רפואיות היסטרוסקופיה אבחנתית / טיפולית רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א </t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>"ישי לוין"</t>
+          <t>"רטן גלעד"</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -7601,7 +7633,7 @@
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-09-04T17:20:48.855691+00:00</t>
+          <t>2026-09-03T21:08:14.761438+00:00</t>
         </is>
       </c>
       <c r="W44" t="n">
@@ -7611,13 +7643,13 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
@@ -7626,11 +7658,11 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>["https://www.ishai-levin.com/", "https://www.ishai-levin.com/about", "https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/", "https://pubmed.ncbi.nlm.nih.gov/?term=Levin%2c%20Ishai%5bFull%20Author%20Name%5d%20OR%20Ishai%2c%20Levin%5bFull%20Author%20Name%5d&amp;cmd=DetailsSearch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F/", "https://dr-gilad.infomed.co.il/", "https://www.facebook.com/TLVMDC/posts/%D7%95%D7%95%D7%90%D7%95-%D7%9E%D7%AA%D7%A8%D7%92%D7%A9%D7%99%D7%9D-%D7%9C%D7%94%D7%9B%D7%99%D7%A8-%D7%9C%D7%9B%D7%9D-%D7%90%D7%AA-%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F-%D7%9E%D7%95%D7%9E%D7%97%D7%94-%D7%91%D7%9B%D7%99%D7%A8-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%A8%D7%A4%D7%95%D7%90%D7%99-tlv_medical_center/1344912312574270/", "https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>3.333212715706692e+19</v>
+        <v>1.053664339784934e+20</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7641,7 +7673,7 @@
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr"/>
@@ -7682,7 +7714,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>לירן הירש</t>
+          <t>דנה ברבינג-גולדשטיין</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7713,7 +7745,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>liranh@tlvmc.gov.il</t>
+          <t>danabr2@clalit.org.il</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -7726,7 +7758,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -7736,17 +7768,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>צועיים החברה הישראלית לרפואת האם והעובר החוג הישראלי למיילדות וגינקולוגיה לידה נדירה - תאומים ברחם נפרד פרק 19 | פרופ' יריב יוגב ופרופ' לירן הירש | תאומים פרק 9 | פרופ' יריב יוגב ופרופ' לירן הירש| הריון בסיכון יצירת קשר liranh@tlvmc.gov.il יחידות רפואיות המחלקה לרפואת האם והעובר מניעת לידה מוקדמת - מרפאה מעקב הריונות תאומים רופאים בכירים בליס-יולדות ונשים היריון ולידה יצירת קשר יחידות רפואיות היריון של 1 למיליון עם פרופ' לירן הירש איכיל</t>
+          <t>ד"ר דנה ברבינג גולדשטיין | מרכז רפואי רבין ד"ר דנה ברבינג גולדשטיין מיילדות וגינקולוגיה, גנטיקה רפואית שם: ד"ר דנה ברבינג גולדשטיין דוא"ל: danabr2@clalit.org.il יחידה: מכון רפאל רקנאטי לגנטיקה</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>"לירן הירש"</t>
+          <t>"דנה ברבינג גולדשטיין" יילוד site:clalit.co.il</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -7763,36 +7795,36 @@
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-09-04T17:39:56.947224+00:00</t>
+          <t>2026-09-08T13:48:01.035843+00:00</t>
         </is>
       </c>
       <c r="W45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>["https://www.profhiersch.com/", "https://www.profhiersch.com/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/", "https://pubmed.ncbi.nlm.nih.gov/?term=HIERSCH+L&amp;sort=date", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx"]</t>
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>3.333212715706692e+19</v>
+        <v>1.054010390061307e+20</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7803,7 +7835,7 @@
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr"/>
@@ -7844,7 +7876,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>נועה גוהר פורטנוי</t>
+          <t>יעל שולמן</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7875,7 +7907,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>noago@post.bgu.ac.il</t>
+          <t>yaelshu@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -7888,7 +7920,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/noago/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -7898,12 +7930,12 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان נועה גוהר פורטנוי נועה גוהר פורטנוי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section noago@post.bgu.ac.il Cookies Settings</t>
+          <t>3zgt8o8y2e /search-result/ /api/as/v1/engines/ פתח חיפוש עוד ... זימון תורים אזור אישי כניסה לאיזור האישי AI צ'אט ד"ר יעל שולמן רופאה בכירה במחלקת נשים, ביה"ח 'ליס' ליולדות ונשים איכילוב צוות איכילוב יעל שולמן יצירת קשר yaelshu@tlvmc.gov.il יחידות רפואיות אשפוז נשים - מחלקה רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך ב</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>"נועה גוהר פורטנוי" יילוד</t>
+          <t>"יעל שולמן"</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -7925,20 +7957,20 @@
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-09-08T14:13:12.580343+00:00</t>
+          <t>2026-09-04T17:01:07.432235+00:00</t>
         </is>
       </c>
       <c r="W46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -7950,11 +7982,11 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>["https://www.doctorita.co.il/experts/126297", "https://www.bgu.ac.il/ar/people/noago/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.agmon-law.co.il/team-member/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/people/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/pfbid02D3uDhLBFvfdSCJScu9afsXcVu6ZWEqNA4AsJgJH4om5Y5hNBNGbDUq3Xyg3nad9hl/", "https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>3.252462724280651e+19</v>
+        <v>9.999638147120076e+19</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7965,7 +7997,7 @@
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/noago/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr"/>
@@ -8006,7 +8038,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>עדי יהודה ווינטראוב</t>
+          <t>ישי לוין</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -8037,7 +8069,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>adiyehud@bgu.ac.il</t>
+          <t>ishail@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -8050,7 +8082,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -8060,12 +8092,12 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>رئيسية جامعة أنشي سيجل في جوريان עדי יהודה ווינטראוב פרופ' עדי יהודה ווינטראוב Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section adiyehud@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0002-4239-8665 Orcid Number Cookies Settings</t>
+          <t>ריוזיס כנס אונליין אנדומטריאוזיס 2025 | פרופ' יריב יוגב ופרופ' ישי לוין מניעה וגילוי מוקדם של מחלות נשים | ערוץ 10 המכון לפריון - כירורגיה של הפריון | ליס פרופ' ישי לוין על כאבי מחזור חזקים , ערוץ 13, סטטוסקופ יצירת קשר ishail@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה אשפוז נשים - מחלקה אנדומטריוזיס - מרכז רב תחומי המרכז לבריאות האשה-מרפאות מומחים הפלות חוזרות - טיפול בכשל הריוני רופאים בכירים בליס-יולדות ונשים יצירת קשר יחיד</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>"עדי יהודה ווינטראוב"</t>
+          <t>"ישי לוין"</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -8082,41 +8114,41 @@
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-09-04T19:20:10.182518+00:00</t>
+          <t>2026-09-04T17:20:48.855691+00:00</t>
         </is>
       </c>
       <c r="W47" t="n">
         <v>2</v>
       </c>
       <c r="X47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/adiyehud/", "https://www.bgu.ac.il/researcher/adi-weintraub/", "https://www.beok.co.il/doctors/Doctors-136810/", "https://cris.bgu.ac.il/en/publications/%D7%94%D7%A1%D7%99%D7%9B%D7%95%D7%9F-%D7%9C%D7%A1%D7%99%D7%91%D7%95%D7%9B%D7%99-%D7%94%D7%99%D7%A8%D7%99%D7%95%D7%9F-%D7%91%D7%A0%D7%A9%D7%99%D7%9D-%D7%A2%D7%9D-%D7%90%D7%A0%D7%93%D7%95%D7%9E%D7%98%D7%A8%D7%99%D7%95%D7%96%D7%99%D7%A1/", "https://www.bgu.ac.il/ar/people/adiyehud/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.ishai-levin.com/", "https://www.ishai-levin.com/about", "https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/", "https://pubmed.ncbi.nlm.nih.gov/?term=Levin%2c%20Ishai%5bFull%20Author%20Name%5d%20OR%20Ishai%2c%20Levin%5bFull%20Author%20Name%5d&amp;cmd=DetailsSearch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>3.252421035472751e+19</v>
+        <v>9.999638147120076e+19</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -8127,7 +8159,7 @@
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr"/>
@@ -8168,7 +8200,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>עמרי זמשטין</t>
+          <t>לירן הירש</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8199,7 +8231,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>omrizam@post.bgu.ac.il</t>
+          <t>liranh@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -8212,7 +8244,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -8222,12 +8254,12 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>ريد البحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان עמרי זמשטין עמרי זמשטין Departments אקדמי לא פעיל הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section omrizam@post.bgu.ac.il Cookies Settings</t>
+          <t>צועיים החברה הישראלית לרפואת האם והעובר החוג הישראלי למיילדות וגינקולוגיה לידה נדירה - תאומים ברחם נפרד פרק 19 | פרופ' יריב יוגב ופרופ' לירן הירש | תאומים פרק 9 | פרופ' יריב יוגב ופרופ' לירן הירש| הריון בסיכון יצירת קשר liranh@tlvmc.gov.il יחידות רפואיות המחלקה לרפואת האם והעובר מניעת לידה מוקדמת - מרפאה מעקב הריונות תאומים רופאים בכירים בליס-יולדות ונשים היריון ולידה יצירת קשר יחידות רפואיות היריון של 1 למיליון עם פרופ' לירן הירש איכיל</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>"עמרי זמשטין"</t>
+          <t>"לירן הירש"</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -8244,25 +8276,25 @@
         <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-09-04T19:35:09.971397+00:00</t>
+          <t>2026-09-04T17:39:56.947224+00:00</t>
         </is>
       </c>
       <c r="W48" t="n">
         <v>2</v>
       </c>
       <c r="X48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -8274,11 +8306,11 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/ar/people/omrizam/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.profhiersch.com/", "https://www.profhiersch.com/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/", "https://pubmed.ncbi.nlm.nih.gov/?term=HIERSCH+L&amp;sort=date", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>3.252421035472751e+19</v>
+        <v>9.999638147120076e+19</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8289,7 +8321,7 @@
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr"/>
@@ -8330,7 +8362,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>רויטל לינדר</t>
+          <t>נועה גוהר פורטנוי</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8361,7 +8393,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>revital@drlinder.co.il</t>
+          <t>noago@post.bgu.ac.il</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -8374,7 +8406,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://www.drlinder.co.il/</t>
+          <t>https://www.bgu.ac.il/ar/people/noago/</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -8384,12 +8416,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>בכירה ביחידה הגניקואונקולוגית , בית חולים רמב״ם, חיפה. 4/2014-4/2019 התמחות במיילדות וגניקולוגיה בית חולים רמב״ם,חיפה. לפרטים מלאים חוות דעת יש לך שאלה ? צרי קשר ד״ר רויטל לינדר צפצפה 2 (ישי סנטר) , רמת ישי 058-6918927​ revital@drlinder.co.il הצהרת נגישות © DR. Revital Linder. All rights Reserved , 2023</t>
+          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان נועה גוהר פורטנוי נועה גוהר פורטנוי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section noago@post.bgu.ac.il Cookies Settings</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>"רויטל לינדר"</t>
+          <t>"נועה גוהר פורטנוי" יילוד</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -8411,14 +8443,14 @@
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-09-04T07:14:47.643108+00:00</t>
+          <t>2026-09-08T14:13:12.580343+00:00</t>
         </is>
       </c>
       <c r="W49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y49" t="n">
         <v>2</v>
@@ -8431,16 +8463,16 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>["https://www.rambam.org.il/?catid=%7B9F8D1CC1-1F5C-46F1-A395-E19ED48FE2EE%7D&amp;itemid=%7B4B21BA59-AF68-46CA-9483-9639E61A75A8%7D", "https://www.rambam.org.il/about-rambam/", "https://www.rambam.org.il/about-rambam/careers/", "https://www.rambam.org.il/departmentsandclinics/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/urology/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/orthopedic/", "https://www.drlinder.co.il/"]</t>
+          <t>["https://www.doctorita.co.il/experts/126297", "https://www.bgu.ac.il/ar/people/noago/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>3.252050431434981e+19</v>
+        <v>9.757388172841951e+19</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8451,7 +8483,7 @@
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>https://www.drlinder.co.il/</t>
+          <t>https://www.bgu.ac.il/ar/people/noago/</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr"/>
@@ -8492,7 +8524,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>רליקה הרשקוביץ</t>
+          <t>עדי יהודה ווינטראוב</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8523,7 +8555,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>ralikah@bgu.ac.il</t>
+          <t>adiyehud@bgu.ac.il</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -8536,7 +8568,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
+          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -8546,12 +8578,12 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان רליקה הרשקוביץ פרופ' רליקה הרשקוביץ Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ralikah@bgu.ac.il رابط ملف الأبحاث Cookies Settings</t>
+          <t>رئيسية جامعة أنشي سيجل في جوريان עדי יהודה ווינטראוב פרופ' עדי יהודה ווינטראוב Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section adiyehud@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0002-4239-8665 Orcid Number Cookies Settings</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>"רליקה הרשקוביץ"</t>
+          <t>"עדי יהודה ווינטראוב"</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -8568,41 +8600,41 @@
         <v>1</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-09-04T07:56:40.372731+00:00</t>
+          <t>2026-09-04T19:20:10.182518+00:00</t>
         </is>
       </c>
       <c r="W50" t="n">
         <v>2</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/ralikah/", "https://www.doctorita.co.il/experts/101245", "https://www.bgu.ac.il/ar/people/ralikah/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.bgu.ac.il/people/adiyehud/", "https://www.bgu.ac.il/researcher/adi-weintraub/", "https://www.beok.co.il/doctors/Doctors-136810/", "https://cris.bgu.ac.il/en/publications/%D7%94%D7%A1%D7%99%D7%9B%D7%95%D7%9F-%D7%9C%D7%A1%D7%99%D7%91%D7%95%D7%9B%D7%99-%D7%94%D7%99%D7%A8%D7%99%D7%95%D7%9F-%D7%91%D7%A0%D7%A9%D7%99%D7%9D-%D7%A2%D7%9D-%D7%90%D7%A0%D7%93%D7%95%D7%9E%D7%98%D7%A8%D7%99%D7%95%D7%96%D7%99%D7%A1/", "https://www.bgu.ac.il/ar/people/adiyehud/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>3.252050431434981e+19</v>
+        <v>9.757263106418254e+19</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8613,7 +8645,7 @@
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
+          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr"/>
@@ -8654,7 +8686,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>שקמה בר און</t>
+          <t>עמרי זמשטין</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8685,7 +8717,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>shikmabo@tlvmc.gov.il</t>
+          <t>omrizam@post.bgu.ac.il</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -8698,7 +8730,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
+          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -8708,12 +8740,12 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>ת לאנדוסקופיה גינקולוגית שטחי התעניינות ועיסוק מיוחדים היסטרוסקופיה עם וללא הרדמה, היסטרוסקופיה ניתוחית ללא הרדמה בשיטת "see and treat" לפרוסקופיות פרק 14 | פרופ' יריב יוגב וד״ר שקמה בר און | מרכז בריאות האישה יצירת קשר shikmabo@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך בהתפתחות ביה"ח איכו</t>
+          <t>ريد البحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان עמרי זמשטין עמרי זמשטין Departments אקדמי לא פעיל הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section omrizam@post.bgu.ac.il Cookies Settings</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>"שקמה בר און"</t>
+          <t>"עמרי זמשטין"</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -8730,28 +8762,28 @@
         <v>1</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-09-04T10:28:27.702590+00:00</t>
+          <t>2026-09-04T19:35:09.971397+00:00</t>
         </is>
       </c>
       <c r="W51" t="n">
         <v>2</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y51" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Z51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AA51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
@@ -8760,11 +8792,11 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>["https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%A9%D7%A7%D7%9E%D7%94-%D7%91%D7%A8-%D7%90%D7%95%D7%9F/", "https://tlvmedical.com/doctors/דר-שקמה-בר-און/", "https://www.rofim.org.il/minisite/%D7%93%D7%A8_%D7%A9%D7%A7%D7%9E%D7%94_%D7%91%D7%A8_%D7%90%D7%95%D7%9F", "https://www.shidurit-ltd.co.il/", "https://www.rofim.org.il/about", "https://www.rofim.org.il/Contact", "https://www.rofim.org.il/specialityPage/%D7%9E%D7%A8%D7%9B%D7%96_%D7%A8%D7%A4%D7%95%D7%90%D7%99", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%9E%D7%92%D7%90%D7%A8", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%91%D7%99%D7%AA_%D7%92%D7%93%D7%99", "https://www.rofim.org.il/minisite/%D7%90%D7%99%D7%99_%D7%90%D7%9C_%D7%A7%D7%9C%D7%99%D7%A0%D7%99%D7%A7", "https://docsrated.com/doctors/שקמה-בר-און", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2FTLVMDC%2Fphotos%2F%25D7%25A2%25D7%2595%25D7%25A7%25D7%2591%25D7%2595%25D7%25AA-%25D7%2595%25D7%259E%25D7%2598%25D7%2595%25D7%25A4%25D7%259C%25D7%2595%25D7%25AA-%25D7%2590%25D7%25A0%25D7%2595-%25D7%25A9%25D7%259E%25D7%2597%25D7%2599%25D7%259D-%25D7%259C%25D7%2594%25D7%259B%25D7%2599%25D7%25A8-%25D7%259C%25D7%259B%25D7%259F-%25D7%2590%25D7%25AA-%25D7%2593%25D7%25A8-%25D7%25A9%25D7%25A7%25D7%259E%25D7%2594-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F%25D7%2593%25D7%25A8-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F-%25D7%2594%25D7%2599%25D7%2590-%25D7%259E%25D7%25A0%25D7%2594%25D7%259C%25D7%25AA-%25D7%2594%25D7%259E%25D7%25A8%25D7%259B%25D7%2596-%25D7%259C%2F1525276317871201%2F", "https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/", "https://www.ncbi.nlm.nih.gov/pubmed/?term=shikma+bar+on", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.bgu.ac.il/ar/people/omrizam/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>3.245379558755114e+19</v>
+        <v>9.757263106418254e+19</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8775,7 +8807,7 @@
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
+          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr"/>
@@ -8816,7 +8848,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>שרית הלמן</t>
+          <t>רויטל לינדר</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8847,7 +8879,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>hsarit@szmc.org.il</t>
+          <t>revital@drlinder.co.il</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -8860,7 +8892,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
+          <t>https://www.drlinder.co.il/</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -8870,12 +8902,12 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t xml:space="preserve"> רופאים בשערי צדק ד"ר שרית  הלמן רופאה בכירה Dr. Sarit  Helman התמחות: גינקולוגיה ויילוד תת התמחות: הריון בסיכון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 026666656 מחלקה: 026666656 hsarit@szmc.org.il hsarit@szmc.org.il נסיון מקצועי Harvard T.H. Chan School of Public Health, Joslin Diabetes Center, Research intern under the supervision of Dr. Florence Brown and Dr. Tamarra James-Todd,     Type 1 Dia</t>
+          <t>בכירה ביחידה הגניקואונקולוגית , בית חולים רמב״ם, חיפה. 4/2014-4/2019 התמחות במיילדות וגניקולוגיה בית חולים רמב״ם,חיפה. לפרטים מלאים חוות דעת יש לך שאלה ? צרי קשר ד״ר רויטל לינדר צפצפה 2 (ישי סנטר) , רמת ישי 058-6918927​ revital@drlinder.co.il הצהרת נגישות © DR. Revital Linder. All rights Reserved , 2023</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>"שרית הלמן"</t>
+          <t>"רויטל לינדר"</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -8892,12 +8924,12 @@
         <v>1</v>
       </c>
       <c r="T52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-09-05T00:06:28.339643+00:00</t>
+          <t>2026-09-04T07:14:47.643108+00:00</t>
         </is>
       </c>
       <c r="W52" t="n">
@@ -8907,26 +8939,26 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z52" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>["https://www.hamichlol.org.il/שרה_(שרית)_הלמן", "https://behevrat-haadam.org/ram-sara-helman/", "https://behevrat-haadam.org/tag/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/IsrAnthro/posts/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F-%D7%A1%D7%95%D7%A6%D7%99%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA%D7%90%D7%A0%D7%97%D7%A0%D7%95-%D7%A9%D7%9E%D7%97%D7%99%D7%9D-%D7%9C%D7%A9%D7%AA%D7%A3-%D7%91%D7%91%D7%97%D7%91%D7%A8%D7%AA-%D7%94%D7%90%D7%93%D7%9D-%D7%90%D7%AA-%D7%93%D7%91%D7%A8%D7%99%D7%95-%D7%A9%D7%9C-%D7%90%D7%95%D7%A8%D7%99-%D7%A8%D7%9D-%D7%A4%D7%A8%D7%95%D7%A4-%D7%90%D7%9E%D7%A8%D7%99%D7%98%D7%95/4246861638775714/", "https://www.doctorita.co.il/experts/137665", "https://www.szmc.org.il/doctors/helman-sarit/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
+          <t>["https://www.rambam.org.il/?catid=%7B9F8D1CC1-1F5C-46F1-A395-E19ED48FE2EE%7D&amp;itemid=%7B4B21BA59-AF68-46CA-9483-9639E61A75A8%7D", "https://www.rambam.org.il/about-rambam/", "https://www.rambam.org.il/about-rambam/careers/", "https://www.rambam.org.il/departmentsandclinics/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/urology/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/orthopedic/", "https://www.drlinder.co.il/"]</t>
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>3.245503093434371e+19</v>
+        <v>9.756151294304942e+19</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8937,7 +8969,7 @@
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
+          <t>https://www.drlinder.co.il/</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr"/>
@@ -8978,12 +9010,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ניצן נבות אבישר</t>
+          <t>רליקה הרשקוביץ</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>family_doctor</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -9009,7 +9041,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>doctor.nitzan@gmail.com</t>
+          <t>ralikah@bgu.ac.il</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -9018,11 +9050,11 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://drnitzan.com/#about</t>
+          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -9032,17 +9064,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>doctor.nitzan@gmail.com</t>
+          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان רליקה הרשקוביץ פרופ' רליקה הרשקוביץ Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ralikah@bgu.ac.il رابط ملف الأبحاث Cookies Settings</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>"ניצן נבות אבישר" רפואת משפחה</t>
+          <t>"רליקה הרשקוביץ"</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>linked_mailto</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -9054,72 +9086,64 @@
         <v>1</v>
       </c>
       <c r="T53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-09-11T08:10:09.398703+00:00</t>
+          <t>2026-09-04T07:56:40.372731+00:00</t>
         </is>
       </c>
       <c r="W53" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="X53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>ddgs:yahoo+ddgs:bing</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>["https://drnitzan.com/", "https://drnitzan.com/#about", "https://drnitzan.com/#contact"]</t>
+          <t>["https://www.bgu.ac.il/people/ralikah/", "https://www.doctorita.co.il/experts/101245", "https://www.bgu.ac.il/ar/people/ralikah/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>3.245421247564433e+19</v>
+        <v>9.756151294304942e+19</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
       </c>
       <c r="AF53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>https://drnitzan.com/</t>
+          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
         </is>
       </c>
       <c r="AI53" t="inlineStr"/>
       <c r="AJ53" t="inlineStr"/>
       <c r="AK53" t="inlineStr"/>
-      <c r="AL53" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM53" t="b">
-        <v>1</v>
-      </c>
-      <c r="AN53" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>ד"ר ניצן נבות אבישר | ליווי וטיפול רפואי בהשמנה ומחלות מטבוליות – שוהם ד"ר ניצן נבות אבישר | ליווי וטיפול רפואי בהשמנה ומחלות מטבוליות – שוהם בית הסבר תהליך עלינו צור קשר לתיאום ייעוץ בית הסבר תהליך עלינו צור קשר לתיאום ייעוץ ד"ר ניצן נבות אבישר · מומחית ברפואת משפחה ליווי וטיפול בהשמנה ומחלות מטבוליות אבחון, טיפול וליווי מותאם אישית, בלי שיפוטיות ובלי סודות. שילוב של ידע מדעי, הקשבה ורגישות. לתיאום ייעוץ הגישה שלי המיקוד הוא בך הזמן שלך לשינוי, המקום שלך בחיים אם הגעת לכאן, אני מאמינה שפינית מקום בלב להתמקד בעצמך ולהעניק לעצמך את המתנה החשובה ביותר – הבריאות שלך. הגעת למקום בחיים שבו הבריאות והצרכים שלך נמצאים במרכז. אני מאמינה שטיפול בהשמנה ובאיזון מטבולי אינו מסתכם בנוסחאות פשוטות של מספרים או קלוריות. מדובר בתהליך רפואי עמוק ומורכב, שחייב להתאים באופן מדויק לשגרת החיים, לפיזיולוגיה וליעדים האישיים שלך. אני כאן כדי להעניק לך מענה מקצועי ומקיף המבוסס על ידע קליני עדכני וניסיון רב שנים, לצד הקשבה עמוקה ורגישות. ההתמקדות היא בך. המענה הרפואי בקליניקה אבחון ואיזון מטבולי מקיף בדיקות והסתכלות רחבה על כל התמונה הבריאותית שלך, כדי להבין מה באמת משפיע על המשקל</t>
-        </is>
-      </c>
-      <c r="AP53" t="inlineStr"/>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr"/>
+      <c r="AO53" t="inlineStr"/>
+      <c r="AP53" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ53" t="inlineStr"/>
       <c r="AR53" t="n">
         <v>1</v>
@@ -9131,11 +9155,11 @@
         <v>1</v>
       </c>
       <c r="AU53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
+          <t>PERSON</t>
         </is>
       </c>
     </row>
@@ -9148,7 +9172,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>דלית דרימן-מדינה</t>
+          <t>שירית גושציני-ביבי</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9179,7 +9203,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>dalit@drdreman.co.il</t>
+          <t>shiritudi@tauex.tau.ac.il</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -9188,11 +9212,11 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://www.drdreman.co.il/%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%9E%D7%98%D7%91%D7%95%D7%9C%D7%99%D7%95%D7%AA/</t>
+          <t>https://www.tau.ac.il/profile/shiritudi</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -9202,17 +9226,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>drdremandalit@gmail.com</t>
+          <t>שיניים טבע בקמפוס מוזיאון הטבע ע"ש שטיינהרדט הגן הזואולוגי הגן הבוטני הינך נמצא כאן לדף הבית של אוניברסיטת תל אביב &gt; ד"ר שירית גושציני-ביבי ד"ר שירית גושציני-ביבי רפואת המשפחה - קלינית ניווט מהיר: English דואר אלקטרוני: shiritudi@tauex.tau.ac.il מידע כללי יצירת קשר ודרכי הגעה אלפון דרושים נהלי האוניברסיטה מכרזים מידע לשעת חירום מבקרת האוניברסיטה תקנון משמעת ופסקי דין לימודים רישום לאוניברסיטה מידע למתעניינים בלימודים חישוב סיכויי קבלה ל</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>"דלית דרימן מדינה" רפואת משפחה (מרפאה OR "צור קשר" OR email OR מייל)</t>
+          <t>"שירית גושציני ביבי" רפואת משפחה</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>direct_mailto</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -9224,52 +9248,52 @@
         <v>1</v>
       </c>
       <c r="T54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-09-10T18:44:56.180135+00:00</t>
+          <t>2026-09-11T18:42:00.189778+00:00</t>
         </is>
       </c>
       <c r="W54" t="n">
         <v>8</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y54" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z54" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AA54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>["https://www.drdreman.co.il/מחלות-מטבוליות/", "https://www.drdreman.co.il/%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%9E%D7%98%D7%91%D7%95%D7%9C%D7%99%D7%95%D7%AA/", "https://www.drdreman.co.il/about/", "https://www.drdreman.co.il/contact/", "https://www.drdreman.co.il/", "https://www.doctorita.co.il/experts/52215", "https://www.drdreman.co.il/%D7%93%D7%A3-%D7%91%D7%99%D7%AA/", "https://www.other-medicine.co.il/author/dalitdrdreman-co-il/", "https://www.izi.co.il/site/6f2c026c8d", "https://www.infomed.co.il/experts/78145/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%93%D7%A8%D7%99%D7%9E%D7%9F-%D7%9E%D7%93%D7%99%D7%A0%D7%94-%D7%93%D7%9C%D7%99%D7%AA/", "https://www.findglocal.com/IL/Unknown/106988607393615/ד״ר-דלית-דרימן-רפואה-פונקציונלית-ואינטגרטיבית"]</t>
+          <t>["https://www.doctorita.co.il/experts/122127", "https://medpage.co.il/doctors/שירית-גושציני-ביבי-25723/", "https://medpage.co.il/doctors/%D7%A9%D7%99%D7%A8%D7%99%D7%AA-%D7%92%D7%95%D7%A9%D7%A6%D7%99%D7%A0%D7%99-%D7%91%D7%99%D7%91%D7%99-25723/", "https://easy.co.il/page/27298045", "https://docsrated.com/doctors/שירית-גושציני-ביבי", "https://www.tau.ac.il/profile/shiritudi", "https://www.tau.ac.il/about", "https://acad-sec.tau.ac.il/senate/about", "https://www.tau.ac.il/rishum-minhal", "https://www.tau.ac.il/academic-units-view", "https://languages.tau.ac.il/", "https://impact.tau.ac.il/impact.projects?field_master_unit1_tid%5B%5D=173", "https://acad-sec.tau.ac.il/academic-secretary/about", "https://acad-sec.tau.ac.il/grantsite/about", "https://acad-sec.tau.ac.il/phd/about", "https://acad-sec.tau.ac.il/academic-secretary/about_1779", "https://www.maccabi4u.co.il/media/jbmh5ory/רשימת-אתרים-לאספקה-נספח-ז.xlsx"]</t>
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>3.332513196361554e+19</v>
+        <v>9.729592870009283e+19</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>https://www.drdreman.co.il/%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%9E%D7%98%D7%91%D7%95%D7%9C%D7%99%D7%95%D7%AA/</t>
+          <t>https://www.tau.ac.il/profile/shiritudi</t>
         </is>
       </c>
       <c r="AI54" t="inlineStr"/>
@@ -9286,8 +9310,7 @@
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>מחלות מטבוליות - ד"ר דלית דרימן-מדינה מחלות מטבוליות - ד"ר דלית דרימן-מדינה דלג לתוכן אודות כיצד נוכל לעזור במה אנחנו מטפלים מפגשים ועלויות שאלות ותשובות מאמרים סרטונים מהתקשורת צור קשר אודות כיצד נוכל לעזור במה אנחנו מטפלים מפגשים ועלויות שאלות ותשובות מאמרים סרטונים מהתקשורת צור קשר 0546033755 חיפוש חיפוש אודות כיצד נוכל לעזור במה אנחנו מטפלים מפגשים ועלויות שאלות ותשובות מאמרים סרטונים מהתקשורת צור קשר אודות כיצד נוכל לעזור במה אנחנו מטפלים מפגשים ועלויות שאלות ותשובות מאמרים סרטונים מהתקשורת צור קשר חיפוש חיפוש מחלות מטבוליות הפרעות מטבוליות, עודף משקל, סוכרת בחירות מזון גרועות, העדר מרכיבי מזון חיוניים, רעלנים, מתח נפשי, ודלקת כרונית גורמים לחוסר איזון מטבולי ולמחלות שמהוות את מרבית המחלות הכרוניות כיום. במה אנו מטפלים? מחלות לב יתר לחץ דם עודף משקל והשמנה תסמונת מטבולית סוכרת הפרעות בכולסטרול ושומני הדם איך זה עובד? אנחנו עורכים למטופלים שלנו בירור נרחב ע״י בדיקות מעבדה מתקדמות כולל בדיקות מיוחדות לשומני הדם שאינן מבוצעות באופן סטנדרטי בקופות החולים.
-בטיפול שלנו אנו מתבססים על המזון ומרכיבי התזונה ככלים הטיפוליים הרא</t>
+          <t>ד"ר שירית גושציני-ביבי | אוניברסיטת ת"א ד"ר שירית גושציני-ביבי | אוניברסיטת ת"א תפריט עליון תפריט ראשי תוכן ראשי אלפון סגל ספריות English Русский العَرَبِية 中文网 מערכת פניות אזור אישי לסטודנטים.יות להרשמה חיפוש חיפוש באתר זה חיפוש בכל האוניברסיטה אודות האוניברסיטה שלנו אסטרטגיה חדשות אירועים מגילת כבוד ופרסים זוכרים את הנופלים נשיאי אוניברסיטת תל אביב שוויון, מגוון וקהילה קשרי תעשייה וחברה קמפוס ירוק סגל ומנהלה אגפים ומשרדי מנהלה דבר הנשיא דבר הרקטורית סנאט האוניברסיטה חברי הוועד המנהל המזכירות האקדמית אגף רישום ומינהל תלמידים דרושים - משרות אקדמיות דרושים - משרות מינהליות מידע שימושי יצירת קשר ודרכי הגעה מפת הקמפוס מכרזים שירותי מחשוב מידע לשעת חירום לוח שנת הלימודים חנות המותג של האוניברסיטה יחידות אקדמיות פקולטות ויחידות הוראה מדעי הרפואה והבריאות מדעים מדויקים מדעי החיים הנדסה מדעי הרוח אמנויות מדעי החברה ניהול משפטים מדעי המוח בית הספר החדש לסביבה מוזיאון הטבע ע"ש שטיינהרדט יחידות כלל אוניברסיטאיות המרכז לננו-טכנולוגיה המרכז למחקר ומדע קוונטי המרכז ל-AI ומדעי הנתונים המרכז להתמודדות עם מגפות מיזם האקלים PlanNetZero מכון</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr"/>
@@ -9302,11 +9325,11 @@
         <v>1</v>
       </c>
       <c r="AU54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
+          <t>PERSON</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9342,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ד"ר ארבל אריאל</t>
+          <t>שקמה בר און</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9339,31 +9362,31 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>ima</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>info@eryaveladan.com</t>
+          <t>shikmabo@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://www.eryaveladan.com/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -9373,12 +9396,12 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>החזיר את האיזון. קראי עוד השאירי פרטים ונחזור אלייך בהקדם שם מלא טלפון דוא״ל שליחה רופא נשים מומחה מחלות העריה והלדן ​ ד״ר אריאל ארבל לקביעת תור: 077-2311245 כתובת המרפאה: בית למומחים ברפואה - בורוכוב 54, גבעתיים דוא״ל: info@eryaveladan.com bottom of page</t>
+          <t>ת לאנדוסקופיה גינקולוגית שטחי התעניינות ועיסוק מיוחדים היסטרוסקופיה עם וללא הרדמה, היסטרוסקופיה ניתוחית ללא הרדמה בשיטת "see and treat" לפרוסקופיות פרק 14 | פרופ' יריב יוגב וד״ר שקמה בר און | מרכז בריאות האישה יצירת קשר shikmabo@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך בהתפתחות ביה"ח איכו</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>"ארבל אריאל"</t>
+          <t>"שקמה בר און"</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -9388,11 +9411,11 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>[{"email": "info@eryaveladan.com", "confidence": 88, "source_url": "https://www.eryaveladan.com/", "identity_url": "https://www.eryaveladan.com/", "evidence": "החזיר את האיזון. קראי עוד השאירי פרטים ונחזור אלייך בהקדם שם מלא טלפון דוא״ל שליחה רופא נשים מומחה מחלות העריה והלדן ​ ד״ר אריאל ארבל לקביעת תור: 077-2311245 כתובת המרפאה: בית למומחים ברפואה - בורוכוב 54, גבעתיים דוא״ל: info@eryaveladan.com bottom of page", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}, {"email": "office@b54.co.il", "confidence": 88, "source_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "identity_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "evidence": "ד\"ר אריאל ארבל - מרפאת מומחים B54, הבית למומחים ברפואה בגבעתיים דילוג לתוכן B54 03-757-8562 office@b54.co.il א׳-ה׳ 8:00-20:00 | ו׳ 08:00-13:00 Facebook-f Youtube Google דף הבית אודות B54 מי אנחנו שכונת בורוכוב מרכז Friendly הנהלת המרפאה שאלות נפוצות הרופאים שלנו קליניקה להשכרה מידע למטופל שאלות ותשובות הורדת טפ", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T55" t="n">
         <v>0</v>
@@ -9400,23 +9423,23 @@
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-09-03T20:23:48.175654+00:00</t>
+          <t>2026-09-04T10:28:27.702590+00:00</t>
         </is>
       </c>
       <c r="W55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X55" t="n">
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
@@ -9425,11 +9448,11 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598", "https://www.facebook.com/people/%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%90%D7%A8%D7%91%D7%9C/pfbid0NCmi7FZgUyu2EVV5mLJMpBfndXiDQPqseAxUny7KWHsDvucQScUiVnBeMef3ByStl/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%90%D7%A8%D7%91%D7%9C-%D7%90%D7%A8%D7%99%D7%90%D7%9C/", "https://www.eryaveladan.com/", "https://www.eryaveladan.com/%D7%90%D7%95%D7%93%D7%95%D7%AA-1", "https://www.b54.co.il/doctors/dr-arbel-ariel/", "https://www.medreviews.co.il/provider/dr-arbel-ariel", "https://www.b54.co.il/about/", "https://www.b54.co.il/about", "https://www.b54.co.il/about#borohov", "https://www.b54.co.il/about#Friendly", "https://www.b54.co.il/about#management", "https://www.b54.co.il/about#qa", "https://www.medreviews.co.il/provider/dr-arbel-ariel#contact-doctor-section", "https://www.medreviews.co.il/contact-us", "https://www.medreviews.co.il/about", "https://woman.mymc.co.il/doctors/dr-arielarbel/", "https://www.ima.org.il/DoctorsIndex/Default.aspx", "https://www.infomed.co.il/experts/145655/", "https://www.ami.org.il/blog/families/not-the-same-shirley"]</t>
+          <t>["https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%A9%D7%A7%D7%9E%D7%94-%D7%91%D7%A8-%D7%90%D7%95%D7%9F/", "https://tlvmedical.com/doctors/דר-שקמה-בר-און/", "https://www.rofim.org.il/minisite/%D7%93%D7%A8_%D7%A9%D7%A7%D7%9E%D7%94_%D7%91%D7%A8_%D7%90%D7%95%D7%9F", "https://www.shidurit-ltd.co.il/", "https://www.rofim.org.il/about", "https://www.rofim.org.il/Contact", "https://www.rofim.org.il/specialityPage/%D7%9E%D7%A8%D7%9B%D7%96_%D7%A8%D7%A4%D7%95%D7%90%D7%99", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%9E%D7%92%D7%90%D7%A8", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%91%D7%99%D7%AA_%D7%92%D7%93%D7%99", "https://www.rofim.org.il/minisite/%D7%90%D7%99%D7%99_%D7%90%D7%9C_%D7%A7%D7%9C%D7%99%D7%A0%D7%99%D7%A7", "https://docsrated.com/doctors/שקמה-בר-און", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2FTLVMDC%2Fphotos%2F%25D7%25A2%25D7%2595%25D7%25A7%25D7%2591%25D7%2595%25D7%25AA-%25D7%2595%25D7%259E%25D7%2598%25D7%2595%25D7%25A4%25D7%259C%25D7%2595%25D7%25AA-%25D7%2590%25D7%25A0%25D7%2595-%25D7%25A9%25D7%259E%25D7%2597%25D7%2599%25D7%259D-%25D7%259C%25D7%2594%25D7%259B%25D7%2599%25D7%25A8-%25D7%259C%25D7%259B%25D7%259F-%25D7%2590%25D7%25AA-%25D7%2593%25D7%25A8-%25D7%25A9%25D7%25A7%25D7%259E%25D7%2594-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F%25D7%2593%25D7%25A8-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F-%25D7%2594%25D7%2599%25D7%2590-%25D7%259E%25D7%25A0%25D7%2594%25D7%259C%25D7%25AA-%25D7%2594%25D7%259E%25D7%25A8%25D7%259B%25D7%2596-%25D7%259C%2F1525276317871201%2F", "https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/", "https://www.ncbi.nlm.nih.gov/pubmed/?term=shikma+bar+on", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>4.322725496553574e+19</v>
+        <v>9.736138676265343e+19</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9440,7 +9463,7 @@
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>https://www.eryaveladan.com/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr"/>
@@ -9455,7 +9478,7 @@
       </c>
       <c r="AQ55" t="inlineStr"/>
       <c r="AR55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS55" t="b">
         <v>0</v>
@@ -9464,11 +9487,11 @@
         <v>1</v>
       </c>
       <c r="AU55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
+          <t>PERSON</t>
         </is>
       </c>
     </row>
@@ -9481,7 +9504,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>יעל כהן</t>
+          <t>שרית הלמן</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9512,20 +9535,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>office@elitemed.co.il</t>
+          <t>hsarit@szmc.org.il</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://elitemed.co.il/doctors/dr-yael-cohen-hebrew/</t>
+          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -9535,12 +9558,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>ד"ר יעל כהן - elitemed.co.il דלג לתוכן Facebook Instagram Whatsapp Office@elitemed.co.il 073-321-4181 בית אודות רופאים שירותים רפואיים אולטרסאונד וביופסיות אוסטאופתיה אורולוגיה אורתופדיה אלרגיה ואימונולגיה אנדוקרינולוגיה סוכרת וירידה במשקל אסתטיקה אף אוזן גרון גינקולוגיה ובריאות האישה ג</t>
+          <t xml:space="preserve"> רופאים בשערי צדק ד"ר שרית  הלמן רופאה בכירה Dr. Sarit  Helman התמחות: גינקולוגיה ויילוד תת התמחות: הריון בסיכון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 026666656 מחלקה: 026666656 hsarit@szmc.org.il hsarit@szmc.org.il נסיון מקצועי Harvard T.H. Chan School of Public Health, Joslin Diabetes Center, Research intern under the supervision of Dr. Florence Brown and Dr. Tamarra James-Todd,     Type 1 Dia</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>"יעל כהן" יילוד</t>
+          <t>"שרית הלמן"</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -9562,67 +9585,59 @@
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-09-10T18:33:08.486465+00:00</t>
+          <t>2026-09-05T00:06:28.339643+00:00</t>
         </is>
       </c>
       <c r="W56" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="X56" t="n">
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Z56" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>ddgs:yahoo+ddgs:bing</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>["https://elitemed.co.il/doctors/dr-yael-cohen-hebrew/", "https://elitemed.co.il/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%A4%D7%95%D7%90%D7%99-%D7%A4%D7%A8%D7%98%D7%99-%D7%91%D7%9E%D7%95%D7%93%D7%99%D7%A2%D7%99%D7%9F/", "https://elitemed.co.il/pain-clinic-modiin/", "https://elitemed.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://elitemed.co.il/%d7%90%d7%95%d6%b9%d7%93%d7%95%d6%b9%d7%aa/", "https://medpage.co.il/doctors/יעל-כהן-23202/", "https://medpage.co.il/doctors/%D7%99%D7%A2%D7%9C-%D7%9B%D7%94%D7%9F-23202/", "https://www.facebook.com/ichilovmedical/posts/תכירו-את-פרופ-יעל-כהןמנהלת-יחידת-המיאלומה-במערך-ההמטולוגי-של-איכילוב-ואחת-מהרופא/1288268913309017/", "https://www.facebook.com/ichilovmedical/videos/%D7%AA%D7%9B%D7%99%D7%A8%D7%95-%D7%90%D7%AA-%D7%A4%D7%A8%D7%95%D7%A4-%D7%99%D7%A2%D7%9C-%D7%9B%D7%94%D7%9F%D7%9E%D7%A0%D7%94%D7%9C%D7%AA-%D7%99%D7%97%D7%99%D7%93%D7%AA-%D7%94%D7%9E%D7%99%D7%90%D7%9C%D7%95%D7%9E%D7%94-%D7%91%D7%9E%D7%A2%D7%A8%D7%9A-%D7%94%D7%94%D7%9E%D7%98%D7%95%D7%9C%D7%95%D7%92%D7%99-%D7%A9%D7%9C-%D7%90%D7%99%D7%9B%D7%99%D7%9C%D7%95%D7%91-%D7%95%D7%90%D7%97%D7%AA-%D7%9E%D7%94%D7%A8%D7%95%D7%A4%D7%90/981973987039095/", "https://www.medico.co.il/doctors/פרופ-יעל-כהן/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%99%D7%A2%D7%9C-%D7%9B%D7%94%D7%9F/", "https://www.medico.co.il/doctors/", "https://www.medico.co.il/doctors/%d7%a4%d7%a8%d7%95%d7%a4-%d7%99%d7%a2%d7%9c-%d7%9b%d7%94%d7%9f/", "https://www.tasmc.org.il/doctorssearch/dr/cohen-yael/", "https://www.szmc.org.il/doctors/cohen-yael/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.vimed.co.il/users/0918fba4-bd6a-4310-ab8f-b51cab0b8f80", "https://www.meuhedet.co.il/poi/ParamedicalDoctors/000189680918100097000000000000_0", "https://www.medreviews.co.il/provider/dr-cohen-yael"]</t>
+          <t>["https://www.hamichlol.org.il/שרה_(שרית)_הלמן", "https://behevrat-haadam.org/ram-sara-helman/", "https://behevrat-haadam.org/tag/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/IsrAnthro/posts/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F-%D7%A1%D7%95%D7%A6%D7%99%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA%D7%90%D7%A0%D7%97%D7%A0%D7%95-%D7%A9%D7%9E%D7%97%D7%99%D7%9D-%D7%9C%D7%A9%D7%AA%D7%A3-%D7%91%D7%91%D7%97%D7%91%D7%A8%D7%AA-%D7%94%D7%90%D7%93%D7%9D-%D7%90%D7%AA-%D7%93%D7%91%D7%A8%D7%99%D7%95-%D7%A9%D7%9C-%D7%90%D7%95%D7%A8%D7%99-%D7%A8%D7%9D-%D7%A4%D7%A8%D7%95%D7%A4-%D7%90%D7%9E%D7%A8%D7%99%D7%98%D7%95/4246861638775714/", "https://www.doctorita.co.il/experts/137665", "https://www.szmc.org.il/doctors/helman-sarit/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>3.333254404514628e+19</v>
+        <v>9.736509280303114e+19</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
       </c>
       <c r="AF56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>https://elitemed.co.il/doctors/dr-yael-cohen-hebrew/</t>
+          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr"/>
       <c r="AJ56" t="inlineStr"/>
       <c r="AK56" t="inlineStr"/>
-      <c r="AL56" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM56" t="b">
-        <v>1</v>
-      </c>
-      <c r="AN56" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>ד"ר יעל כהן - elitemed.co.il ד"ר יעל כהן - elitemed.co.il דלג לתוכן Facebook Instagram Whatsapp Office@elitemed.co.il 073-321-4181 בית אודות רופאים שירותים רפואיים אולטרסאונד וביופסיות אוסטאופתיה אורולוגיה אורתופדיה אלרגיה ואימונולגיה אנדוקרינולוגיה סוכרת וירידה במשקל אסתטיקה אף אוזן גרון גינקולוגיה ובריאות האישה גסטרואנטרולוגיה גֵרִיאַטרִיָה דרמטולגיה המטולוגיה כלי דם ורדיולוגיה פולשנית התמחויות טיפוליות ושיקומיות כירורגיה כירורגיה פלסטית מרפאת כאב נוירולוגיה, קשב וריכוז והתפתחות הילד נפרולוגיה ויתר לחץ דם סקירות מערכות ואקו לב עובר עיניים פודיאטריה כירורגית וכף רגל פולמונולוגיה ורפואת שינה פסיכיאטריה פרוקטולוגיה וכירורגיה קולורקטלית קרדיולוגיה ואלקטרופיזיולוגיה ראומטולוגיה רפואת ילדים מומחית רפואת ספורט ופיזיותרפיה רפואה תעסוקתית תזונה קלינית ודיאטה תור דחוף  24-48 שעות צור קשר השכרת קליניקה במודיעין שירות VIP שירותים מידע רפואי בית אודות רופאים שירותים רפואיים אולטרסאונד וביופסיות אוסטאופתיה אורולוגיה אורתופדיה אלרגיה ואימונולגיה אנדוקרינולוגיה סוכרת וירידה במשקל אסתטיקה אף אוזן גרון גינקולוגיה ובריאות האישה גס</t>
-        </is>
-      </c>
-      <c r="AP56" t="inlineStr"/>
+      <c r="AL56" t="inlineStr"/>
+      <c r="AM56" t="inlineStr"/>
+      <c r="AN56" t="inlineStr"/>
+      <c r="AO56" t="inlineStr"/>
+      <c r="AP56" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ56" t="inlineStr"/>
       <c r="AR56" t="n">
         <v>1</v>
@@ -9634,11 +9649,11 @@
         <v>1</v>
       </c>
       <c r="AU56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
+          <t>PERSON</t>
         </is>
       </c>
     </row>
@@ -9651,12 +9666,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>מאיה שרון וינר</t>
+          <t>ליאור שחר</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -9682,20 +9697,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>clinic@drmayasharonweiner.com</t>
+          <t>leeor.shachar@gmail.com</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://www.drmayasharonweiner.com/</t>
+          <t>https://www.drleeorshachar.com/about</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -9705,17 +9720,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>אני איתך במסע הזה. הצעד הראשון שלך מתחיל כאן. ד"ר מאיה שרון-וינר רופאת נשים מומחית בפריון והפריה חוץ גופית מיילדות וגינקולוגיה לקביעת פגישה © 2026 כל הזכויות שמורות לד"ר מאיה שרון-וינר הברזל 9א', רמת החייל ווטסאפ למרפאה clinic@drmayasharonweiner.com פוריות האישה והגבר טיפולי פוריות הפריה חוץ גופית ו-PGD שימור פוריות פוריות לאחר סרטן ובנשאיות BRCA מעקב וליווי הריון גינקולוגיה כללית Menu Close אודות יצירת קשר מדיניות פרטיות הצהרת נגישות M</t>
+          <t>Leeor.shachar@gmail.com</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>"מאיה שרון וינר"</t>
+          <t>"ליאור שחר" רפואת משפחה</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>linked_mailto</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -9727,64 +9742,72 @@
         <v>1</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-09-04T17:43:40.101946+00:00</t>
+          <t>2026-09-11T18:38:03.913562+00:00</t>
         </is>
       </c>
       <c r="W57" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Z57" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>["https://www.drmayasharonweiner.com/", "https://www.drmayasharonweiner.com/about", "https://www.drmayasharonweiner.com/contact", "https://www.medreviews.co.il/provider/dr-sharon-weiner-maya", "https://www.medreviews.co.il/provider/dr-sharon-weiner-maya/treatment", "https://www.doctorita.co.il/experts/119120", "https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr_maya_sharonweiner%2F&amp;is_from_rle", "https://docsrated.com/doctors/מאיה-שרון-וינר"]</t>
+          <t>["https://www.drleeorshachar.com/", "https://www.drleeorshachar.com/about", "https://www.drleeorshachar.com/contact"]</t>
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>3.333212715706692e+19</v>
+        <v>20415</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>https://www.drmayasharonweiner.com/</t>
+          <t>https://www.drleeorshachar.com/</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr"/>
       <c r="AJ57" t="inlineStr"/>
       <c r="AK57" t="inlineStr"/>
-      <c r="AL57" t="inlineStr"/>
-      <c r="AM57" t="inlineStr"/>
-      <c r="AN57" t="inlineStr"/>
-      <c r="AO57" t="inlineStr"/>
-      <c r="AP57" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL57" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM57" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN57" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>ד"ר ליאור שחר - מומחית ברפואת משפחה ובטיפול בכאב כרוני נוירופלסטי ד"ר ליאור שחר - מומחית ברפואת משפחה ובטיפול בכאב כרוני נוירופלסטי top of page ד"ר ליאור שחר עמוד הבית אודות הרצאות טיפול בכאב תהליך הטיפול בקליניקה גישות הטיפול בקליניקה תהליך הטיפול בקליניקה גישות הטיפול בקליניקה PRT צרו קשר Menu Close מומחית ברפואת משפחה ובסוציולוגיה רפואית, פסיכותרפיסטית מטפלת בשיטות מבוססות טיפול קוגניטיבי-התנהגותי. מרצה ומקדמת בריאות מודעת מין ומגדר וטיפול במחלות כרוניות בנשים. ד"ר ליאור שחר רופאת משפחה, פסיכותרפיסטית, מטפלת בכאב כרוני שם טלפון Email שליחה טיפול אישי בקליניקה ניסיון קליני ומחקרים מראים שמרבית המטופלים הסובלים מכאב כרוני מתקשים למצוא פתרון ולהחלים מהכאב. עבור רבים, טיפול סימפטומי בלבד אינו מספיק כדי לתפקד ולהעלות את רמת איכות החיים. זו הסיבה שיש צורך בטיפול אינטגרטיבי בהפרעות כאב שמתייחס ומשקלל את הכל. טיפול שמשלב שיטות טיפול מבוססות ראיות. ד"ר שחר (MD, PhD) מוסמכת בשיטות טיפול PRT ו-EAET לכאב כרוני, ACT וCBT. מזמינה אתכם לקבוע תור ולהתחיל תהליך שיקום. על הטיפול הרצאות והעשרה לקהל המקצועי הכאב הכרוני הוא אתגר אבחוני וטיפולי רב-ממדי: האם אתם מתוסכל</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr"/>
       <c r="AQ57" t="inlineStr"/>
       <c r="AR57" t="n">
         <v>1</v>
@@ -9813,12 +9836,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>מנחם נוימן</t>
+          <t>ניצן נבות אבישר</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -9844,20 +9867,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>hello@professorneuman.com</t>
+          <t>doctor.nitzan@gmail.com</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://professorneuman.com/he/</t>
+          <t>https://drnitzan.com/#about</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -9867,86 +9890,94 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>פרופ׳ מנחם נוימן — אורוגינקולוגיה ורפואת רצפת האגן מגדל סוזוקי, קומה 4, רח׳ יגאל אלון 82, תל אביב 054-644-2060 · hello@professorneuman.com ראשי מידע לרופאים מידע למטופלות מהתקשורת צרי קשר English פרופ׳ מנחם נוימן אורוגינקולוגיה ורפואת רצפת האגן צניחת איברי האגן ודליפת שתן הן מהתופעות השכיחות ביותר בקרב נשים — וגם מהניתנות ביותר לטי</t>
+          <t>doctor.nitzan@gmail.com</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>"מנחם נוימן"</t>
+          <t>"ניצן נבות אבישר" רפואת משפחה</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>linked_mailto</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>[{"email": "info@raphaelhospitals.co.il", "confidence": 80, "source_url": "https://www.raphaelhospitals.co.il/en/international-department/about/", "identity_url": "https://www.raphaelhospitals.co.il/doctors/neuman-menahem/", "evidence": "info@raphaelhospitals.co.il", "matched_query": "\"מנחם נוימן\"", "extraction_method": "linked_mailto"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-09-04T18:20:49.705154+00:00</t>
+          <t>2026-09-11T08:10:09.398703+00:00</t>
         </is>
       </c>
       <c r="W58" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y58" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Z58" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>["https://professorneuman.com/", "https://professorneuman.com/he/", "https://professorneuman.com/he/contact", "https://professorneuman.com/en/contact", "https://www.facebook.com/public/%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/", "https://www.facebook.com/people/%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/pfbid0371mkxMbe96MNN5gS9XHB7KqrSyxJnXyG9AsLfdZV7j8RjCKyjm8cEEVgjSreLhY8l/", "https://chabadpedia.co.il/wiki/%D7%9E%D7%A0%D7%97%D7%9D_%D7%A0%D7%95%D7%99%D7%9E%D7%9F", "https://www.raphaelhospitals.co.il/doctors/neuman-menahem/", "https://www.raphaelhospitals.co.il/about/aboutus/", "https://www.raphaelhospitals.co.il/fields/endoscopic-unit/about/", "https://www.raphaelhospitals.co.il/fields/pain-clinic/about/", "https://www.raphaelhospitals.co.il/en/international-department/about/", "https://www.raphaelhospitals.co.il/fields/heart-catheterization-clinic/about/", "https://www.raphaelhospitals.co.il/en/about/aboutus/", "https://www.raphaelhospitals.co.il/en/contact/"]</t>
+          <t>["https://drnitzan.com/", "https://drnitzan.com/#about", "https://drnitzan.com/#contact"]</t>
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>3.333212715706692e+19</v>
+        <v>9.736263742693297e+19</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>https://professorneuman.com/he/</t>
+          <t>https://drnitzan.com/</t>
         </is>
       </c>
       <c r="AI58" t="inlineStr"/>
       <c r="AJ58" t="inlineStr"/>
       <c r="AK58" t="inlineStr"/>
-      <c r="AL58" t="inlineStr"/>
-      <c r="AM58" t="inlineStr"/>
-      <c r="AN58" t="inlineStr"/>
-      <c r="AO58" t="inlineStr"/>
-      <c r="AP58" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL58" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM58" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN58" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>ד"ר ניצן נבות אבישר | ליווי וטיפול רפואי בהשמנה ומחלות מטבוליות – שוהם ד"ר ניצן נבות אבישר | ליווי וטיפול רפואי בהשמנה ומחלות מטבוליות – שוהם בית הסבר תהליך עלינו צור קשר לתיאום ייעוץ בית הסבר תהליך עלינו צור קשר לתיאום ייעוץ ד"ר ניצן נבות אבישר · מומחית ברפואת משפחה ליווי וטיפול בהשמנה ומחלות מטבוליות אבחון, טיפול וליווי מותאם אישית, בלי שיפוטיות ובלי סודות. שילוב של ידע מדעי, הקשבה ורגישות. לתיאום ייעוץ הגישה שלי המיקוד הוא בך הזמן שלך לשינוי, המקום שלך בחיים אם הגעת לכאן, אני מאמינה שפינית מקום בלב להתמקד בעצמך ולהעניק לעצמך את המתנה החשובה ביותר – הבריאות שלך. הגעת למקום בחיים שבו הבריאות והצרכים שלך נמצאים במרכז. אני מאמינה שטיפול בהשמנה ובאיזון מטבולי אינו מסתכם בנוסחאות פשוטות של מספרים או קלוריות. מדובר בתהליך רפואי עמוק ומורכב, שחייב להתאים באופן מדויק לשגרת החיים, לפיזיולוגיה וליעדים האישיים שלך. אני כאן כדי להעניק לך מענה מקצועי ומקיף המבוסס על ידע קליני עדכני וניסיון רב שנים, לצד הקשבה עמוקה ורגישות. ההתמקדות היא בך. המענה הרפואי בקליניקה אבחון ואיזון מטבולי מקיף בדיקות והסתכלות רחבה על כל התמונה הבריאותית שלך, כדי להבין מה באמת משפיע על המשקל</t>
+        </is>
+      </c>
+      <c r="AP58" t="inlineStr"/>
       <c r="AQ58" t="inlineStr"/>
       <c r="AR58" t="n">
         <v>1</v>
@@ -9975,12 +10006,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>נעמה מימון</t>
+          <t>לילך מלצקי</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -10006,20 +10037,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>office@medicaltop.co.il</t>
+          <t>lilach.malatskey@biu.ac.il</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/</t>
+          <t>https://medicine.biu.ac.il/node/2836</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -10029,12 +10060,14 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t xml:space="preserve">ד"ר נעמה מימון: מומחית ברפואת נשים - MedicalTop Search Close Facebook 073-3310444 סנטר הגליל רחוב האגס 1, שער הרימון, קומה שניה. ראש פינה. office@medicaltop.co.il לקביעת תור דף הבית אודות תחומי פעילות הצוות שלנו יצירת קשר Menu דף הבית אודות תחומי פעילות הצוות שלנו יצירת קשר ד"ר נעמה מימון: מומחית ברפואת נשים דף הבית / רופאים / ד"ר נעמה מימון: מומחית ברפואת </t>
+          <t xml:space="preserve">ריאות התעסוקתית מניעת הטרדה מינית חדשות חדשות המחקר תקשורת מעבר לגליל כפר הסטודנטים בעמיעד יצירת קשר English הדפסה ד"ר
+  לילך
+  מלצקי מרצה בכירה קליני Clinical Senior Lecturer דוא"ל ms.lilach@gmail.com דוא"ל בר-אילן lilach.malatskey@biu.ac.il תחום הוראה רפואת המשפחה תחומי מחקר Lifestyle Medicine מרכזי מחקר הפקולטה לרפואה ע"ש עזריאלי, אוניברסיטת בר-אילן, צפת מחלקה משפחה מרפאה שירותי בריאות כללית, מחוז שרון\שומרון תאריך עדכון אחרון : </t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>"נעמה מימון"</t>
+          <t>"לילך מלצקי" רפואת משפחה</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -10044,87 +10077,95 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "lilach.malatskey@biu.ac.il", "confidence": 90, "source_url": "https://medicine.biu.ac.il/node/2836", "identity_url": "https://medicine.biu.ac.il/node/2836", "evidence": "ריאות התעסוקתית מניעת הטרדה מינית חדשות חדשות המחקר תקשורת מעבר לגליל כפר הסטודנטים בעמיעד יצירת קשר English הדפסה ד\"ר\n \n  לילך\n \n  מלצקי מרצה בכירה קליני Clinical Senior Lecturer דוא\"ל ms.lilach@gmail.com דוא\"ל בר-אילן lilach.malatskey@biu.ac.il תחום הוראה רפואת המשפחה תחומי מחקר Lifestyle Medicine מרכזי מחקר הפקולטה לרפואה ע\"ש עזריאלי, אוניברסיטת בר-אילן, צפת מחלקה משפחה מרפאה שירותי בריאות כללית, מחוז שרון\\שומרון תאריך עדכון אחרון : ", "matched_query": "\"לילך מלצקי\" רפואת משפחה", "extraction_method": "direct_text", "verification_schema_version": 3, "identity_name_verified": true, "identity_specialty_verified": true, "identity_evidence": "מלצקי לילך | הפקולטה לרפואה בגליל ע״ש עזריאלי מלצקי לילך | הפקולטה לרפואה בגליל ע״ש עזריאלי דילוג לתוכן העיקרי דילוג לתפריט ניווט ראשי תפריט משני ניוזלטר אוגוסט 2026 גלריית תמונות דרושים אירועים צור קשר אוניברסיטת בר-אילן English תפריט הפקולטה לרפואה בגליל ע״ש עזריאלי פייסבוק טוויטר tiktok יוטיוב Linkedin Instagram חיפוש חיפוש חיפוש אודות מי אנחנו חזון הפקולטה מרכזי רפואה מסונפים לפקולטה בקהילה \"פרחי רפואה\" תוכנית עבודות הגמר של גליליום תוכנית כוכבי הצפון הכירו את הבוגרים/ות שלנו לזכרם וזכרן In Memoriam ארכיון ניוזלטר לזכרם של אהרון ורחל דהאן הסגל הנהלת הפקולטה סגל אקדמי מחקרי סגל אקדמי קליני מינויים וקידומים אקדמיים קליניים סגל מינהלי הנהלת החינוך הרפואי והמחקר בעלי תפקידים מחקר ספריה תחום מומחיות מרכזי מחקר בפקולטה מכוני המחקר בבתי החולים טכנולוגיה ומכשור צוות היחידה ציוד היחידה המרכז הגנומי מאמרים Academic Publications לימודי רפואה M.D. לימודים לתואר דוקטור ברפואה (M.D.) - התכנית השש שנתית לימודים לתואר דוקטור ברפואה (M.D.) - התכנית הארבע שנתית לימודים לתואר דוקטור ברפואה (M.D.) - התכנית התלת שנתית תוכנית MD-PhD רום-גליל (רפואת"}]</t>
         </is>
       </c>
       <c r="S59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-09-04T05:17:30.924388+00:00</t>
+          <t>2026-09-11T18:38:12.718732+00:00</t>
         </is>
       </c>
       <c r="W59" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X59" t="n">
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>["https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fn.mh.mymwn.2025%2F", "https://www.facebook.com/SNMaesthetic/services/", "https://www.doctorita.co.il/experts/152626", "https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/", "https://medicaltop.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://medicaltop.co.il/%D7%94%D7%A6%D7%95%D7%95%D7%AA-%D7%A9%D7%9C%D7%A0%D7%95/", "https://medicaltop.co.il/wp-content/uploads/2024/04/אודות.jpg"]</t>
+          <t>["https://www.ima.org.il/MainSiteNew/StaticPage.aspx?Page=13564", "https://www.ima.org.il/Main/ViewContent.aspx?CategoryId=19239", "https://doctorindex.co.il/דוקטור-מלצקי-לילך/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%9E%D7%9C%D7%A6%D7%A7%D7%99-%D7%9C%D7%99%D7%9C%D7%9A/", "https://family.mednet.co.il/writer/דר-לילך-מלצקי/", "https://www.rofim.org.il/minisite/דר_לילך_מלצקי", "https://www.rofim.org.il/minisite/%D7%93%D7%A8_%D7%9C%D7%99%D7%9C%D7%9A_%D7%9E%D7%9C%D7%A6%D7%A7%D7%99", "https://www.shidurit-ltd.co.il/", "https://www.rofim.org.il/about", "https://www.rofim.org.il/Contact", "https://www.rofim.org.il/specialityPage/%D7%9E%D7%A8%D7%9B%D7%96_%D7%A8%D7%A4%D7%95%D7%90%D7%99", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%9E%D7%92%D7%90%D7%A8", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%91%D7%99%D7%AA_%D7%92%D7%93%D7%99", "https://www.rofim.org.il/minisite/%D7%90%D7%99%D7%99_%D7%90%D7%9C_%D7%A7%D7%9C%D7%99%D7%A0%D7%99%D7%A7", "https://medpage.co.il/doctors/לילך-מלצקי-978/", "https://medpage.co.il/doctors/%D7%9C%D7%99%D7%9C%D7%9A-%D7%9E%D7%9C%D7%A6%D7%A7%D7%99-978/", "https://medicine.biu.ac.il/node/2836", "https://medicine.biu.ac.il/contact", "https://medicine.biu.ac.il/node/26", "https://medicine.biu.ac.il/pre_clinical", "https://medicine.biu.ac.il/clinical_faculty", "https://medicine.biu.ac.il/node/6861", "https://medicine.biu.ac.il/node/6760"]</t>
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>3.252050431551207e+19</v>
+        <v>20415</v>
       </c>
       <c r="AE59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/</t>
+          <t>https://medicine.biu.ac.il/node/2836</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr"/>
       <c r="AJ59" t="inlineStr"/>
       <c r="AK59" t="inlineStr"/>
-      <c r="AL59" t="inlineStr"/>
-      <c r="AM59" t="inlineStr"/>
-      <c r="AN59" t="inlineStr"/>
-      <c r="AO59" t="inlineStr"/>
-      <c r="AP59" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL59" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM59" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN59" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>מלצקי לילך | הפקולטה לרפואה בגליל ע״ש עזריאלי מלצקי לילך | הפקולטה לרפואה בגליל ע״ש עזריאלי דילוג לתוכן העיקרי דילוג לתפריט ניווט ראשי תפריט משני ניוזלטר אוגוסט 2026 גלריית תמונות דרושים אירועים צור קשר אוניברסיטת בר-אילן English תפריט הפקולטה לרפואה בגליל ע״ש עזריאלי פייסבוק טוויטר tiktok יוטיוב Linkedin Instagram חיפוש חיפוש חיפוש אודות מי אנחנו חזון הפקולטה מרכזי רפואה מסונפים לפקולטה בקהילה "פרחי רפואה" תוכנית עבודות הגמר של גליליום תוכנית כוכבי הצפון הכירו את הבוגרים/ות שלנו לזכרם וזכרן In Memoriam ארכיון ניוזלטר לזכרם של אהרון ורחל דהאן הסגל הנהלת הפקולטה סגל אקדמי מחקרי סגל אקדמי קליני מינויים וקידומים אקדמיים קליניים סגל מינהלי הנהלת החינוך הרפואי והמחקר בעלי תפקידים מחקר ספריה תחום מומחיות מרכזי מחקר בפקולטה מכוני המחקר בבתי החולים טכנולוגיה ומכשור צוות היחידה ציוד היחידה המרכז הגנומי מאמרים Academic Publications לימודי רפואה M.D. לימודים לתואר דוקטור ברפואה (M.D.) - התכנית השש שנתית לימודים לתואר דוקטור ברפואה (M.D.) - התכנית הארבע שנתית לימודים לתואר דוקטור ברפואה (M.D.) - התכנית התלת שנתית תוכנית MD-PhD רום-גליל (רפואת</t>
+        </is>
+      </c>
+      <c r="AP59" t="inlineStr"/>
       <c r="AQ59" t="inlineStr"/>
       <c r="AR59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT59" t="b">
         <v>1</v>
       </c>
       <c r="AU59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
+          <t>PERSON</t>
         </is>
       </c>
     </row>
@@ -10137,12 +10178,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>תמר גרין</t>
+          <t>אופיר קדרון</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -10168,20 +10209,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>office@keshet-refua.co.il</t>
+          <t>editor@karmel.co.il</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://keshet-refua.co.il/doctors/dr-tamar-green/</t>
+          <t>https://www.karmel.co.il/%D7%A9%D7%95%D7%A0%D7%95%D7%AA/%D7%94%D7%A9%D7%9C%D7%99%D7%97%D7%95%D7%AA-%D7%94%D7%9E%D7%A9%D7%95%D7%AA%D7%A4%D7%AA-%D7%A9%D7%9C-%D7%93-%D7%A8-%D7%90%D7%95%D7%A4%D7%99%D7%A8-%D7%95%D7%90%D7%9E%D7%A8%D7%99-%D7%A7%D7%93%D7%A8%D7%95%D7%9F</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -10191,17 +10232,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>פיזיותרפיה אסתטיקה פודקסטים קליניקות וססיות להשכרה צור קשר זימון תור ד"ר תמר גרין מומחית לגינקולוגיה ומיילדות מעקב הריון, סקירת הריון מוקדמת ומאוחרת, בדיקות אולטרסאונד אבחנתיות, גיל המעבר ובדיקות גינקולוגיות 073-3214111 office@keshet-refua.co.il לזימון תור &gt; תחומי מומחיות מעקב הריון בדיקות אולטרהסאונד אבחנתיות שקיפות עורפית סקירת מערכות מוקדמת ומאוחרת מעקבי גדילה הדמיית אגן והדמיה תלת מימדית של הרחם טיפולי גינקולוגיה פרטית התקנים תוך רח</t>
+          <t>ניתן ליצור איתנו קשר ע"י מילוי ושליחת הטופס מטה או בקשר ישיר באמצעות: יצרת קשר טלפוני: 04-8396187, 054-5823934, 053-5823934 דוא"ל: editor@karmel.co.il</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>"תמר גרין"</t>
+          <t>"אופיר קדרון" רפואת משפחה</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>official_text</t>
+          <t>direct_mailto</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -10213,70 +10254,78 @@
         <v>1</v>
       </c>
       <c r="T60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-09-05T00:09:39.798497+00:00</t>
+          <t>2026-09-11T18:37:05.627099+00:00</t>
         </is>
       </c>
       <c r="W60" t="n">
+        <v>6</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z60" t="n">
         <v>2</v>
       </c>
-      <c r="X60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>6</v>
-      </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>["https://www.medreviews.co.il/provider/dr-green-tamar", "https://keshet-refua.co.il/doctors/dr-tamar-green/", "https://keshet-refua.co.il/about-us/", "https://keshet-refua.co.il/contact-us/", "https://keshet-refua.co.il/clinics-for-rent-sessional-clinics-for-rent/", "https://keshet-refua.co.il/about-us/#contact-keshet-medical-center", "https://keshet-refua.co.il/areas_of_expertise/child-psychology-clinic/", "https://keshet-refua.co.il/doctors/private-clinical-dietician-jerusalem/", "https://keshet-refua.co.il/contact-us/#contact-keshet-medical-center", "https://keshet-refua.co.il/clinics-for-rent-sessional-clinics-for-rent/#contact-keshet-medical-center", "https://keshet-refua.co.il/doctors/dr-tamar-green-private-gynecologist-in-jerusalem/", "https://wayzee.co.il/", "https://keshet-refua.co.il/treatments/menstrual-arrangement-before-the-wedding-private-womens-clinic-private-gynecologist/", "https://keshet-refua.co.il/areas_of_expertise/child-psychology-clinic/#contact-keshet-medical-center", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2F61558661827898%2F", "https://www.facebook.com/public/%D7%AA%D7%9E%D7%A8-%D7%92%D7%A8%D7%99%D7%9F/", "https://www.medreviews.co.il/provider/dr-green-tamar/treatment/gynecologist-clinic", "https://www.szmc.org.il/doctors/grin-tamar/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
+          <t>["https://www.migdalor-news.co.il/129451-2/", "https://nhn.co.il/tyvth-avtvmtyt-9/", "https://www.karmel.co.il/שונות/השליחות-המשותפת-של-ד-ר-אופיר-ואמרי-קדרון", "https://www.karmel.co.il/%D7%A9%D7%95%D7%A0%D7%95%D7%AA/%D7%94%D7%A9%D7%9C%D7%99%D7%97%D7%95%D7%AA-%D7%94%D7%9E%D7%A9%D7%95%D7%AA%D7%A4%D7%AA-%D7%A9%D7%9C-%D7%93-%D7%A8-%D7%90%D7%95%D7%A4%D7%99%D7%A8-%D7%95%D7%90%D7%9E%D7%A8%D7%99-%D7%A7%D7%93%D7%A8%D7%95%D7%9F", "https://www.karmel.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95", "https://www.karmel.co.il/%d7%90%d7%95%d7%93%d7%95%d7%aa%d7%99%d7%a0%d7%95"]</t>
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>3.245503093434371e+19</v>
+        <v>20415</v>
       </c>
       <c r="AE60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>https://keshet-refua.co.il/doctors/dr-tamar-green/</t>
+          <t>https://www.karmel.co.il/%D7%A9%D7%95%D7%A0%D7%95%D7%AA/%D7%94%D7%A9%D7%9C%D7%99%D7%97%D7%95%D7%AA-%D7%94%D7%9E%D7%A9%D7%95%D7%AA%D7%A4%D7%AA-%D7%A9%D7%9C-%D7%93-%D7%A8-%D7%90%D7%95%D7%A4%D7%99%D7%A8-%D7%95%D7%90%D7%9E%D7%A8%D7%99-%D7%A7%D7%93%D7%A8%D7%95%D7%9F</t>
         </is>
       </c>
       <c r="AI60" t="inlineStr"/>
       <c r="AJ60" t="inlineStr"/>
       <c r="AK60" t="inlineStr"/>
-      <c r="AL60" t="inlineStr"/>
-      <c r="AM60" t="inlineStr"/>
-      <c r="AN60" t="inlineStr"/>
-      <c r="AO60" t="inlineStr"/>
-      <c r="AP60" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL60" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM60" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN60" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>השליחות המשותפת של ד"ר אופיר ואמרי קדרון | פורטל הכרמל והצפון השליחות המשותפת של ד"ר אופיר ואמרי קדרון | פורטל הכרמל והצפון ראשי מבזקים פוליטיקה ספורט חינוך ותרבות חברה תכנון ובניה מפגעים עסקים כרמל Tube גלריית היום מדור נפטרים גולשים כותבים שונות צור קשר אודותינו חפש צור קשר אודותינו חפש דואר אדום הדפסה שלח כתבה הרשמה לדיוור תגובה לכתבה השליחות המשותפת של ד"ר אופיר ואמרי קדרון איך נראה בית שבו שני ההורים הם רופאים המלווים את הקהילה ברגעים הכי רגישים? ד"ר אופיר קדרון וד"ר אמרי קדרון הם בני זוג, הורים לשניים ומומחים לרפואת משפחה במאוחדת מחוז צפון. 25.03.2026 מאת: פורטל הכרמל והצפון השמע עצור -10s +10s 00:00 / 00:00 ד"ר אופיר וד"ר אמרי קדרון צילום עצמי רפואה, משפחה וזוגיות בימי מלחמה, השליחות המשותפת של ד"ר אופיר ואמרי קדרון בראיון חשוף הם מספרים על הדינמיקה בבית שבו הרפואה נוכחת תמיד, על האתגר לשמור על רצף טיפולי כשהמסגרות סגורות, ועל הרגעים שבהם דווקא ההיכרות העמוקה עם המטופל מצילה חיים ד"ר אופיר, ספרי קצת על העבודה שלכם במחוז "אני רופאת משפחה במאוחדת כמעט שש שנים ועובדת במרפאה בפרדס חנה-כרכור. בן הזוג שלי, ד"ר אמרי קדרון, רופא משפחה ועובד במרפאת</t>
+        </is>
+      </c>
+      <c r="AP60" t="inlineStr"/>
       <c r="AQ60" t="inlineStr"/>
       <c r="AR60" t="n">
         <v>1</v>
       </c>
       <c r="AS60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT60" t="b">
         <v>1</v>
@@ -10299,12 +10348,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>אבי צפריר</t>
+          <t>דלית דרימן-מדינה</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -10330,20 +10379,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>ivfrec@szmc.org.il</t>
+          <t>dalit@drdreman.co.il</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/tsafrir-avi/</t>
+          <t>https://www.drdreman.co.il/%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%9E%D7%98%D7%91%D7%95%D7%9C%D7%99%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -10353,17 +10402,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t xml:space="preserve">h عربيه Русский צרו קשר צרו קשר אזור אישי אזור אישי רופאים בשערי צדק ד"ר  אבי צפריר רופא בכיר Dr.  Avi Tsafrir התמחות: גינקולוגיה ויילוד תת התמחות: הפריה חוץ גופית תחומים נוספים: שימור פוריות פוריות הגבר פוריות האשה עוד ivfrec@szmc.org.il ivfrec@szmc.org.il נסיון מקצועי מומחה ביילוד ובגינקולוגיה משנת 2005 רופא בכיר להפריה חוץ גופית בשערי צדק משנת 2005 תפקידים ציבוריים חבר ועד האגודה הישראלית לחקר הפוריות משנת 2022 לימודים והכשרה פקולטה </t>
+          <t>drdremandalit@gmail.com</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>"אבי צפריר"</t>
+          <t>"דלית דרימן מדינה" רפואת משפחה (מרפאה OR "צור קשר" OR email OR מייל)</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>direct_mailto</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -10380,11 +10429,11 @@
       <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-09-03T20:26:52.799327+00:00</t>
+          <t>2026-09-10T18:44:56.180135+00:00</t>
         </is>
       </c>
       <c r="W61" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="X61" t="n">
         <v>0</v>
@@ -10405,14 +10454,14 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>["https://www.infomed.co.il/experts/73913/", "https://he.hadassah.org.il/doctor/dr-avi-tsafrir-gaadaabqaa2aaoiag4adaabyaa======/", "https://www.doctors.co.il/expert/obstetrics-and-gynecologists/80043972/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fbyzpryr%2F", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A6%D7%A4%D7%A8%D7%99%D7%A8-%D7%90%D7%91%D7%99/", "https://drtor.co.il/doctor/3910", "https://www.szmc.org.il/doctors/tsafrir-avi/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.clalit.co.il/he/sefersherut/pages/doctordetails.aspx", "https://docsrated.com/doctors/אבי-צפריר", "https://www.doctorita.co.il/experts/44804"]</t>
+          <t>["https://www.drdreman.co.il/מחלות-מטבוליות/", "https://www.drdreman.co.il/%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%9E%D7%98%D7%91%D7%95%D7%9C%D7%99%D7%95%D7%AA/", "https://www.drdreman.co.il/about/", "https://www.drdreman.co.il/contact/", "https://www.drdreman.co.il/", "https://www.doctorita.co.il/experts/52215", "https://www.drdreman.co.il/%D7%93%D7%A3-%D7%91%D7%99%D7%AA/", "https://www.other-medicine.co.il/author/dalitdrdreman-co-il/", "https://www.izi.co.il/site/6f2c026c8d", "https://www.infomed.co.il/experts/78145/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%93%D7%A8%D7%99%D7%9E%D7%9F-%D7%9E%D7%93%D7%99%D7%A0%D7%94-%D7%93%D7%9C%D7%99%D7%AA/", "https://www.findglocal.com/IL/Unknown/106988607393615/ד״ר-דלית-דרימן-רפואה-פונקציונלית-ואינטגרטיבית"]</t>
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>4.322725496669801e+19</v>
+        <v>9.997539589084663e+19</v>
       </c>
       <c r="AE61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF61" t="n">
         <v>0</v>
@@ -10420,25 +10469,34 @@
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/tsafrir-avi/</t>
+          <t>https://www.drdreman.co.il/%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%9E%D7%98%D7%91%D7%95%D7%9C%D7%99%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="AI61" t="inlineStr"/>
       <c r="AJ61" t="inlineStr"/>
       <c r="AK61" t="inlineStr"/>
-      <c r="AL61" t="inlineStr"/>
-      <c r="AM61" t="inlineStr"/>
-      <c r="AN61" t="inlineStr"/>
-      <c r="AO61" t="inlineStr"/>
-      <c r="AP61" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL61" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM61" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN61" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>מחלות מטבוליות - ד"ר דלית דרימן-מדינה מחלות מטבוליות - ד"ר דלית דרימן-מדינה דלג לתוכן אודות כיצד נוכל לעזור במה אנחנו מטפלים מפגשים ועלויות שאלות ותשובות מאמרים סרטונים מהתקשורת צור קשר אודות כיצד נוכל לעזור במה אנחנו מטפלים מפגשים ועלויות שאלות ותשובות מאמרים סרטונים מהתקשורת צור קשר 0546033755 חיפוש חיפוש אודות כיצד נוכל לעזור במה אנחנו מטפלים מפגשים ועלויות שאלות ותשובות מאמרים סרטונים מהתקשורת צור קשר אודות כיצד נוכל לעזור במה אנחנו מטפלים מפגשים ועלויות שאלות ותשובות מאמרים סרטונים מהתקשורת צור קשר חיפוש חיפוש מחלות מטבוליות הפרעות מטבוליות, עודף משקל, סוכרת בחירות מזון גרועות, העדר מרכיבי מזון חיוניים, רעלנים, מתח נפשי, ודלקת כרונית גורמים לחוסר איזון מטבולי ולמחלות שמהוות את מרבית המחלות הכרוניות כיום. במה אנו מטפלים? מחלות לב יתר לחץ דם עודף משקל והשמנה תסמונת מטבולית סוכרת הפרעות בכולסטרול ושומני הדם איך זה עובד? אנחנו עורכים למטופלים שלנו בירור נרחב ע״י בדיקות מעבדה מתקדמות כולל בדיקות מיוחדות לשומני הדם שאינן מבוצעות באופן סטנדרטי בקופות החולים.
+בטיפול שלנו אנו מתבססים על המזון ומרכיבי התזונה ככלים הטיפוליים הרא</t>
+        </is>
+      </c>
+      <c r="AP61" t="inlineStr"/>
       <c r="AQ61" t="inlineStr"/>
       <c r="AR61" t="n">
         <v>1</v>
       </c>
       <c r="AS61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT61" t="b">
         <v>1</v>
@@ -10461,7 +10519,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>אירינה דורפמן אלמוג</t>
+          <t>מוטי אלמוג</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10471,7 +10529,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -10492,7 +10550,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>dr.irenadorfman@gmail.com</t>
+          <t>shluvim@shluvim.com</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -10501,11 +10559,11 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
+          <t>https://shluvim.com/tech/%D7%93%D7%A8-%D7%9E%D7%95%D7%98%D7%99-%D7%90%D7%9C%D7%9E%D7%95%D7%92/</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -10515,86 +10573,94 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>מוג אירינה כרטיס עסק: ד"ר דורפמן אלמוג אירינה » תחום פעילות: בריאות וספורט » רופא » תאור העסק: רופאת משפחה עצמאית קופת חולים לאומית. » איש קשר: אירנה דורפמן » טלפונים: טלפון: 077-7997456 נייד: 054-4616457 » אתר: » מייל: dr.irenadorfman@gmail.com » כתובת: בן גוריון 123 יהוד, מיקוד: 56209 כלים מחשבונים לעסקים מדריכי ניהול עסק, הקמת עסק נושאי האתר הנהלת חשבונות הפקת חשבוניות חשבונית אלקטרונית ניהול לקוחות שותפים עסקיים אילת סיטי - מדריך הע</t>
+          <t>shluvim@shluvim.com</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>"אירינה דורפמן אלמוג"</t>
+          <t>"מוטי אלמוג" רפואת משפחה</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>direct_mailto</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>[{"email": "info@flex.co.il", "confidence": 80, "source_url": "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "identity_url": "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "evidence": "info@flex.co.il", "matched_query": "\"אירינה דורפמן אלמוג\"", "extraction_method": "linked_mailto"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S62" t="n">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
         <v>2</v>
-      </c>
-      <c r="T62" t="n">
-        <v>0</v>
       </c>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-09-04T19:17:26.299485+00:00</t>
+          <t>2026-09-11T18:38:23.366800+00:00</t>
         </is>
       </c>
       <c r="W62" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
         <v>5</v>
       </c>
       <c r="Z62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>["https://www.dunsguide.co.il/C7195b21475cb11a3e5b86def04a3e20c_רופאים/דורפמן_אלמוג_אירינה/", "https://medpage.co.il/doctors/%D7%90%D7%99%D7%A8%D7%A0%D7%94-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-20871/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94/", "https://www.beok.co.il/doctors/Doctors-129241/", "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "https://www.flex.co.il/100_General/005_GeneralPages/006_About.aspx", "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "https://www.flex.co.il/100_General/900_DifferentStuff/900_ForTheCommunity.aspx"]</t>
+          <t>["https://www.doctorita.co.il/experts/131767", "https://drtor.co.il/doctor/23080", "https://drtor.co.il/cdn-cgi/l/email-protection#4c2f2322382d2f380c283e38233e622f23622520", "https://docsrated.com/doctors/מוטי-אלמוג", "https://medpage.co.il/doctors/מוטי-אלמוג-12172037/", "https://medpage.co.il/doctors/%D7%9E%D7%95%D7%98%D7%99-%D7%90%D7%9C%D7%9E%D7%95%D7%92-12172037/", "https://shluvim.com/tech/דר-מוטי-אלמוג/", "https://shluvim.com/tech/%D7%93%D7%A8-%D7%9E%D7%95%D7%98%D7%99-%D7%90%D7%9C%D7%9E%D7%95%D7%92/", "https://brandale.co.il/", "https://shluvim.com/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%9B%D7%9C%D7%99%D7%9D-%D7%A9%D7%9C%D7%95%D7%91%D7%99%D7%9D/"]</t>
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>3.51258506998755e+19</v>
+        <v>20415</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
+          <t>https://shluvim.com/tech/%D7%93%D7%A8-%D7%9E%D7%95%D7%98%D7%99-%D7%90%D7%9C%D7%9E%D7%95%D7%92/</t>
         </is>
       </c>
       <c r="AI62" t="inlineStr"/>
       <c r="AJ62" t="inlineStr"/>
       <c r="AK62" t="inlineStr"/>
-      <c r="AL62" t="inlineStr"/>
-      <c r="AM62" t="inlineStr"/>
-      <c r="AN62" t="inlineStr"/>
-      <c r="AO62" t="inlineStr"/>
-      <c r="AP62" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL62" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM62" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN62" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>ד"ר מוטי אלמוג - כלים שלובים ד"ר מוטי אלמוג - כלים שלובים דילוג לתוכן אודות פסיכותרפיה אנתרופוסופית מהי פסיכותרפיה אנתרופוסופית? ד”ר שטיינר והאנתרופוסופיה הממד הרוחני בטיפול הנפשי תוכניות הלימוד סמינרים וימי עיון עולם תוכן הרצאות מצולמות מאמרים מתוך כתביו של ר. שטיינר משבי רוח ספרים דיגיטליים מרכז טיפולי צרו קשר אודות פסיכותרפיה אנתרופוסופית מהי פסיכותרפיה אנתרופוסופית? ד”ר שטיינר והאנתרופוסופיה הממד הרוחני בטיפול הנפשי תוכניות הלימוד סמינרים וימי עיון עולם תוכן הרצאות מצולמות מאמרים מתוך כתביו של ר. שטיינר משבי רוח ספרים דיגיטליים מרכז טיפולי צרו קשר ד"ר מוטי אלמוג רופא משפחה, בוגר ההכשרה של רפואה אנתרופוסופית באנגליה. רופא של בית ספר וולדורף בפרדס חנה, מלמד בסמינרים שונים העוסקים בתחום האנתרופוסופיה. Facebook Youtube ניווט באתר אודות מהי פסיכותרפיה אנתרופוסופית? מרכז טיפולי צרו קשר תכניות הלימוד פסיכותרפיה אנתרופוסופית – תוכנית הכשרה תלת שנתית למטפלים בעלי תואר שני טיפולי תוכנית הסבה לאקדמאים – פסיכותרפיה אנתרופוסופית תוכנית לטיפול משפחתי וזוגי בגישה אנתרופוסופית תוכנית לטיפול בילדים, נוער והורות פרטי יצירת קשר</t>
+        </is>
+      </c>
+      <c r="AP62" t="inlineStr"/>
       <c r="AQ62" t="inlineStr"/>
       <c r="AR62" t="n">
         <v>1</v>
@@ -10606,11 +10672,11 @@
         <v>1</v>
       </c>
       <c r="AU62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>PERSON</t>
+          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
       </c>
     </row>
@@ -10623,7 +10689,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>אלון שלב</t>
+          <t>עדי ניסימוב</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10633,7 +10699,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -10654,7 +10720,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>alonshalev31@gmail.com</t>
+          <t>nir@niroleen.com</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -10663,11 +10729,11 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://pain.coi.co.il/</t>
+          <t>https://www.niroleen.com/cosmatisohin-doktor-adi.html</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -10677,12 +10743,15 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>הודעה לבעלי האתר תקופת הניסיון הסתיימה, יש ליצור מנוי דרך ממשק ניהול האתר. האתר נכנס לרשימת המחיקה ויימחק בקרוב לחץ כאן אם אינך זוכר את כתובת ממשק ניהול האתר שלך. דר אלון שלב - רופא כאב טלפון: 054-6221105 מייל: alonshalev31@gmail.com כתובת: ילדי טהרן 8, ראשון לציון ד"ר אלון שלב מומחה ברפואת המשפחה רופא כאב דף הבית אודות צור קשר אל תחכו - הזמינו תור לרופא עוד היום.. לייעוץ ראשוני ללא עלות והזמנת תורים מלאו פרטים או התקשרו: 05462</t>
+          <t>א או תחליף להמלצת רפוא מומחה. האתר מוגש כערך מוסף בלבד. למען הסר ספק, האחריות על יישום ההמלצות הנובעות מן האתר הוא על הקוראים בלבד G.L.R.N I.T.B ISRAEL LTD
+אהוד מנור 2, באר יעקוב 7031706
+מוקד ברורים ושאלות: 050-648-4301
+nir@niroleen.com</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>"אלון שלב"</t>
+          <t>"עדי ניסימוב" רפואת משפחה</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -10699,64 +10768,72 @@
         <v>1</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-09-04T19:37:15.755041+00:00</t>
+          <t>2026-09-11T18:38:55.179965+00:00</t>
         </is>
       </c>
       <c r="W63" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X63" t="n">
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>["https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr.shalev.pain%2F&amp;is_from_rle", "https://www.bgu.ac.il/people/shalevn/", "https://www.bgu.ac.il/en/people/shalevn/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fdr.shalev.pain%2F", "https://www.medreviews.co.il/search/pain-management/center/rishon-lezion", "https://pain.coi.co.il/", "https://pain.coi.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA.htm", "https://pain.coi.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8.htm"]</t>
+          <t>["https://www.meuhedet.co.il/poi/Doctors/000964410152100004000000000000_0", "https://www.facebook.com/newshaifakrayot.net/posts/דר-עדי-ניסימוב-מומחית-ברפואת-משפחה-ורופאה-אחראית-בממרכז-מאי-של-מאוחדת-מספרת-על-ה/4719279038101600/", "https://www.facebook.com/newshaifakrayot.net/posts/%D7%93%D7%A8-%D7%A2%D7%93%D7%99-%D7%A0%D7%99%D7%A1%D7%99%D7%9E%D7%95%D7%91-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%AA-%D7%91%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%9E%D7%A9%D7%A4%D7%97%D7%94-%D7%95%D7%A8%D7%95%D7%A4%D7%90%D7%94-%D7%90%D7%97%D7%A8%D7%90%D7%99%D7%AA-%D7%91%D7%9E%D7%9E%D7%A8%D7%9B%D7%96-%D7%9E%D7%90%D7%99-%D7%A9%D7%9C-%D7%9E%D7%90%D7%95%D7%97%D7%93%D7%AA-%D7%9E%D7%A1%D7%A4%D7%A8%D7%AA-%D7%A2%D7%9C-%D7%94/4719279038101600/", "https://drtor.co.il/doctor/10319", "https://drtor.co.il/cdn-cgi/l/email-protection#dfbcb0b1abbebcab9fbbadabb0adf1bcb0f1b6b3", "https://doctorindex.co.il/דוקטור-ניסימוב-עדי/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A0%D7%99%D7%A1%D7%99%D7%9E%D7%95%D7%91-%D7%A2%D7%93%D7%99/", "https://www.niroleen.com/cosmatisohin-doktor-adi.html", "https://www.niroleen.com/contactus.html"]</t>
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>3.51258506998755e+19</v>
+        <v>20415</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>https://pain.coi.co.il/</t>
+          <t>https://www.niroleen.com/cosmatisohin-doktor-adi.html</t>
         </is>
       </c>
       <c r="AI63" t="inlineStr"/>
       <c r="AJ63" t="inlineStr"/>
       <c r="AK63" t="inlineStr"/>
-      <c r="AL63" t="inlineStr"/>
-      <c r="AM63" t="inlineStr"/>
-      <c r="AN63" t="inlineStr"/>
-      <c r="AO63" t="inlineStr"/>
-      <c r="AP63" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL63" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM63" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN63" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>בוטוקס בחיפה-דוקטור עדי ניסימוב בוטוקס בחיפה-דוקטור עדי ניסימוב ‎ הזרקות בוטוקס בחיפה - ד"ר עדי ניסימוב M.D מחפשים הזרקות בוטוקס בחיפה? הכירו את ד"ר עדי ניסימוב בעלת  מרפאת "טיפה של קסם" לאסתטיקה ובריאות העור, 1 שלום, שמי ד"ר עדי ניסימוב, אני רופאת משפחה בהתמחותי ומעל ל- 6 שנים שאני מטפלת ברפואה אסתטית אחרי השתלמות מקיפה במכללה לאסתטיקה של ד"ר קרופניק. מה משך אותי לתחום? להבדיל מהטיפולים המתמשכים ברפואת המשפחה, כאן אני יכולה לראות תוצאות מיידיות ולקבל פידבק חיובי על הטיפולים שלי באופן מידי וזה תענוג! רפואה אסתטית נותנת היום מענה הולם ומהיר למראה צעיר ורענן ללא צורך בניתוח זה גם תחום שמתקדם במהירות, לכן אני דואגת להשתלם ולהשתתף בכנסים, השתלמויות וסדנאות לטיפולים חדשנים ברפואה אסתטית. ואלו טיפולים תוכלו לקבל אצלי? במרפאה האסתטית שלי תוכלו להנות ממגוון טיפולים הכוללים הזרקת בוטוקס, החזרת נפחים ומילוי קמטים, מילוי ועיצוב שפתיים, מזותרפיה, מזוחוטים, טיפולים להזעת יתר, ליפותרפיה, פילינג רפואי, טיפול לאקנה ולצלקות פוסט-אקנה. ומה לגבי שיטת העבודה שלי? לכל מטופלת אני תופרת את החליפה מבחינת הגיל מבחינת סוג העור והתוצאה, חשוב ל</t>
+        </is>
+      </c>
+      <c r="AP63" t="inlineStr"/>
       <c r="AQ63" t="inlineStr"/>
       <c r="AR63" t="n">
         <v>1</v>
@@ -10768,11 +10845,11 @@
         <v>1</v>
       </c>
       <c r="AU63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>PERSON</t>
+          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
       </c>
     </row>
@@ -10785,7 +10862,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>אמיר צבעוני</t>
+          <t>צופיה אילת צנעני</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10795,7 +10872,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -10816,7 +10893,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>healtms@gmail.com</t>
+          <t>sophia.eilat-tsanani@biu.ac.il</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -10825,11 +10902,11 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>https://www.drzivony.co.il/</t>
+          <t>https://medicine.biu.ac.il/node/525</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -10839,12 +10916,15 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>"ר אמיר צבעוני ד"ר אמיר צבעוני רופא משפחה מומחה העוסק בטיפול בכאב כרוני בגישת גוף-נפש ללא שימוש בתרופות או בפרוצדורות רפואיות. הטיפול מבוסס מחקר בתחום מדעי המח והכאב. ניתן לקרוא עליי עוד ב דף האודות . טלפון: 051-2303120 healtms@gmail.com קליניקה בגבעת עדה (סמוך לבנימינה) ניתן ליצור איתי קשר גם ב דף יצירת הקשר פוסטים אחרונים על הענק הירוק והדחקת רגשות לאותת עם המגבים רגישות יתר לאחר פציעה אזהרת טריגר בקשת סליחה מעצמי חפש: חיפוש בית אודות</t>
+          <t>ליל כפר הסטודנטים בעמיעד יצירת קשר English הדפסה יועצת הדקנית לרפואה בקהילה פרופ'
+  צופיה
+  אילת- צנעני Clinical Associate Professor פרופ' חבר קליני יועצת הדקנית לרפואה בקהילה דוא"ל eilat@clalit.org.il דוא"ל בר-אילן sophia.eilat-tsanani@biu.ac.il תחום הוראה רפואת המשפחה מחלקה משפחה מרפאה שירותי בריאות כללית, מחוז צפון תאריך עדכון אחרון : 15/06/2026 כניסה לעורכי האתר כל הזכויות שמורות:
+הפקולטה לרפואה בגליל ע״ש עזריאלי | אוניברסיטת ב</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>"אמיר צבעוני"</t>
+          <t>"צופיה אילת צנעני" רפואת משפחה</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -10861,16 +10941,16 @@
         <v>1</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-09-03T23:00:56.706890+00:00</t>
+          <t>2026-09-11T18:39:12.888907+00:00</t>
         </is>
       </c>
       <c r="W64" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X64" t="n">
         <v>0</v>
@@ -10886,39 +10966,47 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>["https://www.drzivony.co.il/", "https://www.drzivony.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
+          <t>["https://medicine.biu.ac.il/node/525", "https://medicine.biu.ac.il/contact", "https://medicine.biu.ac.il/node/26", "https://medicine.biu.ac.il/pre_clinical", "https://medicine.biu.ac.il/clinical_faculty", "https://medicine.biu.ac.il/node/6861", "https://medicine.biu.ac.il/node/6760"]</t>
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>3.51221446594978e+19</v>
+        <v>20415</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>https://www.drzivony.co.il/</t>
+          <t>https://medicine.biu.ac.il/node/525</t>
         </is>
       </c>
       <c r="AI64" t="inlineStr"/>
       <c r="AJ64" t="inlineStr"/>
       <c r="AK64" t="inlineStr"/>
-      <c r="AL64" t="inlineStr"/>
-      <c r="AM64" t="inlineStr"/>
-      <c r="AN64" t="inlineStr"/>
-      <c r="AO64" t="inlineStr"/>
-      <c r="AP64" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL64" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM64" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN64" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>אילת- צנעני צופיה | הפקולטה לרפואה בגליל ע״ש עזריאלי אילת- צנעני צופיה | הפקולטה לרפואה בגליל ע״ש עזריאלי דילוג לתוכן העיקרי דילוג לתפריט ניווט ראשי תפריט משני ניוזלטר אוגוסט 2026 גלריית תמונות דרושים אירועים צור קשר אוניברסיטת בר-אילן English תפריט הפקולטה לרפואה בגליל ע״ש עזריאלי פייסבוק טוויטר tiktok יוטיוב Linkedin Instagram חיפוש חיפוש חיפוש אודות מי אנחנו חזון הפקולטה מרכזי רפואה מסונפים לפקולטה בקהילה "פרחי רפואה" תוכנית עבודות הגמר של גליליום תוכנית כוכבי הצפון הכירו את הבוגרים/ות שלנו לזכרם וזכרן In Memoriam ארכיון ניוזלטר לזכרם של אהרון ורחל דהאן הסגל הנהלת הפקולטה סגל אקדמי מחקרי סגל אקדמי קליני מינויים וקידומים אקדמיים קליניים סגל מינהלי הנהלת החינוך הרפואי והמחקר בעלי תפקידים מחקר ספריה תחום מומחיות מרכזי מחקר בפקולטה מכוני המחקר בבתי החולים טכנולוגיה ומכשור צוות היחידה ציוד היחידה המרכז הגנומי מאמרים Academic Publications לימודי רפואה M.D. לימודים לתואר דוקטור ברפואה (M.D.) - התכנית השש שנתית לימודים לתואר דוקטור ברפואה (M.D.) - התכנית הארבע שנתית לימודים לתואר דוקטור ברפואה (M.D.) - התכנית התלת שנתית תוכנית MD-PhD רום-גליל</t>
+        </is>
+      </c>
+      <c r="AP64" t="inlineStr"/>
       <c r="AQ64" t="inlineStr"/>
       <c r="AR64" t="n">
         <v>1</v>
@@ -10947,17 +11035,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>בתיה קורנבוים</t>
+          <t>ד"ר ארבל אריאל</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>family_doctor</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -10967,31 +11055,31 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>ima</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>batyakornboim@gmail.com</t>
+          <t>info@eryaveladan.com</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://www.dr-batya-kornboim.com/</t>
+          <t>https://www.eryaveladan.com/</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -11001,12 +11089,12 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>שקל בחיפה אודות חוות דעת יצירת קשר כתבות ופרסומים תפריט ד״ר בתיה קורנבוים - מומחית ברפואת משפחה ורפואת השמנה [תיאור המרפאה יתווסף בהמשך] טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו חיפה 3570901 IL 052-567-1100 batyakornboim@gmail.com התמחויות רפואיות עיקריות: [פירוט תחומי הטיפול יתווסף בהמשך] מידע מעשי: יצירת קשר: טלפון 052-567-1100 או וואטסאפ 052-567-1100 מיקום: טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו , חיפה סוג</t>
+          <t>החזיר את האיזון. קראי עוד השאירי פרטים ונחזור אלייך בהקדם שם מלא טלפון דוא״ל שליחה רופא נשים מומחה מחלות העריה והלדן ​ ד״ר אריאל ארבל לקביעת תור: 077-2311245 כתובת המרפאה: בית למומחים ברפואה - בורוכוב 54, גבעתיים דוא״ל: info@eryaveladan.com bottom of page</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>"בתיה קורנבוים"</t>
+          <t>"ארבל אריאל"</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -11016,11 +11104,11 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "info@eryaveladan.com", "confidence": 88, "source_url": "https://www.eryaveladan.com/", "identity_url": "https://www.eryaveladan.com/", "evidence": "החזיר את האיזון. קראי עוד השאירי פרטים ונחזור אלייך בהקדם שם מלא טלפון דוא״ל שליחה רופא נשים מומחה מחלות העריה והלדן ​ ד״ר אריאל ארבל לקביעת תור: 077-2311245 כתובת המרפאה: בית למומחים ברפואה - בורוכוב 54, גבעתיים דוא״ל: info@eryaveladan.com bottom of page", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}, {"email": "office@b54.co.il", "confidence": 88, "source_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "identity_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "evidence": "ד\"ר אריאל ארבל - מרפאת מומחים B54, הבית למומחים ברפואה בגבעתיים דילוג לתוכן B54 03-757-8562 office@b54.co.il א׳-ה׳ 8:00-20:00 | ו׳ 08:00-13:00 Facebook-f Youtube Google דף הבית אודות B54 מי אנחנו שכונת בורוכוב מרכז Friendly הנהלת המרפאה שאלות נפוצות הרופאים שלנו קליניקה להשכרה מידע למטופל שאלות ותשובות הורדת טפ", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}]</t>
         </is>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T65" t="n">
         <v>0</v>
@@ -11028,23 +11116,23 @@
       <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-09-03T23:52:50.148875+00:00</t>
+          <t>2026-09-03T20:23:48.175654+00:00</t>
         </is>
       </c>
       <c r="W65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X65" t="n">
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z65" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
@@ -11053,11 +11141,11 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>["https://www.dr-batya-kornboim.com/", "https://www.dr-batya-kornboim.com/#%D7%90%D7%95%D7%93%D7%95%D7%AA"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598", "https://www.facebook.com/people/%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%90%D7%A8%D7%91%D7%9C/pfbid0NCmi7FZgUyu2EVV5mLJMpBfndXiDQPqseAxUny7KWHsDvucQScUiVnBeMef3ByStl/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%90%D7%A8%D7%91%D7%9C-%D7%90%D7%A8%D7%99%D7%90%D7%9C/", "https://www.eryaveladan.com/", "https://www.eryaveladan.com/%D7%90%D7%95%D7%93%D7%95%D7%AA-1", "https://www.b54.co.il/doctors/dr-arbel-ariel/", "https://www.medreviews.co.il/provider/dr-arbel-ariel", "https://www.b54.co.il/about/", "https://www.b54.co.il/about", "https://www.b54.co.il/about#borohov", "https://www.b54.co.il/about#Friendly", "https://www.b54.co.il/about#management", "https://www.b54.co.il/about#qa", "https://www.medreviews.co.il/provider/dr-arbel-ariel#contact-doctor-section", "https://www.medreviews.co.il/contact-us", "https://www.medreviews.co.il/about", "https://woman.mymc.co.il/doctors/dr-arielarbel/", "https://www.ima.org.il/DoctorsIndex/Default.aspx", "https://www.infomed.co.il/experts/145655/", "https://www.ami.org.il/blog/families/not-the-same-shirley"]</t>
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>3.51221446594978e+19</v>
+        <v>1.296817648966072e+20</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -11068,7 +11156,7 @@
       <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>https://www.dr-batya-kornboim.com/</t>
+          <t>https://www.eryaveladan.com/</t>
         </is>
       </c>
       <c r="AI65" t="inlineStr"/>
@@ -11083,7 +11171,7 @@
       </c>
       <c r="AQ65" t="inlineStr"/>
       <c r="AR65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS65" t="b">
         <v>0</v>
@@ -11092,11 +11180,11 @@
         <v>1</v>
       </c>
       <c r="AU65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>PERSON</t>
+          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
       </c>
     </row>
@@ -11109,17 +11197,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>שלומית שדמון</t>
+          <t>יעל כהן</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>family_doctor</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -11140,20 +11228,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>shlomitshadmon@gmail.com</t>
+          <t>office@elitemed.co.il</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
+          <t>https://elitemed.co.il/doctors/dr-yael-cohen-hebrew/</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -11163,12 +11251,12 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>ם ופעילויות כנסים והשתלמויות הרצאות מהכנסים מטפלי.ות איט"ם מטפלי.ות איט"ם פיזיותרפיסטים.ית איט"ם מרפאות ציבוריות הצטרפות והתמחות צור קשר פרטי התקשרות טלפון 054-9145177 כתובת אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אימייל shlomitshadmon@gmail.com שדמון שלומית (MD) – תל אביב מקצוע:  רופאת משפחה, מוסמכת ביעוץ וטיפול מיני. התמחות: מטפלת מינית איזור טיפול: תל אביב אודותי אני רופאת משפחה ותיקה, מדריכה קלינית ומרצה בנושאי בריאות האישה, מיניות ה</t>
+          <t>ד"ר יעל כהן - elitemed.co.il דלג לתוכן Facebook Instagram Whatsapp Office@elitemed.co.il 073-321-4181 בית אודות רופאים שירותים רפואיים אולטרסאונד וביופסיות אוסטאופתיה אורולוגיה אורתופדיה אלרגיה ואימונולגיה אנדוקרינולוגיה סוכרת וירידה במשקל אסתטיקה אף אוזן גרון גינקולוגיה ובריאות האישה ג</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>"שלומית שדמון"</t>
+          <t>"יעל כהן" יילוד</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -11178,71 +11266,79 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "identity_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "evidence": "mail.com אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"שלומית שדמון\"", "extraction_method": "direct_text"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-09-04T15:25:57.140597+00:00</t>
+          <t>2026-09-10T18:33:08.486465+00:00</t>
         </is>
       </c>
       <c r="W66" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="X66" t="n">
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Z66" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>["https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA/", "https://moonbellboutique.com/index/%D7%93%D7%A8-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%A9%D7%93%D7%9E%D7%95%D7%9F/", "https://moonbellboutique.com/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/", "https://www.infomed.co.il/experts/145161/", "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
+          <t>["https://elitemed.co.il/doctors/dr-yael-cohen-hebrew/", "https://elitemed.co.il/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%A4%D7%95%D7%90%D7%99-%D7%A4%D7%A8%D7%98%D7%99-%D7%91%D7%9E%D7%95%D7%93%D7%99%D7%A2%D7%99%D7%9F/", "https://elitemed.co.il/pain-clinic-modiin/", "https://elitemed.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://elitemed.co.il/%d7%90%d7%95%d6%b9%d7%93%d7%95%d6%b9%d7%aa/", "https://medpage.co.il/doctors/יעל-כהן-23202/", "https://medpage.co.il/doctors/%D7%99%D7%A2%D7%9C-%D7%9B%D7%94%D7%9F-23202/", "https://www.facebook.com/ichilovmedical/posts/תכירו-את-פרופ-יעל-כהןמנהלת-יחידת-המיאלומה-במערך-ההמטולוגי-של-איכילוב-ואחת-מהרופא/1288268913309017/", "https://www.facebook.com/ichilovmedical/videos/%D7%AA%D7%9B%D7%99%D7%A8%D7%95-%D7%90%D7%AA-%D7%A4%D7%A8%D7%95%D7%A4-%D7%99%D7%A2%D7%9C-%D7%9B%D7%94%D7%9F%D7%9E%D7%A0%D7%94%D7%9C%D7%AA-%D7%99%D7%97%D7%99%D7%93%D7%AA-%D7%94%D7%9E%D7%99%D7%90%D7%9C%D7%95%D7%9E%D7%94-%D7%91%D7%9E%D7%A2%D7%A8%D7%9A-%D7%94%D7%94%D7%9E%D7%98%D7%95%D7%9C%D7%95%D7%92%D7%99-%D7%A9%D7%9C-%D7%90%D7%99%D7%9B%D7%99%D7%9C%D7%95%D7%91-%D7%95%D7%90%D7%97%D7%AA-%D7%9E%D7%94%D7%A8%D7%95%D7%A4%D7%90/981973987039095/", "https://www.medico.co.il/doctors/פרופ-יעל-כהן/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%99%D7%A2%D7%9C-%D7%9B%D7%94%D7%9F/", "https://www.medico.co.il/doctors/", "https://www.medico.co.il/doctors/%d7%a4%d7%a8%d7%95%d7%a4-%d7%99%d7%a2%d7%9c-%d7%9b%d7%94%d7%9f/", "https://www.tasmc.org.il/doctorssearch/dr/cohen-yael/", "https://www.szmc.org.il/doctors/cohen-yael/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.vimed.co.il/users/0918fba4-bd6a-4310-ab8f-b51cab0b8f80", "https://www.meuhedet.co.il/poi/ParamedicalDoctors/000189680918100097000000000000_0", "https://www.medreviews.co.il/provider/dr-cohen-yael"]</t>
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>3.243155934528492e+19</v>
+        <v>9.999763213543884e+19</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
+          <t>https://elitemed.co.il/doctors/dr-yael-cohen-hebrew/</t>
         </is>
       </c>
       <c r="AI66" t="inlineStr"/>
       <c r="AJ66" t="inlineStr"/>
       <c r="AK66" t="inlineStr"/>
-      <c r="AL66" t="inlineStr"/>
-      <c r="AM66" t="inlineStr"/>
-      <c r="AN66" t="inlineStr"/>
-      <c r="AO66" t="inlineStr"/>
-      <c r="AP66" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL66" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM66" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN66" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>ד"ר יעל כהן - elitemed.co.il ד"ר יעל כהן - elitemed.co.il דלג לתוכן Facebook Instagram Whatsapp Office@elitemed.co.il 073-321-4181 בית אודות רופאים שירותים רפואיים אולטרסאונד וביופסיות אוסטאופתיה אורולוגיה אורתופדיה אלרגיה ואימונולגיה אנדוקרינולוגיה סוכרת וירידה במשקל אסתטיקה אף אוזן גרון גינקולוגיה ובריאות האישה גסטרואנטרולוגיה גֵרִיאַטרִיָה דרמטולגיה המטולוגיה כלי דם ורדיולוגיה פולשנית התמחויות טיפוליות ושיקומיות כירורגיה כירורגיה פלסטית מרפאת כאב נוירולוגיה, קשב וריכוז והתפתחות הילד נפרולוגיה ויתר לחץ דם סקירות מערכות ואקו לב עובר עיניים פודיאטריה כירורגית וכף רגל פולמונולוגיה ורפואת שינה פסיכיאטריה פרוקטולוגיה וכירורגיה קולורקטלית קרדיולוגיה ואלקטרופיזיולוגיה ראומטולוגיה רפואת ילדים מומחית רפואת ספורט ופיזיותרפיה רפואה תעסוקתית תזונה קלינית ודיאטה תור דחוף  24-48 שעות צור קשר השכרת קליניקה במודיעין שירות VIP שירותים מידע רפואי בית אודות רופאים שירותים רפואיים אולטרסאונד וביופסיות אוסטאופתיה אורולוגיה אורתופדיה אלרגיה ואימונולגיה אנדוקרינולוגיה סוכרת וירידה במשקל אסתטיקה אף אוזן גרון גינקולוגיה ובריאות האישה גס</t>
+        </is>
+      </c>
+      <c r="AP66" t="inlineStr"/>
       <c r="AQ66" t="inlineStr"/>
       <c r="AR66" t="n">
         <v>1</v>
@@ -11254,11 +11350,11 @@
         <v>1</v>
       </c>
       <c r="AU66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>PERSON</t>
+          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
       </c>
     </row>
@@ -11271,17 +11367,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>שרון שלמה קלייטמן</t>
+          <t>מאיה שרון וינר</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>family_doctor</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -11302,20 +11398,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>sharon.kleitman@gmail.com</t>
+          <t>clinic@drmayasharonweiner.com</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
+          <t>https://www.drmayasharonweiner.com/</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -11325,12 +11421,12 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>ש קשר שיתוף שתפו במייל שתפו בפייסבוק שתפו בטוויטר שתפו בלינקדין ד"ר שרון קלייטמן מומחה ברפואת משפחה, MST - Mind Set Technique, רפואה אינטגרטיבית, IMS - דיקור יבש, תזונה אינטגרטיבית. נייד 052-8325580 פקס 08-6560357 דוא"ל sharon.kleitman@gmail.com אתר www.integrative-med.com שלח/י לי sms פייסבוק אודות ד"ר שרון קלייטמן מומחה ברפואת משפחה, סיים את לימודי הרפואה באוניברסיטת בן גוריון, נשוי ואב לארבעה, מתגורר בקיבוץ שדה בוקר. עוסק בפיתוח והקנ</t>
+          <t>אני איתך במסע הזה. הצעד הראשון שלך מתחיל כאן. ד"ר מאיה שרון-וינר רופאת נשים מומחית בפריון והפריה חוץ גופית מיילדות וגינקולוגיה לקביעת פגישה © 2026 כל הזכויות שמורות לד"ר מאיה שרון-וינר הברזל 9א', רמת החייל ווטסאפ למרפאה clinic@drmayasharonweiner.com פוריות האישה והגבר טיפולי פוריות הפריה חוץ גופית ו-PGD שימור פוריות פוריות לאחר סרטן ובנשאיות BRCA מעקב וליווי הריון גינקולוגיה כללית Menu Close אודות יצירת קשר מדיניות פרטיות הצהרת נגישות M</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>"שרון שלמה קלייטמן"</t>
+          <t>"מאיה שרון וינר"</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -11352,36 +11448,36 @@
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-09-04T15:41:54.743203+00:00</t>
+          <t>2026-09-04T17:43:40.101946+00:00</t>
         </is>
       </c>
       <c r="W67" t="n">
         <v>2</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y67" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AA67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>["https://docsrated.com/doctors/שרון-קלייטמן", "https://www.dunsguide.co.il/Cb6a87819a48606a97ab6b3a3617e9370_רופאים/קלייטמן_שרון_שלמה/", "https://www.facebook.com/sharon.kleitman.md/directory_category/", "https://dns.dibiz.com/sharon-kleitman-md", "https://longevitepalmbeach.com"]</t>
+          <t>["https://www.drmayasharonweiner.com/", "https://www.drmayasharonweiner.com/about", "https://www.drmayasharonweiner.com/contact", "https://www.medreviews.co.il/provider/dr-sharon-weiner-maya", "https://www.medreviews.co.il/provider/dr-sharon-weiner-maya/treatment", "https://www.doctorita.co.il/experts/119120", "https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr_maya_sharonweiner%2F&amp;is_from_rle", "https://docsrated.com/doctors/מאיה-שרון-וינר"]</t>
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>3.243155934528492e+19</v>
+        <v>9.999638147120076e+19</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -11392,7 +11488,7 @@
       <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
+          <t>https://www.drmayasharonweiner.com/</t>
         </is>
       </c>
       <c r="AI67" t="inlineStr"/>
@@ -11416,11 +11512,11 @@
         <v>1</v>
       </c>
       <c r="AU67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>PERSON</t>
+          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
       </c>
     </row>
@@ -11433,17 +11529,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>איה שלם</t>
+          <t>מנחם נוימן</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>family_doctor</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -11464,7 +11560,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>info@shrir-sheled.co.il</t>
+          <t>hello@professorneuman.com</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -11477,7 +11573,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/</t>
+          <t>https://professorneuman.com/he/</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -11487,12 +11583,12 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>ד"ר איה שלם - אינדקס מטפלים ברפואת שריר שלד דלג לתוכן info@shrir-sheled.co.il בית רשימת המטפלים מאמרים מקצועיים אודות מקצוע המטפל רפואת משפחה פיזיותרפיה אוסטיאופתיה כירופרקטיקה אורתופדיה צרו קשר תפריט בית רשימת המטפלים מאמרים מקצועיים אודות מקצוע המטפל רפואת משפחה פיזיותרפי</t>
+          <t>פרופ׳ מנחם נוימן — אורוגינקולוגיה ורפואת רצפת האגן מגדל סוזוקי, קומה 4, רח׳ יגאל אלון 82, תל אביב 054-644-2060 · hello@professorneuman.com ראשי מידע לרופאים מידע למטופלות מהתקשורת צרי קשר English פרופ׳ מנחם נוימן אורוגינקולוגיה ורפואת רצפת האגן צניחת איברי האגן ודליפת שתן הן מהתופעות השכיחות ביותר בקרב נשים — וגם מהניתנות ביותר לטי</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>"איה שלם"</t>
+          <t>"מנחם נוימן"</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -11502,11 +11598,11 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "info@raphaelhospitals.co.il", "confidence": 80, "source_url": "https://www.raphaelhospitals.co.il/en/international-department/about/", "identity_url": "https://www.raphaelhospitals.co.il/doctors/neuman-menahem/", "evidence": "info@raphaelhospitals.co.il", "matched_query": "\"מנחם נוימן\"", "extraction_method": "linked_mailto"}]</t>
         </is>
       </c>
       <c r="S68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T68" t="n">
         <v>0</v>
@@ -11514,7 +11610,7 @@
       <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-09-04T18:58:24.569451+00:00</t>
+          <t>2026-09-04T18:20:49.705154+00:00</t>
         </is>
       </c>
       <c r="W68" t="n">
@@ -11527,10 +11623,10 @@
         <v>7</v>
       </c>
       <c r="Z68" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
@@ -11539,11 +11635,11 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>["https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%9C%D7%9D-%D7%90%D7%99%D7%94/", "https://medpage.co.il/doctors/16196-%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D-8959/", "https://www.doctorita.co.il/experts/124568", "https://drtor.co.il/doctor/19921", "http://me.doctorsonly.co.il/user/2636", "https://www.infomed.co.il/experts/74772/", "https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/", "https://eshkol.media/", "https://shrir-sheled.co.il/about/"]</t>
+          <t>["https://professorneuman.com/", "https://professorneuman.com/he/", "https://professorneuman.com/he/contact", "https://professorneuman.com/en/contact", "https://www.facebook.com/public/%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/", "https://www.facebook.com/people/%D7%9E%D7%A0%D7%97%D7%9D-%D7%A0%D7%95%D7%99%D7%9E%D7%9F/pfbid0371mkxMbe96MNN5gS9XHB7KqrSyxJnXyG9AsLfdZV7j8RjCKyjm8cEEVgjSreLhY8l/", "https://chabadpedia.co.il/wiki/%D7%9E%D7%A0%D7%97%D7%9D_%D7%A0%D7%95%D7%99%D7%9E%D7%9F", "https://www.raphaelhospitals.co.il/doctors/neuman-menahem/", "https://www.raphaelhospitals.co.il/about/aboutus/", "https://www.raphaelhospitals.co.il/fields/endoscopic-unit/about/", "https://www.raphaelhospitals.co.il/fields/pain-clinic/about/", "https://www.raphaelhospitals.co.il/en/international-department/about/", "https://www.raphaelhospitals.co.il/fields/heart-catheterization-clinic/about/", "https://www.raphaelhospitals.co.il/en/about/aboutus/", "https://www.raphaelhospitals.co.il/en/contact/"]</t>
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>3.51258506998755e+19</v>
+        <v>9.999638147120076e+19</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11554,7 +11650,7 @@
       <c r="AG68" t="inlineStr"/>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/</t>
+          <t>https://professorneuman.com/he/</t>
         </is>
       </c>
       <c r="AI68" t="inlineStr"/>
@@ -11586,6 +11682,1796 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>13</v>
+      </c>
+      <c r="B69" t="n">
+        <v>6</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>נעמה מימון</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>moh</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>office@medicaltop.co.il</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>CLINIC_OR_ORGANIZATION</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>88</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ד"ר נעמה מימון: מומחית ברפואת נשים - MedicalTop Search Close Facebook 073-3310444 סנטר הגליל רחוב האגס 1, שער הרימון, קומה שניה. ראש פינה. office@medicaltop.co.il לקביעת תור דף הבית אודות תחומי פעילות הצוות שלנו יצירת קשר Menu דף הבית אודות תחומי פעילות הצוות שלנו יצירת קשר ד"ר נעמה מימון: מומחית ברפואת נשים דף הבית / רופאים / ד"ר נעמה מימון: מומחית ברפואת </t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>"נעמה מימון"</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>direct_text</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-09-04T05:17:30.924388+00:00</t>
+        </is>
+      </c>
+      <c r="W69" t="n">
+        <v>4</v>
+      </c>
+      <c r="X69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>["https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fn.mh.mymwn.2025%2F", "https://www.facebook.com/SNMaesthetic/services/", "https://www.doctorita.co.il/experts/152626", "https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/", "https://medicaltop.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://medicaltop.co.il/%D7%94%D7%A6%D7%95%D7%95%D7%AA-%D7%A9%D7%9C%D7%A0%D7%95/", "https://medicaltop.co.il/wp-content/uploads/2024/04/אודות.jpg"]</t>
+        </is>
+      </c>
+      <c r="AD69" t="n">
+        <v>9.756151294653622e+19</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="inlineStr"/>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>https://medicaltop.co.il/%D7%93%D7%A8-%D7%A0%D7%A2%D7%9E%D7%94-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr"/>
+      <c r="AJ69" t="inlineStr"/>
+      <c r="AK69" t="inlineStr"/>
+      <c r="AL69" t="inlineStr"/>
+      <c r="AM69" t="inlineStr"/>
+      <c r="AN69" t="inlineStr"/>
+      <c r="AO69" t="inlineStr"/>
+      <c r="AP69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ69" t="inlineStr"/>
+      <c r="AR69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS69" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT69" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV69" t="inlineStr">
+        <is>
+          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>13</v>
+      </c>
+      <c r="B70" t="n">
+        <v>6</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>תמר גרין</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>moh</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>office@keshet-refua.co.il</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>CLINIC_OR_ORGANIZATION</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>88</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>https://keshet-refua.co.il/doctors/dr-tamar-green/</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>פיזיותרפיה אסתטיקה פודקסטים קליניקות וססיות להשכרה צור קשר זימון תור ד"ר תמר גרין מומחית לגינקולוגיה ומיילדות מעקב הריון, סקירת הריון מוקדמת ומאוחרת, בדיקות אולטרסאונד אבחנתיות, גיל המעבר ובדיקות גינקולוגיות 073-3214111 office@keshet-refua.co.il לזימון תור &gt; תחומי מומחיות מעקב הריון בדיקות אולטרהסאונד אבחנתיות שקיפות עורפית סקירת מערכות מוקדמת ומאוחרת מעקבי גדילה הדמיית אגן והדמיה תלת מימדית של הרחם טיפולי גינקולוגיה פרטית התקנים תוך רח</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>"תמר גרין"</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>official_text</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S70" t="n">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-09-05T00:09:39.798497+00:00</t>
+        </is>
+      </c>
+      <c r="W70" t="n">
+        <v>2</v>
+      </c>
+      <c r="X70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>["https://www.medreviews.co.il/provider/dr-green-tamar", "https://keshet-refua.co.il/doctors/dr-tamar-green/", "https://keshet-refua.co.il/about-us/", "https://keshet-refua.co.il/contact-us/", "https://keshet-refua.co.il/clinics-for-rent-sessional-clinics-for-rent/", "https://keshet-refua.co.il/about-us/#contact-keshet-medical-center", "https://keshet-refua.co.il/areas_of_expertise/child-psychology-clinic/", "https://keshet-refua.co.il/doctors/private-clinical-dietician-jerusalem/", "https://keshet-refua.co.il/contact-us/#contact-keshet-medical-center", "https://keshet-refua.co.il/clinics-for-rent-sessional-clinics-for-rent/#contact-keshet-medical-center", "https://keshet-refua.co.il/doctors/dr-tamar-green-private-gynecologist-in-jerusalem/", "https://wayzee.co.il/", "https://keshet-refua.co.il/treatments/menstrual-arrangement-before-the-wedding-private-womens-clinic-private-gynecologist/", "https://keshet-refua.co.il/areas_of_expertise/child-psychology-clinic/#contact-keshet-medical-center", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2F61558661827898%2F", "https://www.facebook.com/public/%D7%AA%D7%9E%D7%A8-%D7%92%D7%A8%D7%99%D7%9F/", "https://www.medreviews.co.il/provider/dr-green-tamar/treatment/gynecologist-clinic", "https://www.szmc.org.il/doctors/grin-tamar/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
+        </is>
+      </c>
+      <c r="AD70" t="n">
+        <v>9.736509280303114e+19</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="inlineStr"/>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>https://keshet-refua.co.il/doctors/dr-tamar-green/</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr"/>
+      <c r="AJ70" t="inlineStr"/>
+      <c r="AK70" t="inlineStr"/>
+      <c r="AL70" t="inlineStr"/>
+      <c r="AM70" t="inlineStr"/>
+      <c r="AN70" t="inlineStr"/>
+      <c r="AO70" t="inlineStr"/>
+      <c r="AP70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ70" t="inlineStr"/>
+      <c r="AR70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV70" t="inlineStr">
+        <is>
+          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>13</v>
+      </c>
+      <c r="B71" t="n">
+        <v>6</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>אבי צפריר</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>moh</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>ivfrec@szmc.org.il</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>CLINIC_OR_ORGANIZATION</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>82</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>https://www.szmc.org.il/doctors/tsafrir-avi/</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">h عربيه Русский צרו קשר צרו קשר אזור אישי אזור אישי רופאים בשערי צדק ד"ר  אבי צפריר רופא בכיר Dr.  Avi Tsafrir התמחות: גינקולוגיה ויילוד תת התמחות: הפריה חוץ גופית תחומים נוספים: שימור פוריות פוריות הגבר פוריות האשה עוד ivfrec@szmc.org.il ivfrec@szmc.org.il נסיון מקצועי מומחה ביילוד ובגינקולוגיה משנת 2005 רופא בכיר להפריה חוץ גופית בשערי צדק משנת 2005 תפקידים ציבוריים חבר ועד האגודה הישראלית לחקר הפוריות משנת 2022 לימודים והכשרה פקולטה </t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>"אבי צפריר"</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>direct_text</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S71" t="n">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-09-03T20:26:52.799327+00:00</t>
+        </is>
+      </c>
+      <c r="W71" t="n">
+        <v>4</v>
+      </c>
+      <c r="X71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>["https://www.infomed.co.il/experts/73913/", "https://he.hadassah.org.il/doctor/dr-avi-tsafrir-gaadaabqaa2aaoiag4adaabyaa======/", "https://www.doctors.co.il/expert/obstetrics-and-gynecologists/80043972/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fbyzpryr%2F", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A6%D7%A4%D7%A8%D7%99%D7%A8-%D7%90%D7%91%D7%99/", "https://drtor.co.il/doctor/3910", "https://www.szmc.org.il/doctors/tsafrir-avi/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.clalit.co.il/he/sefersherut/pages/doctordetails.aspx", "https://docsrated.com/doctors/אבי-צפריר", "https://www.doctorita.co.il/experts/44804"]</t>
+        </is>
+      </c>
+      <c r="AD71" t="n">
+        <v>1.29681764900094e+20</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="inlineStr"/>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>https://www.szmc.org.il/doctors/tsafrir-avi/</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr"/>
+      <c r="AJ71" t="inlineStr"/>
+      <c r="AK71" t="inlineStr"/>
+      <c r="AL71" t="inlineStr"/>
+      <c r="AM71" t="inlineStr"/>
+      <c r="AN71" t="inlineStr"/>
+      <c r="AO71" t="inlineStr"/>
+      <c r="AP71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ71" t="inlineStr"/>
+      <c r="AR71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS71" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT71" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV71" t="inlineStr">
+        <is>
+          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>13</v>
+      </c>
+      <c r="B72" t="n">
+        <v>6</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>צחי סטמפלר</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>family_doctor</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>moh</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>info@bekeshevclinic.co.il</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>CLINIC_OR_ORGANIZATION</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>80</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>https://www.bekeshevclinic.co.il/</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>יצירת קשר 📞 03-9660306 💬 WhatsApp ✉️ info@bekeshevclinic.co.il</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>"צחי סטמפלר" רפואת משפחה</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>linked_mailto</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-09-11T18:39:26.792172+00:00</t>
+        </is>
+      </c>
+      <c r="W72" t="n">
+        <v>6</v>
+      </c>
+      <c r="X72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>["https://www.doctorita.co.il/experts/83311", "https://www.olamkal.com/he/pro/stmflr-tzchy-rishon-lezion", "https://www.olamkal.com/he/about", "https://www.olamkal.com/fr/about", "https://www.olamkal.com/en/about", "https://www.olamkal.com/ru/about", "https://www.infomed.co.il/experts/146278/", "https://doctorindex.co.il/דוקטור-סטמפלר-צחי/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A1%D7%98%D7%9E%D7%A4%D7%9C%D7%A8-%D7%A6%D7%97%D7%99/", "https://www.bekeshevclinic.co.il/book", "https://www.medreviews.co.il/provider/dr-stempler-tzahi/page/2", "https://www.bekeshevclinic.co.il/", "https://www.bekeshevclinic.co.il/about", "https://www.bekeshevclinic.co.il/contact", "https://www.bekeshevclinic.co.il/services/%D7%90%D7%91%D7%97%D7%95%D7%9F-%D7%99%D7%9C%D7%93%D7%99%D7%9D-%D7%95%D7%9E%D7%AA%D7%91%D7%92%D7%A8%D7%99%D7%9D"]</t>
+        </is>
+      </c>
+      <c r="AD72" t="n">
+        <v>20415</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG72" t="inlineStr"/>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>https://www.bekeshevclinic.co.il/about</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr"/>
+      <c r="AJ72" t="inlineStr"/>
+      <c r="AK72" t="inlineStr"/>
+      <c r="AL72" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM72" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN72" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>אודות - ד״ר צחי סטמפלר | מרפאה בקשב מרפאה בקשב אבחון וייעוץ בלוג אודות צור קשר לתיאום שיחת ייעוץ חינם אודות מרפאה בקשב מפענוח הקושי לבניית חוסן ד״ר צחי סטמפלר מומחה לרפואת המשפחה ו מורשה משרד הבריאות לאבחון וטיפול בהפרעות קשב וריכוז מומחה ברפואת המשפחה ומשנת 2014 מורשה משרד הבריאות לאבחון וטיפול בהפרעות קשב וריכוז.  הקמתי  את מרפאה בקשב, שבה טופלו ואובחנו אלפי ילדים, מתבגרים ומבוגרים, וסייעתי לשינוי מסלולי חיים של משפחות וילדים שמתמודדים עם הפרעות קשב. בעבר הנחיתי נוער בתחום האגרו-חקר ועסקתי בחקר דרכי טיפול להעצמה ושיפור תפקוד בקרב ילדים עם הפרעת קשב, במסגרת גינון קהילתי וחממה הידרופונית שהקמתי בכפר הנוער יוענה ז'בוינסקי. בזמני הפנוי אני נהנה מעיסוק בנגרות ובניית כלי נגינה, ומנהל בקהילת הגינון "הגינה הביתית" – תחומים שמאפשרים לי להביא לידי ביטוי חשיבה יצירתית ומעשית. "כמי שמכיר וחווה הפרעת קשב, אני מכיר ביכולות של הפרעת קשב להיות מכשול משמעותי בניצול יכולות ובהתמודדות עם משימות בחיי היום יום. אך יחד עם זאת , עם טיפול נכון, ניתן לשלוט בהפרעה ולעתים אף לרתום אותה להתפתחות וצמיחה. איך הפרעה יכולה להביא להתפתחות וצמיחה? אבחו</t>
+        </is>
+      </c>
+      <c r="AP72" t="inlineStr"/>
+      <c r="AQ72" t="inlineStr"/>
+      <c r="AR72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV72" t="inlineStr">
+        <is>
+          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>13</v>
+      </c>
+      <c r="B73" t="n">
+        <v>6</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>אירינה דורפמן אלמוג</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>family_doctor</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>moh</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>dr.irenadorfman@gmail.com</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>100</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>מוג אירינה כרטיס עסק: ד"ר דורפמן אלמוג אירינה » תחום פעילות: בריאות וספורט » רופא » תאור העסק: רופאת משפחה עצמאית קופת חולים לאומית. » איש קשר: אירנה דורפמן » טלפונים: טלפון: 077-7997456 נייד: 054-4616457 » אתר: » מייל: dr.irenadorfman@gmail.com » כתובת: בן גוריון 123 יהוד, מיקוד: 56209 כלים מחשבונים לעסקים מדריכי ניהול עסק, הקמת עסק נושאי האתר הנהלת חשבונות הפקת חשבוניות חשבונית אלקטרונית ניהול לקוחות שותפים עסקיים אילת סיטי - מדריך הע</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>"אירינה דורפמן אלמוג"</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>direct_text</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>[{"email": "info@flex.co.il", "confidence": 80, "source_url": "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "identity_url": "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "evidence": "info@flex.co.il", "matched_query": "\"אירינה דורפמן אלמוג\"", "extraction_method": "linked_mailto"}]</t>
+        </is>
+      </c>
+      <c r="S73" t="n">
+        <v>2</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-09-04T19:17:26.299485+00:00</t>
+        </is>
+      </c>
+      <c r="W73" t="n">
+        <v>2</v>
+      </c>
+      <c r="X73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>["https://www.dunsguide.co.il/C7195b21475cb11a3e5b86def04a3e20c_רופאים/דורפמן_אלמוג_אירינה/", "https://medpage.co.il/doctors/%D7%90%D7%99%D7%A8%D7%A0%D7%94-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-20871/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94/", "https://www.beok.co.il/doctors/Doctors-129241/", "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "https://www.flex.co.il/100_General/005_GeneralPages/006_About.aspx", "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "https://www.flex.co.il/100_General/900_DifferentStuff/900_ForTheCommunity.aspx"]</t>
+        </is>
+      </c>
+      <c r="AD73" t="n">
+        <v>1.053775520996265e+20</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="inlineStr"/>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr"/>
+      <c r="AJ73" t="inlineStr"/>
+      <c r="AK73" t="inlineStr"/>
+      <c r="AL73" t="inlineStr"/>
+      <c r="AM73" t="inlineStr"/>
+      <c r="AN73" t="inlineStr"/>
+      <c r="AO73" t="inlineStr"/>
+      <c r="AP73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ73" t="inlineStr"/>
+      <c r="AR73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU73" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV73" t="inlineStr">
+        <is>
+          <t>PERSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>13</v>
+      </c>
+      <c r="B74" t="n">
+        <v>6</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>אלון שלב</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>family_doctor</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>moh</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>alonshalev31@gmail.com</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>100</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>https://pain.coi.co.il/</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>הודעה לבעלי האתר תקופת הניסיון הסתיימה, יש ליצור מנוי דרך ממשק ניהול האתר. האתר נכנס לרשימת המחיקה ויימחק בקרוב לחץ כאן אם אינך זוכר את כתובת ממשק ניהול האתר שלך. דר אלון שלב - רופא כאב טלפון: 054-6221105 מייל: alonshalev31@gmail.com כתובת: ילדי טהרן 8, ראשון לציון ד"ר אלון שלב מומחה ברפואת המשפחה רופא כאב דף הבית אודות צור קשר אל תחכו - הזמינו תור לרופא עוד היום.. לייעוץ ראשוני ללא עלות והזמנת תורים מלאו פרטים או התקשרו: 05462</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>"אלון שלב"</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>direct_text</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-09-04T19:37:15.755041+00:00</t>
+        </is>
+      </c>
+      <c r="W74" t="n">
+        <v>2</v>
+      </c>
+      <c r="X74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>["https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr.shalev.pain%2F&amp;is_from_rle", "https://www.bgu.ac.il/people/shalevn/", "https://www.bgu.ac.il/en/people/shalevn/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fdr.shalev.pain%2F", "https://www.medreviews.co.il/search/pain-management/center/rishon-lezion", "https://pain.coi.co.il/", "https://pain.coi.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA.htm", "https://pain.coi.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8.htm"]</t>
+        </is>
+      </c>
+      <c r="AD74" t="n">
+        <v>1.053775520996265e+20</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="inlineStr"/>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>https://pain.coi.co.il/</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr"/>
+      <c r="AJ74" t="inlineStr"/>
+      <c r="AK74" t="inlineStr"/>
+      <c r="AL74" t="inlineStr"/>
+      <c r="AM74" t="inlineStr"/>
+      <c r="AN74" t="inlineStr"/>
+      <c r="AO74" t="inlineStr"/>
+      <c r="AP74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ74" t="inlineStr"/>
+      <c r="AR74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU74" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV74" t="inlineStr">
+        <is>
+          <t>PERSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>13</v>
+      </c>
+      <c r="B75" t="n">
+        <v>6</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>אמיר צבעוני</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>family_doctor</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>moh</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>healtms@gmail.com</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>100</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>https://www.drzivony.co.il/</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>"ר אמיר צבעוני ד"ר אמיר צבעוני רופא משפחה מומחה העוסק בטיפול בכאב כרוני בגישת גוף-נפש ללא שימוש בתרופות או בפרוצדורות רפואיות. הטיפול מבוסס מחקר בתחום מדעי המח והכאב. ניתן לקרוא עליי עוד ב דף האודות . טלפון: 051-2303120 healtms@gmail.com קליניקה בגבעת עדה (סמוך לבנימינה) ניתן ליצור איתי קשר גם ב דף יצירת הקשר פוסטים אחרונים על הענק הירוק והדחקת רגשות לאותת עם המגבים רגישות יתר לאחר פציעה אזהרת טריגר בקשת סליחה מעצמי חפש: חיפוש בית אודות</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>"אמיר צבעוני"</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>direct_text</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-09-03T23:00:56.706890+00:00</t>
+        </is>
+      </c>
+      <c r="W75" t="n">
+        <v>2</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>["https://www.drzivony.co.il/", "https://www.drzivony.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.053664339784934e+20</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="inlineStr"/>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>https://www.drzivony.co.il/</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr"/>
+      <c r="AJ75" t="inlineStr"/>
+      <c r="AK75" t="inlineStr"/>
+      <c r="AL75" t="inlineStr"/>
+      <c r="AM75" t="inlineStr"/>
+      <c r="AN75" t="inlineStr"/>
+      <c r="AO75" t="inlineStr"/>
+      <c r="AP75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ75" t="inlineStr"/>
+      <c r="AR75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU75" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV75" t="inlineStr">
+        <is>
+          <t>PERSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>13</v>
+      </c>
+      <c r="B76" t="n">
+        <v>6</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>בתיה קורנבוים</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>family_doctor</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>moh</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>batyakornboim@gmail.com</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>100</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>https://www.dr-batya-kornboim.com/</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>שקל בחיפה אודות חוות דעת יצירת קשר כתבות ופרסומים תפריט ד״ר בתיה קורנבוים - מומחית ברפואת משפחה ורפואת השמנה [תיאור המרפאה יתווסף בהמשך] טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו חיפה 3570901 IL 052-567-1100 batyakornboim@gmail.com התמחויות רפואיות עיקריות: [פירוט תחומי הטיפול יתווסף בהמשך] מידע מעשי: יצירת קשר: טלפון 052-567-1100 או וואטסאפ 052-567-1100 מיקום: טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו , חיפה סוג</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>"בתיה קורנבוים"</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>direct_text</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S76" t="n">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-09-03T23:52:50.148875+00:00</t>
+        </is>
+      </c>
+      <c r="W76" t="n">
+        <v>2</v>
+      </c>
+      <c r="X76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>["https://www.dr-batya-kornboim.com/", "https://www.dr-batya-kornboim.com/#%D7%90%D7%95%D7%93%D7%95%D7%AA"]</t>
+        </is>
+      </c>
+      <c r="AD76" t="n">
+        <v>1.053664339784934e+20</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="inlineStr"/>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>https://www.dr-batya-kornboim.com/</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr"/>
+      <c r="AJ76" t="inlineStr"/>
+      <c r="AK76" t="inlineStr"/>
+      <c r="AL76" t="inlineStr"/>
+      <c r="AM76" t="inlineStr"/>
+      <c r="AN76" t="inlineStr"/>
+      <c r="AO76" t="inlineStr"/>
+      <c r="AP76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ76" t="inlineStr"/>
+      <c r="AR76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU76" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV76" t="inlineStr">
+        <is>
+          <t>PERSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>13</v>
+      </c>
+      <c r="B77" t="n">
+        <v>6</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>שלומית שדמון</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>family_doctor</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>moh</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>shlomitshadmon@gmail.com</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>100</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>ם ופעילויות כנסים והשתלמויות הרצאות מהכנסים מטפלי.ות איט"ם מטפלי.ות איט"ם פיזיותרפיסטים.ית איט"ם מרפאות ציבוריות הצטרפות והתמחות צור קשר פרטי התקשרות טלפון 054-9145177 כתובת אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אימייל shlomitshadmon@gmail.com שדמון שלומית (MD) – תל אביב מקצוע:  רופאת משפחה, מוסמכת ביעוץ וטיפול מיני. התמחות: מטפלת מינית איזור טיפול: תל אביב אודותי אני רופאת משפחה ותיקה, מדריכה קלינית ומרצה בנושאי בריאות האישה, מיניות ה</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>"שלומית שדמון"</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>direct_text</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "identity_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "evidence": "mail.com אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"שלומית שדמון\"", "extraction_method": "direct_text"}]</t>
+        </is>
+      </c>
+      <c r="S77" t="n">
+        <v>2</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>2026-09-04T15:25:57.140597+00:00</t>
+        </is>
+      </c>
+      <c r="W77" t="n">
+        <v>2</v>
+      </c>
+      <c r="X77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>["https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA/", "https://moonbellboutique.com/index/%D7%93%D7%A8-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%A9%D7%93%D7%9E%D7%95%D7%9F/", "https://moonbellboutique.com/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/", "https://www.infomed.co.il/experts/145161/", "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="AD77" t="n">
+        <v>9.729467803585477e+19</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="inlineStr"/>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr"/>
+      <c r="AJ77" t="inlineStr"/>
+      <c r="AK77" t="inlineStr"/>
+      <c r="AL77" t="inlineStr"/>
+      <c r="AM77" t="inlineStr"/>
+      <c r="AN77" t="inlineStr"/>
+      <c r="AO77" t="inlineStr"/>
+      <c r="AP77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ77" t="inlineStr"/>
+      <c r="AR77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU77" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>PERSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>13</v>
+      </c>
+      <c r="B78" t="n">
+        <v>6</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>שרון שלמה קלייטמן</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>family_doctor</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>moh</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>sharon.kleitman@gmail.com</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>100</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>ש קשר שיתוף שתפו במייל שתפו בפייסבוק שתפו בטוויטר שתפו בלינקדין ד"ר שרון קלייטמן מומחה ברפואת משפחה, MST - Mind Set Technique, רפואה אינטגרטיבית, IMS - דיקור יבש, תזונה אינטגרטיבית. נייד 052-8325580 פקס 08-6560357 דוא"ל sharon.kleitman@gmail.com אתר www.integrative-med.com שלח/י לי sms פייסבוק אודות ד"ר שרון קלייטמן מומחה ברפואת משפחה, סיים את לימודי הרפואה באוניברסיטת בן גוריון, נשוי ואב לארבעה, מתגורר בקיבוץ שדה בוקר. עוסק בפיתוח והקנ</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>"שרון שלמה קלייטמן"</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>direct_text</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S78" t="n">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>2026-09-04T15:41:54.743203+00:00</t>
+        </is>
+      </c>
+      <c r="W78" t="n">
+        <v>2</v>
+      </c>
+      <c r="X78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>["https://docsrated.com/doctors/שרון-קלייטמן", "https://www.dunsguide.co.il/Cb6a87819a48606a97ab6b3a3617e9370_רופאים/קלייטמן_שרון_שלמה/", "https://www.facebook.com/sharon.kleitman.md/directory_category/", "https://dns.dibiz.com/sharon-kleitman-md", "https://longevitepalmbeach.com"]</t>
+        </is>
+      </c>
+      <c r="AD78" t="n">
+        <v>9.729467803585477e+19</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="inlineStr"/>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr"/>
+      <c r="AJ78" t="inlineStr"/>
+      <c r="AK78" t="inlineStr"/>
+      <c r="AL78" t="inlineStr"/>
+      <c r="AM78" t="inlineStr"/>
+      <c r="AN78" t="inlineStr"/>
+      <c r="AO78" t="inlineStr"/>
+      <c r="AP78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ78" t="inlineStr"/>
+      <c r="AR78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU78" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>PERSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>13</v>
+      </c>
+      <c r="B79" t="n">
+        <v>6</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>איה שלם</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>family_doctor</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>moh</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>info@shrir-sheled.co.il</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>CLINIC_OR_ORGANIZATION</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>88</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>ד"ר איה שלם - אינדקס מטפלים ברפואת שריר שלד דלג לתוכן info@shrir-sheled.co.il בית רשימת המטפלים מאמרים מקצועיים אודות מקצוע המטפל רפואת משפחה פיזיותרפיה אוסטיאופתיה כירופרקטיקה אורתופדיה צרו קשר תפריט בית רשימת המטפלים מאמרים מקצועיים אודות מקצוע המטפל רפואת משפחה פיזיותרפי</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>"איה שלם"</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>direct_text</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S79" t="n">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>2026-09-04T18:58:24.569451+00:00</t>
+        </is>
+      </c>
+      <c r="W79" t="n">
+        <v>2</v>
+      </c>
+      <c r="X79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>["https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%9C%D7%9D-%D7%90%D7%99%D7%94/", "https://medpage.co.il/doctors/16196-%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D-8959/", "https://www.doctorita.co.il/experts/124568", "https://drtor.co.il/doctor/19921", "http://me.doctorsonly.co.il/user/2636", "https://www.infomed.co.il/experts/74772/", "https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/", "https://eshkol.media/", "https://shrir-sheled.co.il/about/"]</t>
+        </is>
+      </c>
+      <c r="AD79" t="n">
+        <v>1.053775520996265e+20</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="inlineStr"/>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr"/>
+      <c r="AJ79" t="inlineStr"/>
+      <c r="AK79" t="inlineStr"/>
+      <c r="AL79" t="inlineStr"/>
+      <c r="AM79" t="inlineStr"/>
+      <c r="AN79" t="inlineStr"/>
+      <c r="AO79" t="inlineStr"/>
+      <c r="AP79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ79" t="inlineStr"/>
+      <c r="AR79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/contacts_primary.xlsx
+++ b/output/contacts_primary.xlsx
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>1.054010390061308e+20</v>
+        <v>3.162031170183923e+20</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>1.299819541672012e+20</v>
+        <v>3.899458625016037e+20</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>1.053664339784934e+20</v>
+        <v>3.160993019354802e+20</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>1.053664339784934e+20</v>
+        <v>3.160993019354802e+20</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>1.053664339784934e+20</v>
+        <v>3.160993019354802e+20</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>1.053664339784934e+20</v>
+        <v>3.160993019354802e+20</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>1.296817648966072e+20</v>
+        <v>3.890452946898217e+20</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>1.296817648966072e+20</v>
+        <v>3.890452946898217e+20</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>1.216767176807673e+20</v>
+        <v>3.650301530423019e+20</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>1.054677477329709e+20</v>
+        <v>3.164032431989126e+20</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>1.054664970686914e+20</v>
+        <v>3.163994912060741e+20</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>1.300264266517337e+20</v>
+        <v>3.90079279955201e+20</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>21879</v>
+        <v>65637</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>1.05467747732971e+20</v>
+        <v>3.164032431989131e+20</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>1.296817648966072e+20</v>
+        <v>3.890452946898217e+20</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>1.053664339784934e+20</v>
+        <v>3.160993019354802e+20</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>1.053664339784934e+20</v>
+        <v>3.160993019354802e+20</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3563,7 +3563,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>1.053664339784934e+20</v>
+        <v>3.160993019354802e+20</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>1.05467747732971e+20</v>
+        <v>3.164032431989131e+20</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>1.054664970686914e+20</v>
+        <v>3.163994912060741e+20</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -4049,7 +4049,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>1.054010390061307e+20</v>
+        <v>3.162031170183922e+20</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4211,7 +4211,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>1.053664339784934e+20</v>
+        <v>3.160993019354802e+20</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>1.053664339784934e+20</v>
+        <v>3.160993019354802e+20</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4535,7 +4535,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>9.999638147120076e+19</v>
+        <v>2.999891444136023e+20</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>20415</v>
+        <v>61245</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>20415</v>
+        <v>61245</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>9.999638147120076e+19</v>
+        <v>2.999891444136023e+20</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>9.756151294304942e+19</v>
+        <v>2.926845388291483e+20</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5367,7 +5367,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>9.756151294304942e+19</v>
+        <v>2.926845388291483e+20</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>9.756151294304942e+19</v>
+        <v>2.926845388291483e+20</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>9.756151294304942e+19</v>
+        <v>2.926845388291483e+20</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5854,7 +5854,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>9.756151294304942e+19</v>
+        <v>2.926845388291483e+20</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -6016,7 +6016,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>1.299819541672012e+20</v>
+        <v>3.899458625016037e+20</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -6178,7 +6178,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>9.729592870013428e+19</v>
+        <v>2.918877861004028e+20</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6349,7 +6349,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>9.729592870009283e+19</v>
+        <v>2.918877861002785e+20</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6520,7 +6520,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>1.054010390061724e+20</v>
+        <v>3.162031170185171e+20</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>1.053997883418927e+20</v>
+        <v>3.161993650256782e+20</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>1.053997883418927e+20</v>
+        <v>3.161993650256782e+20</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>1.053997883418927e+20</v>
+        <v>3.161993650256782e+20</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -7176,7 +7176,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>1.053664339784934e+20</v>
+        <v>3.160993019354802e+20</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7338,7 +7338,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>1.216915418422781e+20</v>
+        <v>3.650746255268343e+20</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7500,7 +7500,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>1.296817648966072e+20</v>
+        <v>3.890452946898217e+20</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7662,7 +7662,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>1.053664339784934e+20</v>
+        <v>3.160993019354802e+20</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7824,7 +7824,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>1.054010390061307e+20</v>
+        <v>3.162031170183922e+20</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7986,7 +7986,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>9.999638147120076e+19</v>
+        <v>2.999891444136023e+20</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>9.999638147120076e+19</v>
+        <v>2.999891444136023e+20</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>9.999638147120076e+19</v>
+        <v>2.999891444136023e+20</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8472,7 +8472,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>9.757388172841951e+19</v>
+        <v>2.927216451852586e+20</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8634,7 +8634,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>9.757263106418254e+19</v>
+        <v>2.927178931925476e+20</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8796,7 +8796,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>9.757263106418254e+19</v>
+        <v>2.927178931925476e+20</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8958,7 +8958,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>9.756151294304942e+19</v>
+        <v>2.926845388291483e+20</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -9120,7 +9120,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>9.756151294304942e+19</v>
+        <v>2.926845388291483e+20</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -9282,7 +9282,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>9.729592870009283e+19</v>
+        <v>2.918877861002785e+20</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -9452,7 +9452,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>9.736138676265343e+19</v>
+        <v>2.920841602879603e+20</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9614,7 +9614,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>9.736509280303114e+19</v>
+        <v>2.920952784090934e+20</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9776,7 +9776,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>20415</v>
+        <v>61245</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9946,7 +9946,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>9.736263742693297e+19</v>
+        <v>2.920879122807989e+20</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -10118,7 +10118,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>20415</v>
+        <v>61245</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -10288,7 +10288,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>20415</v>
+        <v>61245</v>
       </c>
       <c r="AE60" t="n">
         <v>4</v>
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>9.997539589084663e+19</v>
+        <v>2.999261876725399e+20</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10629,7 +10629,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>20415</v>
+        <v>61245</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10802,7 +10802,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>20415</v>
+        <v>61245</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10975,7 +10975,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>20415</v>
+        <v>61245</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -11145,7 +11145,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>1.296817648966072e+20</v>
+        <v>3.890452946898217e+20</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -11307,7 +11307,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>9.999763213543884e+19</v>
+        <v>2.999928964063166e+20</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>9.999638147120076e+19</v>
+        <v>2.999891444136023e+20</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -11639,7 +11639,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>9.999638147120076e+19</v>
+        <v>2.999891444136023e+20</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>9.756151294653622e+19</v>
+        <v>2.926845388396086e+20</v>
       </c>
       <c r="AE69" t="n">
         <v>2</v>
@@ -11963,7 +11963,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>9.736509280303114e+19</v>
+        <v>2.920952784090934e+20</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -12125,7 +12125,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>1.29681764900094e+20</v>
+        <v>3.890452947002821e+20</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -12287,7 +12287,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>20415</v>
+        <v>61245</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -12457,7 +12457,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>1.053775520996265e+20</v>
+        <v>3.161326562988795e+20</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -12619,7 +12619,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>1.053775520996265e+20</v>
+        <v>3.161326562988795e+20</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12781,7 +12781,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>1.053664339784934e+20</v>
+        <v>3.160993019354802e+20</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -12943,7 +12943,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>1.053664339784934e+20</v>
+        <v>3.160993019354802e+20</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -13105,7 +13105,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>9.729467803585477e+19</v>
+        <v>2.918840341075643e+20</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>9.729467803585477e+19</v>
+        <v>2.918840341075643e+20</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -13429,7 +13429,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>1.053775520996265e+20</v>
+        <v>3.161326562988795e+20</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>

--- a/output/contacts_primary.xlsx
+++ b/output/contacts_primary.xlsx
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>3.162031170183923e+20</v>
+        <v>9.486093510551769e+20</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>3.899458625016037e+20</v>
+        <v>1.169837587504811e+21</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>3.160993019354802e+20</v>
+        <v>9.482979058064404e+20</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>3.160993019354802e+20</v>
+        <v>9.482979058064404e+20</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>3.160993019354802e+20</v>
+        <v>9.482979058064404e+20</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>3.160993019354802e+20</v>
+        <v>9.482979058064404e+20</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>3.890452946898217e+20</v>
+        <v>1.167135884069465e+21</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>3.890452946898217e+20</v>
+        <v>1.167135884069465e+21</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>3.650301530423019e+20</v>
+        <v>1.095090459126906e+21</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>3.164032431989126e+20</v>
+        <v>9.492097295967378e+20</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>3.163994912060741e+20</v>
+        <v>9.491984736182225e+20</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>3.90079279955201e+20</v>
+        <v>1.170237839865603e+21</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>65637</v>
+        <v>196911</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>3.164032431989131e+20</v>
+        <v>9.492097295967394e+20</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>3.890452946898217e+20</v>
+        <v>1.167135884069465e+21</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>3.160993019354802e+20</v>
+        <v>9.482979058064404e+20</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>3.160993019354802e+20</v>
+        <v>9.482979058064404e+20</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3563,7 +3563,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>3.160993019354802e+20</v>
+        <v>9.482979058064404e+20</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>3.164032431989131e+20</v>
+        <v>9.492097295967394e+20</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>3.163994912060741e+20</v>
+        <v>9.491984736182225e+20</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -4049,7 +4049,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>3.162031170183922e+20</v>
+        <v>9.486093510551768e+20</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4211,7 +4211,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>3.160993019354802e+20</v>
+        <v>9.482979058064404e+20</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>3.160993019354802e+20</v>
+        <v>9.482979058064404e+20</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4535,7 +4535,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>2.999891444136023e+20</v>
+        <v>8.999674332408067e+20</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>61245</v>
+        <v>183735</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>61245</v>
+        <v>183735</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>2.999891444136023e+20</v>
+        <v>8.999674332408067e+20</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>2.926845388291483e+20</v>
+        <v>8.780536164874449e+20</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5367,7 +5367,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>2.926845388291483e+20</v>
+        <v>8.780536164874449e+20</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>2.926845388291483e+20</v>
+        <v>8.780536164874449e+20</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>2.926845388291483e+20</v>
+        <v>8.780536164874449e+20</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5854,7 +5854,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>2.926845388291483e+20</v>
+        <v>8.780536164874449e+20</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -6016,7 +6016,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>3.899458625016037e+20</v>
+        <v>1.169837587504811e+21</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -6178,7 +6178,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>2.918877861004028e+20</v>
+        <v>8.756633583012084e+20</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6349,7 +6349,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>2.918877861002785e+20</v>
+        <v>8.756633583008354e+20</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6520,7 +6520,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>3.162031170185171e+20</v>
+        <v>9.486093510555515e+20</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>3.161993650256782e+20</v>
+        <v>9.485980950770344e+20</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>3.161993650256782e+20</v>
+        <v>9.485980950770344e+20</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>3.161993650256782e+20</v>
+        <v>9.485980950770344e+20</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -7176,7 +7176,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>3.160993019354802e+20</v>
+        <v>9.482979058064404e+20</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7338,7 +7338,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>3.650746255268343e+20</v>
+        <v>1.095223876580503e+21</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7500,7 +7500,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>3.890452946898217e+20</v>
+        <v>1.167135884069465e+21</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7662,7 +7662,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>3.160993019354802e+20</v>
+        <v>9.482979058064404e+20</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7824,7 +7824,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>3.162031170183922e+20</v>
+        <v>9.486093510551768e+20</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7986,7 +7986,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>2.999891444136023e+20</v>
+        <v>8.999674332408067e+20</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>2.999891444136023e+20</v>
+        <v>8.999674332408067e+20</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>2.999891444136023e+20</v>
+        <v>8.999674332408067e+20</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8472,7 +8472,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>2.927216451852586e+20</v>
+        <v>8.781649355557756e+20</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8634,7 +8634,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>2.927178931925476e+20</v>
+        <v>8.781536795776428e+20</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8796,7 +8796,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>2.927178931925476e+20</v>
+        <v>8.781536795776428e+20</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8958,7 +8958,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>2.926845388291483e+20</v>
+        <v>8.780536164874449e+20</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -9120,7 +9120,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>2.926845388291483e+20</v>
+        <v>8.780536164874449e+20</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -9282,7 +9282,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>2.918877861002785e+20</v>
+        <v>8.756633583008354e+20</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -9452,7 +9452,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>2.920841602879603e+20</v>
+        <v>8.762524808638809e+20</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9614,7 +9614,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>2.920952784090934e+20</v>
+        <v>8.762858352272802e+20</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9776,7 +9776,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>61245</v>
+        <v>183735</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9946,7 +9946,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>2.920879122807989e+20</v>
+        <v>8.762637368423968e+20</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -10118,7 +10118,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>61245</v>
+        <v>183735</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -10288,7 +10288,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>61245</v>
+        <v>183735</v>
       </c>
       <c r="AE60" t="n">
         <v>4</v>
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>2.999261876725399e+20</v>
+        <v>8.997785630176197e+20</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10629,7 +10629,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>61245</v>
+        <v>183735</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10802,7 +10802,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>61245</v>
+        <v>183735</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10975,7 +10975,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>61245</v>
+        <v>183735</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -11145,7 +11145,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>3.890452946898217e+20</v>
+        <v>1.167135884069465e+21</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -11307,7 +11307,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>2.999928964063166e+20</v>
+        <v>8.999786892189497e+20</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>2.999891444136023e+20</v>
+        <v>8.999674332408067e+20</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -11639,7 +11639,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>2.999891444136023e+20</v>
+        <v>8.999674332408067e+20</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>2.926845388396086e+20</v>
+        <v>8.780536165188259e+20</v>
       </c>
       <c r="AE69" t="n">
         <v>2</v>
@@ -11963,7 +11963,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>2.920952784090934e+20</v>
+        <v>8.762858352272802e+20</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -12125,7 +12125,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>3.890452947002821e+20</v>
+        <v>1.167135884100846e+21</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -12287,7 +12287,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>61245</v>
+        <v>183735</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -12457,7 +12457,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>3.161326562988795e+20</v>
+        <v>9.483979688966385e+20</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -12619,7 +12619,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>3.161326562988795e+20</v>
+        <v>9.483979688966385e+20</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12781,7 +12781,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>3.160993019354802e+20</v>
+        <v>9.482979058064404e+20</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -12943,7 +12943,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>3.160993019354802e+20</v>
+        <v>9.482979058064404e+20</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -13105,7 +13105,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>2.918840341075643e+20</v>
+        <v>8.756521023226928e+20</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>2.918840341075643e+20</v>
+        <v>8.756521023226928e+20</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -13429,7 +13429,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>3.161326562988795e+20</v>
+        <v>9.483979688966385e+20</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>

--- a/output/contacts_primary.xlsx
+++ b/output/contacts_primary.xlsx
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>9.486093510551769e+20</v>
+        <v>2.845828053165531e+21</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>1.169837587504811e+21</v>
+        <v>3.509512762514434e+21</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>9.482979058064404e+20</v>
+        <v>2.844893717419321e+21</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>9.482979058064404e+20</v>
+        <v>2.844893717419321e+21</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>9.482979058064404e+20</v>
+        <v>2.844893717419321e+21</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>9.482979058064404e+20</v>
+        <v>2.844893717419321e+21</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>1.167135884069465e+21</v>
+        <v>3.501407652208396e+21</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>1.167135884069465e+21</v>
+        <v>3.501407652208396e+21</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>1.095090459126906e+21</v>
+        <v>3.285271377380717e+21</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>9.492097295967378e+20</v>
+        <v>2.847629188790213e+21</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>9.491984736182225e+20</v>
+        <v>2.847595420854667e+21</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>1.170237839865603e+21</v>
+        <v>3.510713519596809e+21</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>196911</v>
+        <v>590733</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>9.492097295967394e+20</v>
+        <v>2.847629188790218e+21</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>1.167135884069465e+21</v>
+        <v>3.501407652208396e+21</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>9.482979058064404e+20</v>
+        <v>2.844893717419321e+21</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>9.482979058064404e+20</v>
+        <v>2.844893717419321e+21</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3563,7 +3563,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>9.482979058064404e+20</v>
+        <v>2.844893717419321e+21</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>9.492097295967394e+20</v>
+        <v>2.847629188790218e+21</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>9.491984736182225e+20</v>
+        <v>2.847595420854667e+21</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -4049,7 +4049,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>9.486093510551768e+20</v>
+        <v>2.84582805316553e+21</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4211,7 +4211,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>9.482979058064404e+20</v>
+        <v>2.844893717419321e+21</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>9.482979058064404e+20</v>
+        <v>2.844893717419321e+21</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4535,7 +4535,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>8.999674332408067e+20</v>
+        <v>2.69990229972242e+21</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>183735</v>
+        <v>551205</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>183735</v>
+        <v>551205</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>8.999674332408067e+20</v>
+        <v>2.69990229972242e+21</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>8.780536164874449e+20</v>
+        <v>2.634160849462334e+21</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5367,7 +5367,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>8.780536164874449e+20</v>
+        <v>2.634160849462334e+21</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>8.780536164874449e+20</v>
+        <v>2.634160849462334e+21</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>8.780536164874449e+20</v>
+        <v>2.634160849462334e+21</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5854,7 +5854,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>8.780536164874449e+20</v>
+        <v>2.634160849462334e+21</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -6016,7 +6016,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>1.169837587504811e+21</v>
+        <v>3.509512762514434e+21</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -6178,7 +6178,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>8.756633583012084e+20</v>
+        <v>2.626990074903625e+21</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6349,7 +6349,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>8.756633583008354e+20</v>
+        <v>2.626990074902506e+21</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6520,7 +6520,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>9.486093510555515e+20</v>
+        <v>2.845828053166654e+21</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>9.485980950770344e+20</v>
+        <v>2.845794285231104e+21</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>9.485980950770344e+20</v>
+        <v>2.845794285231104e+21</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>9.485980950770344e+20</v>
+        <v>2.845794285231104e+21</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -7176,7 +7176,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>9.482979058064404e+20</v>
+        <v>2.844893717419321e+21</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7338,7 +7338,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>1.095223876580503e+21</v>
+        <v>3.285671629741509e+21</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7500,7 +7500,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>1.167135884069465e+21</v>
+        <v>3.501407652208396e+21</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7662,7 +7662,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>9.482979058064404e+20</v>
+        <v>2.844893717419321e+21</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7824,7 +7824,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>9.486093510551768e+20</v>
+        <v>2.84582805316553e+21</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7986,7 +7986,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>8.999674332408067e+20</v>
+        <v>2.69990229972242e+21</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>8.999674332408067e+20</v>
+        <v>2.69990229972242e+21</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>8.999674332408067e+20</v>
+        <v>2.69990229972242e+21</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8472,7 +8472,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>8.781649355557756e+20</v>
+        <v>2.634494806667327e+21</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8634,7 +8634,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>8.781536795776428e+20</v>
+        <v>2.634461038732929e+21</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8796,7 +8796,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>8.781536795776428e+20</v>
+        <v>2.634461038732929e+21</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8958,7 +8958,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>8.780536164874449e+20</v>
+        <v>2.634160849462334e+21</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -9120,7 +9120,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>8.780536164874449e+20</v>
+        <v>2.634160849462334e+21</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -9282,7 +9282,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>8.756633583008354e+20</v>
+        <v>2.626990074902506e+21</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -9452,7 +9452,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>8.762524808638809e+20</v>
+        <v>2.628757442591642e+21</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9614,7 +9614,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>8.762858352272802e+20</v>
+        <v>2.628857505681841e+21</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9776,7 +9776,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>183735</v>
+        <v>551205</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9946,7 +9946,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>8.762637368423968e+20</v>
+        <v>2.62879121052719e+21</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -10118,7 +10118,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>183735</v>
+        <v>551205</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -10288,7 +10288,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>183735</v>
+        <v>551205</v>
       </c>
       <c r="AE60" t="n">
         <v>4</v>
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>8.997785630176197e+20</v>
+        <v>2.699335689052859e+21</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10629,7 +10629,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>183735</v>
+        <v>551205</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10802,7 +10802,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>183735</v>
+        <v>551205</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10975,7 +10975,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>183735</v>
+        <v>551205</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -11145,7 +11145,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>1.167135884069465e+21</v>
+        <v>3.501407652208396e+21</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -11307,7 +11307,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>8.999786892189497e+20</v>
+        <v>2.699936067656849e+21</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>8.999674332408067e+20</v>
+        <v>2.69990229972242e+21</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -11639,7 +11639,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>8.999674332408067e+20</v>
+        <v>2.69990229972242e+21</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>8.780536165188259e+20</v>
+        <v>2.634160849556478e+21</v>
       </c>
       <c r="AE69" t="n">
         <v>2</v>
@@ -11963,7 +11963,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>8.762858352272802e+20</v>
+        <v>2.628857505681841e+21</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -12125,7 +12125,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>1.167135884100846e+21</v>
+        <v>3.501407652302539e+21</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -12287,7 +12287,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>183735</v>
+        <v>551205</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -12457,7 +12457,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>9.483979688966385e+20</v>
+        <v>2.845193906689915e+21</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -12619,7 +12619,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>9.483979688966385e+20</v>
+        <v>2.845193906689915e+21</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12781,7 +12781,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>9.482979058064404e+20</v>
+        <v>2.844893717419321e+21</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -12943,7 +12943,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>9.482979058064404e+20</v>
+        <v>2.844893717419321e+21</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -13105,7 +13105,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>8.756521023226928e+20</v>
+        <v>2.626956306968079e+21</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>8.756521023226928e+20</v>
+        <v>2.626956306968079e+21</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -13429,7 +13429,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>9.483979688966385e+20</v>
+        <v>2.845193906689915e+21</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>

--- a/output/contacts_primary.xlsx
+++ b/output/contacts_primary.xlsx
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>2.845828053165531e+21</v>
+        <v>8.537484159496593e+21</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>3.509512762514434e+21</v>
+        <v>1.05285382875433e+22</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>2.844893717419321e+21</v>
+        <v>8.534681152257964e+21</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>2.844893717419321e+21</v>
+        <v>8.534681152257964e+21</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>2.844893717419321e+21</v>
+        <v>8.534681152257964e+21</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>2.844893717419321e+21</v>
+        <v>8.534681152257964e+21</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>3.501407652208396e+21</v>
+        <v>1.050422295662519e+22</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>3.501407652208396e+21</v>
+        <v>1.050422295662519e+22</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>3.285271377380717e+21</v>
+        <v>9.855814132142151e+21</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>2.847629188790213e+21</v>
+        <v>8.54288756637064e+21</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>2.847595420854667e+21</v>
+        <v>8.542786262564002e+21</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>3.510713519596809e+21</v>
+        <v>1.053214055879043e+22</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>590733</v>
+        <v>1772199</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>2.847629188790218e+21</v>
+        <v>8.542887566370655e+21</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>3.501407652208396e+21</v>
+        <v>1.050422295662519e+22</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>2.844893717419321e+21</v>
+        <v>8.534681152257964e+21</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>2.844893717419321e+21</v>
+        <v>8.534681152257964e+21</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3563,7 +3563,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>2.844893717419321e+21</v>
+        <v>8.534681152257964e+21</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>2.847629188790218e+21</v>
+        <v>8.542887566370655e+21</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>2.847595420854667e+21</v>
+        <v>8.542786262564002e+21</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -4049,7 +4049,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>2.84582805316553e+21</v>
+        <v>8.537484159496591e+21</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4211,7 +4211,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>2.844893717419321e+21</v>
+        <v>8.534681152257964e+21</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>2.844893717419321e+21</v>
+        <v>8.534681152257964e+21</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4535,7 +4535,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>2.69990229972242e+21</v>
+        <v>8.09970689916726e+21</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>551205</v>
+        <v>1653615</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>551205</v>
+        <v>1653615</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>2.69990229972242e+21</v>
+        <v>8.09970689916726e+21</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>2.634160849462334e+21</v>
+        <v>7.902482548387003e+21</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5367,7 +5367,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>2.634160849462334e+21</v>
+        <v>7.902482548387003e+21</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>2.634160849462334e+21</v>
+        <v>7.902482548387003e+21</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>2.634160849462334e+21</v>
+        <v>7.902482548387003e+21</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5854,7 +5854,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>2.634160849462334e+21</v>
+        <v>7.902482548387003e+21</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -6016,7 +6016,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>3.509512762514434e+21</v>
+        <v>1.05285382875433e+22</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -6178,7 +6178,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>2.626990074903625e+21</v>
+        <v>7.880970224710876e+21</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6349,7 +6349,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>2.626990074902506e+21</v>
+        <v>7.880970224707518e+21</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6520,7 +6520,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>2.845828053166654e+21</v>
+        <v>8.537484159499963e+21</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>2.845794285231104e+21</v>
+        <v>8.53738285569331e+21</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>2.845794285231104e+21</v>
+        <v>8.53738285569331e+21</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>2.845794285231104e+21</v>
+        <v>8.53738285569331e+21</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -7176,7 +7176,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>2.844893717419321e+21</v>
+        <v>8.534681152257964e+21</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7338,7 +7338,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>3.285671629741509e+21</v>
+        <v>9.857014889224526e+21</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7500,7 +7500,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>3.501407652208396e+21</v>
+        <v>1.050422295662519e+22</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7662,7 +7662,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>2.844893717419321e+21</v>
+        <v>8.534681152257964e+21</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7824,7 +7824,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>2.84582805316553e+21</v>
+        <v>8.537484159496591e+21</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7986,7 +7986,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>2.69990229972242e+21</v>
+        <v>8.09970689916726e+21</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>2.69990229972242e+21</v>
+        <v>8.09970689916726e+21</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>2.69990229972242e+21</v>
+        <v>8.09970689916726e+21</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8472,7 +8472,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>2.634494806667327e+21</v>
+        <v>7.90348442000198e+21</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8634,7 +8634,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>2.634461038732929e+21</v>
+        <v>7.903383116198786e+21</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8796,7 +8796,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>2.634461038732929e+21</v>
+        <v>7.903383116198786e+21</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8958,7 +8958,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>2.634160849462334e+21</v>
+        <v>7.902482548387003e+21</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -9120,7 +9120,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>2.634160849462334e+21</v>
+        <v>7.902482548387003e+21</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -9282,7 +9282,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>2.626990074902506e+21</v>
+        <v>7.880970224707518e+21</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -9452,7 +9452,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>2.628757442591642e+21</v>
+        <v>7.886272327774928e+21</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9614,7 +9614,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>2.628857505681841e+21</v>
+        <v>7.886572517045521e+21</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9776,7 +9776,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>551205</v>
+        <v>1653615</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9946,7 +9946,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>2.62879121052719e+21</v>
+        <v>7.886373631581571e+21</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -10118,7 +10118,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>551205</v>
+        <v>1653615</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -10288,7 +10288,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>551205</v>
+        <v>1653615</v>
       </c>
       <c r="AE60" t="n">
         <v>4</v>
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>2.699335689052859e+21</v>
+        <v>8.098007067158577e+21</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10629,7 +10629,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>551205</v>
+        <v>1653615</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10802,7 +10802,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>551205</v>
+        <v>1653615</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10975,7 +10975,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>551205</v>
+        <v>1653615</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -11145,7 +11145,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>3.501407652208396e+21</v>
+        <v>1.050422295662519e+22</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -11307,7 +11307,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>2.699936067656849e+21</v>
+        <v>8.099808202970546e+21</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>2.69990229972242e+21</v>
+        <v>8.09970689916726e+21</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -11639,7 +11639,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>2.69990229972242e+21</v>
+        <v>8.09970689916726e+21</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>2.634160849556478e+21</v>
+        <v>7.902482548669433e+21</v>
       </c>
       <c r="AE69" t="n">
         <v>2</v>
@@ -11963,7 +11963,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>2.628857505681841e+21</v>
+        <v>7.886572517045521e+21</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -12125,7 +12125,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>3.501407652302539e+21</v>
+        <v>1.050422295690762e+22</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -12287,7 +12287,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>551205</v>
+        <v>1653615</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -12457,7 +12457,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>2.845193906689915e+21</v>
+        <v>8.535581720069746e+21</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -12619,7 +12619,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>2.845193906689915e+21</v>
+        <v>8.535581720069746e+21</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12781,7 +12781,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>2.844893717419321e+21</v>
+        <v>8.534681152257964e+21</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -12943,7 +12943,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>2.844893717419321e+21</v>
+        <v>8.534681152257964e+21</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -13105,7 +13105,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>2.626956306968079e+21</v>
+        <v>7.880868920904236e+21</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>2.626956306968079e+21</v>
+        <v>7.880868920904236e+21</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -13429,7 +13429,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>2.845193906689915e+21</v>
+        <v>8.535581720069746e+21</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>

--- a/output/contacts_primary.xlsx
+++ b/output/contacts_primary.xlsx
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>8.537484159496593e+21</v>
+        <v>2.561245247848978e+22</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>1.05285382875433e+22</v>
+        <v>3.15856148626299e+22</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>8.534681152257964e+21</v>
+        <v>2.560404345677389e+22</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>8.534681152257964e+21</v>
+        <v>2.560404345677389e+22</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>8.534681152257964e+21</v>
+        <v>2.560404345677389e+22</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>8.534681152257964e+21</v>
+        <v>2.560404345677389e+22</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>1.050422295662519e+22</v>
+        <v>3.151266886987556e+22</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>1.050422295662519e+22</v>
+        <v>3.151266886987556e+22</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>9.855814132142151e+21</v>
+        <v>2.956744239642645e+22</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>8.54288756637064e+21</v>
+        <v>2.562866269911192e+22</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>8.542786262564002e+21</v>
+        <v>2.562835878769201e+22</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>1.053214055879043e+22</v>
+        <v>3.159642167637128e+22</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>1772199</v>
+        <v>5316597</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>8.542887566370655e+21</v>
+        <v>2.562866269911196e+22</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>1.050422295662519e+22</v>
+        <v>3.151266886987556e+22</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>8.534681152257964e+21</v>
+        <v>2.560404345677389e+22</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>8.534681152257964e+21</v>
+        <v>2.560404345677389e+22</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3563,7 +3563,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>8.534681152257964e+21</v>
+        <v>2.560404345677389e+22</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>8.542887566370655e+21</v>
+        <v>2.562866269911196e+22</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>8.542786262564002e+21</v>
+        <v>2.562835878769201e+22</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -4049,7 +4049,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>8.537484159496591e+21</v>
+        <v>2.561245247848977e+22</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4211,7 +4211,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>8.534681152257964e+21</v>
+        <v>2.560404345677389e+22</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>8.534681152257964e+21</v>
+        <v>2.560404345677389e+22</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4535,7 +4535,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>8.09970689916726e+21</v>
+        <v>2.429912069750178e+22</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>1653615</v>
+        <v>4960845</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>1653615</v>
+        <v>4960845</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>8.09970689916726e+21</v>
+        <v>2.429912069750178e+22</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>7.902482548387003e+21</v>
+        <v>2.370744764516101e+22</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5367,7 +5367,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>7.902482548387003e+21</v>
+        <v>2.370744764516101e+22</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>7.902482548387003e+21</v>
+        <v>2.370744764516101e+22</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>7.902482548387003e+21</v>
+        <v>2.370744764516101e+22</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5854,7 +5854,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>7.902482548387003e+21</v>
+        <v>2.370744764516101e+22</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -6016,7 +6016,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>1.05285382875433e+22</v>
+        <v>3.15856148626299e+22</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -6178,7 +6178,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>7.880970224710876e+21</v>
+        <v>2.364291067413263e+22</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6349,7 +6349,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>7.880970224707518e+21</v>
+        <v>2.364291067412256e+22</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6520,7 +6520,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>8.537484159499963e+21</v>
+        <v>2.561245247849989e+22</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>8.53738285569331e+21</v>
+        <v>2.561214856707993e+22</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>8.53738285569331e+21</v>
+        <v>2.561214856707993e+22</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>8.53738285569331e+21</v>
+        <v>2.561214856707993e+22</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -7176,7 +7176,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>8.534681152257964e+21</v>
+        <v>2.560404345677389e+22</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7338,7 +7338,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>9.857014889224526e+21</v>
+        <v>2.957104466767358e+22</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7500,7 +7500,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>1.050422295662519e+22</v>
+        <v>3.151266886987556e+22</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7662,7 +7662,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>8.534681152257964e+21</v>
+        <v>2.560404345677389e+22</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7824,7 +7824,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>8.537484159496591e+21</v>
+        <v>2.561245247848977e+22</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7986,7 +7986,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>8.09970689916726e+21</v>
+        <v>2.429912069750178e+22</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>8.09970689916726e+21</v>
+        <v>2.429912069750178e+22</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>8.09970689916726e+21</v>
+        <v>2.429912069750178e+22</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8472,7 +8472,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>7.90348442000198e+21</v>
+        <v>2.371045326000594e+22</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8634,7 +8634,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>7.903383116198786e+21</v>
+        <v>2.371014934859636e+22</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8796,7 +8796,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>7.903383116198786e+21</v>
+        <v>2.371014934859636e+22</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8958,7 +8958,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>7.902482548387003e+21</v>
+        <v>2.370744764516101e+22</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -9120,7 +9120,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>7.902482548387003e+21</v>
+        <v>2.370744764516101e+22</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -9282,7 +9282,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>7.880970224707518e+21</v>
+        <v>2.364291067412256e+22</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -9452,7 +9452,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>7.886272327774928e+21</v>
+        <v>2.365881698332478e+22</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9614,7 +9614,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>7.886572517045521e+21</v>
+        <v>2.365971755113657e+22</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9776,7 +9776,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>1653615</v>
+        <v>4960845</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9946,7 +9946,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>7.886373631581571e+21</v>
+        <v>2.365912089474472e+22</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -10118,7 +10118,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>1653615</v>
+        <v>4960845</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -10288,7 +10288,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>1653615</v>
+        <v>4960845</v>
       </c>
       <c r="AE60" t="n">
         <v>4</v>
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>8.098007067158577e+21</v>
+        <v>2.429402120147573e+22</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10629,7 +10629,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>1653615</v>
+        <v>4960845</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10802,7 +10802,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>1653615</v>
+        <v>4960845</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10975,7 +10975,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>1653615</v>
+        <v>4960845</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -11145,7 +11145,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>1.050422295662519e+22</v>
+        <v>3.151266886987556e+22</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -11307,7 +11307,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>8.099808202970546e+21</v>
+        <v>2.429942460891164e+22</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>8.09970689916726e+21</v>
+        <v>2.429912069750178e+22</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -11639,7 +11639,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>8.09970689916726e+21</v>
+        <v>2.429912069750178e+22</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>7.902482548669433e+21</v>
+        <v>2.37074476460083e+22</v>
       </c>
       <c r="AE69" t="n">
         <v>2</v>
@@ -11963,7 +11963,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>7.886572517045521e+21</v>
+        <v>2.365971755113657e+22</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -12125,7 +12125,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>1.050422295690762e+22</v>
+        <v>3.151266887072285e+22</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -12287,7 +12287,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>1653615</v>
+        <v>4960845</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -12457,7 +12457,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>8.535581720069746e+21</v>
+        <v>2.560674516020924e+22</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -12619,7 +12619,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>8.535581720069746e+21</v>
+        <v>2.560674516020924e+22</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12781,7 +12781,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>8.534681152257964e+21</v>
+        <v>2.560404345677389e+22</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -12943,7 +12943,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>8.534681152257964e+21</v>
+        <v>2.560404345677389e+22</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -13105,7 +13105,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>7.880868920904236e+21</v>
+        <v>2.364260676271271e+22</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>7.880868920904236e+21</v>
+        <v>2.364260676271271e+22</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -13429,7 +13429,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>8.535581720069746e+21</v>
+        <v>2.560674516020924e+22</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
